--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{219BB067-43D5-5C4C-BE1B-B612562108A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D50079E1-18E7-E743-8053-895205BE371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="27040" windowHeight="16880" tabRatio="702" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="27040" windowHeight="16880" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="181">
   <si>
     <t>%FeT</t>
   </si>
@@ -851,6 +851,42 @@
   <si>
     <t>Embarque Sinter</t>
   </si>
+  <si>
+    <t>SF CRISTALES</t>
+  </si>
+  <si>
+    <t>SF CARO</t>
+  </si>
+  <si>
+    <t>SF ALGARROBO</t>
+  </si>
+  <si>
+    <t>GR ALGARROBO</t>
+  </si>
+  <si>
+    <t>GR CRISTALES</t>
+  </si>
+  <si>
+    <t>GR PLEITO</t>
+  </si>
+  <si>
+    <t>SF APC</t>
+  </si>
+  <si>
+    <t>Recep APC</t>
+  </si>
+  <si>
+    <t>Recep CRISTALES</t>
+  </si>
+  <si>
+    <t>Recep CARO</t>
+  </si>
+  <si>
+    <t>Recep ALGARROBO</t>
+  </si>
+  <si>
+    <t>Recep PLEITO</t>
+  </si>
 </sst>
 </file>
 
@@ -865,7 +901,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
     <numFmt numFmtId="169" formatCode="#,##0.0000000_ ;\-#,##0.0000000\ "/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1793,7 +1829,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="294">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2113,9 +2149,6 @@
     <xf numFmtId="3" fontId="17" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2236,6 +2269,22 @@
     <xf numFmtId="9" fontId="20" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2255,7 +2304,52 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2270,50 +2364,113 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2399,32 +2556,8 @@
     <xf numFmtId="0" fontId="18" fillId="8" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2435,91 +2568,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Millares 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -16491,9 +16542,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -16531,7 +16582,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -16637,7 +16688,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -16779,7 +16830,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -16788,7 +16839,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AT177"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1" outlineLevel="1"/>
     <col min="2" max="2" width="31.1640625" customWidth="1" outlineLevel="1"/>
@@ -16814,7 +16865,7 @@
     <col min="67" max="67" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46">
       <c r="A1" s="134">
         <v>88507</v>
       </c>
@@ -16835,7 +16886,7 @@
       <c r="K1" s="134"/>
       <c r="L1" s="134"/>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:46">
       <c r="A2" s="134">
         <v>0</v>
       </c>
@@ -16856,7 +16907,7 @@
       <c r="K2" s="134"/>
       <c r="L2" s="134"/>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:46">
       <c r="A3" s="134">
         <v>22063</v>
       </c>
@@ -16910,7 +16961,7 @@
       <c r="AR3" s="92"/>
       <c r="AS3" s="92"/>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:46">
       <c r="A4" s="134">
         <v>66444</v>
       </c>
@@ -16931,7 +16982,7 @@
       <c r="K4" s="134"/>
       <c r="L4" s="134"/>
     </row>
-    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:46">
       <c r="A5" s="134">
         <v>43180</v>
       </c>
@@ -16952,7 +17003,7 @@
       <c r="K5" s="134"/>
       <c r="L5" s="134"/>
     </row>
-    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:46">
       <c r="A6" s="134">
         <v>-42218</v>
       </c>
@@ -16973,7 +17024,7 @@
       <c r="K6" s="134"/>
       <c r="L6" s="134"/>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:46">
       <c r="A7" s="134">
         <v>151419</v>
       </c>
@@ -16994,7 +17045,7 @@
       <c r="K7" s="134"/>
       <c r="L7" s="134"/>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:46">
       <c r="A8" s="134">
         <v>0</v>
       </c>
@@ -17015,7 +17066,7 @@
       <c r="K8" s="134"/>
       <c r="L8" s="134"/>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:46">
       <c r="A9" s="134">
         <v>31344</v>
       </c>
@@ -17036,7 +17087,7 @@
       <c r="K9" s="134"/>
       <c r="L9" s="134"/>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:46">
       <c r="A10" s="134">
         <v>9611</v>
       </c>
@@ -17058,7 +17109,7 @@
       <c r="L10" s="134"/>
       <c r="AT10" s="2"/>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:46">
       <c r="A11" s="134">
         <v>56684</v>
       </c>
@@ -17079,7 +17130,7 @@
       <c r="K11" s="134"/>
       <c r="L11" s="134"/>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:46">
       <c r="A12" s="134">
         <v>52614</v>
       </c>
@@ -17100,7 +17151,7 @@
       <c r="K12" s="134"/>
       <c r="L12" s="134"/>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:46">
       <c r="A13" s="134">
         <v>28383</v>
       </c>
@@ -17121,7 +17172,7 @@
       <c r="K13" s="134"/>
       <c r="L13" s="134"/>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:46">
       <c r="A14" s="134">
         <v>4463</v>
       </c>
@@ -17142,7 +17193,7 @@
       <c r="K14" s="134"/>
       <c r="L14" s="134"/>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:46">
       <c r="A15" s="134">
         <v>104882</v>
       </c>
@@ -17163,7 +17214,7 @@
       <c r="K15" s="134"/>
       <c r="L15" s="134"/>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:46">
       <c r="A16" s="134">
         <v>45670</v>
       </c>
@@ -17185,7 +17236,7 @@
       <c r="L16" s="134"/>
       <c r="M16" s="122"/>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32">
       <c r="A17" s="134">
         <v>132791</v>
       </c>
@@ -17207,7 +17258,7 @@
       <c r="L17" s="134"/>
       <c r="M17" s="122"/>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32">
       <c r="A18" s="134">
         <v>2702</v>
       </c>
@@ -17229,7 +17280,7 @@
       <c r="L18" s="134"/>
       <c r="M18" s="122"/>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32">
       <c r="A19" s="134">
         <v>0</v>
       </c>
@@ -17251,7 +17302,7 @@
       <c r="L19" s="134"/>
       <c r="M19" s="122"/>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32">
       <c r="A20" s="134">
         <v>129475</v>
       </c>
@@ -17273,7 +17324,7 @@
       <c r="L20" s="134"/>
       <c r="M20" s="122"/>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32">
       <c r="A21" s="134">
         <v>0</v>
       </c>
@@ -17295,7 +17346,7 @@
       <c r="L21" s="134"/>
       <c r="M21" s="122"/>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32">
       <c r="A22" s="134">
         <v>129475</v>
       </c>
@@ -17317,7 +17368,7 @@
       <c r="L22" s="134"/>
       <c r="M22" s="122"/>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32">
       <c r="A23" s="134">
         <v>26081</v>
       </c>
@@ -17339,7 +17390,7 @@
       <c r="L23" s="134"/>
       <c r="M23" s="123"/>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32">
       <c r="A24" s="134">
         <v>104386</v>
       </c>
@@ -17364,7 +17415,7 @@
       <c r="AE24" s="5"/>
       <c r="AF24" s="5"/>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32">
       <c r="A25" s="134">
         <v>0</v>
       </c>
@@ -17389,7 +17440,7 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32">
       <c r="A26" s="134">
         <v>0</v>
       </c>
@@ -17414,7 +17465,7 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32">
       <c r="A27" s="134">
         <v>0</v>
       </c>
@@ -17439,7 +17490,7 @@
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32">
       <c r="A28" s="134">
         <v>0</v>
       </c>
@@ -17464,7 +17515,7 @@
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32">
       <c r="A29" s="134">
         <v>0</v>
       </c>
@@ -17489,7 +17540,7 @@
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32">
       <c r="A30" s="134">
         <v>0</v>
       </c>
@@ -17514,7 +17565,7 @@
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32">
       <c r="A31" s="134">
         <v>28070</v>
       </c>
@@ -17539,7 +17590,7 @@
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32">
       <c r="A32" s="134">
         <v>18351</v>
       </c>
@@ -17564,7 +17615,7 @@
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32">
       <c r="A33" s="134">
         <v>5360</v>
       </c>
@@ -17589,7 +17640,7 @@
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32">
       <c r="A34" s="134">
         <v>6394</v>
       </c>
@@ -17614,7 +17665,7 @@
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32">
       <c r="A35" s="134">
         <v>0</v>
       </c>
@@ -17639,7 +17690,7 @@
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32">
       <c r="A36" s="134">
         <v>6394</v>
       </c>
@@ -17664,7 +17715,7 @@
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32">
       <c r="A37" s="134">
         <v>0</v>
       </c>
@@ -17689,7 +17740,7 @@
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32">
       <c r="A38" s="134">
         <v>0</v>
       </c>
@@ -17714,7 +17765,7 @@
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32">
       <c r="A39" s="134">
         <v>0</v>
       </c>
@@ -17739,7 +17790,7 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32">
       <c r="A40" s="134">
         <v>0</v>
       </c>
@@ -17764,7 +17815,7 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32">
       <c r="A41" s="134">
         <v>0</v>
       </c>
@@ -17789,7 +17840,7 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:32">
       <c r="A42" s="134">
         <v>0</v>
       </c>
@@ -17814,7 +17865,7 @@
       <c r="AE42" s="3"/>
       <c r="AF42" s="3"/>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:32">
       <c r="A43" s="134">
         <v>0</v>
       </c>
@@ -17839,7 +17890,7 @@
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:32">
       <c r="A44" s="134">
         <v>0</v>
       </c>
@@ -17864,7 +17915,7 @@
       <c r="AE44" s="3"/>
       <c r="AF44" s="3"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:32">
       <c r="A45" s="134">
         <v>0</v>
       </c>
@@ -17889,7 +17940,7 @@
       <c r="AE45" s="3"/>
       <c r="AF45" s="3"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32">
       <c r="A46" s="134">
         <v>0</v>
       </c>
@@ -17914,7 +17965,7 @@
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32">
       <c r="A47" s="134">
         <v>0</v>
       </c>
@@ -17939,7 +17990,7 @@
       <c r="AE47" s="3"/>
       <c r="AF47" s="3"/>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32">
       <c r="A48" s="134">
         <v>0</v>
       </c>
@@ -17964,7 +18015,7 @@
       <c r="AE48" s="3"/>
       <c r="AF48" s="3"/>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32">
       <c r="A49" s="134">
         <v>0</v>
       </c>
@@ -17989,7 +18040,7 @@
       <c r="AE49" s="3"/>
       <c r="AF49" s="3"/>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32">
       <c r="A50" s="134">
         <v>0</v>
       </c>
@@ -18014,7 +18065,7 @@
       <c r="AE50" s="3"/>
       <c r="AF50" s="3"/>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32">
       <c r="A51" s="134">
         <v>0</v>
       </c>
@@ -18039,7 +18090,7 @@
       <c r="AE51" s="3"/>
       <c r="AF51" s="3"/>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:32">
       <c r="A52" s="134">
         <v>77372</v>
       </c>
@@ -18064,7 +18115,7 @@
       <c r="AE52" s="3"/>
       <c r="AF52" s="3"/>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:32">
       <c r="A53" s="134">
         <v>77372</v>
       </c>
@@ -18089,7 +18140,7 @@
       <c r="AE53" s="3"/>
       <c r="AF53" s="3"/>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:32">
       <c r="A54" s="134">
         <v>4403</v>
       </c>
@@ -18114,7 +18165,7 @@
       <c r="AE54" s="3"/>
       <c r="AF54" s="3"/>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:32">
       <c r="A55" s="134">
         <v>127</v>
       </c>
@@ -18139,7 +18190,7 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:32">
       <c r="A56" s="134"/>
       <c r="B56" s="134"/>
       <c r="C56" s="134"/>
@@ -18154,7 +18205,7 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:32">
       <c r="A57" s="134"/>
       <c r="B57" s="134"/>
       <c r="C57" s="134"/>
@@ -18169,7 +18220,7 @@
       <c r="AE57" s="3"/>
       <c r="AF57" s="3"/>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:32">
       <c r="A58" s="134"/>
       <c r="B58" s="134"/>
       <c r="C58" s="134"/>
@@ -18184,7 +18235,7 @@
       <c r="AE58" s="3"/>
       <c r="AF58" s="3"/>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:32">
       <c r="A59" s="134"/>
       <c r="B59" s="134"/>
       <c r="C59" s="134"/>
@@ -18199,27 +18250,27 @@
       <c r="AE59" s="3"/>
       <c r="AF59" s="3"/>
     </row>
-    <row r="60" spans="1:32" ht="19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" ht="19">
       <c r="A60" s="134"/>
       <c r="B60" s="134"/>
       <c r="C60" s="134"/>
       <c r="D60" s="118"/>
       <c r="E60" s="118"/>
       <c r="F60" s="118"/>
-      <c r="J60" s="198" t="s">
+      <c r="J60" s="203" t="s">
         <v>68</v>
       </c>
-      <c r="K60" s="198"/>
-      <c r="L60" s="198"/>
+      <c r="K60" s="203"/>
+      <c r="L60" s="203"/>
       <c r="M60" s="122"/>
-      <c r="N60" s="199"/>
-      <c r="O60" s="199"/>
+      <c r="N60" s="204"/>
+      <c r="O60" s="204"/>
       <c r="R60" s="98"/>
       <c r="AD60" s="5"/>
       <c r="AE60" s="3"/>
       <c r="AF60" s="3"/>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:32">
       <c r="A61" s="134"/>
       <c r="B61" s="134"/>
       <c r="C61" s="134"/>
@@ -18246,7 +18297,7 @@
       <c r="AE61" s="3"/>
       <c r="AF61" s="3"/>
     </row>
-    <row r="62" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:32" ht="16">
       <c r="A62" s="134"/>
       <c r="B62" s="134"/>
       <c r="C62" s="134"/>
@@ -18281,7 +18332,7 @@
       <c r="AE62" s="3"/>
       <c r="AF62" s="3"/>
     </row>
-    <row r="63" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:32" ht="16">
       <c r="A63" s="134"/>
       <c r="B63" s="134"/>
       <c r="C63" s="134"/>
@@ -18316,7 +18367,7 @@
       <c r="AE63" s="3"/>
       <c r="AF63" s="3"/>
     </row>
-    <row r="64" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:32" ht="16">
       <c r="A64" s="134"/>
       <c r="B64" s="134"/>
       <c r="C64" s="134"/>
@@ -18351,15 +18402,15 @@
       <c r="AE64" s="3"/>
       <c r="AF64" s="3"/>
     </row>
-    <row r="65" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:32" ht="16">
       <c r="A65" s="134"/>
       <c r="B65" s="134"/>
       <c r="C65" s="134"/>
       <c r="D65" s="118"/>
       <c r="E65" s="118"/>
       <c r="F65" s="118"/>
-      <c r="G65" s="164"/>
-      <c r="H65" s="165"/>
+      <c r="G65" s="163"/>
+      <c r="H65" s="164"/>
       <c r="I65" s="134" t="s">
         <v>17</v>
       </c>
@@ -18388,15 +18439,15 @@
       <c r="AE65" s="3"/>
       <c r="AF65" s="3"/>
     </row>
-    <row r="66" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:32" ht="16">
       <c r="A66" s="118"/>
       <c r="B66" s="118"/>
       <c r="C66" s="118"/>
       <c r="D66" s="118"/>
       <c r="E66" s="118"/>
       <c r="F66" s="118"/>
-      <c r="G66" s="164"/>
-      <c r="H66" s="165"/>
+      <c r="G66" s="163"/>
+      <c r="H66" s="164"/>
       <c r="I66" s="134" t="s">
         <v>18</v>
       </c>
@@ -18425,15 +18476,15 @@
       <c r="AE66" s="3"/>
       <c r="AF66" s="3"/>
     </row>
-    <row r="67" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:32" ht="16">
       <c r="A67" s="120"/>
       <c r="B67" s="120"/>
       <c r="C67" s="119"/>
       <c r="D67" s="118"/>
       <c r="E67" s="118"/>
       <c r="F67" s="121"/>
-      <c r="G67" s="164"/>
-      <c r="H67" s="165"/>
+      <c r="G67" s="163"/>
+      <c r="H67" s="164"/>
       <c r="I67" s="134" t="s">
         <v>19</v>
       </c>
@@ -18462,15 +18513,15 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
     </row>
-    <row r="68" spans="1:32" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:32" ht="16">
       <c r="A68" s="118"/>
       <c r="B68" s="118"/>
       <c r="C68" s="118"/>
       <c r="D68" s="118"/>
       <c r="E68" s="118"/>
       <c r="F68" s="118"/>
-      <c r="G68" s="164"/>
-      <c r="H68" s="165"/>
+      <c r="G68" s="163"/>
+      <c r="H68" s="164"/>
       <c r="I68" s="134" t="s">
         <v>20</v>
       </c>
@@ -18499,15 +18550,15 @@
       <c r="AE68" s="3"/>
       <c r="AF68" s="3"/>
     </row>
-    <row r="69" spans="1:32" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:32" ht="19" customHeight="1">
       <c r="A69" s="118"/>
       <c r="B69" s="118"/>
       <c r="C69" s="118"/>
       <c r="D69" s="118"/>
       <c r="E69" s="118"/>
       <c r="F69" s="118"/>
-      <c r="G69" s="164"/>
-      <c r="H69" s="165"/>
+      <c r="G69" s="163"/>
+      <c r="H69" s="164"/>
       <c r="I69" s="134" t="s">
         <v>21</v>
       </c>
@@ -18536,15 +18587,15 @@
       <c r="AE69" s="3"/>
       <c r="AF69" s="3"/>
     </row>
-    <row r="70" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" s="160"/>
-      <c r="B70" s="160"/>
-      <c r="C70" s="160"/>
-      <c r="D70" s="160"/>
-      <c r="E70" s="160"/>
-      <c r="F70" s="160"/>
-      <c r="G70" s="164"/>
-      <c r="H70" s="165"/>
+    <row r="70" spans="1:32" ht="16">
+      <c r="A70" s="159"/>
+      <c r="B70" s="159"/>
+      <c r="C70" s="159"/>
+      <c r="D70" s="159"/>
+      <c r="E70" s="159"/>
+      <c r="F70" s="159"/>
+      <c r="G70" s="163"/>
+      <c r="H70" s="164"/>
       <c r="I70" s="134" t="s">
         <v>22</v>
       </c>
@@ -18573,15 +18624,15 @@
       <c r="AE70" s="3"/>
       <c r="AF70" s="3"/>
     </row>
-    <row r="71" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="160"/>
-      <c r="B71" s="160"/>
-      <c r="C71" s="160"/>
-      <c r="D71" s="160"/>
-      <c r="E71" s="160"/>
-      <c r="F71" s="160"/>
-      <c r="G71" s="163"/>
-      <c r="H71" s="165"/>
+    <row r="71" spans="1:32" ht="16">
+      <c r="A71" s="159"/>
+      <c r="B71" s="159"/>
+      <c r="C71" s="159"/>
+      <c r="D71" s="159"/>
+      <c r="E71" s="159"/>
+      <c r="F71" s="159"/>
+      <c r="G71" s="162"/>
+      <c r="H71" s="164"/>
       <c r="I71" s="134" t="s">
         <v>23</v>
       </c>
@@ -18610,15 +18661,15 @@
       <c r="AE71" s="3"/>
       <c r="AF71" s="3"/>
     </row>
-    <row r="72" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="160"/>
-      <c r="B72" s="160"/>
-      <c r="C72" s="160"/>
-      <c r="D72" s="160"/>
-      <c r="E72" s="160"/>
-      <c r="F72" s="160"/>
-      <c r="G72" s="164"/>
-      <c r="H72" s="165"/>
+    <row r="72" spans="1:32" ht="16">
+      <c r="A72" s="159"/>
+      <c r="B72" s="159"/>
+      <c r="C72" s="159"/>
+      <c r="D72" s="159"/>
+      <c r="E72" s="159"/>
+      <c r="F72" s="159"/>
+      <c r="G72" s="163"/>
+      <c r="H72" s="164"/>
       <c r="I72" s="134" t="s">
         <v>24</v>
       </c>
@@ -18647,15 +18698,15 @@
       <c r="AE72" s="3"/>
       <c r="AF72" s="3"/>
     </row>
-    <row r="73" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A73" s="160"/>
-      <c r="B73" s="160"/>
-      <c r="C73" s="160"/>
-      <c r="D73" s="160"/>
-      <c r="E73" s="160"/>
-      <c r="F73" s="160"/>
-      <c r="G73" s="164"/>
-      <c r="H73" s="165"/>
+    <row r="73" spans="1:32" ht="16">
+      <c r="A73" s="159"/>
+      <c r="B73" s="159"/>
+      <c r="C73" s="159"/>
+      <c r="D73" s="159"/>
+      <c r="E73" s="159"/>
+      <c r="F73" s="159"/>
+      <c r="G73" s="163"/>
+      <c r="H73" s="164"/>
       <c r="I73" s="134" t="s">
         <v>25</v>
       </c>
@@ -18684,15 +18735,15 @@
       <c r="AE73" s="3"/>
       <c r="AF73" s="3"/>
     </row>
-    <row r="74" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" s="160"/>
-      <c r="B74" s="160"/>
-      <c r="C74" s="160"/>
-      <c r="D74" s="160"/>
-      <c r="E74" s="160"/>
-      <c r="F74" s="160"/>
-      <c r="G74" s="164"/>
-      <c r="H74" s="165"/>
+    <row r="74" spans="1:32" ht="16">
+      <c r="A74" s="159"/>
+      <c r="B74" s="159"/>
+      <c r="C74" s="159"/>
+      <c r="D74" s="159"/>
+      <c r="E74" s="159"/>
+      <c r="F74" s="159"/>
+      <c r="G74" s="163"/>
+      <c r="H74" s="164"/>
       <c r="I74" s="134" t="s">
         <v>2</v>
       </c>
@@ -18721,15 +18772,15 @@
       <c r="AE74" s="3"/>
       <c r="AF74" s="3"/>
     </row>
-    <row r="75" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" s="163"/>
-      <c r="B75" s="163"/>
-      <c r="C75" s="161"/>
-      <c r="D75" s="160"/>
-      <c r="E75" s="160"/>
-      <c r="F75" s="166"/>
-      <c r="G75" s="164"/>
-      <c r="H75" s="165"/>
+    <row r="75" spans="1:32" ht="16">
+      <c r="A75" s="162"/>
+      <c r="B75" s="162"/>
+      <c r="C75" s="160"/>
+      <c r="D75" s="159"/>
+      <c r="E75" s="159"/>
+      <c r="F75" s="165"/>
+      <c r="G75" s="163"/>
+      <c r="H75" s="164"/>
       <c r="I75" s="134" t="s">
         <v>26</v>
       </c>
@@ -18758,15 +18809,15 @@
       <c r="AE75" s="3"/>
       <c r="AF75" s="3"/>
     </row>
-    <row r="76" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" s="160"/>
-      <c r="B76" s="160"/>
-      <c r="C76" s="160"/>
-      <c r="D76" s="160"/>
-      <c r="E76" s="160"/>
-      <c r="F76" s="160"/>
-      <c r="G76" s="164"/>
-      <c r="H76" s="165"/>
+    <row r="76" spans="1:32" ht="16">
+      <c r="A76" s="159"/>
+      <c r="B76" s="159"/>
+      <c r="C76" s="159"/>
+      <c r="D76" s="159"/>
+      <c r="E76" s="159"/>
+      <c r="F76" s="159"/>
+      <c r="G76" s="163"/>
+      <c r="H76" s="164"/>
       <c r="I76" s="134" t="s">
         <v>27</v>
       </c>
@@ -18795,15 +18846,15 @@
       <c r="AE76" s="3"/>
       <c r="AF76" s="3"/>
     </row>
-    <row r="77" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" s="160"/>
-      <c r="B77" s="160"/>
-      <c r="C77" s="160"/>
-      <c r="D77" s="160"/>
-      <c r="E77" s="160"/>
-      <c r="F77" s="160"/>
-      <c r="G77" s="164"/>
-      <c r="H77" s="165"/>
+    <row r="77" spans="1:32" ht="16">
+      <c r="A77" s="159"/>
+      <c r="B77" s="159"/>
+      <c r="C77" s="159"/>
+      <c r="D77" s="159"/>
+      <c r="E77" s="159"/>
+      <c r="F77" s="159"/>
+      <c r="G77" s="163"/>
+      <c r="H77" s="164"/>
       <c r="I77" s="134" t="s">
         <v>28</v>
       </c>
@@ -18832,15 +18883,15 @@
       <c r="AE77" s="3"/>
       <c r="AF77" s="3"/>
     </row>
-    <row r="78" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="160"/>
-      <c r="B78" s="160"/>
-      <c r="C78" s="160"/>
-      <c r="D78" s="160"/>
-      <c r="E78" s="160"/>
-      <c r="F78" s="160"/>
-      <c r="G78" s="163"/>
-      <c r="H78" s="165"/>
+    <row r="78" spans="1:32" ht="16">
+      <c r="A78" s="159"/>
+      <c r="B78" s="159"/>
+      <c r="C78" s="159"/>
+      <c r="D78" s="159"/>
+      <c r="E78" s="159"/>
+      <c r="F78" s="159"/>
+      <c r="G78" s="162"/>
+      <c r="H78" s="164"/>
       <c r="I78" s="134" t="s">
         <v>29</v>
       </c>
@@ -18869,15 +18920,15 @@
       <c r="AE78" s="3"/>
       <c r="AF78" s="3"/>
     </row>
-    <row r="79" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A79" s="163"/>
-      <c r="B79" s="163"/>
-      <c r="C79" s="161"/>
-      <c r="D79" s="160"/>
-      <c r="E79" s="160"/>
-      <c r="F79" s="166"/>
-      <c r="G79" s="164"/>
-      <c r="H79" s="165"/>
+    <row r="79" spans="1:32" ht="16">
+      <c r="A79" s="162"/>
+      <c r="B79" s="162"/>
+      <c r="C79" s="160"/>
+      <c r="D79" s="159"/>
+      <c r="E79" s="159"/>
+      <c r="F79" s="165"/>
+      <c r="G79" s="163"/>
+      <c r="H79" s="164"/>
       <c r="I79" s="134" t="s">
         <v>30</v>
       </c>
@@ -18904,15 +18955,15 @@
       <c r="AE79" s="3"/>
       <c r="AF79" s="3"/>
     </row>
-    <row r="80" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A80" s="160"/>
-      <c r="B80" s="160"/>
-      <c r="C80" s="160"/>
-      <c r="D80" s="160"/>
-      <c r="E80" s="160"/>
-      <c r="F80" s="160"/>
-      <c r="G80" s="163"/>
-      <c r="H80" s="165"/>
+    <row r="80" spans="1:32" ht="16">
+      <c r="A80" s="159"/>
+      <c r="B80" s="159"/>
+      <c r="C80" s="159"/>
+      <c r="D80" s="159"/>
+      <c r="E80" s="159"/>
+      <c r="F80" s="159"/>
+      <c r="G80" s="162"/>
+      <c r="H80" s="164"/>
       <c r="I80" s="134" t="s">
         <v>31</v>
       </c>
@@ -18936,15 +18987,15 @@
       <c r="R80" s="1"/>
       <c r="S80" s="96"/>
     </row>
-    <row r="81" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="163"/>
-      <c r="B81" s="163"/>
-      <c r="C81" s="161"/>
-      <c r="D81" s="160"/>
-      <c r="E81" s="160"/>
-      <c r="F81" s="166"/>
-      <c r="G81" s="164"/>
-      <c r="H81" s="165"/>
+    <row r="81" spans="1:19" ht="16">
+      <c r="A81" s="162"/>
+      <c r="B81" s="162"/>
+      <c r="C81" s="160"/>
+      <c r="D81" s="159"/>
+      <c r="E81" s="159"/>
+      <c r="F81" s="165"/>
+      <c r="G81" s="163"/>
+      <c r="H81" s="164"/>
       <c r="I81" s="134" t="s">
         <v>32</v>
       </c>
@@ -18968,15 +19019,15 @@
       <c r="R81" s="1"/>
       <c r="S81" s="96"/>
     </row>
-    <row r="82" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="160"/>
-      <c r="B82" s="160"/>
-      <c r="C82" s="160"/>
-      <c r="D82" s="160"/>
-      <c r="E82" s="160"/>
-      <c r="F82" s="160"/>
-      <c r="G82" s="164"/>
-      <c r="H82" s="165"/>
+    <row r="82" spans="1:19" ht="16">
+      <c r="A82" s="159"/>
+      <c r="B82" s="159"/>
+      <c r="C82" s="159"/>
+      <c r="D82" s="159"/>
+      <c r="E82" s="159"/>
+      <c r="F82" s="159"/>
+      <c r="G82" s="163"/>
+      <c r="H82" s="164"/>
       <c r="I82" s="134" t="s">
         <v>33</v>
       </c>
@@ -19000,15 +19051,15 @@
       <c r="R82" s="1"/>
       <c r="S82" s="96"/>
     </row>
-    <row r="83" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="160"/>
-      <c r="B83" s="160"/>
-      <c r="C83" s="160"/>
-      <c r="D83" s="160"/>
-      <c r="E83" s="160"/>
-      <c r="F83" s="160"/>
-      <c r="G83" s="164"/>
-      <c r="H83" s="165"/>
+    <row r="83" spans="1:19" ht="16">
+      <c r="A83" s="159"/>
+      <c r="B83" s="159"/>
+      <c r="C83" s="159"/>
+      <c r="D83" s="159"/>
+      <c r="E83" s="159"/>
+      <c r="F83" s="159"/>
+      <c r="G83" s="163"/>
+      <c r="H83" s="164"/>
       <c r="I83" s="134" t="s">
         <v>35</v>
       </c>
@@ -19032,15 +19083,15 @@
       <c r="R83" s="1"/>
       <c r="S83" s="96"/>
     </row>
-    <row r="84" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="160"/>
-      <c r="B84" s="160"/>
-      <c r="C84" s="160"/>
-      <c r="D84" s="160"/>
-      <c r="E84" s="160"/>
-      <c r="F84" s="160"/>
-      <c r="G84" s="163"/>
-      <c r="H84" s="161"/>
+    <row r="84" spans="1:19" ht="16">
+      <c r="A84" s="159"/>
+      <c r="B84" s="159"/>
+      <c r="C84" s="159"/>
+      <c r="D84" s="159"/>
+      <c r="E84" s="159"/>
+      <c r="F84" s="159"/>
+      <c r="G84" s="162"/>
+      <c r="H84" s="160"/>
       <c r="I84" s="134" t="s">
         <v>36</v>
       </c>
@@ -19064,15 +19115,15 @@
       <c r="R84" s="1"/>
       <c r="S84" s="96"/>
     </row>
-    <row r="85" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A85" s="160"/>
-      <c r="B85" s="160"/>
-      <c r="C85" s="160"/>
-      <c r="D85" s="160"/>
-      <c r="E85" s="160"/>
-      <c r="F85" s="160"/>
-      <c r="G85" s="164"/>
-      <c r="H85" s="165"/>
+    <row r="85" spans="1:19" ht="16">
+      <c r="A85" s="159"/>
+      <c r="B85" s="159"/>
+      <c r="C85" s="159"/>
+      <c r="D85" s="159"/>
+      <c r="E85" s="159"/>
+      <c r="F85" s="159"/>
+      <c r="G85" s="163"/>
+      <c r="H85" s="164"/>
       <c r="I85" s="134" t="s">
         <v>37</v>
       </c>
@@ -19096,15 +19147,15 @@
       <c r="R85" s="1"/>
       <c r="S85" s="96"/>
     </row>
-    <row r="86" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A86" s="163"/>
-      <c r="B86" s="163"/>
-      <c r="C86" s="167"/>
-      <c r="D86" s="160"/>
-      <c r="E86" s="160"/>
-      <c r="F86" s="166"/>
-      <c r="G86" s="164"/>
-      <c r="H86" s="165"/>
+    <row r="86" spans="1:19" ht="16">
+      <c r="A86" s="162"/>
+      <c r="B86" s="162"/>
+      <c r="C86" s="166"/>
+      <c r="D86" s="159"/>
+      <c r="E86" s="159"/>
+      <c r="F86" s="165"/>
+      <c r="G86" s="163"/>
+      <c r="H86" s="164"/>
       <c r="I86" s="134" t="s">
         <v>38</v>
       </c>
@@ -19128,15 +19179,15 @@
       <c r="R86" s="1"/>
       <c r="S86" s="96"/>
     </row>
-    <row r="87" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A87" s="160"/>
-      <c r="B87" s="160"/>
-      <c r="C87" s="160"/>
-      <c r="D87" s="160"/>
-      <c r="E87" s="160"/>
-      <c r="F87" s="166"/>
-      <c r="G87" s="164"/>
-      <c r="H87" s="165"/>
+    <row r="87" spans="1:19" ht="16">
+      <c r="A87" s="159"/>
+      <c r="B87" s="159"/>
+      <c r="C87" s="159"/>
+      <c r="D87" s="159"/>
+      <c r="E87" s="159"/>
+      <c r="F87" s="165"/>
+      <c r="G87" s="163"/>
+      <c r="H87" s="164"/>
       <c r="I87" s="134" t="s">
         <v>39</v>
       </c>
@@ -19160,15 +19211,15 @@
       <c r="R87" s="1"/>
       <c r="S87" s="96"/>
     </row>
-    <row r="88" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="160"/>
-      <c r="B88" s="160"/>
-      <c r="C88" s="160"/>
-      <c r="D88" s="160"/>
-      <c r="E88" s="160"/>
-      <c r="F88" s="160"/>
-      <c r="G88" s="164"/>
-      <c r="H88" s="165"/>
+    <row r="88" spans="1:19" ht="16">
+      <c r="A88" s="159"/>
+      <c r="B88" s="159"/>
+      <c r="C88" s="159"/>
+      <c r="D88" s="159"/>
+      <c r="E88" s="159"/>
+      <c r="F88" s="159"/>
+      <c r="G88" s="163"/>
+      <c r="H88" s="164"/>
       <c r="I88" s="134" t="s">
         <v>140</v>
       </c>
@@ -19192,15 +19243,15 @@
       <c r="R88" s="1"/>
       <c r="S88" s="96"/>
     </row>
-    <row r="89" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A89" s="160"/>
-      <c r="B89" s="160"/>
-      <c r="C89" s="160"/>
-      <c r="D89" s="160"/>
-      <c r="E89" s="160"/>
-      <c r="F89" s="160"/>
-      <c r="G89" s="164"/>
-      <c r="H89" s="165"/>
+    <row r="89" spans="1:19" ht="16">
+      <c r="A89" s="159"/>
+      <c r="B89" s="159"/>
+      <c r="C89" s="159"/>
+      <c r="D89" s="159"/>
+      <c r="E89" s="159"/>
+      <c r="F89" s="159"/>
+      <c r="G89" s="163"/>
+      <c r="H89" s="164"/>
       <c r="I89" s="134" t="s">
         <v>40</v>
       </c>
@@ -19224,15 +19275,15 @@
       <c r="R89" s="1"/>
       <c r="S89" s="96"/>
     </row>
-    <row r="90" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A90" s="160"/>
-      <c r="B90" s="160"/>
-      <c r="C90" s="160"/>
-      <c r="D90" s="160"/>
-      <c r="E90" s="160"/>
-      <c r="F90" s="160"/>
-      <c r="G90" s="164"/>
-      <c r="H90" s="165"/>
+    <row r="90" spans="1:19" ht="16">
+      <c r="A90" s="159"/>
+      <c r="B90" s="159"/>
+      <c r="C90" s="159"/>
+      <c r="D90" s="159"/>
+      <c r="E90" s="159"/>
+      <c r="F90" s="159"/>
+      <c r="G90" s="163"/>
+      <c r="H90" s="164"/>
       <c r="I90" s="134" t="s">
         <v>41</v>
       </c>
@@ -19256,15 +19307,15 @@
       <c r="R90" s="1"/>
       <c r="S90" s="96"/>
     </row>
-    <row r="91" spans="1:19" ht="19" x14ac:dyDescent="0.25">
-      <c r="A91" s="163"/>
-      <c r="B91" s="163"/>
-      <c r="C91" s="161"/>
-      <c r="D91" s="160"/>
-      <c r="E91" s="160"/>
-      <c r="F91" s="166"/>
-      <c r="G91" s="164"/>
-      <c r="H91" s="168"/>
+    <row r="91" spans="1:19" ht="19">
+      <c r="A91" s="162"/>
+      <c r="B91" s="162"/>
+      <c r="C91" s="160"/>
+      <c r="D91" s="159"/>
+      <c r="E91" s="159"/>
+      <c r="F91" s="165"/>
+      <c r="G91" s="163"/>
+      <c r="H91" s="167"/>
       <c r="I91" s="134" t="s">
         <v>42</v>
       </c>
@@ -19288,15 +19339,15 @@
       <c r="R91" s="1"/>
       <c r="S91" s="96"/>
     </row>
-    <row r="92" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A92" s="160"/>
-      <c r="B92" s="160"/>
-      <c r="C92" s="160"/>
-      <c r="D92" s="160"/>
-      <c r="E92" s="160"/>
-      <c r="F92" s="160"/>
-      <c r="G92" s="164"/>
-      <c r="H92" s="165"/>
+    <row r="92" spans="1:19" ht="16">
+      <c r="A92" s="159"/>
+      <c r="B92" s="159"/>
+      <c r="C92" s="159"/>
+      <c r="D92" s="159"/>
+      <c r="E92" s="159"/>
+      <c r="F92" s="159"/>
+      <c r="G92" s="163"/>
+      <c r="H92" s="164"/>
       <c r="I92" s="134" t="s">
         <v>43</v>
       </c>
@@ -19320,15 +19371,15 @@
       <c r="R92" s="1"/>
       <c r="S92" s="96"/>
     </row>
-    <row r="93" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A93" s="160"/>
-      <c r="B93" s="160"/>
-      <c r="C93" s="160"/>
-      <c r="D93" s="160"/>
-      <c r="E93" s="160"/>
-      <c r="F93" s="160"/>
-      <c r="G93" s="164"/>
-      <c r="H93" s="165"/>
+    <row r="93" spans="1:19" ht="16">
+      <c r="A93" s="159"/>
+      <c r="B93" s="159"/>
+      <c r="C93" s="159"/>
+      <c r="D93" s="159"/>
+      <c r="E93" s="159"/>
+      <c r="F93" s="159"/>
+      <c r="G93" s="163"/>
+      <c r="H93" s="164"/>
       <c r="I93" s="134" t="s">
         <v>139</v>
       </c>
@@ -19352,15 +19403,15 @@
       <c r="R93" s="1"/>
       <c r="S93" s="96"/>
     </row>
-    <row r="94" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A94" s="163"/>
-      <c r="B94" s="163"/>
-      <c r="C94" s="167"/>
-      <c r="D94" s="160"/>
-      <c r="E94" s="160"/>
-      <c r="F94" s="166"/>
-      <c r="G94" s="164"/>
-      <c r="H94" s="165"/>
+    <row r="94" spans="1:19" ht="16">
+      <c r="A94" s="162"/>
+      <c r="B94" s="162"/>
+      <c r="C94" s="166"/>
+      <c r="D94" s="159"/>
+      <c r="E94" s="159"/>
+      <c r="F94" s="165"/>
+      <c r="G94" s="163"/>
+      <c r="H94" s="164"/>
       <c r="I94" s="134" t="s">
         <v>45</v>
       </c>
@@ -19384,15 +19435,15 @@
       <c r="R94" s="1"/>
       <c r="S94" s="96"/>
     </row>
-    <row r="95" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A95" s="160"/>
-      <c r="B95" s="160"/>
-      <c r="C95" s="160"/>
-      <c r="D95" s="160"/>
-      <c r="E95" s="160"/>
-      <c r="F95" s="160"/>
-      <c r="G95" s="164"/>
-      <c r="H95" s="165"/>
+    <row r="95" spans="1:19" ht="16">
+      <c r="A95" s="159"/>
+      <c r="B95" s="159"/>
+      <c r="C95" s="159"/>
+      <c r="D95" s="159"/>
+      <c r="E95" s="159"/>
+      <c r="F95" s="159"/>
+      <c r="G95" s="163"/>
+      <c r="H95" s="164"/>
       <c r="I95" s="134" t="s">
         <v>46</v>
       </c>
@@ -19416,15 +19467,15 @@
       <c r="R95" s="1"/>
       <c r="S95" s="96"/>
     </row>
-    <row r="96" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="160"/>
-      <c r="B96" s="160"/>
-      <c r="C96" s="160"/>
-      <c r="D96" s="160"/>
-      <c r="E96" s="160"/>
-      <c r="F96" s="160"/>
-      <c r="G96" s="164"/>
-      <c r="H96" s="165"/>
+    <row r="96" spans="1:19" ht="16">
+      <c r="A96" s="159"/>
+      <c r="B96" s="159"/>
+      <c r="C96" s="159"/>
+      <c r="D96" s="159"/>
+      <c r="E96" s="159"/>
+      <c r="F96" s="159"/>
+      <c r="G96" s="163"/>
+      <c r="H96" s="164"/>
       <c r="I96" s="134" t="s">
         <v>47</v>
       </c>
@@ -19448,15 +19499,15 @@
       <c r="R96" s="1"/>
       <c r="S96" s="96"/>
     </row>
-    <row r="97" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="160"/>
-      <c r="B97" s="160"/>
-      <c r="C97" s="160"/>
-      <c r="D97" s="160"/>
-      <c r="E97" s="160"/>
-      <c r="F97" s="160"/>
-      <c r="G97" s="164"/>
-      <c r="H97" s="165"/>
+    <row r="97" spans="1:19" ht="16">
+      <c r="A97" s="159"/>
+      <c r="B97" s="159"/>
+      <c r="C97" s="159"/>
+      <c r="D97" s="159"/>
+      <c r="E97" s="159"/>
+      <c r="F97" s="159"/>
+      <c r="G97" s="163"/>
+      <c r="H97" s="164"/>
       <c r="I97" s="134" t="s">
         <v>48</v>
       </c>
@@ -19480,15 +19531,15 @@
       <c r="R97" s="1"/>
       <c r="S97" s="96"/>
     </row>
-    <row r="98" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A98" s="160"/>
-      <c r="B98" s="160"/>
-      <c r="C98" s="160"/>
-      <c r="D98" s="160"/>
-      <c r="E98" s="160"/>
-      <c r="F98" s="160"/>
-      <c r="G98" s="164"/>
-      <c r="H98" s="165"/>
+    <row r="98" spans="1:19" ht="16">
+      <c r="A98" s="159"/>
+      <c r="B98" s="159"/>
+      <c r="C98" s="159"/>
+      <c r="D98" s="159"/>
+      <c r="E98" s="159"/>
+      <c r="F98" s="159"/>
+      <c r="G98" s="163"/>
+      <c r="H98" s="164"/>
       <c r="I98" s="134" t="s">
         <v>49</v>
       </c>
@@ -19512,15 +19563,15 @@
       <c r="R98" s="1"/>
       <c r="S98" s="96"/>
     </row>
-    <row r="99" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A99" s="163"/>
-      <c r="B99" s="163"/>
-      <c r="C99" s="161"/>
-      <c r="D99" s="160"/>
-      <c r="E99" s="160"/>
-      <c r="F99" s="166"/>
-      <c r="G99" s="164"/>
-      <c r="H99" s="165"/>
+    <row r="99" spans="1:19" ht="16">
+      <c r="A99" s="162"/>
+      <c r="B99" s="162"/>
+      <c r="C99" s="160"/>
+      <c r="D99" s="159"/>
+      <c r="E99" s="159"/>
+      <c r="F99" s="165"/>
+      <c r="G99" s="163"/>
+      <c r="H99" s="164"/>
       <c r="I99" s="134" t="s">
         <v>50</v>
       </c>
@@ -19544,15 +19595,15 @@
       <c r="R99" s="1"/>
       <c r="S99" s="96"/>
     </row>
-    <row r="100" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A100" s="160"/>
-      <c r="B100" s="160"/>
-      <c r="C100" s="160"/>
-      <c r="D100" s="160"/>
-      <c r="E100" s="160"/>
-      <c r="F100" s="160"/>
-      <c r="G100" s="164"/>
-      <c r="H100" s="165"/>
+    <row r="100" spans="1:19" ht="16">
+      <c r="A100" s="159"/>
+      <c r="B100" s="159"/>
+      <c r="C100" s="159"/>
+      <c r="D100" s="159"/>
+      <c r="E100" s="159"/>
+      <c r="F100" s="159"/>
+      <c r="G100" s="163"/>
+      <c r="H100" s="164"/>
       <c r="I100" s="134" t="s">
         <v>51</v>
       </c>
@@ -19576,15 +19627,15 @@
       <c r="R100" s="1"/>
       <c r="S100" s="96"/>
     </row>
-    <row r="101" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A101" s="160"/>
-      <c r="B101" s="160"/>
-      <c r="C101" s="160"/>
-      <c r="D101" s="160"/>
-      <c r="E101" s="160"/>
-      <c r="F101" s="160"/>
-      <c r="G101" s="164"/>
-      <c r="H101" s="165"/>
+    <row r="101" spans="1:19" ht="16">
+      <c r="A101" s="159"/>
+      <c r="B101" s="159"/>
+      <c r="C101" s="159"/>
+      <c r="D101" s="159"/>
+      <c r="E101" s="159"/>
+      <c r="F101" s="159"/>
+      <c r="G101" s="163"/>
+      <c r="H101" s="164"/>
       <c r="I101" s="134" t="s">
         <v>52</v>
       </c>
@@ -19608,15 +19659,15 @@
       <c r="R101" s="1"/>
       <c r="S101" s="96"/>
     </row>
-    <row r="102" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A102" s="163"/>
-      <c r="B102" s="163"/>
-      <c r="C102" s="161"/>
-      <c r="D102" s="160"/>
-      <c r="E102" s="160"/>
-      <c r="F102" s="166"/>
-      <c r="G102" s="164"/>
-      <c r="H102" s="165"/>
+    <row r="102" spans="1:19" ht="16">
+      <c r="A102" s="162"/>
+      <c r="B102" s="162"/>
+      <c r="C102" s="160"/>
+      <c r="D102" s="159"/>
+      <c r="E102" s="159"/>
+      <c r="F102" s="165"/>
+      <c r="G102" s="163"/>
+      <c r="H102" s="164"/>
       <c r="I102" s="134" t="s">
         <v>53</v>
       </c>
@@ -19640,15 +19691,15 @@
       <c r="R102" s="1"/>
       <c r="S102" s="96"/>
     </row>
-    <row r="103" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A103" s="160"/>
-      <c r="B103" s="160"/>
-      <c r="C103" s="160"/>
-      <c r="D103" s="160"/>
-      <c r="E103" s="160"/>
-      <c r="F103" s="160"/>
-      <c r="G103" s="164"/>
-      <c r="H103" s="165"/>
+    <row r="103" spans="1:19" ht="16">
+      <c r="A103" s="159"/>
+      <c r="B103" s="159"/>
+      <c r="C103" s="159"/>
+      <c r="D103" s="159"/>
+      <c r="E103" s="159"/>
+      <c r="F103" s="159"/>
+      <c r="G103" s="163"/>
+      <c r="H103" s="164"/>
       <c r="I103" s="134" t="s">
         <v>54</v>
       </c>
@@ -19672,15 +19723,15 @@
       <c r="R103" s="1"/>
       <c r="S103" s="96"/>
     </row>
-    <row r="104" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A104" s="163"/>
-      <c r="B104" s="163"/>
-      <c r="C104" s="161"/>
-      <c r="D104" s="160"/>
-      <c r="E104" s="160"/>
-      <c r="F104" s="166"/>
-      <c r="G104" s="164"/>
-      <c r="H104" s="165"/>
+    <row r="104" spans="1:19" ht="16">
+      <c r="A104" s="162"/>
+      <c r="B104" s="162"/>
+      <c r="C104" s="160"/>
+      <c r="D104" s="159"/>
+      <c r="E104" s="159"/>
+      <c r="F104" s="165"/>
+      <c r="G104" s="163"/>
+      <c r="H104" s="164"/>
       <c r="I104" s="134" t="s">
         <v>55</v>
       </c>
@@ -19704,15 +19755,15 @@
       <c r="R104" s="1"/>
       <c r="S104" s="96"/>
     </row>
-    <row r="105" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A105" s="160"/>
-      <c r="B105" s="160"/>
-      <c r="C105" s="160"/>
-      <c r="D105" s="160"/>
-      <c r="E105" s="160"/>
-      <c r="F105" s="160"/>
-      <c r="G105" s="164"/>
-      <c r="H105" s="165"/>
+    <row r="105" spans="1:19" ht="16">
+      <c r="A105" s="159"/>
+      <c r="B105" s="159"/>
+      <c r="C105" s="159"/>
+      <c r="D105" s="159"/>
+      <c r="E105" s="159"/>
+      <c r="F105" s="159"/>
+      <c r="G105" s="163"/>
+      <c r="H105" s="164"/>
       <c r="I105" s="134" t="s">
         <v>56</v>
       </c>
@@ -19736,15 +19787,15 @@
       <c r="R105" s="1"/>
       <c r="S105" s="96"/>
     </row>
-    <row r="106" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A106" s="163"/>
-      <c r="B106" s="163"/>
-      <c r="C106" s="161"/>
-      <c r="D106" s="160"/>
-      <c r="E106" s="160"/>
-      <c r="F106" s="160"/>
-      <c r="G106" s="164"/>
-      <c r="H106" s="165"/>
+    <row r="106" spans="1:19" ht="16">
+      <c r="A106" s="162"/>
+      <c r="B106" s="162"/>
+      <c r="C106" s="160"/>
+      <c r="D106" s="159"/>
+      <c r="E106" s="159"/>
+      <c r="F106" s="159"/>
+      <c r="G106" s="163"/>
+      <c r="H106" s="164"/>
       <c r="I106" s="134" t="s">
         <v>57</v>
       </c>
@@ -19768,15 +19819,15 @@
       <c r="R106" s="1"/>
       <c r="S106" s="96"/>
     </row>
-    <row r="107" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A107" s="163"/>
-      <c r="B107" s="163"/>
-      <c r="C107" s="161"/>
-      <c r="D107" s="160"/>
-      <c r="E107" s="160"/>
-      <c r="F107" s="160"/>
-      <c r="G107" s="164"/>
-      <c r="H107" s="165"/>
+    <row r="107" spans="1:19" ht="16">
+      <c r="A107" s="162"/>
+      <c r="B107" s="162"/>
+      <c r="C107" s="160"/>
+      <c r="D107" s="159"/>
+      <c r="E107" s="159"/>
+      <c r="F107" s="159"/>
+      <c r="G107" s="163"/>
+      <c r="H107" s="164"/>
       <c r="I107" s="134" t="s">
         <v>58</v>
       </c>
@@ -19800,15 +19851,15 @@
       <c r="R107" s="1"/>
       <c r="S107" s="96"/>
     </row>
-    <row r="108" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A108" s="160"/>
-      <c r="B108" s="160"/>
-      <c r="C108" s="160"/>
-      <c r="D108" s="160"/>
-      <c r="E108" s="160"/>
-      <c r="F108" s="160"/>
-      <c r="G108" s="164"/>
-      <c r="H108" s="165"/>
+    <row r="108" spans="1:19" ht="16">
+      <c r="A108" s="159"/>
+      <c r="B108" s="159"/>
+      <c r="C108" s="159"/>
+      <c r="D108" s="159"/>
+      <c r="E108" s="159"/>
+      <c r="F108" s="159"/>
+      <c r="G108" s="163"/>
+      <c r="H108" s="164"/>
       <c r="I108" s="134" t="s">
         <v>59</v>
       </c>
@@ -19832,15 +19883,15 @@
       <c r="R108" s="1"/>
       <c r="S108" s="96"/>
     </row>
-    <row r="109" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A109" s="160"/>
-      <c r="B109" s="160"/>
-      <c r="C109" s="160"/>
-      <c r="D109" s="160"/>
-      <c r="E109" s="160"/>
-      <c r="F109" s="160"/>
-      <c r="G109" s="164"/>
-      <c r="H109" s="165"/>
+    <row r="109" spans="1:19" ht="16">
+      <c r="A109" s="159"/>
+      <c r="B109" s="159"/>
+      <c r="C109" s="159"/>
+      <c r="D109" s="159"/>
+      <c r="E109" s="159"/>
+      <c r="F109" s="159"/>
+      <c r="G109" s="163"/>
+      <c r="H109" s="164"/>
       <c r="I109" s="134" t="s">
         <v>60</v>
       </c>
@@ -19864,15 +19915,15 @@
       <c r="R109" s="1"/>
       <c r="S109" s="96"/>
     </row>
-    <row r="110" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A110" s="163"/>
-      <c r="B110" s="163"/>
-      <c r="C110" s="161"/>
-      <c r="D110" s="160"/>
-      <c r="E110" s="160"/>
-      <c r="F110" s="166"/>
-      <c r="G110" s="164"/>
-      <c r="H110" s="165"/>
+    <row r="110" spans="1:19" ht="16">
+      <c r="A110" s="162"/>
+      <c r="B110" s="162"/>
+      <c r="C110" s="160"/>
+      <c r="D110" s="159"/>
+      <c r="E110" s="159"/>
+      <c r="F110" s="165"/>
+      <c r="G110" s="163"/>
+      <c r="H110" s="164"/>
       <c r="I110" s="134" t="s">
         <v>61</v>
       </c>
@@ -19896,15 +19947,15 @@
       <c r="R110" s="1"/>
       <c r="S110" s="96"/>
     </row>
-    <row r="111" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A111" s="160"/>
-      <c r="B111" s="160"/>
-      <c r="C111" s="160"/>
-      <c r="D111" s="160"/>
-      <c r="E111" s="160"/>
-      <c r="F111" s="160"/>
-      <c r="G111" s="164"/>
-      <c r="H111" s="165"/>
+    <row r="111" spans="1:19" ht="16">
+      <c r="A111" s="159"/>
+      <c r="B111" s="159"/>
+      <c r="C111" s="159"/>
+      <c r="D111" s="159"/>
+      <c r="E111" s="159"/>
+      <c r="F111" s="159"/>
+      <c r="G111" s="163"/>
+      <c r="H111" s="164"/>
       <c r="I111" s="134" t="s">
         <v>62</v>
       </c>
@@ -19928,15 +19979,15 @@
       <c r="R111" s="1"/>
       <c r="S111" s="96"/>
     </row>
-    <row r="112" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A112" s="160"/>
-      <c r="B112" s="160"/>
-      <c r="C112" s="160"/>
-      <c r="D112" s="160"/>
-      <c r="E112" s="160"/>
-      <c r="F112" s="160"/>
-      <c r="G112" s="164"/>
-      <c r="H112" s="165"/>
+    <row r="112" spans="1:19" ht="16">
+      <c r="A112" s="159"/>
+      <c r="B112" s="159"/>
+      <c r="C112" s="159"/>
+      <c r="D112" s="159"/>
+      <c r="E112" s="159"/>
+      <c r="F112" s="159"/>
+      <c r="G112" s="163"/>
+      <c r="H112" s="164"/>
       <c r="I112" s="134" t="s">
         <v>63</v>
       </c>
@@ -19960,15 +20011,15 @@
       <c r="R112" s="1"/>
       <c r="S112" s="96"/>
     </row>
-    <row r="113" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A113" s="163"/>
-      <c r="B113" s="163"/>
-      <c r="C113" s="161"/>
-      <c r="D113" s="160"/>
-      <c r="E113" s="160"/>
-      <c r="F113" s="166"/>
-      <c r="G113" s="164"/>
-      <c r="H113" s="165"/>
+    <row r="113" spans="1:19" ht="16">
+      <c r="A113" s="162"/>
+      <c r="B113" s="162"/>
+      <c r="C113" s="160"/>
+      <c r="D113" s="159"/>
+      <c r="E113" s="159"/>
+      <c r="F113" s="165"/>
+      <c r="G113" s="163"/>
+      <c r="H113" s="164"/>
       <c r="I113" s="134" t="s">
         <v>64</v>
       </c>
@@ -19992,15 +20043,15 @@
       <c r="R113" s="1"/>
       <c r="S113" s="96"/>
     </row>
-    <row r="114" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A114" s="160"/>
-      <c r="B114" s="160"/>
-      <c r="C114" s="160"/>
-      <c r="D114" s="160"/>
-      <c r="E114" s="160"/>
-      <c r="F114" s="160"/>
-      <c r="G114" s="164"/>
-      <c r="H114" s="165"/>
+    <row r="114" spans="1:19" ht="16">
+      <c r="A114" s="159"/>
+      <c r="B114" s="159"/>
+      <c r="C114" s="159"/>
+      <c r="D114" s="159"/>
+      <c r="E114" s="159"/>
+      <c r="F114" s="159"/>
+      <c r="G114" s="163"/>
+      <c r="H114" s="164"/>
       <c r="I114" s="134" t="s">
         <v>65</v>
       </c>
@@ -20024,15 +20075,15 @@
       <c r="R114" s="1"/>
       <c r="S114" s="96"/>
     </row>
-    <row r="115" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A115" s="160"/>
-      <c r="B115" s="160"/>
-      <c r="C115" s="160"/>
-      <c r="D115" s="160"/>
-      <c r="E115" s="160"/>
-      <c r="F115" s="160"/>
-      <c r="G115" s="164"/>
-      <c r="H115" s="165"/>
+    <row r="115" spans="1:19" ht="16">
+      <c r="A115" s="159"/>
+      <c r="B115" s="159"/>
+      <c r="C115" s="159"/>
+      <c r="D115" s="159"/>
+      <c r="E115" s="159"/>
+      <c r="F115" s="159"/>
+      <c r="G115" s="163"/>
+      <c r="H115" s="164"/>
       <c r="I115" s="134" t="s">
         <v>66</v>
       </c>
@@ -20056,15 +20107,15 @@
       <c r="R115" s="1"/>
       <c r="S115" s="96"/>
     </row>
-    <row r="116" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A116" s="160"/>
-      <c r="B116" s="160"/>
-      <c r="C116" s="160"/>
-      <c r="D116" s="160"/>
-      <c r="E116" s="160"/>
-      <c r="F116" s="160"/>
-      <c r="G116" s="163"/>
-      <c r="H116" s="161"/>
+    <row r="116" spans="1:19" ht="16">
+      <c r="A116" s="159"/>
+      <c r="B116" s="159"/>
+      <c r="C116" s="159"/>
+      <c r="D116" s="159"/>
+      <c r="E116" s="159"/>
+      <c r="F116" s="159"/>
+      <c r="G116" s="162"/>
+      <c r="H116" s="160"/>
       <c r="I116" s="134" t="s">
         <v>67</v>
       </c>
@@ -20088,523 +20139,523 @@
       <c r="R116" s="1"/>
       <c r="S116" s="96"/>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A117" s="160"/>
-      <c r="B117" s="160"/>
-      <c r="C117" s="160"/>
-      <c r="D117" s="160"/>
-      <c r="E117" s="160"/>
-      <c r="F117" s="160"/>
-      <c r="G117" s="160"/>
-      <c r="H117" s="160"/>
+    <row r="117" spans="1:19">
+      <c r="A117" s="159"/>
+      <c r="B117" s="159"/>
+      <c r="C117" s="159"/>
+      <c r="D117" s="159"/>
+      <c r="E117" s="159"/>
+      <c r="F117" s="159"/>
+      <c r="G117" s="159"/>
+      <c r="H117" s="159"/>
       <c r="I117" s="134"/>
       <c r="J117" s="134"/>
       <c r="K117" s="134"/>
       <c r="L117" s="134"/>
       <c r="M117" s="122"/>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A118" s="160"/>
-      <c r="B118" s="160"/>
-      <c r="C118" s="160"/>
-      <c r="D118" s="160"/>
-      <c r="E118" s="160"/>
-      <c r="F118" s="160"/>
-      <c r="G118" s="200"/>
-      <c r="H118" s="201"/>
+    <row r="118" spans="1:19">
+      <c r="A118" s="159"/>
+      <c r="B118" s="159"/>
+      <c r="C118" s="159"/>
+      <c r="D118" s="159"/>
+      <c r="E118" s="159"/>
+      <c r="F118" s="159"/>
+      <c r="G118" s="205"/>
+      <c r="H118" s="206"/>
       <c r="I118" s="134"/>
       <c r="J118" s="139"/>
       <c r="K118" s="139"/>
       <c r="L118" s="134"/>
       <c r="M118" s="122"/>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A119" s="160"/>
-      <c r="B119" s="160"/>
-      <c r="C119" s="160"/>
-      <c r="D119" s="160"/>
-      <c r="E119" s="160"/>
-      <c r="F119" s="160"/>
-      <c r="G119" s="162"/>
-      <c r="H119" s="162"/>
+    <row r="119" spans="1:19">
+      <c r="A119" s="159"/>
+      <c r="B119" s="159"/>
+      <c r="C119" s="159"/>
+      <c r="D119" s="159"/>
+      <c r="E119" s="159"/>
+      <c r="F119" s="159"/>
+      <c r="G119" s="161"/>
+      <c r="H119" s="161"/>
       <c r="I119" s="134"/>
       <c r="J119" s="139"/>
       <c r="K119" s="139"/>
       <c r="L119" s="134"/>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A120" s="160"/>
-      <c r="B120" s="160"/>
-      <c r="C120" s="160"/>
-      <c r="D120" s="160"/>
-      <c r="E120" s="160"/>
-      <c r="F120" s="160"/>
-      <c r="G120" s="160"/>
-      <c r="H120" s="160"/>
+    <row r="120" spans="1:19">
+      <c r="A120" s="159"/>
+      <c r="B120" s="159"/>
+      <c r="C120" s="159"/>
+      <c r="D120" s="159"/>
+      <c r="E120" s="159"/>
+      <c r="F120" s="159"/>
+      <c r="G120" s="159"/>
+      <c r="H120" s="159"/>
       <c r="I120" s="134"/>
       <c r="J120" s="137"/>
       <c r="K120" s="138"/>
       <c r="L120" s="134"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A121" s="160"/>
-      <c r="B121" s="160"/>
-      <c r="C121" s="160"/>
-      <c r="D121" s="160"/>
-      <c r="E121" s="160"/>
-      <c r="F121" s="160"/>
-      <c r="G121" s="160"/>
-      <c r="H121" s="160"/>
+    <row r="121" spans="1:19">
+      <c r="A121" s="159"/>
+      <c r="B121" s="159"/>
+      <c r="C121" s="159"/>
+      <c r="D121" s="159"/>
+      <c r="E121" s="159"/>
+      <c r="F121" s="159"/>
+      <c r="G121" s="159"/>
+      <c r="H121" s="159"/>
       <c r="I121" s="134"/>
       <c r="J121" s="137"/>
       <c r="K121" s="138"/>
       <c r="L121" s="134"/>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A122" s="160"/>
-      <c r="B122" s="160"/>
-      <c r="C122" s="160"/>
-      <c r="D122" s="160"/>
-      <c r="E122" s="160"/>
-      <c r="F122" s="160"/>
-      <c r="G122" s="160"/>
-      <c r="H122" s="160"/>
+    <row r="122" spans="1:19">
+      <c r="A122" s="159"/>
+      <c r="B122" s="159"/>
+      <c r="C122" s="159"/>
+      <c r="D122" s="159"/>
+      <c r="E122" s="159"/>
+      <c r="F122" s="159"/>
+      <c r="G122" s="159"/>
+      <c r="H122" s="159"/>
       <c r="I122" s="134"/>
       <c r="J122" s="137"/>
       <c r="K122" s="138"/>
       <c r="L122" s="134"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A123" s="160"/>
-      <c r="B123" s="160"/>
-      <c r="C123" s="160"/>
-      <c r="D123" s="160"/>
-      <c r="E123" s="160"/>
-      <c r="F123" s="160"/>
+    <row r="123" spans="1:19">
+      <c r="A123" s="159"/>
+      <c r="B123" s="159"/>
+      <c r="C123" s="159"/>
+      <c r="D123" s="159"/>
+      <c r="E123" s="159"/>
+      <c r="F123" s="159"/>
       <c r="J123" s="2"/>
       <c r="K123" s="1"/>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A124" s="160"/>
-      <c r="B124" s="160"/>
-      <c r="C124" s="160"/>
-      <c r="D124" s="160"/>
-      <c r="E124" s="160"/>
-      <c r="F124" s="160"/>
+    <row r="124" spans="1:19">
+      <c r="A124" s="159"/>
+      <c r="B124" s="159"/>
+      <c r="C124" s="159"/>
+      <c r="D124" s="159"/>
+      <c r="E124" s="159"/>
+      <c r="F124" s="159"/>
       <c r="J124" s="2"/>
       <c r="K124" s="1"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A125" s="160"/>
-      <c r="B125" s="160"/>
-      <c r="C125" s="160"/>
-      <c r="D125" s="160"/>
-      <c r="E125" s="160"/>
-      <c r="F125" s="160"/>
+    <row r="125" spans="1:19">
+      <c r="A125" s="159"/>
+      <c r="B125" s="159"/>
+      <c r="C125" s="159"/>
+      <c r="D125" s="159"/>
+      <c r="E125" s="159"/>
+      <c r="F125" s="159"/>
       <c r="J125" s="2"/>
       <c r="K125" s="1"/>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A126" s="160"/>
-      <c r="B126" s="160"/>
-      <c r="C126" s="160"/>
-      <c r="D126" s="160"/>
-      <c r="E126" s="160"/>
-      <c r="F126" s="160"/>
+    <row r="126" spans="1:19">
+      <c r="A126" s="159"/>
+      <c r="B126" s="159"/>
+      <c r="C126" s="159"/>
+      <c r="D126" s="159"/>
+      <c r="E126" s="159"/>
+      <c r="F126" s="159"/>
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A127" s="160"/>
-      <c r="B127" s="160"/>
-      <c r="C127" s="160"/>
-      <c r="D127" s="160"/>
-      <c r="E127" s="160"/>
-      <c r="F127" s="160"/>
+    <row r="127" spans="1:19">
+      <c r="A127" s="159"/>
+      <c r="B127" s="159"/>
+      <c r="C127" s="159"/>
+      <c r="D127" s="159"/>
+      <c r="E127" s="159"/>
+      <c r="F127" s="159"/>
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A128" s="160"/>
-      <c r="B128" s="160"/>
-      <c r="C128" s="160"/>
-      <c r="D128" s="160"/>
-      <c r="E128" s="160"/>
-      <c r="F128" s="160"/>
+    <row r="128" spans="1:19">
+      <c r="A128" s="159"/>
+      <c r="B128" s="159"/>
+      <c r="C128" s="159"/>
+      <c r="D128" s="159"/>
+      <c r="E128" s="159"/>
+      <c r="F128" s="159"/>
       <c r="J128" s="2"/>
       <c r="K128" s="1"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A129" s="160"/>
-      <c r="B129" s="160"/>
-      <c r="C129" s="160"/>
-      <c r="D129" s="160"/>
-      <c r="E129" s="160"/>
-      <c r="F129" s="160"/>
+    <row r="129" spans="1:11">
+      <c r="A129" s="159"/>
+      <c r="B129" s="159"/>
+      <c r="C129" s="159"/>
+      <c r="D129" s="159"/>
+      <c r="E129" s="159"/>
+      <c r="F129" s="159"/>
       <c r="J129" s="2"/>
       <c r="K129" s="1"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A130" s="160"/>
-      <c r="B130" s="160"/>
-      <c r="C130" s="160"/>
-      <c r="D130" s="160"/>
-      <c r="E130" s="160"/>
-      <c r="F130" s="160"/>
+    <row r="130" spans="1:11">
+      <c r="A130" s="159"/>
+      <c r="B130" s="159"/>
+      <c r="C130" s="159"/>
+      <c r="D130" s="159"/>
+      <c r="E130" s="159"/>
+      <c r="F130" s="159"/>
       <c r="J130" s="2"/>
       <c r="K130" s="1"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A131" s="160"/>
-      <c r="B131" s="160"/>
-      <c r="C131" s="160"/>
-      <c r="D131" s="160"/>
-      <c r="E131" s="160"/>
-      <c r="F131" s="160"/>
+    <row r="131" spans="1:11">
+      <c r="A131" s="159"/>
+      <c r="B131" s="159"/>
+      <c r="C131" s="159"/>
+      <c r="D131" s="159"/>
+      <c r="E131" s="159"/>
+      <c r="F131" s="159"/>
       <c r="J131" s="2"/>
       <c r="K131" s="1"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A132" s="160"/>
-      <c r="B132" s="160"/>
-      <c r="C132" s="160"/>
-      <c r="D132" s="160"/>
-      <c r="E132" s="160"/>
-      <c r="F132" s="160"/>
+    <row r="132" spans="1:11">
+      <c r="A132" s="159"/>
+      <c r="B132" s="159"/>
+      <c r="C132" s="159"/>
+      <c r="D132" s="159"/>
+      <c r="E132" s="159"/>
+      <c r="F132" s="159"/>
       <c r="J132" s="2"/>
       <c r="K132" s="1"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A133" s="160"/>
-      <c r="B133" s="160"/>
-      <c r="C133" s="160"/>
-      <c r="D133" s="160"/>
-      <c r="E133" s="160"/>
-      <c r="F133" s="160"/>
+    <row r="133" spans="1:11">
+      <c r="A133" s="159"/>
+      <c r="B133" s="159"/>
+      <c r="C133" s="159"/>
+      <c r="D133" s="159"/>
+      <c r="E133" s="159"/>
+      <c r="F133" s="159"/>
       <c r="J133" s="2"/>
       <c r="K133" s="1"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A134" s="160"/>
-      <c r="B134" s="160"/>
-      <c r="C134" s="160"/>
-      <c r="D134" s="160"/>
-      <c r="E134" s="160"/>
-      <c r="F134" s="160"/>
+    <row r="134" spans="1:11">
+      <c r="A134" s="159"/>
+      <c r="B134" s="159"/>
+      <c r="C134" s="159"/>
+      <c r="D134" s="159"/>
+      <c r="E134" s="159"/>
+      <c r="F134" s="159"/>
       <c r="J134" s="2"/>
       <c r="K134" s="1"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="160"/>
-      <c r="B135" s="160"/>
-      <c r="C135" s="160"/>
-      <c r="D135" s="160"/>
-      <c r="E135" s="160"/>
-      <c r="F135" s="160"/>
+    <row r="135" spans="1:11">
+      <c r="A135" s="159"/>
+      <c r="B135" s="159"/>
+      <c r="C135" s="159"/>
+      <c r="D135" s="159"/>
+      <c r="E135" s="159"/>
+      <c r="F135" s="159"/>
       <c r="J135" s="2"/>
       <c r="K135" s="1"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A136" s="160"/>
-      <c r="B136" s="160"/>
-      <c r="C136" s="160"/>
-      <c r="D136" s="160"/>
-      <c r="E136" s="160"/>
-      <c r="F136" s="160"/>
+    <row r="136" spans="1:11">
+      <c r="A136" s="159"/>
+      <c r="B136" s="159"/>
+      <c r="C136" s="159"/>
+      <c r="D136" s="159"/>
+      <c r="E136" s="159"/>
+      <c r="F136" s="159"/>
       <c r="J136" s="2"/>
       <c r="K136" s="1"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A137" s="160"/>
-      <c r="B137" s="160"/>
-      <c r="C137" s="160"/>
-      <c r="D137" s="160"/>
-      <c r="E137" s="160"/>
-      <c r="F137" s="160"/>
+    <row r="137" spans="1:11">
+      <c r="A137" s="159"/>
+      <c r="B137" s="159"/>
+      <c r="C137" s="159"/>
+      <c r="D137" s="159"/>
+      <c r="E137" s="159"/>
+      <c r="F137" s="159"/>
       <c r="J137" s="2"/>
       <c r="K137" s="1"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A138" s="160"/>
-      <c r="B138" s="160"/>
-      <c r="C138" s="160"/>
-      <c r="D138" s="160"/>
-      <c r="E138" s="160"/>
-      <c r="F138" s="160"/>
+    <row r="138" spans="1:11">
+      <c r="A138" s="159"/>
+      <c r="B138" s="159"/>
+      <c r="C138" s="159"/>
+      <c r="D138" s="159"/>
+      <c r="E138" s="159"/>
+      <c r="F138" s="159"/>
       <c r="J138" s="2"/>
       <c r="K138" s="1"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A139" s="160"/>
-      <c r="B139" s="160"/>
-      <c r="C139" s="160"/>
-      <c r="D139" s="160"/>
-      <c r="E139" s="160"/>
-      <c r="F139" s="160"/>
+    <row r="139" spans="1:11">
+      <c r="A139" s="159"/>
+      <c r="B139" s="159"/>
+      <c r="C139" s="159"/>
+      <c r="D139" s="159"/>
+      <c r="E139" s="159"/>
+      <c r="F139" s="159"/>
       <c r="J139" s="2"/>
       <c r="K139" s="1"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A140" s="160"/>
-      <c r="B140" s="160"/>
-      <c r="C140" s="160"/>
-      <c r="D140" s="160"/>
-      <c r="E140" s="160"/>
-      <c r="F140" s="160"/>
+    <row r="140" spans="1:11">
+      <c r="A140" s="159"/>
+      <c r="B140" s="159"/>
+      <c r="C140" s="159"/>
+      <c r="D140" s="159"/>
+      <c r="E140" s="159"/>
+      <c r="F140" s="159"/>
       <c r="J140" s="2"/>
       <c r="K140" s="1"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A141" s="160"/>
-      <c r="B141" s="160"/>
-      <c r="C141" s="160"/>
-      <c r="D141" s="160"/>
-      <c r="E141" s="160"/>
-      <c r="F141" s="160"/>
+    <row r="141" spans="1:11">
+      <c r="A141" s="159"/>
+      <c r="B141" s="159"/>
+      <c r="C141" s="159"/>
+      <c r="D141" s="159"/>
+      <c r="E141" s="159"/>
+      <c r="F141" s="159"/>
       <c r="J141" s="2"/>
       <c r="K141" s="1"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A142" s="160"/>
-      <c r="B142" s="160"/>
-      <c r="C142" s="160"/>
-      <c r="D142" s="160"/>
-      <c r="E142" s="160"/>
-      <c r="F142" s="160"/>
+    <row r="142" spans="1:11">
+      <c r="A142" s="159"/>
+      <c r="B142" s="159"/>
+      <c r="C142" s="159"/>
+      <c r="D142" s="159"/>
+      <c r="E142" s="159"/>
+      <c r="F142" s="159"/>
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A143" s="160"/>
-      <c r="B143" s="160"/>
-      <c r="C143" s="160"/>
-      <c r="D143" s="160"/>
-      <c r="E143" s="160"/>
-      <c r="F143" s="160"/>
+    <row r="143" spans="1:11">
+      <c r="A143" s="159"/>
+      <c r="B143" s="159"/>
+      <c r="C143" s="159"/>
+      <c r="D143" s="159"/>
+      <c r="E143" s="159"/>
+      <c r="F143" s="159"/>
       <c r="J143" s="2"/>
       <c r="K143" s="1"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A144" s="160"/>
-      <c r="B144" s="160"/>
-      <c r="C144" s="160"/>
-      <c r="D144" s="160"/>
-      <c r="E144" s="160"/>
-      <c r="F144" s="160"/>
+    <row r="144" spans="1:11">
+      <c r="A144" s="159"/>
+      <c r="B144" s="159"/>
+      <c r="C144" s="159"/>
+      <c r="D144" s="159"/>
+      <c r="E144" s="159"/>
+      <c r="F144" s="159"/>
       <c r="J144" s="2"/>
       <c r="K144" s="1"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A145" s="160"/>
-      <c r="B145" s="160"/>
-      <c r="C145" s="160"/>
-      <c r="D145" s="160"/>
-      <c r="E145" s="160"/>
-      <c r="F145" s="160"/>
+    <row r="145" spans="1:11">
+      <c r="A145" s="159"/>
+      <c r="B145" s="159"/>
+      <c r="C145" s="159"/>
+      <c r="D145" s="159"/>
+      <c r="E145" s="159"/>
+      <c r="F145" s="159"/>
       <c r="J145" s="2"/>
       <c r="K145" s="1"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A146" s="160"/>
-      <c r="B146" s="160"/>
-      <c r="C146" s="160"/>
-      <c r="D146" s="160"/>
-      <c r="E146" s="160"/>
-      <c r="F146" s="160"/>
+    <row r="146" spans="1:11">
+      <c r="A146" s="159"/>
+      <c r="B146" s="159"/>
+      <c r="C146" s="159"/>
+      <c r="D146" s="159"/>
+      <c r="E146" s="159"/>
+      <c r="F146" s="159"/>
       <c r="J146" s="2"/>
       <c r="K146" s="1"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A147" s="160"/>
-      <c r="B147" s="160"/>
-      <c r="C147" s="160"/>
-      <c r="D147" s="160"/>
-      <c r="E147" s="160"/>
-      <c r="F147" s="160"/>
+    <row r="147" spans="1:11">
+      <c r="A147" s="159"/>
+      <c r="B147" s="159"/>
+      <c r="C147" s="159"/>
+      <c r="D147" s="159"/>
+      <c r="E147" s="159"/>
+      <c r="F147" s="159"/>
       <c r="J147" s="2"/>
       <c r="K147" s="1"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A148" s="160"/>
-      <c r="B148" s="160"/>
-      <c r="C148" s="160"/>
-      <c r="D148" s="160"/>
-      <c r="E148" s="160"/>
-      <c r="F148" s="160"/>
+    <row r="148" spans="1:11">
+      <c r="A148" s="159"/>
+      <c r="B148" s="159"/>
+      <c r="C148" s="159"/>
+      <c r="D148" s="159"/>
+      <c r="E148" s="159"/>
+      <c r="F148" s="159"/>
       <c r="J148" s="2"/>
       <c r="K148" s="1"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A149" s="160"/>
-      <c r="B149" s="160"/>
-      <c r="C149" s="160"/>
-      <c r="D149" s="160"/>
-      <c r="E149" s="160"/>
-      <c r="F149" s="160"/>
+    <row r="149" spans="1:11">
+      <c r="A149" s="159"/>
+      <c r="B149" s="159"/>
+      <c r="C149" s="159"/>
+      <c r="D149" s="159"/>
+      <c r="E149" s="159"/>
+      <c r="F149" s="159"/>
       <c r="J149" s="2"/>
       <c r="K149" s="1"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A150" s="160"/>
-      <c r="B150" s="160"/>
-      <c r="C150" s="160"/>
-      <c r="D150" s="160"/>
-      <c r="E150" s="160"/>
-      <c r="F150" s="160"/>
+    <row r="150" spans="1:11">
+      <c r="A150" s="159"/>
+      <c r="B150" s="159"/>
+      <c r="C150" s="159"/>
+      <c r="D150" s="159"/>
+      <c r="E150" s="159"/>
+      <c r="F150" s="159"/>
       <c r="J150" s="2"/>
       <c r="K150" s="1"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A151" s="160"/>
-      <c r="B151" s="160"/>
-      <c r="C151" s="160"/>
-      <c r="D151" s="160"/>
-      <c r="E151" s="160"/>
-      <c r="F151" s="160"/>
+    <row r="151" spans="1:11">
+      <c r="A151" s="159"/>
+      <c r="B151" s="159"/>
+      <c r="C151" s="159"/>
+      <c r="D151" s="159"/>
+      <c r="E151" s="159"/>
+      <c r="F151" s="159"/>
       <c r="J151" s="2"/>
       <c r="K151" s="1"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A152" s="160"/>
-      <c r="B152" s="160"/>
-      <c r="C152" s="160"/>
-      <c r="D152" s="160"/>
-      <c r="E152" s="160"/>
-      <c r="F152" s="160"/>
+    <row r="152" spans="1:11">
+      <c r="A152" s="159"/>
+      <c r="B152" s="159"/>
+      <c r="C152" s="159"/>
+      <c r="D152" s="159"/>
+      <c r="E152" s="159"/>
+      <c r="F152" s="159"/>
       <c r="J152" s="2"/>
       <c r="K152" s="1"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A153" s="160"/>
-      <c r="B153" s="160"/>
-      <c r="C153" s="160"/>
-      <c r="D153" s="160"/>
-      <c r="E153" s="160"/>
-      <c r="F153" s="160"/>
+    <row r="153" spans="1:11">
+      <c r="A153" s="159"/>
+      <c r="B153" s="159"/>
+      <c r="C153" s="159"/>
+      <c r="D153" s="159"/>
+      <c r="E153" s="159"/>
+      <c r="F153" s="159"/>
       <c r="J153" s="2"/>
       <c r="K153" s="1"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A154" s="160"/>
-      <c r="B154" s="160"/>
-      <c r="C154" s="160"/>
-      <c r="D154" s="160"/>
-      <c r="E154" s="160"/>
-      <c r="F154" s="160"/>
+    <row r="154" spans="1:11">
+      <c r="A154" s="159"/>
+      <c r="B154" s="159"/>
+      <c r="C154" s="159"/>
+      <c r="D154" s="159"/>
+      <c r="E154" s="159"/>
+      <c r="F154" s="159"/>
       <c r="J154" s="2"/>
       <c r="K154" s="1"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A155" s="160"/>
-      <c r="B155" s="160"/>
-      <c r="C155" s="160"/>
-      <c r="D155" s="160"/>
-      <c r="E155" s="160"/>
-      <c r="F155" s="160"/>
+    <row r="155" spans="1:11">
+      <c r="A155" s="159"/>
+      <c r="B155" s="159"/>
+      <c r="C155" s="159"/>
+      <c r="D155" s="159"/>
+      <c r="E155" s="159"/>
+      <c r="F155" s="159"/>
       <c r="J155" s="2"/>
       <c r="K155" s="1"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A156" s="160"/>
-      <c r="B156" s="160"/>
-      <c r="C156" s="160"/>
-      <c r="D156" s="160"/>
-      <c r="E156" s="160"/>
-      <c r="F156" s="160"/>
+    <row r="156" spans="1:11">
+      <c r="A156" s="159"/>
+      <c r="B156" s="159"/>
+      <c r="C156" s="159"/>
+      <c r="D156" s="159"/>
+      <c r="E156" s="159"/>
+      <c r="F156" s="159"/>
       <c r="J156" s="2"/>
       <c r="K156" s="1"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A157" s="160"/>
-      <c r="B157" s="160"/>
-      <c r="C157" s="160"/>
-      <c r="D157" s="160"/>
-      <c r="E157" s="160"/>
-      <c r="F157" s="160"/>
+    <row r="157" spans="1:11">
+      <c r="A157" s="159"/>
+      <c r="B157" s="159"/>
+      <c r="C157" s="159"/>
+      <c r="D157" s="159"/>
+      <c r="E157" s="159"/>
+      <c r="F157" s="159"/>
       <c r="J157" s="2"/>
       <c r="K157" s="1"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A158" s="160"/>
-      <c r="B158" s="160"/>
-      <c r="C158" s="160"/>
-      <c r="D158" s="160"/>
-      <c r="E158" s="160"/>
-      <c r="F158" s="160"/>
+    <row r="158" spans="1:11">
+      <c r="A158" s="159"/>
+      <c r="B158" s="159"/>
+      <c r="C158" s="159"/>
+      <c r="D158" s="159"/>
+      <c r="E158" s="159"/>
+      <c r="F158" s="159"/>
       <c r="J158" s="2"/>
       <c r="K158" s="1"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="J159" s="2"/>
       <c r="K159" s="1"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="J160" s="2"/>
       <c r="K160" s="1"/>
     </row>
-    <row r="161" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="7:11">
       <c r="J161" s="2"/>
       <c r="K161" s="1"/>
     </row>
-    <row r="162" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="7:11">
       <c r="J162" s="2"/>
       <c r="K162" s="1"/>
     </row>
-    <row r="163" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="7:11">
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
     </row>
-    <row r="164" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="7:11">
       <c r="J164" s="2"/>
       <c r="K164" s="1"/>
     </row>
-    <row r="165" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="7:11">
       <c r="J165" s="2"/>
       <c r="K165" s="1"/>
     </row>
-    <row r="166" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="7:11">
       <c r="J166" s="2"/>
       <c r="K166" s="1"/>
     </row>
-    <row r="167" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="7:11">
       <c r="J167" s="2"/>
       <c r="K167" s="1"/>
     </row>
-    <row r="168" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="7:11">
       <c r="J168" s="2"/>
       <c r="K168" s="1"/>
     </row>
-    <row r="169" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="7:11">
       <c r="J169" s="2"/>
       <c r="K169" s="1"/>
     </row>
-    <row r="170" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="7:11">
       <c r="J170" s="2"/>
       <c r="K170" s="1"/>
     </row>
-    <row r="171" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="7:11">
       <c r="J171" s="2"/>
       <c r="K171" s="1"/>
     </row>
-    <row r="172" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="7:11">
       <c r="J172" s="2"/>
       <c r="K172" s="1"/>
     </row>
-    <row r="173" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="7:11">
       <c r="J173" s="2"/>
       <c r="K173" s="1"/>
     </row>
-    <row r="174" spans="7:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="7:11">
       <c r="J174" s="2"/>
       <c r="K174" s="1"/>
     </row>
-    <row r="176" spans="7:11" x14ac:dyDescent="0.2">
-      <c r="G176" s="169"/>
-      <c r="H176" s="169"/>
-    </row>
-    <row r="177" spans="7:8" x14ac:dyDescent="0.2">
-      <c r="G177" s="169"/>
-      <c r="H177" s="169"/>
+    <row r="176" spans="7:11">
+      <c r="G176" s="168"/>
+      <c r="H176" s="168"/>
+    </row>
+    <row r="177" spans="7:8">
+      <c r="G177" s="168"/>
+      <c r="H177" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -20713,7 +20764,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFFF4F9-97DA-0445-9F68-74756A3E2648}">
   <dimension ref="A1:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58.6640625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -20721,535 +20772,535 @@
     <col min="4" max="4" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+    <row r="1" spans="1:4" ht="24">
+      <c r="A1" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="151">
+      <c r="B1" s="150">
         <v>4991.0799999999981</v>
       </c>
-      <c r="C1" s="156">
+      <c r="C1" s="155">
         <v>0.5</v>
       </c>
-      <c r="D1" s="157">
+      <c r="D1" s="156">
         <v>0.01</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A2" s="150" t="s">
+    <row r="2" spans="1:4" ht="24">
+      <c r="A2" s="149" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="151">
+      <c r="B2" s="150">
         <v>88872.295000000173</v>
       </c>
-      <c r="C2" s="156">
+      <c r="C2" s="155">
         <v>0.5</v>
       </c>
-      <c r="D2" s="157">
+      <c r="D2" s="156">
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A3" s="150" t="s">
+    <row r="3" spans="1:4" ht="24">
+      <c r="A3" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="151">
+      <c r="B3" s="150">
         <v>2985</v>
       </c>
-      <c r="C3" s="156">
+      <c r="C3" s="155">
         <v>0.5</v>
       </c>
-      <c r="D3" s="157">
+      <c r="D3" s="156">
         <v>8.4083959293394767E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A4" s="150" t="s">
+    <row r="4" spans="1:4" ht="24">
+      <c r="A4" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="151">
-        <v>0</v>
-      </c>
-      <c r="C4" s="156">
+      <c r="B4" s="150">
+        <v>0</v>
+      </c>
+      <c r="C4" s="155">
         <v>0.5</v>
       </c>
-      <c r="D4" s="157">
+      <c r="D4" s="156">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A5" s="150" t="s">
+    <row r="5" spans="1:4" ht="24">
+      <c r="A5" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="151">
+      <c r="B5" s="150">
         <v>144052.08999999997</v>
       </c>
-      <c r="C5" s="156">
+      <c r="C5" s="155">
         <v>0.5</v>
       </c>
-      <c r="D5" s="157">
+      <c r="D5" s="156">
         <v>8.6167918586789544E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="150" t="s">
+    <row r="6" spans="1:4" ht="24">
+      <c r="A6" s="149" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="151">
+      <c r="B6" s="150">
         <v>87099.612182495111</v>
       </c>
-      <c r="C6" s="156">
+      <c r="C6" s="155">
         <v>0.5</v>
       </c>
-      <c r="D6" s="157">
+      <c r="D6" s="156">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A7" s="150" t="s">
+    <row r="7" spans="1:4" ht="24">
+      <c r="A7" s="149" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="152">
+      <c r="B7" s="151">
         <v>27059.240058898926</v>
       </c>
-      <c r="C7" s="156">
+      <c r="C7" s="155">
         <v>0.5</v>
       </c>
-      <c r="D7" s="156">
+      <c r="D7" s="155">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A8" s="150" t="s">
+    <row r="8" spans="1:4" ht="24">
+      <c r="A8" s="149" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="152">
+      <c r="B8" s="151">
         <v>129475.38462294932</v>
       </c>
-      <c r="C8" s="156">
+      <c r="C8" s="155">
         <v>0.68412600000000001</v>
       </c>
-      <c r="D8" s="156">
+      <c r="D8" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A9" s="150" t="s">
+    <row r="9" spans="1:4" ht="24">
+      <c r="A9" s="149" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="151">
+      <c r="B9" s="150">
         <v>132791.454</v>
       </c>
-      <c r="C9" s="158">
+      <c r="C9" s="157">
         <v>0.68410599999999999</v>
       </c>
-      <c r="D9" s="156">
+      <c r="D9" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A10" s="150" t="s">
+    <row r="10" spans="1:4" ht="24">
+      <c r="A10" s="149" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="151">
+      <c r="B10" s="150">
         <v>18351.4911288</v>
       </c>
-      <c r="C10" s="158">
+      <c r="C10" s="157">
         <v>0.62109999999999999</v>
       </c>
-      <c r="D10" s="156">
+      <c r="D10" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A11" s="150" t="s">
+    <row r="11" spans="1:4" ht="24">
+      <c r="A11" s="149" t="s">
         <v>151</v>
       </c>
-      <c r="B11" s="151">
+      <c r="B11" s="150">
         <v>5359.78701</v>
       </c>
-      <c r="C11" s="158">
+      <c r="C11" s="157">
         <v>0.61180000000000001</v>
       </c>
-      <c r="D11" s="156">
+      <c r="D11" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A12" s="150" t="s">
+    <row r="12" spans="1:4" ht="24">
+      <c r="A12" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="151">
-        <v>0</v>
-      </c>
-      <c r="C12" s="158">
+      <c r="B12" s="150">
+        <v>0</v>
+      </c>
+      <c r="C12" s="157">
         <v>0.6099</v>
       </c>
-      <c r="D12" s="156">
+      <c r="D12" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A13" s="150" t="s">
+    <row r="13" spans="1:4" ht="24">
+      <c r="A13" s="149" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="152">
+      <c r="B13" s="151">
         <v>6393.6610499999997</v>
       </c>
-      <c r="C13" s="156">
+      <c r="C13" s="155">
         <v>0.61070000000000002</v>
       </c>
-      <c r="D13" s="156">
+      <c r="D13" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A14" s="150" t="s">
+    <row r="14" spans="1:4" ht="24">
+      <c r="A14" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="B14" s="152">
-        <v>0</v>
-      </c>
-      <c r="C14" s="156">
+      <c r="B14" s="151">
+        <v>0</v>
+      </c>
+      <c r="C14" s="155">
         <v>0.56729999999999992</v>
       </c>
-      <c r="D14" s="156">
+      <c r="D14" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A15" s="150" t="s">
+    <row r="15" spans="1:4" ht="24">
+      <c r="A15" s="149" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="152">
+      <c r="B15" s="151">
         <v>152453.07</v>
       </c>
-      <c r="C15" s="156">
+      <c r="C15" s="155">
         <v>0.36777300000000002</v>
       </c>
-      <c r="D15" s="156">
+      <c r="D15" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A16" s="143" t="s">
+    <row r="16" spans="1:4" ht="24">
+      <c r="A16" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="153">
+      <c r="B16" s="152">
         <v>107865.3576</v>
       </c>
-      <c r="C16" s="159">
-        <v>0</v>
-      </c>
-      <c r="D16" s="156">
+      <c r="C16" s="158">
+        <v>0</v>
+      </c>
+      <c r="D16" s="155">
         <v>0.01</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A17" s="143" t="s">
+    <row r="17" spans="1:4" ht="24">
+      <c r="A17" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="153">
-        <v>0</v>
-      </c>
-      <c r="C17" s="144">
-        <v>0</v>
-      </c>
-      <c r="D17" s="152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A18" s="145" t="s">
+      <c r="B17" s="152">
+        <v>0</v>
+      </c>
+      <c r="C17" s="143">
+        <v>0</v>
+      </c>
+      <c r="D17" s="151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="24">
+      <c r="A18" s="144" t="s">
         <v>166</v>
       </c>
-      <c r="B18" s="154">
+      <c r="B18" s="153">
         <v>0.01</v>
       </c>
-      <c r="C18" s="146">
-        <v>0</v>
-      </c>
-      <c r="D18" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A19" s="145" t="s">
+      <c r="C18" s="145">
+        <v>0</v>
+      </c>
+      <c r="D18" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="24">
+      <c r="A19" s="144" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="154">
-        <v>0</v>
-      </c>
-      <c r="C19" s="146">
-        <v>0</v>
-      </c>
-      <c r="D19" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A20" s="145" t="s">
+      <c r="B19" s="153">
+        <v>0</v>
+      </c>
+      <c r="C19" s="145">
+        <v>0</v>
+      </c>
+      <c r="D19" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="24">
+      <c r="A20" s="144" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="154">
+      <c r="B20" s="153">
         <v>5.5270451317286735E-3</v>
       </c>
-      <c r="C20" s="146">
-        <v>0</v>
-      </c>
-      <c r="D20" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A21" s="145" t="s">
+      <c r="C20" s="145">
+        <v>0</v>
+      </c>
+      <c r="D20" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="24">
+      <c r="A21" s="144" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="154">
+      <c r="B21" s="153">
         <v>2.0286666666666665E-2</v>
       </c>
-      <c r="C21" s="146">
-        <v>0</v>
-      </c>
-      <c r="D21" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A22" s="145" t="s">
+      <c r="C21" s="145">
+        <v>0</v>
+      </c>
+      <c r="D21" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="24">
+      <c r="A22" s="144" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="154">
+      <c r="B22" s="153">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C22" s="146">
-        <v>0</v>
-      </c>
-      <c r="D22" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A23" s="145" t="s">
+      <c r="C22" s="145">
+        <v>0</v>
+      </c>
+      <c r="D22" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="24">
+      <c r="A23" s="144" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="154">
+      <c r="B23" s="153">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="C23" s="146">
-        <v>0</v>
-      </c>
-      <c r="D23" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A24" s="145" t="s">
+      <c r="C23" s="145">
+        <v>0</v>
+      </c>
+      <c r="D23" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="24">
+      <c r="A24" s="144" t="s">
         <v>168</v>
       </c>
-      <c r="B24" s="154">
-        <v>0</v>
-      </c>
-      <c r="C24" s="146">
-        <v>0</v>
-      </c>
-      <c r="D24" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A25" s="145" t="s">
+      <c r="B24" s="153">
+        <v>0</v>
+      </c>
+      <c r="C24" s="145">
+        <v>0</v>
+      </c>
+      <c r="D24" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="24">
+      <c r="A25" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="154">
-        <v>0</v>
-      </c>
-      <c r="C25" s="146">
-        <v>0</v>
-      </c>
-      <c r="D25" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A26" s="145" t="s">
+      <c r="B25" s="153">
+        <v>0</v>
+      </c>
+      <c r="C25" s="145">
+        <v>0</v>
+      </c>
+      <c r="D25" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="24">
+      <c r="A26" s="144" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="154">
-        <v>0</v>
-      </c>
-      <c r="C26" s="146">
-        <v>0</v>
-      </c>
-      <c r="D26" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A27" s="145" t="s">
+      <c r="B26" s="153">
+        <v>0</v>
+      </c>
+      <c r="C26" s="145">
+        <v>0</v>
+      </c>
+      <c r="D26" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="24">
+      <c r="A27" s="144" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="154">
+      <c r="B27" s="153">
         <v>8.6167918586789544E-2</v>
       </c>
-      <c r="C27" s="146">
-        <v>0</v>
-      </c>
-      <c r="D27" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A28" s="145" t="s">
+      <c r="C27" s="145">
+        <v>0</v>
+      </c>
+      <c r="D27" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="24">
+      <c r="A28" s="144" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="154">
+      <c r="B28" s="153">
         <v>8.199999999999999E-2</v>
       </c>
-      <c r="C28" s="146">
-        <v>0</v>
-      </c>
-      <c r="D28" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A29" s="145" t="s">
+      <c r="C28" s="145">
+        <v>0</v>
+      </c>
+      <c r="D28" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="24">
+      <c r="A29" s="144" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="154">
+      <c r="B29" s="153">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C29" s="146">
-        <v>0</v>
-      </c>
-      <c r="D29" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A30" s="145" t="s">
+      <c r="C29" s="145">
+        <v>0</v>
+      </c>
+      <c r="D29" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="24">
+      <c r="A30" s="144" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="154">
+      <c r="B30" s="153">
         <v>7.0699999999999999E-3</v>
       </c>
-      <c r="C30" s="146">
-        <v>0</v>
-      </c>
-      <c r="D30" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A31" s="145" t="s">
+      <c r="C30" s="145">
+        <v>0</v>
+      </c>
+      <c r="D30" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="24">
+      <c r="A31" s="144" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="154">
+      <c r="B31" s="153">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C31" s="146">
-        <v>0</v>
-      </c>
-      <c r="D31" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A32" s="145" t="s">
+      <c r="C31" s="145">
+        <v>0</v>
+      </c>
+      <c r="D31" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="24">
+      <c r="A32" s="144" t="s">
         <v>138</v>
       </c>
-      <c r="B32" s="174">
+      <c r="B32" s="173">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="C32" s="146">
-        <v>0</v>
-      </c>
-      <c r="D32" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A33" s="148" t="s">
+      <c r="C32" s="145">
+        <v>0</v>
+      </c>
+      <c r="D32" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="24">
+      <c r="A33" s="147" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="154">
+      <c r="B33" s="153">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C33" s="149">
-        <v>0</v>
-      </c>
-      <c r="D33" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A34" s="148" t="s">
+      <c r="C33" s="148">
+        <v>0</v>
+      </c>
+      <c r="D33" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="24">
+      <c r="A34" s="147" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="154">
-        <v>0</v>
-      </c>
-      <c r="C34" s="149">
-        <v>0</v>
-      </c>
-      <c r="D34" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A35" s="148" t="s">
+      <c r="B34" s="153">
+        <v>0</v>
+      </c>
+      <c r="C34" s="148">
+        <v>0</v>
+      </c>
+      <c r="D34" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="24">
+      <c r="A35" s="147" t="s">
         <v>128</v>
       </c>
-      <c r="B35" s="154">
+      <c r="B35" s="153">
         <v>0.01</v>
       </c>
-      <c r="C35" s="149">
-        <v>0</v>
-      </c>
-      <c r="D35" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A36" s="148" t="s">
+      <c r="C35" s="148">
+        <v>0</v>
+      </c>
+      <c r="D35" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="24">
+      <c r="A36" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="154">
+      <c r="B36" s="153">
         <v>9.7942392473118284E-2</v>
       </c>
-      <c r="C36" s="149">
-        <v>0</v>
-      </c>
-      <c r="D36" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A37" s="155" t="s">
+      <c r="C36" s="148">
+        <v>0</v>
+      </c>
+      <c r="D36" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="24">
+      <c r="A37" s="154" t="s">
         <v>131</v>
       </c>
-      <c r="B37" s="147">
-        <v>0</v>
-      </c>
-      <c r="C37" s="156">
-        <v>0</v>
-      </c>
-      <c r="D37" s="147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A38" s="155" t="s">
+      <c r="B37" s="146">
+        <v>0</v>
+      </c>
+      <c r="C37" s="155">
+        <v>0</v>
+      </c>
+      <c r="D37" s="146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="24">
+      <c r="A38" s="154" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="147">
-        <v>0</v>
-      </c>
-      <c r="C38" s="156">
-        <v>0</v>
-      </c>
-      <c r="D38" s="147">
+      <c r="B38" s="146">
+        <v>0</v>
+      </c>
+      <c r="C38" s="155">
+        <v>0</v>
+      </c>
+      <c r="D38" s="146">
         <v>0</v>
       </c>
     </row>
@@ -21260,8 +21311,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731AE742-D316-A04E-A3DB-C52263974828}">
-  <dimension ref="B2:Q58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:Q64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="53.5" customWidth="1"/>
@@ -21269,21 +21320,21 @@
     <col min="13" max="14" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="20" x14ac:dyDescent="0.25">
-      <c r="B2" s="202" t="s">
+    <row r="2" spans="2:17" ht="20">
+      <c r="B2" s="207" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="F2" s="202" t="s">
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="F2" s="207" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="202"/>
-      <c r="H2" s="202"/>
-      <c r="J2" s="203" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="J2" s="208" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="204"/>
+      <c r="K2" s="209"/>
       <c r="L2" s="108"/>
       <c r="M2" s="109" t="s">
         <v>145</v>
@@ -21292,7 +21343,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" ht="19">
       <c r="B3" s="105" t="s">
         <v>142</v>
       </c>
@@ -21321,7 +21372,7 @@
       <c r="M3" s="113"/>
       <c r="N3" s="113"/>
     </row>
-    <row r="4" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" ht="19">
       <c r="B4" s="105" t="s">
         <v>14</v>
       </c>
@@ -21333,14 +21384,14 @@
         <f>IF(Utilidad!C1&gt;1,Utilidad!C1/100,Utilidad!C1)</f>
         <v>0.39119999999999999</v>
       </c>
-      <c r="F4" s="293" t="s">
+      <c r="F4" s="202" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="106">
         <f>Utilidad!B1</f>
         <v>88507</v>
       </c>
-      <c r="H4" s="193">
+      <c r="H4" s="192">
         <f>IF(Utilidad!D1&gt;1,Utilidad!D1/100,Utilidad!D1)</f>
         <v>0.38135957855999997</v>
       </c>
@@ -21362,7 +21413,7 @@
         <v>2.5154451533742395E-2</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" ht="19">
       <c r="B5" s="105" t="s">
         <v>15</v>
       </c>
@@ -21374,14 +21425,14 @@
         <f>IF(Utilidad!C2&gt;1,Utilidad!C2/100,Utilidad!C2)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="293" t="s">
+      <c r="F5" s="202" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="106">
         <f>Utilidad!B2</f>
         <v>0</v>
       </c>
-      <c r="H5" s="193">
+      <c r="H5" s="192">
         <f>IF(Utilidad!D2&gt;1,Utilidad!D2/100,Utilidad!D2)</f>
         <v>0</v>
       </c>
@@ -21403,7 +21454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" ht="19">
       <c r="B6" s="105" t="s">
         <v>16</v>
       </c>
@@ -21415,14 +21466,14 @@
         <f>IF(Utilidad!C3&gt;1,Utilidad!C3/100,Utilidad!C3)</f>
         <v>0.18059999999999998</v>
       </c>
-      <c r="F6" s="293" t="s">
+      <c r="F6" s="202" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="106">
         <f>Utilidad!B3</f>
         <v>22063</v>
       </c>
-      <c r="H6" s="193">
+      <c r="H6" s="192">
         <f>IF(Utilidad!D3&gt;1,Utilidad!D3/100,Utilidad!D3)</f>
         <v>0.18112284201000001</v>
       </c>
@@ -21443,7 +21494,7 @@
         <v>2.8950277408639215E-3</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" ht="19">
       <c r="B7" s="105" t="s">
         <v>17</v>
       </c>
@@ -21455,14 +21506,14 @@
         <f>IF(Utilidad!C4&gt;1,Utilidad!C4/100,Utilidad!C4)</f>
         <v>0.4617</v>
       </c>
-      <c r="F7" s="293" t="s">
+      <c r="F7" s="202" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="106">
         <f>Utilidad!B4</f>
         <v>66444</v>
       </c>
-      <c r="H7" s="193">
+      <c r="H7" s="192">
         <f>IF(Utilidad!D4&gt;1,Utilidad!D4/100,Utilidad!D4)</f>
         <v>0.447849</v>
       </c>
@@ -21483,7 +21534,7 @@
         <v>3.0000000000000006E-2</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" ht="19">
       <c r="B8" s="105" t="s">
         <v>18</v>
       </c>
@@ -21495,14 +21546,14 @@
         <f>IF(Utilidad!C5&gt;1,Utilidad!C5/100,Utilidad!C5)</f>
         <v>0.4824</v>
       </c>
-      <c r="F8" s="293" t="s">
+      <c r="F8" s="202" t="s">
         <v>18</v>
       </c>
       <c r="G8" s="106">
         <f>Utilidad!B5</f>
         <v>43180</v>
       </c>
-      <c r="H8" s="193">
+      <c r="H8" s="192">
         <f>IF(Utilidad!D5&gt;1,Utilidad!D5/100,Utilidad!D5)</f>
         <v>0.4824</v>
       </c>
@@ -21523,7 +21574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" ht="19">
       <c r="B9" s="105" t="s">
         <v>19</v>
       </c>
@@ -21535,7 +21586,7 @@
         <f>IF(Utilidad!C6&gt;1,Utilidad!C6/100,Utilidad!C6)</f>
         <v>0.4824</v>
       </c>
-      <c r="F9" s="293" t="s">
+      <c r="F9" s="202" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="106">
@@ -21567,7 +21618,7 @@
         <v>57462.465614000001</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" ht="19">
       <c r="B10" s="105" t="s">
         <v>20</v>
       </c>
@@ -21586,7 +21637,7 @@
         <f>Utilidad!B7</f>
         <v>151419</v>
       </c>
-      <c r="H10" s="193">
+      <c r="H10" s="192">
         <f>IF(Utilidad!D7&gt;1,Utilidad!D7/100,Utilidad!D7)</f>
         <v>0.46058106021</v>
       </c>
@@ -21611,7 +21662,7 @@
         <v>57462.465614000001</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" ht="19">
       <c r="B11" s="105" t="s">
         <v>21</v>
       </c>
@@ -21630,7 +21681,7 @@
         <f>Utilidad!B8</f>
         <v>0</v>
       </c>
-      <c r="H11" s="193">
+      <c r="H11" s="192">
         <f>IF(Utilidad!D8&gt;1,Utilidad!D8/100,Utilidad!D8)</f>
         <v>0</v>
       </c>
@@ -21651,7 +21702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" ht="19">
       <c r="B12" s="105" t="s">
         <v>22</v>
       </c>
@@ -21666,11 +21717,11 @@
       <c r="F12" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="194">
+      <c r="G12" s="193">
         <f>Utilidad!B9</f>
         <v>47016</v>
       </c>
-      <c r="H12" s="193">
+      <c r="H12" s="192">
         <f>IF(Utilidad!D9&gt;1,Utilidad!D9/100,Utilidad!D9)</f>
         <v>0.34271999999999997</v>
       </c>
@@ -21691,7 +21742,7 @@
         <v>4.9999999999999829E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" ht="19">
       <c r="B13" s="105" t="s">
         <v>23</v>
       </c>
@@ -21703,14 +21754,14 @@
         <f>IF(Utilidad!C10&gt;1,Utilidad!C10/100,Utilidad!C10)</f>
         <v>0.17600000000000002</v>
       </c>
-      <c r="F13" s="293" t="s">
+      <c r="F13" s="202" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="194">
+      <c r="G13" s="193">
         <f>Utilidad!B10</f>
         <v>10446.465614000001</v>
       </c>
-      <c r="H13" s="193">
+      <c r="H13" s="192">
         <f>IF(Utilidad!D10&gt;1,Utilidad!D10/100,Utilidad!D10)</f>
         <v>0.18479999999999999</v>
       </c>
@@ -21731,7 +21782,7 @@
         <v>4.999999999999985E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" ht="19">
       <c r="B14" s="105" t="s">
         <v>24</v>
       </c>
@@ -21746,11 +21797,11 @@
       <c r="F14" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="194">
+      <c r="G14" s="193">
         <f>Utilidad!B11</f>
         <v>56684</v>
       </c>
-      <c r="H14" s="195">
+      <c r="H14" s="194">
         <f>IF(Utilidad!D11&gt;1,Utilidad!D11/100,Utilidad!D11)</f>
         <v>0.52903037013999998</v>
       </c>
@@ -21771,7 +21822,7 @@
         <v>1.7366096423076856E-2</v>
       </c>
     </row>
-    <row r="15" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" ht="19">
       <c r="B15" s="105" t="s">
         <v>25</v>
       </c>
@@ -21783,14 +21834,14 @@
         <f>IF(Utilidad!C12&gt;1,Utilidad!C12/100,Utilidad!C12)</f>
         <v>0.57600000000000007</v>
       </c>
-      <c r="F15" s="293" t="s">
+      <c r="F15" s="202" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="194">
+      <c r="G15" s="193">
         <f>Utilidad!B12</f>
         <v>37272.534385999999</v>
       </c>
-      <c r="H15" s="193">
+      <c r="H15" s="192">
         <f>IF(Utilidad!D12&gt;1,Utilidad!D12/100,Utilidad!D12)</f>
         <v>0.58244860585000002</v>
       </c>
@@ -21811,7 +21862,7 @@
         <v>1.1195496267361032E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="19" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" ht="19">
       <c r="B16" s="105" t="s">
         <v>2</v>
       </c>
@@ -21851,7 +21902,7 @@
         <v>9.7596482283465887E-4</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="19">
       <c r="B17" s="105" t="s">
         <v>26</v>
       </c>
@@ -21891,7 +21942,7 @@
         <v>8.0945642600073572E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" ht="19">
       <c r="B18" s="105" t="s">
         <v>27</v>
       </c>
@@ -21903,14 +21954,14 @@
         <f>IF(Utilidad!C15&gt;1,Utilidad!C15/100,Utilidad!C15)</f>
         <v>0.54459999999999997</v>
       </c>
-      <c r="F18" s="293" t="s">
+      <c r="F18" s="202" t="s">
         <v>27</v>
       </c>
       <c r="G18" s="106">
         <f>Utilidad!B15</f>
         <v>104882</v>
       </c>
-      <c r="H18" s="193">
+      <c r="H18" s="192">
         <f>IF(Utilidad!D15&gt;1,Utilidad!D15/100,Utilidad!D15)</f>
         <v>0.54249821000999998</v>
       </c>
@@ -21931,7 +21982,7 @@
         <v>3.8593279287550339E-3</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" ht="19">
       <c r="B19" s="105" t="s">
         <v>28</v>
       </c>
@@ -21943,14 +21994,14 @@
         <f>IF(Utilidad!C16&gt;1,Utilidad!C16/100,Utilidad!C16)</f>
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="F19" s="293" t="s">
+      <c r="F19" s="202" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="196">
+      <c r="G19" s="195">
         <f>Utilidad!B16</f>
         <v>37746.534385999999</v>
       </c>
-      <c r="H19" s="193">
+      <c r="H19" s="192">
         <f>IF(Utilidad!D16&gt;1,Utilidad!D16/100,Utilidad!D16)</f>
         <v>8.5890000000000008E-2</v>
       </c>
@@ -21971,7 +22022,7 @@
         <v>5.0000000000000128E-2</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" ht="19">
       <c r="B20" s="105" t="s">
         <v>31</v>
       </c>
@@ -21983,14 +22034,14 @@
         <f>IF(Utilidad!C17&gt;1,Utilidad!C17/100,Utilidad!C17)</f>
         <v>0.66599999999999993</v>
       </c>
-      <c r="F20" s="293" t="s">
+      <c r="F20" s="202" t="s">
         <v>31</v>
       </c>
       <c r="G20" s="106">
         <f>Utilidad!B17</f>
         <v>132791</v>
       </c>
-      <c r="H20" s="193">
+      <c r="H20" s="192">
         <f>IF(Utilidad!D17&gt;1,Utilidad!D17/100,Utilidad!D17)</f>
         <v>0.67602529614999995</v>
       </c>
@@ -22011,7 +22062,7 @@
         <v>1.5052997222222269E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" ht="19">
       <c r="B21" s="105" t="s">
         <v>32</v>
       </c>
@@ -22051,7 +22102,7 @@
         <v>0.41476205391891924</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" ht="19">
       <c r="B22" s="105" t="s">
         <v>33</v>
       </c>
@@ -22091,7 +22142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" ht="19">
       <c r="B23" s="105" t="s">
         <v>35</v>
       </c>
@@ -22131,7 +22182,7 @@
         <v>4.9668958101817618E-3</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" ht="19">
       <c r="B24" s="105" t="s">
         <v>36</v>
       </c>
@@ -22171,7 +22222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" ht="19">
       <c r="B25" s="105" t="s">
         <v>37</v>
       </c>
@@ -22211,7 +22262,7 @@
         <v>4.9668958101817618E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" ht="19">
       <c r="B26" s="105" t="s">
         <v>38</v>
       </c>
@@ -22251,7 +22302,7 @@
         <v>4.999999999999994E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" ht="19">
       <c r="B27" s="105" t="s">
         <v>39</v>
       </c>
@@ -22291,7 +22342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" ht="19">
       <c r="B28" s="105" t="s">
         <v>140</v>
       </c>
@@ -22331,7 +22382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" ht="19">
       <c r="B29" s="105" t="s">
         <v>40</v>
       </c>
@@ -22371,7 +22422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" ht="19">
       <c r="B30" s="105" t="s">
         <v>41</v>
       </c>
@@ -22411,7 +22462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" ht="19">
       <c r="B31" s="105" t="s">
         <v>42</v>
       </c>
@@ -22451,7 +22502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" ht="19">
       <c r="B32" s="105" t="s">
         <v>43</v>
       </c>
@@ -22491,7 +22542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" ht="19">
       <c r="B33" s="105" t="s">
         <v>139</v>
       </c>
@@ -22531,7 +22582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" ht="19">
       <c r="B34" s="105" t="s">
         <v>45</v>
       </c>
@@ -22571,7 +22622,7 @@
         <v>6.1068680802849539E-4</v>
       </c>
     </row>
-    <row r="35" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" ht="19">
       <c r="B35" s="105" t="s">
         <v>46</v>
       </c>
@@ -22611,7 +22662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" ht="19">
       <c r="B36" s="105" t="s">
         <v>47</v>
       </c>
@@ -22651,7 +22702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:14" ht="19">
       <c r="B37" s="105" t="s">
         <v>48</v>
       </c>
@@ -22691,7 +22742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" ht="19">
       <c r="B38" s="105" t="s">
         <v>49</v>
       </c>
@@ -22731,7 +22782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" ht="19">
       <c r="B39" s="105" t="s">
         <v>50</v>
       </c>
@@ -22771,7 +22822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:14" ht="19">
       <c r="B40" s="105" t="s">
         <v>51</v>
       </c>
@@ -22811,7 +22862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14" ht="19">
       <c r="B41" s="105" t="s">
         <v>52</v>
       </c>
@@ -22851,7 +22902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:14" ht="19">
       <c r="B42" s="105" t="s">
         <v>53</v>
       </c>
@@ -22891,7 +22942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" ht="19">
       <c r="B43" s="105" t="s">
         <v>54</v>
       </c>
@@ -22931,7 +22982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" ht="19">
       <c r="B44" s="105" t="s">
         <v>55</v>
       </c>
@@ -22971,7 +23022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" ht="19">
       <c r="B45" s="105" t="s">
         <v>56</v>
       </c>
@@ -23011,7 +23062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" ht="19">
       <c r="B46" s="105" t="s">
         <v>57</v>
       </c>
@@ -23051,7 +23102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14" ht="19">
       <c r="B47" s="105" t="s">
         <v>58</v>
       </c>
@@ -23091,7 +23142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14" ht="19">
       <c r="B48" s="105" t="s">
         <v>59</v>
       </c>
@@ -23131,7 +23182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14" ht="19">
       <c r="B49" s="105" t="s">
         <v>60</v>
       </c>
@@ -23171,7 +23222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14" ht="19">
       <c r="B50" s="105" t="s">
         <v>61</v>
       </c>
@@ -23211,7 +23262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" ht="19">
       <c r="B51" s="105" t="s">
         <v>62</v>
       </c>
@@ -23251,7 +23302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14" ht="19">
       <c r="B52" s="105" t="s">
         <v>63</v>
       </c>
@@ -23291,7 +23342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:14" ht="19">
       <c r="B53" s="105" t="s">
         <v>64</v>
       </c>
@@ -23331,7 +23382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:14" ht="19">
       <c r="B54" s="105" t="s">
         <v>65</v>
       </c>
@@ -23371,7 +23422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14" ht="19">
       <c r="B55" s="105" t="s">
         <v>66</v>
       </c>
@@ -23411,7 +23462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14" ht="19">
       <c r="B56" s="105" t="s">
         <v>67</v>
       </c>
@@ -23451,9 +23502,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14" ht="19">
       <c r="B57" s="105" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C57" s="106">
         <f>Utilidad!A54</f>
@@ -23491,7 +23542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14" ht="19">
       <c r="B58" s="105" t="s">
         <v>160</v>
       </c>
@@ -23528,6 +23579,246 @@
       </c>
       <c r="N58" s="116">
         <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:14" ht="19">
+      <c r="B59" s="105" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" s="106">
+        <f>Utilidad!A56</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="107">
+        <f>IF(Utilidad!C56&gt;1,Utilidad!C56/100,Utilidad!C56)</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="105" t="s">
+        <v>169</v>
+      </c>
+      <c r="G59" s="106">
+        <f>Utilidad!B56</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="107">
+        <f>IF(Utilidad!D56&gt;1,Utilidad!D56/100,Utilidad!D56)</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="114">
+        <f t="shared" ref="J59:J64" si="8">+IF(C59&lt;&gt;0,(G59-C59)/C59,ABS(G59-C59))</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="114">
+        <f t="shared" ref="K59:K64" si="9">+IF(D59&lt;&gt;0,(H59-D59)/D59,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="116">
+        <f t="shared" ref="M59:M64" si="10">+IF(J59&lt;&gt;"",ABS(J59),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="116">
+        <f t="shared" ref="N59:N64" si="11">+IF(J59&lt;&gt;"",ABS(K59),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:14" ht="19">
+      <c r="B60" s="105" t="s">
+        <v>170</v>
+      </c>
+      <c r="C60" s="106">
+        <f>Utilidad!A57</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="107">
+        <f>IF(Utilidad!C57&gt;1,Utilidad!C57/100,Utilidad!C57)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="105" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="106">
+        <f>Utilidad!B57</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="107">
+        <f>IF(Utilidad!D57&gt;1,Utilidad!D57/100,Utilidad!D57)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M60" s="116">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:14" ht="19">
+      <c r="B61" s="105" t="s">
+        <v>171</v>
+      </c>
+      <c r="C61" s="106">
+        <f>Utilidad!A58</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="107">
+        <f>IF(Utilidad!C58&gt;1,Utilidad!C58/100,Utilidad!C58)</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="105" t="s">
+        <v>171</v>
+      </c>
+      <c r="G61" s="106">
+        <f>Utilidad!B58</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="107">
+        <f>IF(Utilidad!D58&gt;1,Utilidad!D58/100,Utilidad!D58)</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M61" s="116">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:14" ht="19">
+      <c r="B62" s="105" t="s">
+        <v>172</v>
+      </c>
+      <c r="C62" s="106">
+        <f>Utilidad!A59</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="107">
+        <f>IF(Utilidad!C59&gt;1,Utilidad!C59/100,Utilidad!C59)</f>
+        <v>0</v>
+      </c>
+      <c r="F62" s="105" t="s">
+        <v>172</v>
+      </c>
+      <c r="G62" s="106">
+        <f>Utilidad!B59</f>
+        <v>0</v>
+      </c>
+      <c r="H62" s="107">
+        <f>IF(Utilidad!D59&gt;1,Utilidad!D59/100,Utilidad!D59)</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="116">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N62" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" ht="19">
+      <c r="B63" s="105" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" s="106">
+        <f>Utilidad!A60</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="107">
+        <f>IF(Utilidad!C60&gt;1,Utilidad!C60/100,Utilidad!C60)</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="105" t="s">
+        <v>173</v>
+      </c>
+      <c r="G63" s="106">
+        <f>Utilidad!B60</f>
+        <v>0</v>
+      </c>
+      <c r="H63" s="107">
+        <f>IF(Utilidad!D60&gt;1,Utilidad!D60/100,Utilidad!D60)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K63" s="114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M63" s="116">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N63" s="116">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" ht="19">
+      <c r="B64" s="105" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="106">
+        <f>Utilidad!A61</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="107">
+        <f>IF(Utilidad!C61&gt;1,Utilidad!C61/100,Utilidad!C61)</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="105" t="s">
+        <v>174</v>
+      </c>
+      <c r="G64" s="106">
+        <f>Utilidad!B61</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="107">
+        <f>IF(Utilidad!D61&gt;1,Utilidad!D61/100,Utilidad!D61)</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K64" s="114">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M64" s="116">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N64" s="116">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -23537,7 +23828,7 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="J2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J4:K58">
+  <conditionalFormatting sqref="J4:K64">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>ABS(J4)&gt;=10%</formula>
     </cfRule>
@@ -23553,8 +23844,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:S135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:S149"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="6" max="6" width="9.83203125" customWidth="1"/>
@@ -23568,8 +23859,8 @@
     <col min="16" max="16" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:19" ht="16" thickBot="1"/>
+    <row r="2" spans="2:19">
       <c r="B2" s="6"/>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -23589,19 +23880,19 @@
       <c r="R2" s="22"/>
       <c r="S2" s="23"/>
     </row>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:19">
       <c r="B3" s="7"/>
       <c r="S3" s="24"/>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:19">
       <c r="B4" s="7"/>
       <c r="S4" s="24"/>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:19">
       <c r="B5" s="7"/>
       <c r="S5" s="24"/>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:19">
       <c r="B6" s="7"/>
       <c r="E6" s="25">
         <f>+Utilidad!J62</f>
@@ -23609,7 +23900,7 @@
       </c>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:19">
       <c r="B7" s="7"/>
       <c r="E7" s="26">
         <f>+Utilidad!K62</f>
@@ -23629,7 +23920,7 @@
       </c>
       <c r="S7" s="24"/>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:19">
       <c r="B8" s="7"/>
       <c r="E8" s="28">
         <f>+Utilidad!L62</f>
@@ -23649,7 +23940,7 @@
       </c>
       <c r="S8" s="24"/>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:19">
       <c r="B9" s="7"/>
       <c r="I9" s="28">
         <f>+Utilidad!L65</f>
@@ -23665,7 +23956,7 @@
       </c>
       <c r="S9" s="24"/>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:19">
       <c r="B10" s="7"/>
       <c r="E10" s="25">
         <f>+Utilidad!J63</f>
@@ -23673,7 +23964,7 @@
       </c>
       <c r="S10" s="24"/>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:19">
       <c r="B11" s="7"/>
       <c r="E11" s="26">
         <f>+Utilidad!K63</f>
@@ -23685,7 +23976,7 @@
       </c>
       <c r="S11" s="24"/>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:19">
       <c r="B12" s="7"/>
       <c r="C12" s="25">
         <f>+Utilidad!J101</f>
@@ -23701,7 +23992,7 @@
       </c>
       <c r="S12" s="24"/>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:19">
       <c r="B13" s="7"/>
       <c r="C13" s="26">
         <f>+Utilidad!K101</f>
@@ -23721,7 +24012,7 @@
       </c>
       <c r="S13" s="24"/>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:19">
       <c r="B14" s="7"/>
       <c r="C14" s="28">
         <f>+Utilidad!L101</f>
@@ -23745,7 +24036,7 @@
       </c>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:19">
       <c r="B15" s="7"/>
       <c r="G15" s="34">
         <f>+Utilidad!J64</f>
@@ -23765,7 +24056,7 @@
       </c>
       <c r="S15" s="24"/>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:19">
       <c r="B16" s="7"/>
       <c r="E16" s="36">
         <f>+C12-E10</f>
@@ -23781,7 +24072,7 @@
       </c>
       <c r="S16" s="24"/>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:19">
       <c r="B17" s="7"/>
       <c r="G17" s="38">
         <f>G15*G16</f>
@@ -23789,7 +24080,7 @@
       </c>
       <c r="S17" s="24"/>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:19">
       <c r="B18" s="7"/>
       <c r="K18" s="25">
         <f>Flujos!C56</f>
@@ -23797,7 +24088,7 @@
       </c>
       <c r="S18" s="24"/>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:19">
       <c r="B19" s="7"/>
       <c r="K19" s="26">
         <f>Flujos!D56</f>
@@ -23805,7 +24096,7 @@
       </c>
       <c r="S19" s="24"/>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:19">
       <c r="B20" s="7"/>
       <c r="K20" s="28">
         <f>K18*K19</f>
@@ -23821,11 +24112,11 @@
       </c>
       <c r="S20" s="24"/>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:19">
       <c r="B21" s="7"/>
       <c r="S21" s="24"/>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:19">
       <c r="B22" s="7"/>
       <c r="L22" s="26">
         <f>+Utilidad!K76</f>
@@ -23841,7 +24132,7 @@
       </c>
       <c r="S22" s="24"/>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:19">
       <c r="B23" s="7"/>
       <c r="L23" s="28">
         <f>+Utilidad!L76</f>
@@ -23857,7 +24148,7 @@
       </c>
       <c r="S23" s="24"/>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:19">
       <c r="B24" s="7"/>
       <c r="M24" s="28">
         <f>+Utilidad!L74</f>
@@ -23873,18 +24164,18 @@
       </c>
       <c r="S24" s="24"/>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:19">
       <c r="B25" s="7"/>
-      <c r="C25" s="142"/>
+      <c r="C25" s="141"/>
       <c r="G25" s="25">
         <f>+Utilidad!J105</f>
         <v>0</v>
       </c>
       <c r="S25" s="24"/>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:19">
       <c r="B26" s="7"/>
-      <c r="C26" s="170">
+      <c r="C26" s="169">
         <f>+Utilidad!J103</f>
         <v>0</v>
       </c>
@@ -23894,9 +24185,9 @@
       </c>
       <c r="S26" s="24"/>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:19">
       <c r="B27" s="7"/>
-      <c r="C27" s="171">
+      <c r="C27" s="170">
         <f>+Utilidad!K103</f>
         <v>0</v>
       </c>
@@ -23910,9 +24201,9 @@
       </c>
       <c r="S27" s="24"/>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:19">
       <c r="B28" s="7"/>
-      <c r="C28" s="172">
+      <c r="C28" s="171">
         <f>+Utilidad!L103</f>
         <v>0</v>
       </c>
@@ -23922,9 +24213,9 @@
       </c>
       <c r="S28" s="24"/>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:19">
       <c r="B29" s="7"/>
-      <c r="C29" s="142"/>
+      <c r="C29" s="141"/>
       <c r="F29" s="39">
         <f>+C26-G25</f>
         <v>0</v>
@@ -23943,9 +24234,9 @@
       </c>
       <c r="S29" s="24"/>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:19">
       <c r="B30" s="7"/>
-      <c r="C30" s="142"/>
+      <c r="C30" s="141"/>
       <c r="I30" s="34">
         <f>+Utilidad!J77</f>
         <v>37746.534385999999</v>
@@ -23960,32 +24251,32 @@
       </c>
       <c r="S30" s="24"/>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:19">
       <c r="B31" s="7"/>
-      <c r="C31" s="142"/>
+      <c r="C31" s="141"/>
       <c r="I31" s="37">
         <f>+Utilidad!K77</f>
         <v>8.5890000000000008E-2</v>
       </c>
       <c r="S31" s="24"/>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:19">
       <c r="B32" s="7"/>
-      <c r="C32" s="142"/>
+      <c r="C32" s="141"/>
       <c r="I32" s="38">
         <f>I30*I31</f>
         <v>3242.0498384135403</v>
       </c>
       <c r="S32" s="24"/>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19">
       <c r="B33" s="7"/>
-      <c r="C33" s="142"/>
+      <c r="C33" s="141"/>
       <c r="S33" s="24"/>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19">
       <c r="B34" s="7"/>
-      <c r="C34" s="142"/>
+      <c r="C34" s="141"/>
       <c r="G34" s="25">
         <f>+Utilidad!J108</f>
         <v>0</v>
@@ -23993,9 +24284,9 @@
       <c r="L34" s="33"/>
       <c r="S34" s="24"/>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:19">
       <c r="B35" s="7"/>
-      <c r="C35" s="170">
+      <c r="C35" s="169">
         <f>+Utilidad!J106</f>
         <v>0</v>
       </c>
@@ -24007,9 +24298,9 @@
       <c r="N35" s="2"/>
       <c r="S35" s="24"/>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:19">
       <c r="B36" s="7"/>
-      <c r="C36" s="171">
+      <c r="C36" s="170">
         <f>+Utilidad!K106</f>
         <v>0</v>
       </c>
@@ -24019,55 +24310,55 @@
       </c>
       <c r="S36" s="24"/>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19">
       <c r="B37" s="7"/>
-      <c r="C37" s="172">
+      <c r="C37" s="171">
         <f>+Utilidad!L106</f>
         <v>0</v>
       </c>
       <c r="S37" s="24"/>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19">
       <c r="B38" s="7"/>
-      <c r="C38" s="142"/>
+      <c r="C38" s="141"/>
       <c r="F38" s="39">
         <f>+C35-G34</f>
         <v>0</v>
       </c>
       <c r="S38" s="24"/>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19">
       <c r="B39" s="7"/>
-      <c r="C39" s="142"/>
+      <c r="C39" s="141"/>
       <c r="K39" s="40">
         <f>K28-(I53+L53)</f>
         <v>3316</v>
       </c>
       <c r="S39" s="24"/>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:19">
       <c r="B40" s="7"/>
-      <c r="C40" s="142"/>
+      <c r="C40" s="141"/>
       <c r="S40" s="24"/>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:19">
       <c r="B41" s="7"/>
-      <c r="C41" s="142"/>
+      <c r="C41" s="141"/>
       <c r="S41" s="24"/>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19">
       <c r="B42" s="7"/>
-      <c r="C42" s="142"/>
+      <c r="C42" s="141"/>
       <c r="S42" s="24"/>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19">
       <c r="B43" s="7"/>
-      <c r="C43" s="142"/>
+      <c r="C43" s="141"/>
       <c r="S43" s="24"/>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19">
       <c r="B44" s="7"/>
-      <c r="C44" s="170">
+      <c r="C44" s="169">
         <f>+Utilidad!J109</f>
         <v>0</v>
       </c>
@@ -24077,9 +24368,9 @@
       </c>
       <c r="S44" s="24"/>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19">
       <c r="B45" s="7"/>
-      <c r="C45" s="171">
+      <c r="C45" s="170">
         <f>+Utilidad!K109</f>
         <v>0</v>
       </c>
@@ -24089,9 +24380,9 @@
       </c>
       <c r="S45" s="24"/>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19">
       <c r="B46" s="7"/>
-      <c r="C46" s="172">
+      <c r="C46" s="171">
         <f>+Utilidad!L109</f>
         <v>0</v>
       </c>
@@ -24101,43 +24392,43 @@
       </c>
       <c r="S46" s="24"/>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19">
       <c r="B47" s="7"/>
-      <c r="C47" s="142"/>
+      <c r="C47" s="141"/>
       <c r="S47" s="24"/>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19">
       <c r="B48" s="7"/>
-      <c r="C48" s="142"/>
+      <c r="C48" s="141"/>
       <c r="F48" s="39">
         <f>+C44-G44</f>
         <v>0</v>
       </c>
       <c r="S48" s="24"/>
     </row>
-    <row r="49" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:19">
       <c r="B49" s="7"/>
-      <c r="C49" s="142"/>
+      <c r="C49" s="141"/>
       <c r="S49" s="24"/>
     </row>
-    <row r="50" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:19">
       <c r="B50" s="7"/>
-      <c r="C50" s="142"/>
+      <c r="C50" s="141"/>
       <c r="S50" s="24"/>
     </row>
-    <row r="51" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:19">
       <c r="B51" s="7"/>
-      <c r="C51" s="142"/>
+      <c r="C51" s="141"/>
       <c r="S51" s="24"/>
     </row>
-    <row r="52" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:19">
       <c r="B52" s="7"/>
-      <c r="C52" s="142"/>
+      <c r="C52" s="141"/>
       <c r="S52" s="24"/>
     </row>
-    <row r="53" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:19">
       <c r="B53" s="7"/>
-      <c r="C53" s="142"/>
+      <c r="C53" s="141"/>
       <c r="I53" s="31">
         <f>+Utilidad!J82</f>
         <v>0</v>
@@ -24148,9 +24439,9 @@
       </c>
       <c r="S53" s="24"/>
     </row>
-    <row r="54" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:19">
       <c r="B54" s="7"/>
-      <c r="C54" s="170">
+      <c r="C54" s="169">
         <f>+Utilidad!J112</f>
         <v>0</v>
       </c>
@@ -24164,9 +24455,9 @@
       </c>
       <c r="S54" s="24"/>
     </row>
-    <row r="55" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:19">
       <c r="B55" s="7"/>
-      <c r="C55" s="171">
+      <c r="C55" s="170">
         <f>+Utilidad!K112</f>
         <v>0</v>
       </c>
@@ -24180,19 +24471,19 @@
       </c>
       <c r="S55" s="24"/>
     </row>
-    <row r="56" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:19">
       <c r="B56" s="7"/>
-      <c r="C56" s="172">
+      <c r="C56" s="171">
         <f>+Utilidad!L112</f>
         <v>0</v>
       </c>
       <c r="S56" s="24"/>
     </row>
-    <row r="57" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:19">
       <c r="B57" s="7"/>
       <c r="S57" s="24"/>
     </row>
-    <row r="58" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:19">
       <c r="B58" s="7"/>
       <c r="M58" s="27">
         <f>Flujos!G24</f>
@@ -24204,7 +24495,7 @@
       </c>
       <c r="S58" s="24"/>
     </row>
-    <row r="59" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:19">
       <c r="B59" s="7"/>
       <c r="M59" s="29">
         <f>Flujos!H24</f>
@@ -24212,7 +24503,7 @@
       </c>
       <c r="S59" s="24"/>
     </row>
-    <row r="60" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:19">
       <c r="B60" s="7"/>
       <c r="M60" s="30">
         <f>M59*M58</f>
@@ -24220,11 +24511,11 @@
       </c>
       <c r="S60" s="24"/>
     </row>
-    <row r="61" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:19">
       <c r="B61" s="7"/>
       <c r="S61" s="24"/>
     </row>
-    <row r="62" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:19">
       <c r="B62" s="7"/>
       <c r="C62" s="25">
         <f>Flujos!C55</f>
@@ -24232,7 +24523,7 @@
       </c>
       <c r="S62" s="24"/>
     </row>
-    <row r="63" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:19">
       <c r="B63" s="7"/>
       <c r="C63" s="26">
         <f>Flujos!D55</f>
@@ -24244,7 +24535,7 @@
       </c>
       <c r="S63" s="24"/>
     </row>
-    <row r="64" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:19">
       <c r="B64" s="7"/>
       <c r="C64" s="28">
         <f>C63*C62</f>
@@ -24256,7 +24547,7 @@
       </c>
       <c r="S64" s="24"/>
     </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:19">
       <c r="B65" s="7"/>
       <c r="L65" s="27">
         <f>Flujos!G25</f>
@@ -24268,7 +24559,7 @@
       </c>
       <c r="S65" s="24"/>
     </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:19">
       <c r="B66" s="7"/>
       <c r="L66" s="29">
         <f>Flujos!H25</f>
@@ -24276,7 +24567,7 @@
       </c>
       <c r="S66" s="24"/>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19">
       <c r="B67" s="7"/>
       <c r="L67" s="30">
         <f>L66*L65</f>
@@ -24292,7 +24583,7 @@
       </c>
       <c r="S67" s="24"/>
     </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:19">
       <c r="B68" s="7"/>
       <c r="O68" s="32">
         <f>Flujos!H28</f>
@@ -24300,7 +24591,7 @@
       </c>
       <c r="S68" s="24"/>
     </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:19">
       <c r="B69" s="7"/>
       <c r="O69" s="35">
         <f>O67*O68</f>
@@ -24308,7 +24599,7 @@
       </c>
       <c r="S69" s="24"/>
     </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:19">
       <c r="B70" s="7"/>
       <c r="H70" s="31">
         <f>Flujos!G29</f>
@@ -24320,7 +24611,7 @@
       </c>
       <c r="S70" s="24"/>
     </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:19">
       <c r="B71" s="7"/>
       <c r="H71" s="32">
         <f>Flujos!H29</f>
@@ -24332,7 +24623,7 @@
       </c>
       <c r="S71" s="24"/>
     </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:19">
       <c r="B72" s="7"/>
       <c r="H72" s="35">
         <f>H70*H71</f>
@@ -24344,11 +24635,11 @@
       </c>
       <c r="S72" s="24"/>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19">
       <c r="B73" s="7"/>
       <c r="S73" s="24"/>
     </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:19">
       <c r="B74" s="7"/>
       <c r="L74" s="31">
         <f>Flujos!G35</f>
@@ -24360,7 +24651,7 @@
       </c>
       <c r="S74" s="24"/>
     </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:19">
       <c r="B75" s="7"/>
       <c r="H75" s="31">
         <f>Flujos!G30</f>
@@ -24384,7 +24675,7 @@
       </c>
       <c r="S75" s="24"/>
     </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:19">
       <c r="B76" s="7"/>
       <c r="H76" s="32">
         <f>Flujos!H30</f>
@@ -24400,7 +24691,7 @@
       </c>
       <c r="S76" s="24"/>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19">
       <c r="B77" s="7"/>
       <c r="H77" s="35">
         <f>H76*H75</f>
@@ -24408,7 +24699,7 @@
       </c>
       <c r="S77" s="24"/>
     </row>
-    <row r="78" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:19">
       <c r="B78" s="7"/>
       <c r="L78" s="31">
         <f>Flujos!G36</f>
@@ -24416,7 +24707,7 @@
       </c>
       <c r="S78" s="24"/>
     </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:19">
       <c r="B79" s="7"/>
       <c r="L79" s="32">
         <f>Flujos!H36</f>
@@ -24428,7 +24719,7 @@
       </c>
       <c r="S79" s="24"/>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19">
       <c r="B80" s="7"/>
       <c r="L80" s="35">
         <f>L79*L78</f>
@@ -24440,7 +24731,7 @@
       </c>
       <c r="S80" s="24"/>
     </row>
-    <row r="81" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:19">
       <c r="B81" s="7"/>
       <c r="Q81" s="35">
         <f>Q79*Q80</f>
@@ -24448,7 +24739,7 @@
       </c>
       <c r="S81" s="24"/>
     </row>
-    <row r="82" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:19">
       <c r="B82" s="7"/>
       <c r="K82" s="31">
         <f>Flujos!G57</f>
@@ -24456,7 +24747,7 @@
       </c>
       <c r="S82" s="24"/>
     </row>
-    <row r="83" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:19">
       <c r="B83" s="7"/>
       <c r="K83" s="32">
         <f>Flujos!H57</f>
@@ -24464,7 +24755,7 @@
       </c>
       <c r="S83" s="24"/>
     </row>
-    <row r="84" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:19">
       <c r="B84" s="7"/>
       <c r="K84" s="35">
         <f>K82*K83</f>
@@ -24476,7 +24767,7 @@
       </c>
       <c r="S84" s="24"/>
     </row>
-    <row r="85" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:19">
       <c r="B85" s="7"/>
       <c r="H85" s="2">
         <f>5562+L74</f>
@@ -24488,7 +24779,7 @@
       </c>
       <c r="S85" s="24"/>
     </row>
-    <row r="86" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:19">
       <c r="B86" s="7"/>
       <c r="K86" s="31">
         <f>+Utilidad!J98</f>
@@ -24500,7 +24791,7 @@
       </c>
       <c r="S86" s="24"/>
     </row>
-    <row r="87" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:19">
       <c r="B87" s="7"/>
       <c r="K87" s="32">
         <f>+Utilidad!K98</f>
@@ -24508,7 +24799,7 @@
       </c>
       <c r="S87" s="24"/>
     </row>
-    <row r="88" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:19">
       <c r="B88" s="7"/>
       <c r="K88" s="35">
         <f>+Utilidad!L98</f>
@@ -24520,11 +24811,11 @@
       </c>
       <c r="S88" s="24"/>
     </row>
-    <row r="89" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:19">
       <c r="B89" s="7"/>
       <c r="S89" s="24"/>
     </row>
-    <row r="90" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:19">
       <c r="B90" s="7"/>
       <c r="L90" s="31">
         <f>+Utilidad!J97</f>
@@ -24532,7 +24823,7 @@
       </c>
       <c r="S90" s="24"/>
     </row>
-    <row r="91" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:19">
       <c r="B91" s="7"/>
       <c r="L91" s="32">
         <f>+Utilidad!K97</f>
@@ -24540,7 +24831,7 @@
       </c>
       <c r="S91" s="24"/>
     </row>
-    <row r="92" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:19">
       <c r="B92" s="7"/>
       <c r="L92" s="35">
         <f>+Utilidad!L97</f>
@@ -24548,11 +24839,11 @@
       </c>
       <c r="S92" s="24"/>
     </row>
-    <row r="93" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:19">
       <c r="B93" s="7"/>
       <c r="S93" s="24"/>
     </row>
-    <row r="94" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:19" ht="16" thickBot="1">
       <c r="B94" s="8"/>
       <c r="C94" s="42"/>
       <c r="D94" s="42"/>
@@ -24572,168 +24863,168 @@
       <c r="R94" s="42"/>
       <c r="S94" s="43"/>
     </row>
-    <row r="95" spans="2:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:19" ht="16">
       <c r="G95" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G96" s="206" t="s">
+    <row r="96" spans="2:19" ht="25.5" customHeight="1">
+      <c r="G96" s="226" t="s">
         <v>71</v>
       </c>
-      <c r="H96" s="206"/>
-      <c r="I96" s="207"/>
-      <c r="J96" s="208" t="s">
+      <c r="H96" s="226"/>
+      <c r="I96" s="227"/>
+      <c r="J96" s="228" t="s">
         <v>72</v>
       </c>
-      <c r="K96" s="208"/>
-      <c r="L96" s="208"/>
-      <c r="M96" s="209" t="s">
+      <c r="K96" s="228"/>
+      <c r="L96" s="228"/>
+      <c r="M96" s="229" t="s">
         <v>73</v>
       </c>
-      <c r="N96" s="209"/>
-      <c r="O96" s="209"/>
-      <c r="P96" s="209"/>
-    </row>
-    <row r="97" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G97" s="210" t="s">
+      <c r="N96" s="229"/>
+      <c r="O96" s="229"/>
+      <c r="P96" s="229"/>
+    </row>
+    <row r="97" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G97" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="H97" s="211"/>
+      <c r="H97" s="219"/>
       <c r="I97" s="21">
         <f>+E6</f>
         <v>88507</v>
       </c>
-      <c r="J97" s="212" t="s">
+      <c r="J97" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="K97" s="205"/>
+      <c r="K97" s="213"/>
       <c r="L97" s="10">
         <f>Flujos!G9</f>
         <v>-41795</v>
       </c>
-      <c r="M97" s="205" t="s">
+      <c r="M97" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="N97" s="205"/>
-      <c r="O97" s="205"/>
+      <c r="N97" s="213"/>
+      <c r="O97" s="213"/>
       <c r="P97" s="10">
         <f>+G15</f>
         <v>22063</v>
       </c>
     </row>
-    <row r="98" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G98" s="210" t="s">
+    <row r="98" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G98" s="218" t="s">
         <v>76</v>
       </c>
-      <c r="H98" s="211"/>
+      <c r="H98" s="219"/>
       <c r="I98" s="21">
         <f>+C12</f>
         <v>0</v>
       </c>
-      <c r="J98" s="205" t="s">
+      <c r="J98" s="213" t="s">
         <v>8</v>
       </c>
-      <c r="K98" s="205"/>
+      <c r="K98" s="213"/>
       <c r="L98" s="10">
         <f>Flujos!G17</f>
         <v>791</v>
       </c>
-      <c r="M98" s="205" t="s">
+      <c r="M98" s="213" t="s">
         <v>22</v>
       </c>
-      <c r="N98" s="205"/>
-      <c r="O98" s="205"/>
+      <c r="N98" s="213"/>
+      <c r="O98" s="213"/>
       <c r="P98" s="10">
         <f>+Q7</f>
         <v>47016</v>
       </c>
     </row>
-    <row r="99" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G99" s="210" t="s">
+    <row r="99" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G99" s="218" t="s">
         <v>77</v>
       </c>
-      <c r="H99" s="211"/>
+      <c r="H99" s="219"/>
       <c r="I99" s="21">
         <f>+H13</f>
         <v>43180</v>
       </c>
-      <c r="J99" s="205" t="s">
+      <c r="J99" s="213" t="s">
         <v>78</v>
       </c>
-      <c r="K99" s="205"/>
+      <c r="K99" s="213"/>
       <c r="L99" s="10">
         <v>0</v>
       </c>
-      <c r="M99" s="205" t="s">
+      <c r="M99" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="N99" s="205"/>
-      <c r="O99" s="205"/>
+      <c r="N99" s="213"/>
+      <c r="O99" s="213"/>
       <c r="P99" s="10">
         <f>+Q11</f>
         <v>10446.465614000001</v>
       </c>
     </row>
-    <row r="100" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G100" s="213" t="s">
+    <row r="100" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G100" s="216" t="s">
         <v>79</v>
       </c>
-      <c r="H100" s="214"/>
+      <c r="H100" s="217"/>
       <c r="I100" s="21">
         <f>+C26</f>
         <v>0</v>
       </c>
-      <c r="J100" s="205" t="s">
+      <c r="J100" s="213" t="s">
         <v>11</v>
       </c>
-      <c r="K100" s="205"/>
+      <c r="K100" s="213"/>
       <c r="L100" s="10">
         <f>Flujos!G21</f>
         <v>3316</v>
       </c>
-      <c r="M100" s="205" t="s">
+      <c r="M100" s="213" t="s">
         <v>80</v>
       </c>
-      <c r="N100" s="205"/>
-      <c r="O100" s="205"/>
+      <c r="N100" s="213"/>
+      <c r="O100" s="213"/>
       <c r="P100" s="10">
         <f>+I30</f>
         <v>37746.534385999999</v>
       </c>
     </row>
-    <row r="101" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G101" s="213" t="s">
+    <row r="101" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G101" s="216" t="s">
         <v>57</v>
       </c>
-      <c r="H101" s="214"/>
+      <c r="H101" s="217"/>
       <c r="I101" s="21">
         <f>+C35</f>
         <v>0</v>
       </c>
-      <c r="J101" s="205" t="s">
+      <c r="J101" s="213" t="s">
         <v>81</v>
       </c>
-      <c r="K101" s="205"/>
+      <c r="K101" s="213"/>
       <c r="L101" s="10">
         <f>Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="M101" s="205" t="s">
+      <c r="M101" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="N101" s="205"/>
-      <c r="O101" s="205"/>
+      <c r="N101" s="213"/>
+      <c r="O101" s="213"/>
       <c r="P101" s="10">
         <f>+M58</f>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G102" s="213" t="s">
+    <row r="102" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G102" s="216" t="s">
         <v>60</v>
       </c>
-      <c r="H102" s="214"/>
+      <c r="H102" s="217"/>
       <c r="I102" s="21">
         <f>+C44</f>
         <v>0</v>
@@ -24746,21 +25037,21 @@
         <f>Flujos!G44</f>
         <v>0</v>
       </c>
-      <c r="M102" s="205" t="s">
+      <c r="M102" s="213" t="s">
         <v>84</v>
       </c>
-      <c r="N102" s="205"/>
-      <c r="O102" s="205"/>
+      <c r="N102" s="213"/>
+      <c r="O102" s="213"/>
       <c r="P102" s="10">
         <f>+O63</f>
         <v>104386</v>
       </c>
     </row>
-    <row r="103" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G103" s="213" t="s">
+    <row r="103" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G103" s="216" t="s">
         <v>85</v>
       </c>
-      <c r="H103" s="214"/>
+      <c r="H103" s="217"/>
       <c r="I103" s="21">
         <f>+C54</f>
         <v>0</v>
@@ -24773,21 +25064,21 @@
         <f>Flujos!G47</f>
         <v>0</v>
       </c>
-      <c r="M103" s="205" t="s">
+      <c r="M103" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="N103" s="205"/>
-      <c r="O103" s="205"/>
+      <c r="N103" s="213"/>
+      <c r="O103" s="213"/>
       <c r="P103" s="10">
         <f>+O67</f>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G104" s="213" t="s">
+    <row r="104" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G104" s="216" t="s">
         <v>88</v>
       </c>
-      <c r="H104" s="214"/>
+      <c r="H104" s="217"/>
       <c r="I104" s="21">
         <f>+C62</f>
         <v>77372</v>
@@ -24800,21 +25091,21 @@
         <f>Flujos!G50</f>
         <v>0</v>
       </c>
-      <c r="M104" s="205" t="s">
+      <c r="M104" s="213" t="s">
         <v>44</v>
       </c>
-      <c r="N104" s="205"/>
-      <c r="O104" s="205"/>
+      <c r="N104" s="213"/>
+      <c r="O104" s="213"/>
       <c r="P104" s="10">
         <f>+O74</f>
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G105" s="213" t="s">
+    <row r="105" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G105" s="216" t="s">
         <v>90</v>
       </c>
-      <c r="H105" s="214"/>
+      <c r="H105" s="217"/>
       <c r="I105" s="21">
         <f>+H70</f>
         <v>0</v>
@@ -24827,44 +25118,44 @@
         <f>Flujos!G53</f>
         <v>0</v>
       </c>
-      <c r="M105" s="205" t="s">
+      <c r="M105" s="213" t="s">
         <v>92</v>
       </c>
-      <c r="N105" s="205"/>
-      <c r="O105" s="205"/>
+      <c r="N105" s="213"/>
+      <c r="O105" s="213"/>
       <c r="P105" s="10">
         <f>+O84</f>
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G106" s="213" t="s">
+    <row r="106" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G106" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="H106" s="214"/>
+      <c r="H106" s="217"/>
       <c r="I106" s="21">
         <f>+H75</f>
         <v>0</v>
       </c>
-      <c r="J106" s="205" t="s">
+      <c r="J106" s="213" t="s">
         <v>13</v>
       </c>
-      <c r="K106" s="205"/>
+      <c r="K106" s="213"/>
       <c r="L106" s="10">
         <f>Flujos!G42</f>
         <v>0</v>
       </c>
-      <c r="M106" s="205" t="s">
+      <c r="M106" s="213" t="s">
         <v>160</v>
       </c>
-      <c r="N106" s="205"/>
-      <c r="O106" s="205"/>
+      <c r="N106" s="213"/>
+      <c r="O106" s="213"/>
       <c r="P106" s="10">
         <f>Q79</f>
         <v>127</v>
       </c>
     </row>
-    <row r="107" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="7:16" ht="25.5" customHeight="1">
       <c r="G107" s="19" t="s">
         <v>94</v>
       </c>
@@ -24881,12 +25172,12 @@
         <f>Flujos!G26</f>
         <v>25089</v>
       </c>
-      <c r="M107" s="218"/>
-      <c r="N107" s="219"/>
-      <c r="O107" s="220"/>
+      <c r="M107" s="210"/>
+      <c r="N107" s="211"/>
+      <c r="O107" s="212"/>
       <c r="P107" s="10"/>
     </row>
-    <row r="108" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="7:16" ht="25.5" customHeight="1">
       <c r="G108" s="19" t="s">
         <v>96</v>
       </c>
@@ -24895,20 +25186,20 @@
         <f>+L78</f>
         <v>5360</v>
       </c>
-      <c r="J108" s="205" t="s">
+      <c r="J108" s="213" t="s">
         <v>12</v>
       </c>
-      <c r="K108" s="205"/>
+      <c r="K108" s="213"/>
       <c r="L108" s="10">
         <f>Flujos!G34</f>
         <v>27987</v>
       </c>
-      <c r="M108" s="218"/>
-      <c r="N108" s="219"/>
-      <c r="O108" s="220"/>
+      <c r="M108" s="210"/>
+      <c r="N108" s="211"/>
+      <c r="O108" s="212"/>
       <c r="P108" s="10"/>
     </row>
-    <row r="109" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="7:16" ht="25.5" customHeight="1">
       <c r="G109" s="19" t="s">
         <v>97</v>
       </c>
@@ -24917,617 +25208,800 @@
         <f>+K86</f>
         <v>0</v>
       </c>
-      <c r="J109" s="205" t="s">
+      <c r="J109" s="213" t="s">
         <v>10</v>
       </c>
-      <c r="K109" s="205"/>
+      <c r="K109" s="213"/>
       <c r="L109" s="10">
         <f>Flujos!G39</f>
         <v>6394</v>
       </c>
-      <c r="M109" s="218"/>
-      <c r="N109" s="219"/>
-      <c r="O109" s="220"/>
+      <c r="M109" s="210"/>
+      <c r="N109" s="211"/>
+      <c r="O109" s="212"/>
       <c r="P109" s="10"/>
     </row>
-    <row r="110" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G110" s="213" t="s">
+    <row r="110" spans="7:16" ht="25.5" customHeight="1">
+      <c r="G110" s="216" t="s">
         <v>98</v>
       </c>
-      <c r="H110" s="214"/>
+      <c r="H110" s="217"/>
       <c r="I110" s="21">
         <f>+L90</f>
         <v>6394</v>
       </c>
-      <c r="J110" s="205"/>
-      <c r="K110" s="205"/>
+      <c r="J110" s="213"/>
+      <c r="K110" s="213"/>
       <c r="L110" s="10"/>
-      <c r="M110" s="205"/>
-      <c r="N110" s="205"/>
-      <c r="O110" s="205"/>
+      <c r="M110" s="213"/>
+      <c r="N110" s="213"/>
+      <c r="O110" s="213"/>
       <c r="P110" s="10"/>
     </row>
-    <row r="111" spans="7:16" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G111" s="213" t="s">
-        <v>161</v>
-      </c>
-      <c r="H111" s="214"/>
+    <row r="111" spans="7:16" ht="26" customHeight="1">
+      <c r="G111" s="216" t="s">
+        <v>176</v>
+      </c>
+      <c r="H111" s="217"/>
       <c r="I111" s="21">
         <f>K82</f>
         <v>4403</v>
       </c>
-      <c r="J111" s="205"/>
-      <c r="K111" s="205"/>
+      <c r="J111" s="213"/>
+      <c r="K111" s="213"/>
       <c r="L111" s="10"/>
-      <c r="M111" s="205"/>
-      <c r="N111" s="205"/>
-      <c r="O111" s="205"/>
+      <c r="M111" s="213"/>
+      <c r="N111" s="213"/>
+      <c r="O111" s="213"/>
       <c r="P111" s="10"/>
     </row>
-    <row r="112" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G112" s="215" t="s">
+    <row r="112" spans="7:16">
+      <c r="G112" s="216" t="s">
+        <v>177</v>
+      </c>
+      <c r="H112" s="217"/>
+      <c r="I112" s="21">
+        <f>Flujos!G59</f>
+        <v>0</v>
+      </c>
+      <c r="J112" s="213"/>
+      <c r="K112" s="213"/>
+      <c r="L112" s="10"/>
+      <c r="M112" s="213"/>
+      <c r="N112" s="213"/>
+      <c r="O112" s="213"/>
+      <c r="P112" s="10"/>
+    </row>
+    <row r="113" spans="7:16">
+      <c r="G113" s="216" t="s">
+        <v>178</v>
+      </c>
+      <c r="H113" s="217"/>
+      <c r="I113" s="21">
+        <f>Flujos!G60</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="213"/>
+      <c r="K113" s="213"/>
+      <c r="L113" s="10"/>
+      <c r="M113" s="213"/>
+      <c r="N113" s="213"/>
+      <c r="O113" s="213"/>
+      <c r="P113" s="10"/>
+    </row>
+    <row r="114" spans="7:16">
+      <c r="G114" s="216" t="s">
+        <v>179</v>
+      </c>
+      <c r="H114" s="217"/>
+      <c r="I114" s="21">
+        <f>Flujos!G61</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="213"/>
+      <c r="K114" s="213"/>
+      <c r="L114" s="10"/>
+      <c r="M114" s="213"/>
+      <c r="N114" s="213"/>
+      <c r="O114" s="213"/>
+      <c r="P114" s="10"/>
+    </row>
+    <row r="115" spans="7:16">
+      <c r="G115" s="216" t="s">
+        <v>179</v>
+      </c>
+      <c r="H115" s="217"/>
+      <c r="I115" s="21">
+        <f>Flujos!G62</f>
+        <v>0</v>
+      </c>
+      <c r="J115" s="213"/>
+      <c r="K115" s="213"/>
+      <c r="L115" s="10"/>
+      <c r="M115" s="213"/>
+      <c r="N115" s="213"/>
+      <c r="O115" s="213"/>
+      <c r="P115" s="10"/>
+    </row>
+    <row r="116" spans="7:16">
+      <c r="G116" s="216" t="s">
+        <v>177</v>
+      </c>
+      <c r="H116" s="217"/>
+      <c r="I116" s="21">
+        <f>Flujos!G63</f>
+        <v>0</v>
+      </c>
+      <c r="J116" s="213"/>
+      <c r="K116" s="213"/>
+      <c r="L116" s="10"/>
+      <c r="M116" s="213"/>
+      <c r="N116" s="213"/>
+      <c r="O116" s="213"/>
+      <c r="P116" s="10"/>
+    </row>
+    <row r="117" spans="7:16">
+      <c r="G117" s="216" t="s">
+        <v>180</v>
+      </c>
+      <c r="H117" s="217"/>
+      <c r="I117" s="21">
+        <f>Flujos!G64</f>
+        <v>0</v>
+      </c>
+      <c r="J117" s="213"/>
+      <c r="K117" s="213"/>
+      <c r="L117" s="10"/>
+      <c r="M117" s="213"/>
+      <c r="N117" s="213"/>
+      <c r="O117" s="213"/>
+      <c r="P117" s="10"/>
+    </row>
+    <row r="118" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G118" s="214" t="s">
         <v>99</v>
       </c>
-      <c r="H112" s="216"/>
-      <c r="I112" s="12">
-        <f>+SUM(I97:I111)</f>
+      <c r="H118" s="215"/>
+      <c r="I118" s="12">
+        <f>+SUM(I97:I117)</f>
         <v>243567</v>
       </c>
-      <c r="J112" s="217" t="s">
+      <c r="J118" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="K112" s="217"/>
-      <c r="L112" s="13">
+      <c r="K118" s="225"/>
+      <c r="L118" s="13">
         <f>+SUM(L97:L110)</f>
         <v>21782</v>
       </c>
-      <c r="M112" s="217" t="s">
+      <c r="M118" s="225" t="s">
         <v>101</v>
       </c>
-      <c r="N112" s="217"/>
-      <c r="O112" s="217"/>
-      <c r="P112" s="12">
+      <c r="N118" s="225"/>
+      <c r="O118" s="225"/>
+      <c r="P118" s="12">
         <f>+SUM(P97:P110)</f>
         <v>221785</v>
       </c>
     </row>
-    <row r="113" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G113" s="14"/>
-      <c r="H113" s="14"/>
-      <c r="I113" s="14"/>
-      <c r="J113" s="14"/>
-      <c r="K113" s="14"/>
-      <c r="L113" s="14"/>
-      <c r="M113" s="14"/>
-      <c r="N113" s="14"/>
-      <c r="O113" s="14"/>
-      <c r="P113" s="14"/>
-    </row>
-    <row r="114" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G114" s="14"/>
-      <c r="H114" s="14"/>
-      <c r="I114" s="14"/>
-      <c r="J114" s="14"/>
-      <c r="K114" s="14"/>
-      <c r="L114" s="15" t="s">
+    <row r="119" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="14"/>
+      <c r="K119" s="14"/>
+      <c r="L119" s="14"/>
+      <c r="M119" s="14"/>
+      <c r="N119" s="14"/>
+      <c r="O119" s="14"/>
+      <c r="P119" s="14"/>
+    </row>
+    <row r="120" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G120" s="14"/>
+      <c r="J120" s="14"/>
+      <c r="K120" s="14"/>
+      <c r="L120" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="M114" s="16"/>
-      <c r="N114" s="17"/>
-      <c r="O114" s="16"/>
-      <c r="P114" s="18">
-        <f>+I112-L112-P112</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="7:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="G116" s="9" t="s">
+      <c r="M120" s="16"/>
+      <c r="N120" s="17"/>
+      <c r="O120" s="16"/>
+      <c r="P120" s="18">
+        <f>+I118-L118-P118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="7:16" ht="27.75" customHeight="1"/>
+    <row r="122" spans="7:16" ht="27.75" customHeight="1"/>
+    <row r="123" spans="7:16" ht="27.75" customHeight="1"/>
+    <row r="124" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G124" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="117" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G117" s="221" t="s">
+    <row r="125" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G125" s="220" t="s">
         <v>71</v>
       </c>
-      <c r="H117" s="221"/>
-      <c r="I117" s="222"/>
-      <c r="J117" s="223" t="s">
+      <c r="H125" s="220"/>
+      <c r="I125" s="221"/>
+      <c r="J125" s="222" t="s">
         <v>72</v>
       </c>
-      <c r="K117" s="223"/>
-      <c r="L117" s="223"/>
-      <c r="M117" s="224" t="s">
+      <c r="K125" s="222"/>
+      <c r="L125" s="222"/>
+      <c r="M125" s="223" t="s">
         <v>73</v>
       </c>
-      <c r="N117" s="224"/>
-      <c r="O117" s="224"/>
-      <c r="P117" s="224"/>
-    </row>
-    <row r="118" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G118" s="210" t="s">
+      <c r="N125" s="223"/>
+      <c r="O125" s="223"/>
+      <c r="P125" s="223"/>
+    </row>
+    <row r="126" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G126" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="H118" s="211"/>
-      <c r="I118" s="21">
+      <c r="H126" s="219"/>
+      <c r="I126" s="21">
         <f>+E8</f>
         <v>33752.992219609914</v>
       </c>
-      <c r="J118" s="212" t="s">
+      <c r="J126" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="K118" s="205"/>
-      <c r="L118" s="10">
+      <c r="K126" s="213"/>
+      <c r="L126" s="10">
         <f>Flujos!G9*Flujos!H9</f>
         <v>-19153.812600000001</v>
       </c>
-      <c r="M118" s="205" t="s">
+      <c r="M126" s="213" t="s">
         <v>75</v>
       </c>
-      <c r="N118" s="205"/>
-      <c r="O118" s="205"/>
-      <c r="P118" s="10">
+      <c r="N126" s="213"/>
+      <c r="O126" s="213"/>
+      <c r="P126" s="10">
         <f>+G17</f>
         <v>3996.1132632666299</v>
       </c>
     </row>
-    <row r="119" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G119" s="210" t="s">
+    <row r="127" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G127" s="197" t="s">
         <v>76</v>
       </c>
-      <c r="H119" s="211"/>
-      <c r="I119" s="21">
+      <c r="H127" s="298"/>
+      <c r="I127" s="21">
         <f>+C14</f>
         <v>0</v>
       </c>
-      <c r="J119" s="205" t="s">
+      <c r="J127" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K119" s="205"/>
-      <c r="L119" s="10">
+      <c r="K127" s="11"/>
+      <c r="L127" s="10">
         <f>Flujos!G17*Flujos!H17</f>
         <v>465.64825059536003</v>
       </c>
-      <c r="M119" s="205" t="s">
+      <c r="M127" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="N119" s="205"/>
-      <c r="O119" s="205"/>
-      <c r="P119" s="10">
+      <c r="N127" s="11"/>
+      <c r="O127" s="11"/>
+      <c r="P127" s="10">
         <f>+Q9</f>
         <v>16113.323519999998</v>
       </c>
     </row>
-    <row r="120" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G120" s="210" t="s">
+    <row r="128" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G128" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="H120" s="211"/>
-      <c r="I120" s="21">
+      <c r="H128" s="198"/>
+      <c r="I128" s="21">
         <f>+H15</f>
         <v>20830.031999999999</v>
       </c>
-      <c r="J120" s="205" t="s">
+      <c r="J128" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="K120" s="205"/>
-      <c r="L120" s="10">
-        <v>0</v>
-      </c>
-      <c r="M120" s="205" t="s">
+      <c r="K128" s="11"/>
+      <c r="L128" s="10">
+        <v>0</v>
+      </c>
+      <c r="M128" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="N120" s="205"/>
-      <c r="O120" s="205"/>
-      <c r="P120" s="10">
+      <c r="N128" s="11"/>
+      <c r="O128" s="11"/>
+      <c r="P128" s="10">
         <f>+Q13</f>
         <v>1930.5068454672</v>
       </c>
     </row>
-    <row r="121" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G121" s="213" t="s">
+    <row r="129" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G129" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H121" s="214"/>
-      <c r="I121" s="21">
+      <c r="H129" s="20"/>
+      <c r="I129" s="21">
         <f>+C28</f>
         <v>0</v>
       </c>
-      <c r="J121" s="205" t="s">
+      <c r="J129" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="K121" s="205"/>
-      <c r="L121" s="10">
+      <c r="K129" s="11"/>
+      <c r="L129" s="10">
         <f>Flujos!G21*Flujos!H21</f>
         <v>3124.4397465495604</v>
       </c>
-      <c r="M121" s="205" t="s">
+      <c r="M129" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="N121" s="205"/>
-      <c r="O121" s="205"/>
-      <c r="P121" s="10">
+      <c r="N129" s="11"/>
+      <c r="O129" s="11"/>
+      <c r="P129" s="10">
         <f>+I32</f>
         <v>3242.0498384135403</v>
       </c>
     </row>
-    <row r="122" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G122" s="213" t="s">
+    <row r="130" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G130" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H122" s="214"/>
-      <c r="I122" s="21">
+      <c r="H130" s="20"/>
+      <c r="I130" s="21">
         <f>+C37</f>
         <v>0</v>
       </c>
-      <c r="J122" s="205" t="s">
+      <c r="J130" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K122" s="205"/>
-      <c r="L122" s="10">
+      <c r="K130" s="11"/>
+      <c r="L130" s="10">
         <f>Flujos!G31*Flujos!H31</f>
         <v>0</v>
       </c>
-      <c r="M122" s="205" t="s">
+      <c r="M130" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="N122" s="205"/>
-      <c r="O122" s="205"/>
-      <c r="P122" s="10">
+      <c r="N130" s="11"/>
+      <c r="O130" s="11"/>
+      <c r="P130" s="10">
         <f>+M60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G123" s="213" t="s">
+    <row r="131" spans="7:16" ht="27.75" customHeight="1">
+      <c r="G131" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H123" s="214"/>
-      <c r="I123" s="21">
+      <c r="H131" s="20"/>
+      <c r="I131" s="21">
         <f>+C46</f>
         <v>0</v>
       </c>
-      <c r="J123" s="11" t="s">
+      <c r="J131" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K123" s="11"/>
-      <c r="L123" s="10">
+      <c r="K131" s="11"/>
+      <c r="L131" s="10">
         <f>Flujos!G44*Flujos!H44</f>
         <v>0</v>
       </c>
-      <c r="M123" s="205" t="s">
+      <c r="M131" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="N123" s="205"/>
-      <c r="O123" s="205"/>
-      <c r="P123" s="10">
+      <c r="N131" s="11"/>
+      <c r="O131" s="11"/>
+      <c r="P131" s="10">
         <f>+O65</f>
         <v>69103.532000000007</v>
       </c>
     </row>
-    <row r="124" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G124" s="213" t="s">
+    <row r="132" spans="7:16" ht="23" customHeight="1">
+      <c r="G132" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="H124" s="214"/>
-      <c r="I124" s="21">
+      <c r="H132" s="20"/>
+      <c r="I132" s="21">
         <f>+C56</f>
         <v>0</v>
       </c>
-      <c r="J124" s="11" t="s">
+      <c r="J132" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="K124" s="11"/>
-      <c r="L124" s="10">
+      <c r="K132" s="11"/>
+      <c r="L132" s="10">
         <f>Flujos!G47*Flujos!H47</f>
         <v>0</v>
       </c>
-      <c r="M124" s="205" t="s">
+      <c r="M132" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="N124" s="205"/>
-      <c r="O124" s="205"/>
-      <c r="P124" s="10">
+      <c r="N132" s="11"/>
+      <c r="O132" s="11"/>
+      <c r="P132" s="10">
         <f>+O69</f>
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G125" s="213" t="s">
+    <row r="133" spans="7:16">
+      <c r="G133" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="H125" s="214"/>
-      <c r="I125" s="21">
+      <c r="H133" s="20"/>
+      <c r="I133" s="21">
         <f>C64</f>
         <v>41780.880000000005</v>
       </c>
-      <c r="J125" s="11" t="s">
+      <c r="J133" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="K125" s="11"/>
-      <c r="L125" s="10">
+      <c r="K133" s="11"/>
+      <c r="L133" s="10">
         <f>Flujos!G50*Flujos!H50</f>
         <v>0</v>
       </c>
-      <c r="M125" s="205" t="s">
+      <c r="M133" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N125" s="205"/>
-      <c r="O125" s="205"/>
-      <c r="P125" s="10">
+      <c r="N133" s="11"/>
+      <c r="O133" s="11"/>
+      <c r="P133" s="10">
         <f>+O76</f>
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G126" s="213" t="s">
+    <row r="134" spans="7:16">
+      <c r="G134" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="H126" s="214"/>
-      <c r="I126" s="21">
+      <c r="H134" s="20"/>
+      <c r="I134" s="21">
         <f>+H72</f>
         <v>0</v>
       </c>
-      <c r="J126" s="11" t="s">
+      <c r="J134" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="K126" s="11"/>
-      <c r="L126" s="10">
+      <c r="K134" s="11"/>
+      <c r="L134" s="10">
         <f>Flujos!G53*Flujos!H53</f>
         <v>0</v>
       </c>
-      <c r="M126" s="205" t="s">
+      <c r="M134" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="N126" s="205"/>
-      <c r="O126" s="205"/>
-      <c r="P126" s="10">
+      <c r="N134" s="11"/>
+      <c r="O134" s="11"/>
+      <c r="P134" s="10">
         <f>+O86</f>
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G127" s="213" t="s">
+    <row r="135" spans="7:16">
+      <c r="G135" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="H127" s="214"/>
-      <c r="I127" s="21">
+      <c r="H135" s="20"/>
+      <c r="I135" s="21">
         <f>+H77</f>
         <v>0</v>
       </c>
-      <c r="J127" s="205" t="s">
+      <c r="J135" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K127" s="205"/>
-      <c r="L127" s="10">
+      <c r="K135" s="11"/>
+      <c r="L135" s="10">
         <f>Flujos!G42*Flujos!H42</f>
         <v>0</v>
       </c>
-      <c r="M127" s="205" t="s">
+      <c r="M135" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="N127" s="205"/>
-      <c r="O127" s="205"/>
-      <c r="P127" s="10">
+      <c r="N135" s="11"/>
+      <c r="O135" s="11"/>
+      <c r="P135" s="10">
         <f>Q81</f>
         <v>84.569300000000013</v>
       </c>
     </row>
-    <row r="128" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G128" s="19" t="s">
+    <row r="136" spans="7:16">
+      <c r="G136" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="H128" s="20"/>
-      <c r="I128" s="21">
+      <c r="H136" s="20"/>
+      <c r="I136" s="21">
         <f>+L76</f>
         <v>11408.816700000001</v>
       </c>
-      <c r="J128" s="11" t="s">
+      <c r="J136" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="K128" s="11"/>
-      <c r="L128" s="10">
+      <c r="K136" s="11"/>
+      <c r="L136" s="10">
         <f>Flujos!G26*Flujos!H26</f>
         <v>17542.103354999999</v>
       </c>
-      <c r="M128" s="218"/>
-      <c r="N128" s="219"/>
-      <c r="O128" s="220"/>
-      <c r="P128" s="10"/>
-    </row>
-    <row r="129" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G129" s="19" t="s">
+      <c r="M136" s="199"/>
+      <c r="N136" s="200"/>
+      <c r="O136" s="201"/>
+      <c r="P136" s="10"/>
+    </row>
+    <row r="137" spans="7:16">
+      <c r="G137" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="H129" s="20"/>
-      <c r="I129" s="21">
+      <c r="H137" s="20"/>
+      <c r="I137" s="21">
         <f>+L80</f>
         <v>3240.6559999999999</v>
       </c>
-      <c r="J129" s="205" t="s">
+      <c r="J137" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K129" s="205"/>
-      <c r="L129" s="10">
+      <c r="K137" s="11"/>
+      <c r="L137" s="10">
         <f>Flujos!G34*Flujos!H34</f>
         <v>17300.927600009971</v>
       </c>
-      <c r="M129" s="218"/>
-      <c r="N129" s="219"/>
-      <c r="O129" s="220"/>
-      <c r="P129" s="10"/>
-    </row>
-    <row r="130" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G130" s="19" t="s">
+      <c r="M137" s="199"/>
+      <c r="N137" s="200"/>
+      <c r="O137" s="201"/>
+      <c r="P137" s="10"/>
+    </row>
+    <row r="138" spans="7:16">
+      <c r="G138" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="H130" s="20"/>
-      <c r="I130" s="21">
+      <c r="H138" s="20"/>
+      <c r="I138" s="21">
         <f>+K88</f>
         <v>0</v>
       </c>
-      <c r="J130" s="205" t="s">
+      <c r="J138" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K130" s="205"/>
-      <c r="L130" s="10">
+      <c r="K138" s="11"/>
+      <c r="L138" s="10">
         <f>Flujos!G39*Flujos!H39</f>
         <v>3773.0993999999996</v>
       </c>
-      <c r="M130" s="218"/>
-      <c r="N130" s="219"/>
-      <c r="O130" s="220"/>
-      <c r="P130" s="10"/>
-    </row>
-    <row r="131" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G131" s="213" t="s">
+      <c r="M138" s="199"/>
+      <c r="N138" s="200"/>
+      <c r="O138" s="201"/>
+      <c r="P138" s="10"/>
+    </row>
+    <row r="139" spans="7:16">
+      <c r="G139" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="H131" s="214"/>
-      <c r="I131" s="21">
+      <c r="H139" s="20"/>
+      <c r="I139" s="21">
         <f>+L92</f>
         <v>3773.0993999999996</v>
       </c>
-      <c r="J131" s="205"/>
-      <c r="K131" s="205"/>
-      <c r="L131" s="10"/>
-      <c r="M131" s="205"/>
-      <c r="N131" s="205"/>
-      <c r="O131" s="205"/>
-      <c r="P131" s="10"/>
-    </row>
-    <row r="132" spans="7:16" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G132" s="213" t="s">
+      <c r="J139" s="11"/>
+      <c r="K139" s="11"/>
+      <c r="L139" s="10"/>
+      <c r="M139" s="11"/>
+      <c r="N139" s="11"/>
+      <c r="O139" s="11"/>
+      <c r="P139" s="10"/>
+    </row>
+    <row r="140" spans="7:16">
+      <c r="G140" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="H132" s="214"/>
-      <c r="I132" s="21">
+      <c r="H140" s="20"/>
+      <c r="I140" s="21">
         <f>K84</f>
         <v>2736.0241999999998</v>
       </c>
-      <c r="J132" s="205"/>
-      <c r="K132" s="205"/>
-      <c r="L132" s="10"/>
-      <c r="M132" s="205"/>
-      <c r="N132" s="205"/>
-      <c r="O132" s="205"/>
-      <c r="P132" s="10"/>
-    </row>
-    <row r="133" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G133" s="215" t="s">
+      <c r="J140" s="11"/>
+      <c r="K140" s="11"/>
+      <c r="L140" s="10"/>
+      <c r="M140" s="11"/>
+      <c r="N140" s="11"/>
+      <c r="O140" s="11"/>
+      <c r="P140" s="10"/>
+    </row>
+    <row r="141" spans="7:16">
+      <c r="G141" s="216" t="s">
+        <v>177</v>
+      </c>
+      <c r="H141" s="217"/>
+      <c r="I141" s="21">
+        <f>Flujos!G59*Flujos!H59</f>
+        <v>0</v>
+      </c>
+      <c r="J141" s="213"/>
+      <c r="K141" s="213"/>
+      <c r="L141" s="10"/>
+      <c r="M141" s="213"/>
+      <c r="N141" s="213"/>
+      <c r="O141" s="213"/>
+      <c r="P141" s="10"/>
+    </row>
+    <row r="142" spans="7:16">
+      <c r="G142" s="216" t="s">
+        <v>178</v>
+      </c>
+      <c r="H142" s="217"/>
+      <c r="I142" s="21">
+        <f>Flujos!G60*Flujos!H60</f>
+        <v>0</v>
+      </c>
+      <c r="J142" s="213"/>
+      <c r="K142" s="213"/>
+      <c r="L142" s="10"/>
+      <c r="M142" s="213"/>
+      <c r="N142" s="213"/>
+      <c r="O142" s="213"/>
+      <c r="P142" s="10"/>
+    </row>
+    <row r="143" spans="7:16">
+      <c r="G143" s="216" t="s">
+        <v>179</v>
+      </c>
+      <c r="H143" s="217"/>
+      <c r="I143" s="21">
+        <f>Flujos!G61*Flujos!H61</f>
+        <v>0</v>
+      </c>
+      <c r="J143" s="213"/>
+      <c r="K143" s="213"/>
+      <c r="L143" s="10"/>
+      <c r="M143" s="213"/>
+      <c r="N143" s="213"/>
+      <c r="O143" s="213"/>
+      <c r="P143" s="10"/>
+    </row>
+    <row r="144" spans="7:16">
+      <c r="G144" s="216" t="s">
+        <v>179</v>
+      </c>
+      <c r="H144" s="217"/>
+      <c r="I144" s="21">
+        <f>Flujos!G62*Flujos!H62</f>
+        <v>0</v>
+      </c>
+      <c r="J144" s="213"/>
+      <c r="K144" s="213"/>
+      <c r="L144" s="10"/>
+      <c r="M144" s="213"/>
+      <c r="N144" s="213"/>
+      <c r="O144" s="213"/>
+      <c r="P144" s="10"/>
+    </row>
+    <row r="145" spans="7:16">
+      <c r="G145" s="216" t="s">
+        <v>177</v>
+      </c>
+      <c r="H145" s="217"/>
+      <c r="I145" s="21">
+        <f>Flujos!G63*Flujos!H63</f>
+        <v>0</v>
+      </c>
+      <c r="J145" s="213"/>
+      <c r="K145" s="213"/>
+      <c r="L145" s="10"/>
+      <c r="M145" s="213"/>
+      <c r="N145" s="213"/>
+      <c r="O145" s="213"/>
+      <c r="P145" s="10"/>
+    </row>
+    <row r="146" spans="7:16">
+      <c r="G146" s="216" t="s">
+        <v>180</v>
+      </c>
+      <c r="H146" s="217"/>
+      <c r="I146" s="21">
+        <f>Flujos!G64*Flujos!H64</f>
+        <v>0</v>
+      </c>
+      <c r="J146" s="213"/>
+      <c r="K146" s="213"/>
+      <c r="L146" s="10"/>
+      <c r="M146" s="213"/>
+      <c r="N146" s="213"/>
+      <c r="O146" s="213"/>
+      <c r="P146" s="10"/>
+    </row>
+    <row r="147" spans="7:16" ht="19">
+      <c r="G147" s="214" t="s">
         <v>99</v>
       </c>
-      <c r="H133" s="216"/>
-      <c r="I133" s="12">
-        <f>+SUM(I118:I132)</f>
+      <c r="H147" s="215"/>
+      <c r="I147" s="12">
+        <f>+SUM(I126:I146)</f>
         <v>117522.50051960992</v>
       </c>
-      <c r="J133" s="141" t="s">
+      <c r="J147" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="K133" s="141"/>
-      <c r="L133" s="13">
-        <f>+SUM(L118:L131)</f>
+      <c r="K147" s="225"/>
+      <c r="L147" s="13">
+        <f>+SUM(L126:L139)</f>
         <v>23052.405752154889</v>
       </c>
-      <c r="M133" s="141" t="s">
+      <c r="M147" s="225" t="s">
         <v>101</v>
       </c>
-      <c r="N133" s="141"/>
-      <c r="O133" s="141"/>
-      <c r="P133" s="12">
-        <f>+SUM(P118:P131)</f>
+      <c r="N147" s="225"/>
+      <c r="O147" s="225"/>
+      <c r="P147" s="12">
+        <f>+SUM(P126:P139)</f>
         <v>94470.094767147384</v>
       </c>
     </row>
-    <row r="135" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="L135" s="15" t="s">
+    <row r="148" spans="7:16">
+      <c r="G148" s="14"/>
+      <c r="H148" s="14"/>
+      <c r="I148" s="14"/>
+      <c r="J148" s="14"/>
+      <c r="K148" s="14"/>
+      <c r="L148" s="14"/>
+      <c r="M148" s="14"/>
+      <c r="N148" s="14"/>
+      <c r="O148" s="14"/>
+      <c r="P148" s="14"/>
+    </row>
+    <row r="149" spans="7:16" ht="19">
+      <c r="G149" s="14"/>
+      <c r="J149" s="14"/>
+      <c r="K149" s="14"/>
+      <c r="L149" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="M135" s="16"/>
-      <c r="N135" s="17"/>
-      <c r="O135" s="16"/>
-      <c r="P135" s="18">
-        <f>+I133-L133-P133</f>
+      <c r="M149" s="16"/>
+      <c r="N149" s="17"/>
+      <c r="O149" s="16"/>
+      <c r="P149" s="18">
+        <f>+I147-L147-P147</f>
         <v>3.0765659175813198E-7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="M128:O128"/>
-    <mergeCell ref="J129:K129"/>
-    <mergeCell ref="M129:O129"/>
-    <mergeCell ref="J130:K130"/>
-    <mergeCell ref="M130:O130"/>
-    <mergeCell ref="G133:H133"/>
-    <mergeCell ref="G132:H132"/>
-    <mergeCell ref="J132:K132"/>
-    <mergeCell ref="M132:O132"/>
-    <mergeCell ref="G131:H131"/>
-    <mergeCell ref="J131:K131"/>
-    <mergeCell ref="M131:O131"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="J127:K127"/>
-    <mergeCell ref="M127:O127"/>
-    <mergeCell ref="G123:H123"/>
-    <mergeCell ref="M123:O123"/>
-    <mergeCell ref="G124:H124"/>
-    <mergeCell ref="M124:O124"/>
-    <mergeCell ref="G125:H125"/>
-    <mergeCell ref="M125:O125"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="M126:O126"/>
-    <mergeCell ref="G121:H121"/>
-    <mergeCell ref="J121:K121"/>
-    <mergeCell ref="M121:O121"/>
-    <mergeCell ref="G122:H122"/>
-    <mergeCell ref="J122:K122"/>
-    <mergeCell ref="M122:O122"/>
-    <mergeCell ref="G119:H119"/>
-    <mergeCell ref="J119:K119"/>
-    <mergeCell ref="M119:O119"/>
-    <mergeCell ref="G120:H120"/>
-    <mergeCell ref="J120:K120"/>
-    <mergeCell ref="M120:O120"/>
-    <mergeCell ref="G117:I117"/>
-    <mergeCell ref="J117:L117"/>
-    <mergeCell ref="M117:P117"/>
-    <mergeCell ref="G118:H118"/>
-    <mergeCell ref="J118:K118"/>
-    <mergeCell ref="M118:O118"/>
-    <mergeCell ref="M106:O106"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="J110:K110"/>
-    <mergeCell ref="M110:O110"/>
-    <mergeCell ref="G112:H112"/>
+  <mergeCells count="88">
+    <mergeCell ref="G147:H147"/>
+    <mergeCell ref="J147:K147"/>
+    <mergeCell ref="M147:O147"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="J145:K145"/>
+    <mergeCell ref="M145:O145"/>
+    <mergeCell ref="G146:H146"/>
+    <mergeCell ref="J146:K146"/>
+    <mergeCell ref="M146:O146"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="J143:K143"/>
+    <mergeCell ref="M143:O143"/>
+    <mergeCell ref="G144:H144"/>
+    <mergeCell ref="J144:K144"/>
+    <mergeCell ref="M144:O144"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="J141:K141"/>
+    <mergeCell ref="M141:O141"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="J142:K142"/>
+    <mergeCell ref="M142:O142"/>
+    <mergeCell ref="J115:K115"/>
+    <mergeCell ref="M115:O115"/>
+    <mergeCell ref="J116:K116"/>
+    <mergeCell ref="M116:O116"/>
+    <mergeCell ref="J117:K117"/>
+    <mergeCell ref="M117:O117"/>
     <mergeCell ref="J112:K112"/>
     <mergeCell ref="M112:O112"/>
-    <mergeCell ref="J108:K108"/>
-    <mergeCell ref="J109:K109"/>
-    <mergeCell ref="M107:O107"/>
-    <mergeCell ref="M108:O108"/>
-    <mergeCell ref="M109:O109"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="M111:O111"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="J106:K106"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="J101:K101"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="G96:I96"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="M96:P96"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="J113:K113"/>
+    <mergeCell ref="M113:O113"/>
+    <mergeCell ref="J114:K114"/>
+    <mergeCell ref="M114:O114"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="G117:H117"/>
     <mergeCell ref="M105:O105"/>
     <mergeCell ref="M97:O97"/>
     <mergeCell ref="M99:O99"/>
@@ -25537,6 +26011,47 @@
     <mergeCell ref="M103:O103"/>
     <mergeCell ref="M98:O98"/>
     <mergeCell ref="M104:O104"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="M96:P96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="M106:O106"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="J110:K110"/>
+    <mergeCell ref="M110:O110"/>
+    <mergeCell ref="G118:H118"/>
+    <mergeCell ref="J118:K118"/>
+    <mergeCell ref="M118:O118"/>
+    <mergeCell ref="J108:K108"/>
+    <mergeCell ref="J109:K109"/>
+    <mergeCell ref="M107:O107"/>
+    <mergeCell ref="M108:O108"/>
+    <mergeCell ref="M109:O109"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="M111:O111"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="G125:I125"/>
+    <mergeCell ref="J125:L125"/>
+    <mergeCell ref="M125:P125"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="J126:K126"/>
+    <mergeCell ref="M126:O126"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25545,7 +26060,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{11C74377-02BB-4CEC-AD32-574DE43F3C6D}">
+          <x14:cfRule type="iconSet" priority="16" id="{11C74377-02BB-4CEC-AD32-574DE43F3C6D}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25564,7 +26079,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{E9B417B4-502F-4EEE-9D7C-CE6F00A1381A}">
+          <x14:cfRule type="iconSet" priority="7" id="{E9B417B4-502F-4EEE-9D7C-CE6F00A1381A}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25583,7 +26098,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{0AD6243A-45A5-47DB-B15A-FDB68117E664}">
+          <x14:cfRule type="iconSet" priority="5" id="{0AD6243A-45A5-47DB-B15A-FDB68117E664}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25602,7 +26117,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{9285488E-FB57-43D0-9C6B-A32A74A1B820}">
+          <x14:cfRule type="iconSet" priority="4" id="{9285488E-FB57-43D0-9C6B-A32A74A1B820}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25621,7 +26136,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{AA6884B4-5B87-4B2B-90B0-5B1AFEF428AE}">
+          <x14:cfRule type="iconSet" priority="15" id="{AA6884B4-5B87-4B2B-90B0-5B1AFEF428AE}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25640,7 +26155,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{F1405932-F310-492D-8E03-60D676711988}">
+          <x14:cfRule type="iconSet" priority="10" id="{F1405932-F310-492D-8E03-60D676711988}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25659,7 +26174,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{CFEF6902-F9F8-426F-A2C0-0814CBFADAB0}">
+          <x14:cfRule type="iconSet" priority="12" id="{CFEF6902-F9F8-426F-A2C0-0814CBFADAB0}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25678,7 +26193,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{47D46443-C13F-4E8F-88E0-E379DBDAAA18}">
+          <x14:cfRule type="iconSet" priority="13" id="{47D46443-C13F-4E8F-88E0-E379DBDAAA18}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25697,7 +26212,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{5855D640-0D68-403A-BE2B-1C0438B48E40}">
+          <x14:cfRule type="iconSet" priority="3" id="{5855D640-0D68-403A-BE2B-1C0438B48E40}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25713,29 +26228,10 @@
               <x14:cfIcon iconSet="3Arrows" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>L112</xm:sqref>
+          <xm:sqref>L118</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{3FB60B19-64D8-41FB-8DC4-66A873610FC0}">
-            <x14:iconSet iconSet="3Arrows" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L133</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{F70366D2-FE7D-4A63-84D5-66BF541E67E6}">
+          <x14:cfRule type="iconSet" priority="14" id="{F70366D2-FE7D-4A63-84D5-66BF541E67E6}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25754,7 +26250,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{29BFAB21-DC84-4910-A669-C11C96143384}">
+          <x14:cfRule type="iconSet" priority="11" id="{29BFAB21-DC84-4910-A669-C11C96143384}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25773,7 +26269,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{B5F9C961-80B8-4994-9078-D395E6E07091}">
+          <x14:cfRule type="iconSet" priority="9" id="{B5F9C961-80B8-4994-9078-D395E6E07091}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25792,7 +26288,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{20F55917-D3CE-4692-B77E-7860663EC1E4}">
+          <x14:cfRule type="iconSet" priority="8" id="{20F55917-D3CE-4692-B77E-7860663EC1E4}">
             <x14:iconSet iconSet="3Arrows" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -25810,6 +26306,25 @@
           </x14:cfRule>
           <xm:sqref>N88</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{DB53FB84-6938-564F-81FC-41C7CEB5A866}">
+            <x14:iconSet iconSet="3Arrows" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L147</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
@@ -25819,7 +26334,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A180942-FDE9-9742-9791-B717C09345EC}">
   <dimension ref="B1:U41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="6.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="6.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="2.5" style="48" customWidth="1"/>
     <col min="3" max="3" width="15.5" style="48" hidden="1" customWidth="1"/>
@@ -28383,7 +28898,7 @@
     <col min="16176" max="16384" width="6.5" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" thickBot="1">
       <c r="B1" s="44"/>
       <c r="C1" s="45"/>
       <c r="D1" s="45"/>
@@ -28402,91 +28917,91 @@
       <c r="Q1" s="46"/>
       <c r="R1" s="47"/>
     </row>
-    <row r="2" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:20" ht="14">
       <c r="B2" s="49"/>
       <c r="C2" s="50"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="242" t="s">
+      <c r="D2" s="277"/>
+      <c r="E2" s="278"/>
+      <c r="F2" s="283" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="M2" s="242"/>
-      <c r="N2" s="242"/>
-      <c r="O2" s="242"/>
-      <c r="P2" s="242"/>
-      <c r="Q2" s="243"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="283"/>
+      <c r="N2" s="283"/>
+      <c r="O2" s="283"/>
+      <c r="P2" s="283"/>
+      <c r="Q2" s="284"/>
       <c r="R2" s="51"/>
     </row>
-    <row r="3" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:20" ht="14">
       <c r="B3" s="49"/>
       <c r="C3" s="50"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="239"/>
-      <c r="F3" s="244"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="244"/>
-      <c r="I3" s="244"/>
-      <c r="J3" s="244"/>
-      <c r="K3" s="244"/>
-      <c r="L3" s="244"/>
-      <c r="M3" s="244"/>
-      <c r="N3" s="244"/>
-      <c r="O3" s="244"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="245"/>
+      <c r="D3" s="279"/>
+      <c r="E3" s="280"/>
+      <c r="F3" s="285"/>
+      <c r="G3" s="285"/>
+      <c r="H3" s="285"/>
+      <c r="I3" s="285"/>
+      <c r="J3" s="285"/>
+      <c r="K3" s="285"/>
+      <c r="L3" s="285"/>
+      <c r="M3" s="285"/>
+      <c r="N3" s="285"/>
+      <c r="O3" s="285"/>
+      <c r="P3" s="285"/>
+      <c r="Q3" s="286"/>
       <c r="R3" s="51"/>
     </row>
-    <row r="4" spans="2:20" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:20" ht="16">
       <c r="B4" s="49"/>
       <c r="C4" s="50"/>
-      <c r="D4" s="238"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="244" t="s">
+      <c r="D4" s="279"/>
+      <c r="E4" s="280"/>
+      <c r="F4" s="285" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244" t="s">
+      <c r="G4" s="285"/>
+      <c r="H4" s="285"/>
+      <c r="I4" s="285"/>
+      <c r="J4" s="285"/>
+      <c r="K4" s="285"/>
+      <c r="L4" s="285"/>
+      <c r="M4" s="285" t="s">
         <v>109</v>
       </c>
-      <c r="N4" s="244"/>
+      <c r="N4" s="285"/>
       <c r="O4" s="129"/>
-      <c r="P4" s="247">
+      <c r="P4" s="288">
         <v>45230</v>
       </c>
-      <c r="Q4" s="248"/>
+      <c r="Q4" s="289"/>
       <c r="R4" s="51"/>
     </row>
-    <row r="5" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" ht="17" thickBot="1">
       <c r="B5" s="49"/>
       <c r="C5" s="50"/>
-      <c r="D5" s="240"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="246"/>
-      <c r="G5" s="246"/>
-      <c r="H5" s="246"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="246"/>
-      <c r="M5" s="246"/>
-      <c r="N5" s="246"/>
+      <c r="D5" s="281"/>
+      <c r="E5" s="282"/>
+      <c r="F5" s="287"/>
+      <c r="G5" s="287"/>
+      <c r="H5" s="287"/>
+      <c r="I5" s="287"/>
+      <c r="J5" s="287"/>
+      <c r="K5" s="287"/>
+      <c r="L5" s="287"/>
+      <c r="M5" s="287"/>
+      <c r="N5" s="287"/>
       <c r="O5" s="130"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="250"/>
+      <c r="P5" s="290"/>
+      <c r="Q5" s="291"/>
       <c r="R5" s="51"/>
     </row>
-    <row r="6" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" thickBot="1">
       <c r="B6" s="49"/>
       <c r="C6" s="50"/>
       <c r="D6" s="52"/>
@@ -28503,29 +29018,29 @@
       <c r="O6" s="50"/>
       <c r="R6" s="51"/>
     </row>
-    <row r="7" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:20" ht="15" customHeight="1">
       <c r="B7" s="54"/>
       <c r="C7" s="55"/>
-      <c r="D7" s="228"/>
-      <c r="E7" s="229"/>
-      <c r="F7" s="229"/>
-      <c r="G7" s="251" t="s">
+      <c r="D7" s="269"/>
+      <c r="E7" s="270"/>
+      <c r="F7" s="270"/>
+      <c r="G7" s="292" t="s">
         <v>110</v>
       </c>
-      <c r="H7" s="252"/>
+      <c r="H7" s="293"/>
       <c r="I7" s="56" t="s">
         <v>111</v>
       </c>
       <c r="J7" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="K7" s="232"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="251" t="s">
+      <c r="K7" s="273"/>
+      <c r="L7" s="274"/>
+      <c r="M7" s="274"/>
+      <c r="N7" s="292" t="s">
         <v>110</v>
       </c>
-      <c r="O7" s="252"/>
+      <c r="O7" s="293"/>
       <c r="P7" s="56" t="s">
         <v>111</v>
       </c>
@@ -28534,12 +29049,12 @@
       </c>
       <c r="R7" s="51"/>
     </row>
-    <row r="8" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:20" thickBot="1">
       <c r="B8" s="54"/>
       <c r="C8" s="55"/>
-      <c r="D8" s="230"/>
-      <c r="E8" s="231"/>
-      <c r="F8" s="231"/>
+      <c r="D8" s="271"/>
+      <c r="E8" s="272"/>
+      <c r="F8" s="272"/>
       <c r="G8" s="58" t="s">
         <v>1</v>
       </c>
@@ -28552,9 +29067,9 @@
       <c r="J8" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="234"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
+      <c r="K8" s="275"/>
+      <c r="L8" s="276"/>
+      <c r="M8" s="276"/>
       <c r="N8" s="58" t="s">
         <v>1</v>
       </c>
@@ -28569,39 +29084,39 @@
       </c>
       <c r="R8" s="51"/>
     </row>
-    <row r="9" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:20" ht="14">
       <c r="B9" s="54"/>
       <c r="C9" s="55"/>
-      <c r="D9" s="253" t="s">
+      <c r="D9" s="247" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="254"/>
-      <c r="F9" s="254"/>
-      <c r="G9" s="254"/>
-      <c r="H9" s="254"/>
-      <c r="I9" s="254"/>
-      <c r="J9" s="255"/>
-      <c r="K9" s="256" t="s">
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="294"/>
+      <c r="K9" s="244" t="s">
         <v>153</v>
       </c>
-      <c r="L9" s="257"/>
-      <c r="M9" s="257"/>
-      <c r="N9" s="257"/>
-      <c r="O9" s="257"/>
-      <c r="P9" s="257"/>
-      <c r="Q9" s="258"/>
+      <c r="L9" s="245"/>
+      <c r="M9" s="245"/>
+      <c r="N9" s="245"/>
+      <c r="O9" s="245"/>
+      <c r="P9" s="245"/>
+      <c r="Q9" s="246"/>
       <c r="R9" s="51"/>
     </row>
-    <row r="10" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" thickBot="1">
       <c r="B10" s="54"/>
       <c r="C10" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="259" t="s">
+      <c r="D10" s="230" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="260"/>
-      <c r="F10" s="261"/>
+      <c r="E10" s="231"/>
+      <c r="F10" s="252"/>
       <c r="G10" s="62">
         <f>Flujos!G4</f>
         <v>88507</v>
@@ -28618,11 +29133,11 @@
         <f>+I10*G10</f>
         <v>33752.992219609914</v>
       </c>
-      <c r="K10" s="265" t="s">
+      <c r="K10" s="233" t="s">
         <v>116</v>
       </c>
-      <c r="L10" s="266"/>
-      <c r="M10" s="267"/>
+      <c r="L10" s="234"/>
+      <c r="M10" s="253"/>
       <c r="N10" s="117">
         <f>Flujos!G20</f>
         <v>132791</v>
@@ -28631,7 +29146,7 @@
         <f>N10/(1-'Datos Extra'!B28)</f>
         <v>144652.50544662308</v>
       </c>
-      <c r="P10" s="176">
+      <c r="P10" s="175">
         <f>Flujos!H20</f>
         <v>0.67602529614999995</v>
       </c>
@@ -28642,14 +29157,14 @@
       <c r="R10" s="51"/>
       <c r="T10" s="87"/>
     </row>
-    <row r="11" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:20" ht="14">
       <c r="B11" s="54"/>
       <c r="C11" s="55"/>
-      <c r="D11" s="265" t="s">
+      <c r="D11" s="233" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="266"/>
-      <c r="F11" s="267"/>
+      <c r="E11" s="234"/>
+      <c r="F11" s="253"/>
       <c r="G11" s="64">
         <f>Flujos!G5</f>
         <v>0</v>
@@ -28666,26 +29181,26 @@
         <f>+I11*G11</f>
         <v>0</v>
       </c>
-      <c r="K11" s="268" t="s">
+      <c r="K11" s="257" t="s">
         <v>127</v>
       </c>
-      <c r="L11" s="269"/>
-      <c r="M11" s="269"/>
-      <c r="N11" s="269"/>
-      <c r="O11" s="269"/>
-      <c r="P11" s="269"/>
-      <c r="Q11" s="270"/>
+      <c r="L11" s="258"/>
+      <c r="M11" s="258"/>
+      <c r="N11" s="258"/>
+      <c r="O11" s="258"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="259"/>
       <c r="R11" s="51"/>
       <c r="T11" s="87"/>
     </row>
-    <row r="12" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:20" ht="14">
       <c r="B12" s="54"/>
       <c r="C12" s="55"/>
-      <c r="D12" s="259" t="s">
+      <c r="D12" s="230" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="260"/>
-      <c r="F12" s="261"/>
+      <c r="E12" s="231"/>
+      <c r="F12" s="252"/>
       <c r="G12" s="60">
         <f>Flujos!G8</f>
         <v>43180</v>
@@ -28702,11 +29217,11 @@
         <f>+I12*G12</f>
         <v>20830.031999999999</v>
       </c>
-      <c r="K12" s="271" t="s">
+      <c r="K12" s="260" t="s">
         <v>128</v>
       </c>
-      <c r="L12" s="272"/>
-      <c r="M12" s="273"/>
+      <c r="L12" s="261"/>
+      <c r="M12" s="262"/>
       <c r="N12" s="60">
         <f>Flujos!G6</f>
         <v>22063</v>
@@ -28725,14 +29240,14 @@
       </c>
       <c r="R12" s="51"/>
     </row>
-    <row r="13" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:20" ht="14">
       <c r="B13" s="54"/>
       <c r="C13" s="55"/>
-      <c r="D13" s="265" t="s">
+      <c r="D13" s="233" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="266"/>
-      <c r="F13" s="267"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="253"/>
       <c r="G13" s="64">
         <f>Flujos!G55</f>
         <v>77372</v>
@@ -28749,11 +29264,11 @@
         <f>+I13*G13</f>
         <v>41780.880000000005</v>
       </c>
-      <c r="K13" s="274" t="s">
+      <c r="K13" s="263" t="s">
         <v>130</v>
       </c>
-      <c r="L13" s="275"/>
-      <c r="M13" s="276"/>
+      <c r="L13" s="264"/>
+      <c r="M13" s="265"/>
       <c r="N13" s="73">
         <f>Flujos!G12</f>
         <v>47016</v>
@@ -28762,7 +29277,7 @@
         <f>N13/(1-'Datos Extra'!B36)</f>
         <v>52120.839742043754</v>
       </c>
-      <c r="P13" s="197">
+      <c r="P13" s="196">
         <f>Flujos!H12</f>
         <v>0.34271999999999997</v>
       </c>
@@ -28772,14 +29287,14 @@
       </c>
       <c r="R13" s="51"/>
     </row>
-    <row r="14" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:20" ht="14">
       <c r="B14" s="54"/>
       <c r="C14" s="55"/>
-      <c r="D14" s="259" t="s">
+      <c r="D14" s="230" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="260"/>
-      <c r="F14" s="261"/>
+      <c r="E14" s="231"/>
+      <c r="F14" s="252"/>
       <c r="G14" s="60">
         <f>Flujos!G31</f>
         <v>0</v>
@@ -28796,11 +29311,11 @@
         <f>+I14*G14</f>
         <v>0</v>
       </c>
-      <c r="K14" s="271" t="s">
+      <c r="K14" s="260" t="s">
         <v>131</v>
       </c>
-      <c r="L14" s="272"/>
-      <c r="M14" s="273"/>
+      <c r="L14" s="261"/>
+      <c r="M14" s="262"/>
       <c r="N14" s="74">
         <f>Flujos!G13</f>
         <v>10446.465614000001</v>
@@ -28816,7 +29331,7 @@
       </c>
       <c r="R14" s="51"/>
     </row>
-    <row r="15" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" thickBot="1">
       <c r="B15" s="54"/>
       <c r="C15" s="55"/>
       <c r="D15" s="99"/>
@@ -28836,7 +29351,7 @@
         <v>37746.534385999999</v>
       </c>
       <c r="O15" s="76"/>
-      <c r="P15" s="175">
+      <c r="P15" s="174">
         <f>Flujos!H19</f>
         <v>8.5890000000000008E-2</v>
       </c>
@@ -28846,21 +29361,21 @@
       </c>
       <c r="R15" s="51"/>
     </row>
-    <row r="16" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" thickBot="1">
       <c r="B16" s="54"/>
       <c r="C16" s="55"/>
-      <c r="D16" s="259"/>
-      <c r="E16" s="260"/>
-      <c r="F16" s="261"/>
+      <c r="D16" s="230"/>
+      <c r="E16" s="231"/>
+      <c r="F16" s="252"/>
       <c r="G16" s="60"/>
       <c r="H16" s="60"/>
       <c r="I16" s="61"/>
       <c r="J16" s="60"/>
-      <c r="K16" s="277" t="s">
+      <c r="K16" s="250" t="s">
         <v>125</v>
       </c>
-      <c r="L16" s="278"/>
-      <c r="M16" s="278"/>
+      <c r="L16" s="251"/>
+      <c r="M16" s="251"/>
       <c r="N16" s="67">
         <f>+SUM(N12:N15)</f>
         <v>117272</v>
@@ -28876,37 +29391,37 @@
       </c>
       <c r="R16" s="51"/>
     </row>
-    <row r="17" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" thickBot="1">
       <c r="B17" s="54"/>
       <c r="C17" s="55"/>
-      <c r="D17" s="259"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="261"/>
+      <c r="D17" s="230"/>
+      <c r="E17" s="231"/>
+      <c r="F17" s="252"/>
       <c r="G17" s="60"/>
       <c r="H17" s="60"/>
       <c r="I17" s="61"/>
       <c r="J17" s="60"/>
-      <c r="K17" s="256" t="s">
+      <c r="K17" s="244" t="s">
         <v>154</v>
       </c>
-      <c r="L17" s="257"/>
-      <c r="M17" s="257"/>
-      <c r="N17" s="257"/>
-      <c r="O17" s="257"/>
-      <c r="P17" s="257"/>
-      <c r="Q17" s="258"/>
+      <c r="L17" s="245"/>
+      <c r="M17" s="245"/>
+      <c r="N17" s="245"/>
+      <c r="O17" s="245"/>
+      <c r="P17" s="245"/>
+      <c r="Q17" s="246"/>
       <c r="R17" s="51"/>
     </row>
-    <row r="18" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" thickBot="1">
       <c r="B18" s="54"/>
       <c r="C18" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="277" t="s">
+      <c r="D18" s="250" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="278"/>
-      <c r="F18" s="278"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
       <c r="G18" s="67">
         <f>+SUM(G10:G17)</f>
         <v>209059</v>
@@ -28920,11 +29435,11 @@
         <f>+SUM(J10:J17)</f>
         <v>96363.904219609918</v>
       </c>
-      <c r="K18" s="262" t="s">
+      <c r="K18" s="295" t="s">
         <v>136</v>
       </c>
-      <c r="L18" s="263"/>
-      <c r="M18" s="264"/>
+      <c r="L18" s="296"/>
+      <c r="M18" s="297"/>
       <c r="N18" s="62">
         <f>Flujos!G25</f>
         <v>129475</v>
@@ -28942,26 +29457,26 @@
         <v>86645.635355242004</v>
       </c>
       <c r="R18" s="51"/>
-      <c r="S18" s="188"/>
+      <c r="S18" s="187"/>
       <c r="T18" s="69"/>
     </row>
-    <row r="19" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" ht="14">
       <c r="B19" s="54"/>
       <c r="C19" s="55"/>
-      <c r="D19" s="253" t="s">
+      <c r="D19" s="247" t="s">
         <v>126</v>
       </c>
-      <c r="E19" s="254"/>
-      <c r="F19" s="254"/>
-      <c r="G19" s="254"/>
-      <c r="H19" s="254"/>
-      <c r="I19" s="254"/>
-      <c r="J19" s="286"/>
-      <c r="K19" s="265" t="s">
+      <c r="E19" s="248"/>
+      <c r="F19" s="248"/>
+      <c r="G19" s="248"/>
+      <c r="H19" s="248"/>
+      <c r="I19" s="248"/>
+      <c r="J19" s="249"/>
+      <c r="K19" s="233" t="s">
         <v>119</v>
       </c>
-      <c r="L19" s="266"/>
-      <c r="M19" s="267"/>
+      <c r="L19" s="234"/>
+      <c r="M19" s="253"/>
       <c r="N19" s="117">
         <f>Flujos!G35</f>
         <v>18351</v>
@@ -28981,14 +29496,14 @@
       <c r="R19" s="51"/>
       <c r="S19" s="70"/>
     </row>
-    <row r="20" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" ht="14">
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
-      <c r="D20" s="259" t="s">
+      <c r="D20" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="260"/>
-      <c r="F20" s="261"/>
+      <c r="E20" s="231"/>
+      <c r="F20" s="252"/>
       <c r="G20" s="133">
         <f>'Mapa de Procesos'!P102</f>
         <v>104386</v>
@@ -29005,11 +29520,11 @@
         <f>+I20*G20</f>
         <v>69103.532000000007</v>
       </c>
-      <c r="K20" s="259" t="s">
+      <c r="K20" s="230" t="s">
         <v>121</v>
       </c>
-      <c r="L20" s="260"/>
-      <c r="M20" s="261"/>
+      <c r="L20" s="231"/>
+      <c r="M20" s="252"/>
       <c r="N20" s="62">
         <f>Flujos!G36</f>
         <v>5360</v>
@@ -29027,16 +29542,16 @@
         <v>3240.6559999999999</v>
       </c>
       <c r="R20" s="51"/>
-      <c r="S20" s="187"/>
-    </row>
-    <row r="21" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="S20" s="186"/>
+    </row>
+    <row r="21" spans="2:21" ht="14">
       <c r="B21" s="54"/>
       <c r="C21" s="55"/>
-      <c r="D21" s="265" t="s">
+      <c r="D21" s="233" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="266"/>
-      <c r="F21" s="267"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="253"/>
       <c r="G21" s="71">
         <f>Flujos!G33</f>
         <v>0</v>
@@ -29053,11 +29568,11 @@
         <f>+I21*G21</f>
         <v>0</v>
       </c>
-      <c r="K21" s="265" t="s">
+      <c r="K21" s="233" t="s">
         <v>138</v>
       </c>
-      <c r="L21" s="266"/>
-      <c r="M21" s="267"/>
+      <c r="L21" s="234"/>
+      <c r="M21" s="253"/>
       <c r="N21" s="117">
         <f>Flujos!G57</f>
         <v>4403</v>
@@ -29066,7 +29581,7 @@
         <f>N21/(1-'Datos Extra'!B32)</f>
         <v>4426.9052885582141</v>
       </c>
-      <c r="P21" s="173">
+      <c r="P21" s="172">
         <f>Flujos!H57</f>
         <v>0.62139999999999995</v>
       </c>
@@ -29075,16 +29590,16 @@
         <v>2736.0241999999998</v>
       </c>
       <c r="R21" s="51"/>
-      <c r="S21" s="187"/>
-    </row>
-    <row r="22" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="S21" s="186"/>
+    </row>
+    <row r="22" spans="2:21" ht="14">
       <c r="B22" s="54"/>
       <c r="C22" s="55"/>
-      <c r="D22" s="259" t="s">
+      <c r="D22" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="260"/>
-      <c r="F22" s="261"/>
+      <c r="E22" s="231"/>
+      <c r="F22" s="252"/>
       <c r="G22" s="60">
         <f>Flujos!G40</f>
         <v>0</v>
@@ -29101,11 +29616,11 @@
         <f>+I22*G22</f>
         <v>0</v>
       </c>
-      <c r="K22" s="259" t="s">
+      <c r="K22" s="230" t="s">
         <v>122</v>
       </c>
-      <c r="L22" s="260"/>
-      <c r="M22" s="261"/>
+      <c r="L22" s="231"/>
+      <c r="M22" s="252"/>
       <c r="N22" s="62">
         <f>Flujos!G37</f>
         <v>6394</v>
@@ -29123,16 +29638,16 @@
         <v>3773.0993999999996</v>
       </c>
       <c r="R22" s="51"/>
-      <c r="S22" s="187"/>
-    </row>
-    <row r="23" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="S22" s="186"/>
+    </row>
+    <row r="23" spans="2:21" thickBot="1">
       <c r="B23" s="54"/>
       <c r="C23" s="55"/>
-      <c r="D23" s="287" t="s">
+      <c r="D23" s="254" t="s">
         <v>132</v>
       </c>
-      <c r="E23" s="288"/>
-      <c r="F23" s="289"/>
+      <c r="E23" s="255"/>
+      <c r="F23" s="256"/>
       <c r="G23" s="71">
         <f>Flujos!G58</f>
         <v>127</v>
@@ -29149,11 +29664,11 @@
         <f>G23*I23</f>
         <v>84.569300000000013</v>
       </c>
-      <c r="K23" s="265" t="s">
+      <c r="K23" s="233" t="s">
         <v>123</v>
       </c>
-      <c r="L23" s="266"/>
-      <c r="M23" s="267"/>
+      <c r="L23" s="234"/>
+      <c r="M23" s="253"/>
       <c r="N23" s="117">
         <f>Flujos!G38</f>
         <v>0</v>
@@ -29173,14 +29688,14 @@
       <c r="R23" s="51"/>
       <c r="S23" s="70"/>
     </row>
-    <row r="24" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" thickBot="1">
       <c r="B24" s="54"/>
       <c r="C24" s="55"/>
-      <c r="D24" s="277" t="s">
+      <c r="D24" s="250" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="278"/>
-      <c r="F24" s="278"/>
+      <c r="E24" s="251"/>
+      <c r="F24" s="251"/>
       <c r="G24" s="67">
         <f>+SUM(G20:G23)</f>
         <v>104513</v>
@@ -29194,11 +29709,11 @@
         <f t="shared" ref="J24" si="1">+SUM(J20:J23)</f>
         <v>69188.101300000009</v>
       </c>
-      <c r="K24" s="277" t="s">
+      <c r="K24" s="250" t="s">
         <v>125</v>
       </c>
-      <c r="L24" s="278"/>
-      <c r="M24" s="278"/>
+      <c r="L24" s="251"/>
+      <c r="M24" s="251"/>
       <c r="N24" s="67">
         <f>SUM(N18:N23)</f>
         <v>163983</v>
@@ -29214,67 +29729,67 @@
       </c>
       <c r="R24" s="51"/>
     </row>
-    <row r="25" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" thickBot="1">
       <c r="B25" s="54"/>
       <c r="C25" s="55"/>
-      <c r="D25" s="279"/>
-      <c r="E25" s="279"/>
-      <c r="F25" s="279"/>
+      <c r="D25" s="237"/>
+      <c r="E25" s="237"/>
+      <c r="F25" s="237"/>
       <c r="G25" s="77"/>
       <c r="H25" s="77"/>
       <c r="I25" s="78"/>
       <c r="J25" s="79"/>
       <c r="R25" s="51"/>
-      <c r="S25" s="187"/>
-    </row>
-    <row r="26" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S25" s="186"/>
+    </row>
+    <row r="26" spans="2:21" ht="14.5" customHeight="1">
       <c r="B26" s="54"/>
       <c r="C26" s="55"/>
-      <c r="D26" s="225" t="s">
+      <c r="D26" s="266" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="226"/>
-      <c r="F26" s="226"/>
-      <c r="G26" s="226"/>
-      <c r="H26" s="227"/>
+      <c r="E26" s="267"/>
+      <c r="F26" s="267"/>
+      <c r="G26" s="267"/>
+      <c r="H26" s="268"/>
       <c r="R26" s="80"/>
     </row>
-    <row r="27" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:21" thickBot="1">
       <c r="B27" s="54"/>
       <c r="C27" s="55"/>
-      <c r="D27" s="280"/>
-      <c r="E27" s="281"/>
-      <c r="F27" s="282"/>
+      <c r="D27" s="238"/>
+      <c r="E27" s="239"/>
+      <c r="F27" s="240"/>
       <c r="G27" s="89" t="s">
         <v>104</v>
       </c>
       <c r="H27" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="I27" s="190" t="s">
+      <c r="I27" s="189" t="s">
         <v>157</v>
       </c>
-      <c r="J27" s="190" t="s">
+      <c r="J27" s="189" t="s">
         <v>158</v>
       </c>
-      <c r="L27" s="178"/>
-      <c r="M27" s="178"/>
-      <c r="N27" s="178"/>
-      <c r="O27" s="178"/>
-      <c r="P27" s="178"/>
-      <c r="Q27" s="178"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="177"/>
+      <c r="N27" s="177"/>
+      <c r="O27" s="177"/>
+      <c r="P27" s="177"/>
+      <c r="Q27" s="177"/>
       <c r="R27" s="51"/>
       <c r="U27" s="81"/>
     </row>
-    <row r="28" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:21" ht="14">
       <c r="B28" s="54"/>
       <c r="C28" s="55"/>
-      <c r="D28" s="283" t="s">
+      <c r="D28" s="241" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="284"/>
-      <c r="F28" s="285"/>
-      <c r="G28" s="181">
+      <c r="E28" s="242"/>
+      <c r="F28" s="243"/>
+      <c r="G28" s="180">
         <f>'Datos Extra'!B1</f>
         <v>4991.0799999999981</v>
       </c>
@@ -29282,263 +29797,263 @@
         <f>G28*(1-'Datos Extra'!D1)</f>
         <v>4941.1691999999985</v>
       </c>
-      <c r="I28" s="191">
+      <c r="I28" s="190">
         <f>Flujos!G9</f>
         <v>-41795</v>
       </c>
-      <c r="J28" s="191">
-        <f>'Mapa de Procesos'!L118</f>
+      <c r="J28" s="190">
+        <f>'Mapa de Procesos'!L126</f>
         <v>-19153.812600000001</v>
       </c>
-      <c r="K28" s="178"/>
-      <c r="L28" s="178"/>
-      <c r="M28" s="178"/>
-      <c r="N28" s="178"/>
-      <c r="O28" s="178"/>
-      <c r="P28" s="178"/>
-      <c r="Q28" s="178"/>
+      <c r="K28" s="177"/>
+      <c r="L28" s="177"/>
+      <c r="M28" s="177"/>
+      <c r="N28" s="177"/>
+      <c r="O28" s="177"/>
+      <c r="P28" s="177"/>
+      <c r="Q28" s="177"/>
       <c r="R28" s="80"/>
       <c r="U28" s="81"/>
     </row>
-    <row r="29" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" ht="14">
       <c r="B29" s="54"/>
       <c r="C29" s="55"/>
-      <c r="D29" s="259" t="s">
+      <c r="D29" s="230" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="260"/>
-      <c r="F29" s="260"/>
-      <c r="G29" s="182">
+      <c r="E29" s="231"/>
+      <c r="F29" s="231"/>
+      <c r="G29" s="181">
         <f>'Datos Extra'!B2</f>
         <v>88872.295000000173</v>
       </c>
-      <c r="H29" s="183">
+      <c r="H29" s="182">
         <f>G29*(1-'Datos Extra'!D2)</f>
         <v>87983.572050000177</v>
       </c>
-      <c r="I29" s="191">
+      <c r="I29" s="190">
         <f>Flujos!G17</f>
         <v>791</v>
       </c>
-      <c r="J29" s="191">
-        <f>'Mapa de Procesos'!L119</f>
+      <c r="J29" s="190">
+        <f>'Mapa de Procesos'!L127</f>
         <v>465.64825059536003</v>
       </c>
-      <c r="K29" s="178"/>
-      <c r="L29" s="178"/>
-      <c r="M29" s="178" t="s">
+      <c r="K29" s="177"/>
+      <c r="L29" s="177"/>
+      <c r="M29" s="177" t="s">
         <v>71</v>
       </c>
-      <c r="N29" s="178" t="s">
+      <c r="N29" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="O29" s="178" t="s">
+      <c r="O29" s="177" t="s">
         <v>155</v>
       </c>
-      <c r="P29" s="178" t="s">
+      <c r="P29" s="177" t="s">
         <v>156</v>
       </c>
-      <c r="Q29" s="178"/>
+      <c r="Q29" s="177"/>
       <c r="R29" s="51"/>
       <c r="U29" s="81"/>
     </row>
-    <row r="30" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" ht="14">
       <c r="B30" s="54"/>
       <c r="C30" s="55"/>
-      <c r="D30" s="259" t="s">
+      <c r="D30" s="230" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="260"/>
-      <c r="F30" s="260"/>
-      <c r="G30" s="182">
+      <c r="E30" s="231"/>
+      <c r="F30" s="231"/>
+      <c r="G30" s="181">
         <f>'Datos Extra'!B3</f>
         <v>2985</v>
       </c>
-      <c r="H30" s="183">
+      <c r="H30" s="182">
         <f>G30*(1-'Datos Extra'!D3)</f>
         <v>2734.0093815092168</v>
       </c>
-      <c r="I30" s="191">
+      <c r="I30" s="190">
         <f>Flujos!G21</f>
         <v>3316</v>
       </c>
-      <c r="J30" s="191">
-        <f>'Mapa de Procesos'!L121</f>
+      <c r="J30" s="190">
+        <f>'Mapa de Procesos'!L129</f>
         <v>3124.4397465495604</v>
       </c>
-      <c r="K30" s="178"/>
-      <c r="L30" s="178" t="s">
+      <c r="K30" s="177"/>
+      <c r="L30" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="M30" s="177">
+      <c r="M30" s="176">
         <f>G18+N19+N20+N21+N22+N23</f>
         <v>243567</v>
       </c>
-      <c r="N30" s="177">
+      <c r="N30" s="176">
         <f>G20+G21+G22+N16+G23</f>
         <v>221785</v>
       </c>
-      <c r="O30" s="179">
+      <c r="O30" s="178">
         <f>I35</f>
         <v>21782</v>
       </c>
-      <c r="P30" s="177">
+      <c r="P30" s="176">
         <f>M30-N30-O30</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="178"/>
+      <c r="Q30" s="177"/>
       <c r="R30" s="51"/>
       <c r="U30" s="81"/>
     </row>
-    <row r="31" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" ht="14">
       <c r="B31" s="54"/>
       <c r="C31" s="55"/>
-      <c r="D31" s="259" t="s">
+      <c r="D31" s="230" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="260"/>
-      <c r="F31" s="260"/>
-      <c r="G31" s="182">
+      <c r="E31" s="231"/>
+      <c r="F31" s="231"/>
+      <c r="G31" s="181">
         <f>'Datos Extra'!B4</f>
         <v>0</v>
       </c>
-      <c r="H31" s="183">
+      <c r="H31" s="182">
         <f>G31*(1-'Datos Extra'!D4)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="191">
+      <c r="I31" s="190">
         <f>Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="J31" s="191">
-        <f>'Mapa de Procesos'!L122</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="178"/>
-      <c r="L31" s="178" t="s">
+      <c r="J31" s="190">
+        <f>'Mapa de Procesos'!L130</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="177"/>
+      <c r="L31" s="177" t="s">
         <v>34</v>
       </c>
-      <c r="M31" s="177">
+      <c r="M31" s="176">
         <f>J18+Q19+Q20+Q21+Q22+Q23</f>
         <v>117522.50051960992</v>
       </c>
-      <c r="N31" s="177">
+      <c r="N31" s="176">
         <f>Q16+J20+J21+J22+J23</f>
         <v>94470.094767147384</v>
       </c>
-      <c r="O31" s="180">
+      <c r="O31" s="179">
         <f>J35</f>
         <v>23052.405752154889</v>
       </c>
-      <c r="P31" s="177">
+      <c r="P31" s="176">
         <f>M31-N31-O31</f>
         <v>3.076493158005178E-7</v>
       </c>
-      <c r="Q31" s="178"/>
+      <c r="Q31" s="177"/>
       <c r="R31" s="80"/>
       <c r="U31" s="81"/>
     </row>
-    <row r="32" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" ht="14">
       <c r="B32" s="54"/>
       <c r="C32" s="55"/>
-      <c r="D32" s="265" t="s">
+      <c r="D32" s="233" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="266"/>
-      <c r="F32" s="266"/>
-      <c r="G32" s="182">
+      <c r="E32" s="234"/>
+      <c r="F32" s="234"/>
+      <c r="G32" s="181">
         <f>'Datos Extra'!B5</f>
         <v>144052.08999999997</v>
       </c>
-      <c r="H32" s="183">
+      <c r="H32" s="182">
         <f>G32*(1-'Datos Extra'!D5)</f>
         <v>131639.42123662311</v>
       </c>
-      <c r="I32" s="191">
+      <c r="I32" s="190">
         <f>Flujos!G26</f>
         <v>25089</v>
       </c>
-      <c r="J32" s="191">
-        <f>'Mapa de Procesos'!L128</f>
+      <c r="J32" s="190">
+        <f>'Mapa de Procesos'!L136</f>
         <v>17542.103354999999</v>
       </c>
-      <c r="K32" s="178"/>
-      <c r="L32" s="177"/>
-      <c r="M32" s="178"/>
-      <c r="N32" s="178"/>
-      <c r="O32" s="178"/>
-      <c r="P32" s="178"/>
-      <c r="Q32" s="178"/>
+      <c r="K32" s="177"/>
+      <c r="L32" s="176"/>
+      <c r="M32" s="177"/>
+      <c r="N32" s="177"/>
+      <c r="O32" s="177"/>
+      <c r="P32" s="177"/>
+      <c r="Q32" s="177"/>
       <c r="R32" s="51"/>
       <c r="U32" s="81"/>
     </row>
-    <row r="33" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" ht="14">
       <c r="B33" s="54"/>
       <c r="C33" s="55"/>
-      <c r="D33" s="265" t="s">
+      <c r="D33" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="266"/>
-      <c r="F33" s="266"/>
-      <c r="G33" s="182">
+      <c r="E33" s="234"/>
+      <c r="F33" s="234"/>
+      <c r="G33" s="181">
         <f>'Datos Extra'!B6</f>
         <v>87099.612182495111</v>
       </c>
-      <c r="H33" s="183">
+      <c r="H33" s="182">
         <f>G33*(1-'Datos Extra'!D6)</f>
         <v>86664.114121582636</v>
       </c>
-      <c r="I33" s="191">
+      <c r="I33" s="190">
         <f>Flujos!G34</f>
         <v>27987</v>
       </c>
-      <c r="J33" s="191">
-        <f>'Mapa de Procesos'!L129</f>
+      <c r="J33" s="190">
+        <f>'Mapa de Procesos'!L137</f>
         <v>17300.927600009971</v>
       </c>
-      <c r="L33" s="189"/>
-      <c r="M33" s="189"/>
-      <c r="N33" s="189"/>
-      <c r="O33" s="189"/>
-      <c r="P33" s="189"/>
-      <c r="Q33" s="186"/>
+      <c r="L33" s="188"/>
+      <c r="M33" s="188"/>
+      <c r="N33" s="188"/>
+      <c r="O33" s="188"/>
+      <c r="P33" s="188"/>
+      <c r="Q33" s="185"/>
       <c r="R33" s="80"/>
       <c r="U33" s="81"/>
     </row>
-    <row r="34" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:21" thickBot="1">
       <c r="B34" s="54"/>
       <c r="C34" s="55"/>
-      <c r="D34" s="291" t="s">
+      <c r="D34" s="235" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="292"/>
-      <c r="F34" s="292"/>
-      <c r="G34" s="184">
+      <c r="E34" s="236"/>
+      <c r="F34" s="236"/>
+      <c r="G34" s="183">
         <f>'Datos Extra'!B7</f>
         <v>27059.240058898926</v>
       </c>
-      <c r="H34" s="185">
+      <c r="H34" s="184">
         <f>G34*(1-'Datos Extra'!D7)</f>
         <v>26923.943858604431</v>
       </c>
-      <c r="I34" s="191">
+      <c r="I34" s="190">
         <f>Flujos!G39</f>
         <v>6394</v>
       </c>
-      <c r="J34" s="191">
-        <f>'Mapa de Procesos'!L130</f>
+      <c r="J34" s="190">
+        <f>'Mapa de Procesos'!L138</f>
         <v>3773.0993999999996</v>
       </c>
-      <c r="L34" s="186"/>
-      <c r="M34" s="186"/>
-      <c r="N34" s="186"/>
-      <c r="O34" s="186"/>
-      <c r="P34" s="186"/>
-      <c r="Q34" s="186"/>
+      <c r="L34" s="185"/>
+      <c r="M34" s="185"/>
+      <c r="N34" s="185"/>
+      <c r="O34" s="185"/>
+      <c r="P34" s="185"/>
+      <c r="Q34" s="185"/>
       <c r="R34" s="51"/>
       <c r="U34" s="81"/>
     </row>
-    <row r="35" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" thickBot="1">
       <c r="B35" s="82"/>
       <c r="C35" s="83"/>
       <c r="D35" s="83"/>
@@ -29546,11 +30061,11 @@
       <c r="F35" s="83"/>
       <c r="G35" s="83"/>
       <c r="H35" s="83"/>
-      <c r="I35" s="192">
+      <c r="I35" s="191">
         <f>SUM(I28:I34)</f>
         <v>21782</v>
       </c>
-      <c r="J35" s="192">
+      <c r="J35" s="191">
         <f>SUM(J28:J34)</f>
         <v>23052.405752154889</v>
       </c>
@@ -29563,7 +30078,7 @@
       <c r="Q35" s="83"/>
       <c r="R35" s="84"/>
     </row>
-    <row r="38" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" ht="15" customHeight="1">
       <c r="E38" s="128"/>
       <c r="F38" s="128"/>
       <c r="G38" s="128"/>
@@ -29571,7 +30086,7 @@
       <c r="I38" s="127"/>
       <c r="J38" s="127"/>
     </row>
-    <row r="39" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" ht="14">
       <c r="E39" s="128"/>
       <c r="F39" s="128"/>
       <c r="G39" s="128"/>
@@ -29579,7 +30094,7 @@
       <c r="I39" s="127"/>
       <c r="J39" s="127"/>
     </row>
-    <row r="40" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:21" ht="14">
       <c r="E40" s="86"/>
       <c r="F40" s="86"/>
       <c r="G40" s="86"/>
@@ -29588,10 +30103,10 @@
       <c r="J40" s="86"/>
       <c r="K40" s="86"/>
     </row>
-    <row r="41" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E41" s="290"/>
-      <c r="F41" s="290"/>
-      <c r="G41" s="290"/>
+    <row r="41" spans="2:21" ht="15" customHeight="1">
+      <c r="E41" s="232"/>
+      <c r="F41" s="232"/>
+      <c r="G41" s="232"/>
       <c r="H41" s="131"/>
       <c r="I41" s="88"/>
       <c r="J41" s="126"/>
@@ -29599,12 +30114,34 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="K7:M8"/>
+    <mergeCell ref="D2:E5"/>
+    <mergeCell ref="F2:Q3"/>
+    <mergeCell ref="F4:L5"/>
+    <mergeCell ref="M4:N5"/>
+    <mergeCell ref="P4:Q5"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="D28:F28"/>
@@ -29621,34 +30158,12 @@
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="K20:M20"/>
     <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="K11:Q11"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D7:F8"/>
-    <mergeCell ref="K7:M8"/>
-    <mergeCell ref="D2:E5"/>
-    <mergeCell ref="F2:Q3"/>
-    <mergeCell ref="F4:L5"/>
-    <mergeCell ref="M4:N5"/>
-    <mergeCell ref="P4:Q5"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="45" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -29657,17 +30172,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f53f264-df38-4c5e-a089-ad7f07a2b911">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1490ee3b-8825-4a14-a799-bb3413729370" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A6756668BF342349B2041C16AA74819C" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="08eddba80e67fcdf0e7dbb3dbc3e0d70">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f53f264-df38-4c5e-a089-ad7f07a2b911" xmlns:ns3="1490ee3b-8825-4a14-a799-bb3413729370" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31c7a2af7ff0f9db171af585e46ec1a5" ns2:_="" ns3:_="">
     <xsd:import namespace="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
@@ -29902,6 +30406,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f53f264-df38-4c5e-a089-ad7f07a2b911">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1490ee3b-8825-4a14-a799-bb3413729370" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -29912,23 +30427,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79956576-308D-4576-AFE1-2F4C0F3C33E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1490ee3b-8825-4a14-a799-bb3413729370"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{511DD2B5-8036-4C02-853A-E0965342EFE0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -29947,6 +30445,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79956576-308D-4576-AFE1-2F4C0F3C33E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1490ee3b-8825-4a14-a799-bb3413729370"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFCA9A7-8661-43F7-BFD7-3C6B027F5CB3}">
   <ds:schemaRefs>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D50079E1-18E7-E743-8053-895205BE371E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7592E4B-E368-A142-8097-971D21686C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="27040" windowHeight="16880" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="27040" windowHeight="16880" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="187">
   <si>
     <t>%FeT</t>
   </si>
@@ -887,6 +887,24 @@
   <si>
     <t>Recep PLEITO</t>
   </si>
+  <si>
+    <t>Recep SF CRISTALES</t>
+  </si>
+  <si>
+    <t>Recep SF CARO</t>
+  </si>
+  <si>
+    <t>Recep SF ALGARROBO</t>
+  </si>
+  <si>
+    <t>Recep GR ALGARROBO</t>
+  </si>
+  <si>
+    <t>Recep GR CRISTALES</t>
+  </si>
+  <si>
+    <t>Recep GR PLEITO</t>
+  </si>
 </sst>
 </file>
 
@@ -901,7 +919,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
     <numFmt numFmtId="169" formatCode="#,##0.0000000_ ;\-#,##0.0000000\ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1075,14 +1093,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="2"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -1161,12 +1171,12 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1263,8 +1273,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="44">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -1819,6 +1835,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1829,7 +1860,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="296">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2106,7 +2137,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2134,85 +2164,85 @@
     <xf numFmtId="165" fontId="17" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2221,7 +2251,7 @@
     <xf numFmtId="9" fontId="17" fillId="14" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="27" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="26" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="17" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2230,10 +2260,10 @@
     <xf numFmtId="164" fontId="17" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="3" fontId="32" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="32" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="31" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2249,23 +2279,19 @@
     <xf numFmtId="3" fontId="17" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="9" fontId="35" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="35" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="36" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="20" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2285,13 +2311,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2571,6 +2597,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="35" fillId="17" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Millares 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -16866,13 +16894,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46">
-      <c r="A1" s="134">
+      <c r="A1" s="133">
         <v>88507</v>
       </c>
-      <c r="B1" s="134">
+      <c r="B1" s="133">
         <v>88507</v>
       </c>
-      <c r="C1" s="138">
+      <c r="C1" s="137">
         <v>39.119999999999997</v>
       </c>
       <c r="D1" s="119">
@@ -16882,18 +16910,18 @@
         <v>0.01</v>
       </c>
       <c r="F1" s="118"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="134"/>
-      <c r="L1" s="134"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
     </row>
     <row r="2" spans="1:46">
-      <c r="A2" s="134">
-        <v>0</v>
-      </c>
-      <c r="B2" s="134">
-        <v>0</v>
-      </c>
-      <c r="C2" s="138">
+      <c r="A2" s="133">
+        <v>0</v>
+      </c>
+      <c r="B2" s="133">
+        <v>0</v>
+      </c>
+      <c r="C2" s="137">
         <v>0</v>
       </c>
       <c r="D2" s="119">
@@ -16903,18 +16931,18 @@
         <v>2E-3</v>
       </c>
       <c r="F2" s="118"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="134"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
     </row>
     <row r="3" spans="1:46">
-      <c r="A3" s="134">
+      <c r="A3" s="133">
         <v>22063</v>
       </c>
-      <c r="B3" s="134">
+      <c r="B3" s="133">
         <v>22063</v>
       </c>
-      <c r="C3" s="138">
+      <c r="C3" s="137">
         <v>18.059999999999999</v>
       </c>
       <c r="D3" s="119">
@@ -16924,9 +16952,9 @@
         <v>0.01</v>
       </c>
       <c r="F3" s="118"/>
-      <c r="J3" s="135"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="135"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
       <c r="M3" s="93"/>
       <c r="N3" s="93"/>
       <c r="O3" s="93"/>
@@ -16962,13 +16990,13 @@
       <c r="AS3" s="92"/>
     </row>
     <row r="4" spans="1:46">
-      <c r="A4" s="134">
+      <c r="A4" s="133">
         <v>66444</v>
       </c>
-      <c r="B4" s="134">
+      <c r="B4" s="133">
         <v>66444</v>
       </c>
-      <c r="C4" s="138">
+      <c r="C4" s="137">
         <v>46.17</v>
       </c>
       <c r="D4" s="119">
@@ -16978,18 +17006,18 @@
         <v>0.01</v>
       </c>
       <c r="F4" s="118"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
     </row>
     <row r="5" spans="1:46">
-      <c r="A5" s="134">
+      <c r="A5" s="133">
         <v>43180</v>
       </c>
-      <c r="B5" s="134">
+      <c r="B5" s="133">
         <v>43180</v>
       </c>
-      <c r="C5" s="138">
+      <c r="C5" s="137">
         <v>48.24</v>
       </c>
       <c r="D5" s="119">
@@ -16999,18 +17027,18 @@
         <v>5.5270451317286735E-3</v>
       </c>
       <c r="F5" s="118"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
     </row>
     <row r="6" spans="1:46">
-      <c r="A6" s="134">
+      <c r="A6" s="133">
         <v>-42218</v>
       </c>
-      <c r="B6" s="134">
+      <c r="B6" s="133">
         <v>-41795</v>
       </c>
-      <c r="C6" s="138">
+      <c r="C6" s="137">
         <v>48.24</v>
       </c>
       <c r="D6" s="119">
@@ -17020,18 +17048,18 @@
         <v>8.2429505952969703E-3</v>
       </c>
       <c r="F6" s="118"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="133"/>
     </row>
     <row r="7" spans="1:46">
-      <c r="A7" s="134">
+      <c r="A7" s="133">
         <v>151419</v>
       </c>
-      <c r="B7" s="134">
+      <c r="B7" s="133">
         <v>151419</v>
       </c>
-      <c r="C7" s="138">
+      <c r="C7" s="137">
         <v>45.68</v>
       </c>
       <c r="D7" s="119">
@@ -17041,18 +17069,18 @@
         <v>1.0993716565736344E-2</v>
       </c>
       <c r="F7" s="118"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
-      <c r="L7" s="134"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
     </row>
     <row r="8" spans="1:46">
-      <c r="A8" s="134">
-        <v>0</v>
-      </c>
-      <c r="B8" s="134">
-        <v>0</v>
-      </c>
-      <c r="C8" s="138">
+      <c r="A8" s="133">
+        <v>0</v>
+      </c>
+      <c r="B8" s="133">
+        <v>0</v>
+      </c>
+      <c r="C8" s="137">
         <v>0</v>
       </c>
       <c r="D8" s="119">
@@ -17062,18 +17090,18 @@
         <v>0</v>
       </c>
       <c r="F8" s="118"/>
-      <c r="J8" s="134"/>
-      <c r="K8" s="134"/>
-      <c r="L8" s="134"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
     </row>
     <row r="9" spans="1:46">
-      <c r="A9" s="134">
+      <c r="A9" s="133">
         <v>31344</v>
       </c>
-      <c r="B9" s="134">
+      <c r="B9" s="133">
         <v>47016</v>
       </c>
-      <c r="C9" s="138">
+      <c r="C9" s="137">
         <v>32.64</v>
       </c>
       <c r="D9" s="119">
@@ -17083,18 +17111,18 @@
         <v>9.7942392473118298E-2</v>
       </c>
       <c r="F9" s="118"/>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
     </row>
     <row r="10" spans="1:46">
-      <c r="A10" s="134">
+      <c r="A10" s="133">
         <v>9611</v>
       </c>
-      <c r="B10" s="134">
+      <c r="B10" s="133">
         <v>10446.465614000001</v>
       </c>
-      <c r="C10" s="138">
+      <c r="C10" s="137">
         <v>17.600000000000001</v>
       </c>
       <c r="D10" s="119">
@@ -17104,19 +17132,19 @@
         <v>0</v>
       </c>
       <c r="F10" s="118"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
       <c r="AT10" s="2"/>
     </row>
     <row r="11" spans="1:46">
-      <c r="A11" s="134">
+      <c r="A11" s="133">
         <v>56684</v>
       </c>
-      <c r="B11" s="134">
+      <c r="B11" s="133">
         <v>56684</v>
       </c>
-      <c r="C11" s="138">
+      <c r="C11" s="137">
         <v>52</v>
       </c>
       <c r="D11" s="119">
@@ -17126,18 +17154,18 @@
         <v>6.1987555650731198E-2</v>
       </c>
       <c r="F11" s="118"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
     </row>
     <row r="12" spans="1:46">
-      <c r="A12" s="134">
+      <c r="A12" s="133">
         <v>52614</v>
       </c>
-      <c r="B12" s="134">
+      <c r="B12" s="133">
         <v>37272.534385999999</v>
       </c>
-      <c r="C12" s="138">
+      <c r="C12" s="137">
         <v>57.6</v>
       </c>
       <c r="D12" s="119">
@@ -17147,18 +17175,18 @@
         <v>2.2000000000000002E-2</v>
       </c>
       <c r="F12" s="118"/>
-      <c r="J12" s="134"/>
-      <c r="K12" s="134"/>
-      <c r="L12" s="134"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
     </row>
     <row r="13" spans="1:46">
-      <c r="A13" s="134">
+      <c r="A13" s="133">
         <v>28383</v>
       </c>
-      <c r="B13" s="134">
+      <c r="B13" s="133">
         <v>28383</v>
       </c>
-      <c r="C13" s="138">
+      <c r="C13" s="137">
         <v>50.8</v>
       </c>
       <c r="D13" s="119">
@@ -17168,18 +17196,18 @@
         <v>6.3612580645161274E-2</v>
       </c>
       <c r="F13" s="118"/>
-      <c r="J13" s="134"/>
-      <c r="K13" s="134"/>
-      <c r="L13" s="134"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
     </row>
     <row r="14" spans="1:46">
-      <c r="A14" s="134">
+      <c r="A14" s="133">
         <v>4463</v>
       </c>
-      <c r="B14" s="134">
+      <c r="B14" s="133">
         <v>791</v>
       </c>
-      <c r="C14" s="138">
+      <c r="C14" s="137">
         <v>54.46</v>
       </c>
       <c r="D14" s="119">
@@ -17189,18 +17217,18 @@
         <v>0.01</v>
       </c>
       <c r="F14" s="118"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
     </row>
     <row r="15" spans="1:46">
-      <c r="A15" s="134">
+      <c r="A15" s="133">
         <v>104882</v>
       </c>
-      <c r="B15" s="134">
+      <c r="B15" s="133">
         <v>104882</v>
       </c>
-      <c r="C15" s="138">
+      <c r="C15" s="137">
         <v>54.46</v>
       </c>
       <c r="D15" s="119">
@@ -17210,18 +17238,18 @@
         <v>2.2000000000000002E-2</v>
       </c>
       <c r="F15" s="118"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="134"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
     </row>
     <row r="16" spans="1:46">
-      <c r="A16" s="134">
+      <c r="A16" s="133">
         <v>45670</v>
       </c>
-      <c r="B16" s="134">
+      <c r="B16" s="133">
         <v>37746.534385999999</v>
       </c>
-      <c r="C16" s="138">
+      <c r="C16" s="137">
         <v>8.18</v>
       </c>
       <c r="D16" s="119">
@@ -17231,19 +17259,19 @@
         <v>0</v>
       </c>
       <c r="F16" s="118"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
       <c r="M16" s="122"/>
     </row>
     <row r="17" spans="1:32">
-      <c r="A17" s="134">
+      <c r="A17" s="133">
         <v>132791</v>
       </c>
-      <c r="B17" s="134">
+      <c r="B17" s="133">
         <v>132791</v>
       </c>
-      <c r="C17" s="138">
+      <c r="C17" s="137">
         <v>66.599999999999994</v>
       </c>
       <c r="D17" s="119">
@@ -17253,19 +17281,19 @@
         <v>8.199999999999999E-2</v>
       </c>
       <c r="F17" s="118"/>
-      <c r="J17" s="134"/>
-      <c r="K17" s="134"/>
-      <c r="L17" s="134"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="133"/>
       <c r="M17" s="122"/>
     </row>
     <row r="18" spans="1:32">
-      <c r="A18" s="134">
+      <c r="A18" s="133">
         <v>2702</v>
       </c>
-      <c r="B18" s="134">
+      <c r="B18" s="133">
         <v>3316</v>
       </c>
-      <c r="C18" s="138">
+      <c r="C18" s="137">
         <v>66.599999999999994</v>
       </c>
       <c r="D18" s="119">
@@ -17275,19 +17303,19 @@
         <v>8.4083959293394767E-2</v>
       </c>
       <c r="F18" s="118"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="134"/>
+      <c r="J18" s="133"/>
+      <c r="K18" s="133"/>
+      <c r="L18" s="133"/>
       <c r="M18" s="122"/>
     </row>
     <row r="19" spans="1:32">
-      <c r="A19" s="134">
-        <v>0</v>
-      </c>
-      <c r="B19" s="134">
-        <v>0</v>
-      </c>
-      <c r="C19" s="138">
+      <c r="A19" s="133">
+        <v>0</v>
+      </c>
+      <c r="B19" s="133">
+        <v>0</v>
+      </c>
+      <c r="C19" s="137">
         <v>0</v>
       </c>
       <c r="D19" s="119">
@@ -17297,19 +17325,19 @@
         <v>0</v>
       </c>
       <c r="F19" s="118"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="134"/>
+      <c r="J19" s="133"/>
+      <c r="K19" s="133"/>
+      <c r="L19" s="133"/>
       <c r="M19" s="122"/>
     </row>
     <row r="20" spans="1:32">
-      <c r="A20" s="134">
+      <c r="A20" s="133">
         <v>129475</v>
       </c>
-      <c r="B20" s="134">
+      <c r="B20" s="133">
         <v>129475</v>
       </c>
-      <c r="C20" s="138">
+      <c r="C20" s="137">
         <v>66.59</v>
       </c>
       <c r="D20" s="119">
@@ -17319,19 +17347,19 @@
         <v>8.6167918586789544E-2</v>
       </c>
       <c r="F20" s="118"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="134"/>
+      <c r="J20" s="133"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="133"/>
       <c r="M20" s="122"/>
     </row>
     <row r="21" spans="1:32">
-      <c r="A21" s="134">
-        <v>0</v>
-      </c>
-      <c r="B21" s="134">
-        <v>0</v>
-      </c>
-      <c r="C21" s="138">
+      <c r="A21" s="133">
+        <v>0</v>
+      </c>
+      <c r="B21" s="133">
+        <v>0</v>
+      </c>
+      <c r="C21" s="137">
         <v>66.59</v>
       </c>
       <c r="D21" s="119">
@@ -17341,19 +17369,19 @@
         <v>8.6167918586789544E-2</v>
       </c>
       <c r="F21" s="118"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
-      <c r="L21" s="134"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="133"/>
       <c r="M21" s="122"/>
     </row>
     <row r="22" spans="1:32">
-      <c r="A22" s="134">
+      <c r="A22" s="133">
         <v>129475</v>
       </c>
-      <c r="B22" s="134">
+      <c r="B22" s="133">
         <v>129475</v>
       </c>
-      <c r="C22" s="138">
+      <c r="C22" s="137">
         <v>66.59</v>
       </c>
       <c r="D22" s="119">
@@ -17363,19 +17391,19 @@
         <v>8.6167918586789544E-2</v>
       </c>
       <c r="F22" s="118"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="133"/>
       <c r="M22" s="122"/>
     </row>
     <row r="23" spans="1:32">
-      <c r="A23" s="134">
+      <c r="A23" s="133">
         <v>26081</v>
       </c>
-      <c r="B23" s="134">
+      <c r="B23" s="133">
         <v>25089</v>
       </c>
-      <c r="C23" s="138">
+      <c r="C23" s="137">
         <v>66.59</v>
       </c>
       <c r="D23" s="119">
@@ -17385,19 +17413,19 @@
         <v>8.6167918586789544E-2</v>
       </c>
       <c r="F23" s="118"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="134"/>
-      <c r="L23" s="134"/>
+      <c r="J23" s="133"/>
+      <c r="K23" s="133"/>
+      <c r="L23" s="133"/>
       <c r="M23" s="123"/>
     </row>
     <row r="24" spans="1:32">
-      <c r="A24" s="134">
+      <c r="A24" s="133">
         <v>104386</v>
       </c>
-      <c r="B24" s="134">
+      <c r="B24" s="133">
         <v>104386</v>
       </c>
-      <c r="C24" s="138">
+      <c r="C24" s="137">
         <v>66.2</v>
       </c>
       <c r="D24" s="119">
@@ -17407,22 +17435,22 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="F24" s="118"/>
-      <c r="J24" s="134"/>
-      <c r="K24" s="134"/>
-      <c r="L24" s="134"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="133"/>
       <c r="M24" s="122"/>
       <c r="AD24" s="5"/>
       <c r="AE24" s="5"/>
       <c r="AF24" s="5"/>
     </row>
     <row r="25" spans="1:32">
-      <c r="A25" s="134">
-        <v>0</v>
-      </c>
-      <c r="B25" s="134">
-        <v>0</v>
-      </c>
-      <c r="C25" s="138">
+      <c r="A25" s="133">
+        <v>0</v>
+      </c>
+      <c r="B25" s="133">
+        <v>0</v>
+      </c>
+      <c r="C25" s="137">
         <v>0</v>
       </c>
       <c r="D25" s="119">
@@ -17432,22 +17460,22 @@
         <v>0</v>
       </c>
       <c r="F25" s="118"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="134"/>
-      <c r="L25" s="134"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="133"/>
       <c r="M25" s="122"/>
       <c r="AD25" s="5"/>
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
     <row r="26" spans="1:32">
-      <c r="A26" s="134">
-        <v>0</v>
-      </c>
-      <c r="B26" s="134">
-        <v>0</v>
-      </c>
-      <c r="C26" s="138">
+      <c r="A26" s="133">
+        <v>0</v>
+      </c>
+      <c r="B26" s="133">
+        <v>0</v>
+      </c>
+      <c r="C26" s="137">
         <v>0</v>
       </c>
       <c r="D26" s="119">
@@ -17457,22 +17485,22 @@
         <v>7.0699999999999999E-3</v>
       </c>
       <c r="F26" s="118"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="134"/>
-      <c r="L26" s="134"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="133"/>
       <c r="M26" s="122"/>
       <c r="AD26" s="5"/>
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
     <row r="27" spans="1:32">
-      <c r="A27" s="134">
-        <v>0</v>
-      </c>
-      <c r="B27" s="134">
-        <v>0</v>
-      </c>
-      <c r="C27" s="138">
+      <c r="A27" s="133">
+        <v>0</v>
+      </c>
+      <c r="B27" s="133">
+        <v>0</v>
+      </c>
+      <c r="C27" s="137">
         <v>0</v>
       </c>
       <c r="D27" s="119">
@@ -17482,22 +17510,22 @@
         <v>0</v>
       </c>
       <c r="F27" s="118"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="134"/>
-      <c r="L27" s="134"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="133"/>
+      <c r="L27" s="133"/>
       <c r="M27" s="122"/>
       <c r="AD27" s="5"/>
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
     <row r="28" spans="1:32">
-      <c r="A28" s="134">
-        <v>0</v>
-      </c>
-      <c r="B28" s="134">
-        <v>0</v>
-      </c>
-      <c r="C28" s="138">
+      <c r="A28" s="133">
+        <v>0</v>
+      </c>
+      <c r="B28" s="133">
+        <v>0</v>
+      </c>
+      <c r="C28" s="137">
         <v>0</v>
       </c>
       <c r="D28" s="119">
@@ -17507,22 +17535,22 @@
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="F28" s="118"/>
-      <c r="J28" s="134"/>
-      <c r="K28" s="134"/>
-      <c r="L28" s="134"/>
+      <c r="J28" s="133"/>
+      <c r="K28" s="133"/>
+      <c r="L28" s="133"/>
       <c r="M28" s="122"/>
       <c r="AD28" s="5"/>
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
     </row>
     <row r="29" spans="1:32">
-      <c r="A29" s="134">
-        <v>0</v>
-      </c>
-      <c r="B29" s="134">
-        <v>0</v>
-      </c>
-      <c r="C29" s="138">
+      <c r="A29" s="133">
+        <v>0</v>
+      </c>
+      <c r="B29" s="133">
+        <v>0</v>
+      </c>
+      <c r="C29" s="137">
         <v>0</v>
       </c>
       <c r="D29" s="119">
@@ -17532,22 +17560,22 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="F29" s="118"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="134"/>
-      <c r="L29" s="134"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="133"/>
+      <c r="L29" s="133"/>
       <c r="M29" s="122"/>
       <c r="AD29" s="5"/>
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
     <row r="30" spans="1:32">
-      <c r="A30" s="134">
-        <v>0</v>
-      </c>
-      <c r="B30" s="134">
-        <v>0</v>
-      </c>
-      <c r="C30" s="138">
+      <c r="A30" s="133">
+        <v>0</v>
+      </c>
+      <c r="B30" s="133">
+        <v>0</v>
+      </c>
+      <c r="C30" s="137">
         <v>0</v>
       </c>
       <c r="D30" s="119">
@@ -17557,22 +17585,22 @@
         <v>0</v>
       </c>
       <c r="F30" s="118"/>
-      <c r="J30" s="134"/>
-      <c r="K30" s="134"/>
-      <c r="L30" s="134"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="133"/>
+      <c r="L30" s="133"/>
       <c r="M30" s="122"/>
       <c r="AD30" s="5"/>
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
     <row r="31" spans="1:32">
-      <c r="A31" s="134">
+      <c r="A31" s="133">
         <v>28070</v>
       </c>
-      <c r="B31" s="134">
+      <c r="B31" s="133">
         <v>27987</v>
       </c>
-      <c r="C31" s="138">
+      <c r="C31" s="137">
         <v>61.78</v>
       </c>
       <c r="D31" s="119">
@@ -17582,22 +17610,22 @@
         <v>0</v>
       </c>
       <c r="F31" s="118"/>
-      <c r="J31" s="134"/>
-      <c r="K31" s="134"/>
-      <c r="L31" s="134"/>
+      <c r="J31" s="133"/>
+      <c r="K31" s="133"/>
+      <c r="L31" s="133"/>
       <c r="M31" s="122"/>
       <c r="AD31" s="5"/>
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
     </row>
     <row r="32" spans="1:32">
-      <c r="A32" s="134">
+      <c r="A32" s="133">
         <v>18351</v>
       </c>
-      <c r="B32" s="134">
+      <c r="B32" s="133">
         <v>18351</v>
       </c>
-      <c r="C32" s="138">
+      <c r="C32" s="137">
         <v>62.17</v>
       </c>
       <c r="D32" s="119">
@@ -17607,22 +17635,22 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F32" s="118"/>
-      <c r="J32" s="134"/>
-      <c r="K32" s="134"/>
-      <c r="L32" s="134"/>
+      <c r="J32" s="133"/>
+      <c r="K32" s="133"/>
+      <c r="L32" s="133"/>
       <c r="M32" s="122"/>
       <c r="AD32" s="5"/>
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
     </row>
     <row r="33" spans="1:32">
-      <c r="A33" s="134">
+      <c r="A33" s="133">
         <v>5360</v>
       </c>
-      <c r="B33" s="134">
+      <c r="B33" s="133">
         <v>5360</v>
       </c>
-      <c r="C33" s="138">
+      <c r="C33" s="137">
         <v>60.46</v>
       </c>
       <c r="D33" s="119">
@@ -17632,22 +17660,22 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="F33" s="118"/>
-      <c r="J33" s="134"/>
-      <c r="K33" s="134"/>
-      <c r="L33" s="134"/>
+      <c r="J33" s="133"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
       <c r="M33" s="122"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
     </row>
     <row r="34" spans="1:32">
-      <c r="A34" s="134">
+      <c r="A34" s="133">
         <v>6394</v>
       </c>
-      <c r="B34" s="134">
+      <c r="B34" s="133">
         <v>6394</v>
       </c>
-      <c r="C34" s="138">
+      <c r="C34" s="137">
         <v>59.01</v>
       </c>
       <c r="D34" s="119">
@@ -17657,22 +17685,22 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F34" s="118"/>
-      <c r="J34" s="134"/>
-      <c r="K34" s="134"/>
-      <c r="L34" s="134"/>
+      <c r="J34" s="133"/>
+      <c r="K34" s="133"/>
+      <c r="L34" s="133"/>
       <c r="M34" s="122"/>
       <c r="AD34" s="5"/>
       <c r="AE34" s="3"/>
       <c r="AF34" s="3"/>
     </row>
     <row r="35" spans="1:32">
-      <c r="A35" s="134">
-        <v>0</v>
-      </c>
-      <c r="B35" s="134">
-        <v>0</v>
-      </c>
-      <c r="C35" s="138">
+      <c r="A35" s="133">
+        <v>0</v>
+      </c>
+      <c r="B35" s="133">
+        <v>0</v>
+      </c>
+      <c r="C35" s="137">
         <v>0</v>
       </c>
       <c r="D35" s="119">
@@ -17682,22 +17710,22 @@
         <v>0</v>
       </c>
       <c r="F35" s="118"/>
-      <c r="J35" s="134"/>
-      <c r="K35" s="134"/>
-      <c r="L35" s="134"/>
+      <c r="J35" s="133"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="133"/>
       <c r="M35" s="122"/>
       <c r="AD35" s="5"/>
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
     </row>
     <row r="36" spans="1:32">
-      <c r="A36" s="134">
+      <c r="A36" s="133">
         <v>6394</v>
       </c>
-      <c r="B36" s="134">
+      <c r="B36" s="133">
         <v>6394</v>
       </c>
-      <c r="C36" s="138">
+      <c r="C36" s="137">
         <v>59.01</v>
       </c>
       <c r="D36" s="119">
@@ -17707,22 +17735,22 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F36" s="118"/>
-      <c r="J36" s="134"/>
-      <c r="K36" s="134"/>
-      <c r="L36" s="134"/>
+      <c r="J36" s="133"/>
+      <c r="K36" s="133"/>
+      <c r="L36" s="133"/>
       <c r="M36" s="122"/>
       <c r="AD36" s="5"/>
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
     </row>
     <row r="37" spans="1:32">
-      <c r="A37" s="134">
-        <v>0</v>
-      </c>
-      <c r="B37" s="134">
-        <v>0</v>
-      </c>
-      <c r="C37" s="138">
+      <c r="A37" s="133">
+        <v>0</v>
+      </c>
+      <c r="B37" s="133">
+        <v>0</v>
+      </c>
+      <c r="C37" s="137">
         <v>0</v>
       </c>
       <c r="D37" s="119">
@@ -17732,22 +17760,22 @@
         <v>0</v>
       </c>
       <c r="F37" s="118"/>
-      <c r="J37" s="134"/>
-      <c r="K37" s="134"/>
-      <c r="L37" s="134"/>
+      <c r="J37" s="133"/>
+      <c r="K37" s="133"/>
+      <c r="L37" s="133"/>
       <c r="M37" s="122"/>
       <c r="AD37" s="5"/>
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
     <row r="38" spans="1:32">
-      <c r="A38" s="134">
-        <v>0</v>
-      </c>
-      <c r="B38" s="134">
-        <v>0</v>
-      </c>
-      <c r="C38" s="138">
+      <c r="A38" s="133">
+        <v>0</v>
+      </c>
+      <c r="B38" s="133">
+        <v>0</v>
+      </c>
+      <c r="C38" s="137">
         <v>0</v>
       </c>
       <c r="D38" s="119">
@@ -17757,22 +17785,22 @@
         <v>0</v>
       </c>
       <c r="F38" s="118"/>
-      <c r="J38" s="134"/>
-      <c r="K38" s="134"/>
-      <c r="L38" s="134"/>
+      <c r="J38" s="133"/>
+      <c r="K38" s="133"/>
+      <c r="L38" s="133"/>
       <c r="M38" s="122"/>
       <c r="AD38" s="5"/>
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
     </row>
     <row r="39" spans="1:32">
-      <c r="A39" s="134">
-        <v>0</v>
-      </c>
-      <c r="B39" s="134">
-        <v>0</v>
-      </c>
-      <c r="C39" s="138">
+      <c r="A39" s="133">
+        <v>0</v>
+      </c>
+      <c r="B39" s="133">
+        <v>0</v>
+      </c>
+      <c r="C39" s="137">
         <v>0</v>
       </c>
       <c r="D39" s="119">
@@ -17782,22 +17810,22 @@
         <v>0</v>
       </c>
       <c r="F39" s="118"/>
-      <c r="J39" s="134"/>
-      <c r="K39" s="134"/>
-      <c r="L39" s="134"/>
+      <c r="J39" s="133"/>
+      <c r="K39" s="133"/>
+      <c r="L39" s="133"/>
       <c r="M39" s="122"/>
       <c r="AD39" s="5"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
     </row>
     <row r="40" spans="1:32">
-      <c r="A40" s="134">
-        <v>0</v>
-      </c>
-      <c r="B40" s="134">
-        <v>0</v>
-      </c>
-      <c r="C40" s="138">
+      <c r="A40" s="133">
+        <v>0</v>
+      </c>
+      <c r="B40" s="133">
+        <v>0</v>
+      </c>
+      <c r="C40" s="137">
         <v>0</v>
       </c>
       <c r="D40" s="119">
@@ -17807,22 +17835,22 @@
         <v>0</v>
       </c>
       <c r="F40" s="118"/>
-      <c r="J40" s="134"/>
-      <c r="K40" s="134"/>
-      <c r="L40" s="134"/>
+      <c r="J40" s="133"/>
+      <c r="K40" s="133"/>
+      <c r="L40" s="133"/>
       <c r="M40" s="122"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
     </row>
     <row r="41" spans="1:32">
-      <c r="A41" s="134">
-        <v>0</v>
-      </c>
-      <c r="B41" s="134">
-        <v>0</v>
-      </c>
-      <c r="C41" s="138">
+      <c r="A41" s="133">
+        <v>0</v>
+      </c>
+      <c r="B41" s="133">
+        <v>0</v>
+      </c>
+      <c r="C41" s="137">
         <v>0</v>
       </c>
       <c r="D41" s="119">
@@ -17832,22 +17860,22 @@
         <v>0</v>
       </c>
       <c r="F41" s="118"/>
-      <c r="J41" s="134"/>
-      <c r="K41" s="134"/>
-      <c r="L41" s="134"/>
+      <c r="J41" s="133"/>
+      <c r="K41" s="133"/>
+      <c r="L41" s="133"/>
       <c r="M41" s="122"/>
       <c r="AD41" s="5"/>
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
     <row r="42" spans="1:32">
-      <c r="A42" s="134">
-        <v>0</v>
-      </c>
-      <c r="B42" s="134">
-        <v>0</v>
-      </c>
-      <c r="C42" s="138">
+      <c r="A42" s="133">
+        <v>0</v>
+      </c>
+      <c r="B42" s="133">
+        <v>0</v>
+      </c>
+      <c r="C42" s="137">
         <v>0</v>
       </c>
       <c r="D42" s="119">
@@ -17857,22 +17885,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="118"/>
-      <c r="J42" s="134"/>
-      <c r="K42" s="134"/>
-      <c r="L42" s="134"/>
+      <c r="J42" s="133"/>
+      <c r="K42" s="133"/>
+      <c r="L42" s="133"/>
       <c r="M42" s="122"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="3"/>
       <c r="AF42" s="3"/>
     </row>
     <row r="43" spans="1:32">
-      <c r="A43" s="134">
-        <v>0</v>
-      </c>
-      <c r="B43" s="134">
-        <v>0</v>
-      </c>
-      <c r="C43" s="138">
+      <c r="A43" s="133">
+        <v>0</v>
+      </c>
+      <c r="B43" s="133">
+        <v>0</v>
+      </c>
+      <c r="C43" s="137">
         <v>0</v>
       </c>
       <c r="D43" s="119">
@@ -17882,22 +17910,22 @@
         <v>0</v>
       </c>
       <c r="F43" s="118"/>
-      <c r="J43" s="134"/>
-      <c r="K43" s="134"/>
-      <c r="L43" s="134"/>
+      <c r="J43" s="133"/>
+      <c r="K43" s="133"/>
+      <c r="L43" s="133"/>
       <c r="M43" s="122"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
     </row>
     <row r="44" spans="1:32">
-      <c r="A44" s="134">
-        <v>0</v>
-      </c>
-      <c r="B44" s="134">
-        <v>0</v>
-      </c>
-      <c r="C44" s="138">
+      <c r="A44" s="133">
+        <v>0</v>
+      </c>
+      <c r="B44" s="133">
+        <v>0</v>
+      </c>
+      <c r="C44" s="137">
         <v>0</v>
       </c>
       <c r="D44" s="119">
@@ -17907,22 +17935,22 @@
         <v>0</v>
       </c>
       <c r="F44" s="118"/>
-      <c r="J44" s="134"/>
-      <c r="K44" s="134"/>
-      <c r="L44" s="134"/>
+      <c r="J44" s="133"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="133"/>
       <c r="M44" s="122"/>
       <c r="AD44" s="5"/>
       <c r="AE44" s="3"/>
       <c r="AF44" s="3"/>
     </row>
     <row r="45" spans="1:32">
-      <c r="A45" s="134">
-        <v>0</v>
-      </c>
-      <c r="B45" s="134">
-        <v>0</v>
-      </c>
-      <c r="C45" s="138">
+      <c r="A45" s="133">
+        <v>0</v>
+      </c>
+      <c r="B45" s="133">
+        <v>0</v>
+      </c>
+      <c r="C45" s="137">
         <v>0</v>
       </c>
       <c r="D45" s="119">
@@ -17932,22 +17960,22 @@
         <v>0</v>
       </c>
       <c r="F45" s="118"/>
-      <c r="J45" s="134"/>
-      <c r="K45" s="134"/>
-      <c r="L45" s="134"/>
+      <c r="J45" s="133"/>
+      <c r="K45" s="133"/>
+      <c r="L45" s="133"/>
       <c r="M45" s="122"/>
       <c r="AD45" s="5"/>
       <c r="AE45" s="3"/>
       <c r="AF45" s="3"/>
     </row>
     <row r="46" spans="1:32">
-      <c r="A46" s="134">
-        <v>0</v>
-      </c>
-      <c r="B46" s="134">
-        <v>0</v>
-      </c>
-      <c r="C46" s="138">
+      <c r="A46" s="133">
+        <v>0</v>
+      </c>
+      <c r="B46" s="133">
+        <v>0</v>
+      </c>
+      <c r="C46" s="137">
         <v>0</v>
       </c>
       <c r="D46" s="119">
@@ -17957,22 +17985,22 @@
         <v>0</v>
       </c>
       <c r="F46" s="118"/>
-      <c r="J46" s="134"/>
-      <c r="K46" s="134"/>
-      <c r="L46" s="134"/>
+      <c r="J46" s="133"/>
+      <c r="K46" s="133"/>
+      <c r="L46" s="133"/>
       <c r="M46" s="122"/>
       <c r="AD46" s="5"/>
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
     <row r="47" spans="1:32">
-      <c r="A47" s="134">
-        <v>0</v>
-      </c>
-      <c r="B47" s="134">
-        <v>0</v>
-      </c>
-      <c r="C47" s="138">
+      <c r="A47" s="133">
+        <v>0</v>
+      </c>
+      <c r="B47" s="133">
+        <v>0</v>
+      </c>
+      <c r="C47" s="137">
         <v>0</v>
       </c>
       <c r="D47" s="119">
@@ -17982,22 +18010,22 @@
         <v>0</v>
       </c>
       <c r="F47" s="118"/>
-      <c r="J47" s="134"/>
-      <c r="K47" s="134"/>
-      <c r="L47" s="134"/>
+      <c r="J47" s="133"/>
+      <c r="K47" s="133"/>
+      <c r="L47" s="133"/>
       <c r="M47" s="122"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="3"/>
       <c r="AF47" s="3"/>
     </row>
     <row r="48" spans="1:32">
-      <c r="A48" s="134">
-        <v>0</v>
-      </c>
-      <c r="B48" s="134">
-        <v>0</v>
-      </c>
-      <c r="C48" s="138">
+      <c r="A48" s="133">
+        <v>0</v>
+      </c>
+      <c r="B48" s="133">
+        <v>0</v>
+      </c>
+      <c r="C48" s="137">
         <v>0</v>
       </c>
       <c r="D48" s="119">
@@ -18007,22 +18035,22 @@
         <v>0</v>
       </c>
       <c r="F48" s="118"/>
-      <c r="J48" s="134"/>
-      <c r="K48" s="134"/>
-      <c r="L48" s="134"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="133"/>
+      <c r="L48" s="133"/>
       <c r="M48" s="122"/>
       <c r="AD48" s="5"/>
       <c r="AE48" s="3"/>
       <c r="AF48" s="3"/>
     </row>
     <row r="49" spans="1:32">
-      <c r="A49" s="134">
-        <v>0</v>
-      </c>
-      <c r="B49" s="134">
-        <v>0</v>
-      </c>
-      <c r="C49" s="138">
+      <c r="A49" s="133">
+        <v>0</v>
+      </c>
+      <c r="B49" s="133">
+        <v>0</v>
+      </c>
+      <c r="C49" s="137">
         <v>0</v>
       </c>
       <c r="D49" s="119">
@@ -18032,22 +18060,22 @@
         <v>0</v>
       </c>
       <c r="F49" s="118"/>
-      <c r="J49" s="134"/>
-      <c r="K49" s="134"/>
-      <c r="L49" s="134"/>
+      <c r="J49" s="133"/>
+      <c r="K49" s="133"/>
+      <c r="L49" s="133"/>
       <c r="M49" s="122"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="3"/>
       <c r="AF49" s="3"/>
     </row>
     <row r="50" spans="1:32">
-      <c r="A50" s="134">
-        <v>0</v>
-      </c>
-      <c r="B50" s="134">
-        <v>0</v>
-      </c>
-      <c r="C50" s="138">
+      <c r="A50" s="133">
+        <v>0</v>
+      </c>
+      <c r="B50" s="133">
+        <v>0</v>
+      </c>
+      <c r="C50" s="137">
         <v>0</v>
       </c>
       <c r="D50" s="119">
@@ -18057,22 +18085,22 @@
         <v>0</v>
       </c>
       <c r="F50" s="118"/>
-      <c r="J50" s="134"/>
-      <c r="K50" s="134"/>
-      <c r="L50" s="134"/>
+      <c r="J50" s="133"/>
+      <c r="K50" s="133"/>
+      <c r="L50" s="133"/>
       <c r="M50" s="122"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="3"/>
       <c r="AF50" s="3"/>
     </row>
     <row r="51" spans="1:32">
-      <c r="A51" s="134">
-        <v>0</v>
-      </c>
-      <c r="B51" s="134">
-        <v>0</v>
-      </c>
-      <c r="C51" s="138">
+      <c r="A51" s="133">
+        <v>0</v>
+      </c>
+      <c r="B51" s="133">
+        <v>0</v>
+      </c>
+      <c r="C51" s="137">
         <v>0</v>
       </c>
       <c r="D51" s="119">
@@ -18082,22 +18110,22 @@
         <v>0</v>
       </c>
       <c r="F51" s="118"/>
-      <c r="J51" s="134"/>
-      <c r="K51" s="134"/>
-      <c r="L51" s="134"/>
+      <c r="J51" s="133"/>
+      <c r="K51" s="133"/>
+      <c r="L51" s="133"/>
       <c r="M51" s="122"/>
       <c r="AD51" s="5"/>
       <c r="AE51" s="3"/>
       <c r="AF51" s="3"/>
     </row>
     <row r="52" spans="1:32">
-      <c r="A52" s="134">
+      <c r="A52" s="133">
         <v>77372</v>
       </c>
-      <c r="B52" s="134">
+      <c r="B52" s="133">
         <v>77372</v>
       </c>
-      <c r="C52" s="138">
+      <c r="C52" s="137">
         <v>54</v>
       </c>
       <c r="D52" s="119">
@@ -18107,22 +18135,22 @@
         <v>2.0286666666666665E-2</v>
       </c>
       <c r="F52" s="118"/>
-      <c r="J52" s="134"/>
-      <c r="K52" s="134"/>
-      <c r="L52" s="134"/>
+      <c r="J52" s="133"/>
+      <c r="K52" s="133"/>
+      <c r="L52" s="133"/>
       <c r="M52" s="122"/>
       <c r="AD52" s="5"/>
       <c r="AE52" s="3"/>
       <c r="AF52" s="3"/>
     </row>
     <row r="53" spans="1:32">
-      <c r="A53" s="134">
+      <c r="A53" s="133">
         <v>77372</v>
       </c>
-      <c r="B53" s="134">
+      <c r="B53" s="133">
         <v>77372</v>
       </c>
-      <c r="C53" s="138">
+      <c r="C53" s="137">
         <v>54</v>
       </c>
       <c r="D53" s="119">
@@ -18132,22 +18160,22 @@
         <v>2.0286666666666665E-2</v>
       </c>
       <c r="F53" s="118"/>
-      <c r="J53" s="134"/>
-      <c r="K53" s="134"/>
-      <c r="L53" s="134"/>
+      <c r="J53" s="133"/>
+      <c r="K53" s="133"/>
+      <c r="L53" s="133"/>
       <c r="M53" s="122"/>
       <c r="AD53" s="5"/>
       <c r="AE53" s="3"/>
       <c r="AF53" s="3"/>
     </row>
     <row r="54" spans="1:32">
-      <c r="A54" s="134">
+      <c r="A54" s="133">
         <v>4403</v>
       </c>
-      <c r="B54" s="134">
+      <c r="B54" s="133">
         <v>4403</v>
       </c>
-      <c r="C54" s="138">
+      <c r="C54" s="137">
         <v>62.14</v>
       </c>
       <c r="D54" s="119">
@@ -18157,22 +18185,22 @@
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="F54" s="118"/>
-      <c r="J54" s="134"/>
-      <c r="K54" s="134"/>
-      <c r="L54" s="134"/>
+      <c r="J54" s="133"/>
+      <c r="K54" s="133"/>
+      <c r="L54" s="133"/>
       <c r="M54" s="122"/>
       <c r="AD54" s="5"/>
       <c r="AE54" s="3"/>
       <c r="AF54" s="3"/>
     </row>
     <row r="55" spans="1:32">
-      <c r="A55" s="134">
+      <c r="A55" s="133">
         <v>127</v>
       </c>
-      <c r="B55" s="134">
+      <c r="B55" s="133">
         <v>127</v>
       </c>
-      <c r="C55" s="138">
+      <c r="C55" s="137">
         <v>66.59</v>
       </c>
       <c r="D55" s="119">
@@ -18182,108 +18210,108 @@
         <v>8.6167918586789544E-2</v>
       </c>
       <c r="F55" s="118"/>
-      <c r="J55" s="134"/>
-      <c r="K55" s="134"/>
-      <c r="L55" s="134"/>
+      <c r="J55" s="133"/>
+      <c r="K55" s="133"/>
+      <c r="L55" s="133"/>
       <c r="M55" s="122"/>
       <c r="AD55" s="5"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
     </row>
     <row r="56" spans="1:32">
-      <c r="A56" s="134"/>
-      <c r="B56" s="134"/>
-      <c r="C56" s="134"/>
+      <c r="A56" s="133"/>
+      <c r="B56" s="133"/>
+      <c r="C56" s="133"/>
       <c r="D56" s="118"/>
       <c r="E56" s="118"/>
       <c r="F56" s="118"/>
-      <c r="J56" s="134"/>
-      <c r="K56" s="134"/>
-      <c r="L56" s="134"/>
+      <c r="J56" s="133"/>
+      <c r="K56" s="133"/>
+      <c r="L56" s="133"/>
       <c r="M56" s="122"/>
       <c r="AD56" s="5"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
     </row>
     <row r="57" spans="1:32">
-      <c r="A57" s="134"/>
-      <c r="B57" s="134"/>
-      <c r="C57" s="134"/>
+      <c r="A57" s="133"/>
+      <c r="B57" s="133"/>
+      <c r="C57" s="133"/>
       <c r="D57" s="118"/>
       <c r="E57" s="118"/>
       <c r="F57" s="118"/>
-      <c r="J57" s="134"/>
-      <c r="K57" s="134"/>
-      <c r="L57" s="134"/>
+      <c r="J57" s="133"/>
+      <c r="K57" s="133"/>
+      <c r="L57" s="133"/>
       <c r="M57" s="122"/>
       <c r="AD57" s="5"/>
       <c r="AE57" s="3"/>
       <c r="AF57" s="3"/>
     </row>
     <row r="58" spans="1:32">
-      <c r="A58" s="134"/>
-      <c r="B58" s="134"/>
-      <c r="C58" s="134"/>
+      <c r="A58" s="133"/>
+      <c r="B58" s="133"/>
+      <c r="C58" s="133"/>
       <c r="D58" s="118"/>
       <c r="E58" s="118"/>
       <c r="F58" s="118"/>
-      <c r="J58" s="134"/>
-      <c r="K58" s="134"/>
-      <c r="L58" s="134"/>
+      <c r="J58" s="133"/>
+      <c r="K58" s="133"/>
+      <c r="L58" s="133"/>
       <c r="M58" s="122"/>
       <c r="AD58" s="5"/>
       <c r="AE58" s="3"/>
       <c r="AF58" s="3"/>
     </row>
     <row r="59" spans="1:32">
-      <c r="A59" s="134"/>
-      <c r="B59" s="134"/>
-      <c r="C59" s="134"/>
+      <c r="A59" s="133"/>
+      <c r="B59" s="133"/>
+      <c r="C59" s="133"/>
       <c r="D59" s="118"/>
       <c r="E59" s="118"/>
       <c r="F59" s="118"/>
-      <c r="J59" s="134"/>
-      <c r="K59" s="134"/>
-      <c r="L59" s="134"/>
+      <c r="J59" s="133"/>
+      <c r="K59" s="133"/>
+      <c r="L59" s="133"/>
       <c r="M59" s="122"/>
       <c r="AD59" s="5"/>
       <c r="AE59" s="3"/>
       <c r="AF59" s="3"/>
     </row>
     <row r="60" spans="1:32" ht="19">
-      <c r="A60" s="134"/>
-      <c r="B60" s="134"/>
-      <c r="C60" s="134"/>
+      <c r="A60" s="133"/>
+      <c r="B60" s="133"/>
+      <c r="C60" s="133"/>
       <c r="D60" s="118"/>
       <c r="E60" s="118"/>
       <c r="F60" s="118"/>
-      <c r="J60" s="203" t="s">
+      <c r="J60" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="K60" s="203"/>
-      <c r="L60" s="203"/>
+      <c r="K60" s="198"/>
+      <c r="L60" s="198"/>
       <c r="M60" s="122"/>
-      <c r="N60" s="204"/>
-      <c r="O60" s="204"/>
+      <c r="N60" s="199"/>
+      <c r="O60" s="199"/>
       <c r="R60" s="98"/>
       <c r="AD60" s="5"/>
       <c r="AE60" s="3"/>
       <c r="AF60" s="3"/>
     </row>
     <row r="61" spans="1:32">
-      <c r="A61" s="134"/>
-      <c r="B61" s="134"/>
-      <c r="C61" s="134"/>
+      <c r="A61" s="133"/>
+      <c r="B61" s="133"/>
+      <c r="C61" s="133"/>
       <c r="D61" s="118"/>
       <c r="E61" s="118"/>
       <c r="F61" s="118"/>
-      <c r="J61" s="136" t="s">
+      <c r="J61" s="135" t="s">
         <v>1</v>
       </c>
-      <c r="K61" s="136" t="s">
-        <v>0</v>
-      </c>
-      <c r="L61" s="136" t="s">
+      <c r="K61" s="135" t="s">
+        <v>0</v>
+      </c>
+      <c r="L61" s="135" t="s">
         <v>69</v>
       </c>
       <c r="M61" s="122"/>
@@ -18298,24 +18326,24 @@
       <c r="AF61" s="3"/>
     </row>
     <row r="62" spans="1:32" ht="16">
-      <c r="A62" s="134"/>
-      <c r="B62" s="134"/>
-      <c r="C62" s="134"/>
+      <c r="A62" s="133"/>
+      <c r="B62" s="133"/>
+      <c r="C62" s="133"/>
       <c r="D62" s="118"/>
       <c r="E62" s="118"/>
       <c r="F62" s="118"/>
       <c r="I62" t="s">
         <v>14</v>
       </c>
-      <c r="J62" s="134">
+      <c r="J62" s="133">
         <f>B1</f>
         <v>88507</v>
       </c>
-      <c r="K62" s="138">
+      <c r="K62" s="137">
         <f>IF(D1&gt;1,D1/100,D1)</f>
         <v>0.38135957855999997</v>
       </c>
-      <c r="L62" s="137">
+      <c r="L62" s="136">
         <f>+J62*K62</f>
         <v>33752.992219609914</v>
       </c>
@@ -18333,25 +18361,25 @@
       <c r="AF62" s="3"/>
     </row>
     <row r="63" spans="1:32" ht="16">
-      <c r="A63" s="134"/>
-      <c r="B63" s="134"/>
-      <c r="C63" s="134"/>
+      <c r="A63" s="133"/>
+      <c r="B63" s="133"/>
+      <c r="C63" s="133"/>
       <c r="D63" s="118"/>
       <c r="E63" s="118"/>
       <c r="F63" s="118"/>
       <c r="I63" t="s">
         <v>15</v>
       </c>
-      <c r="J63" s="134">
-        <f t="shared" ref="J63:J116" si="0">B2</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="138">
-        <f t="shared" ref="K63:K116" si="1">IF(D2&gt;1,D2/100,D2)</f>
-        <v>0</v>
-      </c>
-      <c r="L63" s="137">
-        <f t="shared" ref="L63:L116" si="2">+J63*K63</f>
+      <c r="J63" s="133">
+        <f t="shared" ref="J63:J108" si="0">B2</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="137">
+        <f t="shared" ref="K63:K108" si="1">IF(D2&gt;1,D2/100,D2)</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="136">
+        <f t="shared" ref="L63:L108" si="2">+J63*K63</f>
         <v>0</v>
       </c>
       <c r="M63" s="122"/>
@@ -18368,24 +18396,24 @@
       <c r="AF63" s="3"/>
     </row>
     <row r="64" spans="1:32" ht="16">
-      <c r="A64" s="134"/>
-      <c r="B64" s="134"/>
-      <c r="C64" s="134"/>
+      <c r="A64" s="133"/>
+      <c r="B64" s="133"/>
+      <c r="C64" s="133"/>
       <c r="D64" s="118"/>
       <c r="E64" s="118"/>
       <c r="F64" s="118"/>
       <c r="I64" t="s">
         <v>16</v>
       </c>
-      <c r="J64" s="134">
+      <c r="J64" s="133">
         <f t="shared" si="0"/>
         <v>22063</v>
       </c>
-      <c r="K64" s="138">
+      <c r="K64" s="137">
         <f t="shared" si="1"/>
         <v>0.18112284201000001</v>
       </c>
-      <c r="L64" s="137">
+      <c r="L64" s="136">
         <f t="shared" si="2"/>
         <v>3996.1132632666299</v>
       </c>
@@ -18403,26 +18431,26 @@
       <c r="AF64" s="3"/>
     </row>
     <row r="65" spans="1:32" ht="16">
-      <c r="A65" s="134"/>
-      <c r="B65" s="134"/>
-      <c r="C65" s="134"/>
+      <c r="A65" s="133"/>
+      <c r="B65" s="133"/>
+      <c r="C65" s="133"/>
       <c r="D65" s="118"/>
       <c r="E65" s="118"/>
       <c r="F65" s="118"/>
-      <c r="G65" s="163"/>
-      <c r="H65" s="164"/>
-      <c r="I65" s="134" t="s">
+      <c r="G65" s="162"/>
+      <c r="H65" s="163"/>
+      <c r="I65" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="134">
+      <c r="J65" s="133">
         <f t="shared" si="0"/>
         <v>66444</v>
       </c>
-      <c r="K65" s="138">
+      <c r="K65" s="137">
         <f t="shared" si="1"/>
         <v>0.447849</v>
       </c>
-      <c r="L65" s="137">
+      <c r="L65" s="136">
         <f t="shared" si="2"/>
         <v>29756.878956</v>
       </c>
@@ -18446,20 +18474,20 @@
       <c r="D66" s="118"/>
       <c r="E66" s="118"/>
       <c r="F66" s="118"/>
-      <c r="G66" s="163"/>
-      <c r="H66" s="164"/>
-      <c r="I66" s="134" t="s">
+      <c r="G66" s="162"/>
+      <c r="H66" s="163"/>
+      <c r="I66" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="J66" s="134">
+      <c r="J66" s="133">
         <f t="shared" si="0"/>
         <v>43180</v>
       </c>
-      <c r="K66" s="138">
+      <c r="K66" s="137">
         <f t="shared" si="1"/>
         <v>0.4824</v>
       </c>
-      <c r="L66" s="137">
+      <c r="L66" s="136">
         <f t="shared" si="2"/>
         <v>20830.031999999999</v>
       </c>
@@ -18483,20 +18511,20 @@
       <c r="D67" s="118"/>
       <c r="E67" s="118"/>
       <c r="F67" s="121"/>
-      <c r="G67" s="163"/>
-      <c r="H67" s="164"/>
-      <c r="I67" s="134" t="s">
+      <c r="G67" s="162"/>
+      <c r="H67" s="163"/>
+      <c r="I67" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="J67" s="134">
+      <c r="J67" s="133">
         <f t="shared" si="0"/>
         <v>-41795</v>
       </c>
-      <c r="K67" s="138">
+      <c r="K67" s="137">
         <f t="shared" si="1"/>
         <v>0.45828000000000002</v>
       </c>
-      <c r="L67" s="137">
+      <c r="L67" s="136">
         <f t="shared" si="2"/>
         <v>-19153.812600000001</v>
       </c>
@@ -18520,20 +18548,20 @@
       <c r="D68" s="118"/>
       <c r="E68" s="118"/>
       <c r="F68" s="118"/>
-      <c r="G68" s="163"/>
-      <c r="H68" s="164"/>
-      <c r="I68" s="134" t="s">
+      <c r="G68" s="162"/>
+      <c r="H68" s="163"/>
+      <c r="I68" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="J68" s="134">
+      <c r="J68" s="133">
         <f t="shared" si="0"/>
         <v>151419</v>
       </c>
-      <c r="K68" s="138">
+      <c r="K68" s="137">
         <f t="shared" si="1"/>
         <v>0.46058106021</v>
       </c>
-      <c r="L68" s="137">
+      <c r="L68" s="136">
         <f t="shared" si="2"/>
         <v>69740.723555937991</v>
       </c>
@@ -18557,20 +18585,20 @@
       <c r="D69" s="118"/>
       <c r="E69" s="118"/>
       <c r="F69" s="118"/>
-      <c r="G69" s="163"/>
-      <c r="H69" s="164"/>
-      <c r="I69" s="134" t="s">
+      <c r="G69" s="162"/>
+      <c r="H69" s="163"/>
+      <c r="I69" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="J69" s="134">
+      <c r="J69" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K69" s="138">
+      <c r="K69" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L69" s="137">
+      <c r="L69" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -18588,26 +18616,26 @@
       <c r="AF69" s="3"/>
     </row>
     <row r="70" spans="1:32" ht="16">
-      <c r="A70" s="159"/>
-      <c r="B70" s="159"/>
-      <c r="C70" s="159"/>
-      <c r="D70" s="159"/>
-      <c r="E70" s="159"/>
-      <c r="F70" s="159"/>
-      <c r="G70" s="163"/>
-      <c r="H70" s="164"/>
-      <c r="I70" s="134" t="s">
+      <c r="A70" s="158"/>
+      <c r="B70" s="158"/>
+      <c r="C70" s="158"/>
+      <c r="D70" s="158"/>
+      <c r="E70" s="158"/>
+      <c r="F70" s="158"/>
+      <c r="G70" s="162"/>
+      <c r="H70" s="163"/>
+      <c r="I70" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="J70" s="134">
+      <c r="J70" s="133">
         <f t="shared" si="0"/>
         <v>47016</v>
       </c>
-      <c r="K70" s="138">
+      <c r="K70" s="137">
         <f t="shared" si="1"/>
         <v>0.34271999999999997</v>
       </c>
-      <c r="L70" s="137">
+      <c r="L70" s="136">
         <f t="shared" si="2"/>
         <v>16113.323519999998</v>
       </c>
@@ -18625,26 +18653,26 @@
       <c r="AF70" s="3"/>
     </row>
     <row r="71" spans="1:32" ht="16">
-      <c r="A71" s="159"/>
-      <c r="B71" s="159"/>
-      <c r="C71" s="159"/>
-      <c r="D71" s="159"/>
-      <c r="E71" s="159"/>
-      <c r="F71" s="159"/>
-      <c r="G71" s="162"/>
-      <c r="H71" s="164"/>
-      <c r="I71" s="134" t="s">
+      <c r="A71" s="158"/>
+      <c r="B71" s="158"/>
+      <c r="C71" s="158"/>
+      <c r="D71" s="158"/>
+      <c r="E71" s="158"/>
+      <c r="F71" s="158"/>
+      <c r="G71" s="161"/>
+      <c r="H71" s="163"/>
+      <c r="I71" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="J71" s="134">
+      <c r="J71" s="133">
         <f t="shared" si="0"/>
         <v>10446.465614000001</v>
       </c>
-      <c r="K71" s="138">
+      <c r="K71" s="137">
         <f t="shared" si="1"/>
         <v>0.18479999999999999</v>
       </c>
-      <c r="L71" s="137">
+      <c r="L71" s="136">
         <f t="shared" si="2"/>
         <v>1930.5068454672</v>
       </c>
@@ -18662,26 +18690,26 @@
       <c r="AF71" s="3"/>
     </row>
     <row r="72" spans="1:32" ht="16">
-      <c r="A72" s="159"/>
-      <c r="B72" s="159"/>
-      <c r="C72" s="159"/>
-      <c r="D72" s="159"/>
-      <c r="E72" s="159"/>
-      <c r="F72" s="159"/>
-      <c r="G72" s="163"/>
-      <c r="H72" s="164"/>
-      <c r="I72" s="134" t="s">
+      <c r="A72" s="158"/>
+      <c r="B72" s="158"/>
+      <c r="C72" s="158"/>
+      <c r="D72" s="158"/>
+      <c r="E72" s="158"/>
+      <c r="F72" s="158"/>
+      <c r="G72" s="162"/>
+      <c r="H72" s="163"/>
+      <c r="I72" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="J72" s="134">
+      <c r="J72" s="133">
         <f t="shared" si="0"/>
         <v>56684</v>
       </c>
-      <c r="K72" s="138">
+      <c r="K72" s="137">
         <f t="shared" si="1"/>
         <v>0.52903037013999998</v>
       </c>
-      <c r="L72" s="137">
+      <c r="L72" s="136">
         <f t="shared" si="2"/>
         <v>29987.557501015759</v>
       </c>
@@ -18699,26 +18727,26 @@
       <c r="AF72" s="3"/>
     </row>
     <row r="73" spans="1:32" ht="16">
-      <c r="A73" s="159"/>
-      <c r="B73" s="159"/>
-      <c r="C73" s="159"/>
-      <c r="D73" s="159"/>
-      <c r="E73" s="159"/>
-      <c r="F73" s="159"/>
-      <c r="G73" s="163"/>
-      <c r="H73" s="164"/>
-      <c r="I73" s="134" t="s">
+      <c r="A73" s="158"/>
+      <c r="B73" s="158"/>
+      <c r="C73" s="158"/>
+      <c r="D73" s="158"/>
+      <c r="E73" s="158"/>
+      <c r="F73" s="158"/>
+      <c r="G73" s="162"/>
+      <c r="H73" s="163"/>
+      <c r="I73" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="J73" s="134">
+      <c r="J73" s="133">
         <f t="shared" si="0"/>
         <v>37272.534385999999</v>
       </c>
-      <c r="K73" s="138">
+      <c r="K73" s="137">
         <f t="shared" si="1"/>
         <v>0.58244860585000002</v>
       </c>
-      <c r="L73" s="137">
+      <c r="L73" s="136">
         <f t="shared" si="2"/>
         <v>21709.335689621887</v>
       </c>
@@ -18736,26 +18764,26 @@
       <c r="AF73" s="3"/>
     </row>
     <row r="74" spans="1:32" ht="16">
-      <c r="A74" s="159"/>
-      <c r="B74" s="159"/>
-      <c r="C74" s="159"/>
-      <c r="D74" s="159"/>
-      <c r="E74" s="159"/>
-      <c r="F74" s="159"/>
-      <c r="G74" s="163"/>
-      <c r="H74" s="164"/>
-      <c r="I74" s="134" t="s">
+      <c r="A74" s="158"/>
+      <c r="B74" s="158"/>
+      <c r="C74" s="158"/>
+      <c r="D74" s="158"/>
+      <c r="E74" s="158"/>
+      <c r="F74" s="158"/>
+      <c r="G74" s="162"/>
+      <c r="H74" s="163"/>
+      <c r="I74" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="J74" s="134">
+      <c r="J74" s="133">
         <f t="shared" si="0"/>
         <v>28383</v>
       </c>
-      <c r="K74" s="138">
+      <c r="K74" s="137">
         <f t="shared" si="1"/>
         <v>0.50750420987</v>
       </c>
-      <c r="L74" s="137">
+      <c r="L74" s="136">
         <f t="shared" si="2"/>
         <v>14404.49198874021</v>
       </c>
@@ -18773,26 +18801,26 @@
       <c r="AF74" s="3"/>
     </row>
     <row r="75" spans="1:32" ht="16">
-      <c r="A75" s="162"/>
-      <c r="B75" s="162"/>
-      <c r="C75" s="160"/>
-      <c r="D75" s="159"/>
-      <c r="E75" s="159"/>
-      <c r="F75" s="165"/>
-      <c r="G75" s="163"/>
-      <c r="H75" s="164"/>
-      <c r="I75" s="134" t="s">
+      <c r="A75" s="161"/>
+      <c r="B75" s="161"/>
+      <c r="C75" s="159"/>
+      <c r="D75" s="158"/>
+      <c r="E75" s="158"/>
+      <c r="F75" s="164"/>
+      <c r="G75" s="162"/>
+      <c r="H75" s="163"/>
+      <c r="I75" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="J75" s="134">
+      <c r="J75" s="133">
         <f t="shared" si="0"/>
         <v>791</v>
       </c>
-      <c r="K75" s="138">
+      <c r="K75" s="137">
         <f t="shared" si="1"/>
         <v>0.58868299696000004</v>
       </c>
-      <c r="L75" s="137">
+      <c r="L75" s="136">
         <f t="shared" si="2"/>
         <v>465.64825059536003</v>
       </c>
@@ -18810,30 +18838,30 @@
       <c r="AF75" s="3"/>
     </row>
     <row r="76" spans="1:32" ht="16">
-      <c r="A76" s="159"/>
-      <c r="B76" s="159"/>
-      <c r="C76" s="159"/>
-      <c r="D76" s="159"/>
-      <c r="E76" s="159"/>
-      <c r="F76" s="159"/>
-      <c r="G76" s="163"/>
-      <c r="H76" s="164"/>
-      <c r="I76" s="134" t="s">
+      <c r="A76" s="158"/>
+      <c r="B76" s="158"/>
+      <c r="C76" s="158"/>
+      <c r="D76" s="158"/>
+      <c r="E76" s="158"/>
+      <c r="F76" s="158"/>
+      <c r="G76" s="162"/>
+      <c r="H76" s="163"/>
+      <c r="I76" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="J76" s="134">
+      <c r="J76" s="133">
         <f t="shared" si="0"/>
         <v>104882</v>
       </c>
-      <c r="K76" s="138">
+      <c r="K76" s="137">
         <f t="shared" si="1"/>
         <v>0.54249821000999998</v>
       </c>
-      <c r="L76" s="137">
+      <c r="L76" s="136">
         <f t="shared" si="2"/>
         <v>56898.297262268818</v>
       </c>
-      <c r="M76" s="123"/>
+      <c r="M76" s="122"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
       <c r="P76" s="1"/>
@@ -18847,26 +18875,26 @@
       <c r="AF76" s="3"/>
     </row>
     <row r="77" spans="1:32" ht="16">
-      <c r="A77" s="159"/>
-      <c r="B77" s="159"/>
-      <c r="C77" s="159"/>
-      <c r="D77" s="159"/>
-      <c r="E77" s="159"/>
-      <c r="F77" s="159"/>
-      <c r="G77" s="163"/>
-      <c r="H77" s="164"/>
-      <c r="I77" s="134" t="s">
+      <c r="A77" s="158"/>
+      <c r="B77" s="158"/>
+      <c r="C77" s="158"/>
+      <c r="D77" s="158"/>
+      <c r="E77" s="158"/>
+      <c r="F77" s="158"/>
+      <c r="G77" s="162"/>
+      <c r="H77" s="163"/>
+      <c r="I77" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="J77" s="134">
+      <c r="J77" s="133">
         <f t="shared" si="0"/>
         <v>37746.534385999999</v>
       </c>
-      <c r="K77" s="138">
+      <c r="K77" s="137">
         <f t="shared" si="1"/>
         <v>8.5890000000000008E-2</v>
       </c>
-      <c r="L77" s="137">
+      <c r="L77" s="136">
         <f t="shared" si="2"/>
         <v>3242.0498384135403</v>
       </c>
@@ -18884,26 +18912,26 @@
       <c r="AF77" s="3"/>
     </row>
     <row r="78" spans="1:32" ht="16">
-      <c r="A78" s="159"/>
-      <c r="B78" s="159"/>
-      <c r="C78" s="159"/>
-      <c r="D78" s="159"/>
-      <c r="E78" s="159"/>
-      <c r="F78" s="159"/>
-      <c r="G78" s="162"/>
-      <c r="H78" s="164"/>
-      <c r="I78" s="134" t="s">
+      <c r="A78" s="158"/>
+      <c r="B78" s="158"/>
+      <c r="C78" s="158"/>
+      <c r="D78" s="158"/>
+      <c r="E78" s="158"/>
+      <c r="F78" s="158"/>
+      <c r="G78" s="161"/>
+      <c r="H78" s="163"/>
+      <c r="I78" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="J78" s="134">
+      <c r="J78" s="133">
         <f t="shared" si="0"/>
         <v>132791</v>
       </c>
-      <c r="K78" s="138">
+      <c r="K78" s="137">
         <f t="shared" si="1"/>
         <v>0.67602529614999995</v>
       </c>
-      <c r="L78" s="137">
+      <c r="L78" s="136">
         <f t="shared" si="2"/>
         <v>89770.075101054637</v>
       </c>
@@ -18921,26 +18949,26 @@
       <c r="AF78" s="3"/>
     </row>
     <row r="79" spans="1:32" ht="16">
-      <c r="A79" s="162"/>
-      <c r="B79" s="162"/>
-      <c r="C79" s="160"/>
-      <c r="D79" s="159"/>
-      <c r="E79" s="159"/>
-      <c r="F79" s="165"/>
-      <c r="G79" s="163"/>
-      <c r="H79" s="164"/>
-      <c r="I79" s="134" t="s">
+      <c r="A79" s="161"/>
+      <c r="B79" s="161"/>
+      <c r="C79" s="159"/>
+      <c r="D79" s="158"/>
+      <c r="E79" s="158"/>
+      <c r="F79" s="164"/>
+      <c r="G79" s="162"/>
+      <c r="H79" s="163"/>
+      <c r="I79" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="J79" s="134">
+      <c r="J79" s="133">
         <f t="shared" si="0"/>
         <v>3316</v>
       </c>
-      <c r="K79" s="138">
+      <c r="K79" s="137">
         <f t="shared" si="1"/>
         <v>0.94223152791000009</v>
       </c>
-      <c r="L79" s="137">
+      <c r="L79" s="136">
         <f t="shared" si="2"/>
         <v>3124.4397465495604</v>
       </c>
@@ -18956,26 +18984,26 @@
       <c r="AF79" s="3"/>
     </row>
     <row r="80" spans="1:32" ht="16">
-      <c r="A80" s="159"/>
-      <c r="B80" s="159"/>
-      <c r="C80" s="159"/>
-      <c r="D80" s="159"/>
-      <c r="E80" s="159"/>
-      <c r="F80" s="159"/>
-      <c r="G80" s="162"/>
-      <c r="H80" s="164"/>
-      <c r="I80" s="134" t="s">
+      <c r="A80" s="158"/>
+      <c r="B80" s="158"/>
+      <c r="C80" s="158"/>
+      <c r="D80" s="158"/>
+      <c r="E80" s="158"/>
+      <c r="F80" s="158"/>
+      <c r="G80" s="161"/>
+      <c r="H80" s="163"/>
+      <c r="I80" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="J80" s="134">
+      <c r="J80" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K80" s="138">
+      <c r="K80" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L80" s="137">
+      <c r="L80" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -18988,26 +19016,26 @@
       <c r="S80" s="96"/>
     </row>
     <row r="81" spans="1:19" ht="16">
-      <c r="A81" s="162"/>
-      <c r="B81" s="162"/>
-      <c r="C81" s="160"/>
-      <c r="D81" s="159"/>
-      <c r="E81" s="159"/>
-      <c r="F81" s="165"/>
-      <c r="G81" s="163"/>
-      <c r="H81" s="164"/>
-      <c r="I81" s="134" t="s">
+      <c r="A81" s="161"/>
+      <c r="B81" s="161"/>
+      <c r="C81" s="159"/>
+      <c r="D81" s="158"/>
+      <c r="E81" s="158"/>
+      <c r="F81" s="164"/>
+      <c r="G81" s="162"/>
+      <c r="H81" s="163"/>
+      <c r="I81" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="J81" s="134">
+      <c r="J81" s="133">
         <f t="shared" si="0"/>
         <v>129475</v>
       </c>
-      <c r="K81" s="138">
+      <c r="K81" s="137">
         <f t="shared" si="1"/>
         <v>0.66920745592000008</v>
       </c>
-      <c r="L81" s="137">
+      <c r="L81" s="136">
         <f t="shared" si="2"/>
         <v>86645.635355242004</v>
       </c>
@@ -19020,26 +19048,26 @@
       <c r="S81" s="96"/>
     </row>
     <row r="82" spans="1:19" ht="16">
-      <c r="A82" s="159"/>
-      <c r="B82" s="159"/>
-      <c r="C82" s="159"/>
-      <c r="D82" s="159"/>
-      <c r="E82" s="159"/>
-      <c r="F82" s="159"/>
-      <c r="G82" s="163"/>
-      <c r="H82" s="164"/>
-      <c r="I82" s="134" t="s">
+      <c r="A82" s="158"/>
+      <c r="B82" s="158"/>
+      <c r="C82" s="158"/>
+      <c r="D82" s="158"/>
+      <c r="E82" s="158"/>
+      <c r="F82" s="158"/>
+      <c r="G82" s="162"/>
+      <c r="H82" s="163"/>
+      <c r="I82" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="J82" s="134">
+      <c r="J82" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K82" s="138">
+      <c r="K82" s="137">
         <f t="shared" si="1"/>
         <v>0.66590000000000005</v>
       </c>
-      <c r="L82" s="137">
+      <c r="L82" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19052,26 +19080,26 @@
       <c r="S82" s="96"/>
     </row>
     <row r="83" spans="1:19" ht="16">
-      <c r="A83" s="159"/>
-      <c r="B83" s="159"/>
-      <c r="C83" s="159"/>
-      <c r="D83" s="159"/>
-      <c r="E83" s="159"/>
-      <c r="F83" s="159"/>
-      <c r="G83" s="163"/>
-      <c r="H83" s="164"/>
-      <c r="I83" s="134" t="s">
+      <c r="A83" s="158"/>
+      <c r="B83" s="158"/>
+      <c r="C83" s="158"/>
+      <c r="D83" s="158"/>
+      <c r="E83" s="158"/>
+      <c r="F83" s="158"/>
+      <c r="G83" s="162"/>
+      <c r="H83" s="163"/>
+      <c r="I83" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="J83" s="134">
+      <c r="J83" s="133">
         <f t="shared" si="0"/>
         <v>129475</v>
       </c>
-      <c r="K83" s="138">
+      <c r="K83" s="137">
         <f t="shared" si="1"/>
         <v>0.66920745592000008</v>
       </c>
-      <c r="L83" s="137">
+      <c r="L83" s="136">
         <f t="shared" si="2"/>
         <v>86645.635355242004</v>
       </c>
@@ -19084,26 +19112,26 @@
       <c r="S83" s="96"/>
     </row>
     <row r="84" spans="1:19" ht="16">
-      <c r="A84" s="159"/>
-      <c r="B84" s="159"/>
-      <c r="C84" s="159"/>
-      <c r="D84" s="159"/>
-      <c r="E84" s="159"/>
-      <c r="F84" s="159"/>
-      <c r="G84" s="162"/>
-      <c r="H84" s="160"/>
-      <c r="I84" s="134" t="s">
+      <c r="A84" s="158"/>
+      <c r="B84" s="158"/>
+      <c r="C84" s="158"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="161"/>
+      <c r="H84" s="159"/>
+      <c r="I84" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="J84" s="134">
+      <c r="J84" s="133">
         <f t="shared" si="0"/>
         <v>25089</v>
       </c>
-      <c r="K84" s="138">
+      <c r="K84" s="137">
         <f t="shared" si="1"/>
         <v>0.69919500000000001</v>
       </c>
-      <c r="L84" s="137">
+      <c r="L84" s="136">
         <f t="shared" si="2"/>
         <v>17542.103354999999</v>
       </c>
@@ -19116,26 +19144,26 @@
       <c r="S84" s="96"/>
     </row>
     <row r="85" spans="1:19" ht="16">
-      <c r="A85" s="159"/>
-      <c r="B85" s="159"/>
-      <c r="C85" s="159"/>
-      <c r="D85" s="159"/>
-      <c r="E85" s="159"/>
-      <c r="F85" s="159"/>
-      <c r="G85" s="163"/>
-      <c r="H85" s="164"/>
-      <c r="I85" s="134" t="s">
+      <c r="A85" s="158"/>
+      <c r="B85" s="158"/>
+      <c r="C85" s="158"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="162"/>
+      <c r="H85" s="163"/>
+      <c r="I85" s="133" t="s">
         <v>37</v>
       </c>
-      <c r="J85" s="134">
+      <c r="J85" s="133">
         <f t="shared" si="0"/>
         <v>104386</v>
       </c>
-      <c r="K85" s="138">
+      <c r="K85" s="137">
         <f t="shared" si="1"/>
         <v>0.66200000000000003</v>
       </c>
-      <c r="L85" s="137">
+      <c r="L85" s="136">
         <f t="shared" si="2"/>
         <v>69103.532000000007</v>
       </c>
@@ -19148,26 +19176,26 @@
       <c r="S85" s="96"/>
     </row>
     <row r="86" spans="1:19" ht="16">
-      <c r="A86" s="162"/>
-      <c r="B86" s="162"/>
-      <c r="C86" s="166"/>
-      <c r="D86" s="159"/>
-      <c r="E86" s="159"/>
-      <c r="F86" s="165"/>
-      <c r="G86" s="163"/>
-      <c r="H86" s="164"/>
-      <c r="I86" s="134" t="s">
+      <c r="A86" s="161"/>
+      <c r="B86" s="161"/>
+      <c r="C86" s="165"/>
+      <c r="D86" s="158"/>
+      <c r="E86" s="158"/>
+      <c r="F86" s="164"/>
+      <c r="G86" s="162"/>
+      <c r="H86" s="163"/>
+      <c r="I86" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="J86" s="134">
+      <c r="J86" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K86" s="138">
+      <c r="K86" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L86" s="137">
+      <c r="L86" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19180,30 +19208,30 @@
       <c r="S86" s="96"/>
     </row>
     <row r="87" spans="1:19" ht="16">
-      <c r="A87" s="159"/>
-      <c r="B87" s="159"/>
-      <c r="C87" s="159"/>
-      <c r="D87" s="159"/>
-      <c r="E87" s="159"/>
-      <c r="F87" s="165"/>
-      <c r="G87" s="163"/>
-      <c r="H87" s="164"/>
-      <c r="I87" s="134" t="s">
+      <c r="A87" s="158"/>
+      <c r="B87" s="158"/>
+      <c r="C87" s="158"/>
+      <c r="D87" s="158"/>
+      <c r="E87" s="158"/>
+      <c r="F87" s="164"/>
+      <c r="G87" s="162"/>
+      <c r="H87" s="163"/>
+      <c r="I87" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="J87" s="134">
+      <c r="J87" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K87" s="138">
+      <c r="K87" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L87" s="137">
+      <c r="L87" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M87" s="124"/>
+      <c r="M87" s="122"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
       <c r="P87" s="1"/>
@@ -19212,26 +19240,26 @@
       <c r="S87" s="96"/>
     </row>
     <row r="88" spans="1:19" ht="16">
-      <c r="A88" s="159"/>
-      <c r="B88" s="159"/>
-      <c r="C88" s="159"/>
-      <c r="D88" s="159"/>
-      <c r="E88" s="159"/>
-      <c r="F88" s="159"/>
-      <c r="G88" s="163"/>
-      <c r="H88" s="164"/>
-      <c r="I88" s="134" t="s">
+      <c r="A88" s="158"/>
+      <c r="B88" s="158"/>
+      <c r="C88" s="158"/>
+      <c r="D88" s="158"/>
+      <c r="E88" s="158"/>
+      <c r="F88" s="158"/>
+      <c r="G88" s="162"/>
+      <c r="H88" s="163"/>
+      <c r="I88" s="133" t="s">
         <v>140</v>
       </c>
-      <c r="J88" s="134">
+      <c r="J88" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K88" s="138">
+      <c r="K88" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L88" s="137">
+      <c r="L88" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19244,26 +19272,26 @@
       <c r="S88" s="96"/>
     </row>
     <row r="89" spans="1:19" ht="16">
-      <c r="A89" s="159"/>
-      <c r="B89" s="159"/>
-      <c r="C89" s="159"/>
-      <c r="D89" s="159"/>
-      <c r="E89" s="159"/>
-      <c r="F89" s="159"/>
-      <c r="G89" s="163"/>
-      <c r="H89" s="164"/>
-      <c r="I89" s="134" t="s">
+      <c r="A89" s="158"/>
+      <c r="B89" s="158"/>
+      <c r="C89" s="158"/>
+      <c r="D89" s="158"/>
+      <c r="E89" s="158"/>
+      <c r="F89" s="158"/>
+      <c r="G89" s="162"/>
+      <c r="H89" s="163"/>
+      <c r="I89" s="133" t="s">
         <v>40</v>
       </c>
-      <c r="J89" s="134">
+      <c r="J89" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K89" s="138">
+      <c r="K89" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L89" s="137">
+      <c r="L89" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19276,26 +19304,26 @@
       <c r="S89" s="96"/>
     </row>
     <row r="90" spans="1:19" ht="16">
-      <c r="A90" s="159"/>
-      <c r="B90" s="159"/>
-      <c r="C90" s="159"/>
-      <c r="D90" s="159"/>
-      <c r="E90" s="159"/>
-      <c r="F90" s="159"/>
-      <c r="G90" s="163"/>
-      <c r="H90" s="164"/>
-      <c r="I90" s="134" t="s">
+      <c r="A90" s="158"/>
+      <c r="B90" s="158"/>
+      <c r="C90" s="158"/>
+      <c r="D90" s="158"/>
+      <c r="E90" s="158"/>
+      <c r="F90" s="158"/>
+      <c r="G90" s="162"/>
+      <c r="H90" s="163"/>
+      <c r="I90" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="J90" s="134">
+      <c r="J90" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K90" s="138">
+      <c r="K90" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L90" s="137">
+      <c r="L90" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19308,26 +19336,26 @@
       <c r="S90" s="96"/>
     </row>
     <row r="91" spans="1:19" ht="19">
-      <c r="A91" s="162"/>
-      <c r="B91" s="162"/>
-      <c r="C91" s="160"/>
-      <c r="D91" s="159"/>
-      <c r="E91" s="159"/>
-      <c r="F91" s="165"/>
-      <c r="G91" s="163"/>
-      <c r="H91" s="167"/>
-      <c r="I91" s="134" t="s">
+      <c r="A91" s="161"/>
+      <c r="B91" s="161"/>
+      <c r="C91" s="159"/>
+      <c r="D91" s="158"/>
+      <c r="E91" s="158"/>
+      <c r="F91" s="164"/>
+      <c r="G91" s="162"/>
+      <c r="H91" s="166"/>
+      <c r="I91" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="J91" s="134">
+      <c r="J91" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K91" s="138">
+      <c r="K91" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L91" s="137">
+      <c r="L91" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19340,26 +19368,26 @@
       <c r="S91" s="96"/>
     </row>
     <row r="92" spans="1:19" ht="16">
-      <c r="A92" s="159"/>
-      <c r="B92" s="159"/>
-      <c r="C92" s="159"/>
-      <c r="D92" s="159"/>
-      <c r="E92" s="159"/>
-      <c r="F92" s="159"/>
-      <c r="G92" s="163"/>
-      <c r="H92" s="164"/>
-      <c r="I92" s="134" t="s">
+      <c r="A92" s="158"/>
+      <c r="B92" s="158"/>
+      <c r="C92" s="158"/>
+      <c r="D92" s="158"/>
+      <c r="E92" s="158"/>
+      <c r="F92" s="158"/>
+      <c r="G92" s="162"/>
+      <c r="H92" s="163"/>
+      <c r="I92" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="J92" s="134">
+      <c r="J92" s="133">
         <f t="shared" si="0"/>
         <v>27987</v>
       </c>
-      <c r="K92" s="138">
+      <c r="K92" s="137">
         <f t="shared" si="1"/>
         <v>0.61817728231000002</v>
       </c>
-      <c r="L92" s="137">
+      <c r="L92" s="136">
         <f t="shared" si="2"/>
         <v>17300.927600009971</v>
       </c>
@@ -19372,26 +19400,26 @@
       <c r="S92" s="96"/>
     </row>
     <row r="93" spans="1:19" ht="16">
-      <c r="A93" s="159"/>
-      <c r="B93" s="159"/>
-      <c r="C93" s="159"/>
-      <c r="D93" s="159"/>
-      <c r="E93" s="159"/>
-      <c r="F93" s="159"/>
-      <c r="G93" s="163"/>
-      <c r="H93" s="164"/>
-      <c r="I93" s="134" t="s">
+      <c r="A93" s="158"/>
+      <c r="B93" s="158"/>
+      <c r="C93" s="158"/>
+      <c r="D93" s="158"/>
+      <c r="E93" s="158"/>
+      <c r="F93" s="158"/>
+      <c r="G93" s="162"/>
+      <c r="H93" s="163"/>
+      <c r="I93" s="133" t="s">
         <v>139</v>
       </c>
-      <c r="J93" s="134">
+      <c r="J93" s="133">
         <f t="shared" si="0"/>
         <v>18351</v>
       </c>
-      <c r="K93" s="138">
+      <c r="K93" s="137">
         <f t="shared" si="1"/>
         <v>0.62170000000000003</v>
       </c>
-      <c r="L93" s="137">
+      <c r="L93" s="136">
         <f t="shared" si="2"/>
         <v>11408.816700000001</v>
       </c>
@@ -19404,26 +19432,26 @@
       <c r="S93" s="96"/>
     </row>
     <row r="94" spans="1:19" ht="16">
-      <c r="A94" s="162"/>
-      <c r="B94" s="162"/>
-      <c r="C94" s="166"/>
-      <c r="D94" s="159"/>
-      <c r="E94" s="159"/>
-      <c r="F94" s="165"/>
-      <c r="G94" s="163"/>
-      <c r="H94" s="164"/>
-      <c r="I94" s="134" t="s">
+      <c r="A94" s="161"/>
+      <c r="B94" s="161"/>
+      <c r="C94" s="165"/>
+      <c r="D94" s="158"/>
+      <c r="E94" s="158"/>
+      <c r="F94" s="164"/>
+      <c r="G94" s="162"/>
+      <c r="H94" s="163"/>
+      <c r="I94" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="J94" s="134">
+      <c r="J94" s="133">
         <f t="shared" si="0"/>
         <v>5360</v>
       </c>
-      <c r="K94" s="138">
+      <c r="K94" s="137">
         <f t="shared" si="1"/>
         <v>0.60460000000000003</v>
       </c>
-      <c r="L94" s="137">
+      <c r="L94" s="136">
         <f t="shared" si="2"/>
         <v>3240.6559999999999</v>
       </c>
@@ -19436,26 +19464,26 @@
       <c r="S94" s="96"/>
     </row>
     <row r="95" spans="1:19" ht="16">
-      <c r="A95" s="159"/>
-      <c r="B95" s="159"/>
-      <c r="C95" s="159"/>
-      <c r="D95" s="159"/>
-      <c r="E95" s="159"/>
-      <c r="F95" s="159"/>
-      <c r="G95" s="163"/>
-      <c r="H95" s="164"/>
-      <c r="I95" s="134" t="s">
+      <c r="A95" s="158"/>
+      <c r="B95" s="158"/>
+      <c r="C95" s="158"/>
+      <c r="D95" s="158"/>
+      <c r="E95" s="158"/>
+      <c r="F95" s="158"/>
+      <c r="G95" s="162"/>
+      <c r="H95" s="163"/>
+      <c r="I95" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="J95" s="134">
+      <c r="J95" s="133">
         <f t="shared" si="0"/>
         <v>6394</v>
       </c>
-      <c r="K95" s="138">
+      <c r="K95" s="137">
         <f t="shared" si="1"/>
         <v>0.59009999999999996</v>
       </c>
-      <c r="L95" s="137">
+      <c r="L95" s="136">
         <f t="shared" si="2"/>
         <v>3773.0993999999996</v>
       </c>
@@ -19468,26 +19496,26 @@
       <c r="S95" s="96"/>
     </row>
     <row r="96" spans="1:19" ht="16">
-      <c r="A96" s="159"/>
-      <c r="B96" s="159"/>
-      <c r="C96" s="159"/>
-      <c r="D96" s="159"/>
-      <c r="E96" s="159"/>
-      <c r="F96" s="159"/>
-      <c r="G96" s="163"/>
-      <c r="H96" s="164"/>
-      <c r="I96" s="134" t="s">
+      <c r="A96" s="158"/>
+      <c r="B96" s="158"/>
+      <c r="C96" s="158"/>
+      <c r="D96" s="158"/>
+      <c r="E96" s="158"/>
+      <c r="F96" s="158"/>
+      <c r="G96" s="162"/>
+      <c r="H96" s="163"/>
+      <c r="I96" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="J96" s="134">
+      <c r="J96" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K96" s="138">
+      <c r="K96" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L96" s="137">
+      <c r="L96" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19500,26 +19528,26 @@
       <c r="S96" s="96"/>
     </row>
     <row r="97" spans="1:19" ht="16">
-      <c r="A97" s="159"/>
-      <c r="B97" s="159"/>
-      <c r="C97" s="159"/>
-      <c r="D97" s="159"/>
-      <c r="E97" s="159"/>
-      <c r="F97" s="159"/>
-      <c r="G97" s="163"/>
-      <c r="H97" s="164"/>
-      <c r="I97" s="134" t="s">
+      <c r="A97" s="158"/>
+      <c r="B97" s="158"/>
+      <c r="C97" s="158"/>
+      <c r="D97" s="158"/>
+      <c r="E97" s="158"/>
+      <c r="F97" s="158"/>
+      <c r="G97" s="162"/>
+      <c r="H97" s="163"/>
+      <c r="I97" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="J97" s="134">
+      <c r="J97" s="133">
         <f t="shared" si="0"/>
         <v>6394</v>
       </c>
-      <c r="K97" s="138">
+      <c r="K97" s="137">
         <f t="shared" si="1"/>
         <v>0.59009999999999996</v>
       </c>
-      <c r="L97" s="137">
+      <c r="L97" s="136">
         <f t="shared" si="2"/>
         <v>3773.0993999999996</v>
       </c>
@@ -19532,26 +19560,26 @@
       <c r="S97" s="96"/>
     </row>
     <row r="98" spans="1:19" ht="16">
-      <c r="A98" s="159"/>
-      <c r="B98" s="159"/>
-      <c r="C98" s="159"/>
-      <c r="D98" s="159"/>
-      <c r="E98" s="159"/>
-      <c r="F98" s="159"/>
-      <c r="G98" s="163"/>
-      <c r="H98" s="164"/>
-      <c r="I98" s="134" t="s">
+      <c r="A98" s="158"/>
+      <c r="B98" s="158"/>
+      <c r="C98" s="158"/>
+      <c r="D98" s="158"/>
+      <c r="E98" s="158"/>
+      <c r="F98" s="158"/>
+      <c r="G98" s="162"/>
+      <c r="H98" s="163"/>
+      <c r="I98" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="J98" s="134">
+      <c r="J98" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K98" s="138">
+      <c r="K98" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L98" s="137">
+      <c r="L98" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19564,26 +19592,26 @@
       <c r="S98" s="96"/>
     </row>
     <row r="99" spans="1:19" ht="16">
-      <c r="A99" s="162"/>
-      <c r="B99" s="162"/>
-      <c r="C99" s="160"/>
-      <c r="D99" s="159"/>
-      <c r="E99" s="159"/>
-      <c r="F99" s="165"/>
-      <c r="G99" s="163"/>
-      <c r="H99" s="164"/>
-      <c r="I99" s="134" t="s">
+      <c r="A99" s="161"/>
+      <c r="B99" s="161"/>
+      <c r="C99" s="159"/>
+      <c r="D99" s="158"/>
+      <c r="E99" s="158"/>
+      <c r="F99" s="164"/>
+      <c r="G99" s="162"/>
+      <c r="H99" s="163"/>
+      <c r="I99" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="J99" s="134">
+      <c r="J99" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K99" s="138">
+      <c r="K99" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L99" s="137">
+      <c r="L99" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19596,26 +19624,26 @@
       <c r="S99" s="96"/>
     </row>
     <row r="100" spans="1:19" ht="16">
-      <c r="A100" s="159"/>
-      <c r="B100" s="159"/>
-      <c r="C100" s="159"/>
-      <c r="D100" s="159"/>
-      <c r="E100" s="159"/>
-      <c r="F100" s="159"/>
-      <c r="G100" s="163"/>
-      <c r="H100" s="164"/>
-      <c r="I100" s="134" t="s">
+      <c r="A100" s="158"/>
+      <c r="B100" s="158"/>
+      <c r="C100" s="158"/>
+      <c r="D100" s="158"/>
+      <c r="E100" s="158"/>
+      <c r="F100" s="158"/>
+      <c r="G100" s="162"/>
+      <c r="H100" s="163"/>
+      <c r="I100" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="J100" s="134">
+      <c r="J100" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K100" s="138">
+      <c r="K100" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L100" s="137">
+      <c r="L100" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19628,26 +19656,26 @@
       <c r="S100" s="96"/>
     </row>
     <row r="101" spans="1:19" ht="16">
-      <c r="A101" s="159"/>
-      <c r="B101" s="159"/>
-      <c r="C101" s="159"/>
-      <c r="D101" s="159"/>
-      <c r="E101" s="159"/>
-      <c r="F101" s="159"/>
-      <c r="G101" s="163"/>
-      <c r="H101" s="164"/>
-      <c r="I101" s="134" t="s">
+      <c r="A101" s="158"/>
+      <c r="B101" s="158"/>
+      <c r="C101" s="158"/>
+      <c r="D101" s="158"/>
+      <c r="E101" s="158"/>
+      <c r="F101" s="158"/>
+      <c r="G101" s="162"/>
+      <c r="H101" s="163"/>
+      <c r="I101" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="J101" s="134">
+      <c r="J101" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K101" s="138">
+      <c r="K101" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L101" s="137">
+      <c r="L101" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19660,26 +19688,26 @@
       <c r="S101" s="96"/>
     </row>
     <row r="102" spans="1:19" ht="16">
-      <c r="A102" s="162"/>
-      <c r="B102" s="162"/>
-      <c r="C102" s="160"/>
-      <c r="D102" s="159"/>
-      <c r="E102" s="159"/>
-      <c r="F102" s="165"/>
-      <c r="G102" s="163"/>
-      <c r="H102" s="164"/>
-      <c r="I102" s="134" t="s">
+      <c r="A102" s="161"/>
+      <c r="B102" s="161"/>
+      <c r="C102" s="159"/>
+      <c r="D102" s="158"/>
+      <c r="E102" s="158"/>
+      <c r="F102" s="164"/>
+      <c r="G102" s="162"/>
+      <c r="H102" s="163"/>
+      <c r="I102" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="J102" s="134">
+      <c r="J102" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K102" s="138">
+      <c r="K102" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L102" s="137">
+      <c r="L102" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19692,26 +19720,26 @@
       <c r="S102" s="96"/>
     </row>
     <row r="103" spans="1:19" ht="16">
-      <c r="A103" s="159"/>
-      <c r="B103" s="159"/>
-      <c r="C103" s="159"/>
-      <c r="D103" s="159"/>
-      <c r="E103" s="159"/>
-      <c r="F103" s="159"/>
-      <c r="G103" s="163"/>
-      <c r="H103" s="164"/>
-      <c r="I103" s="134" t="s">
+      <c r="A103" s="158"/>
+      <c r="B103" s="158"/>
+      <c r="C103" s="158"/>
+      <c r="D103" s="158"/>
+      <c r="E103" s="158"/>
+      <c r="F103" s="158"/>
+      <c r="G103" s="162"/>
+      <c r="H103" s="163"/>
+      <c r="I103" s="133" t="s">
         <v>54</v>
       </c>
-      <c r="J103" s="134">
+      <c r="J103" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K103" s="138">
+      <c r="K103" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L103" s="137">
+      <c r="L103" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19724,26 +19752,26 @@
       <c r="S103" s="96"/>
     </row>
     <row r="104" spans="1:19" ht="16">
-      <c r="A104" s="162"/>
-      <c r="B104" s="162"/>
-      <c r="C104" s="160"/>
-      <c r="D104" s="159"/>
-      <c r="E104" s="159"/>
-      <c r="F104" s="165"/>
-      <c r="G104" s="163"/>
-      <c r="H104" s="164"/>
-      <c r="I104" s="134" t="s">
+      <c r="A104" s="161"/>
+      <c r="B104" s="161"/>
+      <c r="C104" s="159"/>
+      <c r="D104" s="158"/>
+      <c r="E104" s="158"/>
+      <c r="F104" s="164"/>
+      <c r="G104" s="162"/>
+      <c r="H104" s="163"/>
+      <c r="I104" s="133" t="s">
         <v>55</v>
       </c>
-      <c r="J104" s="134">
+      <c r="J104" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K104" s="138">
+      <c r="K104" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L104" s="137">
+      <c r="L104" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19756,26 +19784,26 @@
       <c r="S104" s="96"/>
     </row>
     <row r="105" spans="1:19" ht="16">
-      <c r="A105" s="159"/>
-      <c r="B105" s="159"/>
-      <c r="C105" s="159"/>
-      <c r="D105" s="159"/>
-      <c r="E105" s="159"/>
-      <c r="F105" s="159"/>
-      <c r="G105" s="163"/>
-      <c r="H105" s="164"/>
-      <c r="I105" s="134" t="s">
+      <c r="A105" s="158"/>
+      <c r="B105" s="158"/>
+      <c r="C105" s="158"/>
+      <c r="D105" s="158"/>
+      <c r="E105" s="158"/>
+      <c r="F105" s="158"/>
+      <c r="G105" s="162"/>
+      <c r="H105" s="163"/>
+      <c r="I105" s="133" t="s">
         <v>56</v>
       </c>
-      <c r="J105" s="134">
+      <c r="J105" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K105" s="138">
+      <c r="K105" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L105" s="137">
+      <c r="L105" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19788,26 +19816,26 @@
       <c r="S105" s="96"/>
     </row>
     <row r="106" spans="1:19" ht="16">
-      <c r="A106" s="162"/>
-      <c r="B106" s="162"/>
-      <c r="C106" s="160"/>
-      <c r="D106" s="159"/>
-      <c r="E106" s="159"/>
-      <c r="F106" s="159"/>
-      <c r="G106" s="163"/>
-      <c r="H106" s="164"/>
-      <c r="I106" s="134" t="s">
+      <c r="A106" s="161"/>
+      <c r="B106" s="161"/>
+      <c r="C106" s="159"/>
+      <c r="D106" s="158"/>
+      <c r="E106" s="158"/>
+      <c r="F106" s="158"/>
+      <c r="G106" s="162"/>
+      <c r="H106" s="163"/>
+      <c r="I106" s="133" t="s">
         <v>57</v>
       </c>
-      <c r="J106" s="134">
+      <c r="J106" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K106" s="138">
+      <c r="K106" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L106" s="137">
+      <c r="L106" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19820,26 +19848,26 @@
       <c r="S106" s="96"/>
     </row>
     <row r="107" spans="1:19" ht="16">
-      <c r="A107" s="162"/>
-      <c r="B107" s="162"/>
-      <c r="C107" s="160"/>
-      <c r="D107" s="159"/>
-      <c r="E107" s="159"/>
-      <c r="F107" s="159"/>
-      <c r="G107" s="163"/>
-      <c r="H107" s="164"/>
-      <c r="I107" s="134" t="s">
+      <c r="A107" s="161"/>
+      <c r="B107" s="161"/>
+      <c r="C107" s="159"/>
+      <c r="D107" s="158"/>
+      <c r="E107" s="158"/>
+      <c r="F107" s="158"/>
+      <c r="G107" s="162"/>
+      <c r="H107" s="163"/>
+      <c r="I107" s="133" t="s">
         <v>58</v>
       </c>
-      <c r="J107" s="134">
+      <c r="J107" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K107" s="138">
+      <c r="K107" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L107" s="137">
+      <c r="L107" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19852,26 +19880,26 @@
       <c r="S107" s="96"/>
     </row>
     <row r="108" spans="1:19" ht="16">
-      <c r="A108" s="159"/>
-      <c r="B108" s="159"/>
-      <c r="C108" s="159"/>
-      <c r="D108" s="159"/>
-      <c r="E108" s="159"/>
-      <c r="F108" s="159"/>
-      <c r="G108" s="163"/>
-      <c r="H108" s="164"/>
-      <c r="I108" s="134" t="s">
+      <c r="A108" s="158"/>
+      <c r="B108" s="158"/>
+      <c r="C108" s="158"/>
+      <c r="D108" s="158"/>
+      <c r="E108" s="158"/>
+      <c r="F108" s="158"/>
+      <c r="G108" s="162"/>
+      <c r="H108" s="163"/>
+      <c r="I108" s="133" t="s">
         <v>59</v>
       </c>
-      <c r="J108" s="134">
+      <c r="J108" s="133">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K108" s="138">
+      <c r="K108" s="137">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L108" s="137">
+      <c r="L108" s="136">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -19884,27 +19912,27 @@
       <c r="S108" s="96"/>
     </row>
     <row r="109" spans="1:19" ht="16">
-      <c r="A109" s="159"/>
-      <c r="B109" s="159"/>
-      <c r="C109" s="159"/>
-      <c r="D109" s="159"/>
-      <c r="E109" s="159"/>
-      <c r="F109" s="159"/>
-      <c r="G109" s="163"/>
-      <c r="H109" s="164"/>
-      <c r="I109" s="134" t="s">
+      <c r="A109" s="158"/>
+      <c r="B109" s="158"/>
+      <c r="C109" s="158"/>
+      <c r="D109" s="158"/>
+      <c r="E109" s="158"/>
+      <c r="F109" s="158"/>
+      <c r="G109" s="162"/>
+      <c r="H109" s="163"/>
+      <c r="I109" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="J109" s="134">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="138">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L109" s="137">
-        <f t="shared" si="2"/>
+      <c r="J109" s="133">
+        <f t="shared" ref="J63:J111" si="3">B48</f>
+        <v>0</v>
+      </c>
+      <c r="K109" s="137">
+        <f t="shared" ref="K63:K116" si="4">IF(D48&gt;1,D48/100,D48)</f>
+        <v>0</v>
+      </c>
+      <c r="L109" s="136">
+        <f t="shared" ref="L63:L116" si="5">+J109*K109</f>
         <v>0</v>
       </c>
       <c r="M109" s="122"/>
@@ -19916,27 +19944,27 @@
       <c r="S109" s="96"/>
     </row>
     <row r="110" spans="1:19" ht="16">
-      <c r="A110" s="162"/>
-      <c r="B110" s="162"/>
-      <c r="C110" s="160"/>
-      <c r="D110" s="159"/>
-      <c r="E110" s="159"/>
-      <c r="F110" s="165"/>
-      <c r="G110" s="163"/>
-      <c r="H110" s="164"/>
-      <c r="I110" s="134" t="s">
+      <c r="A110" s="161"/>
+      <c r="B110" s="161"/>
+      <c r="C110" s="159"/>
+      <c r="D110" s="158"/>
+      <c r="E110" s="158"/>
+      <c r="F110" s="164"/>
+      <c r="G110" s="162"/>
+      <c r="H110" s="163"/>
+      <c r="I110" s="133" t="s">
         <v>61</v>
       </c>
-      <c r="J110" s="134">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K110" s="138">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L110" s="137">
-        <f t="shared" si="2"/>
+      <c r="J110" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K110" s="137">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="136">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M110" s="122"/>
@@ -19948,27 +19976,27 @@
       <c r="S110" s="96"/>
     </row>
     <row r="111" spans="1:19" ht="16">
-      <c r="A111" s="159"/>
-      <c r="B111" s="159"/>
-      <c r="C111" s="159"/>
-      <c r="D111" s="159"/>
-      <c r="E111" s="159"/>
-      <c r="F111" s="159"/>
-      <c r="G111" s="163"/>
-      <c r="H111" s="164"/>
-      <c r="I111" s="134" t="s">
+      <c r="A111" s="158"/>
+      <c r="B111" s="158"/>
+      <c r="C111" s="158"/>
+      <c r="D111" s="158"/>
+      <c r="E111" s="158"/>
+      <c r="F111" s="158"/>
+      <c r="G111" s="162"/>
+      <c r="H111" s="163"/>
+      <c r="I111" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="J111" s="134">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K111" s="138">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L111" s="137">
-        <f t="shared" si="2"/>
+      <c r="J111" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K111" s="137">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L111" s="136">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M111" s="122"/>
@@ -19980,27 +20008,27 @@
       <c r="S111" s="96"/>
     </row>
     <row r="112" spans="1:19" ht="16">
-      <c r="A112" s="159"/>
-      <c r="B112" s="159"/>
-      <c r="C112" s="159"/>
-      <c r="D112" s="159"/>
-      <c r="E112" s="159"/>
-      <c r="F112" s="159"/>
-      <c r="G112" s="163"/>
-      <c r="H112" s="164"/>
-      <c r="I112" s="134" t="s">
+      <c r="A112" s="158"/>
+      <c r="B112" s="158"/>
+      <c r="C112" s="158"/>
+      <c r="D112" s="158"/>
+      <c r="E112" s="158"/>
+      <c r="F112" s="158"/>
+      <c r="G112" s="162"/>
+      <c r="H112" s="163"/>
+      <c r="I112" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="J112" s="134">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K112" s="138">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L112" s="137">
-        <f t="shared" si="2"/>
+      <c r="J112" s="133">
+        <f t="shared" ref="J63:J116" si="6">B51</f>
+        <v>0</v>
+      </c>
+      <c r="K112" s="137">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L112" s="136">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M112" s="122"/>
@@ -20012,27 +20040,27 @@
       <c r="S112" s="96"/>
     </row>
     <row r="113" spans="1:19" ht="16">
-      <c r="A113" s="162"/>
-      <c r="B113" s="162"/>
-      <c r="C113" s="160"/>
-      <c r="D113" s="159"/>
-      <c r="E113" s="159"/>
-      <c r="F113" s="165"/>
-      <c r="G113" s="163"/>
-      <c r="H113" s="164"/>
-      <c r="I113" s="134" t="s">
+      <c r="A113" s="161"/>
+      <c r="B113" s="161"/>
+      <c r="C113" s="159"/>
+      <c r="D113" s="158"/>
+      <c r="E113" s="158"/>
+      <c r="F113" s="164"/>
+      <c r="G113" s="162"/>
+      <c r="H113" s="163"/>
+      <c r="I113" s="133" t="s">
         <v>64</v>
       </c>
-      <c r="J113" s="134">
-        <f t="shared" si="0"/>
+      <c r="J113" s="133">
+        <f t="shared" si="6"/>
         <v>77372</v>
       </c>
-      <c r="K113" s="138">
-        <f t="shared" si="1"/>
+      <c r="K113" s="137">
+        <f t="shared" si="4"/>
         <v>0.54</v>
       </c>
-      <c r="L113" s="137">
-        <f t="shared" si="2"/>
+      <c r="L113" s="136">
+        <f t="shared" si="5"/>
         <v>41780.880000000005</v>
       </c>
       <c r="M113" s="122"/>
@@ -20044,27 +20072,27 @@
       <c r="S113" s="96"/>
     </row>
     <row r="114" spans="1:19" ht="16">
-      <c r="A114" s="159"/>
-      <c r="B114" s="159"/>
-      <c r="C114" s="159"/>
-      <c r="D114" s="159"/>
-      <c r="E114" s="159"/>
-      <c r="F114" s="159"/>
-      <c r="G114" s="163"/>
-      <c r="H114" s="164"/>
-      <c r="I114" s="134" t="s">
+      <c r="A114" s="158"/>
+      <c r="B114" s="158"/>
+      <c r="C114" s="158"/>
+      <c r="D114" s="158"/>
+      <c r="E114" s="158"/>
+      <c r="F114" s="158"/>
+      <c r="G114" s="162"/>
+      <c r="H114" s="163"/>
+      <c r="I114" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="J114" s="134">
-        <f t="shared" si="0"/>
+      <c r="J114" s="133">
+        <f t="shared" si="6"/>
         <v>77372</v>
       </c>
-      <c r="K114" s="138">
-        <f t="shared" si="1"/>
+      <c r="K114" s="137">
+        <f t="shared" si="4"/>
         <v>0.54</v>
       </c>
-      <c r="L114" s="137">
-        <f t="shared" si="2"/>
+      <c r="L114" s="136">
+        <f t="shared" si="5"/>
         <v>41780.880000000005</v>
       </c>
       <c r="M114" s="122"/>
@@ -20076,27 +20104,27 @@
       <c r="S114" s="96"/>
     </row>
     <row r="115" spans="1:19" ht="16">
-      <c r="A115" s="159"/>
-      <c r="B115" s="159"/>
-      <c r="C115" s="159"/>
-      <c r="D115" s="159"/>
-      <c r="E115" s="159"/>
-      <c r="F115" s="159"/>
-      <c r="G115" s="163"/>
-      <c r="H115" s="164"/>
-      <c r="I115" s="134" t="s">
+      <c r="A115" s="158"/>
+      <c r="B115" s="158"/>
+      <c r="C115" s="158"/>
+      <c r="D115" s="158"/>
+      <c r="E115" s="158"/>
+      <c r="F115" s="158"/>
+      <c r="G115" s="162"/>
+      <c r="H115" s="163"/>
+      <c r="I115" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="J115" s="134">
-        <f t="shared" si="0"/>
+      <c r="J115" s="133">
+        <f t="shared" si="6"/>
         <v>4403</v>
       </c>
-      <c r="K115" s="138">
-        <f t="shared" si="1"/>
+      <c r="K115" s="137">
+        <f t="shared" si="4"/>
         <v>0.62139999999999995</v>
       </c>
-      <c r="L115" s="137">
-        <f t="shared" si="2"/>
+      <c r="L115" s="136">
+        <f t="shared" si="5"/>
         <v>2736.0241999999998</v>
       </c>
       <c r="M115" s="122"/>
@@ -20108,27 +20136,27 @@
       <c r="S115" s="96"/>
     </row>
     <row r="116" spans="1:19" ht="16">
-      <c r="A116" s="159"/>
-      <c r="B116" s="159"/>
-      <c r="C116" s="159"/>
-      <c r="D116" s="159"/>
-      <c r="E116" s="159"/>
-      <c r="F116" s="159"/>
-      <c r="G116" s="162"/>
-      <c r="H116" s="160"/>
-      <c r="I116" s="134" t="s">
+      <c r="A116" s="158"/>
+      <c r="B116" s="158"/>
+      <c r="C116" s="158"/>
+      <c r="D116" s="158"/>
+      <c r="E116" s="158"/>
+      <c r="F116" s="158"/>
+      <c r="G116" s="161"/>
+      <c r="H116" s="159"/>
+      <c r="I116" s="133" t="s">
         <v>67</v>
       </c>
-      <c r="J116" s="134">
-        <f t="shared" si="0"/>
+      <c r="J116" s="133">
+        <f t="shared" si="6"/>
         <v>127</v>
       </c>
-      <c r="K116" s="138">
-        <f t="shared" si="1"/>
+      <c r="K116" s="137">
+        <f t="shared" si="4"/>
         <v>0.66590000000000005</v>
       </c>
-      <c r="L116" s="137">
-        <f t="shared" si="2"/>
+      <c r="L116" s="136">
+        <f t="shared" si="5"/>
         <v>84.569300000000013</v>
       </c>
       <c r="M116" s="122"/>
@@ -20140,448 +20168,448 @@
       <c r="S116" s="96"/>
     </row>
     <row r="117" spans="1:19">
-      <c r="A117" s="159"/>
-      <c r="B117" s="159"/>
-      <c r="C117" s="159"/>
-      <c r="D117" s="159"/>
-      <c r="E117" s="159"/>
-      <c r="F117" s="159"/>
-      <c r="G117" s="159"/>
-      <c r="H117" s="159"/>
-      <c r="I117" s="134"/>
-      <c r="J117" s="134"/>
-      <c r="K117" s="134"/>
-      <c r="L117" s="134"/>
+      <c r="A117" s="158"/>
+      <c r="B117" s="158"/>
+      <c r="C117" s="158"/>
+      <c r="D117" s="158"/>
+      <c r="E117" s="158"/>
+      <c r="F117" s="158"/>
+      <c r="G117" s="158"/>
+      <c r="H117" s="158"/>
+      <c r="I117" s="133"/>
+      <c r="J117" s="133"/>
+      <c r="K117" s="133"/>
+      <c r="L117" s="133"/>
       <c r="M117" s="122"/>
     </row>
     <row r="118" spans="1:19">
-      <c r="A118" s="159"/>
-      <c r="B118" s="159"/>
-      <c r="C118" s="159"/>
-      <c r="D118" s="159"/>
-      <c r="E118" s="159"/>
-      <c r="F118" s="159"/>
-      <c r="G118" s="205"/>
-      <c r="H118" s="206"/>
-      <c r="I118" s="134"/>
-      <c r="J118" s="139"/>
-      <c r="K118" s="139"/>
-      <c r="L118" s="134"/>
+      <c r="A118" s="158"/>
+      <c r="B118" s="158"/>
+      <c r="C118" s="158"/>
+      <c r="D118" s="158"/>
+      <c r="E118" s="158"/>
+      <c r="F118" s="158"/>
+      <c r="G118" s="200"/>
+      <c r="H118" s="201"/>
+      <c r="I118" s="133"/>
+      <c r="J118" s="138"/>
+      <c r="K118" s="138"/>
+      <c r="L118" s="133"/>
       <c r="M118" s="122"/>
     </row>
     <row r="119" spans="1:19">
-      <c r="A119" s="159"/>
-      <c r="B119" s="159"/>
-      <c r="C119" s="159"/>
-      <c r="D119" s="159"/>
-      <c r="E119" s="159"/>
-      <c r="F119" s="159"/>
-      <c r="G119" s="161"/>
-      <c r="H119" s="161"/>
-      <c r="I119" s="134"/>
-      <c r="J119" s="139"/>
-      <c r="K119" s="139"/>
-      <c r="L119" s="134"/>
+      <c r="A119" s="158"/>
+      <c r="B119" s="158"/>
+      <c r="C119" s="158"/>
+      <c r="D119" s="158"/>
+      <c r="E119" s="158"/>
+      <c r="F119" s="158"/>
+      <c r="G119" s="160"/>
+      <c r="H119" s="160"/>
+      <c r="I119" s="133"/>
+      <c r="J119" s="138"/>
+      <c r="K119" s="138"/>
+      <c r="L119" s="133"/>
     </row>
     <row r="120" spans="1:19">
-      <c r="A120" s="159"/>
-      <c r="B120" s="159"/>
-      <c r="C120" s="159"/>
-      <c r="D120" s="159"/>
-      <c r="E120" s="159"/>
-      <c r="F120" s="159"/>
-      <c r="G120" s="159"/>
-      <c r="H120" s="159"/>
-      <c r="I120" s="134"/>
-      <c r="J120" s="137"/>
-      <c r="K120" s="138"/>
-      <c r="L120" s="134"/>
+      <c r="A120" s="158"/>
+      <c r="B120" s="158"/>
+      <c r="C120" s="158"/>
+      <c r="D120" s="158"/>
+      <c r="E120" s="158"/>
+      <c r="F120" s="158"/>
+      <c r="G120" s="158"/>
+      <c r="H120" s="158"/>
+      <c r="I120" s="133"/>
+      <c r="J120" s="136"/>
+      <c r="K120" s="137"/>
+      <c r="L120" s="133"/>
     </row>
     <row r="121" spans="1:19">
-      <c r="A121" s="159"/>
-      <c r="B121" s="159"/>
-      <c r="C121" s="159"/>
-      <c r="D121" s="159"/>
-      <c r="E121" s="159"/>
-      <c r="F121" s="159"/>
-      <c r="G121" s="159"/>
-      <c r="H121" s="159"/>
-      <c r="I121" s="134"/>
-      <c r="J121" s="137"/>
-      <c r="K121" s="138"/>
-      <c r="L121" s="134"/>
+      <c r="A121" s="158"/>
+      <c r="B121" s="158"/>
+      <c r="C121" s="158"/>
+      <c r="D121" s="158"/>
+      <c r="E121" s="158"/>
+      <c r="F121" s="158"/>
+      <c r="G121" s="158"/>
+      <c r="H121" s="158"/>
+      <c r="I121" s="133"/>
+      <c r="J121" s="136"/>
+      <c r="K121" s="137"/>
+      <c r="L121" s="133"/>
     </row>
     <row r="122" spans="1:19">
-      <c r="A122" s="159"/>
-      <c r="B122" s="159"/>
-      <c r="C122" s="159"/>
-      <c r="D122" s="159"/>
-      <c r="E122" s="159"/>
-      <c r="F122" s="159"/>
-      <c r="G122" s="159"/>
-      <c r="H122" s="159"/>
-      <c r="I122" s="134"/>
-      <c r="J122" s="137"/>
-      <c r="K122" s="138"/>
-      <c r="L122" s="134"/>
+      <c r="A122" s="158"/>
+      <c r="B122" s="158"/>
+      <c r="C122" s="158"/>
+      <c r="D122" s="158"/>
+      <c r="E122" s="158"/>
+      <c r="F122" s="158"/>
+      <c r="G122" s="158"/>
+      <c r="H122" s="158"/>
+      <c r="I122" s="133"/>
+      <c r="J122" s="136"/>
+      <c r="K122" s="137"/>
+      <c r="L122" s="133"/>
     </row>
     <row r="123" spans="1:19">
-      <c r="A123" s="159"/>
-      <c r="B123" s="159"/>
-      <c r="C123" s="159"/>
-      <c r="D123" s="159"/>
-      <c r="E123" s="159"/>
-      <c r="F123" s="159"/>
+      <c r="A123" s="158"/>
+      <c r="B123" s="158"/>
+      <c r="C123" s="158"/>
+      <c r="D123" s="158"/>
+      <c r="E123" s="158"/>
+      <c r="F123" s="158"/>
       <c r="J123" s="2"/>
       <c r="K123" s="1"/>
     </row>
     <row r="124" spans="1:19">
-      <c r="A124" s="159"/>
-      <c r="B124" s="159"/>
-      <c r="C124" s="159"/>
-      <c r="D124" s="159"/>
-      <c r="E124" s="159"/>
-      <c r="F124" s="159"/>
+      <c r="A124" s="158"/>
+      <c r="B124" s="158"/>
+      <c r="C124" s="158"/>
+      <c r="D124" s="158"/>
+      <c r="E124" s="158"/>
+      <c r="F124" s="158"/>
       <c r="J124" s="2"/>
       <c r="K124" s="1"/>
     </row>
     <row r="125" spans="1:19">
-      <c r="A125" s="159"/>
-      <c r="B125" s="159"/>
-      <c r="C125" s="159"/>
-      <c r="D125" s="159"/>
-      <c r="E125" s="159"/>
-      <c r="F125" s="159"/>
+      <c r="A125" s="158"/>
+      <c r="B125" s="158"/>
+      <c r="C125" s="158"/>
+      <c r="D125" s="158"/>
+      <c r="E125" s="158"/>
+      <c r="F125" s="158"/>
       <c r="J125" s="2"/>
       <c r="K125" s="1"/>
     </row>
     <row r="126" spans="1:19">
-      <c r="A126" s="159"/>
-      <c r="B126" s="159"/>
-      <c r="C126" s="159"/>
-      <c r="D126" s="159"/>
-      <c r="E126" s="159"/>
-      <c r="F126" s="159"/>
+      <c r="A126" s="158"/>
+      <c r="B126" s="158"/>
+      <c r="C126" s="158"/>
+      <c r="D126" s="158"/>
+      <c r="E126" s="158"/>
+      <c r="F126" s="158"/>
       <c r="J126" s="2"/>
       <c r="K126" s="1"/>
     </row>
     <row r="127" spans="1:19">
-      <c r="A127" s="159"/>
-      <c r="B127" s="159"/>
-      <c r="C127" s="159"/>
-      <c r="D127" s="159"/>
-      <c r="E127" s="159"/>
-      <c r="F127" s="159"/>
+      <c r="A127" s="158"/>
+      <c r="B127" s="158"/>
+      <c r="C127" s="158"/>
+      <c r="D127" s="158"/>
+      <c r="E127" s="158"/>
+      <c r="F127" s="158"/>
       <c r="J127" s="2"/>
       <c r="K127" s="1"/>
     </row>
     <row r="128" spans="1:19">
-      <c r="A128" s="159"/>
-      <c r="B128" s="159"/>
-      <c r="C128" s="159"/>
-      <c r="D128" s="159"/>
-      <c r="E128" s="159"/>
-      <c r="F128" s="159"/>
+      <c r="A128" s="158"/>
+      <c r="B128" s="158"/>
+      <c r="C128" s="158"/>
+      <c r="D128" s="158"/>
+      <c r="E128" s="158"/>
+      <c r="F128" s="158"/>
       <c r="J128" s="2"/>
       <c r="K128" s="1"/>
     </row>
     <row r="129" spans="1:11">
-      <c r="A129" s="159"/>
-      <c r="B129" s="159"/>
-      <c r="C129" s="159"/>
-      <c r="D129" s="159"/>
-      <c r="E129" s="159"/>
-      <c r="F129" s="159"/>
+      <c r="A129" s="158"/>
+      <c r="B129" s="158"/>
+      <c r="C129" s="158"/>
+      <c r="D129" s="158"/>
+      <c r="E129" s="158"/>
+      <c r="F129" s="158"/>
       <c r="J129" s="2"/>
       <c r="K129" s="1"/>
     </row>
     <row r="130" spans="1:11">
-      <c r="A130" s="159"/>
-      <c r="B130" s="159"/>
-      <c r="C130" s="159"/>
-      <c r="D130" s="159"/>
-      <c r="E130" s="159"/>
-      <c r="F130" s="159"/>
+      <c r="A130" s="158"/>
+      <c r="B130" s="158"/>
+      <c r="C130" s="158"/>
+      <c r="D130" s="158"/>
+      <c r="E130" s="158"/>
+      <c r="F130" s="158"/>
       <c r="J130" s="2"/>
       <c r="K130" s="1"/>
     </row>
     <row r="131" spans="1:11">
-      <c r="A131" s="159"/>
-      <c r="B131" s="159"/>
-      <c r="C131" s="159"/>
-      <c r="D131" s="159"/>
-      <c r="E131" s="159"/>
-      <c r="F131" s="159"/>
+      <c r="A131" s="158"/>
+      <c r="B131" s="158"/>
+      <c r="C131" s="158"/>
+      <c r="D131" s="158"/>
+      <c r="E131" s="158"/>
+      <c r="F131" s="158"/>
       <c r="J131" s="2"/>
       <c r="K131" s="1"/>
     </row>
     <row r="132" spans="1:11">
-      <c r="A132" s="159"/>
-      <c r="B132" s="159"/>
-      <c r="C132" s="159"/>
-      <c r="D132" s="159"/>
-      <c r="E132" s="159"/>
-      <c r="F132" s="159"/>
+      <c r="A132" s="158"/>
+      <c r="B132" s="158"/>
+      <c r="C132" s="158"/>
+      <c r="D132" s="158"/>
+      <c r="E132" s="158"/>
+      <c r="F132" s="158"/>
       <c r="J132" s="2"/>
       <c r="K132" s="1"/>
     </row>
     <row r="133" spans="1:11">
-      <c r="A133" s="159"/>
-      <c r="B133" s="159"/>
-      <c r="C133" s="159"/>
-      <c r="D133" s="159"/>
-      <c r="E133" s="159"/>
-      <c r="F133" s="159"/>
+      <c r="A133" s="158"/>
+      <c r="B133" s="158"/>
+      <c r="C133" s="158"/>
+      <c r="D133" s="158"/>
+      <c r="E133" s="158"/>
+      <c r="F133" s="158"/>
       <c r="J133" s="2"/>
       <c r="K133" s="1"/>
     </row>
     <row r="134" spans="1:11">
-      <c r="A134" s="159"/>
-      <c r="B134" s="159"/>
-      <c r="C134" s="159"/>
-      <c r="D134" s="159"/>
-      <c r="E134" s="159"/>
-      <c r="F134" s="159"/>
+      <c r="A134" s="158"/>
+      <c r="B134" s="158"/>
+      <c r="C134" s="158"/>
+      <c r="D134" s="158"/>
+      <c r="E134" s="158"/>
+      <c r="F134" s="158"/>
       <c r="J134" s="2"/>
       <c r="K134" s="1"/>
     </row>
     <row r="135" spans="1:11">
-      <c r="A135" s="159"/>
-      <c r="B135" s="159"/>
-      <c r="C135" s="159"/>
-      <c r="D135" s="159"/>
-      <c r="E135" s="159"/>
-      <c r="F135" s="159"/>
+      <c r="A135" s="158"/>
+      <c r="B135" s="158"/>
+      <c r="C135" s="158"/>
+      <c r="D135" s="158"/>
+      <c r="E135" s="158"/>
+      <c r="F135" s="158"/>
       <c r="J135" s="2"/>
       <c r="K135" s="1"/>
     </row>
     <row r="136" spans="1:11">
-      <c r="A136" s="159"/>
-      <c r="B136" s="159"/>
-      <c r="C136" s="159"/>
-      <c r="D136" s="159"/>
-      <c r="E136" s="159"/>
-      <c r="F136" s="159"/>
+      <c r="A136" s="158"/>
+      <c r="B136" s="158"/>
+      <c r="C136" s="158"/>
+      <c r="D136" s="158"/>
+      <c r="E136" s="158"/>
+      <c r="F136" s="158"/>
       <c r="J136" s="2"/>
       <c r="K136" s="1"/>
     </row>
     <row r="137" spans="1:11">
-      <c r="A137" s="159"/>
-      <c r="B137" s="159"/>
-      <c r="C137" s="159"/>
-      <c r="D137" s="159"/>
-      <c r="E137" s="159"/>
-      <c r="F137" s="159"/>
+      <c r="A137" s="158"/>
+      <c r="B137" s="158"/>
+      <c r="C137" s="158"/>
+      <c r="D137" s="158"/>
+      <c r="E137" s="158"/>
+      <c r="F137" s="158"/>
       <c r="J137" s="2"/>
       <c r="K137" s="1"/>
     </row>
     <row r="138" spans="1:11">
-      <c r="A138" s="159"/>
-      <c r="B138" s="159"/>
-      <c r="C138" s="159"/>
-      <c r="D138" s="159"/>
-      <c r="E138" s="159"/>
-      <c r="F138" s="159"/>
+      <c r="A138" s="158"/>
+      <c r="B138" s="158"/>
+      <c r="C138" s="158"/>
+      <c r="D138" s="158"/>
+      <c r="E138" s="158"/>
+      <c r="F138" s="158"/>
       <c r="J138" s="2"/>
       <c r="K138" s="1"/>
     </row>
     <row r="139" spans="1:11">
-      <c r="A139" s="159"/>
-      <c r="B139" s="159"/>
-      <c r="C139" s="159"/>
-      <c r="D139" s="159"/>
-      <c r="E139" s="159"/>
-      <c r="F139" s="159"/>
+      <c r="A139" s="158"/>
+      <c r="B139" s="158"/>
+      <c r="C139" s="158"/>
+      <c r="D139" s="158"/>
+      <c r="E139" s="158"/>
+      <c r="F139" s="158"/>
       <c r="J139" s="2"/>
       <c r="K139" s="1"/>
     </row>
     <row r="140" spans="1:11">
-      <c r="A140" s="159"/>
-      <c r="B140" s="159"/>
-      <c r="C140" s="159"/>
-      <c r="D140" s="159"/>
-      <c r="E140" s="159"/>
-      <c r="F140" s="159"/>
+      <c r="A140" s="158"/>
+      <c r="B140" s="158"/>
+      <c r="C140" s="158"/>
+      <c r="D140" s="158"/>
+      <c r="E140" s="158"/>
+      <c r="F140" s="158"/>
       <c r="J140" s="2"/>
       <c r="K140" s="1"/>
     </row>
     <row r="141" spans="1:11">
-      <c r="A141" s="159"/>
-      <c r="B141" s="159"/>
-      <c r="C141" s="159"/>
-      <c r="D141" s="159"/>
-      <c r="E141" s="159"/>
-      <c r="F141" s="159"/>
+      <c r="A141" s="158"/>
+      <c r="B141" s="158"/>
+      <c r="C141" s="158"/>
+      <c r="D141" s="158"/>
+      <c r="E141" s="158"/>
+      <c r="F141" s="158"/>
       <c r="J141" s="2"/>
       <c r="K141" s="1"/>
     </row>
     <row r="142" spans="1:11">
-      <c r="A142" s="159"/>
-      <c r="B142" s="159"/>
-      <c r="C142" s="159"/>
-      <c r="D142" s="159"/>
-      <c r="E142" s="159"/>
-      <c r="F142" s="159"/>
+      <c r="A142" s="158"/>
+      <c r="B142" s="158"/>
+      <c r="C142" s="158"/>
+      <c r="D142" s="158"/>
+      <c r="E142" s="158"/>
+      <c r="F142" s="158"/>
       <c r="J142" s="2"/>
       <c r="K142" s="1"/>
     </row>
     <row r="143" spans="1:11">
-      <c r="A143" s="159"/>
-      <c r="B143" s="159"/>
-      <c r="C143" s="159"/>
-      <c r="D143" s="159"/>
-      <c r="E143" s="159"/>
-      <c r="F143" s="159"/>
+      <c r="A143" s="158"/>
+      <c r="B143" s="158"/>
+      <c r="C143" s="158"/>
+      <c r="D143" s="158"/>
+      <c r="E143" s="158"/>
+      <c r="F143" s="158"/>
       <c r="J143" s="2"/>
       <c r="K143" s="1"/>
     </row>
     <row r="144" spans="1:11">
-      <c r="A144" s="159"/>
-      <c r="B144" s="159"/>
-      <c r="C144" s="159"/>
-      <c r="D144" s="159"/>
-      <c r="E144" s="159"/>
-      <c r="F144" s="159"/>
+      <c r="A144" s="158"/>
+      <c r="B144" s="158"/>
+      <c r="C144" s="158"/>
+      <c r="D144" s="158"/>
+      <c r="E144" s="158"/>
+      <c r="F144" s="158"/>
       <c r="J144" s="2"/>
       <c r="K144" s="1"/>
     </row>
     <row r="145" spans="1:11">
-      <c r="A145" s="159"/>
-      <c r="B145" s="159"/>
-      <c r="C145" s="159"/>
-      <c r="D145" s="159"/>
-      <c r="E145" s="159"/>
-      <c r="F145" s="159"/>
+      <c r="A145" s="158"/>
+      <c r="B145" s="158"/>
+      <c r="C145" s="158"/>
+      <c r="D145" s="158"/>
+      <c r="E145" s="158"/>
+      <c r="F145" s="158"/>
       <c r="J145" s="2"/>
       <c r="K145" s="1"/>
     </row>
     <row r="146" spans="1:11">
-      <c r="A146" s="159"/>
-      <c r="B146" s="159"/>
-      <c r="C146" s="159"/>
-      <c r="D146" s="159"/>
-      <c r="E146" s="159"/>
-      <c r="F146" s="159"/>
+      <c r="A146" s="158"/>
+      <c r="B146" s="158"/>
+      <c r="C146" s="158"/>
+      <c r="D146" s="158"/>
+      <c r="E146" s="158"/>
+      <c r="F146" s="158"/>
       <c r="J146" s="2"/>
       <c r="K146" s="1"/>
     </row>
     <row r="147" spans="1:11">
-      <c r="A147" s="159"/>
-      <c r="B147" s="159"/>
-      <c r="C147" s="159"/>
-      <c r="D147" s="159"/>
-      <c r="E147" s="159"/>
-      <c r="F147" s="159"/>
+      <c r="A147" s="158"/>
+      <c r="B147" s="158"/>
+      <c r="C147" s="158"/>
+      <c r="D147" s="158"/>
+      <c r="E147" s="158"/>
+      <c r="F147" s="158"/>
       <c r="J147" s="2"/>
       <c r="K147" s="1"/>
     </row>
     <row r="148" spans="1:11">
-      <c r="A148" s="159"/>
-      <c r="B148" s="159"/>
-      <c r="C148" s="159"/>
-      <c r="D148" s="159"/>
-      <c r="E148" s="159"/>
-      <c r="F148" s="159"/>
+      <c r="A148" s="158"/>
+      <c r="B148" s="158"/>
+      <c r="C148" s="158"/>
+      <c r="D148" s="158"/>
+      <c r="E148" s="158"/>
+      <c r="F148" s="158"/>
       <c r="J148" s="2"/>
       <c r="K148" s="1"/>
     </row>
     <row r="149" spans="1:11">
-      <c r="A149" s="159"/>
-      <c r="B149" s="159"/>
-      <c r="C149" s="159"/>
-      <c r="D149" s="159"/>
-      <c r="E149" s="159"/>
-      <c r="F149" s="159"/>
+      <c r="A149" s="158"/>
+      <c r="B149" s="158"/>
+      <c r="C149" s="158"/>
+      <c r="D149" s="158"/>
+      <c r="E149" s="158"/>
+      <c r="F149" s="158"/>
       <c r="J149" s="2"/>
       <c r="K149" s="1"/>
     </row>
     <row r="150" spans="1:11">
-      <c r="A150" s="159"/>
-      <c r="B150" s="159"/>
-      <c r="C150" s="159"/>
-      <c r="D150" s="159"/>
-      <c r="E150" s="159"/>
-      <c r="F150" s="159"/>
+      <c r="A150" s="158"/>
+      <c r="B150" s="158"/>
+      <c r="C150" s="158"/>
+      <c r="D150" s="158"/>
+      <c r="E150" s="158"/>
+      <c r="F150" s="158"/>
       <c r="J150" s="2"/>
       <c r="K150" s="1"/>
     </row>
     <row r="151" spans="1:11">
-      <c r="A151" s="159"/>
-      <c r="B151" s="159"/>
-      <c r="C151" s="159"/>
-      <c r="D151" s="159"/>
-      <c r="E151" s="159"/>
-      <c r="F151" s="159"/>
+      <c r="A151" s="158"/>
+      <c r="B151" s="158"/>
+      <c r="C151" s="158"/>
+      <c r="D151" s="158"/>
+      <c r="E151" s="158"/>
+      <c r="F151" s="158"/>
       <c r="J151" s="2"/>
       <c r="K151" s="1"/>
     </row>
     <row r="152" spans="1:11">
-      <c r="A152" s="159"/>
-      <c r="B152" s="159"/>
-      <c r="C152" s="159"/>
-      <c r="D152" s="159"/>
-      <c r="E152" s="159"/>
-      <c r="F152" s="159"/>
+      <c r="A152" s="158"/>
+      <c r="B152" s="158"/>
+      <c r="C152" s="158"/>
+      <c r="D152" s="158"/>
+      <c r="E152" s="158"/>
+      <c r="F152" s="158"/>
       <c r="J152" s="2"/>
       <c r="K152" s="1"/>
     </row>
     <row r="153" spans="1:11">
-      <c r="A153" s="159"/>
-      <c r="B153" s="159"/>
-      <c r="C153" s="159"/>
-      <c r="D153" s="159"/>
-      <c r="E153" s="159"/>
-      <c r="F153" s="159"/>
+      <c r="A153" s="158"/>
+      <c r="B153" s="158"/>
+      <c r="C153" s="158"/>
+      <c r="D153" s="158"/>
+      <c r="E153" s="158"/>
+      <c r="F153" s="158"/>
       <c r="J153" s="2"/>
       <c r="K153" s="1"/>
     </row>
     <row r="154" spans="1:11">
-      <c r="A154" s="159"/>
-      <c r="B154" s="159"/>
-      <c r="C154" s="159"/>
-      <c r="D154" s="159"/>
-      <c r="E154" s="159"/>
-      <c r="F154" s="159"/>
+      <c r="A154" s="158"/>
+      <c r="B154" s="158"/>
+      <c r="C154" s="158"/>
+      <c r="D154" s="158"/>
+      <c r="E154" s="158"/>
+      <c r="F154" s="158"/>
       <c r="J154" s="2"/>
       <c r="K154" s="1"/>
     </row>
     <row r="155" spans="1:11">
-      <c r="A155" s="159"/>
-      <c r="B155" s="159"/>
-      <c r="C155" s="159"/>
-      <c r="D155" s="159"/>
-      <c r="E155" s="159"/>
-      <c r="F155" s="159"/>
+      <c r="A155" s="158"/>
+      <c r="B155" s="158"/>
+      <c r="C155" s="158"/>
+      <c r="D155" s="158"/>
+      <c r="E155" s="158"/>
+      <c r="F155" s="158"/>
       <c r="J155" s="2"/>
       <c r="K155" s="1"/>
     </row>
     <row r="156" spans="1:11">
-      <c r="A156" s="159"/>
-      <c r="B156" s="159"/>
-      <c r="C156" s="159"/>
-      <c r="D156" s="159"/>
-      <c r="E156" s="159"/>
-      <c r="F156" s="159"/>
+      <c r="A156" s="158"/>
+      <c r="B156" s="158"/>
+      <c r="C156" s="158"/>
+      <c r="D156" s="158"/>
+      <c r="E156" s="158"/>
+      <c r="F156" s="158"/>
       <c r="J156" s="2"/>
       <c r="K156" s="1"/>
     </row>
     <row r="157" spans="1:11">
-      <c r="A157" s="159"/>
-      <c r="B157" s="159"/>
-      <c r="C157" s="159"/>
-      <c r="D157" s="159"/>
-      <c r="E157" s="159"/>
-      <c r="F157" s="159"/>
+      <c r="A157" s="158"/>
+      <c r="B157" s="158"/>
+      <c r="C157" s="158"/>
+      <c r="D157" s="158"/>
+      <c r="E157" s="158"/>
+      <c r="F157" s="158"/>
       <c r="J157" s="2"/>
       <c r="K157" s="1"/>
     </row>
     <row r="158" spans="1:11">
-      <c r="A158" s="159"/>
-      <c r="B158" s="159"/>
-      <c r="C158" s="159"/>
-      <c r="D158" s="159"/>
-      <c r="E158" s="159"/>
-      <c r="F158" s="159"/>
+      <c r="A158" s="158"/>
+      <c r="B158" s="158"/>
+      <c r="C158" s="158"/>
+      <c r="D158" s="158"/>
+      <c r="E158" s="158"/>
+      <c r="F158" s="158"/>
       <c r="J158" s="2"/>
       <c r="K158" s="1"/>
     </row>
@@ -20650,12 +20678,12 @@
       <c r="K174" s="1"/>
     </row>
     <row r="176" spans="7:11">
-      <c r="G176" s="168"/>
-      <c r="H176" s="168"/>
+      <c r="G176" s="167"/>
+      <c r="H176" s="167"/>
     </row>
     <row r="177" spans="7:8">
-      <c r="G177" s="168"/>
-      <c r="H177" s="168"/>
+      <c r="G177" s="167"/>
+      <c r="H177" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -20768,539 +20796,539 @@
   <cols>
     <col min="1" max="1" width="58.6640625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="124" customWidth="1"/>
     <col min="4" max="4" width="23.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="148" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="150">
+      <c r="B1" s="149">
         <v>4991.0799999999981</v>
       </c>
-      <c r="C1" s="155">
+      <c r="C1" s="154">
         <v>0.5</v>
       </c>
-      <c r="D1" s="156">
+      <c r="D1" s="155">
         <v>0.01</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="24">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="150">
+      <c r="B2" s="149">
         <v>88872.295000000173</v>
       </c>
-      <c r="C2" s="155">
+      <c r="C2" s="154">
         <v>0.5</v>
       </c>
-      <c r="D2" s="156">
+      <c r="D2" s="155">
         <v>0.01</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24">
-      <c r="A3" s="149" t="s">
+      <c r="A3" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="150">
+      <c r="B3" s="149">
         <v>2985</v>
       </c>
-      <c r="C3" s="155">
+      <c r="C3" s="154">
         <v>0.5</v>
       </c>
-      <c r="D3" s="156">
+      <c r="D3" s="155">
         <v>8.4083959293394767E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24">
-      <c r="A4" s="149" t="s">
+      <c r="A4" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="150">
-        <v>0</v>
-      </c>
-      <c r="C4" s="155">
+      <c r="B4" s="149">
+        <v>0</v>
+      </c>
+      <c r="C4" s="154">
         <v>0.5</v>
       </c>
-      <c r="D4" s="156">
+      <c r="D4" s="155">
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="24">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="148" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="150">
+      <c r="B5" s="149">
         <v>144052.08999999997</v>
       </c>
-      <c r="C5" s="155">
+      <c r="C5" s="154">
         <v>0.5</v>
       </c>
-      <c r="D5" s="156">
+      <c r="D5" s="155">
         <v>8.6167918586789544E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24">
-      <c r="A6" s="149" t="s">
+      <c r="A6" s="148" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="150">
+      <c r="B6" s="149">
         <v>87099.612182495111</v>
       </c>
-      <c r="C6" s="155">
+      <c r="C6" s="154">
         <v>0.5</v>
       </c>
-      <c r="D6" s="156">
+      <c r="D6" s="155">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="24">
-      <c r="A7" s="149" t="s">
+      <c r="A7" s="148" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="151">
+      <c r="B7" s="150">
         <v>27059.240058898926</v>
       </c>
-      <c r="C7" s="155">
+      <c r="C7" s="154">
         <v>0.5</v>
       </c>
-      <c r="D7" s="155">
+      <c r="D7" s="154">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="24">
-      <c r="A8" s="149" t="s">
+      <c r="A8" s="148" t="s">
         <v>149</v>
       </c>
-      <c r="B8" s="151">
+      <c r="B8" s="150">
         <v>129475.38462294932</v>
       </c>
-      <c r="C8" s="155">
+      <c r="C8" s="154">
         <v>0.68412600000000001</v>
       </c>
-      <c r="D8" s="155">
+      <c r="D8" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24">
-      <c r="A9" s="149" t="s">
+      <c r="A9" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="150">
+      <c r="B9" s="149">
         <v>132791.454</v>
       </c>
-      <c r="C9" s="157">
+      <c r="C9" s="156">
         <v>0.68410599999999999</v>
       </c>
-      <c r="D9" s="155">
+      <c r="D9" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="24">
-      <c r="A10" s="149" t="s">
+      <c r="A10" s="148" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="150">
+      <c r="B10" s="149">
         <v>18351.4911288</v>
       </c>
-      <c r="C10" s="157">
+      <c r="C10" s="156">
         <v>0.62109999999999999</v>
       </c>
-      <c r="D10" s="155">
+      <c r="D10" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24">
-      <c r="A11" s="149" t="s">
+      <c r="A11" s="148" t="s">
         <v>151</v>
       </c>
-      <c r="B11" s="150">
+      <c r="B11" s="149">
         <v>5359.78701</v>
       </c>
-      <c r="C11" s="157">
+      <c r="C11" s="156">
         <v>0.61180000000000001</v>
       </c>
-      <c r="D11" s="155">
+      <c r="D11" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24">
-      <c r="A12" s="149" t="s">
+      <c r="A12" s="148" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="150">
-        <v>0</v>
-      </c>
-      <c r="C12" s="157">
+      <c r="B12" s="149">
+        <v>0</v>
+      </c>
+      <c r="C12" s="156">
         <v>0.6099</v>
       </c>
-      <c r="D12" s="155">
+      <c r="D12" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24">
-      <c r="A13" s="149" t="s">
+      <c r="A13" s="148" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="151">
+      <c r="B13" s="150">
         <v>6393.6610499999997</v>
       </c>
-      <c r="C13" s="155">
+      <c r="C13" s="154">
         <v>0.61070000000000002</v>
       </c>
-      <c r="D13" s="155">
+      <c r="D13" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24">
-      <c r="A14" s="149" t="s">
+      <c r="A14" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="B14" s="151">
-        <v>0</v>
-      </c>
-      <c r="C14" s="155">
+      <c r="B14" s="150">
+        <v>0</v>
+      </c>
+      <c r="C14" s="154">
         <v>0.56729999999999992</v>
       </c>
-      <c r="D14" s="155">
+      <c r="D14" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="24">
-      <c r="A15" s="149" t="s">
+      <c r="A15" s="148" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="151">
+      <c r="B15" s="150">
         <v>152453.07</v>
       </c>
-      <c r="C15" s="155">
+      <c r="C15" s="154">
         <v>0.36777300000000002</v>
       </c>
-      <c r="D15" s="155">
+      <c r="D15" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="24">
-      <c r="A16" s="142" t="s">
+      <c r="A16" s="141" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="152">
+      <c r="B16" s="151">
         <v>107865.3576</v>
       </c>
-      <c r="C16" s="158">
-        <v>0</v>
-      </c>
-      <c r="D16" s="155">
+      <c r="C16" s="157">
+        <v>0</v>
+      </c>
+      <c r="D16" s="154">
         <v>0.01</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="24">
-      <c r="A17" s="142" t="s">
+      <c r="A17" s="141" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="152">
-        <v>0</v>
-      </c>
-      <c r="C17" s="143">
-        <v>0</v>
-      </c>
-      <c r="D17" s="151">
+      <c r="B17" s="151">
+        <v>0</v>
+      </c>
+      <c r="C17" s="142">
+        <v>0</v>
+      </c>
+      <c r="D17" s="150">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24">
-      <c r="A18" s="144" t="s">
+      <c r="A18" s="143" t="s">
         <v>166</v>
       </c>
-      <c r="B18" s="153">
+      <c r="B18" s="152">
         <v>0.01</v>
       </c>
-      <c r="C18" s="145">
-        <v>0</v>
-      </c>
-      <c r="D18" s="146">
+      <c r="C18" s="144">
+        <v>0</v>
+      </c>
+      <c r="D18" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="24">
-      <c r="A19" s="144" t="s">
+      <c r="A19" s="143" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="153">
-        <v>0</v>
-      </c>
-      <c r="C19" s="145">
-        <v>0</v>
-      </c>
-      <c r="D19" s="146">
+      <c r="B19" s="152">
+        <v>0</v>
+      </c>
+      <c r="C19" s="144">
+        <v>0</v>
+      </c>
+      <c r="D19" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24">
-      <c r="A20" s="144" t="s">
+      <c r="A20" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="153">
+      <c r="B20" s="152">
         <v>5.5270451317286735E-3</v>
       </c>
-      <c r="C20" s="145">
-        <v>0</v>
-      </c>
-      <c r="D20" s="146">
+      <c r="C20" s="144">
+        <v>0</v>
+      </c>
+      <c r="D20" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="24">
-      <c r="A21" s="144" t="s">
+      <c r="A21" s="143" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="153">
+      <c r="B21" s="152">
         <v>2.0286666666666665E-2</v>
       </c>
-      <c r="C21" s="145">
-        <v>0</v>
-      </c>
-      <c r="D21" s="146">
+      <c r="C21" s="144">
+        <v>0</v>
+      </c>
+      <c r="D21" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24">
-      <c r="A22" s="144" t="s">
+      <c r="A22" s="143" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="153">
+      <c r="B22" s="152">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C22" s="145">
-        <v>0</v>
-      </c>
-      <c r="D22" s="146">
+      <c r="C22" s="144">
+        <v>0</v>
+      </c>
+      <c r="D22" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="24">
-      <c r="A23" s="144" t="s">
+      <c r="A23" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="153">
+      <c r="B23" s="152">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="C23" s="145">
-        <v>0</v>
-      </c>
-      <c r="D23" s="146">
+      <c r="C23" s="144">
+        <v>0</v>
+      </c>
+      <c r="D23" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="24">
-      <c r="A24" s="144" t="s">
+      <c r="A24" s="143" t="s">
         <v>168</v>
       </c>
-      <c r="B24" s="153">
-        <v>0</v>
-      </c>
-      <c r="C24" s="145">
-        <v>0</v>
-      </c>
-      <c r="D24" s="146">
+      <c r="B24" s="152">
+        <v>0</v>
+      </c>
+      <c r="C24" s="144">
+        <v>0</v>
+      </c>
+      <c r="D24" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="24">
-      <c r="A25" s="144" t="s">
+      <c r="A25" s="143" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="153">
-        <v>0</v>
-      </c>
-      <c r="C25" s="145">
-        <v>0</v>
-      </c>
-      <c r="D25" s="146">
+      <c r="B25" s="152">
+        <v>0</v>
+      </c>
+      <c r="C25" s="144">
+        <v>0</v>
+      </c>
+      <c r="D25" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="24">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="143" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="153">
-        <v>0</v>
-      </c>
-      <c r="C26" s="145">
-        <v>0</v>
-      </c>
-      <c r="D26" s="146">
+      <c r="B26" s="152">
+        <v>0</v>
+      </c>
+      <c r="C26" s="144">
+        <v>0</v>
+      </c>
+      <c r="D26" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="143" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="153">
+      <c r="B27" s="152">
         <v>8.6167918586789544E-2</v>
       </c>
-      <c r="C27" s="145">
-        <v>0</v>
-      </c>
-      <c r="D27" s="146">
+      <c r="C27" s="144">
+        <v>0</v>
+      </c>
+      <c r="D27" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="24">
-      <c r="A28" s="144" t="s">
+      <c r="A28" s="143" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="153">
+      <c r="B28" s="152">
         <v>8.199999999999999E-2</v>
       </c>
-      <c r="C28" s="145">
-        <v>0</v>
-      </c>
-      <c r="D28" s="146">
+      <c r="C28" s="144">
+        <v>0</v>
+      </c>
+      <c r="D28" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="24">
-      <c r="A29" s="144" t="s">
+      <c r="A29" s="143" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="153">
+      <c r="B29" s="152">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C29" s="145">
-        <v>0</v>
-      </c>
-      <c r="D29" s="146">
+      <c r="C29" s="144">
+        <v>0</v>
+      </c>
+      <c r="D29" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="24">
-      <c r="A30" s="144" t="s">
+      <c r="A30" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B30" s="153">
+      <c r="B30" s="152">
         <v>7.0699999999999999E-3</v>
       </c>
-      <c r="C30" s="145">
-        <v>0</v>
-      </c>
-      <c r="D30" s="146">
+      <c r="C30" s="144">
+        <v>0</v>
+      </c>
+      <c r="D30" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="143" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="153">
+      <c r="B31" s="152">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C31" s="145">
-        <v>0</v>
-      </c>
-      <c r="D31" s="146">
+      <c r="C31" s="144">
+        <v>0</v>
+      </c>
+      <c r="D31" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="24">
-      <c r="A32" s="144" t="s">
+      <c r="A32" s="143" t="s">
         <v>138</v>
       </c>
-      <c r="B32" s="173">
+      <c r="B32" s="172">
         <v>5.4000000000000003E-3</v>
       </c>
-      <c r="C32" s="145">
-        <v>0</v>
-      </c>
-      <c r="D32" s="146">
+      <c r="C32" s="144">
+        <v>0</v>
+      </c>
+      <c r="D32" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="24">
-      <c r="A33" s="147" t="s">
+      <c r="A33" s="146" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="153">
+      <c r="B33" s="152">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C33" s="148">
-        <v>0</v>
-      </c>
-      <c r="D33" s="146">
+      <c r="C33" s="147">
+        <v>0</v>
+      </c>
+      <c r="D33" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="24">
-      <c r="A34" s="147" t="s">
+      <c r="A34" s="146" t="s">
         <v>123</v>
       </c>
-      <c r="B34" s="153">
-        <v>0</v>
-      </c>
-      <c r="C34" s="148">
-        <v>0</v>
-      </c>
-      <c r="D34" s="146">
+      <c r="B34" s="152">
+        <v>0</v>
+      </c>
+      <c r="C34" s="147">
+        <v>0</v>
+      </c>
+      <c r="D34" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="24">
-      <c r="A35" s="147" t="s">
+      <c r="A35" s="146" t="s">
         <v>128</v>
       </c>
-      <c r="B35" s="153">
+      <c r="B35" s="152">
         <v>0.01</v>
       </c>
-      <c r="C35" s="148">
-        <v>0</v>
-      </c>
-      <c r="D35" s="146">
+      <c r="C35" s="147">
+        <v>0</v>
+      </c>
+      <c r="D35" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="24">
-      <c r="A36" s="147" t="s">
+      <c r="A36" s="146" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="153">
+      <c r="B36" s="152">
         <v>9.7942392473118284E-2</v>
       </c>
-      <c r="C36" s="148">
-        <v>0</v>
-      </c>
-      <c r="D36" s="146">
+      <c r="C36" s="147">
+        <v>0</v>
+      </c>
+      <c r="D36" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="24">
-      <c r="A37" s="154" t="s">
+      <c r="A37" s="153" t="s">
         <v>131</v>
       </c>
-      <c r="B37" s="146">
-        <v>0</v>
-      </c>
-      <c r="C37" s="155">
-        <v>0</v>
-      </c>
-      <c r="D37" s="146">
+      <c r="B37" s="145">
+        <v>0</v>
+      </c>
+      <c r="C37" s="154">
+        <v>0</v>
+      </c>
+      <c r="D37" s="145">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="24">
-      <c r="A38" s="154" t="s">
+      <c r="A38" s="153" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="146">
-        <v>0</v>
-      </c>
-      <c r="C38" s="155">
-        <v>0</v>
-      </c>
-      <c r="D38" s="146">
+      <c r="B38" s="145">
+        <v>0</v>
+      </c>
+      <c r="C38" s="154">
+        <v>0</v>
+      </c>
+      <c r="D38" s="145">
         <v>0</v>
       </c>
     </row>
@@ -21317,24 +21345,26 @@
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="53.5" customWidth="1"/>
     <col min="6" max="6" width="53" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
     <col min="13" max="14" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="20">
-      <c r="B2" s="207" t="s">
+      <c r="B2" s="202" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="F2" s="207" t="s">
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="F2" s="202" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="207"/>
-      <c r="J2" s="208" t="s">
+      <c r="G2" s="202"/>
+      <c r="H2" s="202"/>
+      <c r="J2" s="203" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="209"/>
+      <c r="K2" s="204"/>
       <c r="L2" s="108"/>
       <c r="M2" s="109" t="s">
         <v>145</v>
@@ -21384,14 +21414,14 @@
         <f>IF(Utilidad!C1&gt;1,Utilidad!C1/100,Utilidad!C1)</f>
         <v>0.39119999999999999</v>
       </c>
-      <c r="F4" s="202" t="s">
+      <c r="F4" s="197" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="106">
+      <c r="G4" s="294">
         <f>Utilidad!B1</f>
         <v>88507</v>
       </c>
-      <c r="H4" s="192">
+      <c r="H4" s="295">
         <f>IF(Utilidad!D1&gt;1,Utilidad!D1/100,Utilidad!D1)</f>
         <v>0.38135957855999997</v>
       </c>
@@ -21425,14 +21455,14 @@
         <f>IF(Utilidad!C2&gt;1,Utilidad!C2/100,Utilidad!C2)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="202" t="s">
+      <c r="F5" s="197" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="106">
+      <c r="G5" s="294">
         <f>Utilidad!B2</f>
         <v>0</v>
       </c>
-      <c r="H5" s="192">
+      <c r="H5" s="295">
         <f>IF(Utilidad!D2&gt;1,Utilidad!D2/100,Utilidad!D2)</f>
         <v>0</v>
       </c>
@@ -21466,14 +21496,14 @@
         <f>IF(Utilidad!C3&gt;1,Utilidad!C3/100,Utilidad!C3)</f>
         <v>0.18059999999999998</v>
       </c>
-      <c r="F6" s="202" t="s">
+      <c r="F6" s="197" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="106">
+      <c r="G6" s="294">
         <f>Utilidad!B3</f>
         <v>22063</v>
       </c>
-      <c r="H6" s="192">
+      <c r="H6" s="295">
         <f>IF(Utilidad!D3&gt;1,Utilidad!D3/100,Utilidad!D3)</f>
         <v>0.18112284201000001</v>
       </c>
@@ -21506,14 +21536,14 @@
         <f>IF(Utilidad!C4&gt;1,Utilidad!C4/100,Utilidad!C4)</f>
         <v>0.4617</v>
       </c>
-      <c r="F7" s="202" t="s">
+      <c r="F7" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="106">
+      <c r="G7" s="294">
         <f>Utilidad!B4</f>
         <v>66444</v>
       </c>
-      <c r="H7" s="192">
+      <c r="H7" s="295">
         <f>IF(Utilidad!D4&gt;1,Utilidad!D4/100,Utilidad!D4)</f>
         <v>0.447849</v>
       </c>
@@ -21546,14 +21576,14 @@
         <f>IF(Utilidad!C5&gt;1,Utilidad!C5/100,Utilidad!C5)</f>
         <v>0.4824</v>
       </c>
-      <c r="F8" s="202" t="s">
+      <c r="F8" s="197" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="106">
+      <c r="G8" s="294">
         <f>Utilidad!B5</f>
         <v>43180</v>
       </c>
-      <c r="H8" s="192">
+      <c r="H8" s="295">
         <f>IF(Utilidad!D5&gt;1,Utilidad!D5/100,Utilidad!D5)</f>
         <v>0.4824</v>
       </c>
@@ -21586,14 +21616,14 @@
         <f>IF(Utilidad!C6&gt;1,Utilidad!C6/100,Utilidad!C6)</f>
         <v>0.4824</v>
       </c>
-      <c r="F9" s="202" t="s">
+      <c r="F9" s="197" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="106">
+      <c r="G9" s="294">
         <f>Utilidad!B6</f>
         <v>-41795</v>
       </c>
-      <c r="H9" s="107">
+      <c r="H9" s="295">
         <f>IF(Utilidad!D6&gt;1,Utilidad!D6/100,Utilidad!D6)</f>
         <v>0.45828000000000002</v>
       </c>
@@ -21633,11 +21663,11 @@
       <c r="F10" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="294">
         <f>Utilidad!B7</f>
         <v>151419</v>
       </c>
-      <c r="H10" s="192">
+      <c r="H10" s="295">
         <f>IF(Utilidad!D7&gt;1,Utilidad!D7/100,Utilidad!D7)</f>
         <v>0.46058106021</v>
       </c>
@@ -21677,11 +21707,11 @@
       <c r="F11" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="106">
+      <c r="G11" s="294">
         <f>Utilidad!B8</f>
         <v>0</v>
       </c>
-      <c r="H11" s="192">
+      <c r="H11" s="295">
         <f>IF(Utilidad!D8&gt;1,Utilidad!D8/100,Utilidad!D8)</f>
         <v>0</v>
       </c>
@@ -21717,11 +21747,11 @@
       <c r="F12" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="193">
+      <c r="G12" s="294">
         <f>Utilidad!B9</f>
         <v>47016</v>
       </c>
-      <c r="H12" s="192">
+      <c r="H12" s="295">
         <f>IF(Utilidad!D9&gt;1,Utilidad!D9/100,Utilidad!D9)</f>
         <v>0.34271999999999997</v>
       </c>
@@ -21754,14 +21784,14 @@
         <f>IF(Utilidad!C10&gt;1,Utilidad!C10/100,Utilidad!C10)</f>
         <v>0.17600000000000002</v>
       </c>
-      <c r="F13" s="202" t="s">
+      <c r="F13" s="197" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="193">
+      <c r="G13" s="294">
         <f>Utilidad!B10</f>
         <v>10446.465614000001</v>
       </c>
-      <c r="H13" s="192">
+      <c r="H13" s="295">
         <f>IF(Utilidad!D10&gt;1,Utilidad!D10/100,Utilidad!D10)</f>
         <v>0.18479999999999999</v>
       </c>
@@ -21797,11 +21827,11 @@
       <c r="F14" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="193">
+      <c r="G14" s="294">
         <f>Utilidad!B11</f>
         <v>56684</v>
       </c>
-      <c r="H14" s="194">
+      <c r="H14" s="295">
         <f>IF(Utilidad!D11&gt;1,Utilidad!D11/100,Utilidad!D11)</f>
         <v>0.52903037013999998</v>
       </c>
@@ -21834,14 +21864,14 @@
         <f>IF(Utilidad!C12&gt;1,Utilidad!C12/100,Utilidad!C12)</f>
         <v>0.57600000000000007</v>
       </c>
-      <c r="F15" s="202" t="s">
+      <c r="F15" s="197" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="193">
+      <c r="G15" s="294">
         <f>Utilidad!B12</f>
         <v>37272.534385999999</v>
       </c>
-      <c r="H15" s="192">
+      <c r="H15" s="295">
         <f>IF(Utilidad!D12&gt;1,Utilidad!D12/100,Utilidad!D12)</f>
         <v>0.58244860585000002</v>
       </c>
@@ -21877,11 +21907,11 @@
       <c r="F16" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="G16" s="106">
+      <c r="G16" s="294">
         <f>Utilidad!B13</f>
         <v>28383</v>
       </c>
-      <c r="H16" s="107">
+      <c r="H16" s="295">
         <f>IF(Utilidad!D13&gt;1,Utilidad!D13/100,Utilidad!D13)</f>
         <v>0.50750420987</v>
       </c>
@@ -21917,11 +21947,11 @@
       <c r="F17" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="106">
+      <c r="G17" s="294">
         <f>Utilidad!B14</f>
         <v>791</v>
       </c>
-      <c r="H17" s="107">
+      <c r="H17" s="295">
         <f>IF(Utilidad!D14&gt;1,Utilidad!D14/100,Utilidad!D14)</f>
         <v>0.58868299696000004</v>
       </c>
@@ -21954,14 +21984,14 @@
         <f>IF(Utilidad!C15&gt;1,Utilidad!C15/100,Utilidad!C15)</f>
         <v>0.54459999999999997</v>
       </c>
-      <c r="F18" s="202" t="s">
+      <c r="F18" s="197" t="s">
         <v>27</v>
       </c>
-      <c r="G18" s="106">
+      <c r="G18" s="294">
         <f>Utilidad!B15</f>
         <v>104882</v>
       </c>
-      <c r="H18" s="192">
+      <c r="H18" s="295">
         <f>IF(Utilidad!D15&gt;1,Utilidad!D15/100,Utilidad!D15)</f>
         <v>0.54249821000999998</v>
       </c>
@@ -21994,14 +22024,14 @@
         <f>IF(Utilidad!C16&gt;1,Utilidad!C16/100,Utilidad!C16)</f>
         <v>8.1799999999999998E-2</v>
       </c>
-      <c r="F19" s="202" t="s">
+      <c r="F19" s="197" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="195">
+      <c r="G19" s="294">
         <f>Utilidad!B16</f>
         <v>37746.534385999999</v>
       </c>
-      <c r="H19" s="192">
+      <c r="H19" s="295">
         <f>IF(Utilidad!D16&gt;1,Utilidad!D16/100,Utilidad!D16)</f>
         <v>8.5890000000000008E-2</v>
       </c>
@@ -22034,14 +22064,14 @@
         <f>IF(Utilidad!C17&gt;1,Utilidad!C17/100,Utilidad!C17)</f>
         <v>0.66599999999999993</v>
       </c>
-      <c r="F20" s="202" t="s">
+      <c r="F20" s="197" t="s">
         <v>31</v>
       </c>
-      <c r="G20" s="106">
+      <c r="G20" s="294">
         <f>Utilidad!B17</f>
         <v>132791</v>
       </c>
-      <c r="H20" s="192">
+      <c r="H20" s="295">
         <f>IF(Utilidad!D17&gt;1,Utilidad!D17/100,Utilidad!D17)</f>
         <v>0.67602529614999995</v>
       </c>
@@ -22077,11 +22107,11 @@
       <c r="F21" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="106">
+      <c r="G21" s="294">
         <f>Utilidad!B18</f>
         <v>3316</v>
       </c>
-      <c r="H21" s="107">
+      <c r="H21" s="295">
         <f>IF(Utilidad!D18&gt;1,Utilidad!D18/100,Utilidad!D18)</f>
         <v>0.94223152791000009</v>
       </c>
@@ -22117,11 +22147,11 @@
       <c r="F22" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="106">
+      <c r="G22" s="294">
         <f>Utilidad!B19</f>
         <v>0</v>
       </c>
-      <c r="H22" s="107">
+      <c r="H22" s="295">
         <f>IF(Utilidad!D19&gt;1,Utilidad!D19/100,Utilidad!D19)</f>
         <v>0</v>
       </c>
@@ -22157,11 +22187,11 @@
       <c r="F23" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="G23" s="106">
+      <c r="G23" s="294">
         <f>Utilidad!B20</f>
         <v>129475</v>
       </c>
-      <c r="H23" s="107">
+      <c r="H23" s="295">
         <f>IF(Utilidad!D20&gt;1,Utilidad!D20/100,Utilidad!D20)</f>
         <v>0.66920745592000008</v>
       </c>
@@ -22197,11 +22227,11 @@
       <c r="F24" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="106">
+      <c r="G24" s="294">
         <f>Utilidad!B21</f>
         <v>0</v>
       </c>
-      <c r="H24" s="107">
+      <c r="H24" s="295">
         <f>IF(Utilidad!D21&gt;1,Utilidad!D21/100,Utilidad!D21)</f>
         <v>0.66590000000000005</v>
       </c>
@@ -22237,11 +22267,11 @@
       <c r="F25" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="106">
+      <c r="G25" s="294">
         <f>Utilidad!B22</f>
         <v>129475</v>
       </c>
-      <c r="H25" s="107">
+      <c r="H25" s="295">
         <f>IF(Utilidad!D22&gt;1,Utilidad!D22/100,Utilidad!D22)</f>
         <v>0.66920745592000008</v>
       </c>
@@ -22277,11 +22307,11 @@
       <c r="F26" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="G26" s="106">
+      <c r="G26" s="294">
         <f>Utilidad!B23</f>
         <v>25089</v>
       </c>
-      <c r="H26" s="107">
+      <c r="H26" s="295">
         <f>IF(Utilidad!D23&gt;1,Utilidad!D23/100,Utilidad!D23)</f>
         <v>0.69919500000000001</v>
       </c>
@@ -22317,11 +22347,11 @@
       <c r="F27" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="106">
+      <c r="G27" s="294">
         <f>Utilidad!B24</f>
         <v>104386</v>
       </c>
-      <c r="H27" s="107">
+      <c r="H27" s="295">
         <f>IF(Utilidad!D24&gt;1,Utilidad!D24/100,Utilidad!D24)</f>
         <v>0.66200000000000003</v>
       </c>
@@ -22357,11 +22387,11 @@
       <c r="F28" s="105" t="s">
         <v>140</v>
       </c>
-      <c r="G28" s="106">
+      <c r="G28" s="294">
         <f>Utilidad!B25</f>
         <v>0</v>
       </c>
-      <c r="H28" s="107">
+      <c r="H28" s="295">
         <f>IF(Utilidad!D25&gt;1,Utilidad!D25/100,Utilidad!D25)</f>
         <v>0</v>
       </c>
@@ -22397,11 +22427,11 @@
       <c r="F29" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="106">
+      <c r="G29" s="294">
         <f>Utilidad!B26</f>
         <v>0</v>
       </c>
-      <c r="H29" s="107">
+      <c r="H29" s="295">
         <f>IF(Utilidad!D26&gt;1,Utilidad!D26/100,Utilidad!D26)</f>
         <v>0</v>
       </c>
@@ -22437,11 +22467,11 @@
       <c r="F30" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="G30" s="106">
+      <c r="G30" s="294">
         <f>Utilidad!B27</f>
         <v>0</v>
       </c>
-      <c r="H30" s="107">
+      <c r="H30" s="295">
         <f>IF(Utilidad!D27&gt;1,Utilidad!D27/100,Utilidad!D27)</f>
         <v>0</v>
       </c>
@@ -22477,11 +22507,11 @@
       <c r="F31" s="105" t="s">
         <v>42</v>
       </c>
-      <c r="G31" s="106">
+      <c r="G31" s="294">
         <f>Utilidad!B28</f>
         <v>0</v>
       </c>
-      <c r="H31" s="107">
+      <c r="H31" s="295">
         <f>IF(Utilidad!D28&gt;1,Utilidad!D28/100,Utilidad!D28)</f>
         <v>0</v>
       </c>
@@ -22517,11 +22547,11 @@
       <c r="F32" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="G32" s="106">
+      <c r="G32" s="294">
         <f>Utilidad!B29</f>
         <v>0</v>
       </c>
-      <c r="H32" s="107">
+      <c r="H32" s="295">
         <f>IF(Utilidad!D29&gt;1,Utilidad!D29/100,Utilidad!D29)</f>
         <v>0</v>
       </c>
@@ -22557,11 +22587,11 @@
       <c r="F33" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="G33" s="106">
+      <c r="G33" s="294">
         <f>Utilidad!B30</f>
         <v>0</v>
       </c>
-      <c r="H33" s="107">
+      <c r="H33" s="295">
         <f>IF(Utilidad!D30&gt;1,Utilidad!D30/100,Utilidad!D30)</f>
         <v>0</v>
       </c>
@@ -22597,11 +22627,11 @@
       <c r="F34" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="G34" s="106">
+      <c r="G34" s="294">
         <f>Utilidad!B31</f>
         <v>27987</v>
       </c>
-      <c r="H34" s="107">
+      <c r="H34" s="295">
         <f>IF(Utilidad!D31&gt;1,Utilidad!D31/100,Utilidad!D31)</f>
         <v>0.61817728231000002</v>
       </c>
@@ -22637,11 +22667,11 @@
       <c r="F35" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="106">
+      <c r="G35" s="294">
         <f>Utilidad!B32</f>
         <v>18351</v>
       </c>
-      <c r="H35" s="107">
+      <c r="H35" s="295">
         <f>IF(Utilidad!D32&gt;1,Utilidad!D32/100,Utilidad!D32)</f>
         <v>0.62170000000000003</v>
       </c>
@@ -22677,11 +22707,11 @@
       <c r="F36" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="106">
+      <c r="G36" s="294">
         <f>Utilidad!B33</f>
         <v>5360</v>
       </c>
-      <c r="H36" s="107">
+      <c r="H36" s="295">
         <f>IF(Utilidad!D33&gt;1,Utilidad!D33/100,Utilidad!D33)</f>
         <v>0.60460000000000003</v>
       </c>
@@ -22717,11 +22747,11 @@
       <c r="F37" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="G37" s="106">
+      <c r="G37" s="294">
         <f>Utilidad!B34</f>
         <v>6394</v>
       </c>
-      <c r="H37" s="107">
+      <c r="H37" s="295">
         <f>IF(Utilidad!D34&gt;1,Utilidad!D34/100,Utilidad!D34)</f>
         <v>0.59009999999999996</v>
       </c>
@@ -22757,11 +22787,11 @@
       <c r="F38" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="G38" s="106">
+      <c r="G38" s="294">
         <f>Utilidad!B35</f>
         <v>0</v>
       </c>
-      <c r="H38" s="107">
+      <c r="H38" s="295">
         <f>IF(Utilidad!D35&gt;1,Utilidad!D35/100,Utilidad!D35)</f>
         <v>0</v>
       </c>
@@ -22797,11 +22827,11 @@
       <c r="F39" s="105" t="s">
         <v>50</v>
       </c>
-      <c r="G39" s="106">
+      <c r="G39" s="294">
         <f>Utilidad!B36</f>
         <v>6394</v>
       </c>
-      <c r="H39" s="107">
+      <c r="H39" s="295">
         <f>IF(Utilidad!D36&gt;1,Utilidad!D36/100,Utilidad!D36)</f>
         <v>0.59009999999999996</v>
       </c>
@@ -22837,11 +22867,11 @@
       <c r="F40" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="G40" s="106">
+      <c r="G40" s="294">
         <f>Utilidad!B37</f>
         <v>0</v>
       </c>
-      <c r="H40" s="107">
+      <c r="H40" s="295">
         <f>IF(Utilidad!D37&gt;1,Utilidad!D37/100,Utilidad!D37)</f>
         <v>0</v>
       </c>
@@ -22877,11 +22907,11 @@
       <c r="F41" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="106">
+      <c r="G41" s="294">
         <f>Utilidad!B38</f>
         <v>0</v>
       </c>
-      <c r="H41" s="107">
+      <c r="H41" s="295">
         <f>IF(Utilidad!D38&gt;1,Utilidad!D38/100,Utilidad!D38)</f>
         <v>0</v>
       </c>
@@ -22917,11 +22947,11 @@
       <c r="F42" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="G42" s="106">
+      <c r="G42" s="294">
         <f>Utilidad!B39</f>
         <v>0</v>
       </c>
-      <c r="H42" s="107">
+      <c r="H42" s="295">
         <f>IF(Utilidad!D39&gt;1,Utilidad!D39/100,Utilidad!D39)</f>
         <v>0</v>
       </c>
@@ -22957,11 +22987,11 @@
       <c r="F43" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="G43" s="106">
+      <c r="G43" s="294">
         <f>Utilidad!B40</f>
         <v>0</v>
       </c>
-      <c r="H43" s="107">
+      <c r="H43" s="295">
         <f>IF(Utilidad!D40&gt;1,Utilidad!D40/100,Utilidad!D40)</f>
         <v>0</v>
       </c>
@@ -22997,11 +23027,11 @@
       <c r="F44" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="G44" s="106">
+      <c r="G44" s="294">
         <f>Utilidad!B41</f>
         <v>0</v>
       </c>
-      <c r="H44" s="107">
+      <c r="H44" s="295">
         <f>IF(Utilidad!D41&gt;1,Utilidad!D41/100,Utilidad!D41)</f>
         <v>0</v>
       </c>
@@ -23037,11 +23067,11 @@
       <c r="F45" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="G45" s="106">
+      <c r="G45" s="294">
         <f>Utilidad!B42</f>
         <v>0</v>
       </c>
-      <c r="H45" s="107">
+      <c r="H45" s="295">
         <f>IF(Utilidad!D42&gt;1,Utilidad!D42/100,Utilidad!D42)</f>
         <v>0</v>
       </c>
@@ -23077,11 +23107,11 @@
       <c r="F46" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="G46" s="106">
+      <c r="G46" s="294">
         <f>Utilidad!B43</f>
         <v>0</v>
       </c>
-      <c r="H46" s="107">
+      <c r="H46" s="295">
         <f>IF(Utilidad!D43&gt;1,Utilidad!D43/100,Utilidad!D43)</f>
         <v>0</v>
       </c>
@@ -23117,11 +23147,11 @@
       <c r="F47" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="G47" s="106">
+      <c r="G47" s="294">
         <f>Utilidad!B44</f>
         <v>0</v>
       </c>
-      <c r="H47" s="107">
+      <c r="H47" s="295">
         <f>IF(Utilidad!D44&gt;1,Utilidad!D44/100,Utilidad!D44)</f>
         <v>0</v>
       </c>
@@ -23157,11 +23187,11 @@
       <c r="F48" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="G48" s="106">
+      <c r="G48" s="294">
         <f>Utilidad!B45</f>
         <v>0</v>
       </c>
-      <c r="H48" s="107">
+      <c r="H48" s="295">
         <f>IF(Utilidad!D45&gt;1,Utilidad!D45/100,Utilidad!D45)</f>
         <v>0</v>
       </c>
@@ -23197,11 +23227,11 @@
       <c r="F49" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="G49" s="106">
+      <c r="G49" s="294">
         <f>Utilidad!B46</f>
         <v>0</v>
       </c>
-      <c r="H49" s="107">
+      <c r="H49" s="295">
         <f>IF(Utilidad!D46&gt;1,Utilidad!D46/100,Utilidad!D46)</f>
         <v>0</v>
       </c>
@@ -23237,11 +23267,11 @@
       <c r="F50" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="G50" s="106">
+      <c r="G50" s="294">
         <f>Utilidad!B47</f>
         <v>0</v>
       </c>
-      <c r="H50" s="107">
+      <c r="H50" s="295">
         <f>IF(Utilidad!D47&gt;1,Utilidad!D47/100,Utilidad!D47)</f>
         <v>0</v>
       </c>
@@ -23277,11 +23307,11 @@
       <c r="F51" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="G51" s="106">
+      <c r="G51" s="294">
         <f>Utilidad!B48</f>
         <v>0</v>
       </c>
-      <c r="H51" s="107">
+      <c r="H51" s="295">
         <f>IF(Utilidad!D48&gt;1,Utilidad!D48/100,Utilidad!D48)</f>
         <v>0</v>
       </c>
@@ -23317,11 +23347,11 @@
       <c r="F52" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="G52" s="106">
+      <c r="G52" s="294">
         <f>Utilidad!B49</f>
         <v>0</v>
       </c>
-      <c r="H52" s="107">
+      <c r="H52" s="295">
         <f>IF(Utilidad!D49&gt;1,Utilidad!D49/100,Utilidad!D49)</f>
         <v>0</v>
       </c>
@@ -23357,11 +23387,11 @@
       <c r="F53" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="G53" s="106">
+      <c r="G53" s="294">
         <f>Utilidad!B50</f>
         <v>0</v>
       </c>
-      <c r="H53" s="107">
+      <c r="H53" s="295">
         <f>IF(Utilidad!D50&gt;1,Utilidad!D50/100,Utilidad!D50)</f>
         <v>0</v>
       </c>
@@ -23397,11 +23427,11 @@
       <c r="F54" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="G54" s="106">
+      <c r="G54" s="294">
         <f>Utilidad!B51</f>
         <v>0</v>
       </c>
-      <c r="H54" s="107">
+      <c r="H54" s="295">
         <f>IF(Utilidad!D51&gt;1,Utilidad!D51/100,Utilidad!D51)</f>
         <v>0</v>
       </c>
@@ -23437,11 +23467,11 @@
       <c r="F55" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="G55" s="106">
+      <c r="G55" s="294">
         <f>Utilidad!B52</f>
         <v>77372</v>
       </c>
-      <c r="H55" s="107">
+      <c r="H55" s="295">
         <f>IF(Utilidad!D52&gt;1,Utilidad!D52/100,Utilidad!D52)</f>
         <v>0.54</v>
       </c>
@@ -23477,11 +23507,11 @@
       <c r="F56" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="G56" s="106">
+      <c r="G56" s="294">
         <f>Utilidad!B53</f>
         <v>77372</v>
       </c>
-      <c r="H56" s="107">
+      <c r="H56" s="295">
         <f>IF(Utilidad!D53&gt;1,Utilidad!D53/100,Utilidad!D53)</f>
         <v>0.54</v>
       </c>
@@ -23517,11 +23547,11 @@
       <c r="F57" s="105" t="s">
         <v>159</v>
       </c>
-      <c r="G57" s="106">
+      <c r="G57" s="294">
         <f>Utilidad!B54</f>
         <v>4403</v>
       </c>
-      <c r="H57" s="107">
+      <c r="H57" s="295">
         <f>IF(Utilidad!D54&gt;1,Utilidad!D54/100,Utilidad!D54)</f>
         <v>0.62139999999999995</v>
       </c>
@@ -23557,11 +23587,11 @@
       <c r="F58" s="105" t="s">
         <v>160</v>
       </c>
-      <c r="G58" s="106">
+      <c r="G58" s="294">
         <f>Utilidad!B55</f>
         <v>127</v>
       </c>
-      <c r="H58" s="107">
+      <c r="H58" s="295">
         <f>IF(Utilidad!D55&gt;1,Utilidad!D55/100,Utilidad!D55)</f>
         <v>0.66590000000000005</v>
       </c>
@@ -23597,11 +23627,11 @@
       <c r="F59" s="105" t="s">
         <v>169</v>
       </c>
-      <c r="G59" s="106">
+      <c r="G59" s="294">
         <f>Utilidad!B56</f>
         <v>0</v>
       </c>
-      <c r="H59" s="107">
+      <c r="H59" s="295">
         <f>IF(Utilidad!D56&gt;1,Utilidad!D56/100,Utilidad!D56)</f>
         <v>0</v>
       </c>
@@ -23637,11 +23667,11 @@
       <c r="F60" s="105" t="s">
         <v>170</v>
       </c>
-      <c r="G60" s="106">
+      <c r="G60" s="294">
         <f>Utilidad!B57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="107">
+      <c r="H60" s="295">
         <f>IF(Utilidad!D57&gt;1,Utilidad!D57/100,Utilidad!D57)</f>
         <v>0</v>
       </c>
@@ -23677,11 +23707,11 @@
       <c r="F61" s="105" t="s">
         <v>171</v>
       </c>
-      <c r="G61" s="106">
+      <c r="G61" s="294">
         <f>Utilidad!B58</f>
         <v>0</v>
       </c>
-      <c r="H61" s="107">
+      <c r="H61" s="295">
         <f>IF(Utilidad!D58&gt;1,Utilidad!D58/100,Utilidad!D58)</f>
         <v>0</v>
       </c>
@@ -23717,11 +23747,11 @@
       <c r="F62" s="105" t="s">
         <v>172</v>
       </c>
-      <c r="G62" s="106">
+      <c r="G62" s="294">
         <f>Utilidad!B59</f>
         <v>0</v>
       </c>
-      <c r="H62" s="107">
+      <c r="H62" s="295">
         <f>IF(Utilidad!D59&gt;1,Utilidad!D59/100,Utilidad!D59)</f>
         <v>0</v>
       </c>
@@ -23757,11 +23787,11 @@
       <c r="F63" s="105" t="s">
         <v>173</v>
       </c>
-      <c r="G63" s="106">
+      <c r="G63" s="294">
         <f>Utilidad!B60</f>
         <v>0</v>
       </c>
-      <c r="H63" s="107">
+      <c r="H63" s="295">
         <f>IF(Utilidad!D60&gt;1,Utilidad!D60/100,Utilidad!D60)</f>
         <v>0</v>
       </c>
@@ -23797,11 +23827,11 @@
       <c r="F64" s="105" t="s">
         <v>174</v>
       </c>
-      <c r="G64" s="106">
+      <c r="G64" s="294">
         <f>Utilidad!B61</f>
         <v>0</v>
       </c>
-      <c r="H64" s="107">
+      <c r="H64" s="295">
         <f>IF(Utilidad!D61&gt;1,Utilidad!D61/100,Utilidad!D61)</f>
         <v>0</v>
       </c>
@@ -24166,7 +24196,7 @@
     </row>
     <row r="25" spans="2:19">
       <c r="B25" s="7"/>
-      <c r="C25" s="141"/>
+      <c r="C25" s="140"/>
       <c r="G25" s="25">
         <f>+Utilidad!J105</f>
         <v>0</v>
@@ -24175,7 +24205,7 @@
     </row>
     <row r="26" spans="2:19">
       <c r="B26" s="7"/>
-      <c r="C26" s="169">
+      <c r="C26" s="168">
         <f>+Utilidad!J103</f>
         <v>0</v>
       </c>
@@ -24187,7 +24217,7 @@
     </row>
     <row r="27" spans="2:19">
       <c r="B27" s="7"/>
-      <c r="C27" s="170">
+      <c r="C27" s="169">
         <f>+Utilidad!K103</f>
         <v>0</v>
       </c>
@@ -24203,7 +24233,7 @@
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="7"/>
-      <c r="C28" s="171">
+      <c r="C28" s="170">
         <f>+Utilidad!L103</f>
         <v>0</v>
       </c>
@@ -24215,7 +24245,7 @@
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="7"/>
-      <c r="C29" s="141"/>
+      <c r="C29" s="140"/>
       <c r="F29" s="39">
         <f>+C26-G25</f>
         <v>0</v>
@@ -24236,7 +24266,7 @@
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="7"/>
-      <c r="C30" s="141"/>
+      <c r="C30" s="140"/>
       <c r="I30" s="34">
         <f>+Utilidad!J77</f>
         <v>37746.534385999999</v>
@@ -24253,7 +24283,7 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="7"/>
-      <c r="C31" s="141"/>
+      <c r="C31" s="140"/>
       <c r="I31" s="37">
         <f>+Utilidad!K77</f>
         <v>8.5890000000000008E-2</v>
@@ -24262,7 +24292,7 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="7"/>
-      <c r="C32" s="141"/>
+      <c r="C32" s="140"/>
       <c r="I32" s="38">
         <f>I30*I31</f>
         <v>3242.0498384135403</v>
@@ -24271,12 +24301,12 @@
     </row>
     <row r="33" spans="2:19">
       <c r="B33" s="7"/>
-      <c r="C33" s="141"/>
+      <c r="C33" s="140"/>
       <c r="S33" s="24"/>
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="7"/>
-      <c r="C34" s="141"/>
+      <c r="C34" s="140"/>
       <c r="G34" s="25">
         <f>+Utilidad!J108</f>
         <v>0</v>
@@ -24286,7 +24316,7 @@
     </row>
     <row r="35" spans="2:19">
       <c r="B35" s="7"/>
-      <c r="C35" s="169">
+      <c r="C35" s="168">
         <f>+Utilidad!J106</f>
         <v>0</v>
       </c>
@@ -24300,7 +24330,7 @@
     </row>
     <row r="36" spans="2:19">
       <c r="B36" s="7"/>
-      <c r="C36" s="170">
+      <c r="C36" s="169">
         <f>+Utilidad!K106</f>
         <v>0</v>
       </c>
@@ -24312,7 +24342,7 @@
     </row>
     <row r="37" spans="2:19">
       <c r="B37" s="7"/>
-      <c r="C37" s="171">
+      <c r="C37" s="170">
         <f>+Utilidad!L106</f>
         <v>0</v>
       </c>
@@ -24320,7 +24350,7 @@
     </row>
     <row r="38" spans="2:19">
       <c r="B38" s="7"/>
-      <c r="C38" s="141"/>
+      <c r="C38" s="140"/>
       <c r="F38" s="39">
         <f>+C35-G34</f>
         <v>0</v>
@@ -24329,7 +24359,7 @@
     </row>
     <row r="39" spans="2:19">
       <c r="B39" s="7"/>
-      <c r="C39" s="141"/>
+      <c r="C39" s="140"/>
       <c r="K39" s="40">
         <f>K28-(I53+L53)</f>
         <v>3316</v>
@@ -24338,27 +24368,27 @@
     </row>
     <row r="40" spans="2:19">
       <c r="B40" s="7"/>
-      <c r="C40" s="141"/>
+      <c r="C40" s="140"/>
       <c r="S40" s="24"/>
     </row>
     <row r="41" spans="2:19">
       <c r="B41" s="7"/>
-      <c r="C41" s="141"/>
+      <c r="C41" s="140"/>
       <c r="S41" s="24"/>
     </row>
     <row r="42" spans="2:19">
       <c r="B42" s="7"/>
-      <c r="C42" s="141"/>
+      <c r="C42" s="140"/>
       <c r="S42" s="24"/>
     </row>
     <row r="43" spans="2:19">
       <c r="B43" s="7"/>
-      <c r="C43" s="141"/>
+      <c r="C43" s="140"/>
       <c r="S43" s="24"/>
     </row>
     <row r="44" spans="2:19">
       <c r="B44" s="7"/>
-      <c r="C44" s="169">
+      <c r="C44" s="168">
         <f>+Utilidad!J109</f>
         <v>0</v>
       </c>
@@ -24370,7 +24400,7 @@
     </row>
     <row r="45" spans="2:19">
       <c r="B45" s="7"/>
-      <c r="C45" s="170">
+      <c r="C45" s="169">
         <f>+Utilidad!K109</f>
         <v>0</v>
       </c>
@@ -24382,7 +24412,7 @@
     </row>
     <row r="46" spans="2:19">
       <c r="B46" s="7"/>
-      <c r="C46" s="171">
+      <c r="C46" s="170">
         <f>+Utilidad!L109</f>
         <v>0</v>
       </c>
@@ -24394,12 +24424,12 @@
     </row>
     <row r="47" spans="2:19">
       <c r="B47" s="7"/>
-      <c r="C47" s="141"/>
+      <c r="C47" s="140"/>
       <c r="S47" s="24"/>
     </row>
     <row r="48" spans="2:19">
       <c r="B48" s="7"/>
-      <c r="C48" s="141"/>
+      <c r="C48" s="140"/>
       <c r="F48" s="39">
         <f>+C44-G44</f>
         <v>0</v>
@@ -24408,27 +24438,27 @@
     </row>
     <row r="49" spans="2:19">
       <c r="B49" s="7"/>
-      <c r="C49" s="141"/>
+      <c r="C49" s="140"/>
       <c r="S49" s="24"/>
     </row>
     <row r="50" spans="2:19">
       <c r="B50" s="7"/>
-      <c r="C50" s="141"/>
+      <c r="C50" s="140"/>
       <c r="S50" s="24"/>
     </row>
     <row r="51" spans="2:19">
       <c r="B51" s="7"/>
-      <c r="C51" s="141"/>
+      <c r="C51" s="140"/>
       <c r="S51" s="24"/>
     </row>
     <row r="52" spans="2:19">
       <c r="B52" s="7"/>
-      <c r="C52" s="141"/>
+      <c r="C52" s="140"/>
       <c r="S52" s="24"/>
     </row>
     <row r="53" spans="2:19">
       <c r="B53" s="7"/>
-      <c r="C53" s="141"/>
+      <c r="C53" s="140"/>
       <c r="I53" s="31">
         <f>+Utilidad!J82</f>
         <v>0</v>
@@ -24441,7 +24471,7 @@
     </row>
     <row r="54" spans="2:19">
       <c r="B54" s="7"/>
-      <c r="C54" s="169">
+      <c r="C54" s="168">
         <f>+Utilidad!J112</f>
         <v>0</v>
       </c>
@@ -24457,7 +24487,7 @@
     </row>
     <row r="55" spans="2:19">
       <c r="B55" s="7"/>
-      <c r="C55" s="170">
+      <c r="C55" s="169">
         <f>+Utilidad!K112</f>
         <v>0</v>
       </c>
@@ -24473,7 +24503,7 @@
     </row>
     <row r="56" spans="2:19">
       <c r="B56" s="7"/>
-      <c r="C56" s="171">
+      <c r="C56" s="170">
         <f>+Utilidad!L112</f>
         <v>0</v>
       </c>
@@ -24869,162 +24899,162 @@
       </c>
     </row>
     <row r="96" spans="2:19" ht="25.5" customHeight="1">
-      <c r="G96" s="226" t="s">
+      <c r="G96" s="221" t="s">
         <v>71</v>
       </c>
-      <c r="H96" s="226"/>
-      <c r="I96" s="227"/>
-      <c r="J96" s="228" t="s">
+      <c r="H96" s="221"/>
+      <c r="I96" s="222"/>
+      <c r="J96" s="223" t="s">
         <v>72</v>
       </c>
-      <c r="K96" s="228"/>
-      <c r="L96" s="228"/>
-      <c r="M96" s="229" t="s">
+      <c r="K96" s="223"/>
+      <c r="L96" s="223"/>
+      <c r="M96" s="224" t="s">
         <v>73</v>
       </c>
-      <c r="N96" s="229"/>
-      <c r="O96" s="229"/>
-      <c r="P96" s="229"/>
+      <c r="N96" s="224"/>
+      <c r="O96" s="224"/>
+      <c r="P96" s="224"/>
     </row>
     <row r="97" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G97" s="218" t="s">
+      <c r="G97" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="H97" s="219"/>
+      <c r="H97" s="214"/>
       <c r="I97" s="21">
         <f>+E6</f>
         <v>88507</v>
       </c>
-      <c r="J97" s="224" t="s">
+      <c r="J97" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="K97" s="213"/>
+      <c r="K97" s="208"/>
       <c r="L97" s="10">
         <f>Flujos!G9</f>
         <v>-41795</v>
       </c>
-      <c r="M97" s="213" t="s">
+      <c r="M97" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="N97" s="213"/>
-      <c r="O97" s="213"/>
+      <c r="N97" s="208"/>
+      <c r="O97" s="208"/>
       <c r="P97" s="10">
         <f>+G15</f>
         <v>22063</v>
       </c>
     </row>
     <row r="98" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G98" s="218" t="s">
+      <c r="G98" s="213" t="s">
         <v>76</v>
       </c>
-      <c r="H98" s="219"/>
+      <c r="H98" s="214"/>
       <c r="I98" s="21">
         <f>+C12</f>
         <v>0</v>
       </c>
-      <c r="J98" s="213" t="s">
+      <c r="J98" s="208" t="s">
         <v>8</v>
       </c>
-      <c r="K98" s="213"/>
+      <c r="K98" s="208"/>
       <c r="L98" s="10">
         <f>Flujos!G17</f>
         <v>791</v>
       </c>
-      <c r="M98" s="213" t="s">
+      <c r="M98" s="208" t="s">
         <v>22</v>
       </c>
-      <c r="N98" s="213"/>
-      <c r="O98" s="213"/>
+      <c r="N98" s="208"/>
+      <c r="O98" s="208"/>
       <c r="P98" s="10">
         <f>+Q7</f>
         <v>47016</v>
       </c>
     </row>
     <row r="99" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G99" s="218" t="s">
+      <c r="G99" s="213" t="s">
         <v>77</v>
       </c>
-      <c r="H99" s="219"/>
+      <c r="H99" s="214"/>
       <c r="I99" s="21">
         <f>+H13</f>
         <v>43180</v>
       </c>
-      <c r="J99" s="213" t="s">
+      <c r="J99" s="208" t="s">
         <v>78</v>
       </c>
-      <c r="K99" s="213"/>
+      <c r="K99" s="208"/>
       <c r="L99" s="10">
         <v>0</v>
       </c>
-      <c r="M99" s="213" t="s">
+      <c r="M99" s="208" t="s">
         <v>23</v>
       </c>
-      <c r="N99" s="213"/>
-      <c r="O99" s="213"/>
+      <c r="N99" s="208"/>
+      <c r="O99" s="208"/>
       <c r="P99" s="10">
         <f>+Q11</f>
         <v>10446.465614000001</v>
       </c>
     </row>
     <row r="100" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G100" s="216" t="s">
+      <c r="G100" s="211" t="s">
         <v>79</v>
       </c>
-      <c r="H100" s="217"/>
+      <c r="H100" s="212"/>
       <c r="I100" s="21">
         <f>+C26</f>
         <v>0</v>
       </c>
-      <c r="J100" s="213" t="s">
+      <c r="J100" s="208" t="s">
         <v>11</v>
       </c>
-      <c r="K100" s="213"/>
+      <c r="K100" s="208"/>
       <c r="L100" s="10">
         <f>Flujos!G21</f>
         <v>3316</v>
       </c>
-      <c r="M100" s="213" t="s">
+      <c r="M100" s="208" t="s">
         <v>80</v>
       </c>
-      <c r="N100" s="213"/>
-      <c r="O100" s="213"/>
+      <c r="N100" s="208"/>
+      <c r="O100" s="208"/>
       <c r="P100" s="10">
         <f>+I30</f>
         <v>37746.534385999999</v>
       </c>
     </row>
     <row r="101" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G101" s="216" t="s">
+      <c r="G101" s="211" t="s">
         <v>57</v>
       </c>
-      <c r="H101" s="217"/>
+      <c r="H101" s="212"/>
       <c r="I101" s="21">
         <f>+C35</f>
         <v>0</v>
       </c>
-      <c r="J101" s="213" t="s">
+      <c r="J101" s="208" t="s">
         <v>81</v>
       </c>
-      <c r="K101" s="213"/>
+      <c r="K101" s="208"/>
       <c r="L101" s="10">
         <f>Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="M101" s="213" t="s">
+      <c r="M101" s="208" t="s">
         <v>82</v>
       </c>
-      <c r="N101" s="213"/>
-      <c r="O101" s="213"/>
+      <c r="N101" s="208"/>
+      <c r="O101" s="208"/>
       <c r="P101" s="10">
         <f>+M58</f>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G102" s="216" t="s">
+      <c r="G102" s="211" t="s">
         <v>60</v>
       </c>
-      <c r="H102" s="217"/>
+      <c r="H102" s="212"/>
       <c r="I102" s="21">
         <f>+C44</f>
         <v>0</v>
@@ -25037,21 +25067,21 @@
         <f>Flujos!G44</f>
         <v>0</v>
       </c>
-      <c r="M102" s="213" t="s">
+      <c r="M102" s="208" t="s">
         <v>84</v>
       </c>
-      <c r="N102" s="213"/>
-      <c r="O102" s="213"/>
+      <c r="N102" s="208"/>
+      <c r="O102" s="208"/>
       <c r="P102" s="10">
         <f>+O63</f>
         <v>104386</v>
       </c>
     </row>
     <row r="103" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G103" s="216" t="s">
+      <c r="G103" s="211" t="s">
         <v>85</v>
       </c>
-      <c r="H103" s="217"/>
+      <c r="H103" s="212"/>
       <c r="I103" s="21">
         <f>+C54</f>
         <v>0</v>
@@ -25064,21 +25094,21 @@
         <f>Flujos!G47</f>
         <v>0</v>
       </c>
-      <c r="M103" s="213" t="s">
+      <c r="M103" s="208" t="s">
         <v>87</v>
       </c>
-      <c r="N103" s="213"/>
-      <c r="O103" s="213"/>
+      <c r="N103" s="208"/>
+      <c r="O103" s="208"/>
       <c r="P103" s="10">
         <f>+O67</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G104" s="216" t="s">
+      <c r="G104" s="211" t="s">
         <v>88</v>
       </c>
-      <c r="H104" s="217"/>
+      <c r="H104" s="212"/>
       <c r="I104" s="21">
         <f>+C62</f>
         <v>77372</v>
@@ -25091,21 +25121,21 @@
         <f>Flujos!G50</f>
         <v>0</v>
       </c>
-      <c r="M104" s="213" t="s">
+      <c r="M104" s="208" t="s">
         <v>44</v>
       </c>
-      <c r="N104" s="213"/>
-      <c r="O104" s="213"/>
+      <c r="N104" s="208"/>
+      <c r="O104" s="208"/>
       <c r="P104" s="10">
         <f>+O74</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G105" s="216" t="s">
+      <c r="G105" s="211" t="s">
         <v>90</v>
       </c>
-      <c r="H105" s="217"/>
+      <c r="H105" s="212"/>
       <c r="I105" s="21">
         <f>+H70</f>
         <v>0</v>
@@ -25118,38 +25148,38 @@
         <f>Flujos!G53</f>
         <v>0</v>
       </c>
-      <c r="M105" s="213" t="s">
+      <c r="M105" s="208" t="s">
         <v>92</v>
       </c>
-      <c r="N105" s="213"/>
-      <c r="O105" s="213"/>
+      <c r="N105" s="208"/>
+      <c r="O105" s="208"/>
       <c r="P105" s="10">
         <f>+O84</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G106" s="216" t="s">
+      <c r="G106" s="211" t="s">
         <v>93</v>
       </c>
-      <c r="H106" s="217"/>
+      <c r="H106" s="212"/>
       <c r="I106" s="21">
         <f>+H75</f>
         <v>0</v>
       </c>
-      <c r="J106" s="213" t="s">
+      <c r="J106" s="208" t="s">
         <v>13</v>
       </c>
-      <c r="K106" s="213"/>
+      <c r="K106" s="208"/>
       <c r="L106" s="10">
         <f>Flujos!G42</f>
         <v>0</v>
       </c>
-      <c r="M106" s="213" t="s">
+      <c r="M106" s="208" t="s">
         <v>160</v>
       </c>
-      <c r="N106" s="213"/>
-      <c r="O106" s="213"/>
+      <c r="N106" s="208"/>
+      <c r="O106" s="208"/>
       <c r="P106" s="10">
         <f>Q79</f>
         <v>127</v>
@@ -25172,9 +25202,9 @@
         <f>Flujos!G26</f>
         <v>25089</v>
       </c>
-      <c r="M107" s="210"/>
-      <c r="N107" s="211"/>
-      <c r="O107" s="212"/>
+      <c r="M107" s="205"/>
+      <c r="N107" s="206"/>
+      <c r="O107" s="207"/>
       <c r="P107" s="10"/>
     </row>
     <row r="108" spans="7:16" ht="25.5" customHeight="1">
@@ -25186,17 +25216,17 @@
         <f>+L78</f>
         <v>5360</v>
       </c>
-      <c r="J108" s="213" t="s">
+      <c r="J108" s="208" t="s">
         <v>12</v>
       </c>
-      <c r="K108" s="213"/>
+      <c r="K108" s="208"/>
       <c r="L108" s="10">
         <f>Flujos!G34</f>
         <v>27987</v>
       </c>
-      <c r="M108" s="210"/>
-      <c r="N108" s="211"/>
-      <c r="O108" s="212"/>
+      <c r="M108" s="205"/>
+      <c r="N108" s="206"/>
+      <c r="O108" s="207"/>
       <c r="P108" s="10"/>
     </row>
     <row r="109" spans="7:16" ht="25.5" customHeight="1">
@@ -25208,177 +25238,189 @@
         <f>+K86</f>
         <v>0</v>
       </c>
-      <c r="J109" s="213" t="s">
+      <c r="J109" s="208" t="s">
         <v>10</v>
       </c>
-      <c r="K109" s="213"/>
+      <c r="K109" s="208"/>
       <c r="L109" s="10">
         <f>Flujos!G39</f>
         <v>6394</v>
       </c>
-      <c r="M109" s="210"/>
-      <c r="N109" s="211"/>
-      <c r="O109" s="212"/>
+      <c r="M109" s="205"/>
+      <c r="N109" s="206"/>
+      <c r="O109" s="207"/>
       <c r="P109" s="10"/>
     </row>
     <row r="110" spans="7:16" ht="25.5" customHeight="1">
-      <c r="G110" s="216" t="s">
+      <c r="G110" s="211" t="s">
         <v>98</v>
       </c>
-      <c r="H110" s="217"/>
+      <c r="H110" s="212"/>
       <c r="I110" s="21">
         <f>+L90</f>
         <v>6394</v>
       </c>
-      <c r="J110" s="213"/>
-      <c r="K110" s="213"/>
+      <c r="J110" s="208"/>
+      <c r="K110" s="208"/>
       <c r="L110" s="10"/>
-      <c r="M110" s="213"/>
-      <c r="N110" s="213"/>
-      <c r="O110" s="213"/>
+      <c r="M110" s="208"/>
+      <c r="N110" s="208"/>
+      <c r="O110" s="208"/>
       <c r="P110" s="10"/>
     </row>
     <row r="111" spans="7:16" ht="26" customHeight="1">
-      <c r="G111" s="216" t="s">
+      <c r="G111" s="211" t="s">
         <v>176</v>
       </c>
-      <c r="H111" s="217"/>
+      <c r="H111" s="212"/>
       <c r="I111" s="21">
         <f>K82</f>
         <v>4403</v>
       </c>
-      <c r="J111" s="213"/>
-      <c r="K111" s="213"/>
+      <c r="J111" s="208"/>
+      <c r="K111" s="208"/>
       <c r="L111" s="10"/>
-      <c r="M111" s="213"/>
-      <c r="N111" s="213"/>
-      <c r="O111" s="213"/>
+      <c r="M111" s="208"/>
+      <c r="N111" s="208"/>
+      <c r="O111" s="208"/>
       <c r="P111" s="10"/>
     </row>
     <row r="112" spans="7:16">
-      <c r="G112" s="216" t="s">
-        <v>177</v>
-      </c>
-      <c r="H112" s="217"/>
+      <c r="G112" s="211" t="s">
+        <v>181</v>
+      </c>
+      <c r="H112" s="212" t="s">
+        <v>169</v>
+      </c>
       <c r="I112" s="21">
         <f>Flujos!G59</f>
         <v>0</v>
       </c>
-      <c r="J112" s="213"/>
-      <c r="K112" s="213"/>
+      <c r="J112" s="208"/>
+      <c r="K112" s="208"/>
       <c r="L112" s="10"/>
-      <c r="M112" s="213"/>
-      <c r="N112" s="213"/>
-      <c r="O112" s="213"/>
+      <c r="M112" s="208"/>
+      <c r="N112" s="208"/>
+      <c r="O112" s="208"/>
       <c r="P112" s="10"/>
     </row>
     <row r="113" spans="7:16">
-      <c r="G113" s="216" t="s">
-        <v>178</v>
-      </c>
-      <c r="H113" s="217"/>
+      <c r="G113" s="211" t="s">
+        <v>182</v>
+      </c>
+      <c r="H113" s="212" t="s">
+        <v>170</v>
+      </c>
       <c r="I113" s="21">
         <f>Flujos!G60</f>
         <v>0</v>
       </c>
-      <c r="J113" s="213"/>
-      <c r="K113" s="213"/>
+      <c r="J113" s="208"/>
+      <c r="K113" s="208"/>
       <c r="L113" s="10"/>
-      <c r="M113" s="213"/>
-      <c r="N113" s="213"/>
-      <c r="O113" s="213"/>
+      <c r="M113" s="208"/>
+      <c r="N113" s="208"/>
+      <c r="O113" s="208"/>
       <c r="P113" s="10"/>
     </row>
     <row r="114" spans="7:16">
-      <c r="G114" s="216" t="s">
-        <v>179</v>
-      </c>
-      <c r="H114" s="217"/>
+      <c r="G114" s="211" t="s">
+        <v>183</v>
+      </c>
+      <c r="H114" s="212" t="s">
+        <v>171</v>
+      </c>
       <c r="I114" s="21">
         <f>Flujos!G61</f>
         <v>0</v>
       </c>
-      <c r="J114" s="213"/>
-      <c r="K114" s="213"/>
+      <c r="J114" s="208"/>
+      <c r="K114" s="208"/>
       <c r="L114" s="10"/>
-      <c r="M114" s="213"/>
-      <c r="N114" s="213"/>
-      <c r="O114" s="213"/>
+      <c r="M114" s="208"/>
+      <c r="N114" s="208"/>
+      <c r="O114" s="208"/>
       <c r="P114" s="10"/>
     </row>
     <row r="115" spans="7:16">
-      <c r="G115" s="216" t="s">
-        <v>179</v>
-      </c>
-      <c r="H115" s="217"/>
+      <c r="G115" s="211" t="s">
+        <v>184</v>
+      </c>
+      <c r="H115" s="212" t="s">
+        <v>172</v>
+      </c>
       <c r="I115" s="21">
         <f>Flujos!G62</f>
         <v>0</v>
       </c>
-      <c r="J115" s="213"/>
-      <c r="K115" s="213"/>
+      <c r="J115" s="208"/>
+      <c r="K115" s="208"/>
       <c r="L115" s="10"/>
-      <c r="M115" s="213"/>
-      <c r="N115" s="213"/>
-      <c r="O115" s="213"/>
+      <c r="M115" s="208"/>
+      <c r="N115" s="208"/>
+      <c r="O115" s="208"/>
       <c r="P115" s="10"/>
     </row>
     <row r="116" spans="7:16">
-      <c r="G116" s="216" t="s">
-        <v>177</v>
-      </c>
-      <c r="H116" s="217"/>
+      <c r="G116" s="211" t="s">
+        <v>185</v>
+      </c>
+      <c r="H116" s="212" t="s">
+        <v>173</v>
+      </c>
       <c r="I116" s="21">
         <f>Flujos!G63</f>
         <v>0</v>
       </c>
-      <c r="J116" s="213"/>
-      <c r="K116" s="213"/>
+      <c r="J116" s="208"/>
+      <c r="K116" s="208"/>
       <c r="L116" s="10"/>
-      <c r="M116" s="213"/>
-      <c r="N116" s="213"/>
-      <c r="O116" s="213"/>
+      <c r="M116" s="208"/>
+      <c r="N116" s="208"/>
+      <c r="O116" s="208"/>
       <c r="P116" s="10"/>
     </row>
     <row r="117" spans="7:16">
-      <c r="G117" s="216" t="s">
-        <v>180</v>
-      </c>
-      <c r="H117" s="217"/>
+      <c r="G117" s="211" t="s">
+        <v>186</v>
+      </c>
+      <c r="H117" s="212" t="s">
+        <v>174</v>
+      </c>
       <c r="I117" s="21">
         <f>Flujos!G64</f>
         <v>0</v>
       </c>
-      <c r="J117" s="213"/>
-      <c r="K117" s="213"/>
+      <c r="J117" s="208"/>
+      <c r="K117" s="208"/>
       <c r="L117" s="10"/>
-      <c r="M117" s="213"/>
-      <c r="N117" s="213"/>
-      <c r="O117" s="213"/>
+      <c r="M117" s="208"/>
+      <c r="N117" s="208"/>
+      <c r="O117" s="208"/>
       <c r="P117" s="10"/>
     </row>
     <row r="118" spans="7:16" ht="27.75" customHeight="1">
-      <c r="G118" s="214" t="s">
+      <c r="G118" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="H118" s="215"/>
+      <c r="H118" s="210"/>
       <c r="I118" s="12">
         <f>+SUM(I97:I117)</f>
         <v>243567</v>
       </c>
-      <c r="J118" s="225" t="s">
+      <c r="J118" s="220" t="s">
         <v>100</v>
       </c>
-      <c r="K118" s="225"/>
+      <c r="K118" s="220"/>
       <c r="L118" s="13">
         <f>+SUM(L97:L110)</f>
         <v>21782</v>
       </c>
-      <c r="M118" s="225" t="s">
+      <c r="M118" s="220" t="s">
         <v>101</v>
       </c>
-      <c r="N118" s="225"/>
-      <c r="O118" s="225"/>
+      <c r="N118" s="220"/>
+      <c r="O118" s="220"/>
       <c r="P118" s="12">
         <f>+SUM(P97:P110)</f>
         <v>221785</v>
@@ -25420,55 +25462,55 @@
       </c>
     </row>
     <row r="125" spans="7:16" ht="27.75" customHeight="1">
-      <c r="G125" s="220" t="s">
+      <c r="G125" s="215" t="s">
         <v>71</v>
       </c>
-      <c r="H125" s="220"/>
-      <c r="I125" s="221"/>
-      <c r="J125" s="222" t="s">
+      <c r="H125" s="215"/>
+      <c r="I125" s="216"/>
+      <c r="J125" s="217" t="s">
         <v>72</v>
       </c>
-      <c r="K125" s="222"/>
-      <c r="L125" s="222"/>
-      <c r="M125" s="223" t="s">
+      <c r="K125" s="217"/>
+      <c r="L125" s="217"/>
+      <c r="M125" s="218" t="s">
         <v>73</v>
       </c>
-      <c r="N125" s="223"/>
-      <c r="O125" s="223"/>
-      <c r="P125" s="223"/>
+      <c r="N125" s="218"/>
+      <c r="O125" s="218"/>
+      <c r="P125" s="218"/>
     </row>
     <row r="126" spans="7:16" ht="27.75" customHeight="1">
-      <c r="G126" s="218" t="s">
+      <c r="G126" s="213" t="s">
         <v>74</v>
       </c>
-      <c r="H126" s="219"/>
+      <c r="H126" s="214"/>
       <c r="I126" s="21">
         <f>+E8</f>
         <v>33752.992219609914</v>
       </c>
-      <c r="J126" s="224" t="s">
+      <c r="J126" s="219" t="s">
         <v>7</v>
       </c>
-      <c r="K126" s="213"/>
+      <c r="K126" s="208"/>
       <c r="L126" s="10">
         <f>Flujos!G9*Flujos!H9</f>
         <v>-19153.812600000001</v>
       </c>
-      <c r="M126" s="213" t="s">
+      <c r="M126" s="208" t="s">
         <v>75</v>
       </c>
-      <c r="N126" s="213"/>
-      <c r="O126" s="213"/>
+      <c r="N126" s="208"/>
+      <c r="O126" s="208"/>
       <c r="P126" s="10">
         <f>+G17</f>
         <v>3996.1132632666299</v>
       </c>
     </row>
     <row r="127" spans="7:16" ht="27.75" customHeight="1">
-      <c r="G127" s="197" t="s">
+      <c r="G127" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="H127" s="298"/>
+      <c r="H127" s="293"/>
       <c r="I127" s="21">
         <f>+C14</f>
         <v>0</v>
@@ -25492,10 +25534,10 @@
       </c>
     </row>
     <row r="128" spans="7:16" ht="27.75" customHeight="1">
-      <c r="G128" s="197" t="s">
+      <c r="G128" s="192" t="s">
         <v>77</v>
       </c>
-      <c r="H128" s="198"/>
+      <c r="H128" s="193"/>
       <c r="I128" s="21">
         <f>+H15</f>
         <v>20830.031999999999</v>
@@ -25723,9 +25765,9 @@
         <f>Flujos!G26*Flujos!H26</f>
         <v>17542.103354999999</v>
       </c>
-      <c r="M136" s="199"/>
-      <c r="N136" s="200"/>
-      <c r="O136" s="201"/>
+      <c r="M136" s="194"/>
+      <c r="N136" s="195"/>
+      <c r="O136" s="196"/>
       <c r="P136" s="10"/>
     </row>
     <row r="137" spans="7:16">
@@ -25745,9 +25787,9 @@
         <f>Flujos!G34*Flujos!H34</f>
         <v>17300.927600009971</v>
       </c>
-      <c r="M137" s="199"/>
-      <c r="N137" s="200"/>
-      <c r="O137" s="201"/>
+      <c r="M137" s="194"/>
+      <c r="N137" s="195"/>
+      <c r="O137" s="196"/>
       <c r="P137" s="10"/>
     </row>
     <row r="138" spans="7:16">
@@ -25767,9 +25809,9 @@
         <f>Flujos!G39*Flujos!H39</f>
         <v>3773.0993999999996</v>
       </c>
-      <c r="M138" s="199"/>
-      <c r="N138" s="200"/>
-      <c r="O138" s="201"/>
+      <c r="M138" s="194"/>
+      <c r="N138" s="195"/>
+      <c r="O138" s="196"/>
       <c r="P138" s="10"/>
     </row>
     <row r="139" spans="7:16">
@@ -25807,129 +25849,129 @@
       <c r="P140" s="10"/>
     </row>
     <row r="141" spans="7:16">
-      <c r="G141" s="216" t="s">
+      <c r="G141" s="211" t="s">
         <v>177</v>
       </c>
-      <c r="H141" s="217"/>
+      <c r="H141" s="212"/>
       <c r="I141" s="21">
         <f>Flujos!G59*Flujos!H59</f>
         <v>0</v>
       </c>
-      <c r="J141" s="213"/>
-      <c r="K141" s="213"/>
+      <c r="J141" s="208"/>
+      <c r="K141" s="208"/>
       <c r="L141" s="10"/>
-      <c r="M141" s="213"/>
-      <c r="N141" s="213"/>
-      <c r="O141" s="213"/>
+      <c r="M141" s="208"/>
+      <c r="N141" s="208"/>
+      <c r="O141" s="208"/>
       <c r="P141" s="10"/>
     </row>
     <row r="142" spans="7:16">
-      <c r="G142" s="216" t="s">
+      <c r="G142" s="211" t="s">
         <v>178</v>
       </c>
-      <c r="H142" s="217"/>
+      <c r="H142" s="212"/>
       <c r="I142" s="21">
         <f>Flujos!G60*Flujos!H60</f>
         <v>0</v>
       </c>
-      <c r="J142" s="213"/>
-      <c r="K142" s="213"/>
+      <c r="J142" s="208"/>
+      <c r="K142" s="208"/>
       <c r="L142" s="10"/>
-      <c r="M142" s="213"/>
-      <c r="N142" s="213"/>
-      <c r="O142" s="213"/>
+      <c r="M142" s="208"/>
+      <c r="N142" s="208"/>
+      <c r="O142" s="208"/>
       <c r="P142" s="10"/>
     </row>
     <row r="143" spans="7:16">
-      <c r="G143" s="216" t="s">
+      <c r="G143" s="211" t="s">
         <v>179</v>
       </c>
-      <c r="H143" s="217"/>
+      <c r="H143" s="212"/>
       <c r="I143" s="21">
         <f>Flujos!G61*Flujos!H61</f>
         <v>0</v>
       </c>
-      <c r="J143" s="213"/>
-      <c r="K143" s="213"/>
+      <c r="J143" s="208"/>
+      <c r="K143" s="208"/>
       <c r="L143" s="10"/>
-      <c r="M143" s="213"/>
-      <c r="N143" s="213"/>
-      <c r="O143" s="213"/>
+      <c r="M143" s="208"/>
+      <c r="N143" s="208"/>
+      <c r="O143" s="208"/>
       <c r="P143" s="10"/>
     </row>
     <row r="144" spans="7:16">
-      <c r="G144" s="216" t="s">
+      <c r="G144" s="211" t="s">
         <v>179</v>
       </c>
-      <c r="H144" s="217"/>
+      <c r="H144" s="212"/>
       <c r="I144" s="21">
         <f>Flujos!G62*Flujos!H62</f>
         <v>0</v>
       </c>
-      <c r="J144" s="213"/>
-      <c r="K144" s="213"/>
+      <c r="J144" s="208"/>
+      <c r="K144" s="208"/>
       <c r="L144" s="10"/>
-      <c r="M144" s="213"/>
-      <c r="N144" s="213"/>
-      <c r="O144" s="213"/>
+      <c r="M144" s="208"/>
+      <c r="N144" s="208"/>
+      <c r="O144" s="208"/>
       <c r="P144" s="10"/>
     </row>
     <row r="145" spans="7:16">
-      <c r="G145" s="216" t="s">
+      <c r="G145" s="211" t="s">
         <v>177</v>
       </c>
-      <c r="H145" s="217"/>
+      <c r="H145" s="212"/>
       <c r="I145" s="21">
         <f>Flujos!G63*Flujos!H63</f>
         <v>0</v>
       </c>
-      <c r="J145" s="213"/>
-      <c r="K145" s="213"/>
+      <c r="J145" s="208"/>
+      <c r="K145" s="208"/>
       <c r="L145" s="10"/>
-      <c r="M145" s="213"/>
-      <c r="N145" s="213"/>
-      <c r="O145" s="213"/>
+      <c r="M145" s="208"/>
+      <c r="N145" s="208"/>
+      <c r="O145" s="208"/>
       <c r="P145" s="10"/>
     </row>
     <row r="146" spans="7:16">
-      <c r="G146" s="216" t="s">
+      <c r="G146" s="211" t="s">
         <v>180</v>
       </c>
-      <c r="H146" s="217"/>
+      <c r="H146" s="212"/>
       <c r="I146" s="21">
         <f>Flujos!G64*Flujos!H64</f>
         <v>0</v>
       </c>
-      <c r="J146" s="213"/>
-      <c r="K146" s="213"/>
+      <c r="J146" s="208"/>
+      <c r="K146" s="208"/>
       <c r="L146" s="10"/>
-      <c r="M146" s="213"/>
-      <c r="N146" s="213"/>
-      <c r="O146" s="213"/>
+      <c r="M146" s="208"/>
+      <c r="N146" s="208"/>
+      <c r="O146" s="208"/>
       <c r="P146" s="10"/>
     </row>
     <row r="147" spans="7:16" ht="19">
-      <c r="G147" s="214" t="s">
+      <c r="G147" s="209" t="s">
         <v>99</v>
       </c>
-      <c r="H147" s="215"/>
+      <c r="H147" s="210"/>
       <c r="I147" s="12">
         <f>+SUM(I126:I146)</f>
         <v>117522.50051960992</v>
       </c>
-      <c r="J147" s="225" t="s">
+      <c r="J147" s="220" t="s">
         <v>100</v>
       </c>
-      <c r="K147" s="225"/>
+      <c r="K147" s="220"/>
       <c r="L147" s="13">
         <f>+SUM(L126:L139)</f>
         <v>23052.405752154889</v>
       </c>
-      <c r="M147" s="225" t="s">
+      <c r="M147" s="220" t="s">
         <v>101</v>
       </c>
-      <c r="N147" s="225"/>
-      <c r="O147" s="225"/>
+      <c r="N147" s="220"/>
+      <c r="O147" s="220"/>
       <c r="P147" s="12">
         <f>+SUM(P126:P139)</f>
         <v>94470.094767147384</v>
@@ -28920,85 +28962,85 @@
     <row r="2" spans="2:20" ht="14">
       <c r="B2" s="49"/>
       <c r="C2" s="50"/>
-      <c r="D2" s="277"/>
-      <c r="E2" s="278"/>
-      <c r="F2" s="283" t="s">
+      <c r="D2" s="272"/>
+      <c r="E2" s="273"/>
+      <c r="F2" s="278" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="283"/>
-      <c r="H2" s="283"/>
-      <c r="I2" s="283"/>
-      <c r="J2" s="283"/>
-      <c r="K2" s="283"/>
-      <c r="L2" s="283"/>
-      <c r="M2" s="283"/>
-      <c r="N2" s="283"/>
-      <c r="O2" s="283"/>
-      <c r="P2" s="283"/>
-      <c r="Q2" s="284"/>
+      <c r="G2" s="278"/>
+      <c r="H2" s="278"/>
+      <c r="I2" s="278"/>
+      <c r="J2" s="278"/>
+      <c r="K2" s="278"/>
+      <c r="L2" s="278"/>
+      <c r="M2" s="278"/>
+      <c r="N2" s="278"/>
+      <c r="O2" s="278"/>
+      <c r="P2" s="278"/>
+      <c r="Q2" s="279"/>
       <c r="R2" s="51"/>
     </row>
     <row r="3" spans="2:20" ht="14">
       <c r="B3" s="49"/>
       <c r="C3" s="50"/>
-      <c r="D3" s="279"/>
-      <c r="E3" s="280"/>
-      <c r="F3" s="285"/>
-      <c r="G3" s="285"/>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="285"/>
-      <c r="M3" s="285"/>
-      <c r="N3" s="285"/>
-      <c r="O3" s="285"/>
-      <c r="P3" s="285"/>
-      <c r="Q3" s="286"/>
+      <c r="D3" s="274"/>
+      <c r="E3" s="275"/>
+      <c r="F3" s="280"/>
+      <c r="G3" s="280"/>
+      <c r="H3" s="280"/>
+      <c r="I3" s="280"/>
+      <c r="J3" s="280"/>
+      <c r="K3" s="280"/>
+      <c r="L3" s="280"/>
+      <c r="M3" s="280"/>
+      <c r="N3" s="280"/>
+      <c r="O3" s="280"/>
+      <c r="P3" s="280"/>
+      <c r="Q3" s="281"/>
       <c r="R3" s="51"/>
     </row>
     <row r="4" spans="2:20" ht="16">
       <c r="B4" s="49"/>
       <c r="C4" s="50"/>
-      <c r="D4" s="279"/>
-      <c r="E4" s="280"/>
-      <c r="F4" s="285" t="s">
+      <c r="D4" s="274"/>
+      <c r="E4" s="275"/>
+      <c r="F4" s="280" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="285"/>
-      <c r="H4" s="285"/>
-      <c r="I4" s="285"/>
-      <c r="J4" s="285"/>
-      <c r="K4" s="285"/>
-      <c r="L4" s="285"/>
-      <c r="M4" s="285" t="s">
+      <c r="G4" s="280"/>
+      <c r="H4" s="280"/>
+      <c r="I4" s="280"/>
+      <c r="J4" s="280"/>
+      <c r="K4" s="280"/>
+      <c r="L4" s="280"/>
+      <c r="M4" s="280" t="s">
         <v>109</v>
       </c>
-      <c r="N4" s="285"/>
-      <c r="O4" s="129"/>
-      <c r="P4" s="288">
+      <c r="N4" s="280"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="283">
         <v>45230</v>
       </c>
-      <c r="Q4" s="289"/>
+      <c r="Q4" s="284"/>
       <c r="R4" s="51"/>
     </row>
     <row r="5" spans="2:20" ht="17" thickBot="1">
       <c r="B5" s="49"/>
       <c r="C5" s="50"/>
-      <c r="D5" s="281"/>
-      <c r="E5" s="282"/>
-      <c r="F5" s="287"/>
-      <c r="G5" s="287"/>
-      <c r="H5" s="287"/>
-      <c r="I5" s="287"/>
-      <c r="J5" s="287"/>
-      <c r="K5" s="287"/>
-      <c r="L5" s="287"/>
-      <c r="M5" s="287"/>
-      <c r="N5" s="287"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="290"/>
-      <c r="Q5" s="291"/>
+      <c r="D5" s="276"/>
+      <c r="E5" s="277"/>
+      <c r="F5" s="282"/>
+      <c r="G5" s="282"/>
+      <c r="H5" s="282"/>
+      <c r="I5" s="282"/>
+      <c r="J5" s="282"/>
+      <c r="K5" s="282"/>
+      <c r="L5" s="282"/>
+      <c r="M5" s="282"/>
+      <c r="N5" s="282"/>
+      <c r="O5" s="129"/>
+      <c r="P5" s="285"/>
+      <c r="Q5" s="286"/>
       <c r="R5" s="51"/>
     </row>
     <row r="6" spans="2:20" thickBot="1">
@@ -29021,26 +29063,26 @@
     <row r="7" spans="2:20" ht="15" customHeight="1">
       <c r="B7" s="54"/>
       <c r="C7" s="55"/>
-      <c r="D7" s="269"/>
-      <c r="E7" s="270"/>
-      <c r="F7" s="270"/>
-      <c r="G7" s="292" t="s">
+      <c r="D7" s="264"/>
+      <c r="E7" s="265"/>
+      <c r="F7" s="265"/>
+      <c r="G7" s="287" t="s">
         <v>110</v>
       </c>
-      <c r="H7" s="293"/>
+      <c r="H7" s="288"/>
       <c r="I7" s="56" t="s">
         <v>111</v>
       </c>
       <c r="J7" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="K7" s="273"/>
-      <c r="L7" s="274"/>
-      <c r="M7" s="274"/>
-      <c r="N7" s="292" t="s">
+      <c r="K7" s="268"/>
+      <c r="L7" s="269"/>
+      <c r="M7" s="269"/>
+      <c r="N7" s="287" t="s">
         <v>110</v>
       </c>
-      <c r="O7" s="293"/>
+      <c r="O7" s="288"/>
       <c r="P7" s="56" t="s">
         <v>111</v>
       </c>
@@ -29052,9 +29094,9 @@
     <row r="8" spans="2:20" thickBot="1">
       <c r="B8" s="54"/>
       <c r="C8" s="55"/>
-      <c r="D8" s="271"/>
-      <c r="E8" s="272"/>
-      <c r="F8" s="272"/>
+      <c r="D8" s="266"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
       <c r="G8" s="58" t="s">
         <v>1</v>
       </c>
@@ -29067,9 +29109,9 @@
       <c r="J8" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="275"/>
-      <c r="L8" s="276"/>
-      <c r="M8" s="276"/>
+      <c r="K8" s="270"/>
+      <c r="L8" s="271"/>
+      <c r="M8" s="271"/>
       <c r="N8" s="58" t="s">
         <v>1</v>
       </c>
@@ -29087,24 +29129,24 @@
     <row r="9" spans="2:20" ht="14">
       <c r="B9" s="54"/>
       <c r="C9" s="55"/>
-      <c r="D9" s="247" t="s">
+      <c r="D9" s="242" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="294"/>
-      <c r="K9" s="244" t="s">
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="289"/>
+      <c r="K9" s="239" t="s">
         <v>153</v>
       </c>
-      <c r="L9" s="245"/>
-      <c r="M9" s="245"/>
-      <c r="N9" s="245"/>
-      <c r="O9" s="245"/>
-      <c r="P9" s="245"/>
-      <c r="Q9" s="246"/>
+      <c r="L9" s="240"/>
+      <c r="M9" s="240"/>
+      <c r="N9" s="240"/>
+      <c r="O9" s="240"/>
+      <c r="P9" s="240"/>
+      <c r="Q9" s="241"/>
       <c r="R9" s="51"/>
     </row>
     <row r="10" spans="2:20" thickBot="1">
@@ -29112,11 +29154,11 @@
       <c r="C10" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="230" t="s">
+      <c r="D10" s="225" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="231"/>
-      <c r="F10" s="252"/>
+      <c r="E10" s="226"/>
+      <c r="F10" s="247"/>
       <c r="G10" s="62">
         <f>Flujos!G4</f>
         <v>88507</v>
@@ -29133,11 +29175,11 @@
         <f>+I10*G10</f>
         <v>33752.992219609914</v>
       </c>
-      <c r="K10" s="233" t="s">
+      <c r="K10" s="228" t="s">
         <v>116</v>
       </c>
-      <c r="L10" s="234"/>
-      <c r="M10" s="253"/>
+      <c r="L10" s="229"/>
+      <c r="M10" s="248"/>
       <c r="N10" s="117">
         <f>Flujos!G20</f>
         <v>132791</v>
@@ -29146,7 +29188,7 @@
         <f>N10/(1-'Datos Extra'!B28)</f>
         <v>144652.50544662308</v>
       </c>
-      <c r="P10" s="175">
+      <c r="P10" s="174">
         <f>Flujos!H20</f>
         <v>0.67602529614999995</v>
       </c>
@@ -29160,11 +29202,11 @@
     <row r="11" spans="2:20" ht="14">
       <c r="B11" s="54"/>
       <c r="C11" s="55"/>
-      <c r="D11" s="233" t="s">
+      <c r="D11" s="228" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="234"/>
-      <c r="F11" s="253"/>
+      <c r="E11" s="229"/>
+      <c r="F11" s="248"/>
       <c r="G11" s="64">
         <f>Flujos!G5</f>
         <v>0</v>
@@ -29181,26 +29223,26 @@
         <f>+I11*G11</f>
         <v>0</v>
       </c>
-      <c r="K11" s="257" t="s">
+      <c r="K11" s="252" t="s">
         <v>127</v>
       </c>
-      <c r="L11" s="258"/>
-      <c r="M11" s="258"/>
-      <c r="N11" s="258"/>
-      <c r="O11" s="258"/>
-      <c r="P11" s="258"/>
-      <c r="Q11" s="259"/>
+      <c r="L11" s="253"/>
+      <c r="M11" s="253"/>
+      <c r="N11" s="253"/>
+      <c r="O11" s="253"/>
+      <c r="P11" s="253"/>
+      <c r="Q11" s="254"/>
       <c r="R11" s="51"/>
       <c r="T11" s="87"/>
     </row>
     <row r="12" spans="2:20" ht="14">
       <c r="B12" s="54"/>
       <c r="C12" s="55"/>
-      <c r="D12" s="230" t="s">
+      <c r="D12" s="225" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="231"/>
-      <c r="F12" s="252"/>
+      <c r="E12" s="226"/>
+      <c r="F12" s="247"/>
       <c r="G12" s="60">
         <f>Flujos!G8</f>
         <v>43180</v>
@@ -29217,11 +29259,11 @@
         <f>+I12*G12</f>
         <v>20830.031999999999</v>
       </c>
-      <c r="K12" s="260" t="s">
+      <c r="K12" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="L12" s="261"/>
-      <c r="M12" s="262"/>
+      <c r="L12" s="256"/>
+      <c r="M12" s="257"/>
       <c r="N12" s="60">
         <f>Flujos!G6</f>
         <v>22063</v>
@@ -29243,11 +29285,11 @@
     <row r="13" spans="2:20" ht="14">
       <c r="B13" s="54"/>
       <c r="C13" s="55"/>
-      <c r="D13" s="233" t="s">
+      <c r="D13" s="228" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="234"/>
-      <c r="F13" s="253"/>
+      <c r="E13" s="229"/>
+      <c r="F13" s="248"/>
       <c r="G13" s="64">
         <f>Flujos!G55</f>
         <v>77372</v>
@@ -29264,11 +29306,11 @@
         <f>+I13*G13</f>
         <v>41780.880000000005</v>
       </c>
-      <c r="K13" s="263" t="s">
+      <c r="K13" s="258" t="s">
         <v>130</v>
       </c>
-      <c r="L13" s="264"/>
-      <c r="M13" s="265"/>
+      <c r="L13" s="259"/>
+      <c r="M13" s="260"/>
       <c r="N13" s="73">
         <f>Flujos!G12</f>
         <v>47016</v>
@@ -29277,7 +29319,7 @@
         <f>N13/(1-'Datos Extra'!B36)</f>
         <v>52120.839742043754</v>
       </c>
-      <c r="P13" s="196">
+      <c r="P13" s="191">
         <f>Flujos!H12</f>
         <v>0.34271999999999997</v>
       </c>
@@ -29290,11 +29332,11 @@
     <row r="14" spans="2:20" ht="14">
       <c r="B14" s="54"/>
       <c r="C14" s="55"/>
-      <c r="D14" s="230" t="s">
+      <c r="D14" s="225" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="231"/>
-      <c r="F14" s="252"/>
+      <c r="E14" s="226"/>
+      <c r="F14" s="247"/>
       <c r="G14" s="60">
         <f>Flujos!G31</f>
         <v>0</v>
@@ -29311,11 +29353,11 @@
         <f>+I14*G14</f>
         <v>0</v>
       </c>
-      <c r="K14" s="260" t="s">
+      <c r="K14" s="255" t="s">
         <v>131</v>
       </c>
-      <c r="L14" s="261"/>
-      <c r="M14" s="262"/>
+      <c r="L14" s="256"/>
+      <c r="M14" s="257"/>
       <c r="N14" s="74">
         <f>Flujos!G13</f>
         <v>10446.465614000001</v>
@@ -29351,7 +29393,7 @@
         <v>37746.534385999999</v>
       </c>
       <c r="O15" s="76"/>
-      <c r="P15" s="174">
+      <c r="P15" s="173">
         <f>Flujos!H19</f>
         <v>8.5890000000000008E-2</v>
       </c>
@@ -29364,18 +29406,18 @@
     <row r="16" spans="2:20" thickBot="1">
       <c r="B16" s="54"/>
       <c r="C16" s="55"/>
-      <c r="D16" s="230"/>
-      <c r="E16" s="231"/>
-      <c r="F16" s="252"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="226"/>
+      <c r="F16" s="247"/>
       <c r="G16" s="60"/>
       <c r="H16" s="60"/>
       <c r="I16" s="61"/>
       <c r="J16" s="60"/>
-      <c r="K16" s="250" t="s">
+      <c r="K16" s="245" t="s">
         <v>125</v>
       </c>
-      <c r="L16" s="251"/>
-      <c r="M16" s="251"/>
+      <c r="L16" s="246"/>
+      <c r="M16" s="246"/>
       <c r="N16" s="67">
         <f>+SUM(N12:N15)</f>
         <v>117272</v>
@@ -29394,22 +29436,22 @@
     <row r="17" spans="2:21" thickBot="1">
       <c r="B17" s="54"/>
       <c r="C17" s="55"/>
-      <c r="D17" s="230"/>
-      <c r="E17" s="231"/>
-      <c r="F17" s="252"/>
+      <c r="D17" s="225"/>
+      <c r="E17" s="226"/>
+      <c r="F17" s="247"/>
       <c r="G17" s="60"/>
       <c r="H17" s="60"/>
       <c r="I17" s="61"/>
       <c r="J17" s="60"/>
-      <c r="K17" s="244" t="s">
+      <c r="K17" s="239" t="s">
         <v>154</v>
       </c>
-      <c r="L17" s="245"/>
-      <c r="M17" s="245"/>
-      <c r="N17" s="245"/>
-      <c r="O17" s="245"/>
-      <c r="P17" s="245"/>
-      <c r="Q17" s="246"/>
+      <c r="L17" s="240"/>
+      <c r="M17" s="240"/>
+      <c r="N17" s="240"/>
+      <c r="O17" s="240"/>
+      <c r="P17" s="240"/>
+      <c r="Q17" s="241"/>
       <c r="R17" s="51"/>
     </row>
     <row r="18" spans="2:21" thickBot="1">
@@ -29417,11 +29459,11 @@
       <c r="C18" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="250" t="s">
+      <c r="D18" s="245" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
+      <c r="E18" s="246"/>
+      <c r="F18" s="246"/>
       <c r="G18" s="67">
         <f>+SUM(G10:G17)</f>
         <v>209059</v>
@@ -29435,11 +29477,11 @@
         <f>+SUM(J10:J17)</f>
         <v>96363.904219609918</v>
       </c>
-      <c r="K18" s="295" t="s">
+      <c r="K18" s="290" t="s">
         <v>136</v>
       </c>
-      <c r="L18" s="296"/>
-      <c r="M18" s="297"/>
+      <c r="L18" s="291"/>
+      <c r="M18" s="292"/>
       <c r="N18" s="62">
         <f>Flujos!G25</f>
         <v>129475</v>
@@ -29457,26 +29499,26 @@
         <v>86645.635355242004</v>
       </c>
       <c r="R18" s="51"/>
-      <c r="S18" s="187"/>
+      <c r="S18" s="186"/>
       <c r="T18" s="69"/>
     </row>
     <row r="19" spans="2:21" ht="14">
       <c r="B19" s="54"/>
       <c r="C19" s="55"/>
-      <c r="D19" s="247" t="s">
+      <c r="D19" s="242" t="s">
         <v>126</v>
       </c>
-      <c r="E19" s="248"/>
-      <c r="F19" s="248"/>
-      <c r="G19" s="248"/>
-      <c r="H19" s="248"/>
-      <c r="I19" s="248"/>
-      <c r="J19" s="249"/>
-      <c r="K19" s="233" t="s">
+      <c r="E19" s="243"/>
+      <c r="F19" s="243"/>
+      <c r="G19" s="243"/>
+      <c r="H19" s="243"/>
+      <c r="I19" s="243"/>
+      <c r="J19" s="244"/>
+      <c r="K19" s="228" t="s">
         <v>119</v>
       </c>
-      <c r="L19" s="234"/>
-      <c r="M19" s="253"/>
+      <c r="L19" s="229"/>
+      <c r="M19" s="248"/>
       <c r="N19" s="117">
         <f>Flujos!G35</f>
         <v>18351</v>
@@ -29499,20 +29541,20 @@
     <row r="20" spans="2:21" ht="14">
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
-      <c r="D20" s="230" t="s">
+      <c r="D20" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="231"/>
-      <c r="F20" s="252"/>
-      <c r="G20" s="133">
+      <c r="E20" s="226"/>
+      <c r="F20" s="247"/>
+      <c r="G20" s="132">
         <f>'Mapa de Procesos'!P102</f>
         <v>104386</v>
       </c>
-      <c r="H20" s="133">
+      <c r="H20" s="132">
         <f>G20/(1-'Datos Extra'!B23)</f>
         <v>112971.86147186147</v>
       </c>
-      <c r="I20" s="132">
+      <c r="I20" s="131">
         <f>Flujos!H27</f>
         <v>0.66200000000000003</v>
       </c>
@@ -29520,11 +29562,11 @@
         <f>+I20*G20</f>
         <v>69103.532000000007</v>
       </c>
-      <c r="K20" s="230" t="s">
+      <c r="K20" s="225" t="s">
         <v>121</v>
       </c>
-      <c r="L20" s="231"/>
-      <c r="M20" s="252"/>
+      <c r="L20" s="226"/>
+      <c r="M20" s="247"/>
       <c r="N20" s="62">
         <f>Flujos!G36</f>
         <v>5360</v>
@@ -29542,16 +29584,16 @@
         <v>3240.6559999999999</v>
       </c>
       <c r="R20" s="51"/>
-      <c r="S20" s="186"/>
+      <c r="S20" s="185"/>
     </row>
     <row r="21" spans="2:21" ht="14">
       <c r="B21" s="54"/>
       <c r="C21" s="55"/>
-      <c r="D21" s="233" t="s">
+      <c r="D21" s="228" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="234"/>
-      <c r="F21" s="253"/>
+      <c r="E21" s="229"/>
+      <c r="F21" s="248"/>
       <c r="G21" s="71">
         <f>Flujos!G33</f>
         <v>0</v>
@@ -29568,11 +29610,11 @@
         <f>+I21*G21</f>
         <v>0</v>
       </c>
-      <c r="K21" s="233" t="s">
+      <c r="K21" s="228" t="s">
         <v>138</v>
       </c>
-      <c r="L21" s="234"/>
-      <c r="M21" s="253"/>
+      <c r="L21" s="229"/>
+      <c r="M21" s="248"/>
       <c r="N21" s="117">
         <f>Flujos!G57</f>
         <v>4403</v>
@@ -29581,7 +29623,7 @@
         <f>N21/(1-'Datos Extra'!B32)</f>
         <v>4426.9052885582141</v>
       </c>
-      <c r="P21" s="172">
+      <c r="P21" s="171">
         <f>Flujos!H57</f>
         <v>0.62139999999999995</v>
       </c>
@@ -29590,16 +29632,16 @@
         <v>2736.0241999999998</v>
       </c>
       <c r="R21" s="51"/>
-      <c r="S21" s="186"/>
+      <c r="S21" s="185"/>
     </row>
     <row r="22" spans="2:21" ht="14">
       <c r="B22" s="54"/>
       <c r="C22" s="55"/>
-      <c r="D22" s="230" t="s">
+      <c r="D22" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="231"/>
-      <c r="F22" s="252"/>
+      <c r="E22" s="226"/>
+      <c r="F22" s="247"/>
       <c r="G22" s="60">
         <f>Flujos!G40</f>
         <v>0</v>
@@ -29616,11 +29658,11 @@
         <f>+I22*G22</f>
         <v>0</v>
       </c>
-      <c r="K22" s="230" t="s">
+      <c r="K22" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="L22" s="231"/>
-      <c r="M22" s="252"/>
+      <c r="L22" s="226"/>
+      <c r="M22" s="247"/>
       <c r="N22" s="62">
         <f>Flujos!G37</f>
         <v>6394</v>
@@ -29638,16 +29680,16 @@
         <v>3773.0993999999996</v>
       </c>
       <c r="R22" s="51"/>
-      <c r="S22" s="186"/>
+      <c r="S22" s="185"/>
     </row>
     <row r="23" spans="2:21" thickBot="1">
       <c r="B23" s="54"/>
       <c r="C23" s="55"/>
-      <c r="D23" s="254" t="s">
+      <c r="D23" s="249" t="s">
         <v>132</v>
       </c>
-      <c r="E23" s="255"/>
-      <c r="F23" s="256"/>
+      <c r="E23" s="250"/>
+      <c r="F23" s="251"/>
       <c r="G23" s="71">
         <f>Flujos!G58</f>
         <v>127</v>
@@ -29664,11 +29706,11 @@
         <f>G23*I23</f>
         <v>84.569300000000013</v>
       </c>
-      <c r="K23" s="233" t="s">
+      <c r="K23" s="228" t="s">
         <v>123</v>
       </c>
-      <c r="L23" s="234"/>
-      <c r="M23" s="253"/>
+      <c r="L23" s="229"/>
+      <c r="M23" s="248"/>
       <c r="N23" s="117">
         <f>Flujos!G38</f>
         <v>0</v>
@@ -29691,11 +29733,11 @@
     <row r="24" spans="2:21" thickBot="1">
       <c r="B24" s="54"/>
       <c r="C24" s="55"/>
-      <c r="D24" s="250" t="s">
+      <c r="D24" s="245" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="251"/>
-      <c r="F24" s="251"/>
+      <c r="E24" s="246"/>
+      <c r="F24" s="246"/>
       <c r="G24" s="67">
         <f>+SUM(G20:G23)</f>
         <v>104513</v>
@@ -29709,11 +29751,11 @@
         <f t="shared" ref="J24" si="1">+SUM(J20:J23)</f>
         <v>69188.101300000009</v>
       </c>
-      <c r="K24" s="250" t="s">
+      <c r="K24" s="245" t="s">
         <v>125</v>
       </c>
-      <c r="L24" s="251"/>
-      <c r="M24" s="251"/>
+      <c r="L24" s="246"/>
+      <c r="M24" s="246"/>
       <c r="N24" s="67">
         <f>SUM(N18:N23)</f>
         <v>163983</v>
@@ -29732,324 +29774,324 @@
     <row r="25" spans="2:21" thickBot="1">
       <c r="B25" s="54"/>
       <c r="C25" s="55"/>
-      <c r="D25" s="237"/>
-      <c r="E25" s="237"/>
-      <c r="F25" s="237"/>
+      <c r="D25" s="232"/>
+      <c r="E25" s="232"/>
+      <c r="F25" s="232"/>
       <c r="G25" s="77"/>
       <c r="H25" s="77"/>
       <c r="I25" s="78"/>
       <c r="J25" s="79"/>
       <c r="R25" s="51"/>
-      <c r="S25" s="186"/>
+      <c r="S25" s="185"/>
     </row>
     <row r="26" spans="2:21" ht="14.5" customHeight="1">
       <c r="B26" s="54"/>
       <c r="C26" s="55"/>
-      <c r="D26" s="266" t="s">
+      <c r="D26" s="261" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="267"/>
-      <c r="F26" s="267"/>
-      <c r="G26" s="267"/>
-      <c r="H26" s="268"/>
+      <c r="E26" s="262"/>
+      <c r="F26" s="262"/>
+      <c r="G26" s="262"/>
+      <c r="H26" s="263"/>
       <c r="R26" s="80"/>
     </row>
     <row r="27" spans="2:21" thickBot="1">
       <c r="B27" s="54"/>
       <c r="C27" s="55"/>
-      <c r="D27" s="238"/>
-      <c r="E27" s="239"/>
-      <c r="F27" s="240"/>
+      <c r="D27" s="233"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="235"/>
       <c r="G27" s="89" t="s">
         <v>104</v>
       </c>
       <c r="H27" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="I27" s="189" t="s">
+      <c r="I27" s="188" t="s">
         <v>157</v>
       </c>
-      <c r="J27" s="189" t="s">
+      <c r="J27" s="188" t="s">
         <v>158</v>
       </c>
-      <c r="L27" s="177"/>
-      <c r="M27" s="177"/>
-      <c r="N27" s="177"/>
-      <c r="O27" s="177"/>
-      <c r="P27" s="177"/>
-      <c r="Q27" s="177"/>
+      <c r="L27" s="176"/>
+      <c r="M27" s="176"/>
+      <c r="N27" s="176"/>
+      <c r="O27" s="176"/>
+      <c r="P27" s="176"/>
+      <c r="Q27" s="176"/>
       <c r="R27" s="51"/>
       <c r="U27" s="81"/>
     </row>
     <row r="28" spans="2:21" ht="14">
       <c r="B28" s="54"/>
       <c r="C28" s="55"/>
-      <c r="D28" s="241" t="s">
+      <c r="D28" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="242"/>
-      <c r="F28" s="243"/>
-      <c r="G28" s="180">
+      <c r="E28" s="237"/>
+      <c r="F28" s="238"/>
+      <c r="G28" s="179">
         <f>'Datos Extra'!B1</f>
         <v>4991.0799999999981</v>
       </c>
-      <c r="H28" s="140">
+      <c r="H28" s="139">
         <f>G28*(1-'Datos Extra'!D1)</f>
         <v>4941.1691999999985</v>
       </c>
-      <c r="I28" s="190">
+      <c r="I28" s="189">
         <f>Flujos!G9</f>
         <v>-41795</v>
       </c>
-      <c r="J28" s="190">
+      <c r="J28" s="189">
         <f>'Mapa de Procesos'!L126</f>
         <v>-19153.812600000001</v>
       </c>
-      <c r="K28" s="177"/>
-      <c r="L28" s="177"/>
-      <c r="M28" s="177"/>
-      <c r="N28" s="177"/>
-      <c r="O28" s="177"/>
-      <c r="P28" s="177"/>
-      <c r="Q28" s="177"/>
+      <c r="K28" s="176"/>
+      <c r="L28" s="176"/>
+      <c r="M28" s="176"/>
+      <c r="N28" s="176"/>
+      <c r="O28" s="176"/>
+      <c r="P28" s="176"/>
+      <c r="Q28" s="176"/>
       <c r="R28" s="80"/>
       <c r="U28" s="81"/>
     </row>
     <row r="29" spans="2:21" ht="14">
       <c r="B29" s="54"/>
       <c r="C29" s="55"/>
-      <c r="D29" s="230" t="s">
+      <c r="D29" s="225" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="231"/>
-      <c r="F29" s="231"/>
-      <c r="G29" s="181">
+      <c r="E29" s="226"/>
+      <c r="F29" s="226"/>
+      <c r="G29" s="180">
         <f>'Datos Extra'!B2</f>
         <v>88872.295000000173</v>
       </c>
-      <c r="H29" s="182">
+      <c r="H29" s="181">
         <f>G29*(1-'Datos Extra'!D2)</f>
         <v>87983.572050000177</v>
       </c>
-      <c r="I29" s="190">
+      <c r="I29" s="189">
         <f>Flujos!G17</f>
         <v>791</v>
       </c>
-      <c r="J29" s="190">
+      <c r="J29" s="189">
         <f>'Mapa de Procesos'!L127</f>
         <v>465.64825059536003</v>
       </c>
-      <c r="K29" s="177"/>
-      <c r="L29" s="177"/>
-      <c r="M29" s="177" t="s">
+      <c r="K29" s="176"/>
+      <c r="L29" s="176"/>
+      <c r="M29" s="176" t="s">
         <v>71</v>
       </c>
-      <c r="N29" s="177" t="s">
+      <c r="N29" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="O29" s="177" t="s">
+      <c r="O29" s="176" t="s">
         <v>155</v>
       </c>
-      <c r="P29" s="177" t="s">
+      <c r="P29" s="176" t="s">
         <v>156</v>
       </c>
-      <c r="Q29" s="177"/>
+      <c r="Q29" s="176"/>
       <c r="R29" s="51"/>
       <c r="U29" s="81"/>
     </row>
     <row r="30" spans="2:21" ht="14">
       <c r="B30" s="54"/>
       <c r="C30" s="55"/>
-      <c r="D30" s="230" t="s">
+      <c r="D30" s="225" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="231"/>
-      <c r="F30" s="231"/>
-      <c r="G30" s="181">
+      <c r="E30" s="226"/>
+      <c r="F30" s="226"/>
+      <c r="G30" s="180">
         <f>'Datos Extra'!B3</f>
         <v>2985</v>
       </c>
-      <c r="H30" s="182">
+      <c r="H30" s="181">
         <f>G30*(1-'Datos Extra'!D3)</f>
         <v>2734.0093815092168</v>
       </c>
-      <c r="I30" s="190">
+      <c r="I30" s="189">
         <f>Flujos!G21</f>
         <v>3316</v>
       </c>
-      <c r="J30" s="190">
+      <c r="J30" s="189">
         <f>'Mapa de Procesos'!L129</f>
         <v>3124.4397465495604</v>
       </c>
-      <c r="K30" s="177"/>
-      <c r="L30" s="177" t="s">
+      <c r="K30" s="176"/>
+      <c r="L30" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="M30" s="176">
+      <c r="M30" s="175">
         <f>G18+N19+N20+N21+N22+N23</f>
         <v>243567</v>
       </c>
-      <c r="N30" s="176">
+      <c r="N30" s="175">
         <f>G20+G21+G22+N16+G23</f>
         <v>221785</v>
       </c>
-      <c r="O30" s="178">
+      <c r="O30" s="177">
         <f>I35</f>
         <v>21782</v>
       </c>
-      <c r="P30" s="176">
+      <c r="P30" s="175">
         <f>M30-N30-O30</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="177"/>
+      <c r="Q30" s="176"/>
       <c r="R30" s="51"/>
       <c r="U30" s="81"/>
     </row>
     <row r="31" spans="2:21" ht="14">
       <c r="B31" s="54"/>
       <c r="C31" s="55"/>
-      <c r="D31" s="230" t="s">
+      <c r="D31" s="225" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="231"/>
-      <c r="F31" s="231"/>
-      <c r="G31" s="181">
+      <c r="E31" s="226"/>
+      <c r="F31" s="226"/>
+      <c r="G31" s="180">
         <f>'Datos Extra'!B4</f>
         <v>0</v>
       </c>
-      <c r="H31" s="182">
+      <c r="H31" s="181">
         <f>G31*(1-'Datos Extra'!D4)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="190">
+      <c r="I31" s="189">
         <f>Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="J31" s="190">
+      <c r="J31" s="189">
         <f>'Mapa de Procesos'!L130</f>
         <v>0</v>
       </c>
-      <c r="K31" s="177"/>
-      <c r="L31" s="177" t="s">
+      <c r="K31" s="176"/>
+      <c r="L31" s="176" t="s">
         <v>34</v>
       </c>
-      <c r="M31" s="176">
+      <c r="M31" s="175">
         <f>J18+Q19+Q20+Q21+Q22+Q23</f>
         <v>117522.50051960992</v>
       </c>
-      <c r="N31" s="176">
+      <c r="N31" s="175">
         <f>Q16+J20+J21+J22+J23</f>
         <v>94470.094767147384</v>
       </c>
-      <c r="O31" s="179">
+      <c r="O31" s="178">
         <f>J35</f>
         <v>23052.405752154889</v>
       </c>
-      <c r="P31" s="176">
+      <c r="P31" s="175">
         <f>M31-N31-O31</f>
         <v>3.076493158005178E-7</v>
       </c>
-      <c r="Q31" s="177"/>
+      <c r="Q31" s="176"/>
       <c r="R31" s="80"/>
       <c r="U31" s="81"/>
     </row>
     <row r="32" spans="2:21" ht="14">
       <c r="B32" s="54"/>
       <c r="C32" s="55"/>
-      <c r="D32" s="233" t="s">
+      <c r="D32" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="234"/>
-      <c r="F32" s="234"/>
-      <c r="G32" s="181">
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
+      <c r="G32" s="180">
         <f>'Datos Extra'!B5</f>
         <v>144052.08999999997</v>
       </c>
-      <c r="H32" s="182">
+      <c r="H32" s="181">
         <f>G32*(1-'Datos Extra'!D5)</f>
         <v>131639.42123662311</v>
       </c>
-      <c r="I32" s="190">
+      <c r="I32" s="189">
         <f>Flujos!G26</f>
         <v>25089</v>
       </c>
-      <c r="J32" s="190">
+      <c r="J32" s="189">
         <f>'Mapa de Procesos'!L136</f>
         <v>17542.103354999999</v>
       </c>
-      <c r="K32" s="177"/>
-      <c r="L32" s="176"/>
-      <c r="M32" s="177"/>
-      <c r="N32" s="177"/>
-      <c r="O32" s="177"/>
-      <c r="P32" s="177"/>
-      <c r="Q32" s="177"/>
+      <c r="K32" s="176"/>
+      <c r="L32" s="175"/>
+      <c r="M32" s="176"/>
+      <c r="N32" s="176"/>
+      <c r="O32" s="176"/>
+      <c r="P32" s="176"/>
+      <c r="Q32" s="176"/>
       <c r="R32" s="51"/>
       <c r="U32" s="81"/>
     </row>
     <row r="33" spans="2:21" ht="14">
       <c r="B33" s="54"/>
       <c r="C33" s="55"/>
-      <c r="D33" s="233" t="s">
+      <c r="D33" s="228" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="181">
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
+      <c r="G33" s="180">
         <f>'Datos Extra'!B6</f>
         <v>87099.612182495111</v>
       </c>
-      <c r="H33" s="182">
+      <c r="H33" s="181">
         <f>G33*(1-'Datos Extra'!D6)</f>
         <v>86664.114121582636</v>
       </c>
-      <c r="I33" s="190">
+      <c r="I33" s="189">
         <f>Flujos!G34</f>
         <v>27987</v>
       </c>
-      <c r="J33" s="190">
+      <c r="J33" s="189">
         <f>'Mapa de Procesos'!L137</f>
         <v>17300.927600009971</v>
       </c>
-      <c r="L33" s="188"/>
-      <c r="M33" s="188"/>
-      <c r="N33" s="188"/>
-      <c r="O33" s="188"/>
-      <c r="P33" s="188"/>
-      <c r="Q33" s="185"/>
+      <c r="L33" s="187"/>
+      <c r="M33" s="187"/>
+      <c r="N33" s="187"/>
+      <c r="O33" s="187"/>
+      <c r="P33" s="187"/>
+      <c r="Q33" s="184"/>
       <c r="R33" s="80"/>
       <c r="U33" s="81"/>
     </row>
     <row r="34" spans="2:21" thickBot="1">
       <c r="B34" s="54"/>
       <c r="C34" s="55"/>
-      <c r="D34" s="235" t="s">
+      <c r="D34" s="230" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="236"/>
-      <c r="F34" s="236"/>
-      <c r="G34" s="183">
+      <c r="E34" s="231"/>
+      <c r="F34" s="231"/>
+      <c r="G34" s="182">
         <f>'Datos Extra'!B7</f>
         <v>27059.240058898926</v>
       </c>
-      <c r="H34" s="184">
+      <c r="H34" s="183">
         <f>G34*(1-'Datos Extra'!D7)</f>
         <v>26923.943858604431</v>
       </c>
-      <c r="I34" s="190">
+      <c r="I34" s="189">
         <f>Flujos!G39</f>
         <v>6394</v>
       </c>
-      <c r="J34" s="190">
+      <c r="J34" s="189">
         <f>'Mapa de Procesos'!L138</f>
         <v>3773.0993999999996</v>
       </c>
-      <c r="L34" s="185"/>
-      <c r="M34" s="185"/>
-      <c r="N34" s="185"/>
-      <c r="O34" s="185"/>
-      <c r="P34" s="185"/>
-      <c r="Q34" s="185"/>
+      <c r="L34" s="184"/>
+      <c r="M34" s="184"/>
+      <c r="N34" s="184"/>
+      <c r="O34" s="184"/>
+      <c r="P34" s="184"/>
+      <c r="Q34" s="184"/>
       <c r="R34" s="51"/>
       <c r="U34" s="81"/>
     </row>
@@ -30061,11 +30103,11 @@
       <c r="F35" s="83"/>
       <c r="G35" s="83"/>
       <c r="H35" s="83"/>
-      <c r="I35" s="191">
+      <c r="I35" s="190">
         <f>SUM(I28:I34)</f>
         <v>21782</v>
       </c>
-      <c r="J35" s="191">
+      <c r="J35" s="190">
         <f>SUM(J28:J34)</f>
         <v>23052.405752154889</v>
       </c>
@@ -30079,20 +30121,20 @@
       <c r="R35" s="84"/>
     </row>
     <row r="38" spans="2:21" ht="15" customHeight="1">
-      <c r="E38" s="128"/>
-      <c r="F38" s="128"/>
-      <c r="G38" s="128"/>
-      <c r="H38" s="128"/>
-      <c r="I38" s="127"/>
-      <c r="J38" s="127"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="126"/>
+      <c r="J38" s="126"/>
     </row>
     <row r="39" spans="2:21" ht="14">
-      <c r="E39" s="128"/>
-      <c r="F39" s="128"/>
-      <c r="G39" s="128"/>
-      <c r="H39" s="128"/>
-      <c r="I39" s="127"/>
-      <c r="J39" s="127"/>
+      <c r="E39" s="127"/>
+      <c r="F39" s="127"/>
+      <c r="G39" s="127"/>
+      <c r="H39" s="127"/>
+      <c r="I39" s="126"/>
+      <c r="J39" s="126"/>
     </row>
     <row r="40" spans="2:21" ht="14">
       <c r="E40" s="86"/>
@@ -30104,12 +30146,12 @@
       <c r="K40" s="86"/>
     </row>
     <row r="41" spans="2:21" ht="15" customHeight="1">
-      <c r="E41" s="232"/>
-      <c r="F41" s="232"/>
-      <c r="G41" s="232"/>
-      <c r="H41" s="131"/>
+      <c r="E41" s="227"/>
+      <c r="F41" s="227"/>
+      <c r="G41" s="227"/>
+      <c r="H41" s="130"/>
       <c r="I41" s="88"/>
-      <c r="J41" s="126"/>
+      <c r="J41" s="125"/>
       <c r="K41" s="87"/>
     </row>
   </sheetData>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7592E4B-E368-A142-8097-971D21686C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{69A663D0-26C1-F440-89E4-ADA305907D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="27040" windowHeight="16880" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5400" yWindow="940" windowWidth="27040" windowHeight="16880" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="186">
   <si>
     <t>%FeT</t>
   </si>
@@ -885,9 +885,6 @@
     <t>Recep ALGARROBO</t>
   </si>
   <si>
-    <t>Recep PLEITO</t>
-  </si>
-  <si>
     <t>Recep SF CRISTALES</t>
   </si>
   <si>
@@ -897,13 +894,13 @@
     <t>Recep SF ALGARROBO</t>
   </si>
   <si>
-    <t>Recep GR ALGARROBO</t>
+    <t>Cristales</t>
   </si>
   <si>
-    <t>Recep GR CRISTALES</t>
+    <t>Caro</t>
   </si>
   <si>
-    <t>Recep GR PLEITO</t>
+    <t>Algarrobo</t>
   </si>
 </sst>
 </file>
@@ -16504,11 +16501,238 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>Recepción Infiernillo</a:t>
+            <a:t>Recepción APC</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>510457</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>146114</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>46464</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>15489</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="2" name="Conector: angular 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CEC2146-827F-804E-AD82-1DA7C448E4DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:endCxn id="19" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="10840823" y="16145016"/>
+          <a:ext cx="4507592" cy="984497"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>709321</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>128149</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>402683</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>108415</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="79" name="Conector: angular 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{317567C4-C520-D54D-9D77-0FCAAA0CA77D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="11039687" y="16127051"/>
+          <a:ext cx="5547752" cy="166120"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>510457</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>146113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>449147</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>154878</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="119" name="Conector: angular 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FFD0B59-1B61-294E-AE9C-E6647B1D9314}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:endCxn id="19" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="10840823" y="16145015"/>
+          <a:ext cx="4027470" cy="566326"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector2">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>771913</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>43985</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>223549</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>108267</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="124" name="Conector: angular 105">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB0F477B-8F38-CF44-A379-9E66D8F826E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:endCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5278864" y="12139961"/>
+          <a:ext cx="5275051" cy="1365257"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 60276"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -24579,6 +24803,13 @@
     </row>
     <row r="65" spans="2:19">
       <c r="B65" s="7"/>
+      <c r="F65" s="31">
+        <f>I112</f>
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>183</v>
+      </c>
       <c r="L65" s="27">
         <f>Flujos!G25</f>
         <v>129475</v>
@@ -24591,6 +24822,13 @@
     </row>
     <row r="66" spans="2:19">
       <c r="B66" s="7"/>
+      <c r="F66" s="31">
+        <f>I113</f>
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>184</v>
+      </c>
       <c r="L66" s="29">
         <f>Flujos!H25</f>
         <v>0.66920745592000008</v>
@@ -24599,6 +24837,13 @@
     </row>
     <row r="67" spans="2:19">
       <c r="B67" s="7"/>
+      <c r="F67" s="31">
+        <f>I114</f>
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>185</v>
+      </c>
       <c r="L67" s="30">
         <f>L66*L65</f>
         <v>86645.635355242004</v>
@@ -24827,6 +25072,9 @@
         <f>+Utilidad!K98</f>
         <v>0</v>
       </c>
+      <c r="Q87" t="s">
+        <v>172</v>
+      </c>
       <c r="S87" s="24"/>
     </row>
     <row r="88" spans="2:19">
@@ -24851,6 +25099,9 @@
         <f>+Utilidad!J97</f>
         <v>6394</v>
       </c>
+      <c r="R90" t="s">
+        <v>173</v>
+      </c>
       <c r="S90" s="24"/>
     </row>
     <row r="91" spans="2:19">
@@ -24871,6 +25122,9 @@
     </row>
     <row r="93" spans="2:19">
       <c r="B93" s="7"/>
+      <c r="P93" t="s">
+        <v>174</v>
+      </c>
       <c r="S93" s="24"/>
     </row>
     <row r="94" spans="2:19" ht="16" thickBot="1">
@@ -24888,7 +25142,7 @@
       <c r="M94" s="42"/>
       <c r="N94" s="42"/>
       <c r="O94" s="42"/>
-      <c r="P94" s="42"/>
+      <c r="P94" s="43"/>
       <c r="Q94" s="42"/>
       <c r="R94" s="42"/>
       <c r="S94" s="43"/>
@@ -25287,7 +25541,7 @@
     </row>
     <row r="112" spans="7:16">
       <c r="G112" s="211" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H112" s="212" t="s">
         <v>169</v>
@@ -25306,7 +25560,7 @@
     </row>
     <row r="113" spans="7:16">
       <c r="G113" s="211" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H113" s="212" t="s">
         <v>170</v>
@@ -25325,7 +25579,7 @@
     </row>
     <row r="114" spans="7:16">
       <c r="G114" s="211" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H114" s="212" t="s">
         <v>171</v>
@@ -25343,16 +25597,9 @@
       <c r="P114" s="10"/>
     </row>
     <row r="115" spans="7:16">
-      <c r="G115" s="211" t="s">
-        <v>184</v>
-      </c>
-      <c r="H115" s="212" t="s">
-        <v>172</v>
-      </c>
-      <c r="I115" s="21">
-        <f>Flujos!G62</f>
-        <v>0</v>
-      </c>
+      <c r="G115" s="211"/>
+      <c r="H115" s="212"/>
+      <c r="I115" s="21"/>
       <c r="J115" s="208"/>
       <c r="K115" s="208"/>
       <c r="L115" s="10"/>
@@ -25362,16 +25609,9 @@
       <c r="P115" s="10"/>
     </row>
     <row r="116" spans="7:16">
-      <c r="G116" s="211" t="s">
-        <v>185</v>
-      </c>
-      <c r="H116" s="212" t="s">
-        <v>173</v>
-      </c>
-      <c r="I116" s="21">
-        <f>Flujos!G63</f>
-        <v>0</v>
-      </c>
+      <c r="G116" s="211"/>
+      <c r="H116" s="212"/>
+      <c r="I116" s="21"/>
       <c r="J116" s="208"/>
       <c r="K116" s="208"/>
       <c r="L116" s="10"/>
@@ -25381,16 +25621,9 @@
       <c r="P116" s="10"/>
     </row>
     <row r="117" spans="7:16">
-      <c r="G117" s="211" t="s">
-        <v>186</v>
-      </c>
-      <c r="H117" s="212" t="s">
-        <v>174</v>
-      </c>
-      <c r="I117" s="21">
-        <f>Flujos!G64</f>
-        <v>0</v>
-      </c>
+      <c r="G117" s="211"/>
+      <c r="H117" s="212"/>
+      <c r="I117" s="21"/>
       <c r="J117" s="208"/>
       <c r="K117" s="208"/>
       <c r="L117" s="10"/>
@@ -25900,14 +26133,9 @@
       <c r="P143" s="10"/>
     </row>
     <row r="144" spans="7:16">
-      <c r="G144" s="211" t="s">
-        <v>179</v>
-      </c>
+      <c r="G144" s="211"/>
       <c r="H144" s="212"/>
-      <c r="I144" s="21">
-        <f>Flujos!G62*Flujos!H62</f>
-        <v>0</v>
-      </c>
+      <c r="I144" s="21"/>
       <c r="J144" s="208"/>
       <c r="K144" s="208"/>
       <c r="L144" s="10"/>
@@ -25917,14 +26145,9 @@
       <c r="P144" s="10"/>
     </row>
     <row r="145" spans="7:16">
-      <c r="G145" s="211" t="s">
-        <v>177</v>
-      </c>
+      <c r="G145" s="211"/>
       <c r="H145" s="212"/>
-      <c r="I145" s="21">
-        <f>Flujos!G63*Flujos!H63</f>
-        <v>0</v>
-      </c>
+      <c r="I145" s="21"/>
       <c r="J145" s="208"/>
       <c r="K145" s="208"/>
       <c r="L145" s="10"/>
@@ -25934,14 +26157,9 @@
       <c r="P145" s="10"/>
     </row>
     <row r="146" spans="7:16">
-      <c r="G146" s="211" t="s">
-        <v>180</v>
-      </c>
+      <c r="G146" s="211"/>
       <c r="H146" s="212"/>
-      <c r="I146" s="21">
-        <f>Flujos!G64*Flujos!H64</f>
-        <v>0</v>
-      </c>
+      <c r="I146" s="21"/>
       <c r="J146" s="208"/>
       <c r="K146" s="208"/>
       <c r="L146" s="10"/>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{69A663D0-26C1-F440-89E4-ADA305907D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E70EC03-C2A3-DB40-B6EB-E34454619680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5400" yWindow="940" windowWidth="27040" windowHeight="16880" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="185">
   <si>
     <t>%FeT</t>
   </si>
@@ -826,9 +826,6 @@
   </si>
   <si>
     <t>Ventas locales</t>
-  </si>
-  <si>
-    <t>Recep Infiernillo</t>
   </si>
   <si>
     <t>Stock Pellet Feed Guayacan</t>
@@ -21082,7 +21079,7 @@
     </row>
     <row r="5" spans="1:4" ht="24">
       <c r="A5" s="148" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B5" s="149">
         <v>144052.08999999997</v>
@@ -21096,7 +21093,7 @@
     </row>
     <row r="6" spans="1:4" ht="24">
       <c r="A6" s="148" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" s="149">
         <v>87099.612182495111</v>
@@ -21110,7 +21107,7 @@
     </row>
     <row r="7" spans="1:4" ht="24">
       <c r="A7" s="148" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B7" s="150">
         <v>27059.240058898926</v>
@@ -21138,7 +21135,7 @@
     </row>
     <row r="9" spans="1:4" ht="24">
       <c r="A9" s="148" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9" s="149">
         <v>132791.454</v>
@@ -21222,7 +21219,7 @@
     </row>
     <row r="15" spans="1:4" ht="24">
       <c r="A15" s="148" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B15" s="150">
         <v>152453.07</v>
@@ -21264,7 +21261,7 @@
     </row>
     <row r="18" spans="1:4" ht="24">
       <c r="A18" s="143" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B18" s="152">
         <v>0.01</v>
@@ -21278,7 +21275,7 @@
     </row>
     <row r="19" spans="1:4" ht="24">
       <c r="A19" s="143" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B19" s="152">
         <v>0</v>
@@ -21348,7 +21345,7 @@
     </row>
     <row r="24" spans="1:4" ht="24">
       <c r="A24" s="143" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B24" s="152">
         <v>0</v>
@@ -21404,7 +21401,7 @@
     </row>
     <row r="28" spans="1:4" ht="24">
       <c r="A28" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28" s="152">
         <v>8.199999999999999E-2</v>
@@ -23758,7 +23755,7 @@
     </row>
     <row r="57" spans="2:14" ht="19">
       <c r="B57" s="105" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="106">
         <f>Utilidad!A54</f>
@@ -23838,7 +23835,7 @@
     </row>
     <row r="59" spans="2:14" ht="19">
       <c r="B59" s="105" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C59" s="106">
         <f>Utilidad!A56</f>
@@ -23849,7 +23846,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="105" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G59" s="294">
         <f>Utilidad!B56</f>
@@ -23878,7 +23875,7 @@
     </row>
     <row r="60" spans="2:14" ht="19">
       <c r="B60" s="105" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C60" s="106">
         <f>Utilidad!A57</f>
@@ -23889,7 +23886,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="105" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G60" s="294">
         <f>Utilidad!B57</f>
@@ -23918,7 +23915,7 @@
     </row>
     <row r="61" spans="2:14" ht="19">
       <c r="B61" s="105" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C61" s="106">
         <f>Utilidad!A58</f>
@@ -23929,7 +23926,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="105" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G61" s="294">
         <f>Utilidad!B58</f>
@@ -23958,7 +23955,7 @@
     </row>
     <row r="62" spans="2:14" ht="19">
       <c r="B62" s="105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C62" s="106">
         <f>Utilidad!A59</f>
@@ -23969,7 +23966,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G62" s="294">
         <f>Utilidad!B59</f>
@@ -23998,7 +23995,7 @@
     </row>
     <row r="63" spans="2:14" ht="19">
       <c r="B63" s="105" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C63" s="106">
         <f>Utilidad!A60</f>
@@ -24009,7 +24006,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="105" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G63" s="294">
         <f>Utilidad!B60</f>
@@ -24038,7 +24035,7 @@
     </row>
     <row r="64" spans="2:14" ht="19">
       <c r="B64" s="105" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C64" s="106">
         <f>Utilidad!A61</f>
@@ -24049,7 +24046,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="105" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G64" s="294">
         <f>Utilidad!B61</f>
@@ -24808,7 +24805,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L65" s="27">
         <f>Flujos!G25</f>
@@ -24827,7 +24824,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L66" s="29">
         <f>Flujos!H25</f>
@@ -24842,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L67" s="30">
         <f>L66*L65</f>
@@ -25073,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="Q87" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S87" s="24"/>
     </row>
@@ -25100,7 +25097,7 @@
         <v>6394</v>
       </c>
       <c r="R90" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S90" s="24"/>
     </row>
@@ -25123,7 +25120,7 @@
     <row r="93" spans="2:19">
       <c r="B93" s="7"/>
       <c r="P93" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S93" s="24"/>
     </row>
@@ -25524,7 +25521,7 @@
     </row>
     <row r="111" spans="7:16" ht="26" customHeight="1">
       <c r="G111" s="211" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H111" s="212"/>
       <c r="I111" s="21">
@@ -25541,10 +25538,10 @@
     </row>
     <row r="112" spans="7:16">
       <c r="G112" s="211" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H112" s="212" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I112" s="21">
         <f>Flujos!G59</f>
@@ -25560,10 +25557,10 @@
     </row>
     <row r="113" spans="7:16">
       <c r="G113" s="211" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H113" s="212" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I113" s="21">
         <f>Flujos!G60</f>
@@ -25579,10 +25576,10 @@
     </row>
     <row r="114" spans="7:16">
       <c r="G114" s="211" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H114" s="212" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I114" s="21">
         <f>Flujos!G61</f>
@@ -26065,10 +26062,10 @@
       <c r="P139" s="10"/>
     </row>
     <row r="140" spans="7:16">
-      <c r="G140" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="H140" s="20"/>
+      <c r="G140" s="211" t="s">
+        <v>175</v>
+      </c>
+      <c r="H140" s="212"/>
       <c r="I140" s="21">
         <f>K84</f>
         <v>2736.0241999999998</v>
@@ -26083,7 +26080,7 @@
     </row>
     <row r="141" spans="7:16">
       <c r="G141" s="211" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H141" s="212"/>
       <c r="I141" s="21">
@@ -26100,7 +26097,7 @@
     </row>
     <row r="142" spans="7:16">
       <c r="G142" s="211" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H142" s="212"/>
       <c r="I142" s="21">
@@ -26117,7 +26114,7 @@
     </row>
     <row r="143" spans="7:16">
       <c r="G143" s="211" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H143" s="212"/>
       <c r="I143" s="21">
@@ -26223,10 +26220,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="88">
+  <mergeCells count="89">
     <mergeCell ref="G147:H147"/>
     <mergeCell ref="J147:K147"/>
     <mergeCell ref="M147:O147"/>
+    <mergeCell ref="G140:H140"/>
     <mergeCell ref="G145:H145"/>
     <mergeCell ref="J145:K145"/>
     <mergeCell ref="M145:O145"/>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Documents/GitHub/minera/public/Export/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5E2D9B-4E96-2E4A-9831-C51796360017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC059E9-FAB9-D846-9850-539FFEB7BA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="702" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="206">
   <si>
     <t>%FeT</t>
   </si>
@@ -547,12 +547,6 @@
   </si>
   <si>
     <t>De  nodo Alim Otros Materiales  + Emergencia a S Preconcentrado</t>
-  </si>
-  <si>
-    <t>Valores Calculados</t>
-  </si>
-  <si>
-    <t>TMF Fe</t>
   </si>
   <si>
     <t>BALANCE GLOBAL MASA</t>
@@ -917,6 +911,57 @@
   <si>
     <t>Preconcentrado Ventas</t>
   </si>
+  <si>
+    <t>Prec Ventas</t>
+  </si>
+  <si>
+    <t>Recep Prec Ventas</t>
+  </si>
+  <si>
+    <t>Sinter Feed Dorado (camiones)</t>
+  </si>
+  <si>
+    <t>Sinter Feed Santa Fe (camiones)</t>
+  </si>
+  <si>
+    <t>SF El Dorado</t>
+  </si>
+  <si>
+    <t>SF Santa Fe</t>
+  </si>
+  <si>
+    <t>Embarque Preconcentrado ventas</t>
+  </si>
+  <si>
+    <t>Delta Preconcentrado Ventas</t>
+  </si>
+  <si>
+    <t>Resguardo</t>
+  </si>
+  <si>
+    <t>Stock Preconcentrado Ventas</t>
+  </si>
+  <si>
+    <t>Sinter El Dorado (camiones)</t>
+  </si>
+  <si>
+    <t>Sinter Santa Fe (camiones)</t>
+  </si>
+  <si>
+    <t>Rec EL Dorado</t>
+  </si>
+  <si>
+    <t>Rec Santa Fe</t>
+  </si>
+  <si>
+    <t>Rec Rsguardo</t>
+  </si>
+  <si>
+    <t>Stcck Prec Ventas</t>
+  </si>
+  <si>
+    <t>Embarque Prec Ventas</t>
+  </si>
 </sst>
 </file>
 
@@ -931,7 +976,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
     <numFmt numFmtId="169" formatCode="#,##0.0000000_ ;\-#,##0.0000000\ "/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1187,16 +1232,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF44546A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1329,14 +1366,8 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0CECE"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="48">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1447,19 +1478,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1846,36 +1864,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1943,6 +1937,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1953,7 +1958,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1964,9 +1969,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2004,9 +2009,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2052,38 +2057,38 @@
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="14" fillId="8" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2101,10 +2106,10 @@
     <xf numFmtId="9" fontId="17" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="38" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
@@ -2130,12 +2135,12 @@
     <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="18" fillId="3" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="3" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -2147,10 +2152,10 @@
     <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2174,7 +2179,7 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2215,7 +2220,7 @@
     <xf numFmtId="49" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2239,7 +2244,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
@@ -2321,7 +2326,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="3" fontId="31" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="31" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2330,10 +2335,10 @@
     <xf numFmtId="3" fontId="17" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -2346,7 +2351,7 @@
     <xf numFmtId="3" fontId="34" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2358,7 +2363,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2368,8 +2373,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="35" fillId="17" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="35" fillId="17" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2391,19 +2396,19 @@
     <xf numFmtId="10" fontId="17" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2412,13 +2417,12 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="35" fillId="19" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="35" fillId="20" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="35" fillId="22" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="35" fillId="19" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="35" fillId="20" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="35" fillId="22" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2438,6 +2442,36 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2448,13 +2482,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2468,82 +2502,157 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="45" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="46" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="47" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="36" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="37" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2552,16 +2661,16 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2570,7 +2679,7 @@
     <xf numFmtId="49" fontId="16" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2579,125 +2688,29 @@
     <xf numFmtId="14" fontId="16" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="16" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="16" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="39" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -18663,14 +18676,12 @@
         <v>0</v>
       </c>
       <c r="F60" s="108"/>
-      <c r="J60" s="209" t="s">
-        <v>68</v>
-      </c>
-      <c r="K60" s="209"/>
-      <c r="L60" s="209"/>
+      <c r="J60" s="208"/>
+      <c r="K60" s="208"/>
+      <c r="L60" s="208"/>
       <c r="M60" s="112"/>
-      <c r="N60" s="210"/>
-      <c r="O60" s="210"/>
+      <c r="N60" s="209"/>
+      <c r="O60" s="209"/>
       <c r="R60" s="94"/>
       <c r="AD60" s="5"/>
       <c r="AE60" s="3"/>
@@ -18693,15 +18704,9 @@
         <v>0</v>
       </c>
       <c r="F61" s="108"/>
-      <c r="J61" s="125" t="s">
-        <v>1</v>
-      </c>
-      <c r="K61" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="L61" s="125" t="s">
-        <v>69</v>
-      </c>
+      <c r="J61" s="125"/>
+      <c r="K61" s="125"/>
+      <c r="L61" s="125"/>
       <c r="M61" s="112"/>
       <c r="N61" s="93"/>
       <c r="O61" s="93"/>
@@ -18720,21 +18725,9 @@
       <c r="D62" s="108"/>
       <c r="E62" s="108"/>
       <c r="F62" s="108"/>
-      <c r="I62" t="s">
-        <v>14</v>
-      </c>
-      <c r="J62" s="123">
-        <f>B1</f>
-        <v>150420</v>
-      </c>
-      <c r="K62" s="127">
-        <f>IF(D1&gt;1,D1/100,D1)</f>
-        <v>0.23879999999999998</v>
-      </c>
-      <c r="L62" s="126">
-        <f>+J62*K62</f>
-        <v>35920.295999999995</v>
-      </c>
+      <c r="J62" s="123"/>
+      <c r="K62" s="127"/>
+      <c r="L62" s="126"/>
       <c r="M62" s="112"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
@@ -18755,21 +18748,9 @@
       <c r="D63" s="108"/>
       <c r="E63" s="108"/>
       <c r="F63" s="108"/>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" s="123">
-        <f t="shared" ref="J63:J108" si="0">B2</f>
-        <v>0</v>
-      </c>
-      <c r="K63" s="127">
-        <f t="shared" ref="K63:K108" si="1">IF(D2&gt;1,D2/100,D2)</f>
-        <v>0</v>
-      </c>
-      <c r="L63" s="126">
-        <f t="shared" ref="L63:L108" si="2">+J63*K63</f>
-        <v>0</v>
-      </c>
+      <c r="J63" s="123"/>
+      <c r="K63" s="127"/>
+      <c r="L63" s="126"/>
       <c r="M63" s="112"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
@@ -18790,21 +18771,9 @@
       <c r="D64" s="108"/>
       <c r="E64" s="108"/>
       <c r="F64" s="108"/>
-      <c r="I64" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="123">
-        <f t="shared" si="0"/>
-        <v>60303</v>
-      </c>
-      <c r="K64" s="127">
-        <f t="shared" si="1"/>
-        <v>0.13205</v>
-      </c>
-      <c r="L64" s="126">
-        <f t="shared" si="2"/>
-        <v>7963.0111500000003</v>
-      </c>
+      <c r="J64" s="123"/>
+      <c r="K64" s="127"/>
+      <c r="L64" s="126"/>
       <c r="M64" s="112"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
@@ -18827,21 +18796,10 @@
       <c r="F65" s="108"/>
       <c r="G65" s="152"/>
       <c r="H65" s="153"/>
-      <c r="I65" s="123" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="123">
-        <f t="shared" si="0"/>
-        <v>90117</v>
-      </c>
-      <c r="K65" s="127">
-        <f t="shared" si="1"/>
-        <v>0.31023319518000003</v>
-      </c>
-      <c r="L65" s="126">
-        <f t="shared" si="2"/>
-        <v>27957.284850036063</v>
-      </c>
+      <c r="I65" s="123"/>
+      <c r="J65" s="123"/>
+      <c r="K65" s="127"/>
+      <c r="L65" s="126"/>
       <c r="M65" s="112"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
@@ -18864,21 +18822,10 @@
       <c r="F66" s="108"/>
       <c r="G66" s="152"/>
       <c r="H66" s="153"/>
-      <c r="I66" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="123">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K66" s="127">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L66" s="126">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="I66" s="123"/>
+      <c r="J66" s="123"/>
+      <c r="K66" s="127"/>
+      <c r="L66" s="126"/>
       <c r="M66" s="112"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
@@ -18901,21 +18848,10 @@
       <c r="F67" s="111"/>
       <c r="G67" s="152"/>
       <c r="H67" s="153"/>
-      <c r="I67" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="J67" s="123">
-        <f t="shared" si="0"/>
-        <v>-26556</v>
-      </c>
-      <c r="K67" s="127">
-        <f t="shared" si="1"/>
-        <v>0.35595079067000002</v>
-      </c>
-      <c r="L67" s="126">
-        <f t="shared" si="2"/>
-        <v>-9452.6291970325201</v>
-      </c>
+      <c r="I67" s="123"/>
+      <c r="J67" s="123"/>
+      <c r="K67" s="127"/>
+      <c r="L67" s="126"/>
       <c r="M67" s="112"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
@@ -18938,21 +18874,10 @@
       <c r="F68" s="108"/>
       <c r="G68" s="152"/>
       <c r="H68" s="153"/>
-      <c r="I68" s="123" t="s">
-        <v>20</v>
-      </c>
-      <c r="J68" s="123">
-        <f t="shared" si="0"/>
-        <v>116673</v>
-      </c>
-      <c r="K68" s="127">
-        <f t="shared" si="1"/>
-        <v>0.32063899999999995</v>
-      </c>
-      <c r="L68" s="126">
-        <f t="shared" si="2"/>
-        <v>37409.914046999991</v>
-      </c>
+      <c r="I68" s="123"/>
+      <c r="J68" s="123"/>
+      <c r="K68" s="127"/>
+      <c r="L68" s="126"/>
       <c r="M68" s="112"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
@@ -18975,21 +18900,10 @@
       <c r="F69" s="108"/>
       <c r="G69" s="152"/>
       <c r="H69" s="153"/>
-      <c r="I69" s="123" t="s">
-        <v>21</v>
-      </c>
-      <c r="J69" s="123">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="127">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L69" s="126">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="I69" s="123"/>
+      <c r="J69" s="123"/>
+      <c r="K69" s="127"/>
+      <c r="L69" s="126"/>
       <c r="M69" s="112"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
@@ -19012,21 +18926,10 @@
       <c r="F70" s="148"/>
       <c r="G70" s="152"/>
       <c r="H70" s="153"/>
-      <c r="I70" s="123" t="s">
-        <v>22</v>
-      </c>
-      <c r="J70" s="123">
-        <f t="shared" si="0"/>
-        <v>20626.123299999999</v>
-      </c>
-      <c r="K70" s="127">
-        <f t="shared" si="1"/>
-        <v>0.19247</v>
-      </c>
-      <c r="L70" s="126">
-        <f t="shared" si="2"/>
-        <v>3969.9099515509997</v>
-      </c>
+      <c r="I70" s="123"/>
+      <c r="J70" s="123"/>
+      <c r="K70" s="127"/>
+      <c r="L70" s="126"/>
       <c r="M70" s="112"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
@@ -19053,15 +18956,15 @@
         <v>23</v>
       </c>
       <c r="J71" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J71:J108" si="0">B10</f>
         <v>14883.876700000001</v>
       </c>
       <c r="K71" s="127">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K71:K108" si="1">IF(D10&gt;1,D10/100,D10)</f>
         <v>0.10858499999999999</v>
       </c>
       <c r="L71" s="126">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L71:L108" si="2">+J71*K71</f>
         <v>1616.1657514694998</v>
       </c>
       <c r="M71" s="112"/>
@@ -19637,7 +19540,7 @@
       <c r="G88" s="152"/>
       <c r="H88" s="153"/>
       <c r="I88" s="123" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J88" s="123">
         <f t="shared" si="0"/>
@@ -19797,7 +19700,7 @@
       <c r="G93" s="152"/>
       <c r="H93" s="153"/>
       <c r="I93" s="123" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J93" s="123">
         <f t="shared" si="0"/>
@@ -20577,8 +20480,8 @@
       <c r="D118" s="148"/>
       <c r="E118" s="148"/>
       <c r="F118" s="148"/>
-      <c r="G118" s="211"/>
-      <c r="H118" s="212"/>
+      <c r="G118" s="210"/>
+      <c r="H118" s="211"/>
       <c r="I118" s="123"/>
       <c r="J118" s="128"/>
       <c r="K118" s="128"/>
@@ -21180,7 +21083,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFFF4F9-97DA-0445-9F68-74756A3E2648}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58.6640625" customWidth="1"/>
@@ -21247,7 +21150,7 @@
     </row>
     <row r="5" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="138" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B5" s="139">
         <v>108658.53000000003</v>
@@ -21261,7 +21164,7 @@
     </row>
     <row r="6" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A6" s="138" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B6" s="139">
         <v>60226.45</v>
@@ -21275,7 +21178,7 @@
     </row>
     <row r="7" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A7" s="138" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B7" s="140">
         <v>64802</v>
@@ -21289,7 +21192,7 @@
     </row>
     <row r="8" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A8" s="138" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B8" s="140">
         <v>71110.957552411084</v>
@@ -21303,7 +21206,7 @@
     </row>
     <row r="9" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A9" s="138" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B9" s="139">
         <v>66011.839080000005</v>
@@ -21317,7 +21220,7 @@
     </row>
     <row r="10" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A10" s="138" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B10" s="139">
         <v>0</v>
@@ -21331,7 +21234,7 @@
     </row>
     <row r="11" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A11" s="138" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" s="139">
         <v>0</v>
@@ -21345,7 +21248,7 @@
     </row>
     <row r="12" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A12" s="138" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" s="139">
         <v>0</v>
@@ -21359,7 +21262,7 @@
     </row>
     <row r="13" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A13" s="138" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B13" s="140">
         <v>0</v>
@@ -21373,7 +21276,7 @@
     </row>
     <row r="14" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A14" s="138" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B14" s="140">
         <v>0</v>
@@ -21387,7 +21290,7 @@
     </row>
     <row r="15" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A15" s="138" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B15" s="140">
         <v>150420</v>
@@ -21415,7 +21318,7 @@
     </row>
     <row r="17" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A17" s="131" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B17" s="141">
         <v>0</v>
@@ -21429,7 +21332,7 @@
     </row>
     <row r="18" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A18" s="133" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B18" s="142">
         <v>0</v>
@@ -21443,7 +21346,7 @@
     </row>
     <row r="19" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A19" s="133" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B19" s="142">
         <v>0</v>
@@ -21457,7 +21360,7 @@
     </row>
     <row r="20" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="133" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B20" s="142">
         <v>0</v>
@@ -21471,7 +21374,7 @@
     </row>
     <row r="21" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A21" s="133" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B21" s="142">
         <v>2.9342500000000001E-2</v>
@@ -21485,7 +21388,7 @@
     </row>
     <row r="22" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A22" s="133" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B22" s="142">
         <v>0</v>
@@ -21499,7 +21402,7 @@
     </row>
     <row r="23" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A23" s="133" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B23" s="142">
         <v>8.6260000000000003E-2</v>
@@ -21513,7 +21416,7 @@
     </row>
     <row r="24" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A24" s="133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B24" s="142">
         <v>0</v>
@@ -21527,7 +21430,7 @@
     </row>
     <row r="25" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="133" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B25" s="142">
         <v>0</v>
@@ -21541,7 +21444,7 @@
     </row>
     <row r="26" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A26" s="133" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B26" s="142">
         <v>0</v>
@@ -21555,7 +21458,7 @@
     </row>
     <row r="27" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A27" s="133" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27" s="142">
         <v>9.2189999999999994E-2</v>
@@ -21569,7 +21472,7 @@
     </row>
     <row r="28" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A28" s="133" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B28" s="142">
         <v>8.6669999999999997E-2</v>
@@ -21583,7 +21486,7 @@
     </row>
     <row r="29" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A29" s="133" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B29" s="142">
         <v>0</v>
@@ -21597,7 +21500,7 @@
     </row>
     <row r="30" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A30" s="133" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B30" s="142">
         <v>0</v>
@@ -21611,7 +21514,7 @@
     </row>
     <row r="31" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A31" s="133" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B31" s="142">
         <v>0</v>
@@ -21625,7 +21528,7 @@
     </row>
     <row r="32" spans="1:4" ht="24" x14ac:dyDescent="0.3">
       <c r="A32" s="133" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B32" s="162">
         <v>8.8000000000000005E-3</v>
@@ -21637,9 +21540,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A33" s="136" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B33" s="142">
         <v>0</v>
@@ -21651,9 +21554,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A34" s="136" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B34" s="142">
         <v>0</v>
@@ -21665,23 +21568,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A35" s="136" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="142">
+        <v>0</v>
+      </c>
+      <c r="C35" s="137">
+        <v>0</v>
+      </c>
+      <c r="D35" s="135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="A36" s="136" t="s">
         <v>128</v>
-      </c>
-      <c r="B35" s="142">
-        <v>0</v>
-      </c>
-      <c r="C35" s="137">
-        <v>0</v>
-      </c>
-      <c r="D35" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A36" s="136" t="s">
-        <v>130</v>
       </c>
       <c r="B36" s="142">
         <v>7.7600000000000002E-2</v>
@@ -21692,25 +21595,26 @@
       <c r="D36" s="135">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+      <c r="J36" s="143"/>
+    </row>
+    <row r="37" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A37" s="143" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="142">
+        <v>0</v>
+      </c>
+      <c r="C37" s="144">
+        <v>0</v>
+      </c>
+      <c r="D37" s="135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="A38" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="B37" s="142">
-        <v>0</v>
-      </c>
-      <c r="C37" s="144">
-        <v>0</v>
-      </c>
-      <c r="D37" s="135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A38" s="143" t="s">
-        <v>133</v>
-      </c>
       <c r="B38" s="142">
         <v>0</v>
       </c>
@@ -21721,9 +21625,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A39" s="143" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B39" s="141">
         <v>3185.4799999999996</v>
@@ -21735,9 +21639,9 @@
         <v>8.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A40" s="143" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B40" s="141">
         <v>3108.9800000000005</v>
@@ -21749,17 +21653,59 @@
         <v>1.2699999999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A41" s="208" t="s">
-        <v>188</v>
-      </c>
-      <c r="B41" s="141">
+    <row r="41" spans="1:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="A41" s="143" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41" s="135">
         <v>3108.9800000000005</v>
       </c>
-      <c r="C41" s="142">
+      <c r="C41" s="135">
         <v>0.63</v>
       </c>
-      <c r="D41" s="142">
+      <c r="D41" s="299">
+        <v>1.2699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="A42" s="133" t="s">
+        <v>191</v>
+      </c>
+      <c r="B42" s="141">
+        <v>1000</v>
+      </c>
+      <c r="C42" s="135">
+        <v>0.63</v>
+      </c>
+      <c r="D42" s="299">
+        <v>1.2699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="A43" s="133" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="141">
+        <v>1000</v>
+      </c>
+      <c r="C43" s="135">
+        <v>0.63</v>
+      </c>
+      <c r="D43" s="299">
+        <v>1.2699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="A44" s="300" t="s">
+        <v>197</v>
+      </c>
+      <c r="B44" s="141">
+        <v>1000</v>
+      </c>
+      <c r="C44" s="135">
+        <v>0.63</v>
+      </c>
+      <c r="D44" s="299">
         <v>1.2699999999999999E-2</v>
       </c>
     </row>
@@ -21771,7 +21717,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731AE742-D316-A04E-A3DB-C52263974828}">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="B2:Q65"/>
+  <dimension ref="B2:Q70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
@@ -21783,31 +21729,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="20" x14ac:dyDescent="0.25">
-      <c r="B2" s="213" t="s">
+      <c r="B2" s="212" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="212"/>
+      <c r="D2" s="212"/>
+      <c r="F2" s="212" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="213"/>
-      <c r="D2" s="213"/>
-      <c r="F2" s="213" t="s">
-        <v>143</v>
-      </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="213"/>
-      <c r="J2" s="214" t="s">
-        <v>144</v>
-      </c>
-      <c r="K2" s="215"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="212"/>
+      <c r="J2" s="213" t="s">
+        <v>142</v>
+      </c>
+      <c r="K2" s="214"/>
       <c r="L2" s="98"/>
       <c r="M2" s="99" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N2" s="100" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="19" x14ac:dyDescent="0.25">
       <c r="B3" s="95" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C3" s="95" t="s">
         <v>1</v>
@@ -21816,7 +21762,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="95" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G3" s="95" t="s">
         <v>1</v>
@@ -21825,10 +21771,10 @@
         <v>0</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K3" s="101" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L3" s="102"/>
       <c r="M3" s="103"/>
@@ -22810,7 +22756,7 @@
     </row>
     <row r="28" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B28" s="95" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C28" s="96">
         <f>Utilidad!A25</f>
@@ -22821,7 +22767,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="95" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G28" s="186">
         <f>Utilidad!B25</f>
@@ -23010,7 +22956,7 @@
     </row>
     <row r="33" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B33" s="95" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C33" s="96">
         <f>Utilidad!A30</f>
@@ -23021,7 +22967,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="95" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G33" s="186">
         <f>Utilidad!B30</f>
@@ -23970,7 +23916,7 @@
     </row>
     <row r="57" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B57" s="95" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C57" s="96">
         <f>Utilidad!A54</f>
@@ -23981,7 +23927,7 @@
         <v>0.63460000000000005</v>
       </c>
       <c r="F57" s="95" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G57" s="186">
         <f>Utilidad!B54</f>
@@ -24010,7 +23956,7 @@
     </row>
     <row r="58" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B58" s="95" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C58" s="96">
         <f>Utilidad!A55</f>
@@ -24021,7 +23967,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="95" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G58" s="186">
         <f>Utilidad!B55</f>
@@ -24050,7 +23996,7 @@
     </row>
     <row r="59" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B59" s="95" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C59" s="96">
         <f>Utilidad!A56</f>
@@ -24061,7 +24007,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="95" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G59" s="186">
         <f>Utilidad!B56</f>
@@ -24090,7 +24036,7 @@
     </row>
     <row r="60" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B60" s="95" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C60" s="96">
         <f>Utilidad!A57</f>
@@ -24101,7 +24047,7 @@
         <v>0.63</v>
       </c>
       <c r="F60" s="95" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G60" s="186">
         <f>Utilidad!B57</f>
@@ -24130,7 +24076,7 @@
     </row>
     <row r="61" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B61" s="95" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C61" s="96">
         <f>Utilidad!A58</f>
@@ -24141,7 +24087,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="95" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G61" s="186">
         <f>Utilidad!B58</f>
@@ -24170,7 +24116,7 @@
     </row>
     <row r="62" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B62" s="95" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C62" s="96">
         <f>Utilidad!A59</f>
@@ -24181,7 +24127,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="95" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G62" s="186">
         <f>Utilidad!B59</f>
@@ -24210,7 +24156,7 @@
     </row>
     <row r="63" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B63" s="95" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C63" s="96">
         <f>Utilidad!A60</f>
@@ -24221,7 +24167,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="95" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G63" s="186">
         <f>Utilidad!B60</f>
@@ -24250,7 +24196,7 @@
     </row>
     <row r="64" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B64" s="95" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C64" s="96">
         <f>Utilidad!A61</f>
@@ -24261,7 +24207,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="95" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G64" s="186">
         <f>Utilidad!B61</f>
@@ -24290,7 +24236,7 @@
     </row>
     <row r="65" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B65" s="95" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C65" s="96">
         <f>Utilidad!A62</f>
@@ -24301,7 +24247,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="95" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G65" s="186">
         <f>Utilidad!B62</f>
@@ -24325,6 +24271,206 @@
       </c>
       <c r="N65" s="106">
         <f t="shared" ref="N65" si="15">+IF(J65&lt;&gt;"",ABS(K65),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+      <c r="B66" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="C66" s="96">
+        <f>Utilidad!A63</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="97">
+        <f>IF(Utilidad!C63&gt;1,Utilidad!C63/100,Utilidad!C63)</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="95" t="s">
+        <v>193</v>
+      </c>
+      <c r="G66" s="186">
+        <f>Utilidad!B63</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="187">
+        <f>IF(Utilidad!D63&gt;1,Utilidad!D63/100,Utilidad!D63)</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="104">
+        <f t="shared" ref="J66:J70" si="16">+IF(C66&lt;&gt;0,(G66-C66)/C66,ABS(G66-C66))</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="104">
+        <f t="shared" ref="K66:K70" si="17">+IF(D66&lt;&gt;0,(H66-D66)/D66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="106">
+        <f t="shared" ref="M66:M70" si="18">+IF(J66&lt;&gt;"",ABS(J66),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N66" s="106">
+        <f t="shared" ref="N66:N70" si="19">+IF(J66&lt;&gt;"",ABS(K66),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+      <c r="B67" s="95" t="s">
+        <v>194</v>
+      </c>
+      <c r="C67" s="96">
+        <f>Utilidad!A64</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="97">
+        <f>IF(Utilidad!C64&gt;1,Utilidad!C64/100,Utilidad!C64)</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="95" t="s">
+        <v>194</v>
+      </c>
+      <c r="G67" s="186">
+        <f>Utilidad!B64</f>
+        <v>0</v>
+      </c>
+      <c r="H67" s="187">
+        <f>IF(Utilidad!D64&gt;1,Utilidad!D64/100,Utilidad!D64)</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K67" s="104">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M67" s="106">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N67" s="106">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+      <c r="B68" s="95" t="s">
+        <v>195</v>
+      </c>
+      <c r="C68" s="96">
+        <f>Utilidad!A65</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="97">
+        <f>IF(Utilidad!C65&gt;1,Utilidad!C65/100,Utilidad!C65)</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="95" t="s">
+        <v>195</v>
+      </c>
+      <c r="G68" s="186">
+        <f>Utilidad!B65</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="187">
+        <f>IF(Utilidad!D65&gt;1,Utilidad!D65/100,Utilidad!D65)</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="104">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M68" s="106">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="106">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+      <c r="B69" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" s="96">
+        <f>Utilidad!A66</f>
+        <v>0</v>
+      </c>
+      <c r="D69" s="97">
+        <f>IF(Utilidad!C66&gt;1,Utilidad!C66/100,Utilidad!C66)</f>
+        <v>0</v>
+      </c>
+      <c r="F69" s="95" t="s">
+        <v>196</v>
+      </c>
+      <c r="G69" s="186">
+        <f>Utilidad!B66</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="187">
+        <f>IF(Utilidad!D66&gt;1,Utilidad!D66/100,Utilidad!D66)</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="104">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="106">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N69" s="106">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+      <c r="B70" s="95" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="96">
+        <f>Utilidad!A67</f>
+        <v>0</v>
+      </c>
+      <c r="D70" s="97">
+        <f>IF(Utilidad!C67&gt;1,Utilidad!C67/100,Utilidad!C67)</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="95" t="s">
+        <v>197</v>
+      </c>
+      <c r="G70" s="186">
+        <f>Utilidad!B67</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="187">
+        <f>IF(Utilidad!D67&gt;1,Utilidad!D67/100,Utilidad!D67)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="104">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="104">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="M70" s="106">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N70" s="106">
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -24334,7 +24480,7 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="J2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J4:K65">
+  <conditionalFormatting sqref="J4:K70">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>ABS(J4)&gt;=10%</formula>
     </cfRule>
@@ -24351,7 +24497,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Hoja4"/>
-  <dimension ref="B1:S149"/>
+  <dimension ref="B1:S153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -24403,7 +24549,7 @@
       <c r="B6" s="7"/>
       <c r="E6" s="25">
         <f>+Utilidad!J62</f>
-        <v>150420</v>
+        <v>0</v>
       </c>
       <c r="S6" s="24"/>
     </row>
@@ -24411,19 +24557,19 @@
       <c r="B7" s="7"/>
       <c r="E7" s="26">
         <f>+Utilidad!K62</f>
-        <v>0.23879999999999998</v>
+        <v>0</v>
       </c>
       <c r="I7" s="25">
         <f>+Utilidad!J65</f>
-        <v>90117</v>
+        <v>0</v>
       </c>
       <c r="L7" s="27">
         <f>+Utilidad!J68</f>
-        <v>116673</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="27">
         <f>+Utilidad!J70</f>
-        <v>20626.123299999999</v>
+        <v>0</v>
       </c>
       <c r="S7" s="24"/>
     </row>
@@ -24431,19 +24577,19 @@
       <c r="B8" s="7"/>
       <c r="E8" s="28">
         <f>+Utilidad!L62</f>
-        <v>35920.295999999995</v>
+        <v>0</v>
       </c>
       <c r="I8" s="26">
         <f>+Utilidad!K65</f>
-        <v>0.31023319518000003</v>
+        <v>0</v>
       </c>
       <c r="L8" s="29">
         <f>+Utilidad!K68</f>
-        <v>0.32063899999999995</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="29">
         <f>+Utilidad!K70</f>
-        <v>0.19247</v>
+        <v>0</v>
       </c>
       <c r="S8" s="24"/>
     </row>
@@ -24451,15 +24597,15 @@
       <c r="B9" s="7"/>
       <c r="I9" s="28">
         <f>+Utilidad!L65</f>
-        <v>27957.284850036063</v>
+        <v>0</v>
       </c>
       <c r="L9" s="30">
         <f>+Utilidad!L68</f>
-        <v>37409.914046999991</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="30">
         <f>Q7*Q8</f>
-        <v>3969.9099515509997</v>
+        <v>0</v>
       </c>
       <c r="S9" s="24"/>
     </row>
@@ -24531,7 +24677,7 @@
       </c>
       <c r="J14" s="33">
         <f>+I7+H13-L14-L7</f>
-        <v>-26556</v>
+        <v>0</v>
       </c>
       <c r="L14" s="27">
         <f>+Utilidad!J69</f>
@@ -24547,7 +24693,7 @@
       <c r="B15" s="7"/>
       <c r="G15" s="34">
         <f>+Utilidad!J64</f>
-        <v>60303</v>
+        <v>0</v>
       </c>
       <c r="H15" s="35">
         <f>+Utilidad!L66</f>
@@ -24571,11 +24717,14 @@
       </c>
       <c r="G16" s="37">
         <f>+Utilidad!K64</f>
-        <v>0.13205</v>
+        <v>0</v>
       </c>
       <c r="L16" s="30">
         <f>+Utilidad!L69</f>
         <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>189</v>
       </c>
       <c r="S16" s="24"/>
     </row>
@@ -24583,7 +24732,11 @@
       <c r="B17" s="7"/>
       <c r="G17" s="38">
         <f>G15*G16</f>
-        <v>7963.0111500000003</v>
+        <v>0</v>
+      </c>
+      <c r="P17" s="25">
+        <f>Flujos!G65</f>
+        <v>0</v>
       </c>
       <c r="S17" s="24"/>
     </row>
@@ -24593,6 +24746,10 @@
         <f>Flujos!C56</f>
         <v>37855</v>
       </c>
+      <c r="P18" s="26">
+        <f>Flujos!H65</f>
+        <v>0</v>
+      </c>
       <c r="S18" s="24"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.2">
@@ -24601,6 +24758,10 @@
         <f>Flujos!D56</f>
         <v>0.50360000000000005</v>
       </c>
+      <c r="P19" s="28">
+        <f>P17*P18</f>
+        <v>0</v>
+      </c>
       <c r="S19" s="24"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.2">
@@ -24665,9 +24826,9 @@
         <f>+Utilidad!L73</f>
         <v>9499.3023439999997</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="e">
         <f>+(O22+N13)/(L7)</f>
-        <v>0.69564509355206428</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="S24" s="24"/>
     </row>
@@ -25061,7 +25222,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L65" s="27">
         <f>Flujos!G25</f>
@@ -25080,7 +25241,7 @@
         <v>3069</v>
       </c>
       <c r="G66" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L66" s="29">
         <f>Flujos!H25</f>
@@ -25095,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L67" s="30">
         <f>L66*L65</f>
@@ -25326,7 +25487,7 @@
         <v>0</v>
       </c>
       <c r="Q87" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="S87" s="24"/>
     </row>
@@ -25353,7 +25514,7 @@
         <v>0</v>
       </c>
       <c r="R90" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="S90" s="24"/>
     </row>
@@ -25376,7 +25537,7 @@
     <row r="93" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B93" s="7"/>
       <c r="P93" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="S93" s="24"/>
     </row>
@@ -25402,291 +25563,291 @@
     </row>
     <row r="95" spans="2:19" ht="16" x14ac:dyDescent="0.2">
       <c r="G95" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="96" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G96" s="231" t="s">
+        <v>69</v>
+      </c>
+      <c r="H96" s="231"/>
+      <c r="I96" s="232"/>
+      <c r="J96" s="233" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="96" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G96" s="222" t="s">
+      <c r="K96" s="233"/>
+      <c r="L96" s="233"/>
+      <c r="M96" s="234" t="s">
         <v>71</v>
       </c>
-      <c r="H96" s="222"/>
-      <c r="I96" s="223"/>
-      <c r="J96" s="224" t="s">
+      <c r="N96" s="234"/>
+      <c r="O96" s="234"/>
+      <c r="P96" s="234"/>
+    </row>
+    <row r="97" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G97" s="219" t="s">
         <v>72</v>
       </c>
-      <c r="K96" s="224"/>
-      <c r="L96" s="224"/>
-      <c r="M96" s="225" t="s">
-        <v>73</v>
-      </c>
-      <c r="N96" s="225"/>
-      <c r="O96" s="225"/>
-      <c r="P96" s="225"/>
-    </row>
-    <row r="97" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G97" s="226" t="s">
-        <v>74</v>
-      </c>
-      <c r="H97" s="227"/>
+      <c r="H97" s="220"/>
       <c r="I97" s="21">
         <f>+E6</f>
-        <v>150420</v>
-      </c>
-      <c r="J97" s="228" t="s">
+        <v>0</v>
+      </c>
+      <c r="J97" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="K97" s="221"/>
+      <c r="K97" s="222"/>
       <c r="L97" s="10">
         <f>Flujos!G9</f>
         <v>-26556</v>
       </c>
-      <c r="M97" s="221" t="s">
-        <v>75</v>
-      </c>
-      <c r="N97" s="221"/>
-      <c r="O97" s="221"/>
+      <c r="M97" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="N97" s="222"/>
+      <c r="O97" s="222"/>
       <c r="P97" s="10">
         <f>+G15</f>
-        <v>60303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G98" s="226" t="s">
-        <v>76</v>
-      </c>
-      <c r="H98" s="227"/>
+      <c r="G98" s="219" t="s">
+        <v>74</v>
+      </c>
+      <c r="H98" s="220"/>
       <c r="I98" s="21">
         <f>+C12</f>
         <v>0</v>
       </c>
-      <c r="J98" s="221" t="s">
+      <c r="J98" s="222" t="s">
         <v>8</v>
       </c>
-      <c r="K98" s="221"/>
+      <c r="K98" s="222"/>
       <c r="L98" s="10">
         <f>Flujos!G17</f>
         <v>9165</v>
       </c>
-      <c r="M98" s="221" t="s">
+      <c r="M98" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="N98" s="221"/>
-      <c r="O98" s="221"/>
+      <c r="N98" s="222"/>
+      <c r="O98" s="222"/>
       <c r="P98" s="10">
         <f>+Q7</f>
-        <v>20626.123299999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G99" s="226" t="s">
-        <v>77</v>
-      </c>
-      <c r="H99" s="227"/>
+      <c r="G99" s="219" t="s">
+        <v>75</v>
+      </c>
+      <c r="H99" s="220"/>
       <c r="I99" s="21">
         <f>+H13</f>
         <v>0</v>
       </c>
-      <c r="J99" s="221" t="s">
-        <v>78</v>
-      </c>
-      <c r="K99" s="221"/>
+      <c r="J99" s="222" t="s">
+        <v>76</v>
+      </c>
+      <c r="K99" s="222"/>
       <c r="L99" s="10">
         <v>0</v>
       </c>
-      <c r="M99" s="221" t="s">
+      <c r="M99" s="222" t="s">
         <v>23</v>
       </c>
-      <c r="N99" s="221"/>
-      <c r="O99" s="221"/>
+      <c r="N99" s="222"/>
+      <c r="O99" s="222"/>
       <c r="P99" s="10">
         <f>+Q11</f>
         <v>14883.876700000001</v>
       </c>
     </row>
     <row r="100" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G100" s="219" t="s">
-        <v>79</v>
-      </c>
-      <c r="H100" s="220"/>
+      <c r="G100" s="223" t="s">
+        <v>77</v>
+      </c>
+      <c r="H100" s="224"/>
       <c r="I100" s="21">
         <f>+C26</f>
         <v>0</v>
       </c>
-      <c r="J100" s="221" t="s">
+      <c r="J100" s="222" t="s">
         <v>11</v>
       </c>
-      <c r="K100" s="221"/>
+      <c r="K100" s="222"/>
       <c r="L100" s="10">
         <f>Flujos!G21</f>
         <v>-5099</v>
       </c>
-      <c r="M100" s="221" t="s">
-        <v>80</v>
-      </c>
-      <c r="N100" s="221"/>
-      <c r="O100" s="221"/>
+      <c r="M100" s="222" t="s">
+        <v>78</v>
+      </c>
+      <c r="N100" s="222"/>
+      <c r="O100" s="222"/>
       <c r="P100" s="10">
         <f>+I30</f>
         <v>43841</v>
       </c>
     </row>
     <row r="101" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G101" s="219" t="s">
+      <c r="G101" s="223" t="s">
         <v>57</v>
       </c>
-      <c r="H101" s="220"/>
+      <c r="H101" s="224"/>
       <c r="I101" s="21">
         <f>+C35</f>
         <v>0</v>
       </c>
-      <c r="J101" s="221" t="s">
-        <v>81</v>
-      </c>
-      <c r="K101" s="221"/>
+      <c r="J101" s="222" t="s">
+        <v>79</v>
+      </c>
+      <c r="K101" s="222"/>
       <c r="L101" s="10">
         <f>Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="M101" s="221" t="s">
-        <v>82</v>
-      </c>
-      <c r="N101" s="221"/>
-      <c r="O101" s="221"/>
+      <c r="M101" s="222" t="s">
+        <v>80</v>
+      </c>
+      <c r="N101" s="222"/>
+      <c r="O101" s="222"/>
       <c r="P101" s="10">
         <f>+M58</f>
         <v>1422</v>
       </c>
     </row>
     <row r="102" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G102" s="219" t="s">
+      <c r="G102" s="223" t="s">
         <v>60</v>
       </c>
-      <c r="H102" s="220"/>
+      <c r="H102" s="224"/>
       <c r="I102" s="21">
         <f>+C44</f>
         <v>0</v>
       </c>
       <c r="J102" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K102" s="11"/>
       <c r="L102" s="10">
         <f>Flujos!G44</f>
         <v>0</v>
       </c>
-      <c r="M102" s="221" t="s">
-        <v>84</v>
-      </c>
-      <c r="N102" s="221"/>
-      <c r="O102" s="221"/>
+      <c r="M102" s="222" t="s">
+        <v>82</v>
+      </c>
+      <c r="N102" s="222"/>
+      <c r="O102" s="222"/>
       <c r="P102" s="10">
         <f>+O63</f>
         <v>73127</v>
       </c>
     </row>
     <row r="103" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G103" s="219" t="s">
-        <v>85</v>
-      </c>
-      <c r="H103" s="220"/>
+      <c r="G103" s="223" t="s">
+        <v>83</v>
+      </c>
+      <c r="H103" s="224"/>
       <c r="I103" s="21">
         <f>+C54</f>
         <v>0</v>
       </c>
       <c r="J103" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K103" s="11"/>
       <c r="L103" s="10">
         <f>Flujos!G47</f>
         <v>0</v>
       </c>
-      <c r="M103" s="221" t="s">
-        <v>87</v>
-      </c>
-      <c r="N103" s="221"/>
-      <c r="O103" s="221"/>
+      <c r="M103" s="222" t="s">
+        <v>85</v>
+      </c>
+      <c r="N103" s="222"/>
+      <c r="O103" s="222"/>
       <c r="P103" s="10">
         <f>+O67</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G104" s="219" t="s">
-        <v>88</v>
-      </c>
-      <c r="H104" s="220"/>
+      <c r="G104" s="223" t="s">
+        <v>86</v>
+      </c>
+      <c r="H104" s="224"/>
       <c r="I104" s="21">
         <f>+C62</f>
         <v>37855</v>
       </c>
       <c r="J104" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K104" s="11"/>
       <c r="L104" s="10">
         <f>Flujos!G50</f>
         <v>0</v>
       </c>
-      <c r="M104" s="221" t="s">
+      <c r="M104" s="222" t="s">
         <v>44</v>
       </c>
-      <c r="N104" s="221"/>
-      <c r="O104" s="221"/>
+      <c r="N104" s="222"/>
+      <c r="O104" s="222"/>
       <c r="P104" s="10">
         <f>+O74</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G105" s="219" t="s">
-        <v>90</v>
-      </c>
-      <c r="H105" s="220"/>
+      <c r="G105" s="223" t="s">
+        <v>88</v>
+      </c>
+      <c r="H105" s="224"/>
       <c r="I105" s="21">
         <f>+H70</f>
         <v>0</v>
       </c>
       <c r="J105" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K105" s="11"/>
       <c r="L105" s="10">
         <f>Flujos!G53</f>
         <v>0</v>
       </c>
-      <c r="M105" s="221" t="s">
-        <v>92</v>
-      </c>
-      <c r="N105" s="221"/>
-      <c r="O105" s="221"/>
+      <c r="M105" s="222" t="s">
+        <v>90</v>
+      </c>
+      <c r="N105" s="222"/>
+      <c r="O105" s="222"/>
       <c r="P105" s="10">
         <f>+O84</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G106" s="219" t="s">
-        <v>93</v>
-      </c>
-      <c r="H106" s="220"/>
+      <c r="G106" s="223" t="s">
+        <v>91</v>
+      </c>
+      <c r="H106" s="224"/>
       <c r="I106" s="21">
         <f>+H75</f>
         <v>0</v>
       </c>
-      <c r="J106" s="221" t="s">
+      <c r="J106" s="222" t="s">
         <v>13</v>
       </c>
-      <c r="K106" s="221"/>
+      <c r="K106" s="222"/>
       <c r="L106" s="10">
         <f>Flujos!G42</f>
         <v>0</v>
       </c>
-      <c r="M106" s="221" t="s">
-        <v>160</v>
-      </c>
-      <c r="N106" s="221"/>
-      <c r="O106" s="221"/>
+      <c r="M106" s="222" t="s">
+        <v>158</v>
+      </c>
+      <c r="N106" s="222"/>
+      <c r="O106" s="222"/>
       <c r="P106" s="10">
         <f>Q79</f>
         <v>0</v>
@@ -25694,7 +25855,7 @@
     </row>
     <row r="107" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G107" s="19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H107" s="20"/>
       <c r="I107" s="21">
@@ -25702,794 +25863,956 @@
         <v>0</v>
       </c>
       <c r="J107" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K107" s="11"/>
       <c r="L107" s="10">
         <f>Flujos!G26</f>
         <v>-3438</v>
       </c>
-      <c r="M107" s="229"/>
-      <c r="N107" s="230"/>
-      <c r="O107" s="231"/>
+      <c r="M107" s="301" t="s">
+        <v>205</v>
+      </c>
+      <c r="N107" s="302"/>
+      <c r="O107" s="303"/>
       <c r="P107" s="10"/>
     </row>
     <row r="108" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G108" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H108" s="20"/>
       <c r="I108" s="21">
         <f>+L78</f>
         <v>0</v>
       </c>
-      <c r="J108" s="221" t="s">
+      <c r="J108" s="222" t="s">
         <v>12</v>
       </c>
-      <c r="K108" s="221"/>
+      <c r="K108" s="222"/>
       <c r="L108" s="10">
         <f>Flujos!G34</f>
         <v>6226</v>
       </c>
-      <c r="M108" s="229"/>
-      <c r="N108" s="230"/>
-      <c r="O108" s="231"/>
+      <c r="M108" s="228"/>
+      <c r="N108" s="229"/>
+      <c r="O108" s="230"/>
       <c r="P108" s="10"/>
     </row>
     <row r="109" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G109" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H109" s="20"/>
       <c r="I109" s="21">
         <f>+K86</f>
         <v>0</v>
       </c>
-      <c r="J109" s="221" t="s">
+      <c r="J109" s="222" t="s">
         <v>10</v>
       </c>
-      <c r="K109" s="221"/>
+      <c r="K109" s="222"/>
       <c r="L109" s="10">
         <f>Flujos!G39</f>
         <v>0</v>
       </c>
-      <c r="M109" s="229"/>
-      <c r="N109" s="230"/>
-      <c r="O109" s="231"/>
+      <c r="M109" s="228"/>
+      <c r="N109" s="229"/>
+      <c r="O109" s="230"/>
       <c r="P109" s="10"/>
     </row>
     <row r="110" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G110" s="219" t="s">
-        <v>98</v>
-      </c>
-      <c r="H110" s="220"/>
+      <c r="G110" s="223" t="s">
+        <v>96</v>
+      </c>
+      <c r="H110" s="224"/>
       <c r="I110" s="21">
         <f>+L90</f>
         <v>0</v>
       </c>
-      <c r="J110" s="221"/>
-      <c r="K110" s="221"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="221"/>
-      <c r="N110" s="221"/>
-      <c r="O110" s="221"/>
+      <c r="J110" s="222" t="s">
+        <v>204</v>
+      </c>
+      <c r="K110" s="222"/>
+      <c r="L110" s="10">
+        <f>Flujos!G69</f>
+        <v>0</v>
+      </c>
+      <c r="M110" s="222"/>
+      <c r="N110" s="222"/>
+      <c r="O110" s="222"/>
       <c r="P110" s="10"/>
     </row>
     <row r="111" spans="7:16" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G111" s="219" t="s">
-        <v>175</v>
-      </c>
-      <c r="H111" s="220"/>
+      <c r="G111" s="223" t="s">
+        <v>173</v>
+      </c>
+      <c r="H111" s="224"/>
       <c r="I111" s="21">
         <f>K82</f>
         <v>3157</v>
       </c>
-      <c r="J111" s="221"/>
-      <c r="K111" s="221"/>
+      <c r="J111" s="222"/>
+      <c r="K111" s="222"/>
       <c r="L111" s="10"/>
-      <c r="M111" s="221"/>
-      <c r="N111" s="221"/>
-      <c r="O111" s="221"/>
+      <c r="M111" s="222"/>
+      <c r="N111" s="222"/>
+      <c r="O111" s="222"/>
       <c r="P111" s="10"/>
     </row>
     <row r="112" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G112" s="219" t="s">
-        <v>179</v>
-      </c>
-      <c r="H112" s="220" t="s">
-        <v>168</v>
+      <c r="G112" s="223" t="s">
+        <v>177</v>
+      </c>
+      <c r="H112" s="224" t="s">
+        <v>166</v>
       </c>
       <c r="I112" s="21">
         <f>Flujos!G59</f>
         <v>0</v>
       </c>
-      <c r="J112" s="221"/>
-      <c r="K112" s="221"/>
+      <c r="J112" s="222"/>
+      <c r="K112" s="222"/>
       <c r="L112" s="10"/>
-      <c r="M112" s="221"/>
-      <c r="N112" s="221"/>
-      <c r="O112" s="221"/>
+      <c r="M112" s="222"/>
+      <c r="N112" s="222"/>
+      <c r="O112" s="222"/>
       <c r="P112" s="10"/>
     </row>
     <row r="113" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G113" s="219" t="s">
-        <v>180</v>
-      </c>
-      <c r="H113" s="220" t="s">
-        <v>169</v>
+      <c r="G113" s="223" t="s">
+        <v>178</v>
+      </c>
+      <c r="H113" s="224" t="s">
+        <v>167</v>
       </c>
       <c r="I113" s="21">
         <f>Flujos!G60</f>
         <v>3069</v>
       </c>
-      <c r="J113" s="221"/>
-      <c r="K113" s="221"/>
+      <c r="J113" s="222"/>
+      <c r="K113" s="222"/>
       <c r="L113" s="10"/>
-      <c r="M113" s="221"/>
-      <c r="N113" s="221"/>
-      <c r="O113" s="221"/>
+      <c r="M113" s="222"/>
+      <c r="N113" s="222"/>
+      <c r="O113" s="222"/>
       <c r="P113" s="10"/>
     </row>
     <row r="114" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G114" s="219" t="s">
-        <v>181</v>
-      </c>
-      <c r="H114" s="220" t="s">
-        <v>170</v>
+      <c r="G114" s="223" t="s">
+        <v>179</v>
+      </c>
+      <c r="H114" s="224" t="s">
+        <v>168</v>
       </c>
       <c r="I114" s="21">
         <f>Flujos!G61</f>
         <v>0</v>
       </c>
-      <c r="J114" s="221"/>
-      <c r="K114" s="221"/>
+      <c r="J114" s="222"/>
+      <c r="K114" s="222"/>
       <c r="L114" s="10"/>
-      <c r="M114" s="221"/>
-      <c r="N114" s="221"/>
-      <c r="O114" s="221"/>
+      <c r="M114" s="222"/>
+      <c r="N114" s="222"/>
+      <c r="O114" s="222"/>
       <c r="P114" s="10"/>
     </row>
     <row r="115" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G115" s="219"/>
-      <c r="H115" s="220"/>
-      <c r="I115" s="21"/>
-      <c r="J115" s="221"/>
-      <c r="K115" s="221"/>
+      <c r="G115" s="223" t="s">
+        <v>190</v>
+      </c>
+      <c r="H115" s="224"/>
+      <c r="I115" s="21">
+        <f>Flujos!G62</f>
+        <v>0</v>
+      </c>
+      <c r="J115" s="222"/>
+      <c r="K115" s="222"/>
       <c r="L115" s="10"/>
-      <c r="M115" s="221"/>
-      <c r="N115" s="221"/>
-      <c r="O115" s="221"/>
+      <c r="M115" s="222"/>
+      <c r="N115" s="222"/>
+      <c r="O115" s="222"/>
       <c r="P115" s="10"/>
     </row>
     <row r="116" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G116" s="219"/>
-      <c r="H116" s="220"/>
-      <c r="I116" s="21"/>
-      <c r="J116" s="221"/>
-      <c r="K116" s="221"/>
+      <c r="G116" s="223" t="s">
+        <v>201</v>
+      </c>
+      <c r="H116" s="224"/>
+      <c r="I116" s="21">
+        <f>Flujos!G66</f>
+        <v>0</v>
+      </c>
+      <c r="J116" s="222"/>
+      <c r="K116" s="222"/>
       <c r="L116" s="10"/>
-      <c r="M116" s="221"/>
-      <c r="N116" s="221"/>
-      <c r="O116" s="221"/>
+      <c r="M116" s="222"/>
+      <c r="N116" s="222"/>
+      <c r="O116" s="222"/>
       <c r="P116" s="10"/>
     </row>
     <row r="117" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G117" s="219"/>
-      <c r="H117" s="220"/>
-      <c r="I117" s="21"/>
-      <c r="J117" s="221"/>
-      <c r="K117" s="221"/>
+      <c r="G117" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="H117" s="20"/>
+      <c r="I117" s="21">
+        <f>Flujos!G67</f>
+        <v>0</v>
+      </c>
+      <c r="J117" s="11"/>
+      <c r="K117" s="11"/>
       <c r="L117" s="10"/>
-      <c r="M117" s="221"/>
-      <c r="N117" s="221"/>
-      <c r="O117" s="221"/>
+      <c r="M117" s="11"/>
+      <c r="N117" s="11"/>
+      <c r="O117" s="11"/>
       <c r="P117" s="10"/>
     </row>
-    <row r="118" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G118" s="216" t="s">
-        <v>99</v>
-      </c>
-      <c r="H118" s="217"/>
-      <c r="I118" s="12">
-        <f>+SUM(I97:I117)</f>
-        <v>194501</v>
-      </c>
-      <c r="J118" s="218" t="s">
-        <v>100</v>
-      </c>
-      <c r="K118" s="218"/>
-      <c r="L118" s="13">
+    <row r="118" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G118" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H118" s="20"/>
+      <c r="I118" s="21">
+        <f>Flujos!G70</f>
+        <v>0</v>
+      </c>
+      <c r="J118" s="11"/>
+      <c r="K118" s="11"/>
+      <c r="L118" s="10"/>
+      <c r="M118" s="11"/>
+      <c r="N118" s="11"/>
+      <c r="O118" s="11"/>
+      <c r="P118" s="10"/>
+    </row>
+    <row r="119" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G119" s="223"/>
+      <c r="H119" s="224"/>
+      <c r="I119" s="21"/>
+      <c r="J119" s="222"/>
+      <c r="K119" s="222"/>
+      <c r="L119" s="10"/>
+      <c r="M119" s="222"/>
+      <c r="N119" s="222"/>
+      <c r="O119" s="222"/>
+      <c r="P119" s="10"/>
+    </row>
+    <row r="120" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G120" s="225" t="s">
+        <v>97</v>
+      </c>
+      <c r="H120" s="226"/>
+      <c r="I120" s="12">
+        <f>+SUM(I97:I119)</f>
+        <v>44081</v>
+      </c>
+      <c r="J120" s="227" t="s">
+        <v>98</v>
+      </c>
+      <c r="K120" s="227"/>
+      <c r="L120" s="13">
         <f>+SUM(L97:L110)</f>
         <v>-19702</v>
       </c>
-      <c r="M118" s="218" t="s">
+      <c r="M120" s="227" t="s">
+        <v>99</v>
+      </c>
+      <c r="N120" s="227"/>
+      <c r="O120" s="227"/>
+      <c r="P120" s="12">
+        <f>+SUM(P97:P110)</f>
+        <v>133273.87669999999</v>
+      </c>
+    </row>
+    <row r="121" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G121" s="14"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="14"/>
+      <c r="L121" s="14"/>
+      <c r="M121" s="14"/>
+      <c r="N121" s="14"/>
+      <c r="O121" s="14"/>
+      <c r="P121" s="14"/>
+    </row>
+    <row r="122" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G122" s="14"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="14"/>
+      <c r="L122" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="M122" s="16"/>
+      <c r="N122" s="17"/>
+      <c r="O122" s="16"/>
+      <c r="P122" s="18">
+        <f>+I120-L120-P120</f>
+        <v>-69490.876699999993</v>
+      </c>
+    </row>
+    <row r="123" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G126" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="N118" s="218"/>
-      <c r="O118" s="218"/>
-      <c r="P118" s="12">
-        <f>+SUM(P97:P110)</f>
-        <v>214203</v>
-      </c>
-    </row>
-    <row r="119" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G119" s="14"/>
-      <c r="H119" s="14"/>
-      <c r="I119" s="14"/>
-      <c r="J119" s="14"/>
-      <c r="K119" s="14"/>
-      <c r="L119" s="14"/>
-      <c r="M119" s="14"/>
-      <c r="N119" s="14"/>
-      <c r="O119" s="14"/>
-      <c r="P119" s="14"/>
-    </row>
-    <row r="120" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G120" s="14"/>
-      <c r="J120" s="14"/>
-      <c r="K120" s="14"/>
-      <c r="L120" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="M120" s="16"/>
-      <c r="N120" s="17"/>
-      <c r="O120" s="16"/>
-      <c r="P120" s="18">
-        <f>+I118-L118-P118</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G124" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="125" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G125" s="232" t="s">
+    </row>
+    <row r="127" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G127" s="215" t="s">
+        <v>69</v>
+      </c>
+      <c r="H127" s="215"/>
+      <c r="I127" s="216"/>
+      <c r="J127" s="217" t="s">
+        <v>70</v>
+      </c>
+      <c r="K127" s="217"/>
+      <c r="L127" s="217"/>
+      <c r="M127" s="218" t="s">
         <v>71</v>
       </c>
-      <c r="H125" s="232"/>
-      <c r="I125" s="233"/>
-      <c r="J125" s="234" t="s">
+      <c r="N127" s="218"/>
+      <c r="O127" s="218"/>
+      <c r="P127" s="218"/>
+    </row>
+    <row r="128" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G128" s="219" t="s">
         <v>72</v>
       </c>
-      <c r="K125" s="234"/>
-      <c r="L125" s="234"/>
-      <c r="M125" s="235" t="s">
-        <v>73</v>
-      </c>
-      <c r="N125" s="235"/>
-      <c r="O125" s="235"/>
-      <c r="P125" s="235"/>
-    </row>
-    <row r="126" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G126" s="226" t="s">
-        <v>74</v>
-      </c>
-      <c r="H126" s="227"/>
-      <c r="I126" s="21">
+      <c r="H128" s="220"/>
+      <c r="I128" s="21">
         <f>+E8</f>
-        <v>35920.295999999995</v>
-      </c>
-      <c r="J126" s="228" t="s">
+        <v>0</v>
+      </c>
+      <c r="J128" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="K126" s="221"/>
-      <c r="L126" s="10">
+      <c r="K128" s="222"/>
+      <c r="L128" s="10">
         <f>Flujos!G9*Flujos!H9</f>
         <v>-9452.6291970325201</v>
       </c>
-      <c r="M126" s="221" t="s">
-        <v>75</v>
-      </c>
-      <c r="N126" s="221"/>
-      <c r="O126" s="221"/>
-      <c r="P126" s="10">
+      <c r="M128" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="N128" s="222"/>
+      <c r="O128" s="222"/>
+      <c r="P128" s="10">
         <f>+G17</f>
-        <v>7963.0111500000003</v>
-      </c>
-    </row>
-    <row r="127" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G127" s="179" t="s">
-        <v>76</v>
-      </c>
-      <c r="H127" s="185"/>
-      <c r="I127" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G129" s="179" t="s">
+        <v>74</v>
+      </c>
+      <c r="H129" s="185"/>
+      <c r="I129" s="21">
         <f>+C14</f>
         <v>0</v>
       </c>
-      <c r="J127" s="11" t="s">
+      <c r="J129" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K127" s="11"/>
-      <c r="L127" s="10">
+      <c r="K129" s="11"/>
+      <c r="L129" s="10">
         <f>Flujos!G17*Flujos!H17</f>
         <v>3739.5701419030502</v>
       </c>
-      <c r="M127" s="11" t="s">
+      <c r="M129" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="N127" s="11"/>
-      <c r="O127" s="11"/>
-      <c r="P127" s="10">
-        <f>+Q9</f>
-        <v>3969.9099515509997</v>
-      </c>
-    </row>
-    <row r="128" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G128" s="179" t="s">
-        <v>77</v>
-      </c>
-      <c r="H128" s="180"/>
-      <c r="I128" s="21">
-        <f>+H15</f>
-        <v>0</v>
-      </c>
-      <c r="J128" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="K128" s="11"/>
-      <c r="L128" s="10">
-        <v>0</v>
-      </c>
-      <c r="M128" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="N128" s="11"/>
-      <c r="O128" s="11"/>
-      <c r="P128" s="10">
-        <f>+Q13</f>
-        <v>1616.1657514694998</v>
-      </c>
-    </row>
-    <row r="129" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G129" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="H129" s="20"/>
-      <c r="I129" s="21">
-        <f>+C28</f>
-        <v>0</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="K129" s="11"/>
-      <c r="L129" s="10">
-        <f>Flujos!G21*Flujos!H21</f>
-        <v>-3366.1796673720501</v>
-      </c>
-      <c r="M129" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="N129" s="11"/>
       <c r="O129" s="11"/>
       <c r="P129" s="10">
-        <f>+I32</f>
-        <v>4217.843077032403</v>
+        <f>+Q9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G130" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="H130" s="20"/>
+      <c r="G130" s="179" t="s">
+        <v>75</v>
+      </c>
+      <c r="H130" s="180"/>
       <c r="I130" s="21">
-        <f>+C37</f>
+        <f>+H15</f>
         <v>0</v>
       </c>
       <c r="J130" s="11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K130" s="11"/>
       <c r="L130" s="10">
-        <f>Flujos!G31*Flujos!H31</f>
         <v>0</v>
       </c>
       <c r="M130" s="11" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="N130" s="11"/>
       <c r="O130" s="11"/>
       <c r="P130" s="10">
-        <f>+M60</f>
-        <v>921.73832389422</v>
+        <f>+Q13</f>
+        <v>1616.1657514694998</v>
       </c>
     </row>
     <row r="131" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G131" s="19" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="H131" s="20"/>
       <c r="I131" s="21">
-        <f>+C46</f>
+        <f>+C28</f>
         <v>0</v>
       </c>
       <c r="J131" s="11" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="K131" s="11"/>
       <c r="L131" s="10">
-        <f>Flujos!G44*Flujos!H44</f>
-        <v>0</v>
+        <f>Flujos!G21*Flujos!H21</f>
+        <v>-3366.1796673720501</v>
       </c>
       <c r="M131" s="11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N131" s="11"/>
       <c r="O131" s="11"/>
       <c r="P131" s="10">
-        <f>+O65</f>
-        <v>47634.927799999998</v>
-      </c>
-    </row>
-    <row r="132" spans="7:16" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+        <f>+I32</f>
+        <v>4217.843077032403</v>
+      </c>
+    </row>
+    <row r="132" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G132" s="19" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="H132" s="20"/>
       <c r="I132" s="21">
-        <f>+C56</f>
+        <f>+C37</f>
         <v>0</v>
       </c>
       <c r="J132" s="11" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K132" s="11"/>
       <c r="L132" s="10">
-        <f>Flujos!G47*Flujos!H47</f>
+        <f>Flujos!G31*Flujos!H31</f>
         <v>0</v>
       </c>
       <c r="M132" s="11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="N132" s="11"/>
       <c r="O132" s="11"/>
       <c r="P132" s="10">
-        <f>+O69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="7:16" x14ac:dyDescent="0.2">
+        <f>+M60</f>
+        <v>921.73832389422</v>
+      </c>
+    </row>
+    <row r="133" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G133" s="19" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H133" s="20"/>
       <c r="I133" s="21">
-        <f>C64</f>
-        <v>19063.778000000002</v>
+        <f>+C46</f>
+        <v>0</v>
       </c>
       <c r="J133" s="11" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="K133" s="11"/>
       <c r="L133" s="10">
-        <f>Flujos!G50*Flujos!H50</f>
+        <f>Flujos!G44*Flujos!H44</f>
         <v>0</v>
       </c>
       <c r="M133" s="11" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="N133" s="11"/>
       <c r="O133" s="11"/>
       <c r="P133" s="10">
-        <f>+O76</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="7:16" x14ac:dyDescent="0.2">
+        <f>+O65</f>
+        <v>47634.927799999998</v>
+      </c>
+    </row>
+    <row r="134" spans="7:16" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G134" s="19" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H134" s="20"/>
       <c r="I134" s="21">
-        <f>+H72</f>
+        <f>+C56</f>
         <v>0</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K134" s="11"/>
       <c r="L134" s="10">
-        <f>Flujos!G53*Flujos!H53</f>
+        <f>Flujos!G47*Flujos!H47</f>
         <v>0</v>
       </c>
       <c r="M134" s="11" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N134" s="11"/>
       <c r="O134" s="11"/>
       <c r="P134" s="10">
-        <f>+O86</f>
+        <f>+O69</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G135" s="19" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H135" s="20"/>
       <c r="I135" s="21">
-        <f>+H77</f>
-        <v>0</v>
+        <f>C64</f>
+        <v>19063.778000000002</v>
       </c>
       <c r="J135" s="11" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="K135" s="11"/>
       <c r="L135" s="10">
-        <f>Flujos!G42*Flujos!H42</f>
+        <f>Flujos!G50*Flujos!H50</f>
         <v>0</v>
       </c>
       <c r="M135" s="11" t="s">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="N135" s="11"/>
       <c r="O135" s="11"/>
       <c r="P135" s="10">
-        <f>Q81</f>
+        <f>+O76</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G136" s="19" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H136" s="20"/>
       <c r="I136" s="21">
-        <f>+L76</f>
+        <f>+H72</f>
         <v>0</v>
       </c>
       <c r="J136" s="11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K136" s="11"/>
       <c r="L136" s="10">
+        <f>Flujos!G53*Flujos!H53</f>
+        <v>0</v>
+      </c>
+      <c r="M136" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="N136" s="11"/>
+      <c r="O136" s="11"/>
+      <c r="P136" s="10">
+        <f>+O86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G137" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H137" s="20"/>
+      <c r="I137" s="21">
+        <f>+H77</f>
+        <v>0</v>
+      </c>
+      <c r="J137" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="K137" s="11"/>
+      <c r="L137" s="10">
+        <f>Flujos!G42*Flujos!H42</f>
+        <v>0</v>
+      </c>
+      <c r="M137" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N137" s="11"/>
+      <c r="O137" s="11"/>
+      <c r="P137" s="10">
+        <f>Q81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G138" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H138" s="20"/>
+      <c r="I138" s="21">
+        <f>+L76</f>
+        <v>0</v>
+      </c>
+      <c r="J138" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="K138" s="11"/>
+      <c r="L138" s="10">
         <f>Flujos!G26*Flujos!H26</f>
         <v>-2260.2833314581599</v>
       </c>
-      <c r="M136" s="181"/>
-      <c r="N136" s="182"/>
-      <c r="O136" s="183"/>
-      <c r="P136" s="10"/>
-    </row>
-    <row r="137" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G137" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="H137" s="20"/>
-      <c r="I137" s="21">
+      <c r="M138" s="301" t="s">
+        <v>205</v>
+      </c>
+      <c r="N138" s="302"/>
+      <c r="O138" s="303"/>
+      <c r="P138" s="10">
+        <f>Flujos!G68*Flujos!H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G139" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H139" s="20"/>
+      <c r="I139" s="21">
         <f>+L80</f>
         <v>0</v>
       </c>
-      <c r="J137" s="11" t="s">
+      <c r="J139" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K137" s="11"/>
-      <c r="L137" s="10">
+      <c r="K139" s="11"/>
+      <c r="L139" s="10">
         <f>Flujos!G34*Flujos!H34</f>
         <v>3936.9021999755796</v>
       </c>
-      <c r="M137" s="181"/>
-      <c r="N137" s="182"/>
-      <c r="O137" s="183"/>
-      <c r="P137" s="10"/>
-    </row>
-    <row r="138" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G138" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H138" s="20"/>
-      <c r="I138" s="21">
+      <c r="M139" s="228"/>
+      <c r="N139" s="229"/>
+      <c r="O139" s="230"/>
+      <c r="P139" s="10"/>
+    </row>
+    <row r="140" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G140" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H140" s="20"/>
+      <c r="I140" s="21">
         <f>+K88</f>
         <v>0</v>
       </c>
-      <c r="J138" s="11" t="s">
+      <c r="J140" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K138" s="11"/>
-      <c r="L138" s="10">
+      <c r="K140" s="11"/>
+      <c r="L140" s="10">
         <f>Flujos!G39*Flujos!H39</f>
         <v>0</v>
       </c>
-      <c r="M138" s="181"/>
-      <c r="N138" s="182"/>
-      <c r="O138" s="183"/>
-      <c r="P138" s="10"/>
-    </row>
-    <row r="139" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G139" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="H139" s="20"/>
-      <c r="I139" s="21">
+      <c r="M140" s="181"/>
+      <c r="N140" s="182"/>
+      <c r="O140" s="183"/>
+      <c r="P140" s="10"/>
+    </row>
+    <row r="141" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G141" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="H141" s="20"/>
+      <c r="I141" s="21">
         <f>+L92</f>
         <v>0</v>
       </c>
-      <c r="J139" s="11"/>
-      <c r="K139" s="11"/>
-      <c r="L139" s="10"/>
-      <c r="M139" s="11"/>
-      <c r="N139" s="11"/>
-      <c r="O139" s="11"/>
-      <c r="P139" s="10"/>
-    </row>
-    <row r="140" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G140" s="219" t="s">
-        <v>175</v>
-      </c>
-      <c r="H140" s="220"/>
-      <c r="I140" s="21">
+      <c r="J141" s="222" t="s">
+        <v>204</v>
+      </c>
+      <c r="K141" s="222"/>
+      <c r="L141" s="10">
+        <f>Flujos!G69*Flujos!H69</f>
+        <v>0</v>
+      </c>
+      <c r="M141" s="11"/>
+      <c r="N141" s="11"/>
+      <c r="O141" s="11"/>
+      <c r="P141" s="10"/>
+    </row>
+    <row r="142" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G142" s="223" t="s">
+        <v>173</v>
+      </c>
+      <c r="H142" s="224"/>
+      <c r="I142" s="21">
         <f>K84</f>
         <v>2003.4322000000002</v>
       </c>
-      <c r="J140" s="11"/>
-      <c r="K140" s="11"/>
-      <c r="L140" s="10"/>
-      <c r="M140" s="11"/>
-      <c r="N140" s="11"/>
-      <c r="O140" s="11"/>
-      <c r="P140" s="10"/>
-    </row>
-    <row r="141" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G141" s="219" t="s">
-        <v>176</v>
-      </c>
-      <c r="H141" s="220"/>
-      <c r="I141" s="21">
+      <c r="M142" s="11"/>
+      <c r="N142" s="11"/>
+      <c r="O142" s="11"/>
+      <c r="P142" s="10"/>
+    </row>
+    <row r="143" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G143" s="223" t="s">
+        <v>174</v>
+      </c>
+      <c r="H143" s="224"/>
+      <c r="I143" s="21">
         <f>Flujos!G59*Flujos!H59</f>
         <v>0</v>
       </c>
-      <c r="J141" s="221"/>
-      <c r="K141" s="221"/>
-      <c r="L141" s="10"/>
-      <c r="M141" s="221"/>
-      <c r="N141" s="221"/>
-      <c r="O141" s="221"/>
-      <c r="P141" s="10"/>
-    </row>
-    <row r="142" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G142" s="219" t="s">
-        <v>177</v>
-      </c>
-      <c r="H142" s="220"/>
-      <c r="I142" s="21">
+      <c r="J143" s="222"/>
+      <c r="K143" s="222"/>
+      <c r="L143" s="10"/>
+      <c r="M143" s="304"/>
+      <c r="N143" s="304"/>
+      <c r="O143" s="304"/>
+      <c r="P143" s="10"/>
+    </row>
+    <row r="144" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G144" s="223" t="s">
+        <v>175</v>
+      </c>
+      <c r="H144" s="224"/>
+      <c r="I144" s="21">
         <f>Flujos!G60*Flujos!H60</f>
         <v>1933.47</v>
       </c>
-      <c r="J142" s="221"/>
-      <c r="K142" s="221"/>
-      <c r="L142" s="10"/>
-      <c r="M142" s="221"/>
-      <c r="N142" s="221"/>
-      <c r="O142" s="221"/>
-      <c r="P142" s="10"/>
-    </row>
-    <row r="143" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G143" s="219" t="s">
-        <v>178</v>
-      </c>
-      <c r="H143" s="220"/>
-      <c r="I143" s="21">
+      <c r="J144" s="222"/>
+      <c r="K144" s="222"/>
+      <c r="L144" s="10"/>
+      <c r="M144" s="304"/>
+      <c r="N144" s="304"/>
+      <c r="O144" s="304"/>
+      <c r="P144" s="10"/>
+    </row>
+    <row r="145" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G145" s="223" t="s">
+        <v>176</v>
+      </c>
+      <c r="H145" s="224"/>
+      <c r="I145" s="21">
         <f>Flujos!G61*Flujos!H61</f>
         <v>0</v>
       </c>
-      <c r="J143" s="221"/>
-      <c r="K143" s="221"/>
-      <c r="L143" s="10"/>
-      <c r="M143" s="221"/>
-      <c r="N143" s="221"/>
-      <c r="O143" s="221"/>
-      <c r="P143" s="10"/>
-    </row>
-    <row r="144" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G144" s="219"/>
-      <c r="H144" s="220"/>
-      <c r="I144" s="21"/>
-      <c r="J144" s="221"/>
-      <c r="K144" s="221"/>
-      <c r="L144" s="10"/>
-      <c r="M144" s="221"/>
-      <c r="N144" s="221"/>
-      <c r="O144" s="221"/>
-      <c r="P144" s="10"/>
-    </row>
-    <row r="145" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G145" s="219"/>
-      <c r="H145" s="220"/>
-      <c r="I145" s="21"/>
-      <c r="J145" s="221"/>
-      <c r="K145" s="221"/>
+      <c r="J145" s="222"/>
+      <c r="K145" s="222"/>
       <c r="L145" s="10"/>
-      <c r="M145" s="221"/>
-      <c r="N145" s="221"/>
-      <c r="O145" s="221"/>
+      <c r="M145" s="304"/>
+      <c r="N145" s="304"/>
+      <c r="O145" s="304"/>
       <c r="P145" s="10"/>
     </row>
     <row r="146" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G146" s="219"/>
-      <c r="H146" s="220"/>
-      <c r="I146" s="21"/>
-      <c r="J146" s="221"/>
-      <c r="K146" s="221"/>
+      <c r="G146" s="223" t="s">
+        <v>190</v>
+      </c>
+      <c r="H146" s="224"/>
+      <c r="I146" s="21">
+        <f>Flujos!G62*Flujos!H62</f>
+        <v>0</v>
+      </c>
+      <c r="J146" s="222"/>
+      <c r="K146" s="222"/>
       <c r="L146" s="10"/>
-      <c r="M146" s="221"/>
-      <c r="N146" s="221"/>
-      <c r="O146" s="221"/>
+      <c r="M146" s="304"/>
+      <c r="N146" s="304"/>
+      <c r="O146" s="304"/>
       <c r="P146" s="10"/>
     </row>
-    <row r="147" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G147" s="216" t="s">
+    <row r="147" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G147" s="223" t="s">
+        <v>201</v>
+      </c>
+      <c r="H147" s="224"/>
+      <c r="I147" s="21">
+        <f>Flujos!G66*Flujos!H66</f>
+        <v>0</v>
+      </c>
+      <c r="J147" s="11"/>
+      <c r="K147" s="11"/>
+      <c r="L147" s="10"/>
+      <c r="M147" s="11"/>
+      <c r="N147" s="11"/>
+      <c r="O147" s="11"/>
+      <c r="P147" s="10"/>
+    </row>
+    <row r="148" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G148" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="H148" s="20"/>
+      <c r="I148" s="21">
+        <f>Flujos!G67*Flujos!H67</f>
+        <v>0</v>
+      </c>
+      <c r="J148" s="11"/>
+      <c r="K148" s="11"/>
+      <c r="L148" s="10"/>
+      <c r="M148" s="11"/>
+      <c r="N148" s="11"/>
+      <c r="O148" s="11"/>
+      <c r="P148" s="10"/>
+    </row>
+    <row r="149" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G149" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="H149" s="20"/>
+      <c r="I149" s="21">
+        <f>Flujos!G70*Flujos!H70</f>
+        <v>0</v>
+      </c>
+      <c r="J149" s="222"/>
+      <c r="K149" s="222"/>
+      <c r="L149" s="10"/>
+      <c r="M149" s="222"/>
+      <c r="N149" s="222"/>
+      <c r="O149" s="222"/>
+      <c r="P149" s="10"/>
+    </row>
+    <row r="150" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G150" s="223"/>
+      <c r="H150" s="224"/>
+      <c r="I150" s="21"/>
+      <c r="J150" s="222"/>
+      <c r="K150" s="222"/>
+      <c r="L150" s="10"/>
+      <c r="M150" s="222"/>
+      <c r="N150" s="222"/>
+      <c r="O150" s="222"/>
+      <c r="P150" s="10"/>
+    </row>
+    <row r="151" spans="7:16" ht="19" x14ac:dyDescent="0.2">
+      <c r="G151" s="225" t="s">
+        <v>97</v>
+      </c>
+      <c r="H151" s="226"/>
+      <c r="I151" s="12">
+        <f>+SUM(I128:I150)</f>
+        <v>23000.680200000003</v>
+      </c>
+      <c r="J151" s="227" t="s">
+        <v>98</v>
+      </c>
+      <c r="K151" s="227"/>
+      <c r="L151" s="13">
+        <f>+SUM(L128:L141)</f>
+        <v>-7402.6198539840998</v>
+      </c>
+      <c r="M151" s="227" t="s">
         <v>99</v>
       </c>
-      <c r="H147" s="217"/>
-      <c r="I147" s="12">
-        <f>+SUM(I126:I146)</f>
-        <v>58920.976199999997</v>
-      </c>
-      <c r="J147" s="218" t="s">
+      <c r="N151" s="227"/>
+      <c r="O151" s="227"/>
+      <c r="P151" s="12">
+        <f>+SUM(P128:P141)</f>
+        <v>54390.674952396119</v>
+      </c>
+    </row>
+    <row r="152" spans="7:16" x14ac:dyDescent="0.2">
+      <c r="G152" s="14"/>
+      <c r="H152" s="14"/>
+      <c r="I152" s="14"/>
+      <c r="J152" s="14"/>
+      <c r="K152" s="14"/>
+      <c r="L152" s="14"/>
+      <c r="M152" s="14"/>
+      <c r="N152" s="14"/>
+      <c r="O152" s="14"/>
+      <c r="P152" s="14"/>
+    </row>
+    <row r="153" spans="7:16" ht="19" x14ac:dyDescent="0.2">
+      <c r="G153" s="14"/>
+      <c r="J153" s="14"/>
+      <c r="K153" s="14"/>
+      <c r="L153" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="K147" s="218"/>
-      <c r="L147" s="13">
-        <f>+SUM(L126:L139)</f>
-        <v>-7402.6198539840998</v>
-      </c>
-      <c r="M147" s="218" t="s">
-        <v>101</v>
-      </c>
-      <c r="N147" s="218"/>
-      <c r="O147" s="218"/>
-      <c r="P147" s="12">
-        <f>+SUM(P126:P139)</f>
-        <v>66323.596053947113</v>
-      </c>
-    </row>
-    <row r="148" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G148" s="14"/>
-      <c r="H148" s="14"/>
-      <c r="I148" s="14"/>
-      <c r="J148" s="14"/>
-      <c r="K148" s="14"/>
-      <c r="L148" s="14"/>
-      <c r="M148" s="14"/>
-      <c r="N148" s="14"/>
-      <c r="O148" s="14"/>
-      <c r="P148" s="14"/>
-    </row>
-    <row r="149" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G149" s="14"/>
-      <c r="J149" s="14"/>
-      <c r="K149" s="14"/>
-      <c r="L149" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="M149" s="16"/>
-      <c r="N149" s="17"/>
-      <c r="O149" s="16"/>
-      <c r="P149" s="18">
-        <f>+I147-L147-P147</f>
-        <v>3.6990968510508537E-8</v>
+      <c r="M153" s="16"/>
+      <c r="N153" s="17"/>
+      <c r="O153" s="16"/>
+      <c r="P153" s="18">
+        <f>+I151-L151-P151</f>
+        <v>-23987.374898412018</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="89">
-    <mergeCell ref="G125:I125"/>
-    <mergeCell ref="J125:L125"/>
-    <mergeCell ref="M125:P125"/>
-    <mergeCell ref="G126:H126"/>
-    <mergeCell ref="J126:K126"/>
-    <mergeCell ref="M126:O126"/>
+  <mergeCells count="88">
+    <mergeCell ref="J141:K141"/>
+    <mergeCell ref="G147:H147"/>
+    <mergeCell ref="M138:O138"/>
+    <mergeCell ref="M139:O139"/>
+    <mergeCell ref="G151:H151"/>
+    <mergeCell ref="J151:K151"/>
+    <mergeCell ref="M151:O151"/>
+    <mergeCell ref="G142:H142"/>
+    <mergeCell ref="J149:K149"/>
+    <mergeCell ref="M149:O149"/>
+    <mergeCell ref="G150:H150"/>
+    <mergeCell ref="J150:K150"/>
+    <mergeCell ref="M150:O150"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="J145:K145"/>
+    <mergeCell ref="G146:H146"/>
+    <mergeCell ref="J146:K146"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="J143:K143"/>
+    <mergeCell ref="G144:H144"/>
+    <mergeCell ref="J144:K144"/>
+    <mergeCell ref="J115:K115"/>
+    <mergeCell ref="M115:O115"/>
+    <mergeCell ref="J116:K116"/>
+    <mergeCell ref="M116:O116"/>
+    <mergeCell ref="J119:K119"/>
+    <mergeCell ref="M119:O119"/>
+    <mergeCell ref="J112:K112"/>
+    <mergeCell ref="M112:O112"/>
+    <mergeCell ref="J113:K113"/>
+    <mergeCell ref="M113:O113"/>
+    <mergeCell ref="J114:K114"/>
+    <mergeCell ref="M114:O114"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="M105:O105"/>
+    <mergeCell ref="M97:O97"/>
+    <mergeCell ref="M99:O99"/>
+    <mergeCell ref="M100:O100"/>
+    <mergeCell ref="M101:O101"/>
+    <mergeCell ref="M102:O102"/>
+    <mergeCell ref="M103:O103"/>
+    <mergeCell ref="M98:O98"/>
+    <mergeCell ref="M104:O104"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="M96:P96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="J101:K101"/>
     <mergeCell ref="M106:O106"/>
     <mergeCell ref="G110:H110"/>
     <mergeCell ref="J110:K110"/>
     <mergeCell ref="M110:O110"/>
-    <mergeCell ref="G118:H118"/>
-    <mergeCell ref="J118:K118"/>
-    <mergeCell ref="M118:O118"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="J120:K120"/>
+    <mergeCell ref="M120:O120"/>
     <mergeCell ref="J108:K108"/>
     <mergeCell ref="J109:K109"/>
     <mergeCell ref="M107:O107"/>
@@ -26499,73 +26822,12 @@
     <mergeCell ref="J111:K111"/>
     <mergeCell ref="M111:O111"/>
     <mergeCell ref="G112:H112"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="J106:K106"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="J101:K101"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="G96:I96"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="M96:P96"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="J97:K97"/>
-    <mergeCell ref="M105:O105"/>
-    <mergeCell ref="M97:O97"/>
-    <mergeCell ref="M99:O99"/>
-    <mergeCell ref="M100:O100"/>
-    <mergeCell ref="M101:O101"/>
-    <mergeCell ref="M102:O102"/>
-    <mergeCell ref="M103:O103"/>
-    <mergeCell ref="M98:O98"/>
-    <mergeCell ref="M104:O104"/>
-    <mergeCell ref="G113:H113"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="G117:H117"/>
-    <mergeCell ref="J112:K112"/>
-    <mergeCell ref="M112:O112"/>
-    <mergeCell ref="J113:K113"/>
-    <mergeCell ref="M113:O113"/>
-    <mergeCell ref="J114:K114"/>
-    <mergeCell ref="M114:O114"/>
-    <mergeCell ref="J115:K115"/>
-    <mergeCell ref="M115:O115"/>
-    <mergeCell ref="J116:K116"/>
-    <mergeCell ref="M116:O116"/>
-    <mergeCell ref="J117:K117"/>
-    <mergeCell ref="M117:O117"/>
-    <mergeCell ref="G141:H141"/>
-    <mergeCell ref="J141:K141"/>
-    <mergeCell ref="M141:O141"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="J142:K142"/>
-    <mergeCell ref="M142:O142"/>
-    <mergeCell ref="G147:H147"/>
-    <mergeCell ref="J147:K147"/>
-    <mergeCell ref="M147:O147"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="G145:H145"/>
-    <mergeCell ref="J145:K145"/>
-    <mergeCell ref="M145:O145"/>
-    <mergeCell ref="G146:H146"/>
-    <mergeCell ref="J146:K146"/>
-    <mergeCell ref="M146:O146"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="J143:K143"/>
-    <mergeCell ref="M143:O143"/>
-    <mergeCell ref="G144:H144"/>
-    <mergeCell ref="J144:K144"/>
-    <mergeCell ref="M144:O144"/>
+    <mergeCell ref="G127:I127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="M127:P127"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="M128:O128"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26742,7 +27004,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>L118</xm:sqref>
+          <xm:sqref>L120</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="1" id="{DB53FB84-6938-564F-81FC-41C7CEB5A866}">
@@ -26761,7 +27023,7 @@
               <x14:cfIcon iconSet="3Arrows" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>L147</xm:sqref>
+          <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="14" id="{F70366D2-FE7D-4A63-84D5-66BF541E67E6}">
@@ -26850,7 +27112,7 @@
   <sheetPr codeName="Hoja5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U46"/>
+  <dimension ref="B1:U49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="6.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="2.5" style="48" customWidth="1"/>
@@ -29438,85 +29700,85 @@
     <row r="3" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B3" s="49"/>
       <c r="C3" s="50"/>
-      <c r="D3" s="250"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="256" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="256"/>
-      <c r="H3" s="256"/>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="256"/>
-      <c r="L3" s="256"/>
-      <c r="M3" s="256"/>
-      <c r="N3" s="256"/>
-      <c r="O3" s="256"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="257"/>
+      <c r="D3" s="284"/>
+      <c r="E3" s="285"/>
+      <c r="F3" s="290" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="290"/>
+      <c r="H3" s="290"/>
+      <c r="I3" s="290"/>
+      <c r="J3" s="290"/>
+      <c r="K3" s="290"/>
+      <c r="L3" s="290"/>
+      <c r="M3" s="290"/>
+      <c r="N3" s="290"/>
+      <c r="O3" s="290"/>
+      <c r="P3" s="290"/>
+      <c r="Q3" s="291"/>
       <c r="R3" s="51"/>
     </row>
     <row r="4" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="49"/>
       <c r="C4" s="50"/>
-      <c r="D4" s="252"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="258"/>
-      <c r="K4" s="258"/>
-      <c r="L4" s="258"/>
-      <c r="M4" s="258"/>
-      <c r="N4" s="258"/>
-      <c r="O4" s="258"/>
-      <c r="P4" s="258"/>
-      <c r="Q4" s="259"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="287"/>
+      <c r="F4" s="292"/>
+      <c r="G4" s="292"/>
+      <c r="H4" s="292"/>
+      <c r="I4" s="292"/>
+      <c r="J4" s="292"/>
+      <c r="K4" s="292"/>
+      <c r="L4" s="292"/>
+      <c r="M4" s="292"/>
+      <c r="N4" s="292"/>
+      <c r="O4" s="292"/>
+      <c r="P4" s="292"/>
+      <c r="Q4" s="293"/>
       <c r="R4" s="51"/>
     </row>
     <row r="5" spans="2:20" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="49"/>
       <c r="C5" s="50"/>
-      <c r="D5" s="252"/>
-      <c r="E5" s="253"/>
-      <c r="F5" s="258" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
-      <c r="M5" s="258" t="s">
-        <v>109</v>
-      </c>
-      <c r="N5" s="258"/>
+      <c r="D5" s="286"/>
+      <c r="E5" s="287"/>
+      <c r="F5" s="292" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="292"/>
+      <c r="H5" s="292"/>
+      <c r="I5" s="292"/>
+      <c r="J5" s="292"/>
+      <c r="K5" s="292"/>
+      <c r="L5" s="292"/>
+      <c r="M5" s="292" t="s">
+        <v>107</v>
+      </c>
+      <c r="N5" s="292"/>
       <c r="O5" s="118"/>
-      <c r="P5" s="261">
+      <c r="P5" s="295">
         <v>45915</v>
       </c>
-      <c r="Q5" s="262"/>
+      <c r="Q5" s="296"/>
       <c r="R5" s="51"/>
     </row>
     <row r="6" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="49"/>
       <c r="C6" s="50"/>
-      <c r="D6" s="254"/>
-      <c r="E6" s="255"/>
-      <c r="F6" s="260"/>
-      <c r="G6" s="260"/>
-      <c r="H6" s="260"/>
-      <c r="I6" s="260"/>
-      <c r="J6" s="260"/>
-      <c r="K6" s="260"/>
-      <c r="L6" s="260"/>
-      <c r="M6" s="260"/>
-      <c r="N6" s="260"/>
+      <c r="D6" s="288"/>
+      <c r="E6" s="289"/>
+      <c r="F6" s="294"/>
+      <c r="G6" s="294"/>
+      <c r="H6" s="294"/>
+      <c r="I6" s="294"/>
+      <c r="J6" s="294"/>
+      <c r="K6" s="294"/>
+      <c r="L6" s="294"/>
+      <c r="M6" s="294"/>
+      <c r="N6" s="294"/>
       <c r="O6" s="119"/>
-      <c r="P6" s="263"/>
-      <c r="Q6" s="264"/>
+      <c r="P6" s="297"/>
+      <c r="Q6" s="298"/>
       <c r="R6" s="51"/>
     </row>
     <row r="7" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
@@ -29542,28 +29804,28 @@
       <c r="D8" s="276"/>
       <c r="E8" s="277"/>
       <c r="F8" s="277"/>
-      <c r="G8" s="265" t="s">
+      <c r="G8" s="273" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="274"/>
+      <c r="I8" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J8" s="57" t="s">
         <v>110</v>
-      </c>
-      <c r="H8" s="266"/>
-      <c r="I8" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="J8" s="57" t="s">
-        <v>112</v>
       </c>
       <c r="K8" s="280"/>
       <c r="L8" s="281"/>
       <c r="M8" s="281"/>
-      <c r="N8" s="265" t="s">
+      <c r="N8" s="273" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" s="274"/>
+      <c r="P8" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q8" s="57" t="s">
         <v>110</v>
-      </c>
-      <c r="O8" s="266"/>
-      <c r="P8" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q8" s="57" t="s">
-        <v>112</v>
       </c>
       <c r="R8" s="51"/>
     </row>
@@ -29577,10 +29839,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I9" s="58" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J9" s="59" t="s">
         <v>34</v>
@@ -29592,10 +29854,10 @@
         <v>1</v>
       </c>
       <c r="O9" s="58" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P9" s="58" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="59" t="s">
         <v>34</v>
@@ -29605,36 +29867,36 @@
     <row r="10" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B10" s="54"/>
       <c r="C10" s="55"/>
-      <c r="D10" s="267" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="268"/>
-      <c r="F10" s="268"/>
-      <c r="G10" s="268"/>
-      <c r="H10" s="268"/>
-      <c r="I10" s="268"/>
-      <c r="J10" s="269"/>
-      <c r="K10" s="270" t="s">
-        <v>153</v>
-      </c>
-      <c r="L10" s="271"/>
-      <c r="M10" s="271"/>
-      <c r="N10" s="271"/>
-      <c r="O10" s="271"/>
-      <c r="P10" s="271"/>
-      <c r="Q10" s="272"/>
+      <c r="D10" s="238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="239"/>
+      <c r="F10" s="239"/>
+      <c r="G10" s="239"/>
+      <c r="H10" s="239"/>
+      <c r="I10" s="239"/>
+      <c r="J10" s="275"/>
+      <c r="K10" s="235" t="s">
+        <v>151</v>
+      </c>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+      <c r="Q10" s="237"/>
       <c r="R10" s="51"/>
     </row>
     <row r="11" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="54"/>
       <c r="C11" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="244" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" s="245"/>
-      <c r="F11" s="246"/>
+        <v>112</v>
+      </c>
+      <c r="D11" s="246" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11" s="247"/>
+      <c r="F11" s="248"/>
       <c r="G11" s="61">
         <f>Flujos!G4</f>
         <v>150420</v>
@@ -29651,11 +29913,11 @@
         <f>+I11*G11</f>
         <v>35920.295999999995</v>
       </c>
-      <c r="K11" s="273" t="s">
-        <v>116</v>
-      </c>
-      <c r="L11" s="274"/>
-      <c r="M11" s="275"/>
+      <c r="K11" s="241" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="242"/>
+      <c r="M11" s="243"/>
       <c r="N11" s="107">
         <f>Flujos!G20</f>
         <v>66012</v>
@@ -29678,11 +29940,11 @@
     <row r="12" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B12" s="54"/>
       <c r="C12" s="55"/>
-      <c r="D12" s="273" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="274"/>
-      <c r="F12" s="275"/>
+      <c r="D12" s="241" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="242"/>
+      <c r="F12" s="243"/>
       <c r="G12" s="62">
         <f>Flujos!G5</f>
         <v>0</v>
@@ -29699,26 +29961,26 @@
         <f>+I12*G12</f>
         <v>0</v>
       </c>
-      <c r="K12" s="284" t="s">
-        <v>127</v>
-      </c>
-      <c r="L12" s="285"/>
-      <c r="M12" s="285"/>
-      <c r="N12" s="285"/>
-      <c r="O12" s="285"/>
-      <c r="P12" s="285"/>
-      <c r="Q12" s="286"/>
+      <c r="K12" s="264" t="s">
+        <v>125</v>
+      </c>
+      <c r="L12" s="265"/>
+      <c r="M12" s="265"/>
+      <c r="N12" s="265"/>
+      <c r="O12" s="265"/>
+      <c r="P12" s="265"/>
+      <c r="Q12" s="266"/>
       <c r="R12" s="51"/>
       <c r="T12" s="83"/>
     </row>
     <row r="13" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B13" s="54"/>
       <c r="C13" s="55"/>
-      <c r="D13" s="244" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" s="245"/>
-      <c r="F13" s="246"/>
+      <c r="D13" s="246" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="247"/>
+      <c r="F13" s="248"/>
       <c r="G13" s="60">
         <f>Flujos!G8</f>
         <v>0</v>
@@ -29735,11 +29997,11 @@
         <f>+I13*G13</f>
         <v>0</v>
       </c>
-      <c r="K13" s="236" t="s">
-        <v>128</v>
-      </c>
-      <c r="L13" s="237"/>
-      <c r="M13" s="238"/>
+      <c r="K13" s="267" t="s">
+        <v>126</v>
+      </c>
+      <c r="L13" s="268"/>
+      <c r="M13" s="269"/>
       <c r="N13" s="60">
         <f>Flujos!G6</f>
         <v>60303</v>
@@ -29761,11 +30023,11 @@
     <row r="14" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B14" s="54"/>
       <c r="C14" s="55"/>
-      <c r="D14" s="273" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="274"/>
-      <c r="F14" s="275"/>
+      <c r="D14" s="241" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="242"/>
+      <c r="F14" s="243"/>
       <c r="G14" s="62">
         <f>Flujos!G55</f>
         <v>37855</v>
@@ -29782,11 +30044,11 @@
         <f>+I14*G14</f>
         <v>19063.778000000002</v>
       </c>
-      <c r="K14" s="247" t="s">
-        <v>130</v>
-      </c>
-      <c r="L14" s="248"/>
-      <c r="M14" s="249"/>
+      <c r="K14" s="270" t="s">
+        <v>128</v>
+      </c>
+      <c r="L14" s="271"/>
+      <c r="M14" s="272"/>
       <c r="N14" s="71">
         <f>Flujos!G12</f>
         <v>20626.123299999999</v>
@@ -29808,11 +30070,11 @@
     <row r="15" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="54"/>
       <c r="C15" s="55"/>
-      <c r="D15" s="244" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="245"/>
-      <c r="F15" s="246"/>
+      <c r="D15" s="246" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="247"/>
+      <c r="F15" s="248"/>
       <c r="G15" s="60">
         <f>Flujos!G31</f>
         <v>0</v>
@@ -29829,11 +30091,11 @@
         <f>+I15*G15</f>
         <v>0</v>
       </c>
-      <c r="K15" s="236" t="s">
-        <v>131</v>
-      </c>
-      <c r="L15" s="237"/>
-      <c r="M15" s="238"/>
+      <c r="K15" s="267" t="s">
+        <v>129</v>
+      </c>
+      <c r="L15" s="268"/>
+      <c r="M15" s="269"/>
       <c r="N15" s="72">
         <f>Flujos!G13</f>
         <v>14883.876700000001</v>
@@ -29852,18 +30114,18 @@
     <row r="16" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B16" s="54"/>
       <c r="C16" s="55"/>
-      <c r="D16" s="273"/>
-      <c r="E16" s="274"/>
-      <c r="F16" s="275"/>
+      <c r="D16" s="241"/>
+      <c r="E16" s="242"/>
+      <c r="F16" s="243"/>
       <c r="G16" s="62"/>
       <c r="H16" s="62"/>
       <c r="I16" s="64"/>
       <c r="J16" s="62"/>
-      <c r="K16" s="247" t="s">
-        <v>133</v>
-      </c>
-      <c r="L16" s="248"/>
-      <c r="M16" s="249"/>
+      <c r="K16" s="270" t="s">
+        <v>131</v>
+      </c>
+      <c r="L16" s="271"/>
+      <c r="M16" s="272"/>
       <c r="N16" s="71">
         <f>Flujos!G19</f>
         <v>43841</v>
@@ -29879,54 +30141,54 @@
       </c>
       <c r="R16" s="51"/>
     </row>
-    <row r="17" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B17" s="54"/>
       <c r="C17" s="55"/>
-      <c r="D17" s="244"/>
-      <c r="E17" s="245"/>
-      <c r="F17" s="246"/>
+      <c r="D17" s="246"/>
+      <c r="E17" s="247"/>
+      <c r="F17" s="248"/>
       <c r="G17" s="60"/>
       <c r="H17" s="60"/>
       <c r="I17" s="63"/>
       <c r="J17" s="60"/>
-      <c r="K17" s="236"/>
-      <c r="L17" s="237"/>
-      <c r="M17" s="238"/>
+      <c r="K17" s="267"/>
+      <c r="L17" s="268"/>
+      <c r="M17" s="269"/>
       <c r="N17" s="72"/>
       <c r="O17" s="61"/>
       <c r="P17" s="193"/>
       <c r="Q17" s="60"/>
       <c r="R17" s="51"/>
     </row>
-    <row r="18" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="54"/>
       <c r="C18" s="55"/>
-      <c r="D18" s="273"/>
-      <c r="E18" s="274"/>
-      <c r="F18" s="275"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="243"/>
       <c r="G18" s="62"/>
       <c r="H18" s="62"/>
       <c r="I18" s="64"/>
       <c r="J18" s="62"/>
-      <c r="K18" s="247"/>
-      <c r="L18" s="248"/>
-      <c r="M18" s="249"/>
+      <c r="K18" s="270"/>
+      <c r="L18" s="271"/>
+      <c r="M18" s="272"/>
       <c r="N18" s="71"/>
       <c r="O18" s="71"/>
       <c r="P18" s="192"/>
       <c r="Q18" s="62"/>
       <c r="R18" s="51"/>
     </row>
-    <row r="19" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="54"/>
       <c r="C19" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="242" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" s="243"/>
-      <c r="F19" s="243"/>
+        <v>122</v>
+      </c>
+      <c r="D19" s="244" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="245"/>
+      <c r="F19" s="245"/>
       <c r="G19" s="65">
         <f>+SUM(G11:G15)</f>
         <v>188275</v>
@@ -29940,11 +30202,11 @@
         <f>+SUM(J11:J15)</f>
         <v>54984.073999999993</v>
       </c>
-      <c r="K19" s="239" t="s">
-        <v>125</v>
-      </c>
-      <c r="L19" s="240"/>
-      <c r="M19" s="241"/>
+      <c r="K19" s="249" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" s="250"/>
+      <c r="M19" s="251"/>
       <c r="N19" s="65">
         <f>+SUM(N13:N16)</f>
         <v>139654</v>
@@ -29962,38 +30224,38 @@
       <c r="S19" s="174"/>
       <c r="T19" s="67"/>
     </row>
-    <row r="20" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
-      <c r="D20" s="267" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" s="268"/>
-      <c r="F20" s="268"/>
-      <c r="G20" s="268"/>
-      <c r="H20" s="268"/>
-      <c r="I20" s="268"/>
-      <c r="J20" s="299"/>
-      <c r="K20" s="270" t="s">
-        <v>154</v>
-      </c>
-      <c r="L20" s="271"/>
-      <c r="M20" s="271"/>
-      <c r="N20" s="271"/>
-      <c r="O20" s="271"/>
-      <c r="P20" s="271"/>
-      <c r="Q20" s="272"/>
+      <c r="D20" s="238" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="239"/>
+      <c r="F20" s="239"/>
+      <c r="G20" s="239"/>
+      <c r="H20" s="239"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="240"/>
+      <c r="K20" s="235" t="s">
+        <v>152</v>
+      </c>
+      <c r="L20" s="236"/>
+      <c r="M20" s="236"/>
+      <c r="N20" s="236"/>
+      <c r="O20" s="236"/>
+      <c r="P20" s="236"/>
+      <c r="Q20" s="237"/>
       <c r="R20" s="51"/>
       <c r="S20" s="68"/>
     </row>
-    <row r="21" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="54"/>
       <c r="C21" s="55"/>
-      <c r="D21" s="244" t="s">
+      <c r="D21" s="246" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="245"/>
-      <c r="F21" s="246"/>
+      <c r="E21" s="247"/>
+      <c r="F21" s="248"/>
       <c r="G21" s="122">
         <f>'Mapa de Procesos'!P102</f>
         <v>73127</v>
@@ -30010,11 +30272,11 @@
         <f>+I21*G21</f>
         <v>47634.927799999998</v>
       </c>
-      <c r="K21" s="300" t="s">
-        <v>136</v>
-      </c>
-      <c r="L21" s="301"/>
-      <c r="M21" s="302"/>
+      <c r="K21" s="252" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" s="253"/>
+      <c r="M21" s="254"/>
       <c r="N21" s="61">
         <f>Flujos!G25</f>
         <v>69689</v>
@@ -30028,20 +30290,20 @@
         <v>0.65110195969000006</v>
       </c>
       <c r="Q21" s="60">
-        <f t="shared" ref="Q21:Q28" si="0">+P21*N21</f>
+        <f t="shared" ref="Q21:Q31" si="0">+P21*N21</f>
         <v>45374.644468836414</v>
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="173"/>
     </row>
-    <row r="22" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B22" s="54"/>
       <c r="C22" s="55"/>
-      <c r="D22" s="273" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="274"/>
-      <c r="F22" s="275"/>
+      <c r="D22" s="241" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" s="242"/>
+      <c r="F22" s="243"/>
       <c r="G22" s="69">
         <f>Flujos!G33</f>
         <v>0</v>
@@ -30059,7 +30321,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="198" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L22" s="199"/>
       <c r="M22" s="200"/>
@@ -30082,14 +30344,14 @@
       <c r="R22" s="51"/>
       <c r="S22" s="173"/>
     </row>
-    <row r="23" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B23" s="54"/>
       <c r="C23" s="55"/>
-      <c r="D23" s="244" t="s">
+      <c r="D23" s="246" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="245"/>
-      <c r="F23" s="246"/>
+      <c r="E23" s="247"/>
+      <c r="F23" s="248"/>
       <c r="G23" s="122">
         <f>Flujos!G40</f>
         <v>0</v>
@@ -30107,7 +30369,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="195" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L23" s="196"/>
       <c r="M23" s="197"/>
@@ -30130,20 +30392,20 @@
       <c r="R23" s="51"/>
       <c r="S23" s="173"/>
     </row>
-    <row r="24" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B24" s="54"/>
       <c r="C24" s="55"/>
-      <c r="D24" s="273" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" s="274"/>
-      <c r="F24" s="275"/>
+      <c r="D24" s="241" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="242"/>
+      <c r="F24" s="243"/>
       <c r="G24" s="69">
         <f>Flujos!G58</f>
         <v>0</v>
       </c>
       <c r="H24" s="69">
-        <f>G24/(1-'Datos Extra'!B27)</f>
+        <f>G24/(1-'Datos Extra'!D41)</f>
         <v>0</v>
       </c>
       <c r="I24" s="70">
@@ -30155,7 +30417,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="198" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L24" s="199"/>
       <c r="M24" s="200"/>
@@ -30178,18 +30440,32 @@
       <c r="R24" s="51"/>
       <c r="S24" s="173"/>
     </row>
-    <row r="25" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B25" s="54"/>
       <c r="C25" s="55"/>
-      <c r="D25" s="244"/>
-      <c r="E25" s="245"/>
-      <c r="F25" s="246"/>
-      <c r="G25" s="122"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="121"/>
-      <c r="J25" s="61"/>
+      <c r="D25" s="246" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="247"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="122">
+        <f>Flujos!G68</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="122">
+        <f>G25/(1-'Datos Extra'!B28)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="121">
+        <f>Flujos!H68</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="61">
+        <f>G25*I25</f>
+        <v>0</v>
+      </c>
       <c r="K25" s="195" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L25" s="196"/>
       <c r="M25" s="197"/>
@@ -30212,7 +30488,7 @@
       <c r="R25" s="51"/>
       <c r="S25" s="68"/>
     </row>
-    <row r="26" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B26" s="54"/>
       <c r="C26" s="55"/>
       <c r="D26" s="195"/>
@@ -30222,311 +30498,289 @@
       <c r="H26" s="122"/>
       <c r="I26" s="121"/>
       <c r="J26" s="61"/>
-      <c r="K26" s="195" t="s">
-        <v>190</v>
-      </c>
-      <c r="L26" s="196"/>
-      <c r="M26" s="197"/>
-      <c r="N26" s="61">
-        <f>Flujos!G65</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="61">
+      <c r="K26" s="198" t="s">
+        <v>199</v>
+      </c>
+      <c r="L26" s="199"/>
+      <c r="M26" s="200"/>
+      <c r="N26" s="107">
+        <f>Flujos!G66</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="107">
         <f>N26/(1-'Datos Extra'!D41)</f>
         <v>0</v>
       </c>
-      <c r="P26" s="191">
-        <f>Flujos!H65</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="60">
+      <c r="P26" s="190">
+        <f>Flujos!H66</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R26" s="51"/>
       <c r="S26" s="68"/>
     </row>
-    <row r="27" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B27" s="54"/>
       <c r="C27" s="55"/>
-      <c r="D27" s="273"/>
-      <c r="E27" s="274"/>
-      <c r="F27" s="275"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="198" t="s">
-        <v>122</v>
-      </c>
-      <c r="L27" s="199"/>
-      <c r="M27" s="200"/>
-      <c r="N27" s="107">
-        <f>Flujos!G37</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="107">
-        <f>N27/(1-'Datos Extra'!B33)</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="161">
-        <f>Flujos!H37</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="107">
+      <c r="D27" s="195"/>
+      <c r="E27" s="196"/>
+      <c r="F27" s="197"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="122"/>
+      <c r="I27" s="121"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="195" t="s">
+        <v>200</v>
+      </c>
+      <c r="L27" s="196"/>
+      <c r="M27" s="197"/>
+      <c r="N27" s="61">
+        <f>Flujos!G67</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="61">
+        <f>N27/(1-'Datos Extra'!D42)</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="191">
+        <f>Flujos!H67</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R27" s="51"/>
-    </row>
-    <row r="28" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="S27" s="68"/>
+    </row>
+    <row r="28" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="54"/>
       <c r="C28" s="55"/>
-      <c r="D28" s="244"/>
-      <c r="E28" s="245"/>
-      <c r="F28" s="246"/>
+      <c r="D28" s="195"/>
+      <c r="E28" s="196"/>
+      <c r="F28" s="197"/>
       <c r="G28" s="122"/>
       <c r="H28" s="122"/>
       <c r="I28" s="121"/>
       <c r="J28" s="61"/>
-      <c r="K28" s="195" t="s">
-        <v>123</v>
-      </c>
-      <c r="L28" s="196"/>
-      <c r="M28" s="197"/>
-      <c r="N28" s="61">
-        <f>Flujos!G38</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="61">
-        <f>N28/(1-'Datos Extra'!B34)</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="63">
-        <f>Flujos!H38</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="60">
+      <c r="K28" s="198" t="s">
+        <v>188</v>
+      </c>
+      <c r="L28" s="199"/>
+      <c r="M28" s="200"/>
+      <c r="N28" s="107">
+        <f>Flujos!G65</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="107">
+        <f>N28/(1-'Datos Extra'!D41)</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="190">
+        <f>Flujos!H65</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R28" s="51"/>
-      <c r="S28" s="173"/>
-    </row>
-    <row r="29" spans="2:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="S28" s="68"/>
+    </row>
+    <row r="29" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B29" s="54"/>
       <c r="C29" s="55"/>
-      <c r="D29" s="242" t="s">
-        <v>125</v>
-      </c>
-      <c r="E29" s="243"/>
-      <c r="F29" s="243"/>
-      <c r="G29" s="65">
+      <c r="D29" s="195"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="197"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="122"/>
+      <c r="I29" s="121"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="195" t="s">
+        <v>197</v>
+      </c>
+      <c r="L29" s="196"/>
+      <c r="M29" s="197"/>
+      <c r="N29" s="61">
+        <f>Flujos!G70</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="61">
+        <f>N29/(1-'Datos Extra'!D44)</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="191">
+        <f>Flujos!H70%</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="51"/>
+      <c r="S29" s="68"/>
+    </row>
+    <row r="30" spans="2:20" ht="14" x14ac:dyDescent="0.2">
+      <c r="B30" s="54"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="241"/>
+      <c r="E30" s="242"/>
+      <c r="F30" s="243"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="198" t="s">
+        <v>120</v>
+      </c>
+      <c r="L30" s="199"/>
+      <c r="M30" s="200"/>
+      <c r="N30" s="107">
+        <f>Flujos!G37</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="107">
+        <f>N30/(1-'Datos Extra'!B33)</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="161">
+        <f>Flujos!H37</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="51"/>
+    </row>
+    <row r="31" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="247"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="122"/>
+      <c r="I31" s="121"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="195" t="s">
+        <v>121</v>
+      </c>
+      <c r="L31" s="196"/>
+      <c r="M31" s="197"/>
+      <c r="N31" s="61">
+        <f>Flujos!G38</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="61">
+        <f>N31/(1-'Datos Extra'!B34)</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="63">
+        <f>Flujos!H38</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="51"/>
+      <c r="S31" s="173"/>
+    </row>
+    <row r="32" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="54"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="244" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="245"/>
+      <c r="F32" s="245"/>
+      <c r="G32" s="65">
         <f>+SUM(G21:G24)</f>
         <v>73127</v>
       </c>
-      <c r="H29" s="65">
+      <c r="H32" s="65">
         <f>+SUM(H21:H24)</f>
         <v>80030.424409569459</v>
       </c>
-      <c r="I29" s="81"/>
-      <c r="J29" s="65">
+      <c r="I32" s="81"/>
+      <c r="J32" s="65">
         <f>+SUM(J21:J24)</f>
         <v>47634.927799999998</v>
       </c>
-      <c r="K29" s="239" t="s">
-        <v>125</v>
-      </c>
-      <c r="L29" s="240"/>
-      <c r="M29" s="241"/>
-      <c r="N29" s="65">
-        <f>SUM(N21:N28)</f>
+      <c r="K32" s="249" t="s">
+        <v>123</v>
+      </c>
+      <c r="L32" s="250"/>
+      <c r="M32" s="251"/>
+      <c r="N32" s="65">
+        <f>SUM(N21:N31)</f>
         <v>75915</v>
       </c>
-      <c r="O29" s="65">
-        <f>SUM(O21:O28)</f>
+      <c r="O32" s="65">
+        <f>SUM(O21:O31)</f>
         <v>83059.569298257455</v>
       </c>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="66">
-        <f>SUM(Q21:Q28)</f>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="66">
+        <f>SUM(Q21:Q31)</f>
         <v>49311.546668836418</v>
       </c>
-      <c r="R29" s="51"/>
-      <c r="S29" s="173"/>
-    </row>
-    <row r="30" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="54"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="201"/>
-      <c r="E30" s="201"/>
-      <c r="F30" s="201"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="75"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="173"/>
-    </row>
-    <row r="31" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="54"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="296" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" s="297"/>
-      <c r="F31" s="297"/>
-      <c r="G31" s="297"/>
-      <c r="H31" s="298"/>
-      <c r="R31" s="76"/>
-    </row>
-    <row r="32" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="54"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="290"/>
-      <c r="E32" s="291"/>
-      <c r="F32" s="292"/>
-      <c r="G32" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="86" t="s">
-        <v>1</v>
-      </c>
-      <c r="I32" s="176" t="s">
-        <v>157</v>
-      </c>
-      <c r="J32" s="176" t="s">
-        <v>158</v>
-      </c>
-      <c r="L32" s="164"/>
-      <c r="M32" s="164"/>
-      <c r="N32" s="164"/>
-      <c r="O32" s="164"/>
-      <c r="P32" s="164"/>
-      <c r="Q32" s="164"/>
       <c r="R32" s="51"/>
-      <c r="U32" s="77"/>
-    </row>
-    <row r="33" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="S32" s="173"/>
+    </row>
+    <row r="33" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B33" s="54"/>
       <c r="C33" s="55"/>
-      <c r="D33" s="293" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="294"/>
-      <c r="F33" s="295"/>
-      <c r="G33" s="167">
-        <f>'Datos Extra'!B1</f>
-        <v>11665</v>
-      </c>
-      <c r="H33" s="129">
-        <f>G33*(1-'Datos Extra'!D1)</f>
-        <v>11548.35</v>
-      </c>
-      <c r="I33" s="177">
-        <f>Flujos!G9</f>
-        <v>-26556</v>
-      </c>
-      <c r="J33" s="177">
-        <f>'Mapa de Procesos'!L126</f>
-        <v>-9452.6291970325201</v>
-      </c>
-      <c r="K33" s="164"/>
-      <c r="L33" s="164"/>
-      <c r="M33" s="164"/>
-      <c r="N33" s="164"/>
-      <c r="O33" s="164"/>
-      <c r="P33" s="164"/>
-      <c r="Q33" s="164"/>
-      <c r="R33" s="76"/>
-      <c r="U33" s="77"/>
-    </row>
-    <row r="34" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="D33" s="201"/>
+      <c r="E33" s="201"/>
+      <c r="F33" s="201"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="75"/>
+      <c r="R33" s="51"/>
+      <c r="S33" s="173"/>
+    </row>
+    <row r="34" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="54"/>
       <c r="C34" s="55"/>
-      <c r="D34" s="244" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="245"/>
-      <c r="F34" s="245"/>
-      <c r="G34" s="168">
-        <f>'Datos Extra'!B2</f>
-        <v>32218.641698563333</v>
-      </c>
-      <c r="H34" s="169">
-        <f>G34*(1-'Datos Extra'!D2)</f>
-        <v>31896.455281577699</v>
-      </c>
-      <c r="I34" s="177">
-        <f>Flujos!G17</f>
-        <v>9165</v>
-      </c>
-      <c r="J34" s="177">
-        <f>'Mapa de Procesos'!L127</f>
-        <v>3739.5701419030502</v>
-      </c>
-      <c r="K34" s="164"/>
-      <c r="L34" s="164"/>
-      <c r="M34" s="164" t="s">
-        <v>71</v>
-      </c>
-      <c r="N34" s="164" t="s">
-        <v>73</v>
-      </c>
-      <c r="O34" s="164" t="s">
-        <v>155</v>
-      </c>
-      <c r="P34" s="164" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q34" s="164"/>
-      <c r="R34" s="51"/>
-      <c r="U34" s="77"/>
-    </row>
-    <row r="35" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="D34" s="258" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" s="259"/>
+      <c r="F34" s="259"/>
+      <c r="G34" s="259"/>
+      <c r="H34" s="260"/>
+      <c r="R34" s="76"/>
+    </row>
+    <row r="35" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="54"/>
       <c r="C35" s="55"/>
-      <c r="D35" s="244" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="245"/>
-      <c r="F35" s="245"/>
-      <c r="G35" s="168">
-        <f>'Datos Extra'!B3</f>
-        <v>33</v>
-      </c>
-      <c r="H35" s="169">
-        <f>G35*(1-'Datos Extra'!D3)</f>
-        <v>30.048699798294241</v>
-      </c>
-      <c r="I35" s="177">
-        <f>Flujos!G21</f>
-        <v>-5099</v>
-      </c>
-      <c r="J35" s="177">
-        <f>'Mapa de Procesos'!L129</f>
-        <v>-3366.1796673720501</v>
-      </c>
-      <c r="K35" s="164"/>
-      <c r="L35" s="164" t="s">
+      <c r="D35" s="255"/>
+      <c r="E35" s="256"/>
+      <c r="F35" s="257"/>
+      <c r="G35" s="85" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="M35" s="163">
-        <f>G19+N22+N23+N24+N27+N28</f>
-        <v>191432</v>
-      </c>
-      <c r="N35" s="163">
-        <f>G21+G22+G23+N19+G24</f>
-        <v>212781</v>
-      </c>
-      <c r="O35" s="165">
-        <f>I40</f>
-        <v>-19702</v>
-      </c>
-      <c r="P35" s="163">
-        <f>M35-N35-O35</f>
-        <v>-1647</v>
-      </c>
+      <c r="I35" s="176" t="s">
+        <v>155</v>
+      </c>
+      <c r="J35" s="176" t="s">
+        <v>156</v>
+      </c>
+      <c r="L35" s="164"/>
+      <c r="M35" s="164"/>
+      <c r="N35" s="164"/>
+      <c r="O35" s="164"/>
+      <c r="P35" s="164"/>
       <c r="Q35" s="164"/>
       <c r="R35" s="51"/>
       <c r="U35" s="77"/>
@@ -30534,47 +30788,33 @@
     <row r="36" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B36" s="54"/>
       <c r="C36" s="55"/>
-      <c r="D36" s="244" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="245"/>
-      <c r="F36" s="245"/>
-      <c r="G36" s="168">
-        <f>'Datos Extra'!B4</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="169">
-        <f>G36*(1-'Datos Extra'!D4)</f>
-        <v>0</v>
+      <c r="D36" s="241" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="242"/>
+      <c r="F36" s="242"/>
+      <c r="G36" s="167">
+        <f>'Datos Extra'!B1</f>
+        <v>11665</v>
+      </c>
+      <c r="H36" s="129">
+        <f>G36*(1-'Datos Extra'!D1)</f>
+        <v>11548.35</v>
       </c>
       <c r="I36" s="177">
-        <f>Flujos!G31</f>
-        <v>0</v>
+        <f>Flujos!G9</f>
+        <v>-26556</v>
       </c>
       <c r="J36" s="177">
-        <f>'Mapa de Procesos'!L130</f>
-        <v>0</v>
+        <f>'Mapa de Procesos'!L128</f>
+        <v>-9452.6291970325201</v>
       </c>
       <c r="K36" s="164"/>
-      <c r="L36" s="164" t="s">
-        <v>34</v>
-      </c>
-      <c r="M36" s="163">
-        <f>J19+Q22+Q23+Q24+Q27+Q28</f>
-        <v>56987.506199999996</v>
-      </c>
-      <c r="N36" s="163">
-        <f>Q19+J21+J22+J23+J24</f>
-        <v>65401.8577300529</v>
-      </c>
-      <c r="O36" s="166">
-        <f>J40</f>
-        <v>-7402.6198539840998</v>
-      </c>
-      <c r="P36" s="163">
-        <f>M36-N36-O36</f>
-        <v>-1011.7316760688036</v>
-      </c>
+      <c r="L36" s="164"/>
+      <c r="M36" s="164"/>
+      <c r="N36" s="164"/>
+      <c r="O36" s="164"/>
+      <c r="P36" s="164"/>
       <c r="Q36" s="164"/>
       <c r="R36" s="76"/>
       <c r="U36" s="77"/>
@@ -30582,33 +30822,41 @@
     <row r="37" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B37" s="54"/>
       <c r="C37" s="55"/>
-      <c r="D37" s="273" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="274"/>
-      <c r="F37" s="274"/>
+      <c r="D37" s="241" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="242"/>
+      <c r="F37" s="242"/>
       <c r="G37" s="168">
-        <f>'Datos Extra'!B5</f>
-        <v>108658.53000000003</v>
+        <f>'Datos Extra'!B2</f>
+        <v>32218.641698563333</v>
       </c>
       <c r="H37" s="169">
-        <f>G37*(1-'Datos Extra'!D5)</f>
-        <v>98640.574400793892</v>
+        <f>G37*(1-'Datos Extra'!D2)</f>
+        <v>31896.455281577699</v>
       </c>
       <c r="I37" s="177">
-        <f>Flujos!G26</f>
-        <v>-3438</v>
+        <f>Flujos!G17</f>
+        <v>9165</v>
       </c>
       <c r="J37" s="177">
-        <f>'Mapa de Procesos'!L136</f>
-        <v>-2260.2833314581599</v>
+        <f>'Mapa de Procesos'!L129</f>
+        <v>3739.5701419030502</v>
       </c>
       <c r="K37" s="164"/>
-      <c r="L37" s="163"/>
-      <c r="M37" s="164"/>
-      <c r="N37" s="164"/>
-      <c r="O37" s="164"/>
-      <c r="P37" s="164"/>
+      <c r="L37" s="164"/>
+      <c r="M37" s="164" t="s">
+        <v>69</v>
+      </c>
+      <c r="N37" s="164" t="s">
+        <v>71</v>
+      </c>
+      <c r="O37" s="164" t="s">
+        <v>153</v>
+      </c>
+      <c r="P37" s="164" t="s">
+        <v>154</v>
+      </c>
       <c r="Q37" s="164"/>
       <c r="R37" s="51"/>
       <c r="U37" s="77"/>
@@ -30616,161 +30864,280 @@
     <row r="38" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B38" s="54"/>
       <c r="C38" s="55"/>
-      <c r="D38" s="273" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" s="274"/>
-      <c r="F38" s="274"/>
+      <c r="D38" s="241" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="242"/>
+      <c r="F38" s="242"/>
       <c r="G38" s="168">
+        <f>'Datos Extra'!B3</f>
+        <v>33</v>
+      </c>
+      <c r="H38" s="169">
+        <f>G38*(1-'Datos Extra'!D3)</f>
+        <v>30.048699798294241</v>
+      </c>
+      <c r="I38" s="177">
+        <f>Flujos!G21</f>
+        <v>-5099</v>
+      </c>
+      <c r="J38" s="177">
+        <f>'Mapa de Procesos'!L131</f>
+        <v>-3366.1796673720501</v>
+      </c>
+      <c r="K38" s="164"/>
+      <c r="L38" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="M38" s="163">
+        <f>G19+N22+N23+N24+N30+N31</f>
+        <v>191432</v>
+      </c>
+      <c r="N38" s="163">
+        <f>G21+G22+G23+N19+G24</f>
+        <v>212781</v>
+      </c>
+      <c r="O38" s="165">
+        <f>I43</f>
+        <v>-19702</v>
+      </c>
+      <c r="P38" s="163">
+        <f>M38-N38-O38</f>
+        <v>-1647</v>
+      </c>
+      <c r="Q38" s="164"/>
+      <c r="R38" s="51"/>
+      <c r="U38" s="77"/>
+    </row>
+    <row r="39" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="B39" s="54"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="241" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="242"/>
+      <c r="F39" s="242"/>
+      <c r="G39" s="168">
+        <f>'Datos Extra'!B4</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="169">
+        <f>G39*(1-'Datos Extra'!D4)</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="177">
+        <f>Flujos!G31</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="177">
+        <f>'Mapa de Procesos'!L132</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="164"/>
+      <c r="L39" s="164" t="s">
+        <v>34</v>
+      </c>
+      <c r="M39" s="163">
+        <f>J19+Q22+Q23+Q24+Q30+Q31</f>
+        <v>56987.506199999996</v>
+      </c>
+      <c r="N39" s="163">
+        <f>Q19+J21+J22+J23+J24</f>
+        <v>65401.8577300529</v>
+      </c>
+      <c r="O39" s="166">
+        <f>J43</f>
+        <v>-7402.6198539840998</v>
+      </c>
+      <c r="P39" s="163">
+        <f>M39-N39-O39</f>
+        <v>-1011.7316760688036</v>
+      </c>
+      <c r="Q39" s="164"/>
+      <c r="R39" s="76"/>
+      <c r="U39" s="77"/>
+    </row>
+    <row r="40" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="B40" s="54"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="241" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="242"/>
+      <c r="F40" s="242"/>
+      <c r="G40" s="168">
+        <f>'Datos Extra'!B5</f>
+        <v>108658.53000000003</v>
+      </c>
+      <c r="H40" s="169">
+        <f>G40*(1-'Datos Extra'!D5)</f>
+        <v>98640.574400793892</v>
+      </c>
+      <c r="I40" s="177">
+        <f>Flujos!G26</f>
+        <v>-3438</v>
+      </c>
+      <c r="J40" s="177">
+        <f>'Mapa de Procesos'!L138</f>
+        <v>-2260.2833314581599</v>
+      </c>
+      <c r="K40" s="164"/>
+      <c r="L40" s="163"/>
+      <c r="M40" s="164"/>
+      <c r="N40" s="164"/>
+      <c r="O40" s="164"/>
+      <c r="P40" s="164"/>
+      <c r="Q40" s="164"/>
+      <c r="R40" s="51"/>
+      <c r="U40" s="77"/>
+    </row>
+    <row r="41" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="B41" s="54"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="241" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="242"/>
+      <c r="F41" s="242"/>
+      <c r="G41" s="168">
         <f>'Datos Extra'!B6</f>
         <v>60226.45</v>
       </c>
-      <c r="H38" s="169">
-        <f>G38*(1-'Datos Extra'!D6)</f>
+      <c r="H41" s="169">
+        <f>G41*(1-'Datos Extra'!D6)</f>
         <v>60226.45</v>
       </c>
-      <c r="I38" s="177">
+      <c r="I41" s="177">
         <f>Flujos!G34</f>
         <v>6226</v>
       </c>
-      <c r="J38" s="177">
-        <f>'Mapa de Procesos'!L137</f>
+      <c r="J41" s="177">
+        <f>'Mapa de Procesos'!L139</f>
         <v>3936.9021999755796</v>
       </c>
-      <c r="L38" s="175"/>
-      <c r="M38" s="175"/>
-      <c r="N38" s="175"/>
-      <c r="O38" s="175"/>
-      <c r="P38" s="175"/>
-      <c r="Q38" s="172"/>
-      <c r="R38" s="76"/>
-      <c r="U38" s="77"/>
-    </row>
-    <row r="39" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="54"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="288" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" s="289"/>
-      <c r="F39" s="289"/>
-      <c r="G39" s="170">
+      <c r="L41" s="175"/>
+      <c r="M41" s="122"/>
+      <c r="N41" s="175"/>
+      <c r="O41" s="175"/>
+      <c r="P41" s="175"/>
+      <c r="Q41" s="172"/>
+      <c r="R41" s="76"/>
+      <c r="U41" s="77"/>
+    </row>
+    <row r="42" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="54"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="262" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="263"/>
+      <c r="F42" s="263"/>
+      <c r="G42" s="170">
         <f>'Datos Extra'!B7</f>
         <v>64802</v>
       </c>
-      <c r="H39" s="171">
-        <f>G39*(1-'Datos Extra'!D7)</f>
+      <c r="H42" s="171">
+        <f>G42*(1-'Datos Extra'!D7)</f>
         <v>64802</v>
       </c>
-      <c r="I39" s="177">
+      <c r="I42" s="177">
         <f>Flujos!G39</f>
         <v>0</v>
       </c>
-      <c r="J39" s="177">
-        <f>'Mapa de Procesos'!L138</f>
-        <v>0</v>
-      </c>
-      <c r="L39" s="172"/>
-      <c r="M39" s="172"/>
-      <c r="N39" s="172"/>
-      <c r="O39" s="172"/>
-      <c r="P39" s="172"/>
-      <c r="Q39" s="172"/>
-      <c r="R39" s="51"/>
-      <c r="U39" s="77"/>
-    </row>
-    <row r="40" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="78"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="178">
-        <f>SUM(I33:I39)</f>
+      <c r="J42" s="177">
+        <f>'Mapa de Procesos'!L140</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="172"/>
+      <c r="M42" s="172"/>
+      <c r="N42" s="172"/>
+      <c r="O42" s="172"/>
+      <c r="P42" s="172"/>
+      <c r="Q42" s="172"/>
+      <c r="R42" s="51"/>
+      <c r="U42" s="77"/>
+    </row>
+    <row r="43" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="78"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="262" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="263"/>
+      <c r="F43" s="263"/>
+      <c r="G43" s="170">
+        <f>'Datos Extra'!B8</f>
+        <v>71110.957552411084</v>
+      </c>
+      <c r="H43" s="171">
+        <f>G43*(1-'Datos Extra'!D8)</f>
+        <v>70399.847976886973</v>
+      </c>
+      <c r="I43" s="178">
+        <f>SUM(I36:I42)</f>
         <v>-19702</v>
       </c>
-      <c r="J40" s="178">
-        <f>SUM(J33:J39)</f>
+      <c r="J43" s="178">
+        <f>SUM(J36:J42)</f>
         <v>-7402.6198539840998</v>
       </c>
-      <c r="K40" s="79"/>
-      <c r="L40" s="79"/>
-      <c r="M40" s="79"/>
-      <c r="N40" s="79"/>
-      <c r="O40" s="79"/>
-      <c r="P40" s="79"/>
-      <c r="Q40" s="79"/>
-      <c r="R40" s="80"/>
-    </row>
-    <row r="43" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E43" s="117"/>
-      <c r="F43" s="117"/>
-      <c r="G43" s="117"/>
-      <c r="H43" s="117"/>
-      <c r="I43" s="116"/>
-      <c r="J43" s="116"/>
-    </row>
-    <row r="44" spans="2:21" ht="14" x14ac:dyDescent="0.2">
-      <c r="E44" s="117"/>
-      <c r="F44" s="117"/>
-      <c r="G44" s="117"/>
-      <c r="H44" s="117"/>
-      <c r="I44" s="116"/>
-      <c r="J44" s="116"/>
-    </row>
-    <row r="45" spans="2:21" ht="14" x14ac:dyDescent="0.2">
-      <c r="E45" s="82"/>
-      <c r="F45" s="82"/>
-      <c r="G45" s="82"/>
-      <c r="H45" s="82"/>
-      <c r="I45" s="82"/>
-      <c r="J45" s="82"/>
-      <c r="K45" s="82"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="79"/>
+      <c r="R43" s="80"/>
     </row>
     <row r="46" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E46" s="287"/>
-      <c r="F46" s="287"/>
-      <c r="G46" s="287"/>
-      <c r="H46" s="120"/>
-      <c r="I46" s="84"/>
-      <c r="J46" s="115"/>
-      <c r="K46" s="83"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="117"/>
+      <c r="H46" s="117"/>
+      <c r="I46" s="116"/>
+      <c r="J46" s="116"/>
+    </row>
+    <row r="47" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="116"/>
+      <c r="J47" s="116"/>
+    </row>
+    <row r="48" spans="2:21" ht="14" x14ac:dyDescent="0.2">
+      <c r="E48" s="82"/>
+      <c r="F48" s="82"/>
+      <c r="G48" s="82"/>
+      <c r="H48" s="82"/>
+      <c r="I48" s="82"/>
+      <c r="J48" s="82"/>
+      <c r="K48" s="82"/>
+    </row>
+    <row r="49" spans="5:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E49" s="261"/>
+      <c r="F49" s="261"/>
+      <c r="G49" s="261"/>
+      <c r="H49" s="120"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="115"/>
+      <c r="K49" s="83"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="K20:Q20"/>
-    <mergeCell ref="D20:J20"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="K12:Q12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D12:F12"/>
+  <mergeCells count="52">
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="D3:E6"/>
+    <mergeCell ref="F3:Q4"/>
+    <mergeCell ref="F5:L6"/>
+    <mergeCell ref="M5:N6"/>
+    <mergeCell ref="P5:Q6"/>
     <mergeCell ref="N8:O8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="D10:J10"/>
@@ -30779,18 +31146,38 @@
     <mergeCell ref="K11:M11"/>
     <mergeCell ref="D8:F9"/>
     <mergeCell ref="K8:M9"/>
-    <mergeCell ref="D3:E6"/>
-    <mergeCell ref="F3:Q4"/>
-    <mergeCell ref="F5:L6"/>
-    <mergeCell ref="M5:N6"/>
-    <mergeCell ref="P5:Q6"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="K20:Q20"/>
+    <mergeCell ref="D20:J20"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -30799,14 +31186,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f53f264-df38-4c5e-a089-ad7f07a2b911">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1490ee3b-8825-4a14-a799-bb3413729370" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31051,27 +31436,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f53f264-df38-4c5e-a089-ad7f07a2b911">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1490ee3b-8825-4a14-a799-bb3413729370" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79956576-308D-4576-AFE1-2F4C0F3C33E9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFCA9A7-8661-43F7-BFD7-3C6B027F5CB3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1490ee3b-8825-4a14-a799-bb3413729370"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31096,9 +31474,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFCA9A7-8661-43F7-BFD7-3C6B027F5CB3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79956576-308D-4576-AFE1-2F4C0F3C33E9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1490ee3b-8825-4a14-a799-bb3413729370"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Documents/GitHub/minera/public/Export/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernando/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC059E9-FAB9-D846-9850-539FFEB7BA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4988ACCD-4355-2A44-86C3-8058C217049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="702" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" r:id="rId1"/>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="203">
   <si>
     <t>%FeT</t>
   </si>
@@ -897,9 +897,6 @@
     <t>Sinter Feed Caro (camiones)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sinter Feed APC </t>
-  </si>
-  <si>
     <t>Sinter Feed Caro</t>
   </si>
   <si>
@@ -912,16 +909,7 @@
     <t>Preconcentrado Ventas</t>
   </si>
   <si>
-    <t>Prec Ventas</t>
-  </si>
-  <si>
     <t>Recep Prec Ventas</t>
-  </si>
-  <si>
-    <t>Sinter Feed Dorado (camiones)</t>
-  </si>
-  <si>
-    <t>Sinter Feed Santa Fe (camiones)</t>
   </si>
   <si>
     <t>SF El Dorado</t>
@@ -961,6 +949,9 @@
   </si>
   <si>
     <t>Embarque Prec Ventas</t>
+  </si>
+  <si>
+    <t>Sinter Feed APC</t>
   </si>
 </sst>
 </file>
@@ -2423,6 +2414,15 @@
     <xf numFmtId="10" fontId="35" fillId="20" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="35" fillId="22" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2442,27 +2442,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2472,13 +2451,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2489,6 +2468,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2502,32 +2490,44 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2544,69 +2544,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="42" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="43" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="44" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2615,39 +2552,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2694,23 +2598,110 @@
     <xf numFmtId="14" fontId="16" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="26" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -10717,8 +10708,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10481605" y="3089178"/>
-          <a:ext cx="578485" cy="525210"/>
+          <a:off x="10472875" y="3251941"/>
+          <a:ext cx="578485" cy="556467"/>
           <a:chOff x="7267997" y="2828222"/>
           <a:chExt cx="578485" cy="520570"/>
         </a:xfrm>
@@ -11321,8 +11312,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11323703" y="1561605"/>
-          <a:ext cx="1387018" cy="406944"/>
+          <a:off x="11325392" y="1641015"/>
+          <a:ext cx="1392369" cy="427783"/>
           <a:chOff x="8032552" y="1308634"/>
           <a:chExt cx="1126823" cy="403057"/>
         </a:xfrm>
@@ -12126,8 +12117,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7786045" y="4455124"/>
-          <a:ext cx="1325067" cy="406881"/>
+          <a:off x="7779287" y="4690820"/>
+          <a:ext cx="1323095" cy="438138"/>
           <a:chOff x="5132992" y="4068644"/>
           <a:chExt cx="1126823" cy="403893"/>
         </a:xfrm>
@@ -16851,6 +16842,63 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>674430</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>115454</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>865909</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>145394</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Conector: angular 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95B4F8D5-C7F5-0344-9439-55F254B76C12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="10996066" y="3071090"/>
+          <a:ext cx="2050298" cy="618759"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 22408"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -17377,13 +17425,13 @@
         <v>-28228</v>
       </c>
       <c r="B6" s="123">
-        <v>-26556</v>
+        <v>-34429.130716</v>
       </c>
       <c r="C6" s="127">
         <v>30.55</v>
       </c>
       <c r="D6" s="109">
-        <v>35.595079067</v>
+        <v>32.077500000000001</v>
       </c>
       <c r="E6" s="108">
         <v>0</v>
@@ -17398,13 +17446,13 @@
         <v>116673</v>
       </c>
       <c r="B7" s="123">
-        <v>116673</v>
+        <v>124546.13072</v>
       </c>
       <c r="C7" s="127">
         <v>31.13</v>
       </c>
       <c r="D7" s="109">
-        <v>32.063899999999997</v>
+        <v>31.314733775000001</v>
       </c>
       <c r="E7" s="108">
         <v>1.6500000000000001E-2</v>
@@ -17440,7 +17488,7 @@
         <v>20214</v>
       </c>
       <c r="B9" s="123">
-        <v>20626.123299999999</v>
+        <v>24875.066452999999</v>
       </c>
       <c r="C9" s="127">
         <v>20.260000000000002</v>
@@ -17461,7 +17509,7 @@
         <v>11970</v>
       </c>
       <c r="B10" s="123">
-        <v>14883.876700000001</v>
+        <v>15456.336685</v>
       </c>
       <c r="C10" s="127">
         <v>11.43</v>
@@ -17483,13 +17531,13 @@
         <v>60996</v>
       </c>
       <c r="B11" s="123">
-        <v>60996</v>
+        <v>64047.727577999998</v>
       </c>
       <c r="C11" s="127">
         <v>36.6</v>
       </c>
       <c r="D11" s="109">
-        <v>36.6</v>
+        <v>35.689666414000001</v>
       </c>
       <c r="E11" s="108">
         <v>4.02E-2</v>
@@ -17510,7 +17558,7 @@
         <v>48.56</v>
       </c>
       <c r="D12" s="109">
-        <v>47.103200000000001</v>
+        <v>47.983531085999999</v>
       </c>
       <c r="E12" s="108">
         <v>4.4760000000000001E-2</v>
@@ -17531,7 +17579,7 @@
         <v>49.75</v>
       </c>
       <c r="D13" s="109">
-        <v>49.758945171000001</v>
+        <v>49.744623738000001</v>
       </c>
       <c r="E13" s="108">
         <v>7.3599999999999999E-2</v>
@@ -17546,13 +17594,13 @@
         <v>23352</v>
       </c>
       <c r="B14" s="123">
-        <v>9165</v>
+        <v>12216.727578</v>
       </c>
       <c r="C14" s="127">
         <v>41.47</v>
       </c>
       <c r="D14" s="109">
-        <v>40.802729317000001</v>
+        <v>39.396500000000003</v>
       </c>
       <c r="E14" s="108">
         <v>0.01</v>
@@ -17573,7 +17621,7 @@
         <v>41.47</v>
       </c>
       <c r="D15" s="109">
-        <v>41.851701227</v>
+        <v>41.240586135000001</v>
       </c>
       <c r="E15" s="108">
         <v>4.4760000000000001E-2</v>
@@ -17594,7 +17642,7 @@
         <v>9.81</v>
       </c>
       <c r="D16" s="109">
-        <v>9.6207729683000007</v>
+        <v>9.3194999999999997</v>
       </c>
       <c r="E16" s="108">
         <v>0</v>
@@ -17616,7 +17664,7 @@
         <v>65.05</v>
       </c>
       <c r="D17" s="109">
-        <v>65.033937957999996</v>
+        <v>64.685681119999998</v>
       </c>
       <c r="E17" s="108">
         <v>8.6669999999999997E-2</v>
@@ -17638,7 +17686,7 @@
         <v>65.05</v>
       </c>
       <c r="D18" s="109">
-        <v>66.016467294999998</v>
+        <v>68.302499999999995</v>
       </c>
       <c r="E18" s="108">
         <v>8.9433339445628993E-2</v>
@@ -17682,7 +17730,7 @@
         <v>65.09</v>
       </c>
       <c r="D20" s="109">
-        <v>65.104390026999994</v>
+        <v>64.945024392999997</v>
       </c>
       <c r="E20" s="108">
         <v>9.2196678891257988E-2</v>
@@ -17704,7 +17752,7 @@
         <v>65.09</v>
       </c>
       <c r="D21" s="109">
-        <v>64.819854000999996</v>
+        <v>63.137300000000003</v>
       </c>
       <c r="E21" s="108">
         <v>9.2196678891257988E-2</v>
@@ -17726,7 +17774,7 @@
         <v>65.09</v>
       </c>
       <c r="D22" s="109">
-        <v>65.110195969000003</v>
+        <v>64.981910904000003</v>
       </c>
       <c r="E22" s="108">
         <v>9.2196678891257988E-2</v>
@@ -17748,7 +17796,7 @@
         <v>65.09</v>
       </c>
       <c r="D23" s="109">
-        <v>65.744134131999999</v>
+        <v>68.344499999999996</v>
       </c>
       <c r="E23" s="108">
         <v>9.2196678891257988E-2</v>
@@ -18548,7 +18596,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="108">
-        <v>9.2196678891257988E-2</v>
+        <v>0</v>
       </c>
       <c r="F55" s="108"/>
       <c r="J55" s="123"/>
@@ -18676,12 +18724,12 @@
         <v>0</v>
       </c>
       <c r="F60" s="108"/>
-      <c r="J60" s="208"/>
-      <c r="K60" s="208"/>
-      <c r="L60" s="208"/>
+      <c r="J60" s="211"/>
+      <c r="K60" s="211"/>
+      <c r="L60" s="211"/>
       <c r="M60" s="112"/>
-      <c r="N60" s="209"/>
-      <c r="O60" s="209"/>
+      <c r="N60" s="212"/>
+      <c r="O60" s="212"/>
       <c r="R60" s="94"/>
       <c r="AD60" s="5"/>
       <c r="AE60" s="3"/>
@@ -18719,11 +18767,21 @@
       <c r="AF61" s="3"/>
     </row>
     <row r="62" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="123"/>
-      <c r="B62" s="123"/>
-      <c r="C62" s="123"/>
-      <c r="D62" s="108"/>
-      <c r="E62" s="108"/>
+      <c r="A62" s="123">
+        <v>0</v>
+      </c>
+      <c r="B62" s="123">
+        <v>0</v>
+      </c>
+      <c r="C62" s="123">
+        <v>0</v>
+      </c>
+      <c r="D62" s="108">
+        <v>0</v>
+      </c>
+      <c r="E62" s="108">
+        <v>0</v>
+      </c>
       <c r="F62" s="108"/>
       <c r="J62" s="123"/>
       <c r="K62" s="127"/>
@@ -18742,11 +18800,21 @@
       <c r="AF62" s="3"/>
     </row>
     <row r="63" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="123"/>
-      <c r="B63" s="123"/>
-      <c r="C63" s="123"/>
-      <c r="D63" s="108"/>
-      <c r="E63" s="108"/>
+      <c r="A63" s="123">
+        <v>0</v>
+      </c>
+      <c r="B63" s="123">
+        <v>0</v>
+      </c>
+      <c r="C63" s="123">
+        <v>0</v>
+      </c>
+      <c r="D63" s="108">
+        <v>0</v>
+      </c>
+      <c r="E63" s="108">
+        <v>0</v>
+      </c>
       <c r="F63" s="108"/>
       <c r="J63" s="123"/>
       <c r="K63" s="127"/>
@@ -18765,11 +18833,21 @@
       <c r="AF63" s="3"/>
     </row>
     <row r="64" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="123"/>
-      <c r="B64" s="123"/>
-      <c r="C64" s="123"/>
-      <c r="D64" s="108"/>
-      <c r="E64" s="108"/>
+      <c r="A64" s="123">
+        <v>0</v>
+      </c>
+      <c r="B64" s="123">
+        <v>0</v>
+      </c>
+      <c r="C64" s="123">
+        <v>0</v>
+      </c>
+      <c r="D64" s="108">
+        <v>0</v>
+      </c>
+      <c r="E64" s="108">
+        <v>0</v>
+      </c>
       <c r="F64" s="108"/>
       <c r="J64" s="123"/>
       <c r="K64" s="127"/>
@@ -18788,11 +18866,21 @@
       <c r="AF64" s="3"/>
     </row>
     <row r="65" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="123"/>
-      <c r="B65" s="123"/>
-      <c r="C65" s="123"/>
-      <c r="D65" s="108"/>
-      <c r="E65" s="108"/>
+      <c r="A65" s="123">
+        <v>0</v>
+      </c>
+      <c r="B65" s="123">
+        <v>0</v>
+      </c>
+      <c r="C65" s="123">
+        <v>0</v>
+      </c>
+      <c r="D65" s="108">
+        <v>0</v>
+      </c>
+      <c r="E65" s="108">
+        <v>0</v>
+      </c>
       <c r="F65" s="108"/>
       <c r="G65" s="152"/>
       <c r="H65" s="153"/>
@@ -18814,11 +18902,21 @@
       <c r="AF65" s="3"/>
     </row>
     <row r="66" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="108"/>
-      <c r="B66" s="108"/>
-      <c r="C66" s="108"/>
-      <c r="D66" s="108"/>
-      <c r="E66" s="108"/>
+      <c r="A66" s="108">
+        <v>0</v>
+      </c>
+      <c r="B66" s="108">
+        <v>0</v>
+      </c>
+      <c r="C66" s="108">
+        <v>0</v>
+      </c>
+      <c r="D66" s="108">
+        <v>0</v>
+      </c>
+      <c r="E66" s="108">
+        <v>0</v>
+      </c>
       <c r="F66" s="108"/>
       <c r="G66" s="152"/>
       <c r="H66" s="153"/>
@@ -18840,11 +18938,21 @@
       <c r="AF66" s="3"/>
     </row>
     <row r="67" spans="1:32" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="110"/>
-      <c r="B67" s="110"/>
-      <c r="C67" s="109"/>
-      <c r="D67" s="108"/>
-      <c r="E67" s="108"/>
+      <c r="A67" s="110">
+        <v>0</v>
+      </c>
+      <c r="B67" s="110">
+        <v>0</v>
+      </c>
+      <c r="C67" s="109">
+        <v>0</v>
+      </c>
+      <c r="D67" s="108">
+        <v>0</v>
+      </c>
+      <c r="E67" s="108">
+        <v>0</v>
+      </c>
       <c r="F67" s="111"/>
       <c r="G67" s="152"/>
       <c r="H67" s="153"/>
@@ -18957,7 +19065,7 @@
       </c>
       <c r="J71" s="123">
         <f t="shared" ref="J71:J108" si="0">B10</f>
-        <v>14883.876700000001</v>
+        <v>15456.336685</v>
       </c>
       <c r="K71" s="127">
         <f t="shared" ref="K71:K108" si="1">IF(D10&gt;1,D10/100,D10)</f>
@@ -18965,7 +19073,7 @@
       </c>
       <c r="L71" s="126">
         <f t="shared" ref="L71:L108" si="2">+J71*K71</f>
-        <v>1616.1657514694998</v>
+        <v>1678.3263189407248</v>
       </c>
       <c r="M71" s="112"/>
       <c r="N71" s="4"/>
@@ -18994,15 +19102,15 @@
       </c>
       <c r="J72" s="123">
         <f t="shared" si="0"/>
-        <v>60996</v>
+        <v>64047.727577999998</v>
       </c>
       <c r="K72" s="127">
         <f t="shared" si="1"/>
-        <v>0.36599999999999999</v>
+        <v>0.35689666413999999</v>
       </c>
       <c r="L72" s="126">
         <f t="shared" si="2"/>
-        <v>22324.536</v>
+        <v>22858.42031833568</v>
       </c>
       <c r="M72" s="112"/>
       <c r="N72" s="4"/>
@@ -19035,11 +19143,11 @@
       </c>
       <c r="K73" s="127">
         <f t="shared" si="1"/>
-        <v>0.47103200000000001</v>
+        <v>0.47983531085999998</v>
       </c>
       <c r="L73" s="126">
         <f t="shared" si="2"/>
-        <v>9499.3023439999997</v>
+        <v>9676.8387141136191</v>
       </c>
       <c r="M73" s="112"/>
       <c r="N73" s="4"/>
@@ -19072,11 +19180,11 @@
       </c>
       <c r="K74" s="127">
         <f t="shared" si="1"/>
-        <v>0.49758945171000002</v>
+        <v>0.49744623737999999</v>
       </c>
       <c r="L74" s="126">
         <f t="shared" si="2"/>
-        <v>715.03604210727008</v>
+        <v>714.83024311505994</v>
       </c>
       <c r="M74" s="112"/>
       <c r="N74" s="4"/>
@@ -19105,15 +19213,15 @@
       </c>
       <c r="J75" s="123">
         <f t="shared" si="0"/>
-        <v>9165</v>
+        <v>12216.727578</v>
       </c>
       <c r="K75" s="127">
         <f t="shared" si="1"/>
-        <v>0.40802729317000003</v>
+        <v>0.39396500000000001</v>
       </c>
       <c r="L75" s="126">
         <f t="shared" si="2"/>
-        <v>3739.5701419030502</v>
+        <v>4812.9630802667698</v>
       </c>
       <c r="M75" s="112"/>
       <c r="N75" s="4"/>
@@ -19146,11 +19254,11 @@
       </c>
       <c r="K76" s="127">
         <f t="shared" si="1"/>
-        <v>0.41851701226999999</v>
+        <v>0.41240586135000001</v>
       </c>
       <c r="L76" s="126">
         <f t="shared" si="2"/>
-        <v>36933.707815815229</v>
+        <v>36394.404858276153</v>
       </c>
       <c r="M76" s="112"/>
       <c r="N76" s="4"/>
@@ -19183,11 +19291,11 @@
       </c>
       <c r="K77" s="127">
         <f t="shared" si="1"/>
-        <v>9.6207729683000009E-2</v>
+        <v>9.3195E-2</v>
       </c>
       <c r="L77" s="126">
         <f t="shared" si="2"/>
-        <v>4217.843077032403</v>
+        <v>4085.7619949999998</v>
       </c>
       <c r="M77" s="112"/>
       <c r="N77" s="4"/>
@@ -19220,11 +19328,11 @@
       </c>
       <c r="K78" s="127">
         <f t="shared" si="1"/>
-        <v>0.65033937957999999</v>
+        <v>0.64685681119999994</v>
       </c>
       <c r="L78" s="126">
         <f t="shared" si="2"/>
-        <v>42930.203124834959</v>
+        <v>42700.311820934396</v>
       </c>
       <c r="M78" s="112"/>
       <c r="N78" s="4"/>
@@ -19257,11 +19365,11 @@
       </c>
       <c r="K79" s="127">
         <f t="shared" si="1"/>
-        <v>0.66016467295000003</v>
+        <v>0.68302499999999999</v>
       </c>
       <c r="L79" s="126">
         <f t="shared" si="2"/>
-        <v>-3366.1796673720501</v>
+        <v>-3482.744475</v>
       </c>
       <c r="M79" s="112"/>
       <c r="N79" s="4"/>
@@ -19324,11 +19432,11 @@
       </c>
       <c r="K81" s="127">
         <f t="shared" si="1"/>
-        <v>0.65104390026999992</v>
+        <v>0.64945024392999995</v>
       </c>
       <c r="L81" s="126">
         <f t="shared" si="2"/>
-        <v>46296.382792099961</v>
+        <v>46183.056296106224</v>
       </c>
       <c r="M81" s="112"/>
       <c r="N81" s="4"/>
@@ -19356,11 +19464,11 @@
       </c>
       <c r="K82" s="127">
         <f t="shared" si="1"/>
-        <v>0.64819854000999999</v>
+        <v>0.63137300000000007</v>
       </c>
       <c r="L82" s="126">
         <f t="shared" si="2"/>
-        <v>921.73832389422</v>
+        <v>897.81240600000012</v>
       </c>
       <c r="M82" s="112"/>
       <c r="N82" s="4"/>
@@ -19388,11 +19496,11 @@
       </c>
       <c r="K83" s="127">
         <f t="shared" si="1"/>
-        <v>0.65110195969000006</v>
+        <v>0.64981910904000006</v>
       </c>
       <c r="L83" s="126">
         <f t="shared" si="2"/>
-        <v>45374.644468836414</v>
+        <v>45285.243889888567</v>
       </c>
       <c r="M83" s="112"/>
       <c r="N83" s="4"/>
@@ -19420,11 +19528,11 @@
       </c>
       <c r="K84" s="127">
         <f t="shared" si="1"/>
-        <v>0.65744134131999998</v>
+        <v>0.68344499999999997</v>
       </c>
       <c r="L84" s="126">
         <f t="shared" si="2"/>
-        <v>-2260.2833314581599</v>
+        <v>-2349.6839099999997</v>
       </c>
       <c r="M84" s="112"/>
       <c r="N84" s="4"/>
@@ -20480,8 +20588,8 @@
       <c r="D118" s="148"/>
       <c r="E118" s="148"/>
       <c r="F118" s="148"/>
-      <c r="G118" s="210"/>
-      <c r="H118" s="211"/>
+      <c r="G118" s="213"/>
+      <c r="H118" s="214"/>
       <c r="I118" s="123"/>
       <c r="J118" s="128"/>
       <c r="K118" s="128"/>
@@ -21461,7 +21569,7 @@
         <v>134</v>
       </c>
       <c r="B27" s="142">
-        <v>9.2189999999999994E-2</v>
+        <v>9.2196678891257988E-2</v>
       </c>
       <c r="C27" s="134">
         <v>0</v>
@@ -21627,7 +21735,7 @@
     </row>
     <row r="39" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A39" s="143" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B39" s="141">
         <v>3185.4799999999996</v>
@@ -21641,7 +21749,7 @@
     </row>
     <row r="40" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A40" s="143" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B40" s="141">
         <v>3108.9800000000005</v>
@@ -21655,58 +21763,58 @@
     </row>
     <row r="41" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A41" s="143" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B41" s="135">
-        <v>3108.9800000000005</v>
+        <v>3185.4799999999996</v>
       </c>
       <c r="C41" s="135">
-        <v>0.63</v>
-      </c>
-      <c r="D41" s="299">
-        <v>1.2699999999999999E-2</v>
+        <v>0.63460000000000005</v>
+      </c>
+      <c r="D41" s="208">
+        <v>8.8000000000000005E-3</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A42" s="133" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B42" s="141">
         <v>1000</v>
       </c>
       <c r="C42" s="135">
-        <v>0.63</v>
-      </c>
-      <c r="D42" s="299">
-        <v>1.2699999999999999E-2</v>
+        <v>0.6</v>
+      </c>
+      <c r="D42" s="208">
+        <v>0.6</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="24" x14ac:dyDescent="0.3">
       <c r="A43" s="133" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B43" s="141">
         <v>1000</v>
       </c>
       <c r="C43" s="135">
-        <v>0.63</v>
-      </c>
-      <c r="D43" s="299">
-        <v>1.2699999999999999E-2</v>
+        <v>0.6</v>
+      </c>
+      <c r="D43" s="208">
+        <v>0.6</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="A44" s="300" t="s">
-        <v>197</v>
+      <c r="A44" s="209" t="s">
+        <v>193</v>
       </c>
       <c r="B44" s="141">
         <v>1000</v>
       </c>
       <c r="C44" s="135">
-        <v>0.63</v>
-      </c>
-      <c r="D44" s="299">
-        <v>1.2699999999999999E-2</v>
+        <v>0.6</v>
+      </c>
+      <c r="D44" s="208">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -21729,20 +21837,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="20" x14ac:dyDescent="0.25">
-      <c r="B2" s="212" t="s">
+      <c r="B2" s="215" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="212"/>
-      <c r="D2" s="212"/>
-      <c r="F2" s="212" t="s">
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="F2" s="215" t="s">
         <v>141</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="J2" s="216" t="s">
         <v>142</v>
       </c>
-      <c r="K2" s="214"/>
+      <c r="K2" s="217"/>
       <c r="L2" s="98"/>
       <c r="M2" s="99" t="s">
         <v>143</v>
@@ -21999,31 +22107,31 @@
       </c>
       <c r="G9" s="186">
         <f>Utilidad!B6</f>
-        <v>-26556</v>
+        <v>-34429.130716</v>
       </c>
       <c r="H9" s="187">
         <f>IF(Utilidad!D6&gt;1,Utilidad!D6/100,Utilidad!D6)</f>
-        <v>0.35595079067000002</v>
+        <v>0.32077500000000003</v>
       </c>
       <c r="J9" s="104">
         <f t="shared" si="2"/>
-        <v>-5.9231968258466772E-2</v>
+        <v>0.21968013022530819</v>
       </c>
       <c r="K9" s="104">
         <f t="shared" si="0"/>
-        <v>0.16514170432078568</v>
+        <v>5.0000000000000128E-2</v>
       </c>
       <c r="M9" s="106">
         <f t="shared" si="3"/>
-        <v>5.9231968258466772E-2</v>
+        <v>0.21968013022530819</v>
       </c>
       <c r="N9" s="106">
         <f t="shared" si="1"/>
-        <v>0.16514170432078568</v>
+        <v>5.0000000000000128E-2</v>
       </c>
       <c r="Q9">
         <f>G10-G14-G15</f>
-        <v>35510</v>
+        <v>40331.403142000003</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="19" x14ac:dyDescent="0.25">
@@ -22043,31 +22151,31 @@
       </c>
       <c r="G10" s="204">
         <f>Utilidad!B7</f>
-        <v>116673</v>
+        <v>124546.13072</v>
       </c>
       <c r="H10" s="205">
         <f>IF(Utilidad!D7&gt;1,Utilidad!D7/100,Utilidad!D7)</f>
-        <v>0.32063899999999995</v>
+        <v>0.31314733775000003</v>
       </c>
       <c r="J10" s="104">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.7480314382933504E-2</v>
       </c>
       <c r="K10" s="104">
         <f t="shared" si="0"/>
-        <v>2.9999999999999957E-2</v>
+        <v>5.9342683906201954E-3</v>
       </c>
       <c r="M10" s="106">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6.7480314382933504E-2</v>
       </c>
       <c r="N10" s="106">
         <f t="shared" si="1"/>
-        <v>2.9999999999999957E-2</v>
+        <v>5.9342683906201954E-3</v>
       </c>
       <c r="Q10">
         <f>G13+G12</f>
-        <v>35510</v>
+        <v>40331.403138000001</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="19" x14ac:dyDescent="0.25">
@@ -22127,7 +22235,7 @@
       </c>
       <c r="G12" s="204">
         <f>Utilidad!B9</f>
-        <v>20626.123299999999</v>
+        <v>24875.066452999999</v>
       </c>
       <c r="H12" s="205">
         <f>IF(Utilidad!D9&gt;1,Utilidad!D9/100,Utilidad!D9)</f>
@@ -22135,7 +22243,7 @@
       </c>
       <c r="J12" s="104">
         <f t="shared" si="2"/>
-        <v>2.038801325813789E-2</v>
+        <v>0.23058605189472639</v>
       </c>
       <c r="K12" s="104">
         <f t="shared" si="0"/>
@@ -22143,7 +22251,7 @@
       </c>
       <c r="M12" s="106">
         <f t="shared" si="3"/>
-        <v>2.038801325813789E-2</v>
+        <v>0.23058605189472639</v>
       </c>
       <c r="N12" s="106">
         <f t="shared" si="1"/>
@@ -22167,7 +22275,7 @@
       </c>
       <c r="G13" s="204">
         <f>Utilidad!B10</f>
-        <v>14883.876700000001</v>
+        <v>15456.336685</v>
       </c>
       <c r="H13" s="205">
         <f>IF(Utilidad!D10&gt;1,Utilidad!D10/100,Utilidad!D10)</f>
@@ -22175,7 +22283,7 @@
       </c>
       <c r="J13" s="104">
         <f t="shared" si="2"/>
-        <v>0.24343163742690063</v>
+        <v>0.29125619757727655</v>
       </c>
       <c r="K13" s="104">
         <f t="shared" si="0"/>
@@ -22183,7 +22291,7 @@
       </c>
       <c r="M13" s="106">
         <f t="shared" si="3"/>
-        <v>0.24343163742690063</v>
+        <v>0.29125619757727655</v>
       </c>
       <c r="N13" s="106">
         <f t="shared" si="1"/>
@@ -22207,27 +22315,27 @@
       </c>
       <c r="G14" s="204">
         <f>Utilidad!B11</f>
-        <v>60996</v>
+        <v>64047.727577999998</v>
       </c>
       <c r="H14" s="205">
         <f>IF(Utilidad!D11&gt;1,Utilidad!D11/100,Utilidad!D11)</f>
-        <v>0.36599999999999999</v>
+        <v>0.35689666413999999</v>
       </c>
       <c r="J14" s="104">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.0031601711587617E-2</v>
       </c>
       <c r="K14" s="104">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2.4872502349726794E-2</v>
       </c>
       <c r="M14" s="106">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5.0031601711587617E-2</v>
       </c>
       <c r="N14" s="106">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.4872502349726794E-2</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="19" x14ac:dyDescent="0.25">
@@ -22251,7 +22359,7 @@
       </c>
       <c r="H15" s="205">
         <f>IF(Utilidad!D12&gt;1,Utilidad!D12/100,Utilidad!D12)</f>
-        <v>0.47103200000000001</v>
+        <v>0.47983531085999998</v>
       </c>
       <c r="J15" s="104">
         <f t="shared" si="2"/>
@@ -22259,7 +22367,7 @@
       </c>
       <c r="K15" s="104">
         <f t="shared" si="0"/>
-        <v>-3.0000000000000051E-2</v>
+        <v>-1.1871270881383971E-2</v>
       </c>
       <c r="M15" s="106">
         <f t="shared" si="3"/>
@@ -22267,7 +22375,7 @@
       </c>
       <c r="N15" s="106">
         <f t="shared" si="1"/>
-        <v>3.0000000000000051E-2</v>
+        <v>1.1871270881383971E-2</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="19" x14ac:dyDescent="0.25">
@@ -22291,11 +22399,11 @@
       </c>
       <c r="H16" s="203">
         <f>IF(Utilidad!D13&gt;1,Utilidad!D13/100,Utilidad!D13)</f>
-        <v>0.49758945171000002</v>
+        <v>0.49744623737999999</v>
       </c>
       <c r="I16">
         <f>(G14*H14+G15*H15)/(G14+G15)*100</f>
-        <v>39.209785670810589</v>
+        <v>38.633692666541045</v>
       </c>
       <c r="J16" s="104">
         <f t="shared" si="2"/>
@@ -22303,7 +22411,7 @@
       </c>
       <c r="K16" s="104">
         <f t="shared" si="0"/>
-        <v>1.7980243216084702E-4</v>
+        <v>-1.0806556783921313E-4</v>
       </c>
       <c r="M16" s="106">
         <f t="shared" si="3"/>
@@ -22311,7 +22419,7 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" si="1"/>
-        <v>1.7980243216084702E-4</v>
+        <v>1.0806556783921313E-4</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22331,27 +22439,27 @@
       </c>
       <c r="G17" s="202">
         <f>Utilidad!B14</f>
-        <v>9165</v>
+        <v>12216.727578</v>
       </c>
       <c r="H17" s="203">
         <f>IF(Utilidad!D14&gt;1,Utilidad!D14/100,Utilidad!D14)</f>
-        <v>0.40802729317000003</v>
+        <v>0.39396500000000001</v>
       </c>
       <c r="J17" s="104">
         <f t="shared" si="2"/>
-        <v>-0.6075282631038027</v>
+        <v>-0.47684448535457347</v>
       </c>
       <c r="K17" s="104">
         <f t="shared" si="0"/>
-        <v>-1.609044328430187E-2</v>
+        <v>-5.000000000000001E-2</v>
       </c>
       <c r="M17" s="106">
         <f t="shared" si="3"/>
-        <v>0.6075282631038027</v>
+        <v>0.47684448535457347</v>
       </c>
       <c r="N17" s="106">
         <f t="shared" si="1"/>
-        <v>1.609044328430187E-2</v>
+        <v>5.000000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22375,7 +22483,7 @@
       </c>
       <c r="H18" s="203">
         <f>IF(Utilidad!D15&gt;1,Utilidad!D15/100,Utilidad!D15)</f>
-        <v>0.41851701226999999</v>
+        <v>0.41240586135000001</v>
       </c>
       <c r="J18" s="104">
         <f t="shared" si="2"/>
@@ -22383,7 +22491,7 @@
       </c>
       <c r="K18" s="104">
         <f t="shared" si="0"/>
-        <v>9.2042736194839041E-3</v>
+        <v>-5.5320440077164202E-3</v>
       </c>
       <c r="M18" s="106">
         <f t="shared" si="3"/>
@@ -22391,7 +22499,7 @@
       </c>
       <c r="N18" s="106">
         <f t="shared" si="1"/>
-        <v>9.2042736194839041E-3</v>
+        <v>5.5320440077164202E-3</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22415,7 +22523,7 @@
       </c>
       <c r="H19" s="203">
         <f>IF(Utilidad!D16&gt;1,Utilidad!D16/100,Utilidad!D16)</f>
-        <v>9.6207729683000009E-2</v>
+        <v>9.3195E-2</v>
       </c>
       <c r="J19" s="104">
         <f t="shared" si="2"/>
@@ -22423,7 +22531,7 @@
       </c>
       <c r="K19" s="104">
         <f t="shared" si="0"/>
-        <v>-1.9289197930682945E-2</v>
+        <v>-5.0000000000000065E-2</v>
       </c>
       <c r="M19" s="106">
         <f t="shared" si="3"/>
@@ -22431,7 +22539,7 @@
       </c>
       <c r="N19" s="106">
         <f t="shared" si="1"/>
-        <v>1.9289197930682945E-2</v>
+        <v>5.0000000000000065E-2</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22455,7 +22563,7 @@
       </c>
       <c r="H20" s="203">
         <f>IF(Utilidad!D17&gt;1,Utilidad!D17/100,Utilidad!D17)</f>
-        <v>0.65033937957999999</v>
+        <v>0.64685681119999994</v>
       </c>
       <c r="J20" s="104">
         <f t="shared" si="2"/>
@@ -22463,7 +22571,7 @@
       </c>
       <c r="K20" s="104">
         <f t="shared" si="0"/>
-        <v>-2.4691840122979163E-4</v>
+        <v>-5.600597694081522E-3</v>
       </c>
       <c r="M20" s="106">
         <f t="shared" si="3"/>
@@ -22471,7 +22579,7 @@
       </c>
       <c r="N20" s="106">
         <f t="shared" si="1"/>
-        <v>2.4691840122979163E-4</v>
+        <v>5.600597694081522E-3</v>
       </c>
     </row>
     <row r="21" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22495,7 +22603,7 @@
       </c>
       <c r="H21" s="187">
         <f>IF(Utilidad!D18&gt;1,Utilidad!D18/100,Utilidad!D18)</f>
-        <v>0.66016467295000003</v>
+        <v>0.68302499999999999</v>
       </c>
       <c r="J21" s="104">
         <f t="shared" si="2"/>
@@ -22503,7 +22611,7 @@
       </c>
       <c r="K21" s="104">
         <f t="shared" si="0"/>
-        <v>1.4857298923904787E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="M21" s="106">
         <f t="shared" si="3"/>
@@ -22511,7 +22619,7 @@
       </c>
       <c r="N21" s="106">
         <f t="shared" si="1"/>
-        <v>1.4857298923904787E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22575,7 +22683,7 @@
       </c>
       <c r="H23" s="187">
         <f>IF(Utilidad!D20&gt;1,Utilidad!D20/100,Utilidad!D20)</f>
-        <v>0.65104390026999992</v>
+        <v>0.64945024392999995</v>
       </c>
       <c r="J23" s="104">
         <f t="shared" si="2"/>
@@ -22583,7 +22691,7 @@
       </c>
       <c r="K23" s="104">
         <f t="shared" si="0"/>
-        <v>2.2107892149314168E-4</v>
+        <v>-2.2273099861731226E-3</v>
       </c>
       <c r="M23" s="106">
         <f t="shared" si="3"/>
@@ -22591,7 +22699,7 @@
       </c>
       <c r="N23" s="106">
         <f t="shared" si="1"/>
-        <v>2.2107892149314168E-4</v>
+        <v>2.2273099861731226E-3</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22615,7 +22723,7 @@
       </c>
       <c r="H24" s="187">
         <f>IF(Utilidad!D21&gt;1,Utilidad!D21/100,Utilidad!D21)</f>
-        <v>0.64819854000999999</v>
+        <v>0.63137300000000007</v>
       </c>
       <c r="J24" s="104">
         <f t="shared" si="2"/>
@@ -22623,7 +22731,7 @@
       </c>
       <c r="K24" s="104">
         <f t="shared" si="0"/>
-        <v>-4.1503456598556516E-3</v>
+        <v>-2.999999999999994E-2</v>
       </c>
       <c r="M24" s="106">
         <f t="shared" si="3"/>
@@ -22631,7 +22739,7 @@
       </c>
       <c r="N24" s="106">
         <f t="shared" si="1"/>
-        <v>4.1503456598556516E-3</v>
+        <v>2.999999999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22655,7 +22763,7 @@
       </c>
       <c r="H25" s="187">
         <f>IF(Utilidad!D22&gt;1,Utilidad!D22/100,Utilidad!D22)</f>
-        <v>0.65110195969000006</v>
+        <v>0.64981910904000006</v>
       </c>
       <c r="J25" s="104">
         <f t="shared" si="2"/>
@@ -22663,7 +22771,7 @@
       </c>
       <c r="K25" s="104">
         <f t="shared" si="0"/>
-        <v>3.1027760024586091E-4</v>
+        <v>-1.6606098632661996E-3</v>
       </c>
       <c r="M25" s="106">
         <f t="shared" si="3"/>
@@ -22671,7 +22779,7 @@
       </c>
       <c r="N25" s="106">
         <f t="shared" si="1"/>
-        <v>3.1027760024586091E-4</v>
+        <v>1.6606098632661996E-3</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -22695,7 +22803,7 @@
       </c>
       <c r="H26" s="187">
         <f>IF(Utilidad!D23&gt;1,Utilidad!D23/100,Utilidad!D23)</f>
-        <v>0.65744134131999998</v>
+        <v>0.68344499999999997</v>
       </c>
       <c r="J26" s="104">
         <f t="shared" si="2"/>
@@ -22703,7 +22811,7 @@
       </c>
       <c r="K26" s="104">
         <f t="shared" si="0"/>
-        <v>1.0049687079428405E-2</v>
+        <v>4.9999999999999899E-2</v>
       </c>
       <c r="M26" s="106">
         <f t="shared" si="3"/>
@@ -22711,7 +22819,7 @@
       </c>
       <c r="N26" s="106">
         <f t="shared" si="1"/>
-        <v>1.0049687079428405E-2</v>
+        <v>4.9999999999999899E-2</v>
       </c>
     </row>
     <row r="27" spans="2:14" ht="19" x14ac:dyDescent="0.25">
@@ -24236,7 +24344,7 @@
     </row>
     <row r="65" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B65" s="95" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="96">
         <f>Utilidad!A62</f>
@@ -24247,7 +24355,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="95" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G65" s="186">
         <f>Utilidad!B62</f>
@@ -24276,7 +24384,7 @@
     </row>
     <row r="66" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B66" s="95" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C66" s="96">
         <f>Utilidad!A63</f>
@@ -24287,7 +24395,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="95" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G66" s="186">
         <f>Utilidad!B63</f>
@@ -24316,7 +24424,7 @@
     </row>
     <row r="67" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B67" s="95" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C67" s="96">
         <f>Utilidad!A64</f>
@@ -24327,7 +24435,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="95" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G67" s="186">
         <f>Utilidad!B64</f>
@@ -24356,7 +24464,7 @@
     </row>
     <row r="68" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B68" s="95" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C68" s="96">
         <f>Utilidad!A65</f>
@@ -24367,7 +24475,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="95" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G68" s="186">
         <f>Utilidad!B65</f>
@@ -24396,7 +24504,7 @@
     </row>
     <row r="69" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B69" s="95" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C69" s="96">
         <f>Utilidad!A66</f>
@@ -24407,7 +24515,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="95" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G69" s="186">
         <f>Utilidad!B66</f>
@@ -24436,7 +24544,7 @@
     </row>
     <row r="70" spans="2:14" ht="19" x14ac:dyDescent="0.25">
       <c r="B70" s="95" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C70" s="96">
         <f>Utilidad!A67</f>
@@ -24447,7 +24555,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="95" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G70" s="186">
         <f>Utilidad!B67</f>
@@ -24548,16 +24656,16 @@
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B6" s="7"/>
       <c r="E6" s="25">
-        <f>+Utilidad!J62</f>
-        <v>0</v>
+        <f>Flujos!G4</f>
+        <v>150420</v>
       </c>
       <c r="S6" s="24"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B7" s="7"/>
       <c r="E7" s="26">
-        <f>+Utilidad!K62</f>
-        <v>0</v>
+        <f>Flujos!H4</f>
+        <v>0.23879999999999998</v>
       </c>
       <c r="I7" s="25">
         <f>+Utilidad!J65</f>
@@ -24568,16 +24676,16 @@
         <v>0</v>
       </c>
       <c r="Q7" s="27">
-        <f>+Utilidad!J70</f>
-        <v>0</v>
+        <f>Flujos!G12</f>
+        <v>24875.066452999999</v>
       </c>
       <c r="S7" s="24"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B8" s="7"/>
       <c r="E8" s="28">
-        <f>+Utilidad!L62</f>
-        <v>0</v>
+        <f>E6*E7</f>
+        <v>35920.295999999995</v>
       </c>
       <c r="I8" s="26">
         <f>+Utilidad!K65</f>
@@ -24588,8 +24696,8 @@
         <v>0</v>
       </c>
       <c r="Q8" s="29">
-        <f>+Utilidad!K70</f>
-        <v>0</v>
+        <f>Flujos!H12</f>
+        <v>0.19247</v>
       </c>
       <c r="S8" s="24"/>
     </row>
@@ -24605,7 +24713,7 @@
       </c>
       <c r="Q9" s="30">
         <f>Q7*Q8</f>
-        <v>0</v>
+        <v>4787.7040402089096</v>
       </c>
       <c r="S9" s="24"/>
     </row>
@@ -24625,7 +24733,7 @@
       </c>
       <c r="Q11" s="27">
         <f>+Utilidad!J71</f>
-        <v>14883.876700000001</v>
+        <v>15456.336685</v>
       </c>
       <c r="S11" s="24"/>
     </row>
@@ -24657,11 +24765,11 @@
       </c>
       <c r="N13" s="25">
         <f>+Utilidad!J72</f>
-        <v>60996</v>
+        <v>64047.727577999998</v>
       </c>
       <c r="Q13" s="30">
         <f>+Utilidad!L71</f>
-        <v>1616.1657514694998</v>
+        <v>1678.3263189407248</v>
       </c>
       <c r="S13" s="24"/>
     </row>
@@ -24685,15 +24793,15 @@
       </c>
       <c r="N14" s="26">
         <f>+Utilidad!K72</f>
-        <v>0.36599999999999999</v>
+        <v>0.35689666413999999</v>
       </c>
       <c r="S14" s="24"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B15" s="7"/>
       <c r="G15" s="34">
-        <f>+Utilidad!J64</f>
-        <v>0</v>
+        <f>Flujos!G6</f>
+        <v>60303</v>
       </c>
       <c r="H15" s="35">
         <f>+Utilidad!L66</f>
@@ -24705,7 +24813,7 @@
       </c>
       <c r="N15" s="28">
         <f>+Utilidad!L72</f>
-        <v>22324.536</v>
+        <v>22858.42031833568</v>
       </c>
       <c r="S15" s="24"/>
     </row>
@@ -24716,15 +24824,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="37">
-        <f>+Utilidad!K64</f>
-        <v>0</v>
+        <f>Flujos!H6</f>
+        <v>0.13205</v>
       </c>
       <c r="L16" s="30">
         <f>+Utilidad!L69</f>
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="S16" s="24"/>
     </row>
@@ -24732,10 +24840,10 @@
       <c r="B17" s="7"/>
       <c r="G17" s="38">
         <f>G15*G16</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="25">
-        <f>Flujos!G65</f>
+        <v>7963.0111500000003</v>
+      </c>
+      <c r="P17" s="27">
+        <f>Flujos!G70</f>
         <v>0</v>
       </c>
       <c r="S17" s="24"/>
@@ -24746,8 +24854,8 @@
         <f>Flujos!C56</f>
         <v>37855</v>
       </c>
-      <c r="P18" s="26">
-        <f>Flujos!H65</f>
+      <c r="P18" s="29">
+        <f>Flujos!H70</f>
         <v>0</v>
       </c>
       <c r="S18" s="24"/>
@@ -24758,7 +24866,7 @@
         <f>Flujos!D56</f>
         <v>0.50360000000000005</v>
       </c>
-      <c r="P19" s="28">
+      <c r="P19" s="30">
         <f>P17*P18</f>
         <v>0</v>
       </c>
@@ -24776,7 +24884,7 @@
       </c>
       <c r="N20" s="33">
         <f>+L14+N13+K18-M22-L20</f>
-        <v>9165</v>
+        <v>12216.727577999991</v>
       </c>
       <c r="S20" s="24"/>
     </row>
@@ -24788,7 +24896,7 @@
       <c r="B22" s="7"/>
       <c r="L22" s="26">
         <f>+Utilidad!K76</f>
-        <v>0.41851701226999999</v>
+        <v>0.41240586135000001</v>
       </c>
       <c r="M22" s="25">
         <f>+Utilidad!J74</f>
@@ -24804,15 +24912,15 @@
       <c r="B23" s="7"/>
       <c r="L23" s="28">
         <f>+Utilidad!L76</f>
-        <v>36933.707815815229</v>
+        <v>36394.404858276153</v>
       </c>
       <c r="M23" s="26">
         <f>+Utilidad!K74</f>
-        <v>0.49758945171000002</v>
+        <v>0.49744623737999999</v>
       </c>
       <c r="O23" s="26">
         <f>+Utilidad!K73</f>
-        <v>0.47103200000000001</v>
+        <v>0.47983531085999998</v>
       </c>
       <c r="S23" s="24"/>
     </row>
@@ -24820,11 +24928,11 @@
       <c r="B24" s="7"/>
       <c r="M24" s="28">
         <f>+Utilidad!L74</f>
-        <v>715.03604210727008</v>
+        <v>714.83024311505994</v>
       </c>
       <c r="O24" s="28">
         <f>+Utilidad!L73</f>
-        <v>9499.3023439999997</v>
+        <v>9676.8387141136191</v>
       </c>
       <c r="Q24" t="e">
         <f>+(O22+N13)/(L7)</f>
@@ -24890,7 +24998,7 @@
       </c>
       <c r="K29" s="37">
         <f>+Utilidad!K78</f>
-        <v>0.65033937957999999</v>
+        <v>0.64685681119999994</v>
       </c>
       <c r="M29">
         <f>K28/(L20+M22+O22)</f>
@@ -24911,7 +25019,7 @@
       </c>
       <c r="K30" s="38">
         <f>+Utilidad!L78</f>
-        <v>42930.203124834959</v>
+        <v>42700.311820934396</v>
       </c>
       <c r="O30" s="2">
         <f>O29-K28</f>
@@ -24924,7 +25032,7 @@
       <c r="C31" s="130"/>
       <c r="I31" s="37">
         <f>+Utilidad!K77</f>
-        <v>9.6207729683000009E-2</v>
+        <v>9.3195E-2</v>
       </c>
       <c r="S31" s="24"/>
     </row>
@@ -24933,7 +25041,7 @@
       <c r="C32" s="130"/>
       <c r="I32" s="38">
         <f>I30*I31</f>
-        <v>4217.843077032403</v>
+        <v>4085.7619949999998</v>
       </c>
       <c r="S32" s="24"/>
     </row>
@@ -25002,6 +25110,7 @@
         <f>K28-(I53+L53)</f>
         <v>-5099</v>
       </c>
+      <c r="N39" s="2"/>
       <c r="S39" s="24"/>
     </row>
     <row r="40" spans="2:19" x14ac:dyDescent="0.2">
@@ -25115,11 +25224,11 @@
       </c>
       <c r="I54" s="32">
         <f>+Utilidad!K82</f>
-        <v>0.64819854000999999</v>
+        <v>0.63137300000000007</v>
       </c>
       <c r="L54" s="32">
         <f>+Utilidad!K83</f>
-        <v>0.65110195969000006</v>
+        <v>0.64981910904000006</v>
       </c>
       <c r="S54" s="24"/>
     </row>
@@ -25131,11 +25240,11 @@
       </c>
       <c r="I55" s="35">
         <f>+Utilidad!L82</f>
-        <v>921.73832389422</v>
+        <v>897.81240600000012</v>
       </c>
       <c r="L55" s="35">
         <f>+Utilidad!L83</f>
-        <v>45374.644468836414</v>
+        <v>45285.243889888567</v>
       </c>
       <c r="S55" s="24"/>
     </row>
@@ -25167,7 +25276,7 @@
       <c r="B59" s="7"/>
       <c r="M59" s="29">
         <f>Flujos!H24</f>
-        <v>0.64819854000999999</v>
+        <v>0.63137300000000007</v>
       </c>
       <c r="S59" s="24"/>
     </row>
@@ -25175,7 +25284,7 @@
       <c r="B60" s="7"/>
       <c r="M60" s="30">
         <f>M59*M58</f>
-        <v>921.73832389422</v>
+        <v>897.81240600000012</v>
       </c>
       <c r="S60" s="24"/>
     </row>
@@ -25245,7 +25354,7 @@
       </c>
       <c r="L66" s="29">
         <f>Flujos!H25</f>
-        <v>0.65110195969000006</v>
+        <v>0.64981910904000006</v>
       </c>
       <c r="S66" s="24"/>
     </row>
@@ -25260,7 +25369,7 @@
       </c>
       <c r="L67" s="30">
         <f>L66*L65</f>
-        <v>45374.644468836414</v>
+        <v>45285.243889888567</v>
       </c>
       <c r="N67" s="36">
         <f>Flujos!G26</f>
@@ -25567,162 +25676,162 @@
       </c>
     </row>
     <row r="96" spans="2:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G96" s="231" t="s">
+      <c r="G96" s="230" t="s">
         <v>69</v>
       </c>
-      <c r="H96" s="231"/>
-      <c r="I96" s="232"/>
-      <c r="J96" s="233" t="s">
+      <c r="H96" s="230"/>
+      <c r="I96" s="231"/>
+      <c r="J96" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="K96" s="233"/>
-      <c r="L96" s="233"/>
-      <c r="M96" s="234" t="s">
+      <c r="K96" s="232"/>
+      <c r="L96" s="232"/>
+      <c r="M96" s="233" t="s">
         <v>71</v>
       </c>
-      <c r="N96" s="234"/>
-      <c r="O96" s="234"/>
-      <c r="P96" s="234"/>
+      <c r="N96" s="233"/>
+      <c r="O96" s="233"/>
+      <c r="P96" s="233"/>
     </row>
     <row r="97" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G97" s="219" t="s">
+      <c r="G97" s="234" t="s">
         <v>72</v>
       </c>
-      <c r="H97" s="220"/>
+      <c r="H97" s="235"/>
       <c r="I97" s="21">
         <f>+E6</f>
-        <v>0</v>
-      </c>
-      <c r="J97" s="221" t="s">
+        <v>150420</v>
+      </c>
+      <c r="J97" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="K97" s="222"/>
+      <c r="K97" s="218"/>
       <c r="L97" s="10">
         <f>Flujos!G9</f>
-        <v>-26556</v>
-      </c>
-      <c r="M97" s="222" t="s">
+        <v>-34429.130716</v>
+      </c>
+      <c r="M97" s="218" t="s">
         <v>73</v>
       </c>
-      <c r="N97" s="222"/>
-      <c r="O97" s="222"/>
+      <c r="N97" s="218"/>
+      <c r="O97" s="218"/>
       <c r="P97" s="10">
         <f>+G15</f>
-        <v>0</v>
+        <v>60303</v>
       </c>
     </row>
     <row r="98" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G98" s="219" t="s">
+      <c r="G98" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="H98" s="220"/>
+      <c r="H98" s="235"/>
       <c r="I98" s="21">
         <f>+C12</f>
         <v>0</v>
       </c>
-      <c r="J98" s="222" t="s">
+      <c r="J98" s="218" t="s">
         <v>8</v>
       </c>
-      <c r="K98" s="222"/>
+      <c r="K98" s="218"/>
       <c r="L98" s="10">
         <f>Flujos!G17</f>
-        <v>9165</v>
-      </c>
-      <c r="M98" s="222" t="s">
+        <v>12216.727578</v>
+      </c>
+      <c r="M98" s="218" t="s">
         <v>22</v>
       </c>
-      <c r="N98" s="222"/>
-      <c r="O98" s="222"/>
+      <c r="N98" s="218"/>
+      <c r="O98" s="218"/>
       <c r="P98" s="10">
         <f>+Q7</f>
-        <v>0</v>
+        <v>24875.066452999999</v>
       </c>
     </row>
     <row r="99" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G99" s="219" t="s">
+      <c r="G99" s="234" t="s">
         <v>75</v>
       </c>
-      <c r="H99" s="220"/>
+      <c r="H99" s="235"/>
       <c r="I99" s="21">
         <f>+H13</f>
         <v>0</v>
       </c>
-      <c r="J99" s="222" t="s">
+      <c r="J99" s="218" t="s">
         <v>76</v>
       </c>
-      <c r="K99" s="222"/>
+      <c r="K99" s="218"/>
       <c r="L99" s="10">
         <v>0</v>
       </c>
-      <c r="M99" s="222" t="s">
+      <c r="M99" s="218" t="s">
         <v>23</v>
       </c>
-      <c r="N99" s="222"/>
-      <c r="O99" s="222"/>
+      <c r="N99" s="218"/>
+      <c r="O99" s="218"/>
       <c r="P99" s="10">
         <f>+Q11</f>
-        <v>14883.876700000001</v>
+        <v>15456.336685</v>
       </c>
     </row>
     <row r="100" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G100" s="223" t="s">
+      <c r="G100" s="219" t="s">
         <v>77</v>
       </c>
-      <c r="H100" s="224"/>
+      <c r="H100" s="220"/>
       <c r="I100" s="21">
         <f>+C26</f>
         <v>0</v>
       </c>
-      <c r="J100" s="222" t="s">
+      <c r="J100" s="218" t="s">
         <v>11</v>
       </c>
-      <c r="K100" s="222"/>
+      <c r="K100" s="218"/>
       <c r="L100" s="10">
         <f>Flujos!G21</f>
         <v>-5099</v>
       </c>
-      <c r="M100" s="222" t="s">
+      <c r="M100" s="218" t="s">
         <v>78</v>
       </c>
-      <c r="N100" s="222"/>
-      <c r="O100" s="222"/>
+      <c r="N100" s="218"/>
+      <c r="O100" s="218"/>
       <c r="P100" s="10">
         <f>+I30</f>
         <v>43841</v>
       </c>
     </row>
     <row r="101" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G101" s="223" t="s">
+      <c r="G101" s="219" t="s">
         <v>57</v>
       </c>
-      <c r="H101" s="224"/>
+      <c r="H101" s="220"/>
       <c r="I101" s="21">
         <f>+C35</f>
         <v>0</v>
       </c>
-      <c r="J101" s="222" t="s">
+      <c r="J101" s="218" t="s">
         <v>79</v>
       </c>
-      <c r="K101" s="222"/>
+      <c r="K101" s="218"/>
       <c r="L101" s="10">
         <f>Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="M101" s="222" t="s">
+      <c r="M101" s="218" t="s">
         <v>80</v>
       </c>
-      <c r="N101" s="222"/>
-      <c r="O101" s="222"/>
+      <c r="N101" s="218"/>
+      <c r="O101" s="218"/>
       <c r="P101" s="10">
         <f>+M58</f>
         <v>1422</v>
       </c>
     </row>
     <row r="102" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G102" s="223" t="s">
+      <c r="G102" s="219" t="s">
         <v>60</v>
       </c>
-      <c r="H102" s="224"/>
+      <c r="H102" s="220"/>
       <c r="I102" s="21">
         <f>+C44</f>
         <v>0</v>
@@ -25735,21 +25844,21 @@
         <f>Flujos!G44</f>
         <v>0</v>
       </c>
-      <c r="M102" s="222" t="s">
+      <c r="M102" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="N102" s="222"/>
-      <c r="O102" s="222"/>
+      <c r="N102" s="218"/>
+      <c r="O102" s="218"/>
       <c r="P102" s="10">
         <f>+O63</f>
         <v>73127</v>
       </c>
     </row>
     <row r="103" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G103" s="223" t="s">
+      <c r="G103" s="219" t="s">
         <v>83</v>
       </c>
-      <c r="H103" s="224"/>
+      <c r="H103" s="220"/>
       <c r="I103" s="21">
         <f>+C54</f>
         <v>0</v>
@@ -25762,21 +25871,21 @@
         <f>Flujos!G47</f>
         <v>0</v>
       </c>
-      <c r="M103" s="222" t="s">
+      <c r="M103" s="218" t="s">
         <v>85</v>
       </c>
-      <c r="N103" s="222"/>
-      <c r="O103" s="222"/>
+      <c r="N103" s="218"/>
+      <c r="O103" s="218"/>
       <c r="P103" s="10">
         <f>+O67</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G104" s="223" t="s">
+      <c r="G104" s="219" t="s">
         <v>86</v>
       </c>
-      <c r="H104" s="224"/>
+      <c r="H104" s="220"/>
       <c r="I104" s="21">
         <f>+C62</f>
         <v>37855</v>
@@ -25789,21 +25898,21 @@
         <f>Flujos!G50</f>
         <v>0</v>
       </c>
-      <c r="M104" s="222" t="s">
+      <c r="M104" s="218" t="s">
         <v>44</v>
       </c>
-      <c r="N104" s="222"/>
-      <c r="O104" s="222"/>
+      <c r="N104" s="218"/>
+      <c r="O104" s="218"/>
       <c r="P104" s="10">
         <f>+O74</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G105" s="223" t="s">
+      <c r="G105" s="219" t="s">
         <v>88</v>
       </c>
-      <c r="H105" s="224"/>
+      <c r="H105" s="220"/>
       <c r="I105" s="21">
         <f>+H70</f>
         <v>0</v>
@@ -25816,38 +25925,38 @@
         <f>Flujos!G53</f>
         <v>0</v>
       </c>
-      <c r="M105" s="222" t="s">
+      <c r="M105" s="218" t="s">
         <v>90</v>
       </c>
-      <c r="N105" s="222"/>
-      <c r="O105" s="222"/>
+      <c r="N105" s="218"/>
+      <c r="O105" s="218"/>
       <c r="P105" s="10">
         <f>+O84</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G106" s="223" t="s">
+      <c r="G106" s="219" t="s">
         <v>91</v>
       </c>
-      <c r="H106" s="224"/>
+      <c r="H106" s="220"/>
       <c r="I106" s="21">
         <f>+H75</f>
         <v>0</v>
       </c>
-      <c r="J106" s="222" t="s">
+      <c r="J106" s="218" t="s">
         <v>13</v>
       </c>
-      <c r="K106" s="222"/>
+      <c r="K106" s="218"/>
       <c r="L106" s="10">
         <f>Flujos!G42</f>
         <v>0</v>
       </c>
-      <c r="M106" s="222" t="s">
+      <c r="M106" s="218" t="s">
         <v>158</v>
       </c>
-      <c r="N106" s="222"/>
-      <c r="O106" s="222"/>
+      <c r="N106" s="218"/>
+      <c r="O106" s="218"/>
       <c r="P106" s="10">
         <f>Q79</f>
         <v>0</v>
@@ -25870,11 +25979,11 @@
         <f>Flujos!G26</f>
         <v>-3438</v>
       </c>
-      <c r="M107" s="301" t="s">
-        <v>205</v>
-      </c>
-      <c r="N107" s="302"/>
-      <c r="O107" s="303"/>
+      <c r="M107" s="221" t="s">
+        <v>201</v>
+      </c>
+      <c r="N107" s="222"/>
+      <c r="O107" s="223"/>
       <c r="P107" s="10"/>
     </row>
     <row r="108" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -25886,17 +25995,17 @@
         <f>+L78</f>
         <v>0</v>
       </c>
-      <c r="J108" s="222" t="s">
+      <c r="J108" s="218" t="s">
         <v>12</v>
       </c>
-      <c r="K108" s="222"/>
+      <c r="K108" s="218"/>
       <c r="L108" s="10">
         <f>Flujos!G34</f>
         <v>6226</v>
       </c>
-      <c r="M108" s="228"/>
-      <c r="N108" s="229"/>
-      <c r="O108" s="230"/>
+      <c r="M108" s="224"/>
+      <c r="N108" s="225"/>
+      <c r="O108" s="226"/>
       <c r="P108" s="10"/>
     </row>
     <row r="109" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -25908,152 +26017,152 @@
         <f>+K86</f>
         <v>0</v>
       </c>
-      <c r="J109" s="222" t="s">
+      <c r="J109" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="K109" s="222"/>
+      <c r="K109" s="218"/>
       <c r="L109" s="10">
         <f>Flujos!G39</f>
         <v>0</v>
       </c>
-      <c r="M109" s="228"/>
-      <c r="N109" s="229"/>
-      <c r="O109" s="230"/>
+      <c r="M109" s="224"/>
+      <c r="N109" s="225"/>
+      <c r="O109" s="226"/>
       <c r="P109" s="10"/>
     </row>
     <row r="110" spans="7:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G110" s="223" t="s">
+      <c r="G110" s="219" t="s">
         <v>96</v>
       </c>
-      <c r="H110" s="224"/>
+      <c r="H110" s="220"/>
       <c r="I110" s="21">
         <f>+L90</f>
         <v>0</v>
       </c>
-      <c r="J110" s="222" t="s">
-        <v>204</v>
-      </c>
-      <c r="K110" s="222"/>
+      <c r="J110" s="218" t="s">
+        <v>200</v>
+      </c>
+      <c r="K110" s="218"/>
       <c r="L110" s="10">
         <f>Flujos!G69</f>
         <v>0</v>
       </c>
-      <c r="M110" s="222"/>
-      <c r="N110" s="222"/>
-      <c r="O110" s="222"/>
+      <c r="M110" s="218"/>
+      <c r="N110" s="218"/>
+      <c r="O110" s="218"/>
       <c r="P110" s="10"/>
     </row>
     <row r="111" spans="7:16" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G111" s="223" t="s">
+      <c r="G111" s="219" t="s">
         <v>173</v>
       </c>
-      <c r="H111" s="224"/>
+      <c r="H111" s="220"/>
       <c r="I111" s="21">
         <f>K82</f>
         <v>3157</v>
       </c>
-      <c r="J111" s="222"/>
-      <c r="K111" s="222"/>
+      <c r="J111" s="218"/>
+      <c r="K111" s="218"/>
       <c r="L111" s="10"/>
-      <c r="M111" s="222"/>
-      <c r="N111" s="222"/>
-      <c r="O111" s="222"/>
+      <c r="M111" s="218"/>
+      <c r="N111" s="218"/>
+      <c r="O111" s="218"/>
       <c r="P111" s="10"/>
     </row>
     <row r="112" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G112" s="223" t="s">
+      <c r="G112" s="219" t="s">
         <v>177</v>
       </c>
-      <c r="H112" s="224" t="s">
+      <c r="H112" s="220" t="s">
         <v>166</v>
       </c>
       <c r="I112" s="21">
         <f>Flujos!G59</f>
         <v>0</v>
       </c>
-      <c r="J112" s="222"/>
-      <c r="K112" s="222"/>
+      <c r="J112" s="218"/>
+      <c r="K112" s="218"/>
       <c r="L112" s="10"/>
-      <c r="M112" s="222"/>
-      <c r="N112" s="222"/>
-      <c r="O112" s="222"/>
+      <c r="M112" s="218"/>
+      <c r="N112" s="218"/>
+      <c r="O112" s="218"/>
       <c r="P112" s="10"/>
     </row>
     <row r="113" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G113" s="223" t="s">
+      <c r="G113" s="219" t="s">
         <v>178</v>
       </c>
-      <c r="H113" s="224" t="s">
+      <c r="H113" s="220" t="s">
         <v>167</v>
       </c>
       <c r="I113" s="21">
         <f>Flujos!G60</f>
         <v>3069</v>
       </c>
-      <c r="J113" s="222"/>
-      <c r="K113" s="222"/>
+      <c r="J113" s="218"/>
+      <c r="K113" s="218"/>
       <c r="L113" s="10"/>
-      <c r="M113" s="222"/>
-      <c r="N113" s="222"/>
-      <c r="O113" s="222"/>
+      <c r="M113" s="218"/>
+      <c r="N113" s="218"/>
+      <c r="O113" s="218"/>
       <c r="P113" s="10"/>
     </row>
     <row r="114" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G114" s="223" t="s">
+      <c r="G114" s="219" t="s">
         <v>179</v>
       </c>
-      <c r="H114" s="224" t="s">
+      <c r="H114" s="220" t="s">
         <v>168</v>
       </c>
       <c r="I114" s="21">
         <f>Flujos!G61</f>
         <v>0</v>
       </c>
-      <c r="J114" s="222"/>
-      <c r="K114" s="222"/>
+      <c r="J114" s="218"/>
+      <c r="K114" s="218"/>
       <c r="L114" s="10"/>
-      <c r="M114" s="222"/>
-      <c r="N114" s="222"/>
-      <c r="O114" s="222"/>
+      <c r="M114" s="218"/>
+      <c r="N114" s="218"/>
+      <c r="O114" s="218"/>
       <c r="P114" s="10"/>
     </row>
     <row r="115" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G115" s="223" t="s">
-        <v>190</v>
-      </c>
-      <c r="H115" s="224"/>
+      <c r="G115" s="219" t="s">
+        <v>188</v>
+      </c>
+      <c r="H115" s="220"/>
       <c r="I115" s="21">
         <f>Flujos!G62</f>
         <v>0</v>
       </c>
-      <c r="J115" s="222"/>
-      <c r="K115" s="222"/>
+      <c r="J115" s="218"/>
+      <c r="K115" s="218"/>
       <c r="L115" s="10"/>
-      <c r="M115" s="222"/>
-      <c r="N115" s="222"/>
-      <c r="O115" s="222"/>
+      <c r="M115" s="218"/>
+      <c r="N115" s="218"/>
+      <c r="O115" s="218"/>
       <c r="P115" s="10"/>
     </row>
     <row r="116" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G116" s="223" t="s">
-        <v>201</v>
-      </c>
-      <c r="H116" s="224"/>
+      <c r="G116" s="219" t="s">
+        <v>197</v>
+      </c>
+      <c r="H116" s="220"/>
       <c r="I116" s="21">
         <f>Flujos!G66</f>
         <v>0</v>
       </c>
-      <c r="J116" s="222"/>
-      <c r="K116" s="222"/>
+      <c r="J116" s="218"/>
+      <c r="K116" s="218"/>
       <c r="L116" s="10"/>
-      <c r="M116" s="222"/>
-      <c r="N116" s="222"/>
-      <c r="O116" s="222"/>
+      <c r="M116" s="218"/>
+      <c r="N116" s="218"/>
+      <c r="O116" s="218"/>
       <c r="P116" s="10"/>
     </row>
     <row r="117" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G117" s="19" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H117" s="20"/>
       <c r="I117" s="21">
@@ -26070,7 +26179,7 @@
     </row>
     <row r="118" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G118" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H118" s="20"/>
       <c r="I118" s="21">
@@ -26086,42 +26195,42 @@
       <c r="P118" s="10"/>
     </row>
     <row r="119" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G119" s="223"/>
-      <c r="H119" s="224"/>
+      <c r="G119" s="219"/>
+      <c r="H119" s="220"/>
       <c r="I119" s="21"/>
-      <c r="J119" s="222"/>
-      <c r="K119" s="222"/>
+      <c r="J119" s="218"/>
+      <c r="K119" s="218"/>
       <c r="L119" s="10"/>
-      <c r="M119" s="222"/>
-      <c r="N119" s="222"/>
-      <c r="O119" s="222"/>
+      <c r="M119" s="218"/>
+      <c r="N119" s="218"/>
+      <c r="O119" s="218"/>
       <c r="P119" s="10"/>
     </row>
     <row r="120" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G120" s="225" t="s">
+      <c r="G120" s="227" t="s">
         <v>97</v>
       </c>
-      <c r="H120" s="226"/>
+      <c r="H120" s="228"/>
       <c r="I120" s="12">
         <f>+SUM(I97:I119)</f>
-        <v>44081</v>
-      </c>
-      <c r="J120" s="227" t="s">
+        <v>194501</v>
+      </c>
+      <c r="J120" s="229" t="s">
         <v>98</v>
       </c>
-      <c r="K120" s="227"/>
+      <c r="K120" s="229"/>
       <c r="L120" s="13">
         <f>+SUM(L97:L110)</f>
-        <v>-19702</v>
-      </c>
-      <c r="M120" s="227" t="s">
+        <v>-24523.403138000001</v>
+      </c>
+      <c r="M120" s="229" t="s">
         <v>99</v>
       </c>
-      <c r="N120" s="227"/>
-      <c r="O120" s="227"/>
+      <c r="N120" s="229"/>
+      <c r="O120" s="229"/>
       <c r="P120" s="12">
         <f>+SUM(P97:P110)</f>
-        <v>133273.87669999999</v>
+        <v>219024.40313799999</v>
       </c>
     </row>
     <row r="121" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26148,7 +26257,7 @@
       <c r="O122" s="16"/>
       <c r="P122" s="18">
         <f>+I120-L120-P120</f>
-        <v>-69490.876699999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -26160,48 +26269,48 @@
       </c>
     </row>
     <row r="127" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G127" s="215" t="s">
+      <c r="G127" s="237" t="s">
         <v>69</v>
       </c>
-      <c r="H127" s="215"/>
-      <c r="I127" s="216"/>
-      <c r="J127" s="217" t="s">
+      <c r="H127" s="237"/>
+      <c r="I127" s="238"/>
+      <c r="J127" s="239" t="s">
         <v>70</v>
       </c>
-      <c r="K127" s="217"/>
-      <c r="L127" s="217"/>
-      <c r="M127" s="218" t="s">
+      <c r="K127" s="239"/>
+      <c r="L127" s="239"/>
+      <c r="M127" s="240" t="s">
         <v>71</v>
       </c>
-      <c r="N127" s="218"/>
-      <c r="O127" s="218"/>
-      <c r="P127" s="218"/>
+      <c r="N127" s="240"/>
+      <c r="O127" s="240"/>
+      <c r="P127" s="240"/>
     </row>
     <row r="128" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G128" s="219" t="s">
+      <c r="G128" s="234" t="s">
         <v>72</v>
       </c>
-      <c r="H128" s="220"/>
+      <c r="H128" s="235"/>
       <c r="I128" s="21">
         <f>+E8</f>
-        <v>0</v>
-      </c>
-      <c r="J128" s="221" t="s">
+        <v>35920.295999999995</v>
+      </c>
+      <c r="J128" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="K128" s="222"/>
+      <c r="K128" s="218"/>
       <c r="L128" s="10">
         <f>Flujos!G9*Flujos!H9</f>
-        <v>-9452.6291970325201</v>
-      </c>
-      <c r="M128" s="222" t="s">
+        <v>-11044.004405424901</v>
+      </c>
+      <c r="M128" s="218" t="s">
         <v>73</v>
       </c>
-      <c r="N128" s="222"/>
-      <c r="O128" s="222"/>
+      <c r="N128" s="218"/>
+      <c r="O128" s="218"/>
       <c r="P128" s="10">
         <f>+G17</f>
-        <v>0</v>
+        <v>7963.0111500000003</v>
       </c>
     </row>
     <row r="129" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26219,7 +26328,7 @@
       <c r="K129" s="11"/>
       <c r="L129" s="10">
         <f>Flujos!G17*Flujos!H17</f>
-        <v>3739.5701419030502</v>
+        <v>4812.9630802667698</v>
       </c>
       <c r="M129" s="11" t="s">
         <v>22</v>
@@ -26228,7 +26337,7 @@
       <c r="O129" s="11"/>
       <c r="P129" s="10">
         <f>+Q9</f>
-        <v>0</v>
+        <v>4787.7040402089096</v>
       </c>
     </row>
     <row r="130" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26254,7 +26363,7 @@
       <c r="O130" s="11"/>
       <c r="P130" s="10">
         <f>+Q13</f>
-        <v>1616.1657514694998</v>
+        <v>1678.3263189407248</v>
       </c>
     </row>
     <row r="131" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26272,7 +26381,7 @@
       <c r="K131" s="11"/>
       <c r="L131" s="10">
         <f>Flujos!G21*Flujos!H21</f>
-        <v>-3366.1796673720501</v>
+        <v>-3482.744475</v>
       </c>
       <c r="M131" s="11" t="s">
         <v>78</v>
@@ -26281,7 +26390,7 @@
       <c r="O131" s="11"/>
       <c r="P131" s="10">
         <f>+I32</f>
-        <v>4217.843077032403</v>
+        <v>4085.7619949999998</v>
       </c>
     </row>
     <row r="132" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26308,7 +26417,7 @@
       <c r="O132" s="11"/>
       <c r="P132" s="10">
         <f>+M60</f>
-        <v>921.73832389422</v>
+        <v>897.81240600000012</v>
       </c>
     </row>
     <row r="133" spans="7:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26461,13 +26570,13 @@
       <c r="K138" s="11"/>
       <c r="L138" s="10">
         <f>Flujos!G26*Flujos!H26</f>
-        <v>-2260.2833314581599</v>
-      </c>
-      <c r="M138" s="301" t="s">
-        <v>205</v>
-      </c>
-      <c r="N138" s="302"/>
-      <c r="O138" s="303"/>
+        <v>-2349.6839099999997</v>
+      </c>
+      <c r="M138" s="221" t="s">
+        <v>201</v>
+      </c>
+      <c r="N138" s="222"/>
+      <c r="O138" s="223"/>
       <c r="P138" s="10">
         <f>Flujos!G68*Flujos!H68</f>
         <v>0</v>
@@ -26490,9 +26599,9 @@
         <f>Flujos!G34*Flujos!H34</f>
         <v>3936.9021999755796</v>
       </c>
-      <c r="M139" s="228"/>
-      <c r="N139" s="229"/>
-      <c r="O139" s="230"/>
+      <c r="M139" s="224"/>
+      <c r="N139" s="225"/>
+      <c r="O139" s="226"/>
       <c r="P139" s="10"/>
     </row>
     <row r="140" spans="7:16" x14ac:dyDescent="0.2">
@@ -26526,10 +26635,10 @@
         <f>+L92</f>
         <v>0</v>
       </c>
-      <c r="J141" s="222" t="s">
-        <v>204</v>
-      </c>
-      <c r="K141" s="222"/>
+      <c r="J141" s="218" t="s">
+        <v>200</v>
+      </c>
+      <c r="K141" s="218"/>
       <c r="L141" s="10">
         <f>Flujos!G69*Flujos!H69</f>
         <v>0</v>
@@ -26540,10 +26649,10 @@
       <c r="P141" s="10"/>
     </row>
     <row r="142" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G142" s="223" t="s">
+      <c r="G142" s="219" t="s">
         <v>173</v>
       </c>
-      <c r="H142" s="224"/>
+      <c r="H142" s="220"/>
       <c r="I142" s="21">
         <f>K84</f>
         <v>2003.4322000000002</v>
@@ -26554,78 +26663,78 @@
       <c r="P142" s="10"/>
     </row>
     <row r="143" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G143" s="223" t="s">
+      <c r="G143" s="219" t="s">
         <v>174</v>
       </c>
-      <c r="H143" s="224"/>
+      <c r="H143" s="220"/>
       <c r="I143" s="21">
         <f>Flujos!G59*Flujos!H59</f>
         <v>0</v>
       </c>
-      <c r="J143" s="222"/>
-      <c r="K143" s="222"/>
+      <c r="J143" s="218"/>
+      <c r="K143" s="218"/>
       <c r="L143" s="10"/>
-      <c r="M143" s="304"/>
-      <c r="N143" s="304"/>
-      <c r="O143" s="304"/>
+      <c r="M143" s="210"/>
+      <c r="N143" s="210"/>
+      <c r="O143" s="210"/>
       <c r="P143" s="10"/>
     </row>
     <row r="144" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G144" s="223" t="s">
+      <c r="G144" s="219" t="s">
         <v>175</v>
       </c>
-      <c r="H144" s="224"/>
+      <c r="H144" s="220"/>
       <c r="I144" s="21">
         <f>Flujos!G60*Flujos!H60</f>
         <v>1933.47</v>
       </c>
-      <c r="J144" s="222"/>
-      <c r="K144" s="222"/>
+      <c r="J144" s="218"/>
+      <c r="K144" s="218"/>
       <c r="L144" s="10"/>
-      <c r="M144" s="304"/>
-      <c r="N144" s="304"/>
-      <c r="O144" s="304"/>
+      <c r="M144" s="210"/>
+      <c r="N144" s="210"/>
+      <c r="O144" s="210"/>
       <c r="P144" s="10"/>
     </row>
     <row r="145" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G145" s="223" t="s">
+      <c r="G145" s="219" t="s">
         <v>176</v>
       </c>
-      <c r="H145" s="224"/>
+      <c r="H145" s="220"/>
       <c r="I145" s="21">
         <f>Flujos!G61*Flujos!H61</f>
         <v>0</v>
       </c>
-      <c r="J145" s="222"/>
-      <c r="K145" s="222"/>
+      <c r="J145" s="218"/>
+      <c r="K145" s="218"/>
       <c r="L145" s="10"/>
-      <c r="M145" s="304"/>
-      <c r="N145" s="304"/>
-      <c r="O145" s="304"/>
+      <c r="M145" s="210"/>
+      <c r="N145" s="210"/>
+      <c r="O145" s="210"/>
       <c r="P145" s="10"/>
     </row>
     <row r="146" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G146" s="223" t="s">
-        <v>190</v>
-      </c>
-      <c r="H146" s="224"/>
+      <c r="G146" s="219" t="s">
+        <v>188</v>
+      </c>
+      <c r="H146" s="220"/>
       <c r="I146" s="21">
         <f>Flujos!G62*Flujos!H62</f>
         <v>0</v>
       </c>
-      <c r="J146" s="222"/>
-      <c r="K146" s="222"/>
+      <c r="J146" s="218"/>
+      <c r="K146" s="218"/>
       <c r="L146" s="10"/>
-      <c r="M146" s="304"/>
-      <c r="N146" s="304"/>
-      <c r="O146" s="304"/>
+      <c r="M146" s="210"/>
+      <c r="N146" s="210"/>
+      <c r="O146" s="210"/>
       <c r="P146" s="10"/>
     </row>
     <row r="147" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G147" s="223" t="s">
-        <v>201</v>
-      </c>
-      <c r="H147" s="224"/>
+      <c r="G147" s="219" t="s">
+        <v>197</v>
+      </c>
+      <c r="H147" s="220"/>
       <c r="I147" s="21">
         <f>Flujos!G66*Flujos!H66</f>
         <v>0</v>
@@ -26640,7 +26749,7 @@
     </row>
     <row r="148" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G148" s="19" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H148" s="20"/>
       <c r="I148" s="21">
@@ -26657,58 +26766,58 @@
     </row>
     <row r="149" spans="7:16" x14ac:dyDescent="0.2">
       <c r="G149" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H149" s="20"/>
       <c r="I149" s="21">
         <f>Flujos!G70*Flujos!H70</f>
         <v>0</v>
       </c>
-      <c r="J149" s="222"/>
-      <c r="K149" s="222"/>
+      <c r="J149" s="218"/>
+      <c r="K149" s="218"/>
       <c r="L149" s="10"/>
-      <c r="M149" s="222"/>
-      <c r="N149" s="222"/>
-      <c r="O149" s="222"/>
+      <c r="M149" s="218"/>
+      <c r="N149" s="218"/>
+      <c r="O149" s="218"/>
       <c r="P149" s="10"/>
     </row>
     <row r="150" spans="7:16" x14ac:dyDescent="0.2">
-      <c r="G150" s="223"/>
-      <c r="H150" s="224"/>
+      <c r="G150" s="219"/>
+      <c r="H150" s="220"/>
       <c r="I150" s="21"/>
-      <c r="J150" s="222"/>
-      <c r="K150" s="222"/>
+      <c r="J150" s="218"/>
+      <c r="K150" s="218"/>
       <c r="L150" s="10"/>
-      <c r="M150" s="222"/>
-      <c r="N150" s="222"/>
-      <c r="O150" s="222"/>
+      <c r="M150" s="218"/>
+      <c r="N150" s="218"/>
+      <c r="O150" s="218"/>
       <c r="P150" s="10"/>
     </row>
     <row r="151" spans="7:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="G151" s="225" t="s">
+      <c r="G151" s="227" t="s">
         <v>97</v>
       </c>
-      <c r="H151" s="226"/>
+      <c r="H151" s="228"/>
       <c r="I151" s="12">
         <f>+SUM(I128:I150)</f>
-        <v>23000.680200000003</v>
-      </c>
-      <c r="J151" s="227" t="s">
+        <v>58920.976199999997</v>
+      </c>
+      <c r="J151" s="229" t="s">
         <v>98</v>
       </c>
-      <c r="K151" s="227"/>
+      <c r="K151" s="229"/>
       <c r="L151" s="13">
         <f>+SUM(L128:L141)</f>
-        <v>-7402.6198539840998</v>
-      </c>
-      <c r="M151" s="227" t="s">
+        <v>-8126.5675101825518</v>
+      </c>
+      <c r="M151" s="229" t="s">
         <v>99</v>
       </c>
-      <c r="N151" s="227"/>
-      <c r="O151" s="227"/>
+      <c r="N151" s="229"/>
+      <c r="O151" s="229"/>
       <c r="P151" s="12">
         <f>+SUM(P128:P141)</f>
-        <v>54390.674952396119</v>
+        <v>67047.543710149635</v>
       </c>
     </row>
     <row r="152" spans="7:16" x14ac:dyDescent="0.2">
@@ -26735,11 +26844,83 @@
       <c r="O153" s="16"/>
       <c r="P153" s="18">
         <f>+I151-L151-P151</f>
-        <v>-23987.374898412018</v>
+        <v>3.2916432246565819E-8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="88">
+    <mergeCell ref="G127:I127"/>
+    <mergeCell ref="J127:L127"/>
+    <mergeCell ref="M127:P127"/>
+    <mergeCell ref="G128:H128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="M128:O128"/>
+    <mergeCell ref="M106:O106"/>
+    <mergeCell ref="G110:H110"/>
+    <mergeCell ref="J110:K110"/>
+    <mergeCell ref="M110:O110"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="J120:K120"/>
+    <mergeCell ref="M120:O120"/>
+    <mergeCell ref="J108:K108"/>
+    <mergeCell ref="J109:K109"/>
+    <mergeCell ref="M107:O107"/>
+    <mergeCell ref="M108:O108"/>
+    <mergeCell ref="M109:O109"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="J111:K111"/>
+    <mergeCell ref="M111:O111"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="J106:K106"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="J101:K101"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="J98:K98"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="J99:K99"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="J100:K100"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="J96:L96"/>
+    <mergeCell ref="M96:P96"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="J97:K97"/>
+    <mergeCell ref="M105:O105"/>
+    <mergeCell ref="M97:O97"/>
+    <mergeCell ref="M99:O99"/>
+    <mergeCell ref="M100:O100"/>
+    <mergeCell ref="M101:O101"/>
+    <mergeCell ref="M102:O102"/>
+    <mergeCell ref="M103:O103"/>
+    <mergeCell ref="M98:O98"/>
+    <mergeCell ref="M104:O104"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="J112:K112"/>
+    <mergeCell ref="M112:O112"/>
+    <mergeCell ref="J113:K113"/>
+    <mergeCell ref="M113:O113"/>
+    <mergeCell ref="J114:K114"/>
+    <mergeCell ref="M114:O114"/>
+    <mergeCell ref="J115:K115"/>
+    <mergeCell ref="M115:O115"/>
+    <mergeCell ref="J116:K116"/>
+    <mergeCell ref="M116:O116"/>
+    <mergeCell ref="J119:K119"/>
+    <mergeCell ref="M119:O119"/>
+    <mergeCell ref="J146:K146"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="J143:K143"/>
+    <mergeCell ref="G144:H144"/>
+    <mergeCell ref="J144:K144"/>
     <mergeCell ref="J141:K141"/>
     <mergeCell ref="G147:H147"/>
     <mergeCell ref="M138:O138"/>
@@ -26756,78 +26937,6 @@
     <mergeCell ref="G145:H145"/>
     <mergeCell ref="J145:K145"/>
     <mergeCell ref="G146:H146"/>
-    <mergeCell ref="J146:K146"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="J143:K143"/>
-    <mergeCell ref="G144:H144"/>
-    <mergeCell ref="J144:K144"/>
-    <mergeCell ref="J115:K115"/>
-    <mergeCell ref="M115:O115"/>
-    <mergeCell ref="J116:K116"/>
-    <mergeCell ref="M116:O116"/>
-    <mergeCell ref="J119:K119"/>
-    <mergeCell ref="M119:O119"/>
-    <mergeCell ref="J112:K112"/>
-    <mergeCell ref="M112:O112"/>
-    <mergeCell ref="J113:K113"/>
-    <mergeCell ref="M113:O113"/>
-    <mergeCell ref="J114:K114"/>
-    <mergeCell ref="M114:O114"/>
-    <mergeCell ref="G113:H113"/>
-    <mergeCell ref="G114:H114"/>
-    <mergeCell ref="G115:H115"/>
-    <mergeCell ref="G116:H116"/>
-    <mergeCell ref="G119:H119"/>
-    <mergeCell ref="M105:O105"/>
-    <mergeCell ref="M97:O97"/>
-    <mergeCell ref="M99:O99"/>
-    <mergeCell ref="M100:O100"/>
-    <mergeCell ref="M101:O101"/>
-    <mergeCell ref="M102:O102"/>
-    <mergeCell ref="M103:O103"/>
-    <mergeCell ref="M98:O98"/>
-    <mergeCell ref="M104:O104"/>
-    <mergeCell ref="G96:I96"/>
-    <mergeCell ref="J96:L96"/>
-    <mergeCell ref="M96:P96"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="J97:K97"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="J98:K98"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="J99:K99"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="J100:K100"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="J106:K106"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="G103:H103"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="G106:H106"/>
-    <mergeCell ref="J101:K101"/>
-    <mergeCell ref="M106:O106"/>
-    <mergeCell ref="G110:H110"/>
-    <mergeCell ref="J110:K110"/>
-    <mergeCell ref="M110:O110"/>
-    <mergeCell ref="G120:H120"/>
-    <mergeCell ref="J120:K120"/>
-    <mergeCell ref="M120:O120"/>
-    <mergeCell ref="J108:K108"/>
-    <mergeCell ref="J109:K109"/>
-    <mergeCell ref="M107:O107"/>
-    <mergeCell ref="M108:O108"/>
-    <mergeCell ref="M109:O109"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="J111:K111"/>
-    <mergeCell ref="M111:O111"/>
-    <mergeCell ref="G112:H112"/>
-    <mergeCell ref="G127:I127"/>
-    <mergeCell ref="J127:L127"/>
-    <mergeCell ref="M127:P127"/>
-    <mergeCell ref="G128:H128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="M128:O128"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29700,85 +29809,85 @@
     <row r="3" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B3" s="49"/>
       <c r="C3" s="50"/>
-      <c r="D3" s="284"/>
-      <c r="E3" s="285"/>
-      <c r="F3" s="290" t="s">
+      <c r="D3" s="255"/>
+      <c r="E3" s="256"/>
+      <c r="F3" s="261" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="290"/>
-      <c r="H3" s="290"/>
-      <c r="I3" s="290"/>
-      <c r="J3" s="290"/>
-      <c r="K3" s="290"/>
-      <c r="L3" s="290"/>
-      <c r="M3" s="290"/>
-      <c r="N3" s="290"/>
-      <c r="O3" s="290"/>
-      <c r="P3" s="290"/>
-      <c r="Q3" s="291"/>
+      <c r="G3" s="261"/>
+      <c r="H3" s="261"/>
+      <c r="I3" s="261"/>
+      <c r="J3" s="261"/>
+      <c r="K3" s="261"/>
+      <c r="L3" s="261"/>
+      <c r="M3" s="261"/>
+      <c r="N3" s="261"/>
+      <c r="O3" s="261"/>
+      <c r="P3" s="261"/>
+      <c r="Q3" s="262"/>
       <c r="R3" s="51"/>
     </row>
     <row r="4" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="49"/>
       <c r="C4" s="50"/>
-      <c r="D4" s="286"/>
-      <c r="E4" s="287"/>
-      <c r="F4" s="292"/>
-      <c r="G4" s="292"/>
-      <c r="H4" s="292"/>
-      <c r="I4" s="292"/>
-      <c r="J4" s="292"/>
-      <c r="K4" s="292"/>
-      <c r="L4" s="292"/>
-      <c r="M4" s="292"/>
-      <c r="N4" s="292"/>
-      <c r="O4" s="292"/>
-      <c r="P4" s="292"/>
-      <c r="Q4" s="293"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="258"/>
+      <c r="F4" s="263"/>
+      <c r="G4" s="263"/>
+      <c r="H4" s="263"/>
+      <c r="I4" s="263"/>
+      <c r="J4" s="263"/>
+      <c r="K4" s="263"/>
+      <c r="L4" s="263"/>
+      <c r="M4" s="263"/>
+      <c r="N4" s="263"/>
+      <c r="O4" s="263"/>
+      <c r="P4" s="263"/>
+      <c r="Q4" s="264"/>
       <c r="R4" s="51"/>
     </row>
     <row r="5" spans="2:20" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="49"/>
       <c r="C5" s="50"/>
-      <c r="D5" s="286"/>
-      <c r="E5" s="287"/>
-      <c r="F5" s="292" t="s">
+      <c r="D5" s="257"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="263" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="292"/>
-      <c r="H5" s="292"/>
-      <c r="I5" s="292"/>
-      <c r="J5" s="292"/>
-      <c r="K5" s="292"/>
-      <c r="L5" s="292"/>
-      <c r="M5" s="292" t="s">
+      <c r="G5" s="263"/>
+      <c r="H5" s="263"/>
+      <c r="I5" s="263"/>
+      <c r="J5" s="263"/>
+      <c r="K5" s="263"/>
+      <c r="L5" s="263"/>
+      <c r="M5" s="263" t="s">
         <v>107</v>
       </c>
-      <c r="N5" s="292"/>
+      <c r="N5" s="263"/>
       <c r="O5" s="118"/>
-      <c r="P5" s="295">
+      <c r="P5" s="266">
         <v>45915</v>
       </c>
-      <c r="Q5" s="296"/>
+      <c r="Q5" s="267"/>
       <c r="R5" s="51"/>
     </row>
     <row r="6" spans="2:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="49"/>
       <c r="C6" s="50"/>
-      <c r="D6" s="288"/>
-      <c r="E6" s="289"/>
-      <c r="F6" s="294"/>
-      <c r="G6" s="294"/>
-      <c r="H6" s="294"/>
-      <c r="I6" s="294"/>
-      <c r="J6" s="294"/>
-      <c r="K6" s="294"/>
-      <c r="L6" s="294"/>
-      <c r="M6" s="294"/>
-      <c r="N6" s="294"/>
+      <c r="D6" s="259"/>
+      <c r="E6" s="260"/>
+      <c r="F6" s="265"/>
+      <c r="G6" s="265"/>
+      <c r="H6" s="265"/>
+      <c r="I6" s="265"/>
+      <c r="J6" s="265"/>
+      <c r="K6" s="265"/>
+      <c r="L6" s="265"/>
+      <c r="M6" s="265"/>
+      <c r="N6" s="265"/>
       <c r="O6" s="119"/>
-      <c r="P6" s="297"/>
-      <c r="Q6" s="298"/>
+      <c r="P6" s="268"/>
+      <c r="Q6" s="269"/>
       <c r="R6" s="51"/>
     </row>
     <row r="7" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
@@ -29801,26 +29910,26 @@
     <row r="8" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="54"/>
       <c r="C8" s="55"/>
-      <c r="D8" s="276"/>
-      <c r="E8" s="277"/>
-      <c r="F8" s="277"/>
-      <c r="G8" s="273" t="s">
+      <c r="D8" s="281"/>
+      <c r="E8" s="282"/>
+      <c r="F8" s="282"/>
+      <c r="G8" s="270" t="s">
         <v>108</v>
       </c>
-      <c r="H8" s="274"/>
+      <c r="H8" s="271"/>
       <c r="I8" s="56" t="s">
         <v>109</v>
       </c>
       <c r="J8" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="K8" s="280"/>
-      <c r="L8" s="281"/>
-      <c r="M8" s="281"/>
-      <c r="N8" s="273" t="s">
+      <c r="K8" s="285"/>
+      <c r="L8" s="286"/>
+      <c r="M8" s="286"/>
+      <c r="N8" s="270" t="s">
         <v>108</v>
       </c>
-      <c r="O8" s="274"/>
+      <c r="O8" s="271"/>
       <c r="P8" s="56" t="s">
         <v>109</v>
       </c>
@@ -29832,9 +29941,9 @@
     <row r="9" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="54"/>
       <c r="C9" s="55"/>
-      <c r="D9" s="278"/>
-      <c r="E9" s="279"/>
-      <c r="F9" s="279"/>
+      <c r="D9" s="283"/>
+      <c r="E9" s="284"/>
+      <c r="F9" s="284"/>
       <c r="G9" s="58" t="s">
         <v>1</v>
       </c>
@@ -29847,9 +29956,9 @@
       <c r="J9" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="282"/>
-      <c r="L9" s="283"/>
-      <c r="M9" s="283"/>
+      <c r="K9" s="287"/>
+      <c r="L9" s="288"/>
+      <c r="M9" s="288"/>
       <c r="N9" s="58" t="s">
         <v>1</v>
       </c>
@@ -29867,24 +29976,24 @@
     <row r="10" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B10" s="54"/>
       <c r="C10" s="55"/>
-      <c r="D10" s="238" t="s">
+      <c r="D10" s="272" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="239"/>
-      <c r="F10" s="239"/>
-      <c r="G10" s="239"/>
-      <c r="H10" s="239"/>
-      <c r="I10" s="239"/>
-      <c r="J10" s="275"/>
-      <c r="K10" s="235" t="s">
+      <c r="E10" s="273"/>
+      <c r="F10" s="273"/>
+      <c r="G10" s="273"/>
+      <c r="H10" s="273"/>
+      <c r="I10" s="273"/>
+      <c r="J10" s="274"/>
+      <c r="K10" s="275" t="s">
         <v>151</v>
       </c>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
-      <c r="Q10" s="237"/>
+      <c r="L10" s="276"/>
+      <c r="M10" s="276"/>
+      <c r="N10" s="276"/>
+      <c r="O10" s="276"/>
+      <c r="P10" s="276"/>
+      <c r="Q10" s="277"/>
       <c r="R10" s="51"/>
     </row>
     <row r="11" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
@@ -29892,11 +30001,11 @@
       <c r="C11" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="246" t="s">
+      <c r="D11" s="249" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="247"/>
-      <c r="F11" s="248"/>
+      <c r="E11" s="250"/>
+      <c r="F11" s="251"/>
       <c r="G11" s="61">
         <f>Flujos!G4</f>
         <v>150420</v>
@@ -29913,11 +30022,11 @@
         <f>+I11*G11</f>
         <v>35920.295999999995</v>
       </c>
-      <c r="K11" s="241" t="s">
+      <c r="K11" s="278" t="s">
         <v>114</v>
       </c>
-      <c r="L11" s="242"/>
-      <c r="M11" s="243"/>
+      <c r="L11" s="279"/>
+      <c r="M11" s="280"/>
       <c r="N11" s="107">
         <f>Flujos!G20</f>
         <v>66012</v>
@@ -29928,11 +30037,11 @@
       </c>
       <c r="P11" s="192">
         <f>Flujos!H20</f>
-        <v>0.65033937957999999</v>
+        <v>0.64685681119999994</v>
       </c>
       <c r="Q11" s="107">
         <f>+P11*N11</f>
-        <v>42930.203124834959</v>
+        <v>42700.311820934396</v>
       </c>
       <c r="R11" s="51"/>
       <c r="T11" s="83"/>
@@ -29940,11 +30049,11 @@
     <row r="12" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B12" s="54"/>
       <c r="C12" s="55"/>
-      <c r="D12" s="241" t="s">
+      <c r="D12" s="278" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="242"/>
-      <c r="F12" s="243"/>
+      <c r="E12" s="279"/>
+      <c r="F12" s="280"/>
       <c r="G12" s="62">
         <f>Flujos!G5</f>
         <v>0</v>
@@ -29961,26 +30070,26 @@
         <f>+I12*G12</f>
         <v>0</v>
       </c>
-      <c r="K12" s="264" t="s">
+      <c r="K12" s="289" t="s">
         <v>125</v>
       </c>
-      <c r="L12" s="265"/>
-      <c r="M12" s="265"/>
-      <c r="N12" s="265"/>
-      <c r="O12" s="265"/>
-      <c r="P12" s="265"/>
-      <c r="Q12" s="266"/>
+      <c r="L12" s="290"/>
+      <c r="M12" s="290"/>
+      <c r="N12" s="290"/>
+      <c r="O12" s="290"/>
+      <c r="P12" s="290"/>
+      <c r="Q12" s="291"/>
       <c r="R12" s="51"/>
       <c r="T12" s="83"/>
     </row>
     <row r="13" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B13" s="54"/>
       <c r="C13" s="55"/>
-      <c r="D13" s="246" t="s">
+      <c r="D13" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="247"/>
-      <c r="F13" s="248"/>
+      <c r="E13" s="250"/>
+      <c r="F13" s="251"/>
       <c r="G13" s="60">
         <f>Flujos!G8</f>
         <v>0</v>
@@ -29997,11 +30106,11 @@
         <f>+I13*G13</f>
         <v>0</v>
       </c>
-      <c r="K13" s="267" t="s">
+      <c r="K13" s="241" t="s">
         <v>126</v>
       </c>
-      <c r="L13" s="268"/>
-      <c r="M13" s="269"/>
+      <c r="L13" s="242"/>
+      <c r="M13" s="243"/>
       <c r="N13" s="60">
         <f>Flujos!G6</f>
         <v>60303</v>
@@ -30023,11 +30132,11 @@
     <row r="14" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B14" s="54"/>
       <c r="C14" s="55"/>
-      <c r="D14" s="241" t="s">
+      <c r="D14" s="278" t="s">
         <v>116</v>
       </c>
-      <c r="E14" s="242"/>
-      <c r="F14" s="243"/>
+      <c r="E14" s="279"/>
+      <c r="F14" s="280"/>
       <c r="G14" s="62">
         <f>Flujos!G55</f>
         <v>37855</v>
@@ -30044,18 +30153,18 @@
         <f>+I14*G14</f>
         <v>19063.778000000002</v>
       </c>
-      <c r="K14" s="270" t="s">
+      <c r="K14" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="L14" s="271"/>
-      <c r="M14" s="272"/>
+      <c r="L14" s="253"/>
+      <c r="M14" s="254"/>
       <c r="N14" s="71">
         <f>Flujos!G12</f>
-        <v>20626.123299999999</v>
+        <v>24875.066452999999</v>
       </c>
       <c r="O14" s="71">
         <f>N14/(1-'Datos Extra'!B36)</f>
-        <v>22361.365242844753</v>
+        <v>26967.765018430182</v>
       </c>
       <c r="P14" s="192">
         <f>Flujos!H12</f>
@@ -30063,18 +30172,18 @@
       </c>
       <c r="Q14" s="62">
         <f>+P14*N14</f>
-        <v>3969.9099515509997</v>
+        <v>4787.7040402089096</v>
       </c>
       <c r="R14" s="51"/>
     </row>
     <row r="15" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="54"/>
       <c r="C15" s="55"/>
-      <c r="D15" s="246" t="s">
+      <c r="D15" s="249" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="247"/>
-      <c r="F15" s="248"/>
+      <c r="E15" s="250"/>
+      <c r="F15" s="251"/>
       <c r="G15" s="60">
         <f>Flujos!G31</f>
         <v>0</v>
@@ -30091,14 +30200,14 @@
         <f>+I15*G15</f>
         <v>0</v>
       </c>
-      <c r="K15" s="267" t="s">
+      <c r="K15" s="241" t="s">
         <v>129</v>
       </c>
-      <c r="L15" s="268"/>
-      <c r="M15" s="269"/>
+      <c r="L15" s="242"/>
+      <c r="M15" s="243"/>
       <c r="N15" s="72">
         <f>Flujos!G13</f>
-        <v>14883.876700000001</v>
+        <v>15456.336685</v>
       </c>
       <c r="O15" s="61"/>
       <c r="P15" s="193">
@@ -30107,25 +30216,25 @@
       </c>
       <c r="Q15" s="60">
         <f>+P15*N15</f>
-        <v>1616.1657514694998</v>
+        <v>1678.3263189407248</v>
       </c>
       <c r="R15" s="51"/>
     </row>
     <row r="16" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B16" s="54"/>
       <c r="C16" s="55"/>
-      <c r="D16" s="241"/>
-      <c r="E16" s="242"/>
-      <c r="F16" s="243"/>
+      <c r="D16" s="278"/>
+      <c r="E16" s="279"/>
+      <c r="F16" s="280"/>
       <c r="G16" s="62"/>
       <c r="H16" s="62"/>
       <c r="I16" s="64"/>
       <c r="J16" s="62"/>
-      <c r="K16" s="270" t="s">
+      <c r="K16" s="252" t="s">
         <v>131</v>
       </c>
-      <c r="L16" s="271"/>
-      <c r="M16" s="272"/>
+      <c r="L16" s="253"/>
+      <c r="M16" s="254"/>
       <c r="N16" s="71">
         <f>Flujos!G19</f>
         <v>43841</v>
@@ -30133,27 +30242,27 @@
       <c r="O16" s="71"/>
       <c r="P16" s="192">
         <f>Flujos!H19</f>
-        <v>9.6207729683000009E-2</v>
+        <v>9.3195E-2</v>
       </c>
       <c r="Q16" s="62">
         <f>+P16*N16</f>
-        <v>4217.843077032403</v>
+        <v>4085.7619949999998</v>
       </c>
       <c r="R16" s="51"/>
     </row>
     <row r="17" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B17" s="54"/>
       <c r="C17" s="55"/>
-      <c r="D17" s="246"/>
-      <c r="E17" s="247"/>
-      <c r="F17" s="248"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="250"/>
+      <c r="F17" s="251"/>
       <c r="G17" s="60"/>
       <c r="H17" s="60"/>
       <c r="I17" s="63"/>
       <c r="J17" s="60"/>
-      <c r="K17" s="267"/>
-      <c r="L17" s="268"/>
-      <c r="M17" s="269"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="242"/>
+      <c r="M17" s="243"/>
       <c r="N17" s="72"/>
       <c r="O17" s="61"/>
       <c r="P17" s="193"/>
@@ -30163,16 +30272,16 @@
     <row r="18" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="54"/>
       <c r="C18" s="55"/>
-      <c r="D18" s="241"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="243"/>
+      <c r="D18" s="278"/>
+      <c r="E18" s="279"/>
+      <c r="F18" s="280"/>
       <c r="G18" s="62"/>
       <c r="H18" s="62"/>
       <c r="I18" s="64"/>
       <c r="J18" s="62"/>
-      <c r="K18" s="270"/>
-      <c r="L18" s="271"/>
-      <c r="M18" s="272"/>
+      <c r="K18" s="252"/>
+      <c r="L18" s="253"/>
+      <c r="M18" s="254"/>
       <c r="N18" s="71"/>
       <c r="O18" s="71"/>
       <c r="P18" s="192"/>
@@ -30184,11 +30293,11 @@
       <c r="C19" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="244" t="s">
+      <c r="D19" s="247" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="245"/>
-      <c r="F19" s="245"/>
+      <c r="E19" s="248"/>
+      <c r="F19" s="248"/>
       <c r="G19" s="65">
         <f>+SUM(G11:G15)</f>
         <v>188275</v>
@@ -30202,23 +30311,23 @@
         <f>+SUM(J11:J15)</f>
         <v>54984.073999999993</v>
       </c>
-      <c r="K19" s="249" t="s">
+      <c r="K19" s="244" t="s">
         <v>123</v>
       </c>
-      <c r="L19" s="250"/>
-      <c r="M19" s="251"/>
+      <c r="L19" s="245"/>
+      <c r="M19" s="246"/>
       <c r="N19" s="65">
         <f>+SUM(N13:N16)</f>
-        <v>139654</v>
+        <v>144475.40313799999</v>
       </c>
       <c r="O19" s="65">
         <f>+SUM(O13:O16)</f>
-        <v>82664.365242844753</v>
+        <v>87270.765018430189</v>
       </c>
       <c r="P19" s="65"/>
       <c r="Q19" s="66">
         <f>+SUM(Q13:Q16)</f>
-        <v>17766.929930052902</v>
+        <v>18514.803504149633</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="174"/>
@@ -30227,35 +30336,35 @@
     <row r="20" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="54"/>
       <c r="C20" s="55"/>
-      <c r="D20" s="238" t="s">
+      <c r="D20" s="272" t="s">
         <v>124</v>
       </c>
-      <c r="E20" s="239"/>
-      <c r="F20" s="239"/>
-      <c r="G20" s="239"/>
-      <c r="H20" s="239"/>
-      <c r="I20" s="239"/>
-      <c r="J20" s="240"/>
-      <c r="K20" s="235" t="s">
+      <c r="E20" s="273"/>
+      <c r="F20" s="273"/>
+      <c r="G20" s="273"/>
+      <c r="H20" s="273"/>
+      <c r="I20" s="273"/>
+      <c r="J20" s="301"/>
+      <c r="K20" s="275" t="s">
         <v>152</v>
       </c>
-      <c r="L20" s="236"/>
-      <c r="M20" s="236"/>
-      <c r="N20" s="236"/>
-      <c r="O20" s="236"/>
-      <c r="P20" s="236"/>
-      <c r="Q20" s="237"/>
+      <c r="L20" s="276"/>
+      <c r="M20" s="276"/>
+      <c r="N20" s="276"/>
+      <c r="O20" s="276"/>
+      <c r="P20" s="276"/>
+      <c r="Q20" s="277"/>
       <c r="R20" s="51"/>
       <c r="S20" s="68"/>
     </row>
     <row r="21" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="54"/>
       <c r="C21" s="55"/>
-      <c r="D21" s="246" t="s">
+      <c r="D21" s="249" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="247"/>
-      <c r="F21" s="248"/>
+      <c r="E21" s="250"/>
+      <c r="F21" s="251"/>
       <c r="G21" s="122">
         <f>'Mapa de Procesos'!P102</f>
         <v>73127</v>
@@ -30272,26 +30381,26 @@
         <f>+I21*G21</f>
         <v>47634.927799999998</v>
       </c>
-      <c r="K21" s="252" t="s">
+      <c r="K21" s="302" t="s">
         <v>134</v>
       </c>
-      <c r="L21" s="253"/>
-      <c r="M21" s="254"/>
+      <c r="L21" s="303"/>
+      <c r="M21" s="304"/>
       <c r="N21" s="61">
         <f>Flujos!G25</f>
         <v>69689</v>
       </c>
       <c r="O21" s="61">
         <f>N21/(1-'Datos Extra'!B27)</f>
-        <v>76766.063383307075</v>
+        <v>76766.628166644747</v>
       </c>
       <c r="P21" s="188">
         <f>Flujos!H25</f>
-        <v>0.65110195969000006</v>
+        <v>0.64981910904000006</v>
       </c>
       <c r="Q21" s="60">
         <f t="shared" ref="Q21:Q31" si="0">+P21*N21</f>
-        <v>45374.644468836414</v>
+        <v>45285.243889888567</v>
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="173"/>
@@ -30299,11 +30408,11 @@
     <row r="22" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B22" s="54"/>
       <c r="C22" s="55"/>
-      <c r="D22" s="241" t="s">
+      <c r="D22" s="278" t="s">
         <v>127</v>
       </c>
-      <c r="E22" s="242"/>
-      <c r="F22" s="243"/>
+      <c r="E22" s="279"/>
+      <c r="F22" s="280"/>
       <c r="G22" s="69">
         <f>Flujos!G33</f>
         <v>0</v>
@@ -30347,11 +30456,11 @@
     <row r="23" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B23" s="54"/>
       <c r="C23" s="55"/>
-      <c r="D23" s="246" t="s">
+      <c r="D23" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="247"/>
-      <c r="F23" s="248"/>
+      <c r="E23" s="250"/>
+      <c r="F23" s="251"/>
       <c r="G23" s="122">
         <f>Flujos!G40</f>
         <v>0</v>
@@ -30395,11 +30504,11 @@
     <row r="24" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B24" s="54"/>
       <c r="C24" s="55"/>
-      <c r="D24" s="241" t="s">
+      <c r="D24" s="278" t="s">
         <v>130</v>
       </c>
-      <c r="E24" s="242"/>
-      <c r="F24" s="243"/>
+      <c r="E24" s="279"/>
+      <c r="F24" s="280"/>
       <c r="G24" s="69">
         <f>Flujos!G58</f>
         <v>0</v>
@@ -30417,7 +30526,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="198" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L24" s="199"/>
       <c r="M24" s="200"/>
@@ -30443,11 +30552,11 @@
     <row r="25" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B25" s="54"/>
       <c r="C25" s="55"/>
-      <c r="D25" s="246" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" s="247"/>
-      <c r="F25" s="248"/>
+      <c r="D25" s="249" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" s="250"/>
+      <c r="F25" s="251"/>
       <c r="G25" s="122">
         <f>Flujos!G68</f>
         <v>0</v>
@@ -30499,7 +30608,7 @@
       <c r="I26" s="121"/>
       <c r="J26" s="61"/>
       <c r="K26" s="198" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L26" s="199"/>
       <c r="M26" s="200"/>
@@ -30533,7 +30642,7 @@
       <c r="I27" s="121"/>
       <c r="J27" s="61"/>
       <c r="K27" s="195" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="L27" s="196"/>
       <c r="M27" s="197"/>
@@ -30567,7 +30676,7 @@
       <c r="I28" s="121"/>
       <c r="J28" s="61"/>
       <c r="K28" s="198" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L28" s="199"/>
       <c r="M28" s="200"/>
@@ -30600,25 +30709,25 @@
       <c r="H29" s="122"/>
       <c r="I29" s="121"/>
       <c r="J29" s="61"/>
-      <c r="K29" s="195" t="s">
-        <v>197</v>
-      </c>
-      <c r="L29" s="196"/>
-      <c r="M29" s="197"/>
-      <c r="N29" s="61">
-        <f>Flujos!G70</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="61">
-        <f>N29/(1-'Datos Extra'!D44)</f>
-        <v>0</v>
-      </c>
-      <c r="P29" s="191">
-        <f>Flujos!H70%</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="60">
-        <f t="shared" si="0"/>
+      <c r="K29" s="198" t="s">
+        <v>120</v>
+      </c>
+      <c r="L29" s="199"/>
+      <c r="M29" s="200"/>
+      <c r="N29" s="107">
+        <f>Flujos!G37</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="107">
+        <f>N29/(1-'Datos Extra'!B33)</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="161">
+        <f>Flujos!H37</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="107">
+        <f>+P29*N29</f>
         <v>0</v>
       </c>
       <c r="R29" s="51"/>
@@ -30627,32 +30736,32 @@
     <row r="30" spans="2:20" ht="14" x14ac:dyDescent="0.2">
       <c r="B30" s="54"/>
       <c r="C30" s="55"/>
-      <c r="D30" s="241"/>
-      <c r="E30" s="242"/>
-      <c r="F30" s="243"/>
+      <c r="D30" s="278"/>
+      <c r="E30" s="279"/>
+      <c r="F30" s="280"/>
       <c r="G30" s="69"/>
       <c r="H30" s="69"/>
       <c r="I30" s="70"/>
       <c r="J30" s="62"/>
-      <c r="K30" s="198" t="s">
-        <v>120</v>
-      </c>
-      <c r="L30" s="199"/>
-      <c r="M30" s="200"/>
-      <c r="N30" s="107">
-        <f>Flujos!G37</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="107">
-        <f>N30/(1-'Datos Extra'!B33)</f>
-        <v>0</v>
-      </c>
-      <c r="P30" s="161">
-        <f>Flujos!H37</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="107">
-        <f t="shared" si="0"/>
+      <c r="K30" s="195" t="s">
+        <v>121</v>
+      </c>
+      <c r="L30" s="196"/>
+      <c r="M30" s="197"/>
+      <c r="N30" s="61">
+        <f>Flujos!G38</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="61">
+        <f>N30/(1-'Datos Extra'!B34)</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="63">
+        <f>Flujos!H38</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="60">
+        <f>+P30*N30</f>
         <v>0</v>
       </c>
       <c r="R30" s="51"/>
@@ -30660,45 +30769,24 @@
     <row r="31" spans="2:20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B31" s="54"/>
       <c r="C31" s="55"/>
-      <c r="D31" s="246"/>
-      <c r="E31" s="247"/>
-      <c r="F31" s="248"/>
+      <c r="D31" s="249"/>
+      <c r="E31" s="250"/>
+      <c r="F31" s="251"/>
       <c r="G31" s="122"/>
       <c r="H31" s="122"/>
       <c r="I31" s="121"/>
       <c r="J31" s="61"/>
-      <c r="K31" s="195" t="s">
-        <v>121</v>
-      </c>
-      <c r="L31" s="196"/>
-      <c r="M31" s="197"/>
-      <c r="N31" s="61">
-        <f>Flujos!G38</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="61">
-        <f>N31/(1-'Datos Extra'!B34)</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="63">
-        <f>Flujos!H38</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="60">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
       <c r="R31" s="51"/>
       <c r="S31" s="173"/>
     </row>
     <row r="32" spans="2:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="54"/>
       <c r="C32" s="55"/>
-      <c r="D32" s="244" t="s">
+      <c r="D32" s="247" t="s">
         <v>123</v>
       </c>
-      <c r="E32" s="245"/>
-      <c r="F32" s="245"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="248"/>
       <c r="G32" s="65">
         <f>+SUM(G21:G24)</f>
         <v>73127</v>
@@ -30712,23 +30800,23 @@
         <f>+SUM(J21:J24)</f>
         <v>47634.927799999998</v>
       </c>
-      <c r="K32" s="249" t="s">
+      <c r="K32" s="244" t="s">
         <v>123</v>
       </c>
-      <c r="L32" s="250"/>
-      <c r="M32" s="251"/>
+      <c r="L32" s="245"/>
+      <c r="M32" s="246"/>
       <c r="N32" s="65">
-        <f>SUM(N21:N31)</f>
+        <f>SUM(N21:N30)</f>
         <v>75915</v>
       </c>
       <c r="O32" s="65">
-        <f>SUM(O21:O31)</f>
-        <v>83059.569298257455</v>
+        <f>SUM(O21:O30)</f>
+        <v>83060.134081595126</v>
       </c>
       <c r="P32" s="65"/>
       <c r="Q32" s="66">
-        <f>SUM(Q21:Q31)</f>
-        <v>49311.546668836418</v>
+        <f>SUM(Q21:Q30)</f>
+        <v>49222.146089888571</v>
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="173"/>
@@ -30749,21 +30837,21 @@
     <row r="34" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="54"/>
       <c r="C34" s="55"/>
-      <c r="D34" s="258" t="s">
+      <c r="D34" s="298" t="s">
         <v>132</v>
       </c>
-      <c r="E34" s="259"/>
-      <c r="F34" s="259"/>
-      <c r="G34" s="259"/>
-      <c r="H34" s="260"/>
+      <c r="E34" s="299"/>
+      <c r="F34" s="299"/>
+      <c r="G34" s="299"/>
+      <c r="H34" s="300"/>
       <c r="R34" s="76"/>
     </row>
     <row r="35" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B35" s="54"/>
       <c r="C35" s="55"/>
-      <c r="D35" s="255"/>
-      <c r="E35" s="256"/>
-      <c r="F35" s="257"/>
+      <c r="D35" s="295"/>
+      <c r="E35" s="296"/>
+      <c r="F35" s="297"/>
       <c r="G35" s="85" t="s">
         <v>102</v>
       </c>
@@ -30788,11 +30876,11 @@
     <row r="36" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B36" s="54"/>
       <c r="C36" s="55"/>
-      <c r="D36" s="241" t="s">
+      <c r="D36" s="278" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="242"/>
-      <c r="F36" s="242"/>
+      <c r="E36" s="279"/>
+      <c r="F36" s="279"/>
       <c r="G36" s="167">
         <f>'Datos Extra'!B1</f>
         <v>11665</v>
@@ -30803,11 +30891,11 @@
       </c>
       <c r="I36" s="177">
         <f>Flujos!G9</f>
-        <v>-26556</v>
+        <v>-34429.130716</v>
       </c>
       <c r="J36" s="177">
         <f>'Mapa de Procesos'!L128</f>
-        <v>-9452.6291970325201</v>
+        <v>-11044.004405424901</v>
       </c>
       <c r="K36" s="164"/>
       <c r="L36" s="164"/>
@@ -30822,11 +30910,11 @@
     <row r="37" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B37" s="54"/>
       <c r="C37" s="55"/>
-      <c r="D37" s="241" t="s">
+      <c r="D37" s="278" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="242"/>
-      <c r="F37" s="242"/>
+      <c r="E37" s="279"/>
+      <c r="F37" s="279"/>
       <c r="G37" s="168">
         <f>'Datos Extra'!B2</f>
         <v>32218.641698563333</v>
@@ -30837,11 +30925,11 @@
       </c>
       <c r="I37" s="177">
         <f>Flujos!G17</f>
-        <v>9165</v>
+        <v>12216.727578</v>
       </c>
       <c r="J37" s="177">
         <f>'Mapa de Procesos'!L129</f>
-        <v>3739.5701419030502</v>
+        <v>4812.9630802667698</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="164"/>
@@ -30864,11 +30952,11 @@
     <row r="38" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B38" s="54"/>
       <c r="C38" s="55"/>
-      <c r="D38" s="241" t="s">
+      <c r="D38" s="278" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="242"/>
-      <c r="F38" s="242"/>
+      <c r="E38" s="279"/>
+      <c r="F38" s="279"/>
       <c r="G38" s="168">
         <f>'Datos Extra'!B3</f>
         <v>33</v>
@@ -30883,27 +30971,27 @@
       </c>
       <c r="J38" s="177">
         <f>'Mapa de Procesos'!L131</f>
-        <v>-3366.1796673720501</v>
+        <v>-3482.744475</v>
       </c>
       <c r="K38" s="164"/>
       <c r="L38" s="164" t="s">
         <v>1</v>
       </c>
       <c r="M38" s="163">
-        <f>G19+N22+N23+N24+N30+N31</f>
+        <f>G19+N22+N23+N24+N29+N30</f>
         <v>191432</v>
       </c>
       <c r="N38" s="163">
         <f>G21+G22+G23+N19+G24</f>
-        <v>212781</v>
+        <v>217602.40313799999</v>
       </c>
       <c r="O38" s="165">
         <f>I43</f>
-        <v>-19702</v>
+        <v>-24523.403138000001</v>
       </c>
       <c r="P38" s="163">
         <f>M38-N38-O38</f>
-        <v>-1647</v>
+        <v>-1646.9999999999927</v>
       </c>
       <c r="Q38" s="164"/>
       <c r="R38" s="51"/>
@@ -30912,11 +31000,11 @@
     <row r="39" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B39" s="54"/>
       <c r="C39" s="55"/>
-      <c r="D39" s="241" t="s">
+      <c r="D39" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="242"/>
-      <c r="F39" s="242"/>
+      <c r="E39" s="279"/>
+      <c r="F39" s="279"/>
       <c r="G39" s="168">
         <f>'Datos Extra'!B4</f>
         <v>0</v>
@@ -30938,20 +31026,20 @@
         <v>34</v>
       </c>
       <c r="M39" s="163">
-        <f>J19+Q22+Q23+Q24+Q30+Q31</f>
+        <f>J19+Q22+Q23+Q24+Q29+Q30</f>
         <v>56987.506199999996</v>
       </c>
       <c r="N39" s="163">
         <f>Q19+J21+J22+J23+J24</f>
-        <v>65401.8577300529</v>
+        <v>66149.731304149638</v>
       </c>
       <c r="O39" s="166">
         <f>J43</f>
-        <v>-7402.6198539840998</v>
+        <v>-8126.5675101825518</v>
       </c>
       <c r="P39" s="163">
         <f>M39-N39-O39</f>
-        <v>-1011.7316760688036</v>
+        <v>-1035.6575939670902</v>
       </c>
       <c r="Q39" s="164"/>
       <c r="R39" s="76"/>
@@ -30960,11 +31048,11 @@
     <row r="40" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B40" s="54"/>
       <c r="C40" s="55"/>
-      <c r="D40" s="241" t="s">
+      <c r="D40" s="278" t="s">
         <v>4</v>
       </c>
-      <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
+      <c r="E40" s="279"/>
+      <c r="F40" s="279"/>
       <c r="G40" s="168">
         <f>'Datos Extra'!B5</f>
         <v>108658.53000000003</v>
@@ -30979,7 +31067,7 @@
       </c>
       <c r="J40" s="177">
         <f>'Mapa de Procesos'!L138</f>
-        <v>-2260.2833314581599</v>
+        <v>-2349.6839099999997</v>
       </c>
       <c r="K40" s="164"/>
       <c r="L40" s="163"/>
@@ -30994,11 +31082,11 @@
     <row r="41" spans="2:21" ht="14" x14ac:dyDescent="0.2">
       <c r="B41" s="54"/>
       <c r="C41" s="55"/>
-      <c r="D41" s="241" t="s">
+      <c r="D41" s="278" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="242"/>
-      <c r="F41" s="242"/>
+      <c r="E41" s="279"/>
+      <c r="F41" s="279"/>
       <c r="G41" s="168">
         <f>'Datos Extra'!B6</f>
         <v>60226.45</v>
@@ -31027,11 +31115,11 @@
     <row r="42" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B42" s="54"/>
       <c r="C42" s="55"/>
-      <c r="D42" s="262" t="s">
+      <c r="D42" s="293" t="s">
         <v>104</v>
       </c>
-      <c r="E42" s="263"/>
-      <c r="F42" s="263"/>
+      <c r="E42" s="294"/>
+      <c r="F42" s="294"/>
       <c r="G42" s="170">
         <f>'Datos Extra'!B7</f>
         <v>64802</v>
@@ -31060,11 +31148,11 @@
     <row r="43" spans="2:21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B43" s="78"/>
       <c r="C43" s="79"/>
-      <c r="D43" s="262" t="s">
-        <v>198</v>
-      </c>
-      <c r="E43" s="263"/>
-      <c r="F43" s="263"/>
+      <c r="D43" s="293" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" s="294"/>
+      <c r="F43" s="294"/>
       <c r="G43" s="170">
         <f>'Datos Extra'!B8</f>
         <v>71110.957552411084</v>
@@ -31075,11 +31163,11 @@
       </c>
       <c r="I43" s="178">
         <f>SUM(I36:I42)</f>
-        <v>-19702</v>
+        <v>-24523.403138000001</v>
       </c>
       <c r="J43" s="178">
         <f>SUM(J36:J42)</f>
-        <v>-7402.6198539840998</v>
+        <v>-8126.5675101825518</v>
       </c>
       <c r="K43" s="79"/>
       <c r="L43" s="79"/>
@@ -31116,9 +31204,9 @@
       <c r="K48" s="82"/>
     </row>
     <row r="49" spans="5:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E49" s="261"/>
-      <c r="F49" s="261"/>
-      <c r="G49" s="261"/>
+      <c r="E49" s="292"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
       <c r="H49" s="120"/>
       <c r="I49" s="84"/>
       <c r="J49" s="115"/>
@@ -31126,44 +31214,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="D3:E6"/>
-    <mergeCell ref="F3:Q4"/>
-    <mergeCell ref="F5:L6"/>
-    <mergeCell ref="M5:N6"/>
-    <mergeCell ref="P5:Q6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="D8:F9"/>
-    <mergeCell ref="K8:M9"/>
-    <mergeCell ref="K12:Q12"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D34:H34"/>
     <mergeCell ref="K20:Q20"/>
     <mergeCell ref="D20:J20"/>
     <mergeCell ref="D24:F24"/>
@@ -31178,6 +31228,44 @@
     <mergeCell ref="K21:M21"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="K12:Q12"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="D8:F9"/>
+    <mergeCell ref="K8:M9"/>
+    <mergeCell ref="D3:E6"/>
+    <mergeCell ref="F3:Q4"/>
+    <mergeCell ref="F5:L6"/>
+    <mergeCell ref="M5:N6"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="K18:M18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -31195,6 +31283,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f53f264-df38-4c5e-a089-ad7f07a2b911">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1490ee3b-8825-4a14-a799-bb3413729370" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100A6756668BF342349B2041C16AA74819C" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ef17328499b5dd1fe73808920c9c3ce3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6f53f264-df38-4c5e-a089-ad7f07a2b911" xmlns:ns3="1490ee3b-8825-4a14-a799-bb3413729370" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e3c7ce1721102a54cf77062aa02d40a" ns2:_="" ns3:_="">
     <xsd:import namespace="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
@@ -31435,17 +31534,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6f53f264-df38-4c5e-a089-ad7f07a2b911">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1490ee3b-8825-4a14-a799-bb3413729370" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FFCA9A7-8661-43F7-BFD7-3C6B027F5CB3}">
   <ds:schemaRefs>
@@ -31455,6 +31543,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79956576-308D-4576-AFE1-2F4C0F3C33E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1490ee3b-8825-4a14-a799-bb3413729370"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F59EF74B-C642-4BF6-A2E4-02733809A0C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31471,21 +31576,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79956576-308D-4576-AFE1-2F4C0F3C33E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1490ee3b-8825-4a14-a799-bb3413729370"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6f53f264-df38-4c5e-a089-ad7f07a2b911"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="204">
   <si>
     <t xml:space="preserve">Cola Concentradora (canoa)</t>
   </si>
@@ -467,18 +467,6 @@
     <t xml:space="preserve">De  nodo Alim Otros Materiales  + Emergencia a S Preconcentrado</t>
   </si>
   <si>
-    <t xml:space="preserve">Flujos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leyes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Humedad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stock Intermedio</t>
   </si>
   <si>
@@ -612,6 +600,9 @@
   </si>
   <si>
     <t xml:space="preserve">Max Var  FeT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flujos</t>
   </si>
   <si>
     <t xml:space="preserve">TMS</t>
@@ -2671,9 +2662,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>225000</xdr:colOff>
+      <xdr:colOff>224640</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>184320</xdr:rowOff>
+      <xdr:rowOff>183960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2683,7 +2674,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4077720" y="1483560"/>
-          <a:ext cx="1058400" cy="415440"/>
+          <a:ext cx="1058040" cy="415080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2750,9 +2741,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>649080</xdr:colOff>
+      <xdr:colOff>648720</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>25200</xdr:rowOff>
+      <xdr:rowOff>24840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2762,7 +2753,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7031880" y="2093760"/>
-          <a:ext cx="501120" cy="407880"/>
+          <a:ext cx="500760" cy="407520"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -2803,9 +2794,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>380520</xdr:colOff>
+      <xdr:colOff>380160</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>165240</xdr:rowOff>
+      <xdr:rowOff>164880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2815,7 +2806,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6323400" y="1779840"/>
-          <a:ext cx="941040" cy="480960"/>
+          <a:ext cx="940680" cy="480600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2879,9 +2870,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>96480</xdr:colOff>
+      <xdr:colOff>96120</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>76320</xdr:rowOff>
+      <xdr:rowOff>75960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2891,7 +2882,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10137600" y="3348000"/>
-          <a:ext cx="1202040" cy="347760"/>
+          <a:ext cx="1201680" cy="347400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2955,9 +2946,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>410760</xdr:colOff>
+      <xdr:colOff>410400</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>39600</xdr:rowOff>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2967,7 +2958,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7524720" y="6739920"/>
-          <a:ext cx="651600" cy="538560"/>
+          <a:ext cx="651240" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3008,9 +2999,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>77760</xdr:colOff>
+      <xdr:colOff>77400</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>82800</xdr:rowOff>
+      <xdr:rowOff>82440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3020,7 +3011,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6530400" y="8498160"/>
-          <a:ext cx="1312920" cy="538200"/>
+          <a:ext cx="1312560" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3084,9 +3075,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>719280</xdr:colOff>
+      <xdr:colOff>718920</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3096,7 +3087,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7239240" y="10542960"/>
-          <a:ext cx="1245600" cy="415440"/>
+          <a:ext cx="1245240" cy="415080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3163,9 +3154,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>626760</xdr:colOff>
+      <xdr:colOff>626400</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3175,7 +3166,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9577080" y="12143880"/>
-          <a:ext cx="577800" cy="538200"/>
+          <a:ext cx="577440" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3216,9 +3207,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>700200</xdr:colOff>
+      <xdr:colOff>699840</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>55440</xdr:rowOff>
+      <xdr:rowOff>55080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3228,7 +3219,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9938880" y="12243240"/>
-          <a:ext cx="1052640" cy="385200"/>
+          <a:ext cx="1052280" cy="384840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3292,9 +3283,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>656640</xdr:colOff>
+      <xdr:colOff>656280</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>3960</xdr:rowOff>
+      <xdr:rowOff>3600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3304,7 +3295,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9606960" y="13565880"/>
-          <a:ext cx="577800" cy="534960"/>
+          <a:ext cx="577440" cy="534600"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3345,9 +3336,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>462960</xdr:colOff>
+      <xdr:colOff>462600</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3357,7 +3348,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9701640" y="13191120"/>
-          <a:ext cx="1052640" cy="534600"/>
+          <a:ext cx="1052280" cy="534240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3421,9 +3412,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>492480</xdr:colOff>
+      <xdr:colOff>492120</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>79200</xdr:rowOff>
+      <xdr:rowOff>78840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3433,7 +3424,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12100320" y="12114000"/>
-          <a:ext cx="2513880" cy="538200"/>
+          <a:ext cx="2513520" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3497,9 +3488,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>112320</xdr:colOff>
+      <xdr:colOff>111960</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>88560</xdr:rowOff>
+      <xdr:rowOff>88200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3509,7 +3500,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12152520" y="12885480"/>
-          <a:ext cx="2892600" cy="538200"/>
+          <a:ext cx="2892240" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3573,9 +3564,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>492480</xdr:colOff>
+      <xdr:colOff>492120</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>86040</xdr:rowOff>
+      <xdr:rowOff>85680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3585,7 +3576,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12100320" y="13644360"/>
-          <a:ext cx="2513880" cy="538560"/>
+          <a:ext cx="2513520" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3649,9 +3640,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>7560</xdr:colOff>
+      <xdr:colOff>7200</xdr:colOff>
       <xdr:row>86</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:rowOff>154800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3661,7 +3652,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9720000" y="15999480"/>
-          <a:ext cx="578880" cy="538560"/>
+          <a:ext cx="578520" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3702,9 +3693,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>731160</xdr:colOff>
+      <xdr:colOff>730800</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>31680</xdr:rowOff>
+      <xdr:rowOff>31320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3714,7 +3705,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10071720" y="16066800"/>
-          <a:ext cx="950760" cy="538560"/>
+          <a:ext cx="950400" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3778,9 +3769,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>605160</xdr:colOff>
+      <xdr:colOff>604800</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>72000</xdr:rowOff>
+      <xdr:rowOff>71640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3790,7 +3781,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12213000" y="16107120"/>
-          <a:ext cx="2513880" cy="538560"/>
+          <a:ext cx="2513520" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3854,9 +3845,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>579240</xdr:colOff>
+      <xdr:colOff>578880</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>138960</xdr:rowOff>
+      <xdr:rowOff>138600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3866,7 +3857,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5268600" y="4317840"/>
-          <a:ext cx="221760" cy="202680"/>
+          <a:ext cx="221400" cy="202320"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3946,9 +3937,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>644760</xdr:colOff>
+      <xdr:colOff>644400</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>111600</xdr:rowOff>
+      <xdr:rowOff>111240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3958,7 +3949,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2736000" y="11685960"/>
-          <a:ext cx="1363680" cy="427320"/>
+          <a:ext cx="1363320" cy="426960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4022,9 +4013,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>14400</xdr:colOff>
+      <xdr:colOff>14040</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>173160</xdr:rowOff>
+      <xdr:rowOff>172800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4034,7 +4025,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2647440" y="685800"/>
-          <a:ext cx="1514880" cy="249480"/>
+          <a:ext cx="1514520" cy="249120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4137,9 +4128,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>684720</xdr:colOff>
+      <xdr:colOff>684360</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>44280</xdr:rowOff>
+      <xdr:rowOff>43920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4149,7 +4140,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2751120" y="2363400"/>
-          <a:ext cx="577800" cy="538560"/>
+          <a:ext cx="577440" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4190,9 +4181,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>163800</xdr:colOff>
+      <xdr:colOff>163440</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>31320</xdr:rowOff>
+      <xdr:rowOff>30960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4202,7 +4193,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2023560" y="2752200"/>
-          <a:ext cx="784440" cy="327240"/>
+          <a:ext cx="784080" cy="326880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4266,9 +4257,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>671400</xdr:colOff>
+      <xdr:colOff>671040</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>101880</xdr:rowOff>
+      <xdr:rowOff>101520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4278,7 +4269,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="323280" y="2252520"/>
-          <a:ext cx="559440" cy="325800"/>
+          <a:ext cx="559080" cy="325440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4420,9 +4411,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>123840</xdr:colOff>
+      <xdr:colOff>123480</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>103680</xdr:rowOff>
+      <xdr:rowOff>103320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4432,7 +4423,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1201680" y="3791520"/>
-          <a:ext cx="1566360" cy="312840"/>
+          <a:ext cx="1566000" cy="312480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4611,9 +4602,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>714600</xdr:colOff>
+      <xdr:colOff>714240</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>46440</xdr:rowOff>
+      <xdr:rowOff>46080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4623,7 +4614,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4053600" y="2495160"/>
-          <a:ext cx="808920" cy="218160"/>
+          <a:ext cx="808560" cy="217800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4726,9 +4717,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>240480</xdr:colOff>
+      <xdr:colOff>240120</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>90720</xdr:rowOff>
+      <xdr:rowOff>90360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4738,7 +4729,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3069000" y="4695840"/>
-          <a:ext cx="626400" cy="538560"/>
+          <a:ext cx="626040" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4779,9 +4770,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>716400</xdr:colOff>
+      <xdr:colOff>716040</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>105840</xdr:rowOff>
+      <xdr:rowOff>105480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4791,7 +4782,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2372040" y="5111640"/>
-          <a:ext cx="988560" cy="328320"/>
+          <a:ext cx="988200" cy="327960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4855,9 +4846,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>216360</xdr:colOff>
+      <xdr:colOff>216000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>36720</xdr:rowOff>
+      <xdr:rowOff>36360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4867,7 +4858,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1971720" y="4663800"/>
-          <a:ext cx="888840" cy="325800"/>
+          <a:ext cx="888480" cy="325440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5009,9 +5000,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>144360</xdr:colOff>
+      <xdr:colOff>144000</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>168120</xdr:rowOff>
+      <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5021,7 +5012,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3521520" y="4608720"/>
-          <a:ext cx="770760" cy="321840"/>
+          <a:ext cx="770400" cy="321480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5085,9 +5076,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>258120</xdr:colOff>
+      <xdr:colOff>257760</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>136080</xdr:rowOff>
+      <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5097,7 +5088,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3086640" y="6455880"/>
-          <a:ext cx="626400" cy="538200"/>
+          <a:ext cx="626040" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5138,9 +5129,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>671400</xdr:colOff>
+      <xdr:colOff>671040</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:rowOff>180720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5150,7 +5141,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2329920" y="6979680"/>
-          <a:ext cx="985680" cy="440280"/>
+          <a:ext cx="985320" cy="439920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5292,9 +5283,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>365400</xdr:colOff>
+      <xdr:colOff>365040</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>172800</xdr:rowOff>
+      <xdr:rowOff>172440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5304,7 +5295,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3363480" y="6190200"/>
-          <a:ext cx="1149840" cy="459720"/>
+          <a:ext cx="1149480" cy="459360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5368,9 +5359,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>11880</xdr:colOff>
+      <xdr:colOff>11520</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5380,7 +5371,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2105640" y="6456240"/>
-          <a:ext cx="550440" cy="228960"/>
+          <a:ext cx="550080" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5483,9 +5474,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>266040</xdr:colOff>
+      <xdr:colOff>265680</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>72720</xdr:rowOff>
+      <xdr:rowOff>72360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5495,7 +5486,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3094560" y="8297640"/>
-          <a:ext cx="626400" cy="538200"/>
+          <a:ext cx="626040" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5536,9 +5527,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>746280</xdr:colOff>
+      <xdr:colOff>745920</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>23760</xdr:rowOff>
+      <xdr:rowOff>23400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5548,7 +5539,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2300760" y="8851320"/>
-          <a:ext cx="1089720" cy="316440"/>
+          <a:ext cx="1089360" cy="316080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5651,9 +5642,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>290880</xdr:colOff>
+      <xdr:colOff>290520</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>115560</xdr:rowOff>
+      <xdr:rowOff>115200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5663,7 +5654,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3378960" y="8017920"/>
-          <a:ext cx="1059840" cy="479520"/>
+          <a:ext cx="1059480" cy="479160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5727,9 +5718,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>20160</xdr:colOff>
+      <xdr:colOff>19800</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>121320</xdr:rowOff>
+      <xdr:rowOff>120960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5739,7 +5730,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2113920" y="8152200"/>
-          <a:ext cx="550440" cy="351000"/>
+          <a:ext cx="550080" cy="350640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5842,9 +5833,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>214920</xdr:colOff>
+      <xdr:colOff>214560</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>188280</xdr:rowOff>
+      <xdr:rowOff>187920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5854,7 +5845,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3043440" y="10321200"/>
-          <a:ext cx="626400" cy="534960"/>
+          <a:ext cx="626040" cy="534600"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5895,9 +5886,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>658080</xdr:colOff>
+      <xdr:colOff>657720</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>65880</xdr:rowOff>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5907,7 +5898,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2672280" y="10912320"/>
-          <a:ext cx="1440720" cy="202680"/>
+          <a:ext cx="1440360" cy="202320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6010,9 +6001,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>417600</xdr:colOff>
+      <xdr:colOff>417240</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>111240</xdr:rowOff>
+      <xdr:rowOff>110880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6022,7 +6013,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3495960" y="9997560"/>
-          <a:ext cx="1069560" cy="591120"/>
+          <a:ext cx="1069200" cy="590760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6086,9 +6077,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>120240</xdr:colOff>
+      <xdr:colOff>119880</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>32040</xdr:rowOff>
+      <xdr:rowOff>31680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6098,7 +6089,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1928160" y="10090080"/>
-          <a:ext cx="836280" cy="228960"/>
+          <a:ext cx="835920" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6318,9 +6309,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>729000</xdr:colOff>
+      <xdr:colOff>728640</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>76680</xdr:rowOff>
+      <xdr:rowOff>76320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6330,9 +6321,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="9679320" y="3157560"/>
-          <a:ext cx="577800" cy="538560"/>
+          <a:ext cx="577440" cy="538200"/>
           <a:chOff x="9679320" y="3157560"/>
-          <a:chExt cx="577800" cy="538560"/>
+          <a:chExt cx="577440" cy="538200"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6343,7 +6334,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9679320" y="3157560"/>
-            <a:ext cx="577800" cy="538560"/>
+            <a:ext cx="577440" cy="538200"/>
           </a:xfrm>
           <a:prstGeom prst="triangle">
             <a:avLst>
@@ -6381,7 +6372,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9896400" y="3253680"/>
-            <a:ext cx="144000" cy="126000"/>
+            <a:ext cx="143640" cy="125640"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6414,7 +6405,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9968760" y="3403800"/>
-            <a:ext cx="144000" cy="126000"/>
+            <a:ext cx="143640" cy="125640"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6447,7 +6438,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10040760" y="3535920"/>
-            <a:ext cx="144000" cy="126000"/>
+            <a:ext cx="143640" cy="125640"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6484,9 +6475,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>536400</xdr:colOff>
+      <xdr:colOff>536040</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>103320</xdr:rowOff>
+      <xdr:rowOff>102960</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6496,9 +6487,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="10463760" y="1593000"/>
-          <a:ext cx="1315800" cy="415440"/>
+          <a:ext cx="1315440" cy="415080"/>
           <a:chOff x="10463760" y="1593000"/>
-          <a:chExt cx="1315800" cy="415440"/>
+          <a:chExt cx="1315440" cy="415080"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6509,7 +6500,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10463760" y="1593000"/>
-            <a:ext cx="1315800" cy="415440"/>
+            <a:ext cx="1315440" cy="415080"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6573,7 +6564,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="11449800" y="1881360"/>
-            <a:ext cx="168120" cy="125280"/>
+            <a:ext cx="167760" cy="124920"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6686,9 +6677,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>933840</xdr:colOff>
+      <xdr:colOff>933480</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>162720</xdr:rowOff>
+      <xdr:rowOff>162360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6698,7 +6689,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11955600" y="1823040"/>
-          <a:ext cx="1032480" cy="435240"/>
+          <a:ext cx="1032120" cy="434880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6808,9 +6799,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>797760</xdr:colOff>
+      <xdr:colOff>797400</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>48960</xdr:rowOff>
+      <xdr:rowOff>48600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6820,7 +6811,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11902680" y="1061640"/>
-          <a:ext cx="949320" cy="511200"/>
+          <a:ext cx="948960" cy="510840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6930,9 +6921,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>684720</xdr:colOff>
+      <xdr:colOff>684360</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>23400</xdr:rowOff>
+      <xdr:rowOff>23040</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6942,9 +6933,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="7204680" y="4555800"/>
-          <a:ext cx="1245600" cy="420480"/>
+          <a:ext cx="1245240" cy="420120"/>
           <a:chOff x="7204680" y="4555800"/>
-          <a:chExt cx="1245600" cy="420480"/>
+          <a:chExt cx="1245240" cy="420120"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6955,7 +6946,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="7204680" y="4556880"/>
-            <a:ext cx="1245600" cy="419400"/>
+            <a:ext cx="1245240" cy="419040"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7019,7 +7010,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="8283240" y="4555800"/>
-            <a:ext cx="159120" cy="126720"/>
+            <a:ext cx="158760" cy="126360"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -7134,9 +7125,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>222120</xdr:colOff>
+      <xdr:colOff>221760</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>45360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7146,7 +7137,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9769320" y="4603680"/>
-          <a:ext cx="744120" cy="204480"/>
+          <a:ext cx="743760" cy="204120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7210,9 +7201,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>151200</xdr:colOff>
+      <xdr:colOff>150840</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>182160</xdr:rowOff>
+      <xdr:rowOff>181800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7222,7 +7213,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10801800" y="4813560"/>
-          <a:ext cx="1403640" cy="321480"/>
+          <a:ext cx="1403280" cy="321120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7286,9 +7277,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>260640</xdr:colOff>
+      <xdr:colOff>260280</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>23040</xdr:rowOff>
+      <xdr:rowOff>22680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7298,7 +7289,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9452880" y="1030680"/>
-          <a:ext cx="1099080" cy="325800"/>
+          <a:ext cx="1098720" cy="325440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7362,9 +7353,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
+      <xdr:colOff>319680</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>18720</xdr:rowOff>
+      <xdr:rowOff>18360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7374,7 +7365,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5590440" y="5217840"/>
-          <a:ext cx="1613520" cy="325440"/>
+          <a:ext cx="1613160" cy="325080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7615,9 +7606,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>309240</xdr:colOff>
+      <xdr:colOff>308880</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>169200</xdr:rowOff>
+      <xdr:rowOff>168840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7627,7 +7618,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5999760" y="9350280"/>
-          <a:ext cx="1193400" cy="534600"/>
+          <a:ext cx="1193040" cy="534240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7737,9 +7728,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>509400</xdr:colOff>
+      <xdr:colOff>509040</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>187200</xdr:rowOff>
+      <xdr:rowOff>186840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7749,7 +7740,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8937360" y="9368280"/>
-          <a:ext cx="1100160" cy="534600"/>
+          <a:ext cx="1099800" cy="534240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7896,9 +7887,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>81720</xdr:colOff>
+      <xdr:colOff>81360</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>144720</xdr:rowOff>
+      <xdr:rowOff>144360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7908,7 +7899,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8497800" y="10846080"/>
-          <a:ext cx="1112040" cy="538200"/>
+          <a:ext cx="1111680" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8050,9 +8041,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>647640</xdr:colOff>
+      <xdr:colOff>647280</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>124200</xdr:rowOff>
+      <xdr:rowOff>123840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8062,7 +8053,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7144200" y="11509920"/>
-          <a:ext cx="1269000" cy="425160"/>
+          <a:ext cx="1268640" cy="424800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8195,9 +8186,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>598680</xdr:colOff>
+      <xdr:colOff>598320</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8207,7 +8198,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6904800" y="13568040"/>
-          <a:ext cx="577800" cy="538560"/>
+          <a:ext cx="577440" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -8248,9 +8239,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>579240</xdr:colOff>
+      <xdr:colOff>578880</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>151560</xdr:rowOff>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8260,7 +8251,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6269760" y="13138920"/>
-          <a:ext cx="1193400" cy="538200"/>
+          <a:ext cx="1193040" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8480,9 +8471,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>753840</xdr:colOff>
+      <xdr:colOff>753480</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>71280</xdr:rowOff>
+      <xdr:rowOff>70920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8492,7 +8483,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3919320" y="13439160"/>
-          <a:ext cx="982440" cy="538560"/>
+          <a:ext cx="982080" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8556,9 +8547,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>753480</xdr:colOff>
+      <xdr:colOff>753120</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>135720</xdr:rowOff>
+      <xdr:rowOff>135360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8568,7 +8559,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3918960" y="14266080"/>
-          <a:ext cx="982440" cy="538200"/>
+          <a:ext cx="982080" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8671,9 +8662,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>32400</xdr:colOff>
+      <xdr:colOff>32040</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:rowOff>175320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8683,7 +8674,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5549040" y="14880600"/>
-          <a:ext cx="1367280" cy="534960"/>
+          <a:ext cx="1366920" cy="534600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8786,9 +8777,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>716760</xdr:colOff>
+      <xdr:colOff>716400</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>11880</xdr:rowOff>
+      <xdr:rowOff>11520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8798,7 +8789,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6540120" y="15613560"/>
-          <a:ext cx="1060560" cy="400320"/>
+          <a:ext cx="1060200" cy="399960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8901,9 +8892,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>713520</xdr:colOff>
+      <xdr:colOff>713160</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>109440</xdr:rowOff>
+      <xdr:rowOff>109080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8913,7 +8904,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6338160" y="16476840"/>
-          <a:ext cx="1259280" cy="396720"/>
+          <a:ext cx="1258920" cy="396360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9016,9 +9007,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>18360</xdr:colOff>
+      <xdr:colOff>18000</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:rowOff>85320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9028,7 +9019,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6404760" y="17214480"/>
-          <a:ext cx="1379160" cy="397080"/>
+          <a:ext cx="1378800" cy="396720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9170,9 +9161,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>34560</xdr:colOff>
+      <xdr:colOff>34200</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>56520</xdr:rowOff>
+      <xdr:rowOff>56160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9182,7 +9173,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12523320" y="14757840"/>
-          <a:ext cx="2444040" cy="538560"/>
+          <a:ext cx="2443680" cy="538200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9297,9 +9288,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>929520</xdr:colOff>
+      <xdr:colOff>929160</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>182160</xdr:rowOff>
+      <xdr:rowOff>181800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9309,7 +9300,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7634160" y="15208200"/>
-          <a:ext cx="1060920" cy="404640"/>
+          <a:ext cx="1060560" cy="404280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9573,9 +9564,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>438120</xdr:colOff>
+      <xdr:colOff>437760</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>47880</xdr:rowOff>
+      <xdr:rowOff>47520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9589,7 +9580,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="725760" y="466920"/>
-          <a:ext cx="946800" cy="533520"/>
+          <a:ext cx="946440" cy="533160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13663,22 +13654,22 @@
       <c r="A1" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="36" t="s">
-        <v>49</v>
+      <c r="B1" s="37" t="n">
+        <v>11665</v>
+      </c>
+      <c r="C1" s="38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D1" s="39" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B2" s="37" t="n">
-        <v>11665</v>
+        <v>32218.6416985633</v>
       </c>
       <c r="C2" s="38" t="n">
         <v>0.5</v>
@@ -13689,97 +13680,97 @@
     </row>
     <row r="3" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="36" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B3" s="37" t="n">
-        <v>32218.6416985633</v>
+        <v>33</v>
       </c>
       <c r="C3" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="D3" s="39" t="n">
-        <v>0.01</v>
+        <v>0.089433339445629</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B4" s="37" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C4" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="D4" s="39" t="n">
-        <v>0.089433339445629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B5" s="37" t="n">
-        <v>0</v>
+        <v>108658.53</v>
       </c>
       <c r="C5" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="D5" s="39" t="n">
-        <v>0</v>
+        <v>0.092196678891258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="36" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B6" s="37" t="n">
-        <v>108658.53</v>
+        <v>60226.45</v>
       </c>
       <c r="C6" s="38" t="n">
         <v>0.5</v>
       </c>
       <c r="D6" s="39" t="n">
-        <v>0.092196678891258</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="37" t="n">
-        <v>60226.45</v>
+        <v>52</v>
+      </c>
+      <c r="B7" s="40" t="n">
+        <v>64802</v>
       </c>
       <c r="C7" s="38" t="n">
         <v>0.5</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B8" s="40" t="n">
-        <v>64802</v>
+        <v>71110.9575524111</v>
       </c>
       <c r="C8" s="38" t="n">
-        <v>0.5</v>
+        <v>0.650929547893467</v>
       </c>
       <c r="D8" s="38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="40" t="n">
-        <v>71110.9575524111</v>
-      </c>
-      <c r="C9" s="38" t="n">
-        <v>0.650929547893467</v>
+        <v>54</v>
+      </c>
+      <c r="B9" s="37" t="n">
+        <v>66011.83908</v>
+      </c>
+      <c r="C9" s="41" t="n">
+        <v>0.6505</v>
       </c>
       <c r="D9" s="38" t="n">
         <v>0.01</v>
@@ -13787,13 +13778,13 @@
     </row>
     <row r="10" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B10" s="37" t="n">
-        <v>66011.83908</v>
+        <v>0</v>
       </c>
       <c r="C10" s="41" t="n">
-        <v>0.6505</v>
+        <v>0</v>
       </c>
       <c r="D10" s="38" t="n">
         <v>0.01</v>
@@ -13801,7 +13792,7 @@
     </row>
     <row r="11" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B11" s="37" t="n">
         <v>0</v>
@@ -13815,13 +13806,13 @@
     </row>
     <row r="12" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B12" s="37" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="41" t="n">
-        <v>0</v>
+        <v>0.6346</v>
       </c>
       <c r="D12" s="38" t="n">
         <v>0.01</v>
@@ -13829,13 +13820,13 @@
     </row>
     <row r="13" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="41" t="n">
-        <v>0.6346</v>
+        <v>58</v>
+      </c>
+      <c r="B13" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="38" t="n">
+        <v>0</v>
       </c>
       <c r="D13" s="38" t="n">
         <v>0.01</v>
@@ -13843,7 +13834,7 @@
     </row>
     <row r="14" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B14" s="40" t="n">
         <v>0</v>
@@ -13857,27 +13848,27 @@
     </row>
     <row r="15" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B15" s="40" t="n">
-        <v>0</v>
+        <v>150420</v>
       </c>
       <c r="C15" s="38" t="n">
-        <v>0</v>
+        <v>0.238759403669725</v>
       </c>
       <c r="D15" s="38" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="40" t="n">
-        <v>150420</v>
-      </c>
-      <c r="C16" s="38" t="n">
-        <v>0.238759403669725</v>
+      <c r="A16" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="43" t="n">
+        <v>66011.83908</v>
+      </c>
+      <c r="C16" s="44" t="n">
+        <v>0.6505</v>
       </c>
       <c r="D16" s="38" t="n">
         <v>0.01</v>
@@ -13885,35 +13876,35 @@
     </row>
     <row r="17" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="43" t="n">
-        <v>66011.83908</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>0.6505</v>
-      </c>
-      <c r="D17" s="38" t="n">
-        <v>0.01</v>
+        <v>59</v>
+      </c>
+      <c r="B17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="42" t="s">
-        <v>63</v>
+      <c r="A18" s="47" t="s">
+        <v>60</v>
       </c>
       <c r="B18" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="43" t="n">
+      <c r="C18" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="45" t="n">
         <v>0</v>
@@ -13927,7 +13918,7 @@
     </row>
     <row r="20" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="47" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B20" s="45" t="n">
         <v>0</v>
@@ -13941,7 +13932,7 @@
     </row>
     <row r="21" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="47" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B21" s="45" t="n">
         <v>0</v>
@@ -13950,12 +13941,12 @@
         <v>0</v>
       </c>
       <c r="D21" s="48" t="n">
-        <v>0</v>
+        <v>0.0293425</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="47" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B22" s="45" t="n">
         <v>0</v>
@@ -13964,12 +13955,12 @@
         <v>0</v>
       </c>
       <c r="D22" s="48" t="n">
-        <v>0.0293425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="47" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B23" s="45" t="n">
         <v>0</v>
@@ -13978,12 +13969,12 @@
         <v>0</v>
       </c>
       <c r="D23" s="48" t="n">
-        <v>0</v>
+        <v>0.08626</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="47" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B24" s="45" t="n">
         <v>0</v>
@@ -13992,12 +13983,12 @@
         <v>0</v>
       </c>
       <c r="D24" s="48" t="n">
-        <v>0.08626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="47" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B25" s="45" t="n">
         <v>0</v>
@@ -14011,7 +14002,7 @@
     </row>
     <row r="26" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="47" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B26" s="45" t="n">
         <v>0</v>
@@ -14025,7 +14016,7 @@
     </row>
     <row r="27" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="47" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B27" s="45" t="n">
         <v>0</v>
@@ -14034,12 +14025,12 @@
         <v>0</v>
       </c>
       <c r="D27" s="48" t="n">
-        <v>0</v>
+        <v>0.092196678891258</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="47" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B28" s="45" t="n">
         <v>0</v>
@@ -14048,12 +14039,12 @@
         <v>0</v>
       </c>
       <c r="D28" s="48" t="n">
-        <v>0.092196678891258</v>
+        <v>0.08667</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="47" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B29" s="45" t="n">
         <v>0</v>
@@ -14062,12 +14053,12 @@
         <v>0</v>
       </c>
       <c r="D29" s="48" t="n">
-        <v>0.08667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="47" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B30" s="45" t="n">
         <v>0</v>
@@ -14081,7 +14072,7 @@
     </row>
     <row r="31" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B31" s="45" t="n">
         <v>0</v>
@@ -14095,7 +14086,7 @@
     </row>
     <row r="32" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="47" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B32" s="45" t="n">
         <v>0</v>
@@ -14104,26 +14095,26 @@
         <v>0</v>
       </c>
       <c r="D32" s="48" t="n">
-        <v>0</v>
+        <v>0.0088</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
-        <v>78</v>
+      <c r="A33" s="49" t="s">
+        <v>58</v>
       </c>
       <c r="B33" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="45" t="n">
+      <c r="C33" s="50" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="48" t="n">
-        <v>0.0088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B34" s="45" t="n">
         <v>0</v>
@@ -14137,7 +14128,7 @@
     </row>
     <row r="35" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B35" s="45" t="n">
         <v>0</v>
@@ -14151,7 +14142,7 @@
     </row>
     <row r="36" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B36" s="45" t="n">
         <v>0</v>
@@ -14160,13 +14151,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="48" t="n">
-        <v>0</v>
+        <v>0.0776</v>
       </c>
       <c r="J36" s="51"/>
     </row>
     <row r="37" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49" t="s">
-        <v>80</v>
+      <c r="A37" s="51" t="s">
+        <v>77</v>
       </c>
       <c r="B37" s="45" t="n">
         <v>0</v>
@@ -14175,12 +14166,12 @@
         <v>0</v>
       </c>
       <c r="D37" s="48" t="n">
-        <v>0.0776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="51" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B38" s="45" t="n">
         <v>0</v>
@@ -14194,63 +14185,63 @@
     </row>
     <row r="39" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="50" t="n">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="B39" s="43" t="n">
+        <v>3185.48</v>
+      </c>
+      <c r="C39" s="48" t="n">
+        <v>0.6346</v>
       </c>
       <c r="D39" s="48" t="n">
-        <v>0</v>
+        <v>0.0088</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="51" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B40" s="43" t="n">
-        <v>3185.48</v>
+        <v>3108.98</v>
       </c>
       <c r="C40" s="48" t="n">
-        <v>0.6346</v>
+        <v>0.63</v>
       </c>
       <c r="D40" s="48" t="n">
-        <v>0.0088</v>
+        <v>0.0127</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" s="43" t="n">
-        <v>3108.98</v>
-      </c>
-      <c r="C41" s="48" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D41" s="48" t="n">
-        <v>0.0127</v>
+        <v>81</v>
+      </c>
+      <c r="B41" s="52" t="n">
+        <v>3185.48</v>
+      </c>
+      <c r="C41" s="38" t="n">
+        <v>0.6346</v>
+      </c>
+      <c r="D41" s="53" t="n">
+        <v>0.0088</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42" s="52" t="n">
-        <v>3185.48</v>
+        <v>82</v>
+      </c>
+      <c r="B42" s="43" t="n">
+        <v>1000</v>
       </c>
       <c r="C42" s="38" t="n">
-        <v>0.6346</v>
+        <v>0.6</v>
       </c>
       <c r="D42" s="53" t="n">
-        <v>0.0088</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="51" t="s">
-        <v>86</v>
+      <c r="A43" s="47" t="s">
+        <v>83</v>
       </c>
       <c r="B43" s="43" t="n">
         <v>1000</v>
@@ -14263,8 +14254,8 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="47" t="s">
-        <v>87</v>
+      <c r="A44" s="51" t="s">
+        <v>84</v>
       </c>
       <c r="B44" s="43" t="n">
         <v>1000</v>
@@ -14278,31 +14269,23 @@
     </row>
     <row r="45" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="51" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B45" s="43" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C45" s="38" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="D45" s="53" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="43" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C46" s="38" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="D46" s="53" t="n">
         <v>0.02</v>
       </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0"/>
+      <c r="B46" s="0"/>
+      <c r="C46" s="0"/>
+      <c r="D46" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -14333,51 +14316,51 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="54" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="54"/>
       <c r="F2" s="54" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G2" s="54"/>
       <c r="H2" s="54"/>
       <c r="J2" s="55" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K2" s="55"/>
       <c r="L2" s="56"/>
       <c r="M2" s="57" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N2" s="58" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="59" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="C3" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="60" t="s">
         <v>95</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="H3" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="K3" s="60" t="s">
-        <v>98</v>
       </c>
       <c r="L3" s="61"/>
       <c r="M3" s="62"/>
@@ -14385,7 +14368,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="59" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C4" s="63" t="n">
         <f aca="false">Utilidad!A1</f>
@@ -14396,7 +14379,7 @@
         <v>0.2388</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G4" s="66" t="n">
         <f aca="false">Utilidad!B1</f>
@@ -14426,7 +14409,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="59" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C5" s="63" t="n">
         <f aca="false">Utilidad!A2</f>
@@ -14437,7 +14420,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G5" s="66" t="n">
         <f aca="false">Utilidad!B2</f>
@@ -14467,7 +14450,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="59" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C6" s="63" t="n">
         <f aca="false">Utilidad!A3</f>
@@ -14478,7 +14461,7 @@
         <v>0.139</v>
       </c>
       <c r="F6" s="65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G6" s="66" t="n">
         <f aca="false">Utilidad!B3</f>
@@ -14507,7 +14490,7 @@
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="59" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C7" s="63" t="n">
         <f aca="false">Utilidad!A4</f>
@@ -14518,7 +14501,7 @@
         <v>0.3055</v>
       </c>
       <c r="F7" s="65" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G7" s="66" t="n">
         <f aca="false">Utilidad!B4</f>
@@ -14547,7 +14530,7 @@
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="59" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C8" s="63" t="n">
         <f aca="false">Utilidad!A5</f>
@@ -14558,7 +14541,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="65" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G8" s="63" t="n">
         <f aca="false">Utilidad!B5</f>
@@ -14587,7 +14570,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="59" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C9" s="63" t="n">
         <f aca="false">Utilidad!A6</f>
@@ -14598,7 +14581,7 @@
         <v>0.3055</v>
       </c>
       <c r="F9" s="65" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G9" s="63" t="n">
         <f aca="false">Utilidad!B6</f>
@@ -14631,7 +14614,7 @@
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="59" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C10" s="63" t="n">
         <f aca="false">Utilidad!A7</f>
@@ -14642,7 +14625,7 @@
         <v>0.3113</v>
       </c>
       <c r="F10" s="59" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G10" s="72" t="n">
         <f aca="false">Utilidad!B7</f>
@@ -14675,7 +14658,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="59" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C11" s="63" t="n">
         <f aca="false">Utilidad!A8</f>
@@ -14686,7 +14669,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G11" s="72" t="n">
         <f aca="false">Utilidad!B8</f>
@@ -14715,7 +14698,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="59" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C12" s="63" t="n">
         <f aca="false">Utilidad!A9</f>
@@ -14726,7 +14709,7 @@
         <v>0.2026</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G12" s="72" t="n">
         <f aca="false">Utilidad!B9</f>
@@ -16519,7 +16502,7 @@
     </row>
     <row r="57" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="59" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C57" s="63" t="n">
         <f aca="false">Utilidad!A54</f>
@@ -16530,7 +16513,7 @@
         <v>0.6346</v>
       </c>
       <c r="F57" s="59" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G57" s="63" t="n">
         <f aca="false">Utilidad!B54</f>
@@ -16559,7 +16542,7 @@
     </row>
     <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="59" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C58" s="63" t="n">
         <f aca="false">Utilidad!A55</f>
@@ -16570,7 +16553,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G58" s="63" t="n">
         <f aca="false">Utilidad!B55</f>
@@ -16599,7 +16582,7 @@
     </row>
     <row r="59" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="59" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C59" s="63" t="n">
         <f aca="false">Utilidad!A56</f>
@@ -16610,7 +16593,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="59" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G59" s="63" t="n">
         <f aca="false">Utilidad!B56</f>
@@ -16639,7 +16622,7 @@
     </row>
     <row r="60" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="59" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C60" s="63" t="n">
         <f aca="false">Utilidad!A57</f>
@@ -16650,7 +16633,7 @@
         <v>0.63</v>
       </c>
       <c r="F60" s="59" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G60" s="63" t="n">
         <f aca="false">Utilidad!B57</f>
@@ -16679,7 +16662,7 @@
     </row>
     <row r="61" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="59" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C61" s="63" t="n">
         <f aca="false">Utilidad!A58</f>
@@ -16690,7 +16673,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="59" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G61" s="63" t="n">
         <f aca="false">Utilidad!B58</f>
@@ -16719,7 +16702,7 @@
     </row>
     <row r="62" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="59" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C62" s="63" t="n">
         <f aca="false">Utilidad!A59</f>
@@ -16730,7 +16713,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G62" s="63" t="n">
         <f aca="false">Utilidad!B59</f>
@@ -16759,7 +16742,7 @@
     </row>
     <row r="63" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="59" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C63" s="63" t="n">
         <f aca="false">Utilidad!A60</f>
@@ -16770,7 +16753,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="59" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G63" s="63" t="n">
         <f aca="false">Utilidad!B60</f>
@@ -16799,7 +16782,7 @@
     </row>
     <row r="64" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="59" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C64" s="63" t="n">
         <f aca="false">Utilidad!A61</f>
@@ -16810,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="59" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G64" s="63" t="n">
         <f aca="false">Utilidad!B61</f>
@@ -16839,7 +16822,7 @@
     </row>
     <row r="65" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="59" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C65" s="63" t="n">
         <f aca="false">Utilidad!A62</f>
@@ -16850,7 +16833,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="59" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G65" s="63" t="n">
         <f aca="false">Utilidad!B62</f>
@@ -16879,7 +16862,7 @@
     </row>
     <row r="66" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C66" s="63" t="n">
         <f aca="false">Utilidad!A63</f>
@@ -16890,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G66" s="63" t="n">
         <f aca="false">Utilidad!B63</f>
@@ -16919,7 +16902,7 @@
     </row>
     <row r="67" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="59" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C67" s="63" t="n">
         <f aca="false">Utilidad!A64</f>
@@ -16930,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="59" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G67" s="63" t="n">
         <f aca="false">Utilidad!B64</f>
@@ -16959,7 +16942,7 @@
     </row>
     <row r="68" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C68" s="63" t="n">
         <f aca="false">Utilidad!A65</f>
@@ -16970,7 +16953,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G68" s="63" t="n">
         <f aca="false">Utilidad!B65</f>
@@ -16999,7 +16982,7 @@
     </row>
     <row r="69" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C69" s="63" t="n">
         <f aca="false">Utilidad!A66</f>
@@ -17010,7 +16993,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G69" s="63" t="n">
         <f aca="false">Utilidad!B66</f>
@@ -17039,7 +17022,7 @@
     </row>
     <row r="70" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="59" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C70" s="63" t="n">
         <f aca="false">Utilidad!A67</f>
@@ -17050,7 +17033,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="59" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G70" s="63" t="n">
         <f aca="false">Utilidad!B67</f>
@@ -17079,7 +17062,7 @@
     </row>
     <row r="71" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="59" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C71" s="63" t="n">
         <f aca="false">Utilidad!A68</f>
@@ -17090,7 +17073,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="59" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G71" s="63" t="n">
         <f aca="false">Utilidad!B68</f>
@@ -17369,7 +17352,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="S16" s="80"/>
     </row>
@@ -17868,7 +17851,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L65" s="83" t="n">
         <f aca="false">Flujos!G25</f>
@@ -17887,7 +17870,7 @@
         <v>3069</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L66" s="85" t="n">
         <f aca="false">Flujos!H25</f>
@@ -17902,7 +17885,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L67" s="86" t="n">
         <f aca="false">L66*L65</f>
@@ -18133,7 +18116,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="S87" s="80"/>
     </row>
@@ -18160,7 +18143,7 @@
         <v>0</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S90" s="80"/>
     </row>
@@ -18183,7 +18166,7 @@
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="79"/>
       <c r="P93" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="S93" s="80"/>
     </row>
@@ -18209,22 +18192,22 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G95" s="105" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G96" s="106" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H96" s="106"/>
       <c r="I96" s="106"/>
       <c r="J96" s="107" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K96" s="107"/>
       <c r="L96" s="107"/>
       <c r="M96" s="108" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N96" s="108"/>
       <c r="O96" s="108"/>
@@ -18232,7 +18215,7 @@
     </row>
     <row r="97" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G97" s="109" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H97" s="109"/>
       <c r="I97" s="110" t="n">
@@ -18240,7 +18223,7 @@
         <v>150420</v>
       </c>
       <c r="J97" s="111" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K97" s="111"/>
       <c r="L97" s="112" t="n">
@@ -18248,7 +18231,7 @@
         <v>-34429.130716</v>
       </c>
       <c r="M97" s="113" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N97" s="113"/>
       <c r="O97" s="113"/>
@@ -18259,7 +18242,7 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G98" s="109" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H98" s="109"/>
       <c r="I98" s="110" t="n">
@@ -18267,7 +18250,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="113" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K98" s="113"/>
       <c r="L98" s="112" t="n">
@@ -18275,7 +18258,7 @@
         <v>12216.727578</v>
       </c>
       <c r="M98" s="113" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N98" s="113"/>
       <c r="O98" s="113"/>
@@ -18286,7 +18269,7 @@
     </row>
     <row r="99" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G99" s="109" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H99" s="109"/>
       <c r="I99" s="110" t="n">
@@ -18294,7 +18277,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="113" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K99" s="113"/>
       <c r="L99" s="112" t="n">
@@ -18312,7 +18295,7 @@
     </row>
     <row r="100" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G100" s="114" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H100" s="114"/>
       <c r="I100" s="110" t="n">
@@ -18320,7 +18303,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="113" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K100" s="113"/>
       <c r="L100" s="112" t="n">
@@ -18328,7 +18311,7 @@
         <v>-5099</v>
       </c>
       <c r="M100" s="113" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N100" s="113"/>
       <c r="O100" s="113"/>
@@ -18347,7 +18330,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="113" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K101" s="113"/>
       <c r="L101" s="112" t="n">
@@ -18355,7 +18338,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="113" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N101" s="113"/>
       <c r="O101" s="113"/>
@@ -18374,7 +18357,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="113" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K102" s="113"/>
       <c r="L102" s="112" t="n">
@@ -18382,7 +18365,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="113" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N102" s="113"/>
       <c r="O102" s="113"/>
@@ -18393,7 +18376,7 @@
     </row>
     <row r="103" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G103" s="114" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H103" s="114"/>
       <c r="I103" s="110" t="n">
@@ -18401,7 +18384,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="113" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K103" s="113"/>
       <c r="L103" s="112" t="n">
@@ -18409,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="113" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N103" s="113"/>
       <c r="O103" s="113"/>
@@ -18420,7 +18403,7 @@
     </row>
     <row r="104" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G104" s="114" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H104" s="114"/>
       <c r="I104" s="110" t="n">
@@ -18428,7 +18411,7 @@
         <v>37855</v>
       </c>
       <c r="J104" s="113" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K104" s="113"/>
       <c r="L104" s="112" t="n">
@@ -18436,7 +18419,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="113" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N104" s="113"/>
       <c r="O104" s="113"/>
@@ -18447,7 +18430,7 @@
     </row>
     <row r="105" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G105" s="114" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H105" s="114"/>
       <c r="I105" s="110" t="n">
@@ -18455,7 +18438,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="113" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K105" s="113"/>
       <c r="L105" s="112" t="n">
@@ -18463,7 +18446,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="113" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N105" s="113"/>
       <c r="O105" s="113"/>
@@ -18474,7 +18457,7 @@
     </row>
     <row r="106" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G106" s="114" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H106" s="114"/>
       <c r="I106" s="110" t="n">
@@ -18482,7 +18465,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="113" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K106" s="113"/>
       <c r="L106" s="112" t="n">
@@ -18490,7 +18473,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="113" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N106" s="113"/>
       <c r="O106" s="113"/>
@@ -18501,7 +18484,7 @@
     </row>
     <row r="107" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G107" s="115" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H107" s="116"/>
       <c r="I107" s="110" t="n">
@@ -18509,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="113" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K107" s="113"/>
       <c r="L107" s="112" t="n">
@@ -18517,7 +18500,7 @@
         <v>-3438</v>
       </c>
       <c r="M107" s="113" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N107" s="113"/>
       <c r="O107" s="113"/>
@@ -18525,7 +18508,7 @@
     </row>
     <row r="108" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G108" s="115" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H108" s="116"/>
       <c r="I108" s="110" t="n">
@@ -18533,7 +18516,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="113" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K108" s="113"/>
       <c r="L108" s="112" t="n">
@@ -18547,7 +18530,7 @@
     </row>
     <row r="109" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G109" s="115" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H109" s="116"/>
       <c r="I109" s="110" t="n">
@@ -18555,7 +18538,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="113" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K109" s="113"/>
       <c r="L109" s="112" t="n">
@@ -18569,7 +18552,7 @@
     </row>
     <row r="110" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G110" s="114" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H110" s="114"/>
       <c r="I110" s="110" t="n">
@@ -18577,7 +18560,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="113" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K110" s="113"/>
       <c r="L110" s="112" t="n">
@@ -18591,7 +18574,7 @@
     </row>
     <row r="111" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G111" s="114" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H111" s="114"/>
       <c r="I111" s="110" t="n">
@@ -18608,10 +18591,10 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G112" s="114" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H112" s="114" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I112" s="110" t="n">
         <f aca="false">Flujos!G59</f>
@@ -18627,10 +18610,10 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G113" s="114" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H113" s="114" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I113" s="110" t="n">
         <f aca="false">Flujos!G60</f>
@@ -18646,10 +18629,10 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G114" s="114" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H114" s="114" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I114" s="110" t="n">
         <f aca="false">Flujos!G61</f>
@@ -18665,7 +18648,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G115" s="114" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H115" s="114"/>
       <c r="I115" s="110" t="n">
@@ -18682,7 +18665,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G116" s="114" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H116" s="114"/>
       <c r="I116" s="110" t="n">
@@ -18699,7 +18682,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G117" s="115" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H117" s="116"/>
       <c r="I117" s="110" t="n">
@@ -18716,7 +18699,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G118" s="115" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H118" s="116"/>
       <c r="I118" s="110" t="n">
@@ -18745,7 +18728,7 @@
     </row>
     <row r="120" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G120" s="118" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H120" s="118"/>
       <c r="I120" s="119" t="n">
@@ -18753,7 +18736,7 @@
         <v>194501</v>
       </c>
       <c r="J120" s="120" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K120" s="120"/>
       <c r="L120" s="121" t="n">
@@ -18761,7 +18744,7 @@
         <v>-24523.403138</v>
       </c>
       <c r="M120" s="120" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N120" s="120"/>
       <c r="O120" s="120"/>
@@ -18787,7 +18770,7 @@
       <c r="J122" s="122"/>
       <c r="K122" s="122"/>
       <c r="L122" s="123" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M122" s="124"/>
       <c r="N122" s="125"/>
@@ -18802,22 +18785,22 @@
     <row r="125" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="126" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G126" s="105" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G127" s="127" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H127" s="127"/>
       <c r="I127" s="127"/>
       <c r="J127" s="128" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K127" s="128"/>
       <c r="L127" s="128"/>
       <c r="M127" s="129" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N127" s="129"/>
       <c r="O127" s="129"/>
@@ -18825,7 +18808,7 @@
     </row>
     <row r="128" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G128" s="109" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H128" s="109"/>
       <c r="I128" s="110" t="n">
@@ -18833,7 +18816,7 @@
         <v>35920.296</v>
       </c>
       <c r="J128" s="111" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K128" s="111"/>
       <c r="L128" s="112" t="n">
@@ -18841,7 +18824,7 @@
         <v>-11044.0044054249</v>
       </c>
       <c r="M128" s="113" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N128" s="113"/>
       <c r="O128" s="113"/>
@@ -18852,7 +18835,7 @@
     </row>
     <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G129" s="130" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H129" s="131"/>
       <c r="I129" s="110" t="n">
@@ -18860,7 +18843,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="113" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K129" s="113"/>
       <c r="L129" s="112" t="n">
@@ -18868,7 +18851,7 @@
         <v>4812.96308026677</v>
       </c>
       <c r="M129" s="113" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="N129" s="113"/>
       <c r="O129" s="113"/>
@@ -18879,7 +18862,7 @@
     </row>
     <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G130" s="130" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H130" s="132"/>
       <c r="I130" s="110" t="n">
@@ -18887,7 +18870,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="113" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K130" s="113"/>
       <c r="L130" s="112" t="n">
@@ -18905,7 +18888,7 @@
     </row>
     <row r="131" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G131" s="115" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H131" s="116"/>
       <c r="I131" s="110" t="n">
@@ -18913,7 +18896,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="113" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K131" s="113"/>
       <c r="L131" s="112" t="n">
@@ -18921,7 +18904,7 @@
         <v>-3482.744475</v>
       </c>
       <c r="M131" s="113" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N131" s="113"/>
       <c r="O131" s="113"/>
@@ -18940,7 +18923,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="113" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K132" s="113"/>
       <c r="L132" s="112" t="n">
@@ -18948,7 +18931,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="113" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N132" s="113"/>
       <c r="O132" s="113"/>
@@ -18967,7 +18950,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="113" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K133" s="113"/>
       <c r="L133" s="112" t="n">
@@ -18975,7 +18958,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="113" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N133" s="113"/>
       <c r="O133" s="113"/>
@@ -18986,7 +18969,7 @@
     </row>
     <row r="134" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G134" s="115" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H134" s="116"/>
       <c r="I134" s="110" t="n">
@@ -18994,7 +18977,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="113" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K134" s="113"/>
       <c r="L134" s="112" t="n">
@@ -19002,7 +18985,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="113" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="N134" s="113"/>
       <c r="O134" s="113"/>
@@ -19013,7 +18996,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G135" s="115" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H135" s="116"/>
       <c r="I135" s="110" t="n">
@@ -19021,7 +19004,7 @@
         <v>19063.778</v>
       </c>
       <c r="J135" s="113" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K135" s="113"/>
       <c r="L135" s="112" t="n">
@@ -19029,7 +19012,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="113" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N135" s="113"/>
       <c r="O135" s="113"/>
@@ -19040,7 +19023,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G136" s="115" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H136" s="116"/>
       <c r="I136" s="110" t="n">
@@ -19048,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="113" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K136" s="113"/>
       <c r="L136" s="112" t="n">
@@ -19056,7 +19039,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="113" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N136" s="113"/>
       <c r="O136" s="113"/>
@@ -19067,7 +19050,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G137" s="115" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H137" s="116"/>
       <c r="I137" s="110" t="n">
@@ -19075,7 +19058,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="113" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K137" s="113"/>
       <c r="L137" s="112" t="n">
@@ -19083,7 +19066,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="113" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="N137" s="113"/>
       <c r="O137" s="113"/>
@@ -19094,7 +19077,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G138" s="115" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H138" s="116"/>
       <c r="I138" s="110" t="n">
@@ -19102,7 +19085,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="113" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K138" s="113"/>
       <c r="L138" s="112" t="n">
@@ -19110,7 +19093,7 @@
         <v>-2349.68391</v>
       </c>
       <c r="M138" s="113" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N138" s="113"/>
       <c r="O138" s="113"/>
@@ -19121,7 +19104,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G139" s="115" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H139" s="116"/>
       <c r="I139" s="110" t="n">
@@ -19129,7 +19112,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="113" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="K139" s="113"/>
       <c r="L139" s="112" t="n">
@@ -19143,7 +19126,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G140" s="115" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H140" s="116"/>
       <c r="I140" s="110" t="n">
@@ -19151,7 +19134,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="113" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K140" s="113"/>
       <c r="L140" s="112" t="n">
@@ -19165,7 +19148,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G141" s="115" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H141" s="116"/>
       <c r="I141" s="110" t="n">
@@ -19173,7 +19156,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="113" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K141" s="113"/>
       <c r="L141" s="112" t="n">
@@ -19187,7 +19170,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G142" s="114" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H142" s="114"/>
       <c r="I142" s="110" t="n">
@@ -19201,7 +19184,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G143" s="114" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H143" s="114"/>
       <c r="I143" s="110" t="n">
@@ -19218,7 +19201,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G144" s="114" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H144" s="114"/>
       <c r="I144" s="110" t="n">
@@ -19235,7 +19218,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G145" s="114" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H145" s="114"/>
       <c r="I145" s="110" t="n">
@@ -19252,7 +19235,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G146" s="114" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H146" s="114"/>
       <c r="I146" s="110" t="n">
@@ -19269,7 +19252,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G147" s="114" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H147" s="114"/>
       <c r="I147" s="110" t="n">
@@ -19286,7 +19269,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G148" s="115" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H148" s="116"/>
       <c r="I148" s="110" t="n">
@@ -19303,7 +19286,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G149" s="115" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H149" s="116"/>
       <c r="I149" s="110" t="n">
@@ -19332,7 +19315,7 @@
     </row>
     <row r="151" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G151" s="118" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H151" s="118"/>
       <c r="I151" s="119" t="n">
@@ -19340,7 +19323,7 @@
         <v>58920.9762</v>
       </c>
       <c r="J151" s="120" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K151" s="120"/>
       <c r="L151" s="121" t="n">
@@ -19348,7 +19331,7 @@
         <v>-8126.56751018255</v>
       </c>
       <c r="M151" s="120" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N151" s="120"/>
       <c r="O151" s="120"/>
@@ -19374,7 +19357,7 @@
       <c r="J153" s="122"/>
       <c r="K153" s="122"/>
       <c r="L153" s="123" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M153" s="124"/>
       <c r="N153" s="125"/>
@@ -19487,7 +19470,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{6C2A4A3A-47CF-4E89-ADC0-1885DC32D5C0}">
+          <x14:cfRule type="iconSet" priority="2" id="{52A8A6B7-4761-4345-A1A0-DBC8AD96F8DA}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19506,7 +19489,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{BE1A9312-D24A-421F-A8F2-FF88D3E6B964}">
+          <x14:cfRule type="iconSet" priority="3" id="{ED6856DD-5190-4A18-9044-41DCDC27A076}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19525,7 +19508,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{40BA1312-F713-4210-A382-9CA51F6FD663}">
+          <x14:cfRule type="iconSet" priority="4" id="{2EF0DFA9-2317-4923-B042-C520913BB1CD}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19544,7 +19527,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{CDF8E090-49B4-4F97-B094-EAD9ED616BB0}">
+          <x14:cfRule type="iconSet" priority="5" id="{4B2092C4-E92C-4BED-87F0-667F7C71EFBB}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19563,7 +19546,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{D091932B-4A34-4B80-9DA1-48D2ACDC5481}">
+          <x14:cfRule type="iconSet" priority="6" id="{F2498421-542B-41B0-A096-7F4FBF608270}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19582,7 +19565,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{395E26AC-333E-46AE-B533-FED0283F666B}">
+          <x14:cfRule type="iconSet" priority="7" id="{BD1855EC-DE1A-4BC7-9798-2985C0554A2D}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19601,7 +19584,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{79245B71-155F-48BC-911B-78CECB996D36}">
+          <x14:cfRule type="iconSet" priority="8" id="{59975C3A-4223-4CE0-8038-5D32E08A98B9}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19620,7 +19603,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{FBCBC0DA-B329-47A6-89E2-B3EE55F819A8}">
+          <x14:cfRule type="iconSet" priority="9" id="{CE11DE5D-A395-4644-8D9D-E383834F7E5C}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19639,7 +19622,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{429198C2-8B20-4721-9EA3-FC8EFB8DBB6D}">
+          <x14:cfRule type="iconSet" priority="10" id="{576CC250-B069-4F32-BBF6-BC3DEB209858}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19658,7 +19641,7 @@
           <xm:sqref>L120</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{6CC7E528-6723-4D22-B879-C928BD9ABA4F}">
+          <x14:cfRule type="iconSet" priority="11" id="{3A556A54-E729-4680-981F-A79AA0EC35B6}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19677,7 +19660,7 @@
           <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{FF70D5D7-C262-4421-AB4B-22FE8B47C24F}">
+          <x14:cfRule type="iconSet" priority="12" id="{661BDEEE-76D7-4D63-9082-652AA6A41F36}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19696,7 +19679,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{2A143B23-C9DD-44D4-8AA3-213EF0326C85}">
+          <x14:cfRule type="iconSet" priority="13" id="{B6A057CD-A4E8-4D33-98F0-30B36BBA8635}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19715,7 +19698,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{1DD18614-FEEC-4DF4-A68E-DE5DD8A3C0BB}">
+          <x14:cfRule type="iconSet" priority="14" id="{506FBCC6-712D-484B-AF40-97589123C8BD}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19734,7 +19717,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{BF54E75F-849C-4917-A2AE-C677F39B3BC7}">
+          <x14:cfRule type="iconSet" priority="15" id="{F2E8F3B5-D24A-47CC-98D7-8980DABC7D2C}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22353,7 +22336,7 @@
       <c r="D3" s="144"/>
       <c r="E3" s="144"/>
       <c r="F3" s="145" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G3" s="145"/>
       <c r="H3" s="145"/>
@@ -22393,7 +22376,7 @@
       <c r="D5" s="144"/>
       <c r="E5" s="144"/>
       <c r="F5" s="147" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G5" s="147"/>
       <c r="H5" s="147"/>
@@ -22402,7 +22385,7 @@
       <c r="K5" s="147"/>
       <c r="L5" s="147"/>
       <c r="M5" s="147" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N5" s="147"/>
       <c r="O5" s="148"/>
@@ -22455,27 +22438,27 @@
       <c r="E8" s="154"/>
       <c r="F8" s="154"/>
       <c r="G8" s="155" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H8" s="155"/>
       <c r="I8" s="155" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J8" s="156" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K8" s="157"/>
       <c r="L8" s="157"/>
       <c r="M8" s="157"/>
       <c r="N8" s="155" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="O8" s="155"/>
       <c r="P8" s="155" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q8" s="156" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="R8" s="146"/>
     </row>
@@ -22486,31 +22469,31 @@
       <c r="E9" s="154"/>
       <c r="F9" s="154"/>
       <c r="G9" s="158" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H9" s="158" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I9" s="158" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J9" s="159" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K9" s="157"/>
       <c r="L9" s="157"/>
       <c r="M9" s="157"/>
       <c r="N9" s="158" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O9" s="158" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P9" s="158" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q9" s="159" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="R9" s="146"/>
     </row>
@@ -22518,7 +22501,7 @@
       <c r="B10" s="152"/>
       <c r="C10" s="153"/>
       <c r="D10" s="160" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E10" s="160"/>
       <c r="F10" s="160"/>
@@ -22527,7 +22510,7 @@
       <c r="I10" s="160"/>
       <c r="J10" s="160"/>
       <c r="K10" s="161" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L10" s="161"/>
       <c r="M10" s="161"/>
@@ -22540,10 +22523,10 @@
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="152"/>
       <c r="C11" s="153" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D11" s="162" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
@@ -22552,7 +22535,7 @@
         <v>150420</v>
       </c>
       <c r="H11" s="163" t="n">
-        <f aca="false">G11/(1-'Datos Extra'!D19)</f>
+        <f aca="false">G11/(1-'Datos Extra'!D18)</f>
         <v>150420</v>
       </c>
       <c r="I11" s="164" t="n">
@@ -22564,7 +22547,7 @@
         <v>35920.296</v>
       </c>
       <c r="K11" s="166" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L11" s="166"/>
       <c r="M11" s="166"/>
@@ -22573,7 +22556,7 @@
         <v>66012</v>
       </c>
       <c r="O11" s="167" t="n">
-        <f aca="false">N11/(1-'Datos Extra'!D29)</f>
+        <f aca="false">N11/(1-'Datos Extra'!D28)</f>
         <v>72276.1761904241</v>
       </c>
       <c r="P11" s="168" t="n">
@@ -22591,7 +22574,7 @@
       <c r="B12" s="152"/>
       <c r="C12" s="153"/>
       <c r="D12" s="166" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E12" s="166"/>
       <c r="F12" s="166"/>
@@ -22600,7 +22583,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="170" t="n">
-        <f aca="false">G12/(1-'Datos Extra'!D20)</f>
+        <f aca="false">G12/(1-'Datos Extra'!D19)</f>
         <v>0</v>
       </c>
       <c r="I12" s="171" t="n">
@@ -22612,7 +22595,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="161" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="L12" s="161"/>
       <c r="M12" s="161"/>
@@ -22627,7 +22610,7 @@
       <c r="B13" s="152"/>
       <c r="C13" s="153"/>
       <c r="D13" s="162" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -22636,7 +22619,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="163" t="n">
-        <f aca="false">G13/(1-'Datos Extra'!D21)</f>
+        <f aca="false">G13/(1-'Datos Extra'!D20)</f>
         <v>0</v>
       </c>
       <c r="I13" s="172" t="n">
@@ -22648,7 +22631,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="173" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L13" s="173"/>
       <c r="M13" s="173"/>
@@ -22657,7 +22640,7 @@
         <v>60303</v>
       </c>
       <c r="O13" s="163" t="n">
-        <f aca="false">N13*1/(1-'Datos Extra'!D36)</f>
+        <f aca="false">N13*1/(1-'Datos Extra'!D35)</f>
         <v>60303</v>
       </c>
       <c r="P13" s="164" t="n">
@@ -22674,7 +22657,7 @@
       <c r="B14" s="152"/>
       <c r="C14" s="153"/>
       <c r="D14" s="166" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E14" s="166"/>
       <c r="F14" s="166"/>
@@ -22683,7 +22666,7 @@
         <v>37855</v>
       </c>
       <c r="H14" s="170" t="n">
-        <f aca="false">G14/(1-'Datos Extra'!D22)</f>
+        <f aca="false">G14/(1-'Datos Extra'!D21)</f>
         <v>38999.3380775402</v>
       </c>
       <c r="I14" s="174" t="n">
@@ -22695,7 +22678,7 @@
         <v>19063.778</v>
       </c>
       <c r="K14" s="175" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L14" s="175"/>
       <c r="M14" s="175"/>
@@ -22704,7 +22687,7 @@
         <v>24875.066453</v>
       </c>
       <c r="O14" s="176" t="n">
-        <f aca="false">N14/(1-'Datos Extra'!D37)</f>
+        <f aca="false">N14/(1-'Datos Extra'!D36)</f>
         <v>26967.7650184302</v>
       </c>
       <c r="P14" s="168" t="n">
@@ -22721,7 +22704,7 @@
       <c r="B15" s="152"/>
       <c r="C15" s="153"/>
       <c r="D15" s="162" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E15" s="162"/>
       <c r="F15" s="162"/>
@@ -22730,7 +22713,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="163" t="n">
-        <f aca="false">G15*'Datos Extra'!D23+Report!G15</f>
+        <f aca="false">G15*'Datos Extra'!D22+Report!G15</f>
         <v>0</v>
       </c>
       <c r="I15" s="172" t="n">
@@ -22742,7 +22725,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="173" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L15" s="173"/>
       <c r="M15" s="173"/>
@@ -22772,7 +22755,7 @@
       <c r="I16" s="171"/>
       <c r="J16" s="170"/>
       <c r="K16" s="175" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L16" s="175"/>
       <c r="M16" s="175"/>
@@ -22832,10 +22815,10 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="152"/>
       <c r="C19" s="153" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D19" s="179" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E19" s="179"/>
       <c r="F19" s="179"/>
@@ -22853,7 +22836,7 @@
         <v>54984.074</v>
       </c>
       <c r="K19" s="179" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L19" s="179"/>
       <c r="M19" s="179"/>
@@ -22878,7 +22861,7 @@
       <c r="B20" s="152"/>
       <c r="C20" s="153"/>
       <c r="D20" s="184" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E20" s="184"/>
       <c r="F20" s="184"/>
@@ -22887,7 +22870,7 @@
       <c r="I20" s="184"/>
       <c r="J20" s="184"/>
       <c r="K20" s="161" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L20" s="161"/>
       <c r="M20" s="161"/>
@@ -22902,7 +22885,7 @@
       <c r="B21" s="152"/>
       <c r="C21" s="153"/>
       <c r="D21" s="162" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -22911,7 +22894,7 @@
         <v>73127</v>
       </c>
       <c r="H21" s="186" t="n">
-        <f aca="false">G21/(1-'Datos Extra'!D24)</f>
+        <f aca="false">G21/(1-'Datos Extra'!D23)</f>
         <v>80030.4244095695</v>
       </c>
       <c r="I21" s="187" t="n">
@@ -22923,7 +22906,7 @@
         <v>47634.9278</v>
       </c>
       <c r="K21" s="188" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L21" s="188"/>
       <c r="M21" s="188"/>
@@ -22932,7 +22915,7 @@
         <v>69689</v>
       </c>
       <c r="O21" s="163" t="n">
-        <f aca="false">N21/(1-'Datos Extra'!D28)</f>
+        <f aca="false">N21/(1-'Datos Extra'!D27)</f>
         <v>76766.6281666448</v>
       </c>
       <c r="P21" s="164" t="n">
@@ -22950,7 +22933,7 @@
       <c r="B22" s="152"/>
       <c r="C22" s="153"/>
       <c r="D22" s="166" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E22" s="166"/>
       <c r="F22" s="166"/>
@@ -22959,7 +22942,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="190" t="n">
-        <f aca="false">G22/(1-'Datos Extra'!D25)</f>
+        <f aca="false">G22/(1-'Datos Extra'!D24)</f>
         <v>0</v>
       </c>
       <c r="I22" s="191" t="n">
@@ -22971,7 +22954,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="192" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="L22" s="193"/>
       <c r="M22" s="194"/>
@@ -22980,7 +22963,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="167" t="n">
-        <f aca="false">N22/(1-'Datos Extra'!D31)</f>
+        <f aca="false">N22/(1-'Datos Extra'!D30)</f>
         <v>0</v>
       </c>
       <c r="P22" s="171" t="n">
@@ -22998,7 +22981,7 @@
       <c r="B23" s="152"/>
       <c r="C23" s="153"/>
       <c r="D23" s="162" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E23" s="162"/>
       <c r="F23" s="162"/>
@@ -23007,7 +22990,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="186" t="n">
-        <f aca="false">G23/(1-'Datos Extra'!D26)</f>
+        <f aca="false">G23/(1-'Datos Extra'!D25)</f>
         <v>0</v>
       </c>
       <c r="I23" s="195" t="n">
@@ -23019,7 +23002,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="196" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L23" s="197"/>
       <c r="M23" s="198"/>
@@ -23028,7 +23011,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="163" t="n">
-        <f aca="false">N23/(1-'Datos Extra'!D32)</f>
+        <f aca="false">N23/(1-'Datos Extra'!D31)</f>
         <v>0</v>
       </c>
       <c r="P23" s="172" t="n">
@@ -23046,7 +23029,7 @@
       <c r="B24" s="152"/>
       <c r="C24" s="153"/>
       <c r="D24" s="166" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E24" s="166"/>
       <c r="F24" s="166"/>
@@ -23055,7 +23038,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="190" t="n">
-        <f aca="false">G24/(1-'Datos Extra'!D42)</f>
+        <f aca="false">G24/(1-'Datos Extra'!D41)</f>
         <v>0</v>
       </c>
       <c r="I24" s="191" t="n">
@@ -23067,7 +23050,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="192" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L24" s="193"/>
       <c r="M24" s="194"/>
@@ -23076,7 +23059,7 @@
         <v>3157</v>
       </c>
       <c r="O24" s="167" t="n">
-        <f aca="false">N24/(1-'Datos Extra'!D40)</f>
+        <f aca="false">N24/(1-'Datos Extra'!D39)</f>
         <v>3185.02824858757</v>
       </c>
       <c r="P24" s="199" t="n">
@@ -23094,7 +23077,7 @@
       <c r="B25" s="152"/>
       <c r="C25" s="153"/>
       <c r="D25" s="162" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E25" s="162"/>
       <c r="F25" s="162"/>
@@ -23103,7 +23086,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="186" t="n">
-        <f aca="false">G25/(1-'Datos Extra'!D29)</f>
+        <f aca="false">G25/(1-'Datos Extra'!D28)</f>
         <v>0</v>
       </c>
       <c r="I25" s="195" t="n">
@@ -23115,7 +23098,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="196" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L25" s="197"/>
       <c r="M25" s="198"/>
@@ -23124,7 +23107,7 @@
         <v>3069</v>
       </c>
       <c r="O25" s="163" t="n">
-        <f aca="false">N25/(1-'Datos Extra'!D41)</f>
+        <f aca="false">N25/(1-'Datos Extra'!D40)</f>
         <v>3108.47766636281</v>
       </c>
       <c r="P25" s="164" t="n">
@@ -23149,7 +23132,7 @@
       <c r="I26" s="195"/>
       <c r="J26" s="163"/>
       <c r="K26" s="192" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="L26" s="193"/>
       <c r="M26" s="194"/>
@@ -23158,7 +23141,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="167" t="n">
-        <f aca="false">N26/(1-'Datos Extra'!D42)</f>
+        <f aca="false">N26/(1-'Datos Extra'!D41)</f>
         <v>0</v>
       </c>
       <c r="P26" s="199" t="n">
@@ -23183,7 +23166,7 @@
       <c r="I27" s="195"/>
       <c r="J27" s="163"/>
       <c r="K27" s="196" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L27" s="197"/>
       <c r="M27" s="198"/>
@@ -23192,7 +23175,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="163" t="n">
-        <f aca="false">N27/(1-'Datos Extra'!D43)</f>
+        <f aca="false">N27/(1-'Datos Extra'!D42)</f>
         <v>0</v>
       </c>
       <c r="P27" s="164" t="n">
@@ -23217,7 +23200,7 @@
       <c r="I28" s="195"/>
       <c r="J28" s="163"/>
       <c r="K28" s="192" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L28" s="193"/>
       <c r="M28" s="194"/>
@@ -23226,7 +23209,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="167" t="n">
-        <f aca="false">N28/(1-'Datos Extra'!D42)</f>
+        <f aca="false">N28/(1-'Datos Extra'!D41)</f>
         <v>0</v>
       </c>
       <c r="P28" s="199" t="n">
@@ -23251,7 +23234,7 @@
       <c r="I29" s="195"/>
       <c r="J29" s="163"/>
       <c r="K29" s="192" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L29" s="193"/>
       <c r="M29" s="194"/>
@@ -23260,7 +23243,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="167" t="n">
-        <f aca="false">N29/(1-'Datos Extra'!D34)</f>
+        <f aca="false">N29/(1-'Datos Extra'!D33)</f>
         <v>0</v>
       </c>
       <c r="P29" s="200" t="n">
@@ -23285,7 +23268,7 @@
       <c r="I30" s="191"/>
       <c r="J30" s="170"/>
       <c r="K30" s="196" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L30" s="197"/>
       <c r="M30" s="198"/>
@@ -23294,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="163" t="n">
-        <f aca="false">N30/(1-'Datos Extra'!D35)</f>
+        <f aca="false">N30/(1-'Datos Extra'!D34)</f>
         <v>0</v>
       </c>
       <c r="P30" s="172" t="n">
@@ -23324,7 +23307,7 @@
       <c r="B32" s="152"/>
       <c r="C32" s="153"/>
       <c r="D32" s="179" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E32" s="179"/>
       <c r="F32" s="179"/>
@@ -23342,7 +23325,7 @@
         <v>47634.9278</v>
       </c>
       <c r="K32" s="179" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L32" s="179"/>
       <c r="M32" s="179"/>
@@ -23379,7 +23362,7 @@
       <c r="B34" s="152"/>
       <c r="C34" s="153"/>
       <c r="D34" s="205" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E34" s="205"/>
       <c r="F34" s="205"/>
@@ -23394,16 +23377,16 @@
       <c r="E35" s="207"/>
       <c r="F35" s="207"/>
       <c r="G35" s="208" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H35" s="209" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I35" s="210" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J35" s="210" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="L35" s="211"/>
       <c r="M35" s="211"/>
@@ -23418,16 +23401,16 @@
       <c r="B36" s="152"/>
       <c r="C36" s="153"/>
       <c r="D36" s="192" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E36" s="192"/>
       <c r="F36" s="192"/>
       <c r="G36" s="213" t="n">
-        <f aca="false">'Datos Extra'!B2</f>
+        <f aca="false">'Datos Extra'!B1</f>
         <v>11665</v>
       </c>
       <c r="H36" s="214" t="n">
-        <f aca="false">G36*(1-'Datos Extra'!D2)</f>
+        <f aca="false">G36*(1-'Datos Extra'!D1)</f>
         <v>11548.35</v>
       </c>
       <c r="I36" s="215" t="n">
@@ -23452,16 +23435,16 @@
       <c r="B37" s="152"/>
       <c r="C37" s="153"/>
       <c r="D37" s="192" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E37" s="192"/>
       <c r="F37" s="192"/>
       <c r="G37" s="216" t="n">
-        <f aca="false">'Datos Extra'!B3</f>
+        <f aca="false">'Datos Extra'!B2</f>
         <v>32218.6416985633</v>
       </c>
       <c r="H37" s="217" t="n">
-        <f aca="false">G37*(1-'Datos Extra'!D3)</f>
+        <f aca="false">G37*(1-'Datos Extra'!D2)</f>
         <v>31896.4552815777</v>
       </c>
       <c r="I37" s="215" t="n">
@@ -23475,16 +23458,16 @@
       <c r="K37" s="211"/>
       <c r="L37" s="211"/>
       <c r="M37" s="211" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N37" s="211" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O37" s="211" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P37" s="211" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q37" s="211"/>
       <c r="R37" s="146"/>
@@ -23494,16 +23477,16 @@
       <c r="B38" s="152"/>
       <c r="C38" s="153"/>
       <c r="D38" s="192" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E38" s="192"/>
       <c r="F38" s="192"/>
       <c r="G38" s="216" t="n">
-        <f aca="false">'Datos Extra'!B4</f>
+        <f aca="false">'Datos Extra'!B3</f>
         <v>33</v>
       </c>
       <c r="H38" s="217" t="n">
-        <f aca="false">G38*(1-'Datos Extra'!D4)</f>
+        <f aca="false">G38*(1-'Datos Extra'!D3)</f>
         <v>30.0486997982942</v>
       </c>
       <c r="I38" s="215" t="n">
@@ -23516,7 +23499,7 @@
       </c>
       <c r="K38" s="211"/>
       <c r="L38" s="211" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M38" s="218" t="n">
         <f aca="false">G19+N22+N23+N24+N29+N30</f>
@@ -23542,16 +23525,16 @@
       <c r="B39" s="152"/>
       <c r="C39" s="153"/>
       <c r="D39" s="192" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E39" s="192"/>
       <c r="F39" s="192"/>
       <c r="G39" s="216" t="n">
-        <f aca="false">'Datos Extra'!B5</f>
+        <f aca="false">'Datos Extra'!B4</f>
         <v>0</v>
       </c>
       <c r="H39" s="217" t="n">
-        <f aca="false">G39*(1-'Datos Extra'!D5)</f>
+        <f aca="false">G39*(1-'Datos Extra'!D4)</f>
         <v>0</v>
       </c>
       <c r="I39" s="215" t="n">
@@ -23564,7 +23547,7 @@
       </c>
       <c r="K39" s="211"/>
       <c r="L39" s="211" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M39" s="218" t="n">
         <f aca="false">J19+Q22+Q23+Q24+Q29+Q30</f>
@@ -23590,16 +23573,16 @@
       <c r="B40" s="152"/>
       <c r="C40" s="153"/>
       <c r="D40" s="192" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E40" s="192"/>
       <c r="F40" s="192"/>
       <c r="G40" s="216" t="n">
-        <f aca="false">'Datos Extra'!B6</f>
+        <f aca="false">'Datos Extra'!B5</f>
         <v>108658.53</v>
       </c>
       <c r="H40" s="217" t="n">
-        <f aca="false">G40*(1-'Datos Extra'!D6)</f>
+        <f aca="false">G40*(1-'Datos Extra'!D5)</f>
         <v>98640.5744007939</v>
       </c>
       <c r="I40" s="215" t="n">
@@ -23624,16 +23607,16 @@
       <c r="B41" s="152"/>
       <c r="C41" s="153"/>
       <c r="D41" s="192" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E41" s="192"/>
       <c r="F41" s="192"/>
       <c r="G41" s="216" t="n">
-        <f aca="false">'Datos Extra'!B7</f>
+        <f aca="false">'Datos Extra'!B6</f>
         <v>60226.45</v>
       </c>
       <c r="H41" s="217" t="n">
-        <f aca="false">G41*(1-'Datos Extra'!D7)</f>
+        <f aca="false">G41*(1-'Datos Extra'!D6)</f>
         <v>60226.45</v>
       </c>
       <c r="I41" s="215" t="n">
@@ -23657,16 +23640,16 @@
       <c r="B42" s="152"/>
       <c r="C42" s="153"/>
       <c r="D42" s="223" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E42" s="223"/>
       <c r="F42" s="223"/>
       <c r="G42" s="224" t="n">
-        <f aca="false">'Datos Extra'!B8</f>
+        <f aca="false">'Datos Extra'!B7</f>
         <v>64802</v>
       </c>
       <c r="H42" s="225" t="n">
-        <f aca="false">G42*(1-'Datos Extra'!D8)</f>
+        <f aca="false">G42*(1-'Datos Extra'!D7)</f>
         <v>64802</v>
       </c>
       <c r="I42" s="215" t="n">
@@ -23690,16 +23673,16 @@
       <c r="B43" s="226"/>
       <c r="C43" s="227"/>
       <c r="D43" s="223" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E43" s="223"/>
       <c r="F43" s="223"/>
       <c r="G43" s="224" t="n">
-        <f aca="false">'Datos Extra'!B9</f>
+        <f aca="false">'Datos Extra'!B8</f>
         <v>71110.9575524111</v>
       </c>
       <c r="H43" s="225" t="n">
-        <f aca="false">G43*(1-'Datos Extra'!D9)</f>
+        <f aca="false">G43*(1-'Datos Extra'!D8)</f>
         <v>70399.847976887</v>
       </c>
       <c r="I43" s="228" t="n">

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Utilidad" sheetId="1" state="visible" r:id="rId3"/>
@@ -1316,7 +1316,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="31">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1528,13 +1528,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="medium"/>
       <right/>
       <top style="thin"/>
@@ -1586,7 +1579,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="235">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2439,14 +2432,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="15" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="27" fillId="0" borderId="27" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="15" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2455,10 +2448,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="30" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="173" fontId="32" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2479,7 +2468,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="16" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="27" fillId="16" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2487,16 +2476,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="27" fillId="0" borderId="17" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="8" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="17" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="29" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2662,9 +2651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>224640</xdr:colOff>
+      <xdr:colOff>224280</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>183960</xdr:rowOff>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2674,7 +2663,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4077720" y="1483560"/>
-          <a:ext cx="1058040" cy="415080"/>
+          <a:ext cx="1057680" cy="414720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2712,7 +2701,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -2722,7 +2711,7 @@
             </a:rPr>
             <a:t>CH- CM</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -2741,9 +2730,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>648720</xdr:colOff>
+      <xdr:colOff>648360</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>24840</xdr:rowOff>
+      <xdr:rowOff>24480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2753,7 +2742,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7031880" y="2093760"/>
-          <a:ext cx="500760" cy="407520"/>
+          <a:ext cx="500400" cy="407160"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -2794,9 +2783,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>380160</xdr:colOff>
+      <xdr:colOff>379800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>164880</xdr:rowOff>
+      <xdr:rowOff>164520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2806,7 +2795,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6323400" y="1779840"/>
-          <a:ext cx="940680" cy="480600"/>
+          <a:ext cx="940320" cy="480240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2841,7 +2830,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -2851,7 +2840,7 @@
             </a:rPr>
             <a:t>Stock Intermedio</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -2870,9 +2859,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>96120</xdr:colOff>
+      <xdr:colOff>95760</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>75960</xdr:rowOff>
+      <xdr:rowOff>75600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2882,7 +2871,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10137600" y="3348000"/>
-          <a:ext cx="1201680" cy="347400"/>
+          <a:ext cx="1201320" cy="347040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2917,7 +2906,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -2927,7 +2916,7 @@
             </a:rPr>
             <a:t>Stock Pre concentrado</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -2946,9 +2935,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>410400</xdr:colOff>
+      <xdr:colOff>410040</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>39240</xdr:rowOff>
+      <xdr:rowOff>38880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2958,7 +2947,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7524720" y="6739920"/>
-          <a:ext cx="651240" cy="538200"/>
+          <a:ext cx="650880" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -2999,9 +2988,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>77400</xdr:colOff>
+      <xdr:colOff>77040</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>82440</xdr:rowOff>
+      <xdr:rowOff>82080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3011,7 +3000,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6530400" y="8498160"/>
-          <a:ext cx="1312560" cy="537840"/>
+          <a:ext cx="1312200" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3046,7 +3035,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3056,7 +3045,7 @@
             </a:rPr>
             <a:t>Stock Pellet Feed ROM</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3075,9 +3064,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>718920</xdr:colOff>
+      <xdr:colOff>718560</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>99360</xdr:rowOff>
+      <xdr:rowOff>99000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3087,7 +3076,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7239240" y="10542960"/>
-          <a:ext cx="1245240" cy="415080"/>
+          <a:ext cx="1244880" cy="414720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3125,7 +3114,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3135,7 +3124,7 @@
             </a:rPr>
             <a:t>Nodo Transporte Pellet Feed</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3154,9 +3143,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>626400</xdr:colOff>
+      <xdr:colOff>626040</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>108720</xdr:rowOff>
+      <xdr:rowOff>108360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3166,7 +3155,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9577080" y="12143880"/>
-          <a:ext cx="577440" cy="537840"/>
+          <a:ext cx="577080" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3207,9 +3196,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>699840</xdr:colOff>
+      <xdr:colOff>699480</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:rowOff>54720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3219,7 +3208,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9938880" y="12243240"/>
-          <a:ext cx="1052280" cy="384840"/>
+          <a:ext cx="1051920" cy="384480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3254,7 +3243,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3264,7 +3253,7 @@
             </a:rPr>
             <a:t>Stock P. Feed Guayacan</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3283,9 +3272,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>656280</xdr:colOff>
+      <xdr:colOff>655920</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>3600</xdr:rowOff>
+      <xdr:rowOff>3240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3295,7 +3284,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9606960" y="13565880"/>
-          <a:ext cx="577440" cy="534600"/>
+          <a:ext cx="577080" cy="534240"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3336,9 +3325,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>462600</xdr:colOff>
+      <xdr:colOff>462240</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3348,7 +3337,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9701640" y="13191120"/>
-          <a:ext cx="1052280" cy="534240"/>
+          <a:ext cx="1051920" cy="533880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3383,7 +3372,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3393,7 +3382,7 @@
             </a:rPr>
             <a:t>Stock Finos Guayacan</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3412,9 +3401,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>492120</xdr:colOff>
+      <xdr:colOff>491760</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>78840</xdr:rowOff>
+      <xdr:rowOff>78480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3424,7 +3413,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12100320" y="12114000"/>
-          <a:ext cx="2513520" cy="537840"/>
+          <a:ext cx="2513160" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3459,7 +3448,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3469,7 +3458,7 @@
             </a:rPr>
             <a:t>Embarque Pellet Feed Guayacan</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3488,9 +3477,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>111960</xdr:colOff>
+      <xdr:colOff>111600</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>88200</xdr:rowOff>
+      <xdr:rowOff>87840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3500,7 +3489,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12152520" y="12885480"/>
-          <a:ext cx="2892240" cy="537840"/>
+          <a:ext cx="2891880" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3535,7 +3524,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3545,7 +3534,7 @@
             </a:rPr>
             <a:t>Transporte Camiones P Feed Guayacan</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3564,9 +3553,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>492120</xdr:colOff>
+      <xdr:colOff>491760</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:rowOff>85320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3576,7 +3565,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12100320" y="13644360"/>
-          <a:ext cx="2513520" cy="538200"/>
+          <a:ext cx="2513160" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3611,7 +3600,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3621,7 +3610,7 @@
             </a:rPr>
             <a:t>Embarque SF MLC</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3640,9 +3629,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>7200</xdr:colOff>
+      <xdr:colOff>6840</xdr:colOff>
       <xdr:row>86</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3652,7 +3641,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9720000" y="15999480"/>
-          <a:ext cx="578520" cy="538200"/>
+          <a:ext cx="578160" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3693,9 +3682,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>730800</xdr:colOff>
+      <xdr:colOff>730440</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>31320</xdr:rowOff>
+      <xdr:rowOff>30960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3705,7 +3694,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10071720" y="16066800"/>
-          <a:ext cx="950400" cy="538200"/>
+          <a:ext cx="950040" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3740,7 +3729,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3750,7 +3739,7 @@
             </a:rPr>
             <a:t>Stock Finos Granzas</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3769,9 +3758,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>604800</xdr:colOff>
+      <xdr:colOff>604440</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>71640</xdr:rowOff>
+      <xdr:rowOff>71280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3781,7 +3770,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12213000" y="16107120"/>
-          <a:ext cx="2513520" cy="538200"/>
+          <a:ext cx="2513160" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3816,7 +3805,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3826,7 +3815,7 @@
             </a:rPr>
             <a:t>Embarque Granzas</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -3845,9 +3834,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>578880</xdr:colOff>
+      <xdr:colOff>578520</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>138600</xdr:rowOff>
+      <xdr:rowOff>138240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3857,7 +3846,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5268600" y="4317840"/>
-          <a:ext cx="221400" cy="202320"/>
+          <a:ext cx="221040" cy="201960"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3937,9 +3926,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>644400</xdr:colOff>
+      <xdr:colOff>644040</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>111240</xdr:rowOff>
+      <xdr:rowOff>110880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3949,7 +3938,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2736000" y="11685960"/>
-          <a:ext cx="1363320" cy="426960"/>
+          <a:ext cx="1362960" cy="426600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3984,7 +3973,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3994,7 +3983,7 @@
             </a:rPr>
             <a:t>Otros Materiales a Preconcentradio</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -4013,9 +4002,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>14040</xdr:colOff>
+      <xdr:colOff>13680</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>172800</xdr:rowOff>
+      <xdr:rowOff>172440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4025,7 +4014,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2647440" y="685800"/>
-          <a:ext cx="1514520" cy="249120"/>
+          <a:ext cx="1514160" cy="248760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4060,7 +4049,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4070,7 +4059,7 @@
             </a:rPr>
             <a:t>Alimentación Chancado</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -4128,9 +4117,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>684360</xdr:colOff>
+      <xdr:colOff>684000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>43920</xdr:rowOff>
+      <xdr:rowOff>43560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4140,7 +4129,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2751120" y="2363400"/>
-          <a:ext cx="577440" cy="538200"/>
+          <a:ext cx="577080" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4181,9 +4170,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>163440</xdr:colOff>
+      <xdr:colOff>163080</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>30960</xdr:rowOff>
+      <xdr:rowOff>30600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4193,7 +4182,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2023560" y="2752200"/>
-          <a:ext cx="784080" cy="326880"/>
+          <a:ext cx="783720" cy="326520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4228,7 +4217,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4238,7 +4227,7 @@
             </a:rPr>
             <a:t>Stock ML Pleito</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -4257,9 +4246,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>671040</xdr:colOff>
+      <xdr:colOff>670680</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>101520</xdr:rowOff>
+      <xdr:rowOff>101160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4269,7 +4258,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="323280" y="2252520"/>
-          <a:ext cx="559080" cy="325440"/>
+          <a:ext cx="558720" cy="325080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4304,7 +4293,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4314,7 +4303,7 @@
             </a:rPr>
             <a:t>ML Pleito</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -4411,9 +4400,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>123480</xdr:colOff>
+      <xdr:colOff>123120</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>103320</xdr:rowOff>
+      <xdr:rowOff>102960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4423,7 +4412,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1201680" y="3791520"/>
-          <a:ext cx="1566000" cy="312480"/>
+          <a:ext cx="1565640" cy="312120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4458,7 +4447,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4468,7 +4457,7 @@
             </a:rPr>
             <a:t>Otros Materiales a Stock Intermedio desde Pleito</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -4602,9 +4591,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>714240</xdr:colOff>
+      <xdr:colOff>713880</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>46080</xdr:rowOff>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4614,7 +4603,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4053600" y="2495160"/>
-          <a:ext cx="808560" cy="217800"/>
+          <a:ext cx="808200" cy="217440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4649,7 +4638,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4659,7 +4648,7 @@
             </a:rPr>
             <a:t>RECHAZOS</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -4717,9 +4706,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>240120</xdr:colOff>
+      <xdr:colOff>239760</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>90360</xdr:rowOff>
+      <xdr:rowOff>90000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4729,7 +4718,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3069000" y="4695840"/>
-          <a:ext cx="626040" cy="538200"/>
+          <a:ext cx="625680" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4770,9 +4759,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>716040</xdr:colOff>
+      <xdr:colOff>715680</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>105480</xdr:rowOff>
+      <xdr:rowOff>105120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4782,7 +4771,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2372040" y="5111640"/>
-          <a:ext cx="988200" cy="327960"/>
+          <a:ext cx="987840" cy="327600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4817,7 +4806,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4827,7 +4816,7 @@
             </a:rPr>
             <a:t>Stock Emergencia 1</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -4846,9 +4835,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>216000</xdr:colOff>
+      <xdr:colOff>215640</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>36360</xdr:rowOff>
+      <xdr:rowOff>36000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4858,7 +4847,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1971720" y="4663800"/>
-          <a:ext cx="888480" cy="325440"/>
+          <a:ext cx="888120" cy="325080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4893,7 +4882,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4903,7 +4892,7 @@
             </a:rPr>
             <a:t>Finos Pleito</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5000,9 +4989,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>144000</xdr:colOff>
+      <xdr:colOff>143640</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>167760</xdr:rowOff>
+      <xdr:rowOff>167400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5012,7 +5001,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3521520" y="4608720"/>
-          <a:ext cx="770400" cy="321480"/>
+          <a:ext cx="770040" cy="321120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5047,7 +5036,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5057,7 +5046,7 @@
             </a:rPr>
             <a:t>Alim Finos Pleito</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5076,9 +5065,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>257760</xdr:colOff>
+      <xdr:colOff>257400</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>135720</xdr:rowOff>
+      <xdr:rowOff>135360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5088,7 +5077,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3086640" y="6455880"/>
-          <a:ext cx="626040" cy="537840"/>
+          <a:ext cx="625680" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5129,9 +5118,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>671040</xdr:colOff>
+      <xdr:colOff>670680</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:rowOff>180360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5141,7 +5130,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2329920" y="6979680"/>
-          <a:ext cx="985320" cy="439920"/>
+          <a:ext cx="984960" cy="439560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5176,7 +5165,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5186,7 +5175,7 @@
             </a:rPr>
             <a:t>Stock Emergencia 2</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5283,9 +5272,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>365040</xdr:colOff>
+      <xdr:colOff>364680</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:rowOff>172080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5295,7 +5284,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3363480" y="6190200"/>
-          <a:ext cx="1149480" cy="459360"/>
+          <a:ext cx="1149120" cy="459000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5330,7 +5319,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5340,7 +5329,7 @@
             </a:rPr>
             <a:t>P55  de Emergencia 2 a Pre-concentrado</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5359,9 +5348,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>11520</xdr:colOff>
+      <xdr:colOff>11160</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:rowOff>16920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5371,7 +5360,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2105640" y="6456240"/>
-          <a:ext cx="550080" cy="228600"/>
+          <a:ext cx="549720" cy="228240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5406,7 +5395,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5416,7 +5405,7 @@
             </a:rPr>
             <a:t>P55</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5474,9 +5463,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>265680</xdr:colOff>
+      <xdr:colOff>265320</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>72360</xdr:rowOff>
+      <xdr:rowOff>72000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5486,7 +5475,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3094560" y="8297640"/>
-          <a:ext cx="626040" cy="537840"/>
+          <a:ext cx="625680" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5527,9 +5516,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>745920</xdr:colOff>
+      <xdr:colOff>745560</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>23400</xdr:rowOff>
+      <xdr:rowOff>23040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5539,7 +5528,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2300760" y="8851320"/>
-          <a:ext cx="1089360" cy="316080"/>
+          <a:ext cx="1089000" cy="315720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5574,7 +5563,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5584,7 +5573,7 @@
             </a:rPr>
             <a:t>Stock Emergencia 3</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5642,9 +5631,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>290520</xdr:colOff>
+      <xdr:colOff>290160</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>115200</xdr:rowOff>
+      <xdr:rowOff>114840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5654,7 +5643,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3378960" y="8017920"/>
-          <a:ext cx="1059480" cy="479160"/>
+          <a:ext cx="1059120" cy="478800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5689,7 +5678,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5699,7 +5688,7 @@
             </a:rPr>
             <a:t>P40  de Emergencia 3 a Pre-concentrado</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5718,9 +5707,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>19800</xdr:colOff>
+      <xdr:colOff>19440</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>120960</xdr:rowOff>
+      <xdr:rowOff>120600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5730,7 +5719,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2113920" y="8152200"/>
-          <a:ext cx="550080" cy="350640"/>
+          <a:ext cx="549720" cy="350280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5765,7 +5754,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5775,7 +5764,7 @@
             </a:rPr>
             <a:t>P40</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -5833,9 +5822,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>214560</xdr:colOff>
+      <xdr:colOff>214200</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>187920</xdr:rowOff>
+      <xdr:rowOff>187560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5845,7 +5834,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3043440" y="10321200"/>
-          <a:ext cx="626040" cy="534600"/>
+          <a:ext cx="625680" cy="534240"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5886,9 +5875,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>657720</xdr:colOff>
+      <xdr:colOff>657360</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>65520</xdr:rowOff>
+      <xdr:rowOff>65160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5898,7 +5887,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2672280" y="10912320"/>
-          <a:ext cx="1440360" cy="202320"/>
+          <a:ext cx="1440000" cy="201960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5933,7 +5922,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -5943,7 +5932,7 @@
             </a:rPr>
             <a:t>Stock Emergencia 4</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6001,9 +5990,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>417240</xdr:colOff>
+      <xdr:colOff>416880</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>110880</xdr:rowOff>
+      <xdr:rowOff>110520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6013,7 +6002,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3495960" y="9997560"/>
-          <a:ext cx="1069200" cy="590760"/>
+          <a:ext cx="1068840" cy="590400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6048,7 +6037,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6058,7 +6047,7 @@
             </a:rPr>
             <a:t>Sinter MLC Emergencia 4 a Pre-concentrado</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6077,9 +6066,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>119880</xdr:colOff>
+      <xdr:colOff>119520</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>31680</xdr:rowOff>
+      <xdr:rowOff>31320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6089,7 +6078,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1928160" y="10090080"/>
-          <a:ext cx="835920" cy="228600"/>
+          <a:ext cx="835560" cy="228240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6124,7 +6113,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6134,7 +6123,7 @@
             </a:rPr>
             <a:t>Sinter MLC</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6309,9 +6298,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>728640</xdr:colOff>
+      <xdr:colOff>728280</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>76320</xdr:rowOff>
+      <xdr:rowOff>75960</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6321,9 +6310,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="9679320" y="3157560"/>
-          <a:ext cx="577440" cy="538200"/>
+          <a:ext cx="577080" cy="537840"/>
           <a:chOff x="9679320" y="3157560"/>
-          <a:chExt cx="577440" cy="538200"/>
+          <a:chExt cx="577080" cy="537840"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6334,7 +6323,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9679320" y="3157560"/>
-            <a:ext cx="577440" cy="538200"/>
+            <a:ext cx="577080" cy="537840"/>
           </a:xfrm>
           <a:prstGeom prst="triangle">
             <a:avLst>
@@ -6372,7 +6361,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9896400" y="3253680"/>
-            <a:ext cx="143640" cy="125640"/>
+            <a:ext cx="143280" cy="125280"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6405,7 +6394,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9968760" y="3403800"/>
-            <a:ext cx="143640" cy="125640"/>
+            <a:ext cx="143280" cy="125280"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6438,7 +6427,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10040760" y="3535920"/>
-            <a:ext cx="143640" cy="125640"/>
+            <a:ext cx="143280" cy="125280"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6475,9 +6464,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>536040</xdr:colOff>
+      <xdr:colOff>535680</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>102960</xdr:rowOff>
+      <xdr:rowOff>102600</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6487,9 +6476,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="10463760" y="1593000"/>
-          <a:ext cx="1315440" cy="415080"/>
+          <a:ext cx="1315080" cy="414720"/>
           <a:chOff x="10463760" y="1593000"/>
-          <a:chExt cx="1315440" cy="415080"/>
+          <a:chExt cx="1315080" cy="414720"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6500,7 +6489,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10463760" y="1593000"/>
-            <a:ext cx="1315440" cy="415080"/>
+            <a:ext cx="1315080" cy="414720"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6538,7 +6527,7 @@
               </a:lnSpc>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+              <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -6548,7 +6537,7 @@
               </a:rPr>
               <a:t>Concentradora</a:t>
             </a:r>
-            <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:effectLst/>
               <a:uFillTx/>
               <a:latin typeface="Times New Roman"/>
@@ -6564,7 +6553,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="11449800" y="1881360"/>
-            <a:ext cx="167760" cy="124920"/>
+            <a:ext cx="167400" cy="124560"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6677,9 +6666,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>933480</xdr:colOff>
+      <xdr:colOff>933120</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>162360</xdr:rowOff>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6689,7 +6678,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11955600" y="1823040"/>
-          <a:ext cx="1032120" cy="434880"/>
+          <a:ext cx="1031760" cy="434520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6724,7 +6713,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6734,7 +6723,7 @@
             </a:rPr>
             <a:t>Cola </a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6747,7 +6736,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6757,7 +6746,7 @@
             </a:rPr>
             <a:t>Concentradora</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6770,7 +6759,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6780,7 +6769,7 @@
             </a:rPr>
             <a:t>(canoa)</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6799,9 +6788,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>797400</xdr:colOff>
+      <xdr:colOff>797040</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>48600</xdr:rowOff>
+      <xdr:rowOff>48240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6811,7 +6800,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11902680" y="1061640"/>
-          <a:ext cx="948960" cy="510840"/>
+          <a:ext cx="948600" cy="510480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6846,7 +6835,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6856,7 +6845,7 @@
             </a:rPr>
             <a:t>Rechazo a </a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6869,7 +6858,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6879,7 +6868,7 @@
             </a:rPr>
             <a:t>Botadero</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6892,7 +6881,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -6902,7 +6891,7 @@
             </a:rPr>
             <a:t>+</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -6921,9 +6910,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>684360</xdr:colOff>
+      <xdr:colOff>684000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>23040</xdr:rowOff>
+      <xdr:rowOff>22680</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6933,9 +6922,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="7204680" y="4555800"/>
-          <a:ext cx="1245240" cy="420120"/>
+          <a:ext cx="1244880" cy="419760"/>
           <a:chOff x="7204680" y="4555800"/>
-          <a:chExt cx="1245240" cy="420120"/>
+          <a:chExt cx="1244880" cy="419760"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6946,7 +6935,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="7204680" y="4556880"/>
-            <a:ext cx="1245240" cy="419040"/>
+            <a:ext cx="1244880" cy="418680"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6984,7 +6973,7 @@
               </a:lnSpc>
             </a:pPr>
             <a:r>
-              <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+              <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -6994,7 +6983,7 @@
               </a:rPr>
               <a:t>Molienda</a:t>
             </a:r>
-            <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:effectLst/>
               <a:uFillTx/>
               <a:latin typeface="Times New Roman"/>
@@ -7010,7 +6999,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="8283240" y="4555800"/>
-            <a:ext cx="158760" cy="126360"/>
+            <a:ext cx="158400" cy="126000"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -7125,9 +7114,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>221760</xdr:colOff>
+      <xdr:colOff>221400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>45360</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7137,7 +7126,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9769320" y="4603680"/>
-          <a:ext cx="743760" cy="204120"/>
+          <a:ext cx="743400" cy="203760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7172,7 +7161,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7182,7 +7171,7 @@
             </a:rPr>
             <a:t>Repulpeo </a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7201,9 +7190,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>150840</xdr:colOff>
+      <xdr:colOff>150480</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>181800</xdr:rowOff>
+      <xdr:rowOff>181440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7213,7 +7202,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10801800" y="4813560"/>
-          <a:ext cx="1403280" cy="321120"/>
+          <a:ext cx="1402920" cy="320760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7248,7 +7237,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7258,7 +7247,7 @@
             </a:rPr>
             <a:t>SF a Molienda </a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7277,9 +7266,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>260280</xdr:colOff>
+      <xdr:colOff>259920</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>22680</xdr:rowOff>
+      <xdr:rowOff>22320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7289,7 +7278,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9452880" y="1030680"/>
-          <a:ext cx="1098720" cy="325440"/>
+          <a:ext cx="1098360" cy="325080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7324,7 +7313,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7334,7 +7323,7 @@
             </a:rPr>
             <a:t>Alim a Concentradora</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7353,9 +7342,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>319680</xdr:colOff>
+      <xdr:colOff>319320</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>18360</xdr:rowOff>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7365,7 +7354,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5590440" y="5217840"/>
-          <a:ext cx="1613160" cy="325080"/>
+          <a:ext cx="1612800" cy="324720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7400,7 +7389,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7410,7 +7399,7 @@
             </a:rPr>
             <a:t>COLA</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7423,7 +7412,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7433,7 +7422,7 @@
             </a:rPr>
             <a:t>MOLIENDA</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7606,9 +7595,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>308880</xdr:colOff>
+      <xdr:colOff>308520</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>168840</xdr:rowOff>
+      <xdr:rowOff>168480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7618,7 +7607,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5999760" y="9350280"/>
-          <a:ext cx="1193040" cy="534240"/>
+          <a:ext cx="1192680" cy="533880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7653,7 +7642,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7663,7 +7652,7 @@
             </a:rPr>
             <a:t>Transp</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7676,7 +7665,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7686,7 +7675,7 @@
             </a:rPr>
             <a:t>P. Feed</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7699,7 +7688,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7709,7 +7698,7 @@
             </a:rPr>
             <a:t>Camiones</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7728,9 +7717,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>509040</xdr:colOff>
+      <xdr:colOff>508680</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>186840</xdr:rowOff>
+      <xdr:rowOff>186480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7740,7 +7729,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8937360" y="9368280"/>
-          <a:ext cx="1099800" cy="534240"/>
+          <a:ext cx="1099440" cy="533880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7775,7 +7764,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7785,7 +7774,7 @@
             </a:rPr>
             <a:t>Transp</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7798,7 +7787,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7808,7 +7797,7 @@
             </a:rPr>
             <a:t>P. Feed</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7821,7 +7810,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7831,7 +7820,7 @@
             </a:rPr>
             <a:t>Trenes</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -7887,9 +7876,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>81360</xdr:colOff>
+      <xdr:colOff>81000</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>144360</xdr:rowOff>
+      <xdr:rowOff>144000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7899,7 +7888,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8497800" y="10846080"/>
-          <a:ext cx="1111680" cy="537840"/>
+          <a:ext cx="1111320" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7934,7 +7923,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -7944,7 +7933,7 @@
             </a:rPr>
             <a:t>Pérdidas por Transporte</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8041,9 +8030,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>647280</xdr:colOff>
+      <xdr:colOff>646920</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:rowOff>123480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8053,7 +8042,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7144200" y="11509920"/>
-          <a:ext cx="1268640" cy="424800"/>
+          <a:ext cx="1268280" cy="424440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8088,7 +8077,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8098,7 +8087,7 @@
             </a:rPr>
             <a:t>Transp</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8111,7 +8100,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8121,7 +8110,7 @@
             </a:rPr>
             <a:t>Total</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8134,7 +8123,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8144,7 +8133,7 @@
             </a:rPr>
             <a:t>P. Feed</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8157,7 +8146,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8167,7 +8156,7 @@
             </a:rPr>
             <a:t>A Guayacan</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8186,9 +8175,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>598320</xdr:colOff>
+      <xdr:colOff>597960</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8198,7 +8187,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6904800" y="13568040"/>
-          <a:ext cx="577440" cy="538200"/>
+          <a:ext cx="577080" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -8239,9 +8228,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>578880</xdr:colOff>
+      <xdr:colOff>578520</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:rowOff>150840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8251,7 +8240,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6269760" y="13138920"/>
-          <a:ext cx="1193040" cy="537840"/>
+          <a:ext cx="1192680" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8286,7 +8275,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8296,7 +8285,7 @@
             </a:rPr>
             <a:t>Stock SF Patio Tolva ROM</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8471,9 +8460,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>753480</xdr:colOff>
+      <xdr:colOff>753120</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>70920</xdr:rowOff>
+      <xdr:rowOff>70560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8483,7 +8472,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3919320" y="13439160"/>
-          <a:ext cx="982080" cy="538200"/>
+          <a:ext cx="981720" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8518,7 +8507,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8528,7 +8517,7 @@
             </a:rPr>
             <a:t>Recepción SFMLC</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8547,9 +8536,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>753120</xdr:colOff>
+      <xdr:colOff>752760</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>135360</xdr:rowOff>
+      <xdr:rowOff>135000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8559,7 +8548,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3918960" y="14266080"/>
-          <a:ext cx="982080" cy="537840"/>
+          <a:ext cx="981720" cy="537480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8594,7 +8583,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8604,7 +8593,7 @@
             </a:rPr>
             <a:t>P55 desde MLC</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8662,9 +8651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>32040</xdr:colOff>
+      <xdr:colOff>31680</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>175320</xdr:rowOff>
+      <xdr:rowOff>174960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8674,7 +8663,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5549040" y="14880600"/>
-          <a:ext cx="1366920" cy="534600"/>
+          <a:ext cx="1366560" cy="534240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8709,7 +8698,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8719,7 +8708,7 @@
             </a:rPr>
             <a:t>Recepción SF directo desde MLC</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8777,9 +8766,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>716400</xdr:colOff>
+      <xdr:colOff>716040</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:rowOff>11160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8789,7 +8778,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6540120" y="15613560"/>
-          <a:ext cx="1060200" cy="399960"/>
+          <a:ext cx="1059840" cy="399600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8824,7 +8813,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8834,7 +8823,7 @@
             </a:rPr>
             <a:t>Recepción Finos Pleito</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -8892,9 +8881,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>713160</xdr:colOff>
+      <xdr:colOff>712800</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>109080</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8904,7 +8893,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6338160" y="16476840"/>
-          <a:ext cx="1258920" cy="396360"/>
+          <a:ext cx="1258560" cy="396000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8939,7 +8928,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -8949,7 +8938,7 @@
             </a:rPr>
             <a:t>Recepción Planta Cristales</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -9007,9 +8996,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>18000</xdr:colOff>
+      <xdr:colOff>17640</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>85320</xdr:rowOff>
+      <xdr:rowOff>84960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9019,7 +9008,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6404760" y="17214480"/>
-          <a:ext cx="1378800" cy="396720"/>
+          <a:ext cx="1378440" cy="396360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9054,7 +9043,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -9064,7 +9053,7 @@
             </a:rPr>
             <a:t>Recepción Granzas Pleito</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -9161,9 +9150,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>34200</xdr:colOff>
+      <xdr:colOff>33840</xdr:colOff>
       <xdr:row>80</xdr:row>
-      <xdr:rowOff>56160</xdr:rowOff>
+      <xdr:rowOff>55800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9173,7 +9162,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12523320" y="14757840"/>
-          <a:ext cx="2443680" cy="538200"/>
+          <a:ext cx="2443320" cy="537840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9208,7 +9197,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -9218,7 +9207,7 @@
             </a:rPr>
             <a:t>Ventas locales</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -9230,7 +9219,7 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -9288,9 +9277,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>929160</xdr:colOff>
+      <xdr:colOff>928800</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>181800</xdr:rowOff>
+      <xdr:rowOff>181440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9300,7 +9289,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7634160" y="15208200"/>
-          <a:ext cx="1060560" cy="404280"/>
+          <a:ext cx="1060200" cy="403920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9335,7 +9324,7 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+            <a:rPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -9345,7 +9334,7 @@
             </a:rPr>
             <a:t>Recepción APC</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="es-CL" sz="1000" strike="noStrike" u="none">
+          <a:endParaRPr lang="es-CL" sz="1000" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -9564,13 +9553,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>437760</xdr:colOff>
+      <xdr:colOff>437400</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>47520</xdr:rowOff>
+      <xdr:rowOff>47160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Imagen 1" descr=""/>
+        <xdr:cNvPr id="120" name="Imagen 1"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -9580,7 +9569,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="725760" y="466920"/>
-          <a:ext cx="946440" cy="533160"/>
+          <a:ext cx="946080" cy="532800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14282,10 +14271,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0"/>
-      <c r="B46" s="0"/>
-      <c r="C46" s="0"/>
-      <c r="D46" s="0"/>
+      <c r="C46" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -19364,7 +19350,7 @@
       <c r="O153" s="124"/>
       <c r="P153" s="126" t="n">
         <f aca="false">+I151-L151-P151</f>
-        <v>3.29164322465658E-008</v>
+        <v>3.29309841617942E-008</v>
       </c>
     </row>
   </sheetData>
@@ -19470,7 +19456,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{52A8A6B7-4761-4345-A1A0-DBC8AD96F8DA}">
+          <x14:cfRule type="iconSet" priority="2" id="{ACCBBCB6-9F28-4BC0-A4BE-CF3081F6B7A0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19489,7 +19475,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{ED6856DD-5190-4A18-9044-41DCDC27A076}">
+          <x14:cfRule type="iconSet" priority="3" id="{192222EC-297F-4E61-8E68-1C8B9B8E312A}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19508,7 +19494,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{2EF0DFA9-2317-4923-B042-C520913BB1CD}">
+          <x14:cfRule type="iconSet" priority="4" id="{2F85DB35-9AF0-4712-BA15-9C66D463E739}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19527,7 +19513,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{4B2092C4-E92C-4BED-87F0-667F7C71EFBB}">
+          <x14:cfRule type="iconSet" priority="5" id="{14FF297A-84AA-47E6-B7B8-3EC45C20CD5B}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19546,7 +19532,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{F2498421-542B-41B0-A096-7F4FBF608270}">
+          <x14:cfRule type="iconSet" priority="6" id="{FFFA178A-F6F8-423E-8584-39916B3029E1}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19565,7 +19551,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{BD1855EC-DE1A-4BC7-9798-2985C0554A2D}">
+          <x14:cfRule type="iconSet" priority="7" id="{E2E660C3-4026-4C30-8E1C-1AF2F5F92AAE}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19584,7 +19570,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{59975C3A-4223-4CE0-8038-5D32E08A98B9}">
+          <x14:cfRule type="iconSet" priority="8" id="{E0A9B51C-F218-413D-8C20-BEBC8230F510}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19603,7 +19589,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{CE11DE5D-A395-4644-8D9D-E383834F7E5C}">
+          <x14:cfRule type="iconSet" priority="9" id="{FD5440B9-CA46-4DA8-A39C-F12AC44AA819}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19622,7 +19608,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{576CC250-B069-4F32-BBF6-BC3DEB209858}">
+          <x14:cfRule type="iconSet" priority="10" id="{7FC87CF6-ECF3-4685-88F0-AFECC952EAD0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19641,7 +19627,7 @@
           <xm:sqref>L120</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{3A556A54-E729-4680-981F-A79AA0EC35B6}">
+          <x14:cfRule type="iconSet" priority="11" id="{A6902FE6-485A-4BF1-B8BD-C5BF667FB670}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19660,7 +19646,7 @@
           <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{661BDEEE-76D7-4D63-9082-652AA6A41F36}">
+          <x14:cfRule type="iconSet" priority="12" id="{9BA0FFF1-3071-494A-84DD-A0C6673A2787}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19679,7 +19665,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{B6A057CD-A4E8-4D33-98F0-30B36BBA8635}">
+          <x14:cfRule type="iconSet" priority="13" id="{2FDF46DE-D1D6-4570-924C-F34BA043988F}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19698,7 +19684,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{506FBCC6-712D-484B-AF40-97589123C8BD}">
+          <x14:cfRule type="iconSet" priority="14" id="{59C1A77E-27A0-4E9E-9B2F-EE6B266AA079}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -19717,7 +19703,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{F2E8F3B5-D24A-47CC-98D7-8980DABC7D2C}">
+          <x14:cfRule type="iconSet" priority="15" id="{68309952-8824-4330-8ADC-291130E925A4}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23335,7 +23321,7 @@
       </c>
       <c r="O32" s="180" t="n">
         <f aca="false">SUM(O21:O30)</f>
-        <v>83060.1340815951</v>
+        <v>83060.1340815952</v>
       </c>
       <c r="P32" s="180"/>
       <c r="Q32" s="181" t="n">
@@ -23406,17 +23392,14 @@
       <c r="E36" s="192"/>
       <c r="F36" s="192"/>
       <c r="G36" s="213" t="n">
+        <f aca="false">H36/(1-'Datos Extra'!D1)</f>
+        <v>11782.8282828283</v>
+      </c>
+      <c r="H36" s="214" t="n">
         <f aca="false">'Datos Extra'!B1</f>
         <v>11665</v>
       </c>
-      <c r="H36" s="214" t="n">
-        <f aca="false">G36*(1-'Datos Extra'!D1)</f>
-        <v>11548.35</v>
-      </c>
-      <c r="I36" s="215" t="n">
-        <f aca="false">Flujos!G9</f>
-        <v>-34429.130716</v>
-      </c>
+      <c r="I36" s="0"/>
       <c r="J36" s="215" t="n">
         <f aca="false">'Mapa de Procesos'!L128</f>
         <v>-11044.0044054249</v>
@@ -23439,18 +23422,15 @@
       </c>
       <c r="E37" s="192"/>
       <c r="F37" s="192"/>
-      <c r="G37" s="216" t="n">
+      <c r="G37" s="213" t="n">
+        <f aca="false">H37/(1-'Datos Extra'!D2)</f>
+        <v>32544.0825238013</v>
+      </c>
+      <c r="H37" s="216" t="n">
         <f aca="false">'Datos Extra'!B2</f>
         <v>32218.6416985633</v>
       </c>
-      <c r="H37" s="217" t="n">
-        <f aca="false">G37*(1-'Datos Extra'!D2)</f>
-        <v>31896.4552815777</v>
-      </c>
-      <c r="I37" s="215" t="n">
-        <f aca="false">Flujos!G17</f>
-        <v>12216.727578</v>
-      </c>
+      <c r="I37" s="0"/>
       <c r="J37" s="215" t="n">
         <f aca="false">'Mapa de Procesos'!L129</f>
         <v>4812.96308026677</v>
@@ -23481,18 +23461,15 @@
       </c>
       <c r="E38" s="192"/>
       <c r="F38" s="192"/>
-      <c r="G38" s="216" t="n">
+      <c r="G38" s="213" t="n">
+        <f aca="false">H38/(1-'Datos Extra'!D3)</f>
+        <v>36.2411687464034</v>
+      </c>
+      <c r="H38" s="216" t="n">
         <f aca="false">'Datos Extra'!B3</f>
         <v>33</v>
       </c>
-      <c r="H38" s="217" t="n">
-        <f aca="false">G38*(1-'Datos Extra'!D3)</f>
-        <v>30.0486997982942</v>
-      </c>
-      <c r="I38" s="215" t="n">
-        <f aca="false">Flujos!G21</f>
-        <v>-5099</v>
-      </c>
+      <c r="I38" s="0"/>
       <c r="J38" s="215" t="n">
         <f aca="false">'Mapa de Procesos'!L131</f>
         <v>-3482.744475</v>
@@ -23501,21 +23478,21 @@
       <c r="L38" s="211" t="s">
         <v>92</v>
       </c>
-      <c r="M38" s="218" t="n">
+      <c r="M38" s="217" t="n">
         <f aca="false">G19+N22+N23+N24+N29+N30</f>
         <v>191432</v>
       </c>
-      <c r="N38" s="218" t="n">
+      <c r="N38" s="217" t="n">
         <f aca="false">G21+G22+G23+N19+G24</f>
         <v>217602.403138</v>
       </c>
-      <c r="O38" s="219" t="n">
+      <c r="O38" s="218" t="n">
         <f aca="false">I43</f>
-        <v>-24523.403138</v>
-      </c>
-      <c r="P38" s="218" t="n">
+        <v>289085.513060974</v>
+      </c>
+      <c r="P38" s="217" t="n">
         <f aca="false">M38-N38-O38</f>
-        <v>-1646.99999999999</v>
+        <v>-315255.916198974</v>
       </c>
       <c r="Q38" s="211"/>
       <c r="R38" s="146"/>
@@ -23529,18 +23506,15 @@
       </c>
       <c r="E39" s="192"/>
       <c r="F39" s="192"/>
-      <c r="G39" s="216" t="n">
+      <c r="G39" s="213" t="n">
+        <f aca="false">H39/(1-'Datos Extra'!D4)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="216" t="n">
         <f aca="false">'Datos Extra'!B4</f>
         <v>0</v>
       </c>
-      <c r="H39" s="217" t="n">
-        <f aca="false">G39*(1-'Datos Extra'!D4)</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="215" t="n">
-        <f aca="false">Flujos!G31</f>
-        <v>0</v>
-      </c>
+      <c r="I39" s="0"/>
       <c r="J39" s="215" t="n">
         <f aca="false">'Mapa de Procesos'!L132</f>
         <v>0</v>
@@ -23549,21 +23523,21 @@
       <c r="L39" s="211" t="s">
         <v>178</v>
       </c>
-      <c r="M39" s="218" t="n">
+      <c r="M39" s="217" t="n">
         <f aca="false">J19+Q22+Q23+Q24+Q29+Q30</f>
         <v>56987.5062</v>
       </c>
-      <c r="N39" s="218" t="n">
+      <c r="N39" s="217" t="n">
         <f aca="false">Q19+J21+J22+J23+J24</f>
         <v>66149.7313041496</v>
       </c>
-      <c r="O39" s="220" t="n">
+      <c r="O39" s="219" t="n">
         <f aca="false">J43</f>
         <v>-8126.56751018255</v>
       </c>
-      <c r="P39" s="218" t="n">
+      <c r="P39" s="217" t="n">
         <f aca="false">M39-N39-O39</f>
-        <v>-1035.65759396709</v>
+        <v>-1035.65759396704</v>
       </c>
       <c r="Q39" s="211"/>
       <c r="R39" s="206"/>
@@ -23577,24 +23551,21 @@
       </c>
       <c r="E40" s="192"/>
       <c r="F40" s="192"/>
-      <c r="G40" s="216" t="n">
+      <c r="G40" s="213" t="n">
+        <f aca="false">H40/(1-'Datos Extra'!D5)</f>
+        <v>119693.911085598</v>
+      </c>
+      <c r="H40" s="216" t="n">
         <f aca="false">'Datos Extra'!B5</f>
         <v>108658.53</v>
       </c>
-      <c r="H40" s="217" t="n">
-        <f aca="false">G40*(1-'Datos Extra'!D5)</f>
-        <v>98640.5744007939</v>
-      </c>
-      <c r="I40" s="215" t="n">
-        <f aca="false">Flujos!G26</f>
-        <v>-3438</v>
-      </c>
+      <c r="I40" s="0"/>
       <c r="J40" s="215" t="n">
         <f aca="false">'Mapa de Procesos'!L138</f>
         <v>-2349.68391</v>
       </c>
       <c r="K40" s="211"/>
-      <c r="L40" s="218"/>
+      <c r="L40" s="217"/>
       <c r="M40" s="211"/>
       <c r="N40" s="211"/>
       <c r="O40" s="211"/>
@@ -23611,129 +23582,123 @@
       </c>
       <c r="E41" s="192"/>
       <c r="F41" s="192"/>
-      <c r="G41" s="216" t="n">
+      <c r="G41" s="213" t="n">
+        <f aca="false">H41/(1-'Datos Extra'!D6)</f>
+        <v>60226.45</v>
+      </c>
+      <c r="H41" s="216" t="n">
         <f aca="false">'Datos Extra'!B6</f>
         <v>60226.45</v>
       </c>
-      <c r="H41" s="217" t="n">
-        <f aca="false">G41*(1-'Datos Extra'!D6)</f>
-        <v>60226.45</v>
-      </c>
-      <c r="I41" s="215" t="n">
-        <f aca="false">Flujos!G34</f>
-        <v>6226</v>
-      </c>
+      <c r="I41" s="0"/>
       <c r="J41" s="215" t="n">
         <f aca="false">'Mapa de Procesos'!L139</f>
         <v>3936.90219997558</v>
       </c>
-      <c r="L41" s="221"/>
+      <c r="L41" s="220"/>
       <c r="M41" s="186"/>
-      <c r="N41" s="221"/>
-      <c r="O41" s="221"/>
-      <c r="P41" s="221"/>
-      <c r="Q41" s="222"/>
+      <c r="N41" s="220"/>
+      <c r="O41" s="220"/>
+      <c r="P41" s="220"/>
+      <c r="Q41" s="221"/>
       <c r="R41" s="206"/>
       <c r="U41" s="212"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="152"/>
       <c r="C42" s="153"/>
-      <c r="D42" s="223" t="s">
+      <c r="D42" s="222" t="s">
         <v>202</v>
       </c>
-      <c r="E42" s="223"/>
-      <c r="F42" s="223"/>
-      <c r="G42" s="224" t="n">
+      <c r="E42" s="222"/>
+      <c r="F42" s="222"/>
+      <c r="G42" s="213" t="n">
+        <f aca="false">H42/(1-'Datos Extra'!D7)</f>
+        <v>64802</v>
+      </c>
+      <c r="H42" s="223" t="n">
         <f aca="false">'Datos Extra'!B7</f>
         <v>64802</v>
       </c>
-      <c r="H42" s="225" t="n">
-        <f aca="false">G42*(1-'Datos Extra'!D7)</f>
-        <v>64802</v>
-      </c>
-      <c r="I42" s="215" t="n">
-        <f aca="false">Flujos!G39</f>
-        <v>0</v>
-      </c>
+      <c r="I42" s="0"/>
       <c r="J42" s="215" t="n">
         <f aca="false">'Mapa de Procesos'!L140</f>
         <v>0</v>
       </c>
-      <c r="L42" s="222"/>
-      <c r="M42" s="222"/>
-      <c r="N42" s="222"/>
-      <c r="O42" s="222"/>
-      <c r="P42" s="222"/>
-      <c r="Q42" s="222"/>
+      <c r="L42" s="221"/>
+      <c r="M42" s="221"/>
+      <c r="N42" s="221"/>
+      <c r="O42" s="221"/>
+      <c r="P42" s="221"/>
+      <c r="Q42" s="221"/>
       <c r="R42" s="146"/>
       <c r="U42" s="212"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="226"/>
-      <c r="C43" s="227"/>
-      <c r="D43" s="223" t="s">
+      <c r="B43" s="224"/>
+      <c r="C43" s="225"/>
+      <c r="D43" s="222" t="s">
         <v>203</v>
       </c>
-      <c r="E43" s="223"/>
-      <c r="F43" s="223"/>
-      <c r="G43" s="224" t="n">
+      <c r="E43" s="222"/>
+      <c r="F43" s="222"/>
+      <c r="G43" s="223" t="n">
         <f aca="false">'Datos Extra'!B8</f>
         <v>71110.9575524111</v>
       </c>
-      <c r="H43" s="225" t="n">
+      <c r="H43" s="226" t="n">
         <f aca="false">G43*(1-'Datos Extra'!D8)</f>
         <v>70399.847976887</v>
       </c>
-      <c r="I43" s="228" t="n">
-        <f aca="false">SUM(I36:I42)</f>
-        <v>-24523.403138</v>
-      </c>
-      <c r="J43" s="228" t="n">
+      <c r="I43" s="227" t="n">
+        <f aca="false">SUM(G36:G42)</f>
+        <v>289085.513060974</v>
+      </c>
+      <c r="J43" s="227" t="n">
         <f aca="false">SUM(J36:J42)</f>
         <v>-8126.56751018255</v>
       </c>
-      <c r="K43" s="227"/>
-      <c r="L43" s="227"/>
-      <c r="M43" s="227"/>
-      <c r="N43" s="227"/>
-      <c r="O43" s="227"/>
-      <c r="P43" s="227"/>
-      <c r="Q43" s="227"/>
-      <c r="R43" s="229"/>
+      <c r="K43" s="225"/>
+      <c r="L43" s="225"/>
+      <c r="M43" s="225"/>
+      <c r="N43" s="225"/>
+      <c r="O43" s="225"/>
+      <c r="P43" s="225"/>
+      <c r="Q43" s="225"/>
+      <c r="R43" s="228"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E46" s="230"/>
-      <c r="F46" s="230"/>
-      <c r="G46" s="230"/>
-      <c r="H46" s="230"/>
-      <c r="I46" s="231"/>
-      <c r="J46" s="231"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
+      <c r="G46" s="229"/>
+      <c r="H46" s="229"/>
+      <c r="I46" s="230"/>
+      <c r="J46" s="230"/>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E47" s="230"/>
-      <c r="F47" s="230"/>
-      <c r="G47" s="230"/>
-      <c r="H47" s="230"/>
-      <c r="I47" s="231"/>
-      <c r="J47" s="231"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
+      <c r="G47" s="229"/>
+      <c r="H47" s="229"/>
+      <c r="I47" s="230"/>
+      <c r="J47" s="230"/>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E48" s="232"/>
-      <c r="F48" s="232"/>
-      <c r="G48" s="232"/>
-      <c r="H48" s="232"/>
-      <c r="I48" s="232"/>
-      <c r="J48" s="232"/>
-      <c r="K48" s="232"/>
+      <c r="E48" s="231"/>
+      <c r="F48" s="231"/>
+      <c r="G48" s="231"/>
+      <c r="H48" s="231"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="231"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E49" s="233"/>
-      <c r="F49" s="233"/>
-      <c r="G49" s="233"/>
-      <c r="H49" s="234"/>
+      <c r="E49" s="232"/>
+      <c r="F49" s="232"/>
+      <c r="G49" s="232"/>
+      <c r="H49" s="233"/>
       <c r="I49" s="203"/>
-      <c r="J49" s="235"/>
+      <c r="J49" s="234"/>
       <c r="K49" s="169"/>
     </row>
   </sheetData>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="205">
   <si>
     <t xml:space="preserve">BALANCE METALÚRGICO - VALLE ELQUI</t>
   </si>
@@ -785,6 +785,9 @@
     <t xml:space="preserve">Delta Preconcentrado Ventas</t>
   </si>
   <si>
+    <t xml:space="preserve">Premixto PL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cristales</t>
   </si>
   <si>
@@ -912,6 +915,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rec Rsguardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rec Premixto PL</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL ENTRADAS</t>
@@ -1569,7 +1575,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="232">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2416,6 +2422,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2625,9 +2635,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>440640</xdr:colOff>
+      <xdr:colOff>440280</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>187200</xdr:rowOff>
+      <xdr:rowOff>186840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2641,7 +2651,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="716760" y="438480"/>
-          <a:ext cx="945000" cy="510840"/>
+          <a:ext cx="944640" cy="510480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2668,9 +2678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>223560</xdr:colOff>
+      <xdr:colOff>223200</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>106560</xdr:rowOff>
+      <xdr:rowOff>106200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2680,7 +2690,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4093200" y="1426320"/>
-          <a:ext cx="1050840" cy="394920"/>
+          <a:ext cx="1050480" cy="394560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2747,9 +2757,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>647640</xdr:colOff>
+      <xdr:colOff>647280</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2759,7 +2769,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7032600" y="2008080"/>
-          <a:ext cx="499680" cy="378000"/>
+          <a:ext cx="499320" cy="377640"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -2800,9 +2810,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>379080</xdr:colOff>
+      <xdr:colOff>378720</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>68400</xdr:rowOff>
+      <xdr:rowOff>68040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2812,7 +2822,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6328800" y="1703520"/>
-          <a:ext cx="934920" cy="460440"/>
+          <a:ext cx="934560" cy="460080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2876,9 +2886,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>95040</xdr:colOff>
+      <xdr:colOff>94680</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2888,7 +2898,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10133280" y="3195720"/>
-          <a:ext cx="1193040" cy="327240"/>
+          <a:ext cx="1192680" cy="326880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2952,9 +2962,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>409320</xdr:colOff>
+      <xdr:colOff>408960</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>66600</xdr:rowOff>
+      <xdr:rowOff>66240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2964,7 +2974,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7525440" y="6415920"/>
-          <a:ext cx="645480" cy="508680"/>
+          <a:ext cx="645120" cy="508320"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3005,9 +3015,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>76320</xdr:colOff>
+      <xdr:colOff>75960</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>24120</xdr:rowOff>
+      <xdr:rowOff>23760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3017,7 +3027,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6535800" y="8088840"/>
-          <a:ext cx="1302120" cy="507960"/>
+          <a:ext cx="1301760" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3081,9 +3091,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>717840</xdr:colOff>
+      <xdr:colOff>717480</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>136440</xdr:rowOff>
+      <xdr:rowOff>136080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3093,7 +3103,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7239960" y="10028520"/>
-          <a:ext cx="1239480" cy="394920"/>
+          <a:ext cx="1239120" cy="394560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3160,9 +3170,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>625320</xdr:colOff>
+      <xdr:colOff>624960</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>59760</xdr:rowOff>
+      <xdr:rowOff>59400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3172,7 +3182,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9572760" y="11553120"/>
-          <a:ext cx="576360" cy="508320"/>
+          <a:ext cx="576000" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3213,9 +3223,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>698760</xdr:colOff>
+      <xdr:colOff>698400</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>6120</xdr:rowOff>
+      <xdr:rowOff>5760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3225,7 +3235,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9934560" y="11643120"/>
-          <a:ext cx="1047960" cy="364680"/>
+          <a:ext cx="1047600" cy="364320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3289,9 +3299,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>655200</xdr:colOff>
+      <xdr:colOff>654840</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>69120</xdr:rowOff>
+      <xdr:rowOff>68760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3301,7 +3311,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9602640" y="12899160"/>
-          <a:ext cx="576360" cy="505080"/>
+          <a:ext cx="576000" cy="504720"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3342,9 +3352,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>461520</xdr:colOff>
+      <xdr:colOff>461160</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3354,7 +3364,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9697320" y="12543120"/>
-          <a:ext cx="1047960" cy="504720"/>
+          <a:ext cx="1047600" cy="504360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3418,9 +3428,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>491040</xdr:colOff>
+      <xdr:colOff>490680</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>29880</xdr:rowOff>
+      <xdr:rowOff>29520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3430,7 +3440,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12092040" y="11523240"/>
-          <a:ext cx="2511360" cy="508320"/>
+          <a:ext cx="2511000" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3494,9 +3504,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>110880</xdr:colOff>
+      <xdr:colOff>110520</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>1440</xdr:rowOff>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3506,7 +3516,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12144240" y="12256920"/>
-          <a:ext cx="2893680" cy="507960"/>
+          <a:ext cx="2893320" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3570,9 +3580,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>491040</xdr:colOff>
+      <xdr:colOff>490680</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>151200</xdr:rowOff>
+      <xdr:rowOff>150840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3582,7 +3592,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12092040" y="12977640"/>
-          <a:ext cx="2511360" cy="508680"/>
+          <a:ext cx="2511000" cy="508320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3646,9 +3656,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>6120</xdr:colOff>
+      <xdr:colOff>5760</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>105840</xdr:rowOff>
+      <xdr:rowOff>105480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3658,7 +3668,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9715680" y="15218280"/>
-          <a:ext cx="574200" cy="508680"/>
+          <a:ext cx="573840" cy="508320"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3699,9 +3709,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>729720</xdr:colOff>
+      <xdr:colOff>729360</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>163440</xdr:rowOff>
+      <xdr:rowOff>163080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3711,7 +3721,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10067400" y="15276240"/>
-          <a:ext cx="946080" cy="508320"/>
+          <a:ext cx="945720" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3775,9 +3785,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>603720</xdr:colOff>
+      <xdr:colOff>603360</xdr:colOff>
       <xdr:row>83</xdr:row>
-      <xdr:rowOff>13320</xdr:rowOff>
+      <xdr:rowOff>12960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3787,7 +3797,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12204720" y="15316560"/>
-          <a:ext cx="2511360" cy="508320"/>
+          <a:ext cx="2511000" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3851,9 +3861,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>577800</xdr:colOff>
+      <xdr:colOff>577440</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>118440</xdr:rowOff>
+      <xdr:rowOff>118080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3863,7 +3873,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5277960" y="4117680"/>
-          <a:ext cx="220320" cy="191880"/>
+          <a:ext cx="219960" cy="191520"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -3943,9 +3953,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>643320</xdr:colOff>
+      <xdr:colOff>642960</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>91080</xdr:rowOff>
+      <xdr:rowOff>90720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3955,7 +3965,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2747520" y="11114640"/>
-          <a:ext cx="1366200" cy="406440"/>
+          <a:ext cx="1365840" cy="406080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4019,9 +4029,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
+      <xdr:colOff>12600</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>142920</xdr:rowOff>
+      <xdr:rowOff>142560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4031,7 +4041,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2658960" y="666720"/>
-          <a:ext cx="1514520" cy="238320"/>
+          <a:ext cx="1514160" cy="237960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4134,9 +4144,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>683280</xdr:colOff>
+      <xdr:colOff>682920</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>100080</xdr:rowOff>
+      <xdr:rowOff>99720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4146,7 +4156,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2762640" y="2258640"/>
-          <a:ext cx="576360" cy="508320"/>
+          <a:ext cx="576000" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4187,9 +4197,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>162360</xdr:colOff>
+      <xdr:colOff>162000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>77400</xdr:rowOff>
+      <xdr:rowOff>77040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4199,7 +4209,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2031480" y="2628360"/>
-          <a:ext cx="786600" cy="306720"/>
+          <a:ext cx="786240" cy="306360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4263,9 +4273,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>669960</xdr:colOff>
+      <xdr:colOff>669600</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>176760</xdr:rowOff>
+      <xdr:rowOff>176400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4275,7 +4285,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="323280" y="2157120"/>
-          <a:ext cx="558000" cy="305640"/>
+          <a:ext cx="557640" cy="305280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4417,9 +4427,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>122400</xdr:colOff>
+      <xdr:colOff>122040</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>102240</xdr:rowOff>
+      <xdr:rowOff>101880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4429,7 +4439,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1205280" y="3620160"/>
-          <a:ext cx="1572840" cy="291960"/>
+          <a:ext cx="1572480" cy="291600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4608,9 +4618,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>713160</xdr:colOff>
+      <xdr:colOff>712800</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>111600</xdr:rowOff>
+      <xdr:rowOff>111240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4620,7 +4630,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4069080" y="2381040"/>
-          <a:ext cx="804600" cy="207000"/>
+          <a:ext cx="804240" cy="206640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4723,9 +4733,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>239040</xdr:colOff>
+      <xdr:colOff>238680</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>32400</xdr:rowOff>
+      <xdr:rowOff>32040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4735,7 +4745,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3080520" y="4476600"/>
-          <a:ext cx="628920" cy="508680"/>
+          <a:ext cx="628560" cy="508320"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4776,9 +4786,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>714960</xdr:colOff>
+      <xdr:colOff>714600</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>37440</xdr:rowOff>
+      <xdr:rowOff>37080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4788,7 +4798,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2379960" y="4873680"/>
-          <a:ext cx="990720" cy="307440"/>
+          <a:ext cx="990360" cy="307080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4852,9 +4862,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>214920</xdr:colOff>
+      <xdr:colOff>214560</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>178200</xdr:rowOff>
+      <xdr:rowOff>177840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4864,7 +4874,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1979640" y="4444560"/>
-          <a:ext cx="891000" cy="305640"/>
+          <a:ext cx="890640" cy="305280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5006,9 +5016,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>142920</xdr:colOff>
+      <xdr:colOff>142560</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>128520</xdr:rowOff>
+      <xdr:rowOff>128160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5018,7 +5028,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3537000" y="4389480"/>
-          <a:ext cx="766440" cy="311040"/>
+          <a:ext cx="766080" cy="310680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5082,9 +5092,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>256680</xdr:colOff>
+      <xdr:colOff>256320</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>182160</xdr:rowOff>
+      <xdr:rowOff>181800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5094,7 +5104,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3098160" y="6150960"/>
-          <a:ext cx="628920" cy="508320"/>
+          <a:ext cx="628560" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5135,9 +5145,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>669960</xdr:colOff>
+      <xdr:colOff>669600</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5147,7 +5157,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2337840" y="6646320"/>
-          <a:ext cx="987840" cy="419760"/>
+          <a:ext cx="987480" cy="419400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5289,9 +5299,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>363960</xdr:colOff>
+      <xdr:colOff>363600</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>47520</xdr:rowOff>
+      <xdr:rowOff>47160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5301,7 +5311,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3375000" y="5895000"/>
-          <a:ext cx="1149480" cy="439200"/>
+          <a:ext cx="1149120" cy="438840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5365,9 +5375,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>10440</xdr:colOff>
+      <xdr:colOff>10080</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>73080</xdr:rowOff>
+      <xdr:rowOff>72720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5377,7 +5387,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2113560" y="6151320"/>
-          <a:ext cx="552600" cy="208440"/>
+          <a:ext cx="552240" cy="208080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5480,9 +5490,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>264600</xdr:colOff>
+      <xdr:colOff>264240</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>23760</xdr:rowOff>
+      <xdr:rowOff>23400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5492,7 +5502,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3106080" y="7897680"/>
-          <a:ext cx="628920" cy="507960"/>
+          <a:ext cx="628560" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5533,9 +5543,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>744840</xdr:colOff>
+      <xdr:colOff>744480</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>145800</xdr:rowOff>
+      <xdr:rowOff>145440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5545,7 +5555,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2308680" y="8422560"/>
-          <a:ext cx="1091880" cy="295920"/>
+          <a:ext cx="1091520" cy="295560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5648,9 +5658,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>289440</xdr:colOff>
+      <xdr:colOff>289080</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>85680</xdr:rowOff>
+      <xdr:rowOff>85320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5660,7 +5670,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3390480" y="7627320"/>
-          <a:ext cx="1059480" cy="459360"/>
+          <a:ext cx="1059120" cy="459000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5724,9 +5734,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>18720</xdr:colOff>
+      <xdr:colOff>18360</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>91080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5736,7 +5746,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2121840" y="7761600"/>
-          <a:ext cx="552600" cy="330840"/>
+          <a:ext cx="552240" cy="330480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5839,9 +5849,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>213480</xdr:colOff>
+      <xdr:colOff>213120</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>43920</xdr:rowOff>
+      <xdr:rowOff>43560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5851,7 +5861,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3054960" y="9816480"/>
-          <a:ext cx="628920" cy="514440"/>
+          <a:ext cx="628560" cy="514080"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5892,9 +5902,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>656640</xdr:colOff>
+      <xdr:colOff>656280</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>93240</xdr:rowOff>
+      <xdr:rowOff>92880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5904,7 +5914,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2683800" y="10378800"/>
-          <a:ext cx="1443240" cy="191880"/>
+          <a:ext cx="1442880" cy="191520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6007,9 +6017,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>416160</xdr:colOff>
+      <xdr:colOff>415800</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>166680</xdr:rowOff>
+      <xdr:rowOff>166320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6019,7 +6029,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3511440" y="9511560"/>
-          <a:ext cx="1065240" cy="561240"/>
+          <a:ext cx="1064880" cy="560880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6083,9 +6093,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>118800</xdr:colOff>
+      <xdr:colOff>118440</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>97200</xdr:rowOff>
+      <xdr:rowOff>96840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6095,7 +6105,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1936080" y="9604080"/>
-          <a:ext cx="838440" cy="208800"/>
+          <a:ext cx="838080" cy="208440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6315,9 +6325,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>727560</xdr:colOff>
+      <xdr:colOff>727200</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:rowOff>93960</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6327,9 +6337,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="9675000" y="3014640"/>
-          <a:ext cx="576360" cy="508680"/>
+          <a:ext cx="576000" cy="508320"/>
           <a:chOff x="9675000" y="3014640"/>
-          <a:chExt cx="576360" cy="508680"/>
+          <a:chExt cx="576000" cy="508320"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6340,7 +6350,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9675000" y="3014640"/>
-            <a:ext cx="576360" cy="508680"/>
+            <a:ext cx="576000" cy="508320"/>
           </a:xfrm>
           <a:prstGeom prst="triangle">
             <a:avLst>
@@ -6378,7 +6388,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9892080" y="3105720"/>
-            <a:ext cx="142560" cy="118080"/>
+            <a:ext cx="142200" cy="117720"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6411,7 +6421,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9964440" y="3247920"/>
-            <a:ext cx="142560" cy="118080"/>
+            <a:ext cx="142200" cy="117720"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6444,7 +6454,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10036440" y="3372840"/>
-            <a:ext cx="142560" cy="118080"/>
+            <a:ext cx="142200" cy="117720"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6481,9 +6491,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>534960</xdr:colOff>
+      <xdr:colOff>534600</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>16200</xdr:rowOff>
+      <xdr:rowOff>15840</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6493,9 +6503,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="10456200" y="1526400"/>
-          <a:ext cx="1310040" cy="394920"/>
+          <a:ext cx="1309680" cy="394560"/>
           <a:chOff x="10456200" y="1526400"/>
-          <a:chExt cx="1310040" cy="394920"/>
+          <a:chExt cx="1309680" cy="394560"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6506,7 +6516,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10456200" y="1526400"/>
-            <a:ext cx="1310040" cy="394920"/>
+            <a:ext cx="1309680" cy="394560"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6570,7 +6580,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="11439000" y="1801440"/>
-            <a:ext cx="165960" cy="118080"/>
+            <a:ext cx="165600" cy="117720"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6683,9 +6693,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>932400</xdr:colOff>
+      <xdr:colOff>932040</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>65880</xdr:rowOff>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6695,7 +6705,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11943720" y="1746720"/>
-          <a:ext cx="1034640" cy="414720"/>
+          <a:ext cx="1034280" cy="414360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6805,9 +6815,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>796320</xdr:colOff>
+      <xdr:colOff>795960</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>171360</xdr:rowOff>
+      <xdr:rowOff>171000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6817,7 +6827,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11890800" y="1023480"/>
-          <a:ext cx="951480" cy="481320"/>
+          <a:ext cx="951120" cy="480960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6927,9 +6937,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>683280</xdr:colOff>
+      <xdr:colOff>682920</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>164880</xdr:rowOff>
+      <xdr:rowOff>164520</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6939,9 +6949,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="7205400" y="4346280"/>
-          <a:ext cx="1239480" cy="390600"/>
+          <a:ext cx="1239120" cy="390240"/>
           <a:chOff x="7205400" y="4346280"/>
-          <a:chExt cx="1239480" cy="390600"/>
+          <a:chExt cx="1239120" cy="390240"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6952,7 +6962,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="7205400" y="4347360"/>
-            <a:ext cx="1239480" cy="389520"/>
+            <a:ext cx="1239120" cy="389160"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7016,7 +7026,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="8280000" y="4346280"/>
-            <a:ext cx="156960" cy="116640"/>
+            <a:ext cx="156600" cy="116280"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -7131,9 +7141,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>220680</xdr:colOff>
+      <xdr:colOff>220320</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>6120</xdr:rowOff>
+      <xdr:rowOff>5760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7143,7 +7153,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9765000" y="4384440"/>
-          <a:ext cx="739440" cy="193680"/>
+          <a:ext cx="739080" cy="193320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7207,9 +7217,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>149760</xdr:colOff>
+      <xdr:colOff>149400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7219,7 +7229,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10794240" y="4584960"/>
-          <a:ext cx="1401480" cy="310680"/>
+          <a:ext cx="1401120" cy="310320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7283,9 +7293,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>259200</xdr:colOff>
+      <xdr:colOff>258840</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7295,7 +7305,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9444600" y="992520"/>
-          <a:ext cx="1098360" cy="305280"/>
+          <a:ext cx="1098000" cy="304920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7359,9 +7369,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>318600</xdr:colOff>
+      <xdr:colOff>318240</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>131400</xdr:rowOff>
+      <xdr:rowOff>131040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7371,7 +7381,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5599800" y="4970160"/>
-          <a:ext cx="1603440" cy="304920"/>
+          <a:ext cx="1603080" cy="304560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7612,9 +7622,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>307800</xdr:colOff>
+      <xdr:colOff>307440</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>72720</xdr:rowOff>
+      <xdr:rowOff>72360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7624,7 +7634,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6005160" y="8893080"/>
-          <a:ext cx="1187280" cy="514080"/>
+          <a:ext cx="1186920" cy="513720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7734,9 +7744,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>507960</xdr:colOff>
+      <xdr:colOff>507600</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>90720</xdr:rowOff>
+      <xdr:rowOff>90360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7746,7 +7756,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8929080" y="8911080"/>
-          <a:ext cx="1102680" cy="514080"/>
+          <a:ext cx="1102320" cy="513720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7893,9 +7903,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>80280</xdr:colOff>
+      <xdr:colOff>79920</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>162360</xdr:rowOff>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7905,7 +7915,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8493840" y="10322280"/>
-          <a:ext cx="1110240" cy="507960"/>
+          <a:ext cx="1109880" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8047,9 +8057,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>646200</xdr:colOff>
+      <xdr:colOff>645840</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>113040</xdr:rowOff>
+      <xdr:rowOff>112680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8059,7 +8069,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7144920" y="10947960"/>
-          <a:ext cx="1262880" cy="404640"/>
+          <a:ext cx="1262520" cy="404280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8192,9 +8202,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>597240</xdr:colOff>
+      <xdr:colOff>596880</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>74880</xdr:rowOff>
+      <xdr:rowOff>74520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8204,7 +8214,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6905520" y="12901320"/>
-          <a:ext cx="576360" cy="508680"/>
+          <a:ext cx="576000" cy="508320"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -8245,9 +8255,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>577800</xdr:colOff>
+      <xdr:colOff>577440</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:rowOff>54720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8257,7 +8267,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275160" y="12501000"/>
-          <a:ext cx="1187280" cy="507960"/>
+          <a:ext cx="1186920" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8477,9 +8487,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>752400</xdr:colOff>
+      <xdr:colOff>752040</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>145800</xdr:rowOff>
+      <xdr:rowOff>145440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8489,7 +8499,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3934800" y="12781800"/>
-          <a:ext cx="978120" cy="508680"/>
+          <a:ext cx="977760" cy="508320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8553,9 +8563,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>752040</xdr:colOff>
+      <xdr:colOff>751680</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:rowOff>172080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8565,7 +8575,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3934440" y="13570920"/>
-          <a:ext cx="978120" cy="507960"/>
+          <a:ext cx="977760" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8668,9 +8678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>30960</xdr:colOff>
+      <xdr:colOff>30600</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>183600</xdr:rowOff>
+      <xdr:rowOff>183240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8680,7 +8690,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5558400" y="14147280"/>
-          <a:ext cx="1357200" cy="514440"/>
+          <a:ext cx="1356840" cy="514080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8783,9 +8793,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>715320</xdr:colOff>
+      <xdr:colOff>714960</xdr:colOff>
       <xdr:row>79</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:rowOff>172080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8795,7 +8805,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6545520" y="14851440"/>
-          <a:ext cx="1054440" cy="370440"/>
+          <a:ext cx="1054080" cy="370080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8898,9 +8908,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>712080</xdr:colOff>
+      <xdr:colOff>711720</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>41400</xdr:rowOff>
+      <xdr:rowOff>41040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8910,7 +8920,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6343560" y="15667200"/>
-          <a:ext cx="1253160" cy="376200"/>
+          <a:ext cx="1252800" cy="375840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9013,9 +9023,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>16920</xdr:colOff>
+      <xdr:colOff>16560</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9025,7 +9035,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6410160" y="16366680"/>
-          <a:ext cx="1368360" cy="376920"/>
+          <a:ext cx="1368000" cy="376560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9167,9 +9177,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>33120</xdr:colOff>
+      <xdr:colOff>32760</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>64440</xdr:rowOff>
+      <xdr:rowOff>64080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9179,7 +9189,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12515040" y="14033880"/>
-          <a:ext cx="2445120" cy="508680"/>
+          <a:ext cx="2444760" cy="508320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9294,9 +9304,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>928080</xdr:colOff>
+      <xdr:colOff>927720</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:rowOff>180360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9306,7 +9316,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7634880" y="14465160"/>
-          <a:ext cx="1054800" cy="384120"/>
+          <a:ext cx="1054440" cy="383760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17609,7 +17619,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:Q71"/>
+  <dimension ref="B2:Q72"/>
   <sheetFormatPr defaultColWidth="10.4453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="16.67"/>
@@ -20406,15 +20416,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B72" s="151" t="s">
+        <v>152</v>
+      </c>
+      <c r="C72" s="155" t="n">
+        <f aca="false">Utilidad!A69</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="156" t="n">
+        <f aca="false">IF(Utilidad!C69&gt;1,Utilidad!C69/100,Utilidad!C69)</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="151" t="s">
+        <v>152</v>
+      </c>
+      <c r="G72" s="155" t="n">
+        <f aca="false">Utilidad!B69</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="163" t="n">
+        <f aca="false">IF(Utilidad!D69&gt;1,Utilidad!D69/100,Utilidad!D69)</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="160" t="n">
+        <f aca="false">+IF(C72&lt;&gt;0,(G72-C72)/C72,ABS(G72-C72))</f>
+        <v>0</v>
+      </c>
+      <c r="K72" s="160" t="n">
+        <f aca="false">+IF(D72&lt;&gt;0,(H72-D72)/D72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M72" s="162" t="n">
+        <f aca="false">+IF(J72&lt;&gt;"",ABS(J72),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N72" s="162" t="n">
+        <f aca="false">+IF(J72&lt;&gt;"",ABS(K72),0)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="J2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="L4:L5 J4:K71">
+  <conditionalFormatting sqref="L4:L5 J4:K70 J72:K72">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>ABS(J4)&gt;=10%</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J71:K72">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>ABS(J71)&gt;=10%</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -21157,7 +21212,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="126" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L65" s="175" t="n">
         <f aca="false">Flujos!G25</f>
@@ -21176,7 +21231,7 @@
         <v>2106</v>
       </c>
       <c r="G66" s="126" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L66" s="177" t="n">
         <f aca="false">Flujos!H25</f>
@@ -21191,7 +21246,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="126" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L67" s="178" t="n">
         <f aca="false">L66*L65</f>
@@ -21498,7 +21553,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G95" s="199" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21508,7 +21563,7 @@
       <c r="H96" s="200"/>
       <c r="I96" s="200"/>
       <c r="J96" s="201" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K96" s="201"/>
       <c r="L96" s="201"/>
@@ -21521,7 +21576,7 @@
     </row>
     <row r="97" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G97" s="203" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H97" s="203"/>
       <c r="I97" s="204" t="n">
@@ -21537,7 +21592,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="207" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N97" s="207"/>
       <c r="O97" s="207"/>
@@ -21548,7 +21603,7 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G98" s="203" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H98" s="203"/>
       <c r="I98" s="204" t="n">
@@ -21575,7 +21630,7 @@
     </row>
     <row r="99" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G99" s="203" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H99" s="203"/>
       <c r="I99" s="204" t="n">
@@ -21583,7 +21638,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="207" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K99" s="207"/>
       <c r="L99" s="206" t="n">
@@ -21601,7 +21656,7 @@
     </row>
     <row r="100" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G100" s="208" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H100" s="208"/>
       <c r="I100" s="204" t="n">
@@ -21609,7 +21664,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="207" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K100" s="207"/>
       <c r="L100" s="206" t="n">
@@ -21617,7 +21672,7 @@
         <v>-5362</v>
       </c>
       <c r="M100" s="207" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N100" s="207"/>
       <c r="O100" s="207"/>
@@ -21636,7 +21691,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="207" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K101" s="207"/>
       <c r="L101" s="206" t="n">
@@ -21644,7 +21699,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="207" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N101" s="207"/>
       <c r="O101" s="207"/>
@@ -21663,7 +21718,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="207" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K102" s="207"/>
       <c r="L102" s="206" t="n">
@@ -21682,7 +21737,7 @@
     </row>
     <row r="103" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G103" s="208" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H103" s="208"/>
       <c r="I103" s="204" t="n">
@@ -21690,7 +21745,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="207" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K103" s="207"/>
       <c r="L103" s="206" t="n">
@@ -21698,7 +21753,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="207" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N103" s="207"/>
       <c r="O103" s="207"/>
@@ -21709,7 +21764,7 @@
     </row>
     <row r="104" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G104" s="208" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H104" s="208"/>
       <c r="I104" s="204" t="n">
@@ -21717,7 +21772,7 @@
         <v>41596</v>
       </c>
       <c r="J104" s="207" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K104" s="207"/>
       <c r="L104" s="206" t="n">
@@ -21725,7 +21780,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="207" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N104" s="207"/>
       <c r="O104" s="207"/>
@@ -21736,7 +21791,7 @@
     </row>
     <row r="105" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G105" s="208" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H105" s="208"/>
       <c r="I105" s="204" t="n">
@@ -21744,7 +21799,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="207" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K105" s="207"/>
       <c r="L105" s="206" t="n">
@@ -21763,7 +21818,7 @@
     </row>
     <row r="106" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G106" s="208" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H106" s="208"/>
       <c r="I106" s="204" t="n">
@@ -21771,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="207" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K106" s="207"/>
       <c r="L106" s="206" t="n">
@@ -21790,7 +21845,7 @@
     </row>
     <row r="107" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G107" s="209" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H107" s="210"/>
       <c r="I107" s="204" t="n">
@@ -21798,7 +21853,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="207" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K107" s="207"/>
       <c r="L107" s="206" t="n">
@@ -21806,7 +21861,7 @@
         <v>66433</v>
       </c>
       <c r="M107" s="207" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N107" s="207"/>
       <c r="O107" s="207"/>
@@ -21814,7 +21869,7 @@
     </row>
     <row r="108" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G108" s="209" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H108" s="210"/>
       <c r="I108" s="204" t="n">
@@ -21822,7 +21877,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="207" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K108" s="207"/>
       <c r="L108" s="206" t="n">
@@ -21836,7 +21891,7 @@
     </row>
     <row r="109" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G109" s="209" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H109" s="210"/>
       <c r="I109" s="204" t="n">
@@ -21844,7 +21899,7 @@
         <v>1632</v>
       </c>
       <c r="J109" s="207" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K109" s="207"/>
       <c r="L109" s="206" t="n">
@@ -21858,7 +21913,7 @@
     </row>
     <row r="110" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G110" s="208" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H110" s="208"/>
       <c r="I110" s="204" t="n">
@@ -21866,7 +21921,7 @@
         <v>-1632</v>
       </c>
       <c r="J110" s="207" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K110" s="207"/>
       <c r="L110" s="206" t="n">
@@ -21880,7 +21935,7 @@
     </row>
     <row r="111" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G111" s="208" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H111" s="208"/>
       <c r="I111" s="204" t="n">
@@ -21897,7 +21952,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G112" s="208" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H112" s="208" t="s">
         <v>144</v>
@@ -21916,7 +21971,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G113" s="208" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H113" s="208" t="s">
         <v>145</v>
@@ -21935,7 +21990,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G114" s="208" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H114" s="208" t="s">
         <v>146</v>
@@ -21954,7 +22009,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G115" s="208" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H115" s="208"/>
       <c r="I115" s="204" t="n">
@@ -21971,7 +22026,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G116" s="208" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H116" s="208"/>
       <c r="I116" s="204" t="n">
@@ -21988,15 +22043,15 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G117" s="209" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H117" s="210"/>
       <c r="I117" s="204" t="n">
         <f aca="false">Flujos!G67</f>
         <v>0</v>
       </c>
-      <c r="J117" s="207"/>
-      <c r="K117" s="207"/>
+      <c r="J117" s="212"/>
+      <c r="K117" s="212"/>
       <c r="L117" s="206"/>
       <c r="M117" s="207"/>
       <c r="N117" s="207"/>
@@ -22005,15 +22060,15 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G118" s="209" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H118" s="210"/>
       <c r="I118" s="204" t="n">
         <f aca="false">Flujos!G70</f>
         <v>392</v>
       </c>
-      <c r="J118" s="207"/>
-      <c r="K118" s="207"/>
+      <c r="J118" s="212"/>
+      <c r="K118" s="212"/>
       <c r="L118" s="206"/>
       <c r="M118" s="207"/>
       <c r="N118" s="207"/>
@@ -22021,9 +22076,14 @@
       <c r="P118" s="206"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G119" s="208"/>
-      <c r="H119" s="208"/>
-      <c r="I119" s="204"/>
+      <c r="G119" s="209" t="s">
+        <v>196</v>
+      </c>
+      <c r="H119" s="210"/>
+      <c r="I119" s="204" t="n">
+        <f aca="false">Flujos!G72</f>
+        <v>0</v>
+      </c>
       <c r="J119" s="207"/>
       <c r="K119" s="207"/>
       <c r="L119" s="206"/>
@@ -22033,88 +22093,97 @@
       <c r="P119" s="206"/>
     </row>
     <row r="120" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G120" s="212" t="s">
-        <v>195</v>
-      </c>
-      <c r="H120" s="212"/>
-      <c r="I120" s="213" t="n">
+      <c r="G120" s="0"/>
+      <c r="H120" s="0"/>
+      <c r="I120" s="0"/>
+      <c r="J120" s="0"/>
+      <c r="K120" s="0"/>
+      <c r="M120" s="0"/>
+      <c r="N120" s="0"/>
+      <c r="P120" s="0"/>
+    </row>
+    <row r="121" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G121" s="213" t="s">
+        <v>197</v>
+      </c>
+      <c r="H121" s="213"/>
+      <c r="I121" s="214" t="n">
         <f aca="false">+SUM(I97:I119)</f>
         <v>171270</v>
       </c>
-      <c r="J120" s="214" t="s">
-        <v>196</v>
-      </c>
-      <c r="K120" s="214"/>
-      <c r="L120" s="215" t="n">
+      <c r="J121" s="215" t="s">
+        <v>198</v>
+      </c>
+      <c r="K121" s="215"/>
+      <c r="L121" s="216" t="n">
         <f aca="false">+SUM(L97:L110)</f>
         <v>68383</v>
       </c>
-      <c r="M120" s="214" t="s">
-        <v>197</v>
-      </c>
-      <c r="N120" s="214"/>
-      <c r="O120" s="214"/>
-      <c r="P120" s="213" t="n">
+      <c r="M121" s="215" t="s">
+        <v>199</v>
+      </c>
+      <c r="N121" s="215"/>
+      <c r="O121" s="215"/>
+      <c r="P121" s="214" t="n">
         <f aca="false">+SUM(P97:P110)</f>
         <v>108912</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G121" s="216"/>
-      <c r="H121" s="216"/>
-      <c r="I121" s="216"/>
-      <c r="J121" s="216"/>
-      <c r="K121" s="216"/>
-      <c r="L121" s="216"/>
-      <c r="M121" s="216"/>
-      <c r="N121" s="216"/>
-      <c r="O121" s="216"/>
-      <c r="P121" s="216"/>
-    </row>
     <row r="122" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G122" s="216"/>
-      <c r="J122" s="216"/>
-      <c r="K122" s="216"/>
-      <c r="L122" s="217" t="s">
-        <v>198</v>
-      </c>
-      <c r="M122" s="218"/>
-      <c r="N122" s="219"/>
-      <c r="O122" s="218"/>
-      <c r="P122" s="220" t="n">
-        <f aca="false">+I120-L120-P120</f>
+      <c r="G122" s="217"/>
+      <c r="H122" s="217"/>
+      <c r="I122" s="217"/>
+      <c r="J122" s="217"/>
+      <c r="K122" s="217"/>
+      <c r="L122" s="217"/>
+      <c r="M122" s="217"/>
+      <c r="N122" s="217"/>
+      <c r="O122" s="217"/>
+      <c r="P122" s="217"/>
+    </row>
+    <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G123" s="217"/>
+      <c r="J123" s="217"/>
+      <c r="K123" s="217"/>
+      <c r="L123" s="218" t="s">
+        <v>200</v>
+      </c>
+      <c r="M123" s="219"/>
+      <c r="N123" s="220"/>
+      <c r="O123" s="219"/>
+      <c r="P123" s="221" t="n">
+        <f aca="false">+I121-L121-P121</f>
         <v>-6025</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="124" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="125" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="126" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G126" s="199" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G127" s="221" t="s">
+      <c r="G127" s="222" t="s">
         <v>10</v>
       </c>
-      <c r="H127" s="221"/>
-      <c r="I127" s="221"/>
-      <c r="J127" s="222" t="s">
-        <v>156</v>
-      </c>
-      <c r="K127" s="222"/>
-      <c r="L127" s="222"/>
-      <c r="M127" s="223" t="s">
+      <c r="H127" s="222"/>
+      <c r="I127" s="222"/>
+      <c r="J127" s="223" t="s">
+        <v>157</v>
+      </c>
+      <c r="K127" s="223"/>
+      <c r="L127" s="223"/>
+      <c r="M127" s="224" t="s">
         <v>47</v>
       </c>
-      <c r="N127" s="223"/>
-      <c r="O127" s="223"/>
-      <c r="P127" s="223"/>
+      <c r="N127" s="224"/>
+      <c r="O127" s="224"/>
+      <c r="P127" s="224"/>
     </row>
     <row r="128" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G128" s="203" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H128" s="203"/>
       <c r="I128" s="204" t="n">
@@ -22130,7 +22199,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="207" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N128" s="207"/>
       <c r="O128" s="207"/>
@@ -22140,10 +22209,10 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G129" s="224" t="s">
-        <v>159</v>
-      </c>
-      <c r="H129" s="225"/>
+      <c r="G129" s="225" t="s">
+        <v>160</v>
+      </c>
+      <c r="H129" s="226"/>
       <c r="I129" s="204" t="n">
         <f aca="false">+C14</f>
         <v>0</v>
@@ -22167,16 +22236,16 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G130" s="224" t="s">
-        <v>160</v>
-      </c>
-      <c r="H130" s="226"/>
+      <c r="G130" s="225" t="s">
+        <v>161</v>
+      </c>
+      <c r="H130" s="227"/>
       <c r="I130" s="204" t="n">
         <f aca="false">+H15</f>
         <v>0</v>
       </c>
       <c r="J130" s="207" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K130" s="207"/>
       <c r="L130" s="206" t="n">
@@ -22194,7 +22263,7 @@
     </row>
     <row r="131" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G131" s="209" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H131" s="210"/>
       <c r="I131" s="204" t="n">
@@ -22202,7 +22271,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="207" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K131" s="207"/>
       <c r="L131" s="206" t="n">
@@ -22210,7 +22279,7 @@
         <v>-3439.82088845752</v>
       </c>
       <c r="M131" s="207" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N131" s="207"/>
       <c r="O131" s="207"/>
@@ -22229,7 +22298,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="207" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K132" s="207"/>
       <c r="L132" s="206" t="n">
@@ -22237,7 +22306,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="207" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N132" s="207"/>
       <c r="O132" s="207"/>
@@ -22256,7 +22325,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="207" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K133" s="207"/>
       <c r="L133" s="206" t="n">
@@ -22275,7 +22344,7 @@
     </row>
     <row r="134" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G134" s="209" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H134" s="210"/>
       <c r="I134" s="204" t="n">
@@ -22283,7 +22352,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="207" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K134" s="207"/>
       <c r="L134" s="206" t="n">
@@ -22291,7 +22360,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="207" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N134" s="207"/>
       <c r="O134" s="207"/>
@@ -22302,7 +22371,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G135" s="209" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H135" s="210"/>
       <c r="I135" s="204" t="n">
@@ -22310,7 +22379,7 @@
         <v>18830.5092</v>
       </c>
       <c r="J135" s="207" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K135" s="207"/>
       <c r="L135" s="206" t="n">
@@ -22318,7 +22387,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="207" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N135" s="207"/>
       <c r="O135" s="207"/>
@@ -22329,7 +22398,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G136" s="209" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H136" s="210"/>
       <c r="I136" s="204" t="n">
@@ -22337,7 +22406,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="207" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K136" s="207"/>
       <c r="L136" s="206" t="n">
@@ -22356,7 +22425,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G137" s="209" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H137" s="210"/>
       <c r="I137" s="204" t="n">
@@ -22364,7 +22433,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="207" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K137" s="207"/>
       <c r="L137" s="206" t="n">
@@ -22383,7 +22452,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G138" s="209" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H138" s="210"/>
       <c r="I138" s="204" t="n">
@@ -22391,7 +22460,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="207" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K138" s="207"/>
       <c r="L138" s="206" t="n">
@@ -22399,7 +22468,7 @@
         <v>44164.5778393582</v>
       </c>
       <c r="M138" s="207" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N138" s="207"/>
       <c r="O138" s="207"/>
@@ -22410,7 +22479,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G139" s="209" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H139" s="210"/>
       <c r="I139" s="204" t="n">
@@ -22418,7 +22487,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="207" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K139" s="207"/>
       <c r="L139" s="206" t="n">
@@ -22432,7 +22501,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G140" s="209" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H140" s="210"/>
       <c r="I140" s="204" t="n">
@@ -22440,21 +22509,21 @@
         <v>951.6192</v>
       </c>
       <c r="J140" s="207" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K140" s="207"/>
       <c r="L140" s="206" t="n">
         <f aca="false">Flujos!G39*Flujos!H39</f>
         <v>-951.6192</v>
       </c>
-      <c r="M140" s="227"/>
-      <c r="N140" s="228"/>
-      <c r="O140" s="229"/>
+      <c r="M140" s="228"/>
+      <c r="N140" s="229"/>
+      <c r="O140" s="230"/>
       <c r="P140" s="206"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G141" s="209" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H141" s="210"/>
       <c r="I141" s="204" t="n">
@@ -22462,7 +22531,7 @@
         <v>-951.6192</v>
       </c>
       <c r="J141" s="207" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K141" s="207"/>
       <c r="L141" s="206" t="n">
@@ -22476,7 +22545,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G142" s="208" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H142" s="208"/>
       <c r="I142" s="204" t="n">
@@ -22490,7 +22559,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G143" s="208" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H143" s="208"/>
       <c r="I143" s="204" t="n">
@@ -22500,14 +22569,14 @@
       <c r="J143" s="207"/>
       <c r="K143" s="207"/>
       <c r="L143" s="206"/>
-      <c r="M143" s="230"/>
-      <c r="N143" s="230"/>
-      <c r="O143" s="230"/>
+      <c r="M143" s="231"/>
+      <c r="N143" s="231"/>
+      <c r="O143" s="231"/>
       <c r="P143" s="206"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G144" s="208" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H144" s="208"/>
       <c r="I144" s="204" t="n">
@@ -22517,14 +22586,14 @@
       <c r="J144" s="207"/>
       <c r="K144" s="207"/>
       <c r="L144" s="206"/>
-      <c r="M144" s="230"/>
-      <c r="N144" s="230"/>
-      <c r="O144" s="230"/>
+      <c r="M144" s="231"/>
+      <c r="N144" s="231"/>
+      <c r="O144" s="231"/>
       <c r="P144" s="206"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G145" s="208" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H145" s="208"/>
       <c r="I145" s="204" t="n">
@@ -22534,14 +22603,14 @@
       <c r="J145" s="207"/>
       <c r="K145" s="207"/>
       <c r="L145" s="206"/>
-      <c r="M145" s="230"/>
-      <c r="N145" s="230"/>
-      <c r="O145" s="230"/>
+      <c r="M145" s="231"/>
+      <c r="N145" s="231"/>
+      <c r="O145" s="231"/>
       <c r="P145" s="206"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G146" s="208" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H146" s="208"/>
       <c r="I146" s="204" t="n">
@@ -22551,14 +22620,14 @@
       <c r="J146" s="207"/>
       <c r="K146" s="207"/>
       <c r="L146" s="206"/>
-      <c r="M146" s="230"/>
-      <c r="N146" s="230"/>
-      <c r="O146" s="230"/>
+      <c r="M146" s="231"/>
+      <c r="N146" s="231"/>
+      <c r="O146" s="231"/>
       <c r="P146" s="206"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G147" s="208" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H147" s="208"/>
       <c r="I147" s="204" t="n">
@@ -22575,7 +22644,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G148" s="209" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H148" s="210"/>
       <c r="I148" s="204" t="n">
@@ -22592,7 +22661,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G149" s="209" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H149" s="210"/>
       <c r="I149" s="204" t="n">
@@ -22608,9 +22677,14 @@
       <c r="P149" s="206"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G150" s="208"/>
-      <c r="H150" s="208"/>
-      <c r="I150" s="204"/>
+      <c r="G150" s="209" t="s">
+        <v>195</v>
+      </c>
+      <c r="H150" s="210"/>
+      <c r="I150" s="204" t="n">
+        <f aca="false">Flujos!G72*Flujos!H72</f>
+        <v>0</v>
+      </c>
       <c r="J150" s="207"/>
       <c r="K150" s="207"/>
       <c r="L150" s="206"/>
@@ -22620,61 +22694,61 @@
       <c r="P150" s="206"/>
     </row>
     <row r="151" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G151" s="212" t="s">
-        <v>195</v>
-      </c>
-      <c r="H151" s="212"/>
-      <c r="I151" s="213" t="n">
+      <c r="G151" s="213" t="s">
+        <v>197</v>
+      </c>
+      <c r="H151" s="213"/>
+      <c r="I151" s="214" t="n">
         <f aca="false">+SUM(I128:I150)</f>
         <v>59602.6644799715</v>
       </c>
-      <c r="J151" s="214" t="s">
-        <v>196</v>
-      </c>
-      <c r="K151" s="214"/>
-      <c r="L151" s="215" t="n">
+      <c r="J151" s="215" t="s">
+        <v>198</v>
+      </c>
+      <c r="K151" s="215"/>
+      <c r="L151" s="216" t="n">
         <f aca="false">+SUM(L128:L141)</f>
         <v>45350.9504846625</v>
       </c>
-      <c r="M151" s="214" t="s">
-        <v>197</v>
-      </c>
-      <c r="N151" s="214"/>
-      <c r="O151" s="214"/>
-      <c r="P151" s="213" t="n">
+      <c r="M151" s="215" t="s">
+        <v>199</v>
+      </c>
+      <c r="N151" s="215"/>
+      <c r="O151" s="215"/>
+      <c r="P151" s="214" t="n">
         <f aca="false">+SUM(P128:P141)</f>
         <v>16489.0254945414</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G152" s="216"/>
-      <c r="H152" s="216"/>
-      <c r="I152" s="216"/>
-      <c r="J152" s="216"/>
-      <c r="K152" s="216"/>
-      <c r="L152" s="216"/>
-      <c r="M152" s="216"/>
-      <c r="N152" s="216"/>
-      <c r="O152" s="216"/>
-      <c r="P152" s="216"/>
+      <c r="G152" s="217"/>
+      <c r="H152" s="217"/>
+      <c r="I152" s="217"/>
+      <c r="J152" s="217"/>
+      <c r="K152" s="217"/>
+      <c r="L152" s="217"/>
+      <c r="M152" s="217"/>
+      <c r="N152" s="217"/>
+      <c r="O152" s="217"/>
+      <c r="P152" s="217"/>
     </row>
     <row r="153" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G153" s="216"/>
-      <c r="J153" s="216"/>
-      <c r="K153" s="216"/>
-      <c r="L153" s="217" t="s">
-        <v>198</v>
-      </c>
-      <c r="M153" s="218"/>
-      <c r="N153" s="219"/>
-      <c r="O153" s="218"/>
-      <c r="P153" s="220" t="n">
+      <c r="G153" s="217"/>
+      <c r="J153" s="217"/>
+      <c r="K153" s="217"/>
+      <c r="L153" s="218" t="s">
+        <v>200</v>
+      </c>
+      <c r="M153" s="219"/>
+      <c r="N153" s="220"/>
+      <c r="O153" s="219"/>
+      <c r="P153" s="221" t="n">
         <f aca="false">+I151-L151-P151</f>
-        <v>-2237.31149923233</v>
+        <v>-2237.3114992324</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="88">
+  <mergeCells count="86">
     <mergeCell ref="G96:I96"/>
     <mergeCell ref="J96:L96"/>
     <mergeCell ref="M96:P96"/>
@@ -22730,12 +22804,11 @@
     <mergeCell ref="G116:H116"/>
     <mergeCell ref="J116:K116"/>
     <mergeCell ref="M116:O116"/>
-    <mergeCell ref="G119:H119"/>
     <mergeCell ref="J119:K119"/>
     <mergeCell ref="M119:O119"/>
-    <mergeCell ref="G120:H120"/>
-    <mergeCell ref="J120:K120"/>
-    <mergeCell ref="M120:O120"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="J121:K121"/>
+    <mergeCell ref="M121:O121"/>
     <mergeCell ref="G127:I127"/>
     <mergeCell ref="J127:L127"/>
     <mergeCell ref="M127:P127"/>
@@ -22757,7 +22830,6 @@
     <mergeCell ref="G147:H147"/>
     <mergeCell ref="J149:K149"/>
     <mergeCell ref="M149:O149"/>
-    <mergeCell ref="G150:H150"/>
     <mergeCell ref="J150:K150"/>
     <mergeCell ref="M150:O150"/>
     <mergeCell ref="G151:H151"/>
@@ -22776,7 +22848,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{D23FCD54-B5E6-449F-98C2-6719472BE0B0}">
+          <x14:cfRule type="iconSet" priority="2" id="{1540C97C-D484-42F0-B390-541565331370}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22795,7 +22867,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{91FD8199-38F8-4B24-8B30-1FC070CAE07A}">
+          <x14:cfRule type="iconSet" priority="3" id="{CD44E68F-D072-45FB-B7E2-10D781FE48E6}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22814,7 +22886,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{10F9B0EC-4069-4750-92A8-B71BD01848A1}">
+          <x14:cfRule type="iconSet" priority="4" id="{B2789339-9D20-4ED5-AD6A-134334DFC781}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22833,7 +22905,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{F62014E3-2990-4CBF-9BD4-7D388A406763}">
+          <x14:cfRule type="iconSet" priority="5" id="{21F0D6A6-107E-449F-912A-2BB7C59EC64A}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22852,7 +22924,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{FAB750E3-50FC-4C4C-A54E-9F3B77843C3A}">
+          <x14:cfRule type="iconSet" priority="6" id="{63CDCCB5-AE7A-4F72-9A7E-3353F6D129DA}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22871,7 +22943,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{F3236CB3-AE11-414A-807B-BC298543CD81}">
+          <x14:cfRule type="iconSet" priority="7" id="{DD8EFDBD-A890-4F93-A4C9-BB856DE2E1CA}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22890,7 +22962,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{F07E701A-7F2E-488A-B124-74594EE48FFE}">
+          <x14:cfRule type="iconSet" priority="8" id="{C350D5EB-CE57-4FD8-B87E-5EDC6B185DD3}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22909,7 +22981,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{AACA9B42-11E9-4D57-A05D-3517E180B9F8}">
+          <x14:cfRule type="iconSet" priority="9" id="{2B17E6C8-5E20-4D50-AAA3-5AED1E776916}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22928,26 +23000,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{6B13DBD0-5767-4EF2-9864-2EDCBE7D311C}">
-            <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
-              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
-              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L120</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{FF751C78-4E32-4BE0-B0DC-753AF182C192}">
+          <x14:cfRule type="iconSet" priority="10" id="{3AF7197D-A68F-4649-A1BE-B6ABFD1D1FF4}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22966,7 +23019,7 @@
           <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{A9EAC011-991C-4AC2-BFB5-F42B3C13A8AE}">
+          <x14:cfRule type="iconSet" priority="11" id="{8DBEA9BE-2C42-466C-8A69-318DDB564CC5}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22985,7 +23038,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{CC745037-DC86-46C6-9A93-9DBDC61B7186}">
+          <x14:cfRule type="iconSet" priority="12" id="{71A2E8B4-1FDA-41DF-91C6-538FCB4E6F33}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23004,7 +23057,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{82B09221-10FD-4BDD-9796-E0C0544440AC}">
+          <x14:cfRule type="iconSet" priority="13" id="{4095FB1C-C0AC-4BA0-A617-C8DF665354D7}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23023,7 +23076,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{80BAEB8B-D19C-40BB-A4E2-815C993F13A0}">
+          <x14:cfRule type="iconSet" priority="14" id="{4C60B51A-D08C-446B-8760-46A568BFCF60}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23040,6 +23093,25 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>N88</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="15" id="{6A727339-6FC8-4EFE-9E58-DE615E2034EC}">
+            <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3Triangles" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L122</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" state="visible" r:id="rId3"/>
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="209">
   <si>
     <t xml:space="preserve">BALANCE METALÚRGICO - VALLE ELQUI</t>
   </si>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">Sinter Feed Caro</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconcentrado ventas</t>
+    <t xml:space="preserve">Recepción Preconcentra ventas</t>
   </si>
   <si>
     <t xml:space="preserve">SF SERCOOP</t>
@@ -696,6 +696,12 @@
   </si>
   <si>
     <t xml:space="preserve">SERCOOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embarque Preconcentrado Ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humedad delta stock ventas</t>
   </si>
   <si>
     <t xml:space="preserve">Mediciones</t>
@@ -779,7 +785,53 @@
     <t xml:space="preserve">GR PLEITO</t>
   </si>
   <si>
-    <t xml:space="preserve">Embarque Preconcentrado ventas</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Embarque </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Preconcentrado Ventas</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepción Preconcentrado ventas</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Recepción</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Preconcentrado ventas</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Delta Preconcentrado Ventas</t>
@@ -948,7 +1000,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0\ %"/>
@@ -963,8 +1015,9 @@
     <numFmt numFmtId="175" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
     <numFmt numFmtId="176" formatCode="#,##0.0000000_ ;\-#,##0.0000000\ "/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="0.00\ %"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1126,6 +1179,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -1575,7 +1635,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="233">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2084,6 +2144,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2096,11 +2160,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2108,7 +2172,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2120,11 +2184,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2132,19 +2192,19 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2152,11 +2212,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2248,6 +2304,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2268,59 +2332,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2328,19 +2392,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2348,7 +2412,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2356,7 +2420,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2372,7 +2436,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2380,7 +2444,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="16" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="16" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2440,7 +2504,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2448,7 +2512,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2468,7 +2532,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="29" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2480,7 +2544,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13085,7 +13149,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="50" t="n">
-        <f aca="false">G25/(1-'Datos Extra'!D28)</f>
+        <f aca="false">G25/(1-'Datos Extra'!D41)</f>
         <v>0</v>
       </c>
       <c r="I25" s="59" t="n">
@@ -13320,7 +13384,7 @@
       </c>
       <c r="I32" s="65"/>
       <c r="J32" s="44" t="n">
-        <f aca="false">+SUM(J21:J24)</f>
+        <f aca="false">+SUM(J21:J25)</f>
         <v>4044.8296</v>
       </c>
       <c r="K32" s="43" t="s">
@@ -16912,456 +16976,456 @@
   <sheetFormatPr defaultColWidth="10.4453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="126" width="58.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="126" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="127" width="16.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="127" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="128" width="16.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="126" width="23.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="129" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="129" t="n">
+      <c r="B1" s="130" t="n">
         <v>42771.7642067606</v>
       </c>
-      <c r="C1" s="130" t="n">
+      <c r="C1" s="131" t="n">
         <v>0.297016214982546</v>
       </c>
-      <c r="D1" s="131" t="n">
+      <c r="D1" s="132" t="n">
         <v>0.00329756078931775</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="128" t="s">
+      <c r="A2" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="129" t="n">
+      <c r="B2" s="130" t="n">
         <v>18443.7340071012</v>
       </c>
-      <c r="C2" s="130" t="n">
+      <c r="C2" s="131" t="n">
         <v>0.443385257607103</v>
       </c>
-      <c r="D2" s="131" t="n">
+      <c r="D2" s="132" t="n">
         <v>0.0353904039421967</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="128" t="s">
+      <c r="A3" s="129" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="129" t="n">
+      <c r="B3" s="130" t="n">
         <v>27.2735561007429</v>
       </c>
-      <c r="C3" s="130" t="n">
+      <c r="C3" s="131" t="n">
         <v>0.6457015434965</v>
       </c>
-      <c r="D3" s="131" t="n">
+      <c r="D3" s="132" t="n">
         <v>0.0908814633085687</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="128" t="s">
+      <c r="A4" s="129" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="131" t="n">
+      <c r="B4" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="132" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="129" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="129" t="n">
+      <c r="B5" s="130" t="n">
         <v>103000.636528879</v>
       </c>
-      <c r="C5" s="130" t="n">
+      <c r="C5" s="131" t="n">
         <v>0.646534362331</v>
       </c>
-      <c r="D5" s="131" t="n">
+      <c r="D5" s="132" t="n">
         <v>0.0868543088723792</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="128" t="s">
+      <c r="A6" s="129" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="129" t="n">
+      <c r="B6" s="130" t="n">
         <v>44282.0034194924</v>
       </c>
-      <c r="C6" s="130" t="n">
+      <c r="C6" s="131" t="n">
         <v>0.634567521724109</v>
       </c>
-      <c r="D6" s="131" t="n">
+      <c r="D6" s="132" t="n">
         <v>0.0103007780791007</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="129" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>447.344048308247</v>
       </c>
-      <c r="C7" s="130" t="n">
+      <c r="C7" s="131" t="n">
         <v>0.634567521724109</v>
       </c>
-      <c r="D7" s="130" t="n">
+      <c r="D7" s="131" t="n">
         <v>0.0103007780791007</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="128" t="s">
+      <c r="A8" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>44739.1544280445</v>
       </c>
-      <c r="C8" s="130" t="n">
+      <c r="C8" s="131" t="n">
         <v>0.560701247601677</v>
       </c>
-      <c r="D8" s="130" t="n">
+      <c r="D8" s="131" t="n">
         <v>0.0265642785844565</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="128" t="s">
+      <c r="A9" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="129" t="n">
+      <c r="B9" s="130" t="n">
         <v>67297.4996785832</v>
       </c>
-      <c r="C9" s="133" t="n">
+      <c r="C9" s="134" t="n">
         <v>0.6457015434965</v>
       </c>
-      <c r="D9" s="130" t="n">
+      <c r="D9" s="131" t="n">
         <v>0.0908814633085687</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="128" t="s">
+      <c r="A10" s="129" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="130" t="n">
+      <c r="B10" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="128" t="s">
+      <c r="A11" s="129" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="130" t="n">
+      <c r="B11" s="130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="128" t="s">
+      <c r="A12" s="129" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="129" t="n">
+      <c r="B12" s="130" t="n">
         <v>5026.20372049881</v>
       </c>
-      <c r="C12" s="133" t="n">
+      <c r="C12" s="134" t="n">
         <v>0.637061157842015</v>
       </c>
-      <c r="D12" s="130" t="n">
+      <c r="D12" s="131" t="n">
         <v>0.00842122821785252</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="128" t="s">
+      <c r="A13" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="130" t="n">
+      <c r="B13" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="132" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="130" t="n">
+      <c r="B14" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="128" t="s">
+      <c r="A15" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="132" t="n">
+      <c r="B15" s="133" t="n">
         <v>122150.389294902</v>
       </c>
-      <c r="C15" s="130" t="n">
+      <c r="C15" s="131" t="n">
         <v>0.303910902116075</v>
       </c>
-      <c r="D15" s="130" t="n">
+      <c r="D15" s="131" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="134" t="s">
+      <c r="A16" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="136" t="n">
+      <c r="B16" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="137" t="n">
         <v>0.6457015434965</v>
       </c>
-      <c r="D16" s="130" t="n">
+      <c r="D16" s="131" t="n">
         <v>0.0908814633085687</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="134" t="s">
+      <c r="A17" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="137" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="135" t="n">
+      <c r="B17" s="138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="137" t="n">
+      <c r="B18" s="138" t="n">
         <v>122150.389294902</v>
       </c>
       <c r="C18" s="137" t="n">
         <v>0.303910902116075</v>
       </c>
-      <c r="D18" s="140" t="n">
+      <c r="D18" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="139" t="s">
+      <c r="A19" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="137" t="n">
+      <c r="B19" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="140" t="n">
+      <c r="D19" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="140" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="137" t="n">
+      <c r="B20" s="138" t="n">
         <v>3530.47586486667</v>
       </c>
       <c r="C20" s="137" t="n">
         <v>0.238767740156197</v>
       </c>
-      <c r="D20" s="140" t="n">
+      <c r="D20" s="139" t="n">
         <v>0.00329756078931775</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="139" t="s">
+      <c r="A21" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="137" t="n">
+      <c r="B21" s="138" t="n">
         <v>41596.0816080799</v>
       </c>
       <c r="C21" s="137" t="n">
         <v>0.452727832091303</v>
       </c>
-      <c r="D21" s="140" t="n">
+      <c r="D21" s="139" t="n">
         <v>0.0224600639983852</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="139" t="s">
+      <c r="A22" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="137" t="n">
+      <c r="B22" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="140" t="n">
+      <c r="D22" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="139" t="s">
+      <c r="A23" s="140" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="137" t="n">
+      <c r="B23" s="138" t="n">
         <v>4771.816</v>
       </c>
       <c r="C23" s="137" t="n">
         <v>0.6482</v>
       </c>
-      <c r="D23" s="140" t="n">
+      <c r="D23" s="139" t="n">
         <v>0.0788</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="139" t="s">
+      <c r="A24" s="140" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="137" t="n">
+      <c r="B24" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="140" t="n">
+      <c r="D24" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="139" t="s">
+      <c r="A25" s="140" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="137" t="n">
+      <c r="B25" s="138" t="n">
         <v>1632.13313151707</v>
       </c>
       <c r="C25" s="137" t="n">
         <v>0.583099731976602</v>
       </c>
-      <c r="D25" s="140" t="n">
+      <c r="D25" s="139" t="n">
         <v>0.0054033324088515</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="139" t="s">
+      <c r="A26" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="137" t="n">
+      <c r="B26" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="140" t="n">
+      <c r="D26" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="139" t="s">
+      <c r="A27" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="137" t="n">
+      <c r="B27" s="138" t="n">
         <v>44739.1544280445</v>
       </c>
       <c r="C27" s="137" t="n">
         <v>0.6457015434965</v>
       </c>
-      <c r="D27" s="140" t="n">
+      <c r="D27" s="139" t="n">
         <v>0.0908814633085687</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="139" t="s">
+      <c r="A28" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="137" t="n">
+      <c r="B28" s="138" t="n">
         <v>67297.4996785832</v>
       </c>
       <c r="C28" s="137" t="n">
         <v>0.6457015434965</v>
       </c>
-      <c r="D28" s="140" t="n">
+      <c r="D28" s="139" t="n">
         <v>0.0908814633085687</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="139" t="s">
+      <c r="A29" s="140" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="137" t="n">
+      <c r="B29" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="140" t="n">
+      <c r="D29" s="139" t="n">
         <v>0.0908814633085687</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="139" t="s">
+      <c r="A30" s="140" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="137" t="n">
+      <c r="B30" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="140" t="n">
+      <c r="D30" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="139" t="s">
+      <c r="A31" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="137" t="n">
+      <c r="B31" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="137" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="140" t="n">
+      <c r="D31" s="139" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="140" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="137" t="n">
+      <c r="B32" s="138" t="n">
         <v>5068.89</v>
       </c>
       <c r="C32" s="137" t="n">
         <v>0.637061157842015</v>
       </c>
-      <c r="D32" s="140" t="n">
+      <c r="D32" s="139" t="n">
         <v>0.00842122821785252</v>
       </c>
     </row>
@@ -17369,13 +17433,13 @@
       <c r="A33" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="137" t="n">
+      <c r="B33" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="142" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="140" t="n">
+      <c r="D33" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17383,13 +17447,13 @@
       <c r="A34" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="137" t="n">
+      <c r="B34" s="138" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="142" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="140" t="n">
+      <c r="D34" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17397,13 +17461,13 @@
       <c r="A35" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="137" t="n">
+      <c r="B35" s="138" t="n">
         <v>26963.3892949017</v>
       </c>
       <c r="C35" s="142" t="n">
         <v>0.12055134529148</v>
       </c>
-      <c r="D35" s="140" t="n">
+      <c r="D35" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17411,13 +17475,13 @@
       <c r="A36" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="137" t="n">
+      <c r="B36" s="138" t="n">
         <v>32912</v>
       </c>
       <c r="C36" s="142" t="n">
         <v>0.158896657977879</v>
       </c>
-      <c r="D36" s="140" t="n">
+      <c r="D36" s="139" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="143"/>
@@ -17426,13 +17490,13 @@
       <c r="A37" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="137" t="n">
+      <c r="B37" s="138" t="n">
         <v>15308</v>
       </c>
       <c r="C37" s="142" t="n">
         <v>0.082754873268879</v>
       </c>
-      <c r="D37" s="140" t="n">
+      <c r="D37" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17440,13 +17504,13 @@
       <c r="A38" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="137" t="n">
+      <c r="B38" s="138" t="n">
         <v>46064</v>
       </c>
       <c r="C38" s="142" t="n">
         <v>0.09333</v>
       </c>
-      <c r="D38" s="140" t="n">
+      <c r="D38" s="139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17454,13 +17518,13 @@
       <c r="A39" s="143" t="s">
         <v>116</v>
       </c>
-      <c r="B39" s="135" t="n">
+      <c r="B39" s="136" t="n">
         <v>5026.20372049881</v>
       </c>
-      <c r="C39" s="140" t="n">
+      <c r="C39" s="139" t="n">
         <v>0.637061157842015</v>
       </c>
-      <c r="D39" s="140" t="n">
+      <c r="D39" s="139" t="n">
         <v>0.00842122821785252</v>
       </c>
     </row>
@@ -17468,13 +17532,13 @@
       <c r="A40" s="143" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="135" t="n">
+      <c r="B40" s="136" t="n">
         <v>2106.4266687</v>
       </c>
-      <c r="C40" s="140" t="n">
+      <c r="C40" s="139" t="n">
         <v>0.632073885606203</v>
       </c>
-      <c r="D40" s="140" t="n">
+      <c r="D40" s="139" t="n">
         <v>0.0121803279403489</v>
       </c>
     </row>
@@ -17482,13 +17546,13 @@
       <c r="A41" s="143" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="144" t="n">
+      <c r="B41" s="133" t="n">
         <v>2054.77679255</v>
       </c>
-      <c r="C41" s="130" t="n">
+      <c r="C41" s="131" t="n">
         <v>0.560701247601677</v>
       </c>
-      <c r="D41" s="145" t="n">
+      <c r="D41" s="144" t="n">
         <v>0.0265642785844565</v>
       </c>
     </row>
@@ -17496,27 +17560,27 @@
       <c r="A42" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="145" t="n">
+      <c r="B42" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="144" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="139" t="s">
+      <c r="A43" s="140" t="s">
         <v>120</v>
       </c>
-      <c r="B43" s="135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="145" t="n">
+      <c r="B43" s="136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17524,13 +17588,13 @@
       <c r="A44" s="143" t="s">
         <v>121</v>
       </c>
-      <c r="B44" s="135" t="n">
+      <c r="B44" s="136" t="n">
         <v>391.648416866667</v>
       </c>
-      <c r="C44" s="130" t="n">
+      <c r="C44" s="131" t="n">
         <v>0.525252850899185</v>
       </c>
-      <c r="D44" s="145" t="n">
+      <c r="D44" s="144" t="n">
         <v>0.0181297210522797</v>
       </c>
     </row>
@@ -17538,18 +17602,44 @@
       <c r="A45" s="143" t="s">
         <v>122</v>
       </c>
-      <c r="B45" s="135" t="n">
+      <c r="B45" s="136" t="n">
         <v>1001</v>
       </c>
-      <c r="C45" s="130" t="n">
+      <c r="C45" s="131" t="n">
         <v>0.61</v>
       </c>
-      <c r="D45" s="145" t="n">
+      <c r="D45" s="144" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="143" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="133" t="n">
+        <v>2054.77679255</v>
+      </c>
+      <c r="C46" s="131" t="n">
+        <v>0.560701247601677</v>
+      </c>
+      <c r="D46" s="144" t="n">
+        <v>0.0265642785844565</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="143" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="144" t="n">
+        <v>0.0265642785844565</v>
+      </c>
+    </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -17631,295 +17721,295 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="146" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="F2" s="146" t="s">
-        <v>124</v>
-      </c>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="J2" s="147" t="s">
+      <c r="B2" s="145" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="147"/>
-      <c r="L2" s="148"/>
-      <c r="M2" s="149" t="s">
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="F2" s="145" t="s">
         <v>126</v>
       </c>
-      <c r="N2" s="150" t="s">
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="J2" s="146" t="s">
         <v>127</v>
       </c>
+      <c r="K2" s="146"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="148" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="149" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="151" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" s="151" t="s">
+      <c r="B3" s="150" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="151" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="151" t="s">
-        <v>128</v>
-      </c>
-      <c r="G3" s="151" t="s">
+      <c r="D3" s="150" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="150" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="151" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="152" t="s">
-        <v>130</v>
-      </c>
-      <c r="K3" s="152" t="s">
+      <c r="H3" s="150" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="153"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="154"/>
+      <c r="J3" s="151" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="151" t="s">
+        <v>133</v>
+      </c>
+      <c r="L3" s="152"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="153"/>
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="151" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="155" t="n">
+      <c r="B4" s="150" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="154" t="n">
         <f aca="false">Utilidad!A1</f>
         <v>122150</v>
       </c>
-      <c r="D4" s="156" t="n">
+      <c r="D4" s="155" t="n">
         <f aca="false">IF(Utilidad!C1&gt;1,Utilidad!C1/100,Utilidad!C1)</f>
         <v>0.3039</v>
       </c>
-      <c r="F4" s="157" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="158" t="n">
+      <c r="F4" s="156" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="157" t="n">
         <f aca="false">Utilidad!B1</f>
         <v>122150</v>
       </c>
-      <c r="H4" s="159" t="n">
+      <c r="H4" s="158" t="n">
         <f aca="false">IF(Utilidad!D1&gt;1,Utilidad!D1/100,Utilidad!D1)</f>
         <v>0.29498952501</v>
       </c>
-      <c r="J4" s="160" t="n">
+      <c r="J4" s="159" t="n">
         <f aca="false">+IF(C4&lt;&gt;0,(G4-C4)/C4,ABS(G4-C4))</f>
         <v>0</v>
       </c>
-      <c r="K4" s="160" t="n">
+      <c r="K4" s="159" t="n">
         <f aca="false">+IF(D4&lt;&gt;0,(H4-D4)/D4,0)</f>
         <v>-0.0293204178677196</v>
       </c>
-      <c r="L4" s="161"/>
-      <c r="M4" s="162" t="n">
+      <c r="L4" s="160"/>
+      <c r="M4" s="161" t="n">
         <f aca="false">+IF(J4&lt;&gt;"",ABS(J4),0)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="162" t="n">
+      <c r="N4" s="161" t="n">
         <f aca="false">+IF(J4&lt;&gt;"",ABS(K4),0)</f>
         <v>0.0293204178677196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="151" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="155" t="n">
+      <c r="B5" s="150" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="154" t="n">
         <f aca="false">Utilidad!A2</f>
         <v>0</v>
       </c>
-      <c r="D5" s="156" t="n">
+      <c r="D5" s="155" t="n">
         <f aca="false">IF(Utilidad!C2&gt;1,Utilidad!C2/100,Utilidad!C2)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="157" t="s">
-        <v>133</v>
-      </c>
-      <c r="G5" s="158" t="n">
+      <c r="F5" s="156" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="157" t="n">
         <f aca="false">Utilidad!B2</f>
         <v>0</v>
       </c>
-      <c r="H5" s="159" t="n">
+      <c r="H5" s="158" t="n">
         <f aca="false">IF(Utilidad!D2&gt;1,Utilidad!D2/100,Utilidad!D2)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="160" t="n">
+      <c r="J5" s="159" t="n">
         <f aca="false">+IF(C5&lt;&gt;0,(G5-C5)/C5,ABS(G5-C5))</f>
         <v>0</v>
       </c>
-      <c r="K5" s="160" t="n">
+      <c r="K5" s="159" t="n">
         <f aca="false">+IF(D5&lt;&gt;0,(H5-D5)/D5,0)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="161"/>
-      <c r="M5" s="162" t="n">
+      <c r="L5" s="160"/>
+      <c r="M5" s="161" t="n">
         <f aca="false">+IF(J5&lt;&gt;"",ABS(J5),0)</f>
         <v>0</v>
       </c>
-      <c r="N5" s="162" t="n">
+      <c r="N5" s="161" t="n">
         <f aca="false">+IF(J5&lt;&gt;"",ABS(K5),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="151" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="155" t="n">
+      <c r="B6" s="150" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="154" t="n">
         <f aca="false">Utilidad!A3</f>
         <v>26963</v>
       </c>
-      <c r="D6" s="156" t="n">
+      <c r="D6" s="155" t="n">
         <f aca="false">IF(Utilidad!C3&gt;1,Utilidad!C3/100,Utilidad!C3)</f>
         <v>0.1206</v>
       </c>
-      <c r="F6" s="157" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="158" t="n">
+      <c r="F6" s="156" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="157" t="n">
         <f aca="false">Utilidad!B3</f>
         <v>26963</v>
       </c>
-      <c r="H6" s="159" t="n">
+      <c r="H6" s="158" t="n">
         <f aca="false">IF(Utilidad!D3&gt;1,Utilidad!D3/100,Utilidad!D3)</f>
         <v>0.1206</v>
       </c>
-      <c r="J6" s="160" t="n">
+      <c r="J6" s="159" t="n">
         <f aca="false">+IF(C6&lt;&gt;0,(G6-C6)/C6,ABS(G6-C6))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="160" t="n">
+      <c r="K6" s="159" t="n">
         <f aca="false">+IF(D6&lt;&gt;0,(H6-D6)/D6,0)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="162" t="n">
+      <c r="M6" s="161" t="n">
         <f aca="false">+IF(J6&lt;&gt;"",ABS(J6),0)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="162" t="n">
+      <c r="N6" s="161" t="n">
         <f aca="false">+IF(J6&lt;&gt;"",ABS(K6),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="151" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="155" t="n">
+      <c r="B7" s="150" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="154" t="n">
         <f aca="false">Utilidad!A4</f>
         <v>95187</v>
       </c>
-      <c r="D7" s="156" t="n">
+      <c r="D7" s="155" t="n">
         <f aca="false">IF(Utilidad!C4&gt;1,Utilidad!C4/100,Utilidad!C4)</f>
         <v>0.3553</v>
       </c>
-      <c r="F7" s="157" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="158" t="n">
+      <c r="F7" s="156" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="157" t="n">
         <f aca="false">Utilidad!B4</f>
         <v>95187</v>
       </c>
-      <c r="H7" s="159" t="n">
+      <c r="H7" s="158" t="n">
         <f aca="false">IF(Utilidad!D4&gt;1,Utilidad!D4/100,Utilidad!D4)</f>
         <v>0.34438770714</v>
       </c>
-      <c r="J7" s="160" t="n">
+      <c r="J7" s="159" t="n">
         <f aca="false">+IF(C7&lt;&gt;0,(G7-C7)/C7,ABS(G7-C7))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="160" t="n">
+      <c r="K7" s="159" t="n">
         <f aca="false">+IF(D7&lt;&gt;0,(H7-D7)/D7,0)</f>
         <v>-0.0307128985645933</v>
       </c>
-      <c r="M7" s="162" t="n">
+      <c r="M7" s="161" t="n">
         <f aca="false">+IF(J7&lt;&gt;"",ABS(J7),0)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="162" t="n">
+      <c r="N7" s="161" t="n">
         <f aca="false">+IF(J7&lt;&gt;"",ABS(K7),0)</f>
         <v>0.0307128985645933</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="151" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="155" t="n">
+      <c r="B8" s="150" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="154" t="n">
         <f aca="false">Utilidad!A5</f>
         <v>3530</v>
       </c>
-      <c r="D8" s="156" t="n">
+      <c r="D8" s="155" t="n">
         <f aca="false">IF(Utilidad!C5&gt;1,Utilidad!C5/100,Utilidad!C5)</f>
         <v>0.2388</v>
       </c>
-      <c r="F8" s="157" t="s">
-        <v>136</v>
-      </c>
-      <c r="G8" s="155" t="n">
+      <c r="F8" s="156" t="s">
+        <v>138</v>
+      </c>
+      <c r="G8" s="154" t="n">
         <f aca="false">Utilidad!B5</f>
         <v>3530</v>
       </c>
-      <c r="H8" s="163" t="n">
+      <c r="H8" s="162" t="n">
         <f aca="false">IF(Utilidad!D5&gt;1,Utilidad!D5/100,Utilidad!D5)</f>
         <v>0.2388</v>
       </c>
-      <c r="J8" s="160" t="n">
+      <c r="J8" s="159" t="n">
         <f aca="false">+IF(C8&lt;&gt;0,(G8-C8)/C8,ABS(G8-C8))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="160" t="n">
+      <c r="K8" s="159" t="n">
         <f aca="false">+IF(D8&lt;&gt;0,(H8-D8)/D8,0)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="162" t="n">
+      <c r="M8" s="161" t="n">
         <f aca="false">+IF(J8&lt;&gt;"",ABS(J8),0)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="162" t="n">
+      <c r="N8" s="161" t="n">
         <f aca="false">+IF(J8&lt;&gt;"",ABS(K8),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="151" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="155" t="n">
+      <c r="B9" s="150" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="154" t="n">
         <f aca="false">Utilidad!A6</f>
         <v>-931</v>
       </c>
-      <c r="D9" s="156" t="n">
+      <c r="D9" s="155" t="n">
         <f aca="false">IF(Utilidad!C6&gt;1,Utilidad!C6/100,Utilidad!C6)</f>
         <v>0.297</v>
       </c>
-      <c r="F9" s="157" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" s="155" t="n">
+      <c r="F9" s="156" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="154" t="n">
         <f aca="false">Utilidad!B6</f>
         <v>0</v>
       </c>
-      <c r="H9" s="163" t="n">
+      <c r="H9" s="162" t="n">
         <f aca="false">IF(Utilidad!D6&gt;1,Utilidad!D6/100,Utilidad!D6)</f>
         <v>0.29700000004</v>
       </c>
-      <c r="J9" s="160" t="n">
+      <c r="J9" s="159" t="n">
         <f aca="false">+IF(C9&lt;&gt;0,(G9-C9)/C9,ABS(G9-C9))</f>
         <v>-1</v>
       </c>
-      <c r="K9" s="160" t="n">
+      <c r="K9" s="159" t="n">
         <f aca="false">+IF(D9&lt;&gt;0,(H9-D9)/D9,0)</f>
         <v>1.34680145823619E-010</v>
       </c>
-      <c r="M9" s="162" t="n">
+      <c r="M9" s="161" t="n">
         <f aca="false">+IF(J9&lt;&gt;"",ABS(J9),0)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="162" t="n">
+      <c r="N9" s="161" t="n">
         <f aca="false">+IF(J9&lt;&gt;"",ABS(K9),0)</f>
         <v>1.34680145823619E-010</v>
       </c>
@@ -17929,41 +18019,41 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="151" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="155" t="n">
+      <c r="B10" s="150" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="154" t="n">
         <f aca="false">Utilidad!A7</f>
         <v>98717</v>
       </c>
-      <c r="D10" s="156" t="n">
+      <c r="D10" s="155" t="n">
         <f aca="false">IF(Utilidad!C7&gt;1,Utilidad!C7/100,Utilidad!C7)</f>
         <v>0.3391</v>
       </c>
-      <c r="F10" s="151" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" s="164" t="n">
+      <c r="F10" s="150" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="163" t="n">
         <f aca="false">Utilidad!B7</f>
         <v>98717</v>
       </c>
-      <c r="H10" s="165" t="n">
+      <c r="H10" s="164" t="n">
         <f aca="false">IF(Utilidad!D7&gt;1,Utilidad!D7/100,Utilidad!D7)</f>
         <v>0.340612019</v>
       </c>
-      <c r="J10" s="160" t="n">
+      <c r="J10" s="159" t="n">
         <f aca="false">+IF(C10&lt;&gt;0,(G10-C10)/C10,ABS(G10-C10))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="160" t="n">
+      <c r="K10" s="159" t="n">
         <f aca="false">+IF(D10&lt;&gt;0,(H10-D10)/D10,0)</f>
         <v>0.00445891772338552</v>
       </c>
-      <c r="M10" s="162" t="n">
+      <c r="M10" s="161" t="n">
         <f aca="false">+IF(J10&lt;&gt;"",ABS(J10),0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="162" t="n">
+      <c r="N10" s="161" t="n">
         <f aca="false">+IF(J10&lt;&gt;"",ABS(K10),0)</f>
         <v>0.00445891772338552</v>
       </c>
@@ -17973,225 +18063,225 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="151" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="155" t="n">
+      <c r="B11" s="150" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="154" t="n">
         <f aca="false">Utilidad!A8</f>
         <v>0</v>
       </c>
-      <c r="D11" s="156" t="n">
+      <c r="D11" s="155" t="n">
         <f aca="false">IF(Utilidad!C8&gt;1,Utilidad!C8/100,Utilidad!C8)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="151" t="s">
-        <v>139</v>
-      </c>
-      <c r="G11" s="164" t="n">
+      <c r="F11" s="150" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="163" t="n">
         <f aca="false">Utilidad!B8</f>
         <v>0</v>
       </c>
-      <c r="H11" s="165" t="n">
+      <c r="H11" s="164" t="n">
         <f aca="false">IF(Utilidad!D8&gt;1,Utilidad!D8/100,Utilidad!D8)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="160" t="n">
+      <c r="J11" s="159" t="n">
         <f aca="false">+IF(C11&lt;&gt;0,(G11-C11)/C11,ABS(G11-C11))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="160" t="n">
+      <c r="K11" s="159" t="n">
         <f aca="false">+IF(D11&lt;&gt;0,(H11-D11)/D11,0)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="162" t="n">
+      <c r="M11" s="161" t="n">
         <f aca="false">+IF(J11&lt;&gt;"",ABS(J11),0)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="162" t="n">
+      <c r="N11" s="161" t="n">
         <f aca="false">+IF(J11&lt;&gt;"",ABS(K11),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="151" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="155" t="n">
+      <c r="B12" s="150" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="154" t="n">
         <f aca="false">Utilidad!A9</f>
         <v>32912</v>
       </c>
-      <c r="D12" s="156" t="n">
+      <c r="D12" s="155" t="n">
         <f aca="false">IF(Utilidad!C9&gt;1,Utilidad!C9/100,Utilidad!C9)</f>
         <v>0.1589</v>
       </c>
-      <c r="F12" s="151" t="s">
-        <v>140</v>
-      </c>
-      <c r="G12" s="164" t="n">
+      <c r="F12" s="150" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="163" t="n">
         <f aca="false">Utilidad!B9</f>
         <v>21435.044983</v>
       </c>
-      <c r="H12" s="165" t="n">
+      <c r="H12" s="164" t="n">
         <f aca="false">IF(Utilidad!D9&gt;1,Utilidad!D9/100,Utilidad!D9)</f>
         <v>0.15974666492</v>
       </c>
-      <c r="J12" s="160" t="n">
+      <c r="J12" s="159" t="n">
         <f aca="false">+IF(C12&lt;&gt;0,(G12-C12)/C12,ABS(G12-C12))</f>
         <v>-0.348716426136364</v>
       </c>
-      <c r="K12" s="160" t="n">
+      <c r="K12" s="159" t="n">
         <f aca="false">+IF(D12&lt;&gt;0,(H12-D12)/D12,0)</f>
         <v>0.00532828772813084</v>
       </c>
-      <c r="M12" s="162" t="n">
+      <c r="M12" s="161" t="n">
         <f aca="false">+IF(J12&lt;&gt;"",ABS(J12),0)</f>
         <v>0.348716426136364</v>
       </c>
-      <c r="N12" s="162" t="n">
+      <c r="N12" s="161" t="n">
         <f aca="false">+IF(J12&lt;&gt;"",ABS(K12),0)</f>
         <v>0.00532828772813084</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="150" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="155" t="n">
+      <c r="C13" s="154" t="n">
         <f aca="false">Utilidad!A10</f>
         <v>15308</v>
       </c>
-      <c r="D13" s="156" t="n">
+      <c r="D13" s="155" t="n">
         <f aca="false">IF(Utilidad!C10&gt;1,Utilidad!C10/100,Utilidad!C10)</f>
         <v>0.0828</v>
       </c>
-      <c r="F13" s="157" t="s">
+      <c r="F13" s="156" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="164" t="n">
+      <c r="G13" s="163" t="n">
         <f aca="false">Utilidad!B10</f>
         <v>12796.955017</v>
       </c>
-      <c r="H13" s="165" t="n">
+      <c r="H13" s="164" t="n">
         <f aca="false">IF(Utilidad!D10&gt;1,Utilidad!D10/100,Utilidad!D10)</f>
         <v>0.082951951265</v>
       </c>
-      <c r="J13" s="160" t="n">
+      <c r="J13" s="159" t="n">
         <f aca="false">+IF(C13&lt;&gt;0,(G13-C13)/C13,ABS(G13-C13))</f>
         <v>-0.16403481728508</v>
       </c>
-      <c r="K13" s="160" t="n">
+      <c r="K13" s="159" t="n">
         <f aca="false">+IF(D13&lt;&gt;0,(H13-D13)/D13,0)</f>
         <v>0.00183516020531391</v>
       </c>
-      <c r="M13" s="162" t="n">
+      <c r="M13" s="161" t="n">
         <f aca="false">+IF(J13&lt;&gt;"",ABS(J13),0)</f>
         <v>0.16403481728508</v>
       </c>
-      <c r="N13" s="162" t="n">
+      <c r="N13" s="161" t="n">
         <f aca="false">+IF(J13&lt;&gt;"",ABS(K13),0)</f>
         <v>0.00183516020531391</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="151" t="s">
+      <c r="B14" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="155" t="n">
+      <c r="C14" s="154" t="n">
         <f aca="false">Utilidad!A11</f>
         <v>41025</v>
       </c>
-      <c r="D14" s="156" t="n">
+      <c r="D14" s="155" t="n">
         <f aca="false">IF(Utilidad!C11&gt;1,Utilidad!C11/100,Utilidad!C11)</f>
         <v>0.434</v>
       </c>
-      <c r="F14" s="151" t="s">
+      <c r="F14" s="150" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="164" t="n">
+      <c r="G14" s="163" t="n">
         <f aca="false">Utilidad!B11</f>
         <v>41025</v>
       </c>
-      <c r="H14" s="165" t="n">
+      <c r="H14" s="164" t="n">
         <f aca="false">IF(Utilidad!D11&gt;1,Utilidad!D11/100,Utilidad!D11)</f>
         <v>0.42098</v>
       </c>
-      <c r="J14" s="160" t="n">
+      <c r="J14" s="159" t="n">
         <f aca="false">+IF(C14&lt;&gt;0,(G14-C14)/C14,ABS(G14-C14))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="160" t="n">
+      <c r="K14" s="159" t="n">
         <f aca="false">+IF(D14&lt;&gt;0,(H14-D14)/D14,0)</f>
         <v>-0.0300000000000001</v>
       </c>
-      <c r="M14" s="162" t="n">
+      <c r="M14" s="161" t="n">
         <f aca="false">+IF(J14&lt;&gt;"",ABS(J14),0)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="162" t="n">
+      <c r="N14" s="161" t="n">
         <f aca="false">+IF(J14&lt;&gt;"",ABS(K14),0)</f>
         <v>0.0300000000000001</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="151" t="s">
+      <c r="B15" s="150" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="155" t="n">
+      <c r="C15" s="154" t="n">
         <f aca="false">Utilidad!A12</f>
         <v>23460</v>
       </c>
-      <c r="D15" s="156" t="n">
+      <c r="D15" s="155" t="n">
         <f aca="false">IF(Utilidad!C12&gt;1,Utilidad!C12/100,Utilidad!C12)</f>
         <v>0.5181</v>
       </c>
-      <c r="F15" s="157" t="s">
+      <c r="F15" s="156" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="164" t="n">
+      <c r="G15" s="163" t="n">
         <f aca="false">Utilidad!B12</f>
         <v>23460</v>
       </c>
-      <c r="H15" s="165" t="n">
+      <c r="H15" s="164" t="n">
         <f aca="false">IF(Utilidad!D12&gt;1,Utilidad!D12/100,Utilidad!D12)</f>
         <v>0.50587309641</v>
       </c>
-      <c r="J15" s="160" t="n">
+      <c r="J15" s="159" t="n">
         <f aca="false">+IF(C15&lt;&gt;0,(G15-C15)/C15,ABS(G15-C15))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="160" t="n">
+      <c r="K15" s="159" t="n">
         <f aca="false">+IF(D15&lt;&gt;0,(H15-D15)/D15,0)</f>
         <v>-0.0235995050955414</v>
       </c>
-      <c r="M15" s="162" t="n">
+      <c r="M15" s="161" t="n">
         <f aca="false">+IF(J15&lt;&gt;"",ABS(J15),0)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="162" t="n">
+      <c r="N15" s="161" t="n">
         <f aca="false">+IF(J15&lt;&gt;"",ABS(K15),0)</f>
         <v>0.0235995050955414</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="151" t="s">
+      <c r="B16" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="155" t="n">
+      <c r="C16" s="154" t="n">
         <f aca="false">Utilidad!A13</f>
         <v>0</v>
       </c>
-      <c r="D16" s="156" t="n">
+      <c r="D16" s="155" t="n">
         <f aca="false">IF(Utilidad!C13&gt;1,Utilidad!C13/100,Utilidad!C13)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="151" t="s">
+      <c r="F16" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="166" t="n">
+      <c r="G16" s="165" t="n">
         <f aca="false">Utilidad!B13</f>
         <v>0</v>
       </c>
-      <c r="H16" s="167" t="n">
+      <c r="H16" s="166" t="n">
         <f aca="false">IF(Utilidad!D13&gt;1,Utilidad!D13/100,Utilidad!D13)</f>
         <v>0</v>
       </c>
@@ -18199,2259 +18289,2259 @@
         <f aca="false">(G14*H14+G15*H15)/(G14+G15)*100</f>
         <v>45.1864578456674</v>
       </c>
-      <c r="J16" s="160" t="n">
+      <c r="J16" s="159" t="n">
         <f aca="false">+IF(C16&lt;&gt;0,(G16-C16)/C16,ABS(G16-C16))</f>
         <v>0</v>
       </c>
-      <c r="K16" s="160" t="n">
+      <c r="K16" s="159" t="n">
         <f aca="false">+IF(D16&lt;&gt;0,(H16-D16)/D16,0)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="162" t="n">
+      <c r="M16" s="161" t="n">
         <f aca="false">+IF(J16&lt;&gt;"",ABS(J16),0)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="162" t="n">
+      <c r="N16" s="161" t="n">
         <f aca="false">+IF(J16&lt;&gt;"",ABS(K16),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="151" t="s">
+      <c r="B17" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="155" t="n">
+      <c r="C17" s="154" t="n">
         <f aca="false">Utilidad!A14</f>
         <v>-1782</v>
       </c>
-      <c r="D17" s="156" t="n">
+      <c r="D17" s="155" t="n">
         <f aca="false">IF(Utilidad!C14&gt;1,Utilidad!C14/100,Utilidad!C14)</f>
         <v>0.4434</v>
       </c>
-      <c r="F17" s="151" t="s">
+      <c r="F17" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="166" t="n">
+      <c r="G17" s="165" t="n">
         <f aca="false">Utilidad!B14</f>
         <v>-243</v>
       </c>
-      <c r="H17" s="167" t="n">
+      <c r="H17" s="166" t="n">
         <f aca="false">IF(Utilidad!D14&gt;1,Utilidad!D14/100,Utilidad!D14)</f>
         <v>0.44318093088</v>
       </c>
-      <c r="J17" s="160" t="n">
+      <c r="J17" s="159" t="n">
         <f aca="false">+IF(C17&lt;&gt;0,(G17-C17)/C17,ABS(G17-C17))</f>
         <v>-0.863636363636364</v>
       </c>
-      <c r="K17" s="160" t="n">
+      <c r="K17" s="159" t="n">
         <f aca="false">+IF(D17&lt;&gt;0,(H17-D17)/D17,0)</f>
         <v>-0.000494066576454727</v>
       </c>
-      <c r="M17" s="162" t="n">
+      <c r="M17" s="161" t="n">
         <f aca="false">+IF(J17&lt;&gt;"",ABS(J17),0)</f>
         <v>0.863636363636364</v>
       </c>
-      <c r="N17" s="162" t="n">
+      <c r="N17" s="161" t="n">
         <f aca="false">+IF(J17&lt;&gt;"",ABS(K17),0)</f>
         <v>0.000494066576454727</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="151" t="s">
+      <c r="B18" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="155" t="n">
+      <c r="C18" s="154" t="n">
         <f aca="false">Utilidad!A15</f>
         <v>83697</v>
       </c>
-      <c r="D18" s="156" t="n">
+      <c r="D18" s="155" t="n">
         <f aca="false">IF(Utilidad!C15&gt;1,Utilidad!C15/100,Utilidad!C15)</f>
         <v>0.4219</v>
       </c>
-      <c r="F18" s="157" t="s">
+      <c r="F18" s="156" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="166" t="n">
+      <c r="G18" s="165" t="n">
         <f aca="false">Utilidad!B15</f>
         <v>83697</v>
       </c>
-      <c r="H18" s="167" t="n">
+      <c r="H18" s="166" t="n">
         <f aca="false">IF(Utilidad!D15&gt;1,Utilidad!D15/100,Utilidad!D15)</f>
         <v>0.43797188987</v>
       </c>
-      <c r="J18" s="160" t="n">
+      <c r="J18" s="159" t="n">
         <f aca="false">+IF(C18&lt;&gt;0,(G18-C18)/C18,ABS(G18-C18))</f>
         <v>0</v>
       </c>
-      <c r="K18" s="160" t="n">
+      <c r="K18" s="159" t="n">
         <f aca="false">+IF(D18&lt;&gt;0,(H18-D18)/D18,0)</f>
         <v>0.0380940741170893</v>
       </c>
-      <c r="M18" s="162" t="n">
+      <c r="M18" s="161" t="n">
         <f aca="false">+IF(J18&lt;&gt;"",ABS(J18),0)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="162" t="n">
+      <c r="N18" s="161" t="n">
         <f aca="false">+IF(J18&lt;&gt;"",ABS(K18),0)</f>
         <v>0.0380940741170893</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="155" t="n">
+      <c r="C19" s="154" t="n">
         <f aca="false">Utilidad!A16</f>
         <v>46064</v>
       </c>
-      <c r="D19" s="156" t="n">
+      <c r="D19" s="155" t="n">
         <f aca="false">IF(Utilidad!C16&gt;1,Utilidad!C16/100,Utilidad!C16)</f>
         <v>0.0933</v>
       </c>
-      <c r="F19" s="157" t="s">
+      <c r="F19" s="156" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="166" t="n">
+      <c r="G19" s="165" t="n">
         <f aca="false">Utilidad!B16</f>
         <v>39860</v>
       </c>
-      <c r="H19" s="167" t="n">
+      <c r="H19" s="166" t="n">
         <f aca="false">IF(Utilidad!D16&gt;1,Utilidad!D16/100,Utilidad!D16)</f>
         <v>0.094516633742</v>
       </c>
-      <c r="J19" s="160" t="n">
+      <c r="J19" s="159" t="n">
         <f aca="false">+IF(C19&lt;&gt;0,(G19-C19)/C19,ABS(G19-C19))</f>
         <v>-0.134682181312956</v>
       </c>
-      <c r="K19" s="160" t="n">
+      <c r="K19" s="159" t="n">
         <f aca="false">+IF(D19&lt;&gt;0,(H19-D19)/D19,0)</f>
         <v>0.013040018670954</v>
       </c>
-      <c r="M19" s="162" t="n">
+      <c r="M19" s="161" t="n">
         <f aca="false">+IF(J19&lt;&gt;"",ABS(J19),0)</f>
         <v>0.134682181312956</v>
       </c>
-      <c r="N19" s="162" t="n">
+      <c r="N19" s="161" t="n">
         <f aca="false">+IF(J19&lt;&gt;"",ABS(K19),0)</f>
         <v>0.013040018670954</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="151" t="s">
+      <c r="B20" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="155" t="n">
+      <c r="C20" s="154" t="n">
         <f aca="false">Utilidad!A17</f>
         <v>67297</v>
       </c>
-      <c r="D20" s="156" t="n">
+      <c r="D20" s="155" t="n">
         <f aca="false">IF(Utilidad!C17&gt;1,Utilidad!C17/100,Utilidad!C17)</f>
         <v>0.6457</v>
       </c>
-      <c r="F20" s="157" t="s">
+      <c r="F20" s="156" t="s">
         <v>65</v>
       </c>
-      <c r="G20" s="166" t="n">
+      <c r="G20" s="165" t="n">
         <f aca="false">Utilidad!B17</f>
         <v>67297</v>
       </c>
-      <c r="H20" s="167" t="n">
+      <c r="H20" s="166" t="n">
         <f aca="false">IF(Utilidad!D17&gt;1,Utilidad!D17/100,Utilidad!D17)</f>
         <v>0.665071</v>
       </c>
-      <c r="J20" s="160" t="n">
+      <c r="J20" s="159" t="n">
         <f aca="false">+IF(C20&lt;&gt;0,(G20-C20)/C20,ABS(G20-C20))</f>
         <v>0</v>
       </c>
-      <c r="K20" s="160" t="n">
+      <c r="K20" s="159" t="n">
         <f aca="false">+IF(D20&lt;&gt;0,(H20-D20)/D20,0)</f>
         <v>0.03</v>
       </c>
-      <c r="M20" s="162" t="n">
+      <c r="M20" s="161" t="n">
         <f aca="false">+IF(J20&lt;&gt;"",ABS(J20),0)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="162" t="n">
+      <c r="N20" s="161" t="n">
         <f aca="false">+IF(J20&lt;&gt;"",ABS(K20),0)</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="151" t="s">
+      <c r="B21" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="155" t="n">
+      <c r="C21" s="154" t="n">
         <f aca="false">Utilidad!A18</f>
         <v>-5361</v>
       </c>
-      <c r="D21" s="156" t="n">
+      <c r="D21" s="155" t="n">
         <f aca="false">IF(Utilidad!C18&gt;1,Utilidad!C18/100,Utilidad!C18)</f>
         <v>0.6457</v>
       </c>
-      <c r="F21" s="151" t="s">
+      <c r="F21" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="G21" s="155" t="n">
+      <c r="G21" s="154" t="n">
         <f aca="false">Utilidad!B18</f>
         <v>-5362</v>
       </c>
-      <c r="H21" s="163" t="n">
+      <c r="H21" s="162" t="n">
         <f aca="false">IF(Utilidad!D18&gt;1,Utilidad!D18/100,Utilidad!D18)</f>
         <v>0.64151825596</v>
       </c>
-      <c r="J21" s="160" t="n">
+      <c r="J21" s="159" t="n">
         <f aca="false">+IF(C21&lt;&gt;0,(G21-C21)/C21,ABS(G21-C21))</f>
         <v>0.000186532363365044</v>
       </c>
-      <c r="K21" s="160" t="n">
+      <c r="K21" s="159" t="n">
         <f aca="false">+IF(D21&lt;&gt;0,(H21-D21)/D21,0)</f>
         <v>-0.00647629555521147</v>
       </c>
-      <c r="M21" s="162" t="n">
+      <c r="M21" s="161" t="n">
         <f aca="false">+IF(J21&lt;&gt;"",ABS(J21),0)</f>
         <v>0.000186532363365044</v>
       </c>
-      <c r="N21" s="162" t="n">
+      <c r="N21" s="161" t="n">
         <f aca="false">+IF(J21&lt;&gt;"",ABS(K21),0)</f>
         <v>0.00647629555521147</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="151" t="s">
+      <c r="B22" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="155" t="n">
+      <c r="C22" s="154" t="n">
         <f aca="false">Utilidad!A19</f>
         <v>0</v>
       </c>
-      <c r="D22" s="156" t="n">
+      <c r="D22" s="155" t="n">
         <f aca="false">IF(Utilidad!C19&gt;1,Utilidad!C19/100,Utilidad!C19)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="151" t="s">
+      <c r="F22" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="155" t="n">
+      <c r="G22" s="154" t="n">
         <f aca="false">Utilidad!B19</f>
         <v>0</v>
       </c>
-      <c r="H22" s="163" t="n">
+      <c r="H22" s="162" t="n">
         <f aca="false">IF(Utilidad!D19&gt;1,Utilidad!D19/100,Utilidad!D19)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="160" t="n">
+      <c r="J22" s="159" t="n">
         <f aca="false">+IF(C22&lt;&gt;0,(G22-C22)/C22,ABS(G22-C22))</f>
         <v>0</v>
       </c>
-      <c r="K22" s="160" t="n">
+      <c r="K22" s="159" t="n">
         <f aca="false">+IF(D22&lt;&gt;0,(H22-D22)/D22,0)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="162" t="n">
+      <c r="M22" s="161" t="n">
         <f aca="false">+IF(J22&lt;&gt;"",ABS(J22),0)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="162" t="n">
+      <c r="N22" s="161" t="n">
         <f aca="false">+IF(J22&lt;&gt;"",ABS(K22),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="151" t="s">
+      <c r="B23" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="155" t="n">
+      <c r="C23" s="154" t="n">
         <f aca="false">Utilidad!A20</f>
         <v>72659</v>
       </c>
-      <c r="D23" s="156" t="n">
+      <c r="D23" s="155" t="n">
         <f aca="false">IF(Utilidad!C20&gt;1,Utilidad!C20/100,Utilidad!C20)</f>
         <v>0.6457</v>
       </c>
-      <c r="F23" s="151" t="s">
+      <c r="F23" s="150" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="155" t="n">
+      <c r="G23" s="154" t="n">
         <f aca="false">Utilidad!B20</f>
         <v>72659</v>
       </c>
-      <c r="H23" s="163" t="n">
+      <c r="H23" s="162" t="n">
         <f aca="false">IF(Utilidad!D20&gt;1,Utilidad!D20/100,Utilidad!D20)</f>
         <v>0.66333288341</v>
       </c>
-      <c r="J23" s="160" t="n">
+      <c r="J23" s="159" t="n">
         <f aca="false">+IF(C23&lt;&gt;0,(G23-C23)/C23,ABS(G23-C23))</f>
         <v>0</v>
       </c>
-      <c r="K23" s="160" t="n">
+      <c r="K23" s="159" t="n">
         <f aca="false">+IF(D23&lt;&gt;0,(H23-D23)/D23,0)</f>
         <v>0.0273081669660834</v>
       </c>
-      <c r="M23" s="162" t="n">
+      <c r="M23" s="161" t="n">
         <f aca="false">+IF(J23&lt;&gt;"",ABS(J23),0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="162" t="n">
+      <c r="N23" s="161" t="n">
         <f aca="false">+IF(J23&lt;&gt;"",ABS(K23),0)</f>
         <v>0.0273081669660834</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="151" t="s">
+      <c r="B24" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="155" t="n">
+      <c r="C24" s="154" t="n">
         <f aca="false">Utilidad!A21</f>
         <v>1453</v>
       </c>
-      <c r="D24" s="156" t="n">
+      <c r="D24" s="155" t="n">
         <f aca="false">IF(Utilidad!C21&gt;1,Utilidad!C21/100,Utilidad!C21)</f>
         <v>0.6457</v>
       </c>
-      <c r="F24" s="151" t="s">
+      <c r="F24" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="155" t="n">
+      <c r="G24" s="154" t="n">
         <f aca="false">Utilidad!B21</f>
         <v>1453</v>
       </c>
-      <c r="H24" s="163" t="n">
+      <c r="H24" s="162" t="n">
         <f aca="false">IF(Utilidad!D21&gt;1,Utilidad!D21/100,Utilidad!D21)</f>
         <v>0.64646643925</v>
       </c>
-      <c r="J24" s="160" t="n">
+      <c r="J24" s="159" t="n">
         <f aca="false">+IF(C24&lt;&gt;0,(G24-C24)/C24,ABS(G24-C24))</f>
         <v>0</v>
       </c>
-      <c r="K24" s="160" t="n">
+      <c r="K24" s="159" t="n">
         <f aca="false">+IF(D24&lt;&gt;0,(H24-D24)/D24,0)</f>
         <v>0.00118698970109971</v>
       </c>
-      <c r="M24" s="162" t="n">
+      <c r="M24" s="161" t="n">
         <f aca="false">+IF(J24&lt;&gt;"",ABS(J24),0)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="162" t="n">
+      <c r="N24" s="161" t="n">
         <f aca="false">+IF(J24&lt;&gt;"",ABS(K24),0)</f>
         <v>0.00118698970109971</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="151" t="s">
+      <c r="B25" s="150" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="155" t="n">
+      <c r="C25" s="154" t="n">
         <f aca="false">Utilidad!A22</f>
         <v>71205</v>
       </c>
-      <c r="D25" s="156" t="n">
+      <c r="D25" s="155" t="n">
         <f aca="false">IF(Utilidad!C22&gt;1,Utilidad!C22/100,Utilidad!C22)</f>
         <v>0.6457</v>
       </c>
-      <c r="F25" s="151" t="s">
+      <c r="F25" s="150" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="155" t="n">
+      <c r="G25" s="154" t="n">
         <f aca="false">Utilidad!B22</f>
         <v>71205</v>
       </c>
-      <c r="H25" s="163" t="n">
+      <c r="H25" s="162" t="n">
         <f aca="false">IF(Utilidad!D22&gt;1,Utilidad!D22/100,Utilidad!D22)</f>
         <v>0.6636863737</v>
       </c>
-      <c r="J25" s="160" t="n">
+      <c r="J25" s="159" t="n">
         <f aca="false">+IF(C25&lt;&gt;0,(G25-C25)/C25,ABS(G25-C25))</f>
         <v>0</v>
       </c>
-      <c r="K25" s="160" t="n">
+      <c r="K25" s="159" t="n">
         <f aca="false">+IF(D25&lt;&gt;0,(H25-D25)/D25,0)</f>
         <v>0.0278556197924735</v>
       </c>
-      <c r="M25" s="162" t="n">
+      <c r="M25" s="161" t="n">
         <f aca="false">+IF(J25&lt;&gt;"",ABS(J25),0)</f>
         <v>0</v>
       </c>
-      <c r="N25" s="162" t="n">
+      <c r="N25" s="161" t="n">
         <f aca="false">+IF(J25&lt;&gt;"",ABS(K25),0)</f>
         <v>0.0278556197924735</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="151" t="s">
+      <c r="B26" s="150" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="155" t="n">
+      <c r="C26" s="154" t="n">
         <f aca="false">Utilidad!A23</f>
         <v>66791</v>
       </c>
-      <c r="D26" s="156" t="n">
+      <c r="D26" s="155" t="n">
         <f aca="false">IF(Utilidad!C23&gt;1,Utilidad!C23/100,Utilidad!C23)</f>
         <v>0.6465</v>
       </c>
-      <c r="F26" s="151" t="s">
+      <c r="F26" s="150" t="s">
         <v>71</v>
       </c>
-      <c r="G26" s="155" t="n">
+      <c r="G26" s="154" t="n">
         <f aca="false">Utilidad!B23</f>
         <v>66433</v>
       </c>
-      <c r="H26" s="163" t="n">
+      <c r="H26" s="162" t="n">
         <f aca="false">IF(Utilidad!D23&gt;1,Utilidad!D23/100,Utilidad!D23)</f>
         <v>0.66479878734</v>
       </c>
-      <c r="J26" s="160" t="n">
+      <c r="J26" s="159" t="n">
         <f aca="false">+IF(C26&lt;&gt;0,(G26-C26)/C26,ABS(G26-C26))</f>
         <v>-0.0053600035932985</v>
       </c>
-      <c r="K26" s="160" t="n">
+      <c r="K26" s="159" t="n">
         <f aca="false">+IF(D26&lt;&gt;0,(H26-D26)/D26,0)</f>
         <v>0.0283043887703015</v>
       </c>
-      <c r="M26" s="162" t="n">
+      <c r="M26" s="161" t="n">
         <f aca="false">+IF(J26&lt;&gt;"",ABS(J26),0)</f>
         <v>0.0053600035932985</v>
       </c>
-      <c r="N26" s="162" t="n">
+      <c r="N26" s="161" t="n">
         <f aca="false">+IF(J26&lt;&gt;"",ABS(K26),0)</f>
         <v>0.0283043887703015</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="151" t="s">
+      <c r="B27" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="155" t="n">
+      <c r="C27" s="154" t="n">
         <f aca="false">Utilidad!A24</f>
         <v>4772</v>
       </c>
-      <c r="D27" s="156" t="n">
+      <c r="D27" s="155" t="n">
         <f aca="false">IF(Utilidad!C24&gt;1,Utilidad!C24/100,Utilidad!C24)</f>
         <v>0.6482</v>
       </c>
-      <c r="F27" s="151" t="s">
+      <c r="F27" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="G27" s="155" t="n">
+      <c r="G27" s="154" t="n">
         <f aca="false">Utilidad!B24</f>
         <v>4772</v>
       </c>
-      <c r="H27" s="163" t="n">
+      <c r="H27" s="162" t="n">
         <f aca="false">IF(Utilidad!D24&gt;1,Utilidad!D24/100,Utilidad!D24)</f>
         <v>0.6482</v>
       </c>
-      <c r="J27" s="160" t="n">
+      <c r="J27" s="159" t="n">
         <f aca="false">+IF(C27&lt;&gt;0,(G27-C27)/C27,ABS(G27-C27))</f>
         <v>0</v>
       </c>
-      <c r="K27" s="160" t="n">
+      <c r="K27" s="159" t="n">
         <f aca="false">+IF(D27&lt;&gt;0,(H27-D27)/D27,0)</f>
         <v>0</v>
       </c>
-      <c r="M27" s="162" t="n">
+      <c r="M27" s="161" t="n">
         <f aca="false">+IF(J27&lt;&gt;"",ABS(J27),0)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="162" t="n">
+      <c r="N27" s="161" t="n">
         <f aca="false">+IF(J27&lt;&gt;"",ABS(K27),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="151" t="s">
+      <c r="B28" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="155" t="n">
+      <c r="C28" s="154" t="n">
         <f aca="false">Utilidad!A25</f>
         <v>0</v>
       </c>
-      <c r="D28" s="156" t="n">
+      <c r="D28" s="155" t="n">
         <f aca="false">IF(Utilidad!C25&gt;1,Utilidad!C25/100,Utilidad!C25)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="151" t="s">
+      <c r="F28" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="G28" s="155" t="n">
+      <c r="G28" s="154" t="n">
         <f aca="false">Utilidad!B25</f>
         <v>0</v>
       </c>
-      <c r="H28" s="163" t="n">
+      <c r="H28" s="162" t="n">
         <f aca="false">IF(Utilidad!D25&gt;1,Utilidad!D25/100,Utilidad!D25)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="160" t="n">
+      <c r="J28" s="159" t="n">
         <f aca="false">+IF(C28&lt;&gt;0,(G28-C28)/C28,ABS(G28-C28))</f>
         <v>0</v>
       </c>
-      <c r="K28" s="160" t="n">
+      <c r="K28" s="159" t="n">
         <f aca="false">+IF(D28&lt;&gt;0,(H28-D28)/D28,0)</f>
         <v>0</v>
       </c>
-      <c r="M28" s="162" t="n">
+      <c r="M28" s="161" t="n">
         <f aca="false">+IF(J28&lt;&gt;"",ABS(J28),0)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="162" t="n">
+      <c r="N28" s="161" t="n">
         <f aca="false">+IF(J28&lt;&gt;"",ABS(K28),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="151" t="s">
+      <c r="B29" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="155" t="n">
+      <c r="C29" s="154" t="n">
         <f aca="false">Utilidad!A26</f>
         <v>0</v>
       </c>
-      <c r="D29" s="156" t="n">
+      <c r="D29" s="155" t="n">
         <f aca="false">IF(Utilidad!C26&gt;1,Utilidad!C26/100,Utilidad!C26)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="151" t="s">
+      <c r="F29" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="G29" s="155" t="n">
+      <c r="G29" s="154" t="n">
         <f aca="false">Utilidad!B26</f>
         <v>0</v>
       </c>
-      <c r="H29" s="163" t="n">
+      <c r="H29" s="162" t="n">
         <f aca="false">IF(Utilidad!D26&gt;1,Utilidad!D26/100,Utilidad!D26)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="160" t="n">
+      <c r="J29" s="159" t="n">
         <f aca="false">+IF(C29&lt;&gt;0,(G29-C29)/C29,ABS(G29-C29))</f>
         <v>0</v>
       </c>
-      <c r="K29" s="160" t="n">
+      <c r="K29" s="159" t="n">
         <f aca="false">+IF(D29&lt;&gt;0,(H29-D29)/D29,0)</f>
         <v>0</v>
       </c>
-      <c r="M29" s="162" t="n">
+      <c r="M29" s="161" t="n">
         <f aca="false">+IF(J29&lt;&gt;"",ABS(J29),0)</f>
         <v>0</v>
       </c>
-      <c r="N29" s="162" t="n">
+      <c r="N29" s="161" t="n">
         <f aca="false">+IF(J29&lt;&gt;"",ABS(K29),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="151" t="s">
+      <c r="B30" s="150" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="155" t="n">
+      <c r="C30" s="154" t="n">
         <f aca="false">Utilidad!A27</f>
         <v>0</v>
       </c>
-      <c r="D30" s="156" t="n">
+      <c r="D30" s="155" t="n">
         <f aca="false">IF(Utilidad!C27&gt;1,Utilidad!C27/100,Utilidad!C27)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="151" t="s">
+      <c r="F30" s="150" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="155" t="n">
+      <c r="G30" s="154" t="n">
         <f aca="false">Utilidad!B27</f>
         <v>0</v>
       </c>
-      <c r="H30" s="163" t="n">
+      <c r="H30" s="162" t="n">
         <f aca="false">IF(Utilidad!D27&gt;1,Utilidad!D27/100,Utilidad!D27)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="160" t="n">
+      <c r="J30" s="159" t="n">
         <f aca="false">+IF(C30&lt;&gt;0,(G30-C30)/C30,ABS(G30-C30))</f>
         <v>0</v>
       </c>
-      <c r="K30" s="160" t="n">
+      <c r="K30" s="159" t="n">
         <f aca="false">+IF(D30&lt;&gt;0,(H30-D30)/D30,0)</f>
         <v>0</v>
       </c>
-      <c r="M30" s="162" t="n">
+      <c r="M30" s="161" t="n">
         <f aca="false">+IF(J30&lt;&gt;"",ABS(J30),0)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="162" t="n">
+      <c r="N30" s="161" t="n">
         <f aca="false">+IF(J30&lt;&gt;"",ABS(K30),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="151" t="s">
+      <c r="B31" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="155" t="n">
+      <c r="C31" s="154" t="n">
         <f aca="false">Utilidad!A28</f>
         <v>0</v>
       </c>
-      <c r="D31" s="156" t="n">
+      <c r="D31" s="155" t="n">
         <f aca="false">IF(Utilidad!C28&gt;1,Utilidad!C28/100,Utilidad!C28)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="151" t="s">
+      <c r="F31" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="G31" s="155" t="n">
+      <c r="G31" s="154" t="n">
         <f aca="false">Utilidad!B28</f>
         <v>0</v>
       </c>
-      <c r="H31" s="163" t="n">
+      <c r="H31" s="162" t="n">
         <f aca="false">IF(Utilidad!D28&gt;1,Utilidad!D28/100,Utilidad!D28)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="160" t="n">
+      <c r="J31" s="159" t="n">
         <f aca="false">+IF(C31&lt;&gt;0,(G31-C31)/C31,ABS(G31-C31))</f>
         <v>0</v>
       </c>
-      <c r="K31" s="160" t="n">
+      <c r="K31" s="159" t="n">
         <f aca="false">+IF(D31&lt;&gt;0,(H31-D31)/D31,0)</f>
         <v>0</v>
       </c>
-      <c r="M31" s="162" t="n">
+      <c r="M31" s="161" t="n">
         <f aca="false">+IF(J31&lt;&gt;"",ABS(J31),0)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="162" t="n">
+      <c r="N31" s="161" t="n">
         <f aca="false">+IF(J31&lt;&gt;"",ABS(K31),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="151" t="s">
+      <c r="B32" s="150" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="155" t="n">
+      <c r="C32" s="154" t="n">
         <f aca="false">Utilidad!A29</f>
         <v>0</v>
       </c>
-      <c r="D32" s="156" t="n">
+      <c r="D32" s="155" t="n">
         <f aca="false">IF(Utilidad!C29&gt;1,Utilidad!C29/100,Utilidad!C29)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="151" t="s">
+      <c r="F32" s="150" t="s">
         <v>77</v>
       </c>
-      <c r="G32" s="155" t="n">
+      <c r="G32" s="154" t="n">
         <f aca="false">Utilidad!B29</f>
         <v>0</v>
       </c>
-      <c r="H32" s="163" t="n">
+      <c r="H32" s="162" t="n">
         <f aca="false">IF(Utilidad!D29&gt;1,Utilidad!D29/100,Utilidad!D29)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="160" t="n">
+      <c r="J32" s="159" t="n">
         <f aca="false">+IF(C32&lt;&gt;0,(G32-C32)/C32,ABS(G32-C32))</f>
         <v>0</v>
       </c>
-      <c r="K32" s="160" t="n">
+      <c r="K32" s="159" t="n">
         <f aca="false">+IF(D32&lt;&gt;0,(H32-D32)/D32,0)</f>
         <v>0</v>
       </c>
-      <c r="M32" s="162" t="n">
+      <c r="M32" s="161" t="n">
         <f aca="false">+IF(J32&lt;&gt;"",ABS(J32),0)</f>
         <v>0</v>
       </c>
-      <c r="N32" s="162" t="n">
+      <c r="N32" s="161" t="n">
         <f aca="false">+IF(J32&lt;&gt;"",ABS(K32),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="151" t="s">
+      <c r="B33" s="150" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="155" t="n">
+      <c r="C33" s="154" t="n">
         <f aca="false">Utilidad!A30</f>
         <v>0</v>
       </c>
-      <c r="D33" s="156" t="n">
+      <c r="D33" s="155" t="n">
         <f aca="false">IF(Utilidad!C30&gt;1,Utilidad!C30/100,Utilidad!C30)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="151" t="s">
+      <c r="F33" s="150" t="s">
         <v>78</v>
       </c>
-      <c r="G33" s="155" t="n">
+      <c r="G33" s="154" t="n">
         <f aca="false">Utilidad!B30</f>
         <v>0</v>
       </c>
-      <c r="H33" s="163" t="n">
+      <c r="H33" s="162" t="n">
         <f aca="false">IF(Utilidad!D30&gt;1,Utilidad!D30/100,Utilidad!D30)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="160" t="n">
+      <c r="J33" s="159" t="n">
         <f aca="false">+IF(C33&lt;&gt;0,(G33-C33)/C33,ABS(G33-C33))</f>
         <v>0</v>
       </c>
-      <c r="K33" s="160" t="n">
+      <c r="K33" s="159" t="n">
         <f aca="false">+IF(D33&lt;&gt;0,(H33-D33)/D33,0)</f>
         <v>0</v>
       </c>
-      <c r="M33" s="162" t="n">
+      <c r="M33" s="161" t="n">
         <f aca="false">+IF(J33&lt;&gt;"",ABS(J33),0)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="162" t="n">
+      <c r="N33" s="161" t="n">
         <f aca="false">+IF(J33&lt;&gt;"",ABS(K33),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="151" t="s">
+      <c r="B34" s="150" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="155" t="n">
+      <c r="C34" s="154" t="n">
         <f aca="false">Utilidad!A31</f>
         <v>6294</v>
       </c>
-      <c r="D34" s="156" t="n">
+      <c r="D34" s="155" t="n">
         <f aca="false">IF(Utilidad!C31&gt;1,Utilidad!C31/100,Utilidad!C31)</f>
         <v>0.6346</v>
       </c>
-      <c r="F34" s="151" t="s">
+      <c r="F34" s="150" t="s">
         <v>79</v>
       </c>
-      <c r="G34" s="155" t="n">
+      <c r="G34" s="154" t="n">
         <f aca="false">Utilidad!B31</f>
         <v>7132</v>
       </c>
-      <c r="H34" s="163" t="n">
+      <c r="H34" s="162" t="n">
         <f aca="false">IF(Utilidad!D31&gt;1,Utilidad!D31/100,Utilidad!D31)</f>
         <v>0.6356235558</v>
       </c>
-      <c r="J34" s="160" t="n">
+      <c r="J34" s="159" t="n">
         <f aca="false">+IF(C34&lt;&gt;0,(G34-C34)/C34,ABS(G34-C34))</f>
         <v>0.133142675564029</v>
       </c>
-      <c r="K34" s="160" t="n">
+      <c r="K34" s="159" t="n">
         <f aca="false">+IF(D34&lt;&gt;0,(H34-D34)/D34,0)</f>
         <v>0.00161291490702808</v>
       </c>
-      <c r="M34" s="162" t="n">
+      <c r="M34" s="161" t="n">
         <f aca="false">+IF(J34&lt;&gt;"",ABS(J34),0)</f>
         <v>0.133142675564029</v>
       </c>
-      <c r="N34" s="162" t="n">
+      <c r="N34" s="161" t="n">
         <f aca="false">+IF(J34&lt;&gt;"",ABS(K34),0)</f>
         <v>0.00161291490702808</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="151" t="s">
+      <c r="B35" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="155" t="n">
+      <c r="C35" s="154" t="n">
         <f aca="false">Utilidad!A32</f>
         <v>0</v>
       </c>
-      <c r="D35" s="156" t="n">
+      <c r="D35" s="155" t="n">
         <f aca="false">IF(Utilidad!C32&gt;1,Utilidad!C32/100,Utilidad!C32)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="151" t="s">
+      <c r="F35" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="G35" s="155" t="n">
+      <c r="G35" s="154" t="n">
         <f aca="false">Utilidad!B32</f>
         <v>0</v>
       </c>
-      <c r="H35" s="163" t="n">
+      <c r="H35" s="162" t="n">
         <f aca="false">IF(Utilidad!D32&gt;1,Utilidad!D32/100,Utilidad!D32)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="160" t="n">
+      <c r="J35" s="159" t="n">
         <f aca="false">+IF(C35&lt;&gt;0,(G35-C35)/C35,ABS(G35-C35))</f>
         <v>0</v>
       </c>
-      <c r="K35" s="160" t="n">
+      <c r="K35" s="159" t="n">
         <f aca="false">+IF(D35&lt;&gt;0,(H35-D35)/D35,0)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="162" t="n">
+      <c r="M35" s="161" t="n">
         <f aca="false">+IF(J35&lt;&gt;"",ABS(J35),0)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="162" t="n">
+      <c r="N35" s="161" t="n">
         <f aca="false">+IF(J35&lt;&gt;"",ABS(K35),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="151" t="s">
+      <c r="B36" s="150" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="155" t="n">
+      <c r="C36" s="154" t="n">
         <f aca="false">Utilidad!A33</f>
         <v>0</v>
       </c>
-      <c r="D36" s="156" t="n">
+      <c r="D36" s="155" t="n">
         <f aca="false">IF(Utilidad!C33&gt;1,Utilidad!C33/100,Utilidad!C33)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="151" t="s">
+      <c r="F36" s="150" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="155" t="n">
+      <c r="G36" s="154" t="n">
         <f aca="false">Utilidad!B33</f>
         <v>0</v>
       </c>
-      <c r="H36" s="163" t="n">
+      <c r="H36" s="162" t="n">
         <f aca="false">IF(Utilidad!D33&gt;1,Utilidad!D33/100,Utilidad!D33)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="160" t="n">
+      <c r="J36" s="159" t="n">
         <f aca="false">+IF(C36&lt;&gt;0,(G36-C36)/C36,ABS(G36-C36))</f>
         <v>0</v>
       </c>
-      <c r="K36" s="160" t="n">
+      <c r="K36" s="159" t="n">
         <f aca="false">+IF(D36&lt;&gt;0,(H36-D36)/D36,0)</f>
         <v>0</v>
       </c>
-      <c r="M36" s="162" t="n">
+      <c r="M36" s="161" t="n">
         <f aca="false">+IF(J36&lt;&gt;"",ABS(J36),0)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="162" t="n">
+      <c r="N36" s="161" t="n">
         <f aca="false">+IF(J36&lt;&gt;"",ABS(K36),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="151" t="s">
+      <c r="B37" s="150" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="155" t="n">
+      <c r="C37" s="154" t="n">
         <f aca="false">Utilidad!A34</f>
         <v>0</v>
       </c>
-      <c r="D37" s="156" t="n">
+      <c r="D37" s="155" t="n">
         <f aca="false">IF(Utilidad!C34&gt;1,Utilidad!C34/100,Utilidad!C34)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="151" t="s">
+      <c r="F37" s="150" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="155" t="n">
+      <c r="G37" s="154" t="n">
         <f aca="false">Utilidad!B34</f>
         <v>0</v>
       </c>
-      <c r="H37" s="163" t="n">
+      <c r="H37" s="162" t="n">
         <f aca="false">IF(Utilidad!D34&gt;1,Utilidad!D34/100,Utilidad!D34)</f>
         <v>0</v>
       </c>
-      <c r="J37" s="160" t="n">
+      <c r="J37" s="159" t="n">
         <f aca="false">+IF(C37&lt;&gt;0,(G37-C37)/C37,ABS(G37-C37))</f>
         <v>0</v>
       </c>
-      <c r="K37" s="160" t="n">
+      <c r="K37" s="159" t="n">
         <f aca="false">+IF(D37&lt;&gt;0,(H37-D37)/D37,0)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="162" t="n">
+      <c r="M37" s="161" t="n">
         <f aca="false">+IF(J37&lt;&gt;"",ABS(J37),0)</f>
         <v>0</v>
       </c>
-      <c r="N37" s="162" t="n">
+      <c r="N37" s="161" t="n">
         <f aca="false">+IF(J37&lt;&gt;"",ABS(K37),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="151" t="s">
+      <c r="B38" s="150" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="155" t="n">
+      <c r="C38" s="154" t="n">
         <f aca="false">Utilidad!A35</f>
         <v>0</v>
       </c>
-      <c r="D38" s="156" t="n">
+      <c r="D38" s="155" t="n">
         <f aca="false">IF(Utilidad!C35&gt;1,Utilidad!C35/100,Utilidad!C35)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="151" t="s">
+      <c r="F38" s="150" t="s">
         <v>83</v>
       </c>
-      <c r="G38" s="155" t="n">
+      <c r="G38" s="154" t="n">
         <f aca="false">Utilidad!B35</f>
         <v>0</v>
       </c>
-      <c r="H38" s="163" t="n">
+      <c r="H38" s="162" t="n">
         <f aca="false">IF(Utilidad!D35&gt;1,Utilidad!D35/100,Utilidad!D35)</f>
         <v>0</v>
       </c>
-      <c r="J38" s="160" t="n">
+      <c r="J38" s="159" t="n">
         <f aca="false">+IF(C38&lt;&gt;0,(G38-C38)/C38,ABS(G38-C38))</f>
         <v>0</v>
       </c>
-      <c r="K38" s="160" t="n">
+      <c r="K38" s="159" t="n">
         <f aca="false">+IF(D38&lt;&gt;0,(H38-D38)/D38,0)</f>
         <v>0</v>
       </c>
-      <c r="M38" s="162" t="n">
+      <c r="M38" s="161" t="n">
         <f aca="false">+IF(J38&lt;&gt;"",ABS(J38),0)</f>
         <v>0</v>
       </c>
-      <c r="N38" s="162" t="n">
+      <c r="N38" s="161" t="n">
         <f aca="false">+IF(J38&lt;&gt;"",ABS(K38),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="151" t="s">
+      <c r="B39" s="150" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="155" t="n">
+      <c r="C39" s="154" t="n">
         <f aca="false">Utilidad!A36</f>
         <v>-1624</v>
       </c>
-      <c r="D39" s="156" t="n">
+      <c r="D39" s="155" t="n">
         <f aca="false">IF(Utilidad!C36&gt;1,Utilidad!C36/100,Utilidad!C36)</f>
         <v>0.6346</v>
       </c>
-      <c r="F39" s="151" t="s">
+      <c r="F39" s="150" t="s">
         <v>84</v>
       </c>
-      <c r="G39" s="155" t="n">
+      <c r="G39" s="154" t="n">
         <f aca="false">Utilidad!B36</f>
         <v>-1632</v>
       </c>
-      <c r="H39" s="163" t="n">
+      <c r="H39" s="162" t="n">
         <f aca="false">IF(Utilidad!D36&gt;1,Utilidad!D36/100,Utilidad!D36)</f>
         <v>0.5831</v>
       </c>
-      <c r="J39" s="160" t="n">
+      <c r="J39" s="159" t="n">
         <f aca="false">+IF(C39&lt;&gt;0,(G39-C39)/C39,ABS(G39-C39))</f>
         <v>0.00492610837438424</v>
       </c>
-      <c r="K39" s="160" t="n">
+      <c r="K39" s="159" t="n">
         <f aca="false">+IF(D39&lt;&gt;0,(H39-D39)/D39,0)</f>
         <v>-0.0811534825086669</v>
       </c>
-      <c r="M39" s="162" t="n">
+      <c r="M39" s="161" t="n">
         <f aca="false">+IF(J39&lt;&gt;"",ABS(J39),0)</f>
         <v>0.00492610837438424</v>
       </c>
-      <c r="N39" s="162" t="n">
+      <c r="N39" s="161" t="n">
         <f aca="false">+IF(J39&lt;&gt;"",ABS(K39),0)</f>
         <v>0.0811534825086669</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="151" t="s">
+      <c r="B40" s="150" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="155" t="n">
+      <c r="C40" s="154" t="n">
         <f aca="false">Utilidad!A37</f>
         <v>1632</v>
       </c>
-      <c r="D40" s="156" t="n">
+      <c r="D40" s="155" t="n">
         <f aca="false">IF(Utilidad!C37&gt;1,Utilidad!C37/100,Utilidad!C37)</f>
         <v>0.5831</v>
       </c>
-      <c r="F40" s="151" t="s">
+      <c r="F40" s="150" t="s">
         <v>85</v>
       </c>
-      <c r="G40" s="155" t="n">
+      <c r="G40" s="154" t="n">
         <f aca="false">Utilidad!B37</f>
         <v>1632</v>
       </c>
-      <c r="H40" s="163" t="n">
+      <c r="H40" s="162" t="n">
         <f aca="false">IF(Utilidad!D37&gt;1,Utilidad!D37/100,Utilidad!D37)</f>
         <v>0.5831</v>
       </c>
-      <c r="J40" s="160" t="n">
+      <c r="J40" s="159" t="n">
         <f aca="false">+IF(C40&lt;&gt;0,(G40-C40)/C40,ABS(G40-C40))</f>
         <v>0</v>
       </c>
-      <c r="K40" s="160" t="n">
+      <c r="K40" s="159" t="n">
         <f aca="false">+IF(D40&lt;&gt;0,(H40-D40)/D40,0)</f>
         <v>0</v>
       </c>
-      <c r="M40" s="162" t="n">
+      <c r="M40" s="161" t="n">
         <f aca="false">+IF(J40&lt;&gt;"",ABS(J40),0)</f>
         <v>0</v>
       </c>
-      <c r="N40" s="162" t="n">
+      <c r="N40" s="161" t="n">
         <f aca="false">+IF(J40&lt;&gt;"",ABS(K40),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="151" t="s">
+      <c r="B41" s="150" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="155" t="n">
+      <c r="C41" s="154" t="n">
         <f aca="false">Utilidad!A38</f>
         <v>0</v>
       </c>
-      <c r="D41" s="156" t="n">
+      <c r="D41" s="155" t="n">
         <f aca="false">IF(Utilidad!C38&gt;1,Utilidad!C38/100,Utilidad!C38)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="151" t="s">
+      <c r="F41" s="150" t="s">
         <v>86</v>
       </c>
-      <c r="G41" s="155" t="n">
+      <c r="G41" s="154" t="n">
         <f aca="false">Utilidad!B38</f>
         <v>0</v>
       </c>
-      <c r="H41" s="163" t="n">
+      <c r="H41" s="162" t="n">
         <f aca="false">IF(Utilidad!D38&gt;1,Utilidad!D38/100,Utilidad!D38)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="160" t="n">
+      <c r="J41" s="159" t="n">
         <f aca="false">+IF(C41&lt;&gt;0,(G41-C41)/C41,ABS(G41-C41))</f>
         <v>0</v>
       </c>
-      <c r="K41" s="160" t="n">
+      <c r="K41" s="159" t="n">
         <f aca="false">+IF(D41&lt;&gt;0,(H41-D41)/D41,0)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="162" t="n">
+      <c r="M41" s="161" t="n">
         <f aca="false">+IF(J41&lt;&gt;"",ABS(J41),0)</f>
         <v>0</v>
       </c>
-      <c r="N41" s="162" t="n">
+      <c r="N41" s="161" t="n">
         <f aca="false">+IF(J41&lt;&gt;"",ABS(K41),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="151" t="s">
+      <c r="B42" s="150" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="155" t="n">
+      <c r="C42" s="154" t="n">
         <f aca="false">Utilidad!A39</f>
         <v>0</v>
       </c>
-      <c r="D42" s="156" t="n">
+      <c r="D42" s="155" t="n">
         <f aca="false">IF(Utilidad!C39&gt;1,Utilidad!C39/100,Utilidad!C39)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="151" t="s">
+      <c r="F42" s="150" t="s">
         <v>87</v>
       </c>
-      <c r="G42" s="155" t="n">
+      <c r="G42" s="154" t="n">
         <f aca="false">Utilidad!B39</f>
         <v>0</v>
       </c>
-      <c r="H42" s="163" t="n">
+      <c r="H42" s="162" t="n">
         <f aca="false">IF(Utilidad!D39&gt;1,Utilidad!D39/100,Utilidad!D39)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="160" t="n">
+      <c r="J42" s="159" t="n">
         <f aca="false">+IF(C42&lt;&gt;0,(G42-C42)/C42,ABS(G42-C42))</f>
         <v>0</v>
       </c>
-      <c r="K42" s="160" t="n">
+      <c r="K42" s="159" t="n">
         <f aca="false">+IF(D42&lt;&gt;0,(H42-D42)/D42,0)</f>
         <v>0</v>
       </c>
-      <c r="M42" s="162" t="n">
+      <c r="M42" s="161" t="n">
         <f aca="false">+IF(J42&lt;&gt;"",ABS(J42),0)</f>
         <v>0</v>
       </c>
-      <c r="N42" s="162" t="n">
+      <c r="N42" s="161" t="n">
         <f aca="false">+IF(J42&lt;&gt;"",ABS(K42),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="151" t="s">
+      <c r="B43" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="C43" s="155" t="n">
+      <c r="C43" s="154" t="n">
         <f aca="false">Utilidad!A40</f>
         <v>0</v>
       </c>
-      <c r="D43" s="156" t="n">
+      <c r="D43" s="155" t="n">
         <f aca="false">IF(Utilidad!C40&gt;1,Utilidad!C40/100,Utilidad!C40)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="151" t="s">
+      <c r="F43" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="G43" s="155" t="n">
+      <c r="G43" s="154" t="n">
         <f aca="false">Utilidad!B40</f>
         <v>0</v>
       </c>
-      <c r="H43" s="163" t="n">
+      <c r="H43" s="162" t="n">
         <f aca="false">IF(Utilidad!D40&gt;1,Utilidad!D40/100,Utilidad!D40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="160" t="n">
+      <c r="J43" s="159" t="n">
         <f aca="false">+IF(C43&lt;&gt;0,(G43-C43)/C43,ABS(G43-C43))</f>
         <v>0</v>
       </c>
-      <c r="K43" s="160" t="n">
+      <c r="K43" s="159" t="n">
         <f aca="false">+IF(D43&lt;&gt;0,(H43-D43)/D43,0)</f>
         <v>0</v>
       </c>
-      <c r="M43" s="162" t="n">
+      <c r="M43" s="161" t="n">
         <f aca="false">+IF(J43&lt;&gt;"",ABS(J43),0)</f>
         <v>0</v>
       </c>
-      <c r="N43" s="162" t="n">
+      <c r="N43" s="161" t="n">
         <f aca="false">+IF(J43&lt;&gt;"",ABS(K43),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="151" t="s">
+      <c r="B44" s="150" t="s">
         <v>89</v>
       </c>
-      <c r="C44" s="155" t="n">
+      <c r="C44" s="154" t="n">
         <f aca="false">Utilidad!A41</f>
         <v>0</v>
       </c>
-      <c r="D44" s="156" t="n">
+      <c r="D44" s="155" t="n">
         <f aca="false">IF(Utilidad!C41&gt;1,Utilidad!C41/100,Utilidad!C41)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="151" t="s">
+      <c r="F44" s="150" t="s">
         <v>89</v>
       </c>
-      <c r="G44" s="155" t="n">
+      <c r="G44" s="154" t="n">
         <f aca="false">Utilidad!B41</f>
         <v>0</v>
       </c>
-      <c r="H44" s="163" t="n">
+      <c r="H44" s="162" t="n">
         <f aca="false">IF(Utilidad!D41&gt;1,Utilidad!D41/100,Utilidad!D41)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="160" t="n">
+      <c r="J44" s="159" t="n">
         <f aca="false">+IF(C44&lt;&gt;0,(G44-C44)/C44,ABS(G44-C44))</f>
         <v>0</v>
       </c>
-      <c r="K44" s="160" t="n">
+      <c r="K44" s="159" t="n">
         <f aca="false">+IF(D44&lt;&gt;0,(H44-D44)/D44,0)</f>
         <v>0</v>
       </c>
-      <c r="M44" s="162" t="n">
+      <c r="M44" s="161" t="n">
         <f aca="false">+IF(J44&lt;&gt;"",ABS(J44),0)</f>
         <v>0</v>
       </c>
-      <c r="N44" s="162" t="n">
+      <c r="N44" s="161" t="n">
         <f aca="false">+IF(J44&lt;&gt;"",ABS(K44),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="151" t="s">
+      <c r="B45" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="155" t="n">
+      <c r="C45" s="154" t="n">
         <f aca="false">Utilidad!A42</f>
         <v>0</v>
       </c>
-      <c r="D45" s="156" t="n">
+      <c r="D45" s="155" t="n">
         <f aca="false">IF(Utilidad!C42&gt;1,Utilidad!C42/100,Utilidad!C42)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="151" t="s">
+      <c r="F45" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="G45" s="155" t="n">
+      <c r="G45" s="154" t="n">
         <f aca="false">Utilidad!B42</f>
         <v>0</v>
       </c>
-      <c r="H45" s="163" t="n">
+      <c r="H45" s="162" t="n">
         <f aca="false">IF(Utilidad!D42&gt;1,Utilidad!D42/100,Utilidad!D42)</f>
         <v>0</v>
       </c>
-      <c r="J45" s="160" t="n">
+      <c r="J45" s="159" t="n">
         <f aca="false">+IF(C45&lt;&gt;0,(G45-C45)/C45,ABS(G45-C45))</f>
         <v>0</v>
       </c>
-      <c r="K45" s="160" t="n">
+      <c r="K45" s="159" t="n">
         <f aca="false">+IF(D45&lt;&gt;0,(H45-D45)/D45,0)</f>
         <v>0</v>
       </c>
-      <c r="M45" s="162" t="n">
+      <c r="M45" s="161" t="n">
         <f aca="false">+IF(J45&lt;&gt;"",ABS(J45),0)</f>
         <v>0</v>
       </c>
-      <c r="N45" s="162" t="n">
+      <c r="N45" s="161" t="n">
         <f aca="false">+IF(J45&lt;&gt;"",ABS(K45),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="151" t="s">
+      <c r="B46" s="150" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="155" t="n">
+      <c r="C46" s="154" t="n">
         <f aca="false">Utilidad!A43</f>
         <v>0</v>
       </c>
-      <c r="D46" s="156" t="n">
+      <c r="D46" s="155" t="n">
         <f aca="false">IF(Utilidad!C43&gt;1,Utilidad!C43/100,Utilidad!C43)</f>
         <v>0</v>
       </c>
-      <c r="F46" s="151" t="s">
+      <c r="F46" s="150" t="s">
         <v>91</v>
       </c>
-      <c r="G46" s="155" t="n">
+      <c r="G46" s="154" t="n">
         <f aca="false">Utilidad!B43</f>
         <v>0</v>
       </c>
-      <c r="H46" s="163" t="n">
+      <c r="H46" s="162" t="n">
         <f aca="false">IF(Utilidad!D43&gt;1,Utilidad!D43/100,Utilidad!D43)</f>
         <v>0</v>
       </c>
-      <c r="J46" s="160" t="n">
+      <c r="J46" s="159" t="n">
         <f aca="false">+IF(C46&lt;&gt;0,(G46-C46)/C46,ABS(G46-C46))</f>
         <v>0</v>
       </c>
-      <c r="K46" s="160" t="n">
+      <c r="K46" s="159" t="n">
         <f aca="false">+IF(D46&lt;&gt;0,(H46-D46)/D46,0)</f>
         <v>0</v>
       </c>
-      <c r="M46" s="162" t="n">
+      <c r="M46" s="161" t="n">
         <f aca="false">+IF(J46&lt;&gt;"",ABS(J46),0)</f>
         <v>0</v>
       </c>
-      <c r="N46" s="162" t="n">
+      <c r="N46" s="161" t="n">
         <f aca="false">+IF(J46&lt;&gt;"",ABS(K46),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="151" t="s">
+      <c r="B47" s="150" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="155" t="n">
+      <c r="C47" s="154" t="n">
         <f aca="false">Utilidad!A44</f>
         <v>0</v>
       </c>
-      <c r="D47" s="156" t="n">
+      <c r="D47" s="155" t="n">
         <f aca="false">IF(Utilidad!C44&gt;1,Utilidad!C44/100,Utilidad!C44)</f>
         <v>0</v>
       </c>
-      <c r="F47" s="151" t="s">
+      <c r="F47" s="150" t="s">
         <v>92</v>
       </c>
-      <c r="G47" s="155" t="n">
+      <c r="G47" s="154" t="n">
         <f aca="false">Utilidad!B44</f>
         <v>0</v>
       </c>
-      <c r="H47" s="163" t="n">
+      <c r="H47" s="162" t="n">
         <f aca="false">IF(Utilidad!D44&gt;1,Utilidad!D44/100,Utilidad!D44)</f>
         <v>0</v>
       </c>
-      <c r="J47" s="160" t="n">
+      <c r="J47" s="159" t="n">
         <f aca="false">+IF(C47&lt;&gt;0,(G47-C47)/C47,ABS(G47-C47))</f>
         <v>0</v>
       </c>
-      <c r="K47" s="160" t="n">
+      <c r="K47" s="159" t="n">
         <f aca="false">+IF(D47&lt;&gt;0,(H47-D47)/D47,0)</f>
         <v>0</v>
       </c>
-      <c r="M47" s="162" t="n">
+      <c r="M47" s="161" t="n">
         <f aca="false">+IF(J47&lt;&gt;"",ABS(J47),0)</f>
         <v>0</v>
       </c>
-      <c r="N47" s="162" t="n">
+      <c r="N47" s="161" t="n">
         <f aca="false">+IF(J47&lt;&gt;"",ABS(K47),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="151" t="s">
+      <c r="B48" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="155" t="n">
+      <c r="C48" s="154" t="n">
         <f aca="false">Utilidad!A45</f>
         <v>0</v>
       </c>
-      <c r="D48" s="156" t="n">
+      <c r="D48" s="155" t="n">
         <f aca="false">IF(Utilidad!C45&gt;1,Utilidad!C45/100,Utilidad!C45)</f>
         <v>0</v>
       </c>
-      <c r="F48" s="151" t="s">
+      <c r="F48" s="150" t="s">
         <v>93</v>
       </c>
-      <c r="G48" s="155" t="n">
+      <c r="G48" s="154" t="n">
         <f aca="false">Utilidad!B45</f>
         <v>0</v>
       </c>
-      <c r="H48" s="163" t="n">
+      <c r="H48" s="162" t="n">
         <f aca="false">IF(Utilidad!D45&gt;1,Utilidad!D45/100,Utilidad!D45)</f>
         <v>0</v>
       </c>
-      <c r="J48" s="160" t="n">
+      <c r="J48" s="159" t="n">
         <f aca="false">+IF(C48&lt;&gt;0,(G48-C48)/C48,ABS(G48-C48))</f>
         <v>0</v>
       </c>
-      <c r="K48" s="160" t="n">
+      <c r="K48" s="159" t="n">
         <f aca="false">+IF(D48&lt;&gt;0,(H48-D48)/D48,0)</f>
         <v>0</v>
       </c>
-      <c r="M48" s="162" t="n">
+      <c r="M48" s="161" t="n">
         <f aca="false">+IF(J48&lt;&gt;"",ABS(J48),0)</f>
         <v>0</v>
       </c>
-      <c r="N48" s="162" t="n">
+      <c r="N48" s="161" t="n">
         <f aca="false">+IF(J48&lt;&gt;"",ABS(K48),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="151" t="s">
+      <c r="B49" s="150" t="s">
         <v>94</v>
       </c>
-      <c r="C49" s="155" t="n">
+      <c r="C49" s="154" t="n">
         <f aca="false">Utilidad!A46</f>
         <v>0</v>
       </c>
-      <c r="D49" s="156" t="n">
+      <c r="D49" s="155" t="n">
         <f aca="false">IF(Utilidad!C46&gt;1,Utilidad!C46/100,Utilidad!C46)</f>
         <v>0</v>
       </c>
-      <c r="F49" s="151" t="s">
+      <c r="F49" s="150" t="s">
         <v>94</v>
       </c>
-      <c r="G49" s="155" t="n">
+      <c r="G49" s="154" t="n">
         <f aca="false">Utilidad!B46</f>
         <v>0</v>
       </c>
-      <c r="H49" s="163" t="n">
+      <c r="H49" s="162" t="n">
         <f aca="false">IF(Utilidad!D46&gt;1,Utilidad!D46/100,Utilidad!D46)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="160" t="n">
+      <c r="J49" s="159" t="n">
         <f aca="false">+IF(C49&lt;&gt;0,(G49-C49)/C49,ABS(G49-C49))</f>
         <v>0</v>
       </c>
-      <c r="K49" s="160" t="n">
+      <c r="K49" s="159" t="n">
         <f aca="false">+IF(D49&lt;&gt;0,(H49-D49)/D49,0)</f>
         <v>0</v>
       </c>
-      <c r="M49" s="162" t="n">
+      <c r="M49" s="161" t="n">
         <f aca="false">+IF(J49&lt;&gt;"",ABS(J49),0)</f>
         <v>0</v>
       </c>
-      <c r="N49" s="162" t="n">
+      <c r="N49" s="161" t="n">
         <f aca="false">+IF(J49&lt;&gt;"",ABS(K49),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="151" t="s">
+      <c r="B50" s="150" t="s">
         <v>95</v>
       </c>
-      <c r="C50" s="155" t="n">
+      <c r="C50" s="154" t="n">
         <f aca="false">Utilidad!A47</f>
         <v>0</v>
       </c>
-      <c r="D50" s="156" t="n">
+      <c r="D50" s="155" t="n">
         <f aca="false">IF(Utilidad!C47&gt;1,Utilidad!C47/100,Utilidad!C47)</f>
         <v>0</v>
       </c>
-      <c r="F50" s="151" t="s">
+      <c r="F50" s="150" t="s">
         <v>95</v>
       </c>
-      <c r="G50" s="155" t="n">
+      <c r="G50" s="154" t="n">
         <f aca="false">Utilidad!B47</f>
         <v>0</v>
       </c>
-      <c r="H50" s="163" t="n">
+      <c r="H50" s="162" t="n">
         <f aca="false">IF(Utilidad!D47&gt;1,Utilidad!D47/100,Utilidad!D47)</f>
         <v>0</v>
       </c>
-      <c r="J50" s="160" t="n">
+      <c r="J50" s="159" t="n">
         <f aca="false">+IF(C50&lt;&gt;0,(G50-C50)/C50,ABS(G50-C50))</f>
         <v>0</v>
       </c>
-      <c r="K50" s="160" t="n">
+      <c r="K50" s="159" t="n">
         <f aca="false">+IF(D50&lt;&gt;0,(H50-D50)/D50,0)</f>
         <v>0</v>
       </c>
-      <c r="M50" s="162" t="n">
+      <c r="M50" s="161" t="n">
         <f aca="false">+IF(J50&lt;&gt;"",ABS(J50),0)</f>
         <v>0</v>
       </c>
-      <c r="N50" s="162" t="n">
+      <c r="N50" s="161" t="n">
         <f aca="false">+IF(J50&lt;&gt;"",ABS(K50),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="151" t="s">
+      <c r="B51" s="150" t="s">
         <v>96</v>
       </c>
-      <c r="C51" s="155" t="n">
+      <c r="C51" s="154" t="n">
         <f aca="false">Utilidad!A48</f>
         <v>0</v>
       </c>
-      <c r="D51" s="156" t="n">
+      <c r="D51" s="155" t="n">
         <f aca="false">IF(Utilidad!C48&gt;1,Utilidad!C48/100,Utilidad!C48)</f>
         <v>0</v>
       </c>
-      <c r="F51" s="151" t="s">
+      <c r="F51" s="150" t="s">
         <v>96</v>
       </c>
-      <c r="G51" s="155" t="n">
+      <c r="G51" s="154" t="n">
         <f aca="false">Utilidad!B48</f>
         <v>0</v>
       </c>
-      <c r="H51" s="163" t="n">
+      <c r="H51" s="162" t="n">
         <f aca="false">IF(Utilidad!D48&gt;1,Utilidad!D48/100,Utilidad!D48)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="160" t="n">
+      <c r="J51" s="159" t="n">
         <f aca="false">+IF(C51&lt;&gt;0,(G51-C51)/C51,ABS(G51-C51))</f>
         <v>0</v>
       </c>
-      <c r="K51" s="160" t="n">
+      <c r="K51" s="159" t="n">
         <f aca="false">+IF(D51&lt;&gt;0,(H51-D51)/D51,0)</f>
         <v>0</v>
       </c>
-      <c r="M51" s="162" t="n">
+      <c r="M51" s="161" t="n">
         <f aca="false">+IF(J51&lt;&gt;"",ABS(J51),0)</f>
         <v>0</v>
       </c>
-      <c r="N51" s="162" t="n">
+      <c r="N51" s="161" t="n">
         <f aca="false">+IF(J51&lt;&gt;"",ABS(K51),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="151" t="s">
+      <c r="B52" s="150" t="s">
         <v>97</v>
       </c>
-      <c r="C52" s="155" t="n">
+      <c r="C52" s="154" t="n">
         <f aca="false">Utilidad!A49</f>
         <v>0</v>
       </c>
-      <c r="D52" s="156" t="n">
+      <c r="D52" s="155" t="n">
         <f aca="false">IF(Utilidad!C49&gt;1,Utilidad!C49/100,Utilidad!C49)</f>
         <v>0</v>
       </c>
-      <c r="F52" s="151" t="s">
+      <c r="F52" s="150" t="s">
         <v>97</v>
       </c>
-      <c r="G52" s="155" t="n">
+      <c r="G52" s="154" t="n">
         <f aca="false">Utilidad!B49</f>
         <v>0</v>
       </c>
-      <c r="H52" s="163" t="n">
+      <c r="H52" s="162" t="n">
         <f aca="false">IF(Utilidad!D49&gt;1,Utilidad!D49/100,Utilidad!D49)</f>
         <v>0</v>
       </c>
-      <c r="J52" s="160" t="n">
+      <c r="J52" s="159" t="n">
         <f aca="false">+IF(C52&lt;&gt;0,(G52-C52)/C52,ABS(G52-C52))</f>
         <v>0</v>
       </c>
-      <c r="K52" s="160" t="n">
+      <c r="K52" s="159" t="n">
         <f aca="false">+IF(D52&lt;&gt;0,(H52-D52)/D52,0)</f>
         <v>0</v>
       </c>
-      <c r="M52" s="162" t="n">
+      <c r="M52" s="161" t="n">
         <f aca="false">+IF(J52&lt;&gt;"",ABS(J52),0)</f>
         <v>0</v>
       </c>
-      <c r="N52" s="162" t="n">
+      <c r="N52" s="161" t="n">
         <f aca="false">+IF(J52&lt;&gt;"",ABS(K52),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="151" t="s">
+      <c r="B53" s="150" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="155" t="n">
+      <c r="C53" s="154" t="n">
         <f aca="false">Utilidad!A50</f>
         <v>0</v>
       </c>
-      <c r="D53" s="156" t="n">
+      <c r="D53" s="155" t="n">
         <f aca="false">IF(Utilidad!C50&gt;1,Utilidad!C50/100,Utilidad!C50)</f>
         <v>0</v>
       </c>
-      <c r="F53" s="151" t="s">
+      <c r="F53" s="150" t="s">
         <v>98</v>
       </c>
-      <c r="G53" s="155" t="n">
+      <c r="G53" s="154" t="n">
         <f aca="false">Utilidad!B50</f>
         <v>0</v>
       </c>
-      <c r="H53" s="163" t="n">
+      <c r="H53" s="162" t="n">
         <f aca="false">IF(Utilidad!D50&gt;1,Utilidad!D50/100,Utilidad!D50)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="160" t="n">
+      <c r="J53" s="159" t="n">
         <f aca="false">+IF(C53&lt;&gt;0,(G53-C53)/C53,ABS(G53-C53))</f>
         <v>0</v>
       </c>
-      <c r="K53" s="160" t="n">
+      <c r="K53" s="159" t="n">
         <f aca="false">+IF(D53&lt;&gt;0,(H53-D53)/D53,0)</f>
         <v>0</v>
       </c>
-      <c r="M53" s="162" t="n">
+      <c r="M53" s="161" t="n">
         <f aca="false">+IF(J53&lt;&gt;"",ABS(J53),0)</f>
         <v>0</v>
       </c>
-      <c r="N53" s="162" t="n">
+      <c r="N53" s="161" t="n">
         <f aca="false">+IF(J53&lt;&gt;"",ABS(K53),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="151" t="s">
+      <c r="B54" s="150" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="155" t="n">
+      <c r="C54" s="154" t="n">
         <f aca="false">Utilidad!A51</f>
         <v>0</v>
       </c>
-      <c r="D54" s="156" t="n">
+      <c r="D54" s="155" t="n">
         <f aca="false">IF(Utilidad!C51&gt;1,Utilidad!C51/100,Utilidad!C51)</f>
         <v>0</v>
       </c>
-      <c r="F54" s="151" t="s">
+      <c r="F54" s="150" t="s">
         <v>99</v>
       </c>
-      <c r="G54" s="155" t="n">
+      <c r="G54" s="154" t="n">
         <f aca="false">Utilidad!B51</f>
         <v>0</v>
       </c>
-      <c r="H54" s="163" t="n">
+      <c r="H54" s="162" t="n">
         <f aca="false">IF(Utilidad!D51&gt;1,Utilidad!D51/100,Utilidad!D51)</f>
         <v>0</v>
       </c>
-      <c r="J54" s="160" t="n">
+      <c r="J54" s="159" t="n">
         <f aca="false">+IF(C54&lt;&gt;0,(G54-C54)/C54,ABS(G54-C54))</f>
         <v>0</v>
       </c>
-      <c r="K54" s="160" t="n">
+      <c r="K54" s="159" t="n">
         <f aca="false">+IF(D54&lt;&gt;0,(H54-D54)/D54,0)</f>
         <v>0</v>
       </c>
-      <c r="M54" s="162" t="n">
+      <c r="M54" s="161" t="n">
         <f aca="false">+IF(J54&lt;&gt;"",ABS(J54),0)</f>
         <v>0</v>
       </c>
-      <c r="N54" s="162" t="n">
+      <c r="N54" s="161" t="n">
         <f aca="false">+IF(J54&lt;&gt;"",ABS(K54),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="151" t="s">
+      <c r="B55" s="150" t="s">
         <v>100</v>
       </c>
-      <c r="C55" s="155" t="n">
+      <c r="C55" s="154" t="n">
         <f aca="false">Utilidad!A52</f>
         <v>41596</v>
       </c>
-      <c r="D55" s="156" t="n">
+      <c r="D55" s="155" t="n">
         <f aca="false">IF(Utilidad!C52&gt;1,Utilidad!C52/100,Utilidad!C52)</f>
         <v>0.4527</v>
       </c>
-      <c r="F55" s="151" t="s">
+      <c r="F55" s="150" t="s">
         <v>100</v>
       </c>
-      <c r="G55" s="155" t="n">
+      <c r="G55" s="154" t="n">
         <f aca="false">Utilidad!B52</f>
         <v>41596</v>
       </c>
-      <c r="H55" s="163" t="n">
+      <c r="H55" s="162" t="n">
         <f aca="false">IF(Utilidad!D52&gt;1,Utilidad!D52/100,Utilidad!D52)</f>
         <v>0.4527</v>
       </c>
-      <c r="J55" s="160" t="n">
+      <c r="J55" s="159" t="n">
         <f aca="false">+IF(C55&lt;&gt;0,(G55-C55)/C55,ABS(G55-C55))</f>
         <v>0</v>
       </c>
-      <c r="K55" s="160" t="n">
+      <c r="K55" s="159" t="n">
         <f aca="false">+IF(D55&lt;&gt;0,(H55-D55)/D55,0)</f>
         <v>0</v>
       </c>
-      <c r="M55" s="162" t="n">
+      <c r="M55" s="161" t="n">
         <f aca="false">+IF(J55&lt;&gt;"",ABS(J55),0)</f>
         <v>0</v>
       </c>
-      <c r="N55" s="162" t="n">
+      <c r="N55" s="161" t="n">
         <f aca="false">+IF(J55&lt;&gt;"",ABS(K55),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="151" t="s">
+      <c r="B56" s="150" t="s">
         <v>101</v>
       </c>
-      <c r="C56" s="155" t="n">
+      <c r="C56" s="154" t="n">
         <f aca="false">Utilidad!A53</f>
         <v>41596</v>
       </c>
-      <c r="D56" s="156" t="n">
+      <c r="D56" s="155" t="n">
         <f aca="false">IF(Utilidad!C53&gt;1,Utilidad!C53/100,Utilidad!C53)</f>
         <v>0.4527</v>
       </c>
-      <c r="F56" s="151" t="s">
+      <c r="F56" s="150" t="s">
         <v>101</v>
       </c>
-      <c r="G56" s="155" t="n">
+      <c r="G56" s="154" t="n">
         <f aca="false">Utilidad!B53</f>
         <v>41596</v>
       </c>
-      <c r="H56" s="163" t="n">
+      <c r="H56" s="162" t="n">
         <f aca="false">IF(Utilidad!D53&gt;1,Utilidad!D53/100,Utilidad!D53)</f>
         <v>0.4527</v>
       </c>
-      <c r="J56" s="160" t="n">
+      <c r="J56" s="159" t="n">
         <f aca="false">+IF(C56&lt;&gt;0,(G56-C56)/C56,ABS(G56-C56))</f>
         <v>0</v>
       </c>
-      <c r="K56" s="160" t="n">
+      <c r="K56" s="159" t="n">
         <f aca="false">+IF(D56&lt;&gt;0,(H56-D56)/D56,0)</f>
         <v>0</v>
       </c>
-      <c r="M56" s="162" t="n">
+      <c r="M56" s="161" t="n">
         <f aca="false">+IF(J56&lt;&gt;"",ABS(J56),0)</f>
         <v>0</v>
       </c>
-      <c r="N56" s="162" t="n">
+      <c r="N56" s="161" t="n">
         <f aca="false">+IF(J56&lt;&gt;"",ABS(K56),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="151" t="s">
-        <v>141</v>
-      </c>
-      <c r="C57" s="155" t="n">
+      <c r="B57" s="150" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" s="154" t="n">
         <f aca="false">Utilidad!A54</f>
         <v>5026</v>
       </c>
-      <c r="D57" s="156" t="n">
+      <c r="D57" s="155" t="n">
         <f aca="false">IF(Utilidad!C54&gt;1,Utilidad!C54/100,Utilidad!C54)</f>
         <v>0.6371</v>
       </c>
-      <c r="F57" s="151" t="s">
-        <v>142</v>
-      </c>
-      <c r="G57" s="155" t="n">
+      <c r="F57" s="150" t="s">
+        <v>144</v>
+      </c>
+      <c r="G57" s="154" t="n">
         <f aca="false">Utilidad!B54</f>
         <v>5026</v>
       </c>
-      <c r="H57" s="163" t="n">
+      <c r="H57" s="162" t="n">
         <f aca="false">IF(Utilidad!D54&gt;1,Utilidad!D54/100,Utilidad!D54)</f>
         <v>0.6371</v>
       </c>
-      <c r="J57" s="160" t="n">
+      <c r="J57" s="159" t="n">
         <f aca="false">+IF(C57&lt;&gt;0,(G57-C57)/C57,ABS(G57-C57))</f>
         <v>0</v>
       </c>
-      <c r="K57" s="160" t="n">
+      <c r="K57" s="159" t="n">
         <f aca="false">+IF(D57&lt;&gt;0,(H57-D57)/D57,0)</f>
         <v>0</v>
       </c>
-      <c r="M57" s="162" t="n">
+      <c r="M57" s="161" t="n">
         <f aca="false">+IF(J57&lt;&gt;"",ABS(J57),0)</f>
         <v>0</v>
       </c>
-      <c r="N57" s="162" t="n">
+      <c r="N57" s="161" t="n">
         <f aca="false">+IF(J57&lt;&gt;"",ABS(K57),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="151" t="s">
-        <v>143</v>
-      </c>
-      <c r="C58" s="155" t="n">
+      <c r="B58" s="150" t="s">
+        <v>145</v>
+      </c>
+      <c r="C58" s="154" t="n">
         <f aca="false">Utilidad!A55</f>
         <v>0</v>
       </c>
-      <c r="D58" s="156" t="n">
+      <c r="D58" s="155" t="n">
         <f aca="false">IF(Utilidad!C55&gt;1,Utilidad!C55/100,Utilidad!C55)</f>
         <v>0</v>
       </c>
-      <c r="F58" s="151" t="s">
-        <v>143</v>
-      </c>
-      <c r="G58" s="155" t="n">
+      <c r="F58" s="150" t="s">
+        <v>145</v>
+      </c>
+      <c r="G58" s="154" t="n">
         <f aca="false">Utilidad!B55</f>
         <v>0</v>
       </c>
-      <c r="H58" s="163" t="n">
+      <c r="H58" s="162" t="n">
         <f aca="false">IF(Utilidad!D55&gt;1,Utilidad!D55/100,Utilidad!D55)</f>
         <v>0</v>
       </c>
-      <c r="J58" s="160" t="n">
+      <c r="J58" s="159" t="n">
         <f aca="false">+IF(C58&lt;&gt;0,(G58-C58)/C58,ABS(G58-C58))</f>
         <v>0</v>
       </c>
-      <c r="K58" s="160" t="n">
+      <c r="K58" s="159" t="n">
         <f aca="false">+IF(D58&lt;&gt;0,(H58-D58)/D58,0)</f>
         <v>0</v>
       </c>
-      <c r="M58" s="162" t="n">
+      <c r="M58" s="161" t="n">
         <f aca="false">+IF(J58&lt;&gt;"",ABS(J58),0)</f>
         <v>0</v>
       </c>
-      <c r="N58" s="162" t="n">
+      <c r="N58" s="161" t="n">
         <f aca="false">+IF(J58&lt;&gt;"",ABS(K58),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="151" t="s">
-        <v>144</v>
-      </c>
-      <c r="C59" s="155" t="n">
+      <c r="B59" s="150" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" s="154" t="n">
         <f aca="false">Utilidad!A56</f>
         <v>0</v>
       </c>
-      <c r="D59" s="156" t="n">
+      <c r="D59" s="155" t="n">
         <f aca="false">IF(Utilidad!C56&gt;1,Utilidad!C56/100,Utilidad!C56)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="151" t="s">
-        <v>144</v>
-      </c>
-      <c r="G59" s="155" t="n">
+      <c r="F59" s="150" t="s">
+        <v>146</v>
+      </c>
+      <c r="G59" s="154" t="n">
         <f aca="false">Utilidad!B56</f>
         <v>0</v>
       </c>
-      <c r="H59" s="163" t="n">
+      <c r="H59" s="162" t="n">
         <f aca="false">IF(Utilidad!D56&gt;1,Utilidad!D56/100,Utilidad!D56)</f>
         <v>0</v>
       </c>
-      <c r="J59" s="160" t="n">
+      <c r="J59" s="159" t="n">
         <f aca="false">+IF(C59&lt;&gt;0,(G59-C59)/C59,ABS(G59-C59))</f>
         <v>0</v>
       </c>
-      <c r="K59" s="160" t="n">
+      <c r="K59" s="159" t="n">
         <f aca="false">+IF(D59&lt;&gt;0,(H59-D59)/D59,0)</f>
         <v>0</v>
       </c>
-      <c r="M59" s="162" t="n">
+      <c r="M59" s="161" t="n">
         <f aca="false">+IF(J59&lt;&gt;"",ABS(J59),0)</f>
         <v>0</v>
       </c>
-      <c r="N59" s="162" t="n">
+      <c r="N59" s="161" t="n">
         <f aca="false">+IF(J59&lt;&gt;"",ABS(K59),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="151" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" s="155" t="n">
+      <c r="B60" s="150" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" s="154" t="n">
         <f aca="false">Utilidad!A57</f>
         <v>2106</v>
       </c>
-      <c r="D60" s="156" t="n">
+      <c r="D60" s="155" t="n">
         <f aca="false">IF(Utilidad!C57&gt;1,Utilidad!C57/100,Utilidad!C57)</f>
         <v>0.6321</v>
       </c>
-      <c r="F60" s="151" t="s">
-        <v>145</v>
-      </c>
-      <c r="G60" s="155" t="n">
+      <c r="F60" s="150" t="s">
+        <v>147</v>
+      </c>
+      <c r="G60" s="154" t="n">
         <f aca="false">Utilidad!B57</f>
         <v>2106</v>
       </c>
-      <c r="H60" s="163" t="n">
+      <c r="H60" s="162" t="n">
         <f aca="false">IF(Utilidad!D57&gt;1,Utilidad!D57/100,Utilidad!D57)</f>
         <v>0.6321</v>
       </c>
-      <c r="J60" s="160" t="n">
+      <c r="J60" s="159" t="n">
         <f aca="false">+IF(C60&lt;&gt;0,(G60-C60)/C60,ABS(G60-C60))</f>
         <v>0</v>
       </c>
-      <c r="K60" s="160" t="n">
+      <c r="K60" s="159" t="n">
         <f aca="false">+IF(D60&lt;&gt;0,(H60-D60)/D60,0)</f>
         <v>0</v>
       </c>
-      <c r="M60" s="162" t="n">
+      <c r="M60" s="161" t="n">
         <f aca="false">+IF(J60&lt;&gt;"",ABS(J60),0)</f>
         <v>0</v>
       </c>
-      <c r="N60" s="162" t="n">
+      <c r="N60" s="161" t="n">
         <f aca="false">+IF(J60&lt;&gt;"",ABS(K60),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="151" t="s">
-        <v>146</v>
-      </c>
-      <c r="C61" s="155" t="n">
+      <c r="B61" s="150" t="s">
+        <v>148</v>
+      </c>
+      <c r="C61" s="154" t="n">
         <f aca="false">Utilidad!A58</f>
         <v>0</v>
       </c>
-      <c r="D61" s="156" t="n">
+      <c r="D61" s="155" t="n">
         <f aca="false">IF(Utilidad!C58&gt;1,Utilidad!C58/100,Utilidad!C58)</f>
         <v>0</v>
       </c>
-      <c r="F61" s="151" t="s">
-        <v>146</v>
-      </c>
-      <c r="G61" s="155" t="n">
+      <c r="F61" s="150" t="s">
+        <v>148</v>
+      </c>
+      <c r="G61" s="154" t="n">
         <f aca="false">Utilidad!B58</f>
         <v>0</v>
       </c>
-      <c r="H61" s="163" t="n">
+      <c r="H61" s="162" t="n">
         <f aca="false">IF(Utilidad!D58&gt;1,Utilidad!D58/100,Utilidad!D58)</f>
         <v>0</v>
       </c>
-      <c r="J61" s="160" t="n">
+      <c r="J61" s="159" t="n">
         <f aca="false">+IF(C61&lt;&gt;0,(G61-C61)/C61,ABS(G61-C61))</f>
         <v>0</v>
       </c>
-      <c r="K61" s="160" t="n">
+      <c r="K61" s="159" t="n">
         <f aca="false">+IF(D61&lt;&gt;0,(H61-D61)/D61,0)</f>
         <v>0</v>
       </c>
-      <c r="M61" s="162" t="n">
+      <c r="M61" s="161" t="n">
         <f aca="false">+IF(J61&lt;&gt;"",ABS(J61),0)</f>
         <v>0</v>
       </c>
-      <c r="N61" s="162" t="n">
+      <c r="N61" s="161" t="n">
         <f aca="false">+IF(J61&lt;&gt;"",ABS(K61),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="151" t="s">
-        <v>147</v>
-      </c>
-      <c r="C62" s="155" t="n">
+      <c r="B62" s="150" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" s="154" t="n">
         <f aca="false">Utilidad!A59</f>
         <v>0</v>
       </c>
-      <c r="D62" s="156" t="n">
+      <c r="D62" s="155" t="n">
         <f aca="false">IF(Utilidad!C59&gt;1,Utilidad!C59/100,Utilidad!C59)</f>
         <v>0</v>
       </c>
-      <c r="F62" s="151" t="s">
-        <v>147</v>
-      </c>
-      <c r="G62" s="155" t="n">
+      <c r="F62" s="150" t="s">
+        <v>149</v>
+      </c>
+      <c r="G62" s="154" t="n">
         <f aca="false">Utilidad!B59</f>
         <v>0</v>
       </c>
-      <c r="H62" s="163" t="n">
+      <c r="H62" s="162" t="n">
         <f aca="false">IF(Utilidad!D59&gt;1,Utilidad!D59/100,Utilidad!D59)</f>
         <v>0</v>
       </c>
-      <c r="J62" s="160" t="n">
+      <c r="J62" s="159" t="n">
         <f aca="false">+IF(C62&lt;&gt;0,(G62-C62)/C62,ABS(G62-C62))</f>
         <v>0</v>
       </c>
-      <c r="K62" s="160" t="n">
+      <c r="K62" s="159" t="n">
         <f aca="false">+IF(D62&lt;&gt;0,(H62-D62)/D62,0)</f>
         <v>0</v>
       </c>
-      <c r="M62" s="162" t="n">
+      <c r="M62" s="161" t="n">
         <f aca="false">+IF(J62&lt;&gt;"",ABS(J62),0)</f>
         <v>0</v>
       </c>
-      <c r="N62" s="162" t="n">
+      <c r="N62" s="161" t="n">
         <f aca="false">+IF(J62&lt;&gt;"",ABS(K62),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="151" t="s">
-        <v>148</v>
-      </c>
-      <c r="C63" s="155" t="n">
+      <c r="B63" s="150" t="s">
+        <v>150</v>
+      </c>
+      <c r="C63" s="154" t="n">
         <f aca="false">Utilidad!A60</f>
         <v>0</v>
       </c>
-      <c r="D63" s="156" t="n">
+      <c r="D63" s="155" t="n">
         <f aca="false">IF(Utilidad!C60&gt;1,Utilidad!C60/100,Utilidad!C60)</f>
         <v>0</v>
       </c>
-      <c r="F63" s="151" t="s">
-        <v>148</v>
-      </c>
-      <c r="G63" s="155" t="n">
+      <c r="F63" s="150" t="s">
+        <v>150</v>
+      </c>
+      <c r="G63" s="154" t="n">
         <f aca="false">Utilidad!B60</f>
         <v>0</v>
       </c>
-      <c r="H63" s="163" t="n">
+      <c r="H63" s="162" t="n">
         <f aca="false">IF(Utilidad!D60&gt;1,Utilidad!D60/100,Utilidad!D60)</f>
         <v>0</v>
       </c>
-      <c r="J63" s="160" t="n">
+      <c r="J63" s="159" t="n">
         <f aca="false">+IF(C63&lt;&gt;0,(G63-C63)/C63,ABS(G63-C63))</f>
         <v>0</v>
       </c>
-      <c r="K63" s="160" t="n">
+      <c r="K63" s="159" t="n">
         <f aca="false">+IF(D63&lt;&gt;0,(H63-D63)/D63,0)</f>
         <v>0</v>
       </c>
-      <c r="M63" s="162" t="n">
+      <c r="M63" s="161" t="n">
         <f aca="false">+IF(J63&lt;&gt;"",ABS(J63),0)</f>
         <v>0</v>
       </c>
-      <c r="N63" s="162" t="n">
+      <c r="N63" s="161" t="n">
         <f aca="false">+IF(J63&lt;&gt;"",ABS(K63),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="151" t="s">
-        <v>149</v>
-      </c>
-      <c r="C64" s="155" t="n">
+      <c r="B64" s="150" t="s">
+        <v>151</v>
+      </c>
+      <c r="C64" s="154" t="n">
         <f aca="false">Utilidad!A61</f>
         <v>0</v>
       </c>
-      <c r="D64" s="156" t="n">
+      <c r="D64" s="155" t="n">
         <f aca="false">IF(Utilidad!C61&gt;1,Utilidad!C61/100,Utilidad!C61)</f>
         <v>0</v>
       </c>
-      <c r="F64" s="151" t="s">
-        <v>149</v>
-      </c>
-      <c r="G64" s="155" t="n">
+      <c r="F64" s="150" t="s">
+        <v>151</v>
+      </c>
+      <c r="G64" s="154" t="n">
         <f aca="false">Utilidad!B61</f>
         <v>0</v>
       </c>
-      <c r="H64" s="163" t="n">
+      <c r="H64" s="162" t="n">
         <f aca="false">IF(Utilidad!D61&gt;1,Utilidad!D61/100,Utilidad!D61)</f>
         <v>0</v>
       </c>
-      <c r="J64" s="160" t="n">
+      <c r="J64" s="159" t="n">
         <f aca="false">+IF(C64&lt;&gt;0,(G64-C64)/C64,ABS(G64-C64))</f>
         <v>0</v>
       </c>
-      <c r="K64" s="160" t="n">
+      <c r="K64" s="159" t="n">
         <f aca="false">+IF(D64&lt;&gt;0,(H64-D64)/D64,0)</f>
         <v>0</v>
       </c>
-      <c r="M64" s="162" t="n">
+      <c r="M64" s="161" t="n">
         <f aca="false">+IF(J64&lt;&gt;"",ABS(J64),0)</f>
         <v>0</v>
       </c>
-      <c r="N64" s="162" t="n">
+      <c r="N64" s="161" t="n">
         <f aca="false">+IF(J64&lt;&gt;"",ABS(K64),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="151" t="s">
-        <v>36</v>
-      </c>
-      <c r="C65" s="155" t="n">
+      <c r="B65" s="167" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" s="154" t="n">
         <f aca="false">Utilidad!A62</f>
         <v>2055</v>
       </c>
-      <c r="D65" s="156" t="n">
+      <c r="D65" s="155" t="n">
         <f aca="false">IF(Utilidad!C62&gt;1,Utilidad!C62/100,Utilidad!C62)</f>
         <v>0.5607</v>
       </c>
-      <c r="F65" s="151" t="s">
-        <v>36</v>
-      </c>
-      <c r="G65" s="155" t="n">
+      <c r="F65" s="167" t="s">
+        <v>152</v>
+      </c>
+      <c r="G65" s="154" t="n">
         <f aca="false">Utilidad!B62</f>
         <v>2055</v>
       </c>
-      <c r="H65" s="163" t="n">
+      <c r="H65" s="162" t="n">
         <f aca="false">IF(Utilidad!D62&gt;1,Utilidad!D62/100,Utilidad!D62)</f>
         <v>0.5607</v>
       </c>
-      <c r="J65" s="160" t="n">
+      <c r="J65" s="159" t="n">
         <f aca="false">+IF(C65&lt;&gt;0,(G65-C65)/C65,ABS(G65-C65))</f>
         <v>0</v>
       </c>
-      <c r="K65" s="160" t="n">
+      <c r="K65" s="159" t="n">
         <f aca="false">+IF(D65&lt;&gt;0,(H65-D65)/D65,0)</f>
         <v>0</v>
       </c>
-      <c r="M65" s="162" t="n">
+      <c r="M65" s="161" t="n">
         <f aca="false">+IF(J65&lt;&gt;"",ABS(J65),0)</f>
         <v>0</v>
       </c>
-      <c r="N65" s="162" t="n">
+      <c r="N65" s="161" t="n">
         <f aca="false">+IF(J65&lt;&gt;"",ABS(K65),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="151" t="s">
+      <c r="B66" s="150" t="s">
         <v>119</v>
       </c>
-      <c r="C66" s="155" t="n">
+      <c r="C66" s="154" t="n">
         <f aca="false">Utilidad!A63</f>
         <v>0</v>
       </c>
-      <c r="D66" s="156" t="n">
+      <c r="D66" s="155" t="n">
         <f aca="false">IF(Utilidad!C63&gt;1,Utilidad!C63/100,Utilidad!C63)</f>
         <v>0</v>
       </c>
-      <c r="F66" s="151" t="s">
+      <c r="F66" s="150" t="s">
         <v>119</v>
       </c>
-      <c r="G66" s="155" t="n">
+      <c r="G66" s="154" t="n">
         <f aca="false">Utilidad!B63</f>
         <v>0</v>
       </c>
-      <c r="H66" s="163" t="n">
+      <c r="H66" s="162" t="n">
         <f aca="false">IF(Utilidad!D63&gt;1,Utilidad!D63/100,Utilidad!D63)</f>
         <v>0</v>
       </c>
-      <c r="J66" s="160" t="n">
+      <c r="J66" s="159" t="n">
         <f aca="false">+IF(C66&lt;&gt;0,(G66-C66)/C66,ABS(G66-C66))</f>
         <v>0</v>
       </c>
-      <c r="K66" s="160" t="n">
+      <c r="K66" s="159" t="n">
         <f aca="false">+IF(D66&lt;&gt;0,(H66-D66)/D66,0)</f>
         <v>0</v>
       </c>
-      <c r="M66" s="162" t="n">
+      <c r="M66" s="161" t="n">
         <f aca="false">+IF(J66&lt;&gt;"",ABS(J66),0)</f>
         <v>0</v>
       </c>
-      <c r="N66" s="162" t="n">
+      <c r="N66" s="161" t="n">
         <f aca="false">+IF(J66&lt;&gt;"",ABS(K66),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="151" t="s">
+      <c r="B67" s="150" t="s">
         <v>120</v>
       </c>
-      <c r="C67" s="155" t="n">
+      <c r="C67" s="154" t="n">
         <f aca="false">Utilidad!A64</f>
         <v>0</v>
       </c>
-      <c r="D67" s="156" t="n">
+      <c r="D67" s="155" t="n">
         <f aca="false">IF(Utilidad!C64&gt;1,Utilidad!C64/100,Utilidad!C64)</f>
         <v>0</v>
       </c>
-      <c r="F67" s="151" t="s">
+      <c r="F67" s="150" t="s">
         <v>120</v>
       </c>
-      <c r="G67" s="155" t="n">
+      <c r="G67" s="154" t="n">
         <f aca="false">Utilidad!B64</f>
         <v>0</v>
       </c>
-      <c r="H67" s="163" t="n">
+      <c r="H67" s="162" t="n">
         <f aca="false">IF(Utilidad!D64&gt;1,Utilidad!D64/100,Utilidad!D64)</f>
         <v>0</v>
       </c>
-      <c r="J67" s="160" t="n">
+      <c r="J67" s="159" t="n">
         <f aca="false">+IF(C67&lt;&gt;0,(G67-C67)/C67,ABS(G67-C67))</f>
         <v>0</v>
       </c>
-      <c r="K67" s="160" t="n">
+      <c r="K67" s="159" t="n">
         <f aca="false">+IF(D67&lt;&gt;0,(H67-D67)/D67,0)</f>
         <v>0</v>
       </c>
-      <c r="M67" s="162" t="n">
+      <c r="M67" s="161" t="n">
         <f aca="false">+IF(J67&lt;&gt;"",ABS(J67),0)</f>
         <v>0</v>
       </c>
-      <c r="N67" s="162" t="n">
+      <c r="N67" s="161" t="n">
         <f aca="false">+IF(J67&lt;&gt;"",ABS(K67),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="151" t="s">
-        <v>150</v>
-      </c>
-      <c r="C68" s="155" t="n">
+      <c r="B68" s="150" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="154" t="n">
         <f aca="false">Utilidad!A65</f>
         <v>0</v>
       </c>
-      <c r="D68" s="156" t="n">
+      <c r="D68" s="155" t="n">
         <f aca="false">IF(Utilidad!C65&gt;1,Utilidad!C65/100,Utilidad!C65)</f>
         <v>0</v>
       </c>
-      <c r="F68" s="151" t="s">
-        <v>150</v>
-      </c>
-      <c r="G68" s="155" t="n">
+      <c r="F68" s="168" t="s">
+        <v>154</v>
+      </c>
+      <c r="G68" s="154" t="n">
         <f aca="false">Utilidad!B65</f>
         <v>0</v>
       </c>
-      <c r="H68" s="163" t="n">
+      <c r="H68" s="162" t="n">
         <f aca="false">IF(Utilidad!D65&gt;1,Utilidad!D65/100,Utilidad!D65)</f>
         <v>0</v>
       </c>
-      <c r="J68" s="160" t="n">
+      <c r="J68" s="159" t="n">
         <f aca="false">+IF(C68&lt;&gt;0,(G68-C68)/C68,ABS(G68-C68))</f>
         <v>0</v>
       </c>
-      <c r="K68" s="160" t="n">
+      <c r="K68" s="159" t="n">
         <f aca="false">+IF(D68&lt;&gt;0,(H68-D68)/D68,0)</f>
         <v>0</v>
       </c>
-      <c r="M68" s="162" t="n">
+      <c r="M68" s="161" t="n">
         <f aca="false">+IF(J68&lt;&gt;"",ABS(J68),0)</f>
         <v>0</v>
       </c>
-      <c r="N68" s="162" t="n">
+      <c r="N68" s="161" t="n">
         <f aca="false">+IF(J68&lt;&gt;"",ABS(K68),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="151" t="s">
-        <v>151</v>
-      </c>
-      <c r="C69" s="155" t="n">
+      <c r="B69" s="150" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" s="154" t="n">
         <f aca="false">Utilidad!A66</f>
         <v>2055</v>
       </c>
-      <c r="D69" s="156" t="n">
+      <c r="D69" s="155" t="n">
         <f aca="false">IF(Utilidad!C66&gt;1,Utilidad!C66/100,Utilidad!C66)</f>
         <v>0.5607</v>
       </c>
-      <c r="F69" s="151" t="s">
-        <v>151</v>
-      </c>
-      <c r="G69" s="155" t="n">
+      <c r="F69" s="150" t="s">
+        <v>155</v>
+      </c>
+      <c r="G69" s="154" t="n">
         <f aca="false">Utilidad!B66</f>
         <v>2055</v>
       </c>
-      <c r="H69" s="163" t="n">
+      <c r="H69" s="162" t="n">
         <f aca="false">IF(Utilidad!D66&gt;1,Utilidad!D66/100,Utilidad!D66)</f>
         <v>0.5607</v>
       </c>
-      <c r="J69" s="160" t="n">
+      <c r="J69" s="159" t="n">
         <f aca="false">+IF(C69&lt;&gt;0,(G69-C69)/C69,ABS(G69-C69))</f>
         <v>0</v>
       </c>
-      <c r="K69" s="160" t="n">
+      <c r="K69" s="159" t="n">
         <f aca="false">+IF(D69&lt;&gt;0,(H69-D69)/D69,0)</f>
         <v>0</v>
       </c>
-      <c r="M69" s="162" t="n">
+      <c r="M69" s="161" t="n">
         <f aca="false">+IF(J69&lt;&gt;"",ABS(J69),0)</f>
         <v>0</v>
       </c>
-      <c r="N69" s="162" t="n">
+      <c r="N69" s="161" t="n">
         <f aca="false">+IF(J69&lt;&gt;"",ABS(K69),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="151" t="s">
+      <c r="B70" s="150" t="s">
         <v>121</v>
       </c>
-      <c r="C70" s="155" t="n">
+      <c r="C70" s="154" t="n">
         <f aca="false">Utilidad!A67</f>
         <v>392</v>
       </c>
-      <c r="D70" s="156" t="n">
+      <c r="D70" s="155" t="n">
         <f aca="false">IF(Utilidad!C67&gt;1,Utilidad!C67/100,Utilidad!C67)</f>
         <v>0.5253</v>
       </c>
-      <c r="F70" s="151" t="s">
+      <c r="F70" s="150" t="s">
         <v>121</v>
       </c>
-      <c r="G70" s="155" t="n">
+      <c r="G70" s="154" t="n">
         <f aca="false">Utilidad!B67</f>
         <v>392</v>
       </c>
-      <c r="H70" s="163" t="n">
+      <c r="H70" s="162" t="n">
         <f aca="false">IF(Utilidad!D67&gt;1,Utilidad!D67/100,Utilidad!D67)</f>
         <v>0.5253</v>
       </c>
-      <c r="J70" s="160" t="n">
+      <c r="J70" s="159" t="n">
         <f aca="false">+IF(C70&lt;&gt;0,(G70-C70)/C70,ABS(G70-C70))</f>
         <v>0</v>
       </c>
-      <c r="K70" s="160" t="n">
+      <c r="K70" s="159" t="n">
         <f aca="false">+IF(D70&lt;&gt;0,(H70-D70)/D70,0)</f>
         <v>0</v>
       </c>
-      <c r="M70" s="162" t="n">
+      <c r="M70" s="161" t="n">
         <f aca="false">+IF(J70&lt;&gt;"",ABS(J70),0)</f>
         <v>0</v>
       </c>
-      <c r="N70" s="162" t="n">
+      <c r="N70" s="161" t="n">
         <f aca="false">+IF(J70&lt;&gt;"",ABS(K70),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="151" t="s">
+      <c r="B71" s="150" t="s">
         <v>122</v>
       </c>
-      <c r="C71" s="155" t="n">
+      <c r="C71" s="154" t="n">
         <f aca="false">Utilidad!A68</f>
         <v>441</v>
       </c>
-      <c r="D71" s="156" t="n">
+      <c r="D71" s="155" t="n">
         <f aca="false">IF(Utilidad!C68&gt;1,Utilidad!C68/100,Utilidad!C68)</f>
         <v>0.549</v>
       </c>
-      <c r="F71" s="151" t="s">
+      <c r="F71" s="150" t="s">
         <v>122</v>
       </c>
-      <c r="G71" s="155" t="n">
+      <c r="G71" s="154" t="n">
         <f aca="false">Utilidad!B68</f>
         <v>441</v>
       </c>
-      <c r="H71" s="163" t="n">
+      <c r="H71" s="162" t="n">
         <f aca="false">IF(Utilidad!D68&gt;1,Utilidad!D68/100,Utilidad!D68)</f>
         <v>0.549</v>
       </c>
-      <c r="J71" s="160" t="n">
+      <c r="J71" s="159" t="n">
         <f aca="false">+IF(C71&lt;&gt;0,(G71-C71)/C71,ABS(G71-C71))</f>
         <v>0</v>
       </c>
-      <c r="K71" s="160" t="n">
+      <c r="K71" s="159" t="n">
         <f aca="false">+IF(D71&lt;&gt;0,(H71-D71)/D71,0)</f>
         <v>0</v>
       </c>
-      <c r="M71" s="162" t="n">
+      <c r="M71" s="161" t="n">
         <f aca="false">+IF(J71&lt;&gt;"",ABS(J71),0)</f>
         <v>0</v>
       </c>
-      <c r="N71" s="162" t="n">
+      <c r="N71" s="161" t="n">
         <f aca="false">+IF(J71&lt;&gt;"",ABS(K71),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B72" s="151" t="s">
-        <v>152</v>
-      </c>
-      <c r="C72" s="155" t="n">
+      <c r="B72" s="150" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="154" t="n">
         <f aca="false">Utilidad!A69</f>
         <v>0</v>
       </c>
-      <c r="D72" s="156" t="n">
+      <c r="D72" s="155" t="n">
         <f aca="false">IF(Utilidad!C69&gt;1,Utilidad!C69/100,Utilidad!C69)</f>
         <v>0</v>
       </c>
-      <c r="F72" s="151" t="s">
-        <v>152</v>
-      </c>
-      <c r="G72" s="155" t="n">
+      <c r="F72" s="150" t="s">
+        <v>156</v>
+      </c>
+      <c r="G72" s="154" t="n">
         <f aca="false">Utilidad!B69</f>
         <v>0</v>
       </c>
-      <c r="H72" s="163" t="n">
+      <c r="H72" s="162" t="n">
         <f aca="false">IF(Utilidad!D69&gt;1,Utilidad!D69/100,Utilidad!D69)</f>
         <v>0</v>
       </c>
-      <c r="J72" s="160" t="n">
+      <c r="J72" s="159" t="n">
         <f aca="false">+IF(C72&lt;&gt;0,(G72-C72)/C72,ABS(G72-C72))</f>
         <v>0</v>
       </c>
-      <c r="K72" s="160" t="n">
+      <c r="K72" s="159" t="n">
         <f aca="false">+IF(D72&lt;&gt;0,(H72-D72)/D72,0)</f>
         <v>0</v>
       </c>
-      <c r="M72" s="162" t="n">
+      <c r="M72" s="161" t="n">
         <f aca="false">+IF(J72&lt;&gt;"",ABS(J72),0)</f>
         <v>0</v>
       </c>
-      <c r="N72" s="162" t="n">
+      <c r="N72" s="161" t="n">
         <f aca="false">+IF(J72&lt;&gt;"",ABS(K72),0)</f>
         <v>0</v>
       </c>
@@ -20503,315 +20593,315 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="168"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="169"/>
-      <c r="Q2" s="169"/>
-      <c r="R2" s="169"/>
-      <c r="S2" s="170"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
+      <c r="L2" s="170"/>
+      <c r="M2" s="170"/>
+      <c r="N2" s="170"/>
+      <c r="O2" s="170"/>
+      <c r="P2" s="170"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="170"/>
+      <c r="S2" s="171"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="171"/>
-      <c r="S3" s="172"/>
+      <c r="B3" s="172"/>
+      <c r="S3" s="173"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="171"/>
-      <c r="S4" s="172"/>
+      <c r="B4" s="172"/>
+      <c r="S4" s="173"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="171"/>
-      <c r="S5" s="172"/>
+      <c r="B5" s="172"/>
+      <c r="S5" s="173"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="171"/>
-      <c r="E6" s="173" t="n">
+      <c r="B6" s="172"/>
+      <c r="E6" s="174" t="n">
         <f aca="false">Flujos!G4</f>
         <v>122150</v>
       </c>
-      <c r="S6" s="172"/>
+      <c r="S6" s="173"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="171"/>
-      <c r="E7" s="174" t="n">
+      <c r="B7" s="172"/>
+      <c r="E7" s="175" t="n">
         <f aca="false">Flujos!H4</f>
         <v>0.29498952501</v>
       </c>
-      <c r="I7" s="173" t="n">
+      <c r="I7" s="174" t="n">
         <f aca="false">+Utilidad!J65</f>
         <v>0</v>
       </c>
-      <c r="L7" s="175" t="n">
+      <c r="L7" s="176" t="n">
         <f aca="false">+Utilidad!J68</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="175" t="n">
+      <c r="Q7" s="176" t="n">
         <f aca="false">Flujos!G12</f>
         <v>21435.044983</v>
       </c>
-      <c r="S7" s="172"/>
+      <c r="S7" s="173"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="171"/>
-      <c r="E8" s="176" t="n">
+      <c r="B8" s="172"/>
+      <c r="E8" s="177" t="n">
         <f aca="false">E6*E7</f>
         <v>36032.9704799715</v>
       </c>
-      <c r="I8" s="174" t="n">
+      <c r="I8" s="175" t="n">
         <f aca="false">+Utilidad!K65</f>
         <v>0</v>
       </c>
-      <c r="L8" s="177" t="n">
+      <c r="L8" s="178" t="n">
         <f aca="false">+Utilidad!K68</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="177" t="n">
+      <c r="Q8" s="178" t="n">
         <f aca="false">Flujos!H12</f>
         <v>0.15974666492</v>
       </c>
-      <c r="S8" s="172"/>
+      <c r="S8" s="173"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="171"/>
-      <c r="I9" s="176" t="n">
+      <c r="B9" s="172"/>
+      <c r="I9" s="177" t="n">
         <f aca="false">+Utilidad!L65</f>
         <v>0</v>
       </c>
-      <c r="L9" s="178" t="n">
+      <c r="L9" s="179" t="n">
         <f aca="false">+Utilidad!L68</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="178" t="n">
+      <c r="Q9" s="179" t="n">
         <f aca="false">Q7*Q8</f>
         <v>3424.17694844443</v>
       </c>
-      <c r="S9" s="172"/>
+      <c r="S9" s="173"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="171"/>
-      <c r="E10" s="173" t="n">
+      <c r="B10" s="172"/>
+      <c r="E10" s="174" t="n">
         <f aca="false">+Utilidad!J63</f>
         <v>0</v>
       </c>
-      <c r="S10" s="172"/>
+      <c r="S10" s="173"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="171"/>
-      <c r="E11" s="174" t="n">
+      <c r="B11" s="172"/>
+      <c r="E11" s="175" t="n">
         <f aca="false">+Utilidad!K63</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="175" t="n">
+      <c r="Q11" s="176" t="n">
         <f aca="false">+Utilidad!J71</f>
         <v>12796.955017</v>
       </c>
-      <c r="S11" s="172"/>
+      <c r="S11" s="173"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="171"/>
-      <c r="C12" s="173" t="n">
+      <c r="B12" s="172"/>
+      <c r="C12" s="174" t="n">
         <f aca="false">+Utilidad!J101</f>
         <v>0</v>
       </c>
-      <c r="E12" s="176" t="n">
+      <c r="E12" s="177" t="n">
         <f aca="false">+Utilidad!L63</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="177" t="n">
+      <c r="Q12" s="178" t="n">
         <f aca="false">+Utilidad!K71</f>
         <v>0.082951951265</v>
       </c>
-      <c r="S12" s="172"/>
+      <c r="S12" s="173"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="171"/>
-      <c r="C13" s="174" t="n">
+      <c r="B13" s="172"/>
+      <c r="C13" s="175" t="n">
         <f aca="false">+Utilidad!K101</f>
         <v>0</v>
       </c>
-      <c r="H13" s="179" t="n">
+      <c r="H13" s="180" t="n">
         <f aca="false">+Utilidad!J66</f>
         <v>0</v>
       </c>
-      <c r="N13" s="173" t="n">
+      <c r="N13" s="174" t="n">
         <f aca="false">+Utilidad!J72</f>
         <v>41025</v>
       </c>
-      <c r="Q13" s="178" t="n">
+      <c r="Q13" s="179" t="n">
         <f aca="false">+Utilidad!L71</f>
         <v>1061.53238891058</v>
       </c>
-      <c r="S13" s="172"/>
+      <c r="S13" s="173"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="171"/>
-      <c r="C14" s="176" t="n">
+      <c r="B14" s="172"/>
+      <c r="C14" s="177" t="n">
         <f aca="false">+Utilidad!L101</f>
         <v>0</v>
       </c>
-      <c r="H14" s="180" t="n">
+      <c r="H14" s="181" t="n">
         <f aca="false">+Utilidad!K66</f>
         <v>0</v>
       </c>
-      <c r="J14" s="181" t="n">
+      <c r="J14" s="182" t="n">
         <f aca="false">+I7+H13-L14-L7</f>
         <v>0</v>
       </c>
-      <c r="L14" s="175" t="n">
+      <c r="L14" s="176" t="n">
         <f aca="false">+Utilidad!J69</f>
         <v>0</v>
       </c>
-      <c r="N14" s="174" t="n">
+      <c r="N14" s="175" t="n">
         <f aca="false">+Utilidad!K72</f>
         <v>0.42098</v>
       </c>
-      <c r="S14" s="172"/>
+      <c r="S14" s="173"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="171"/>
-      <c r="G15" s="182" t="n">
+      <c r="B15" s="172"/>
+      <c r="G15" s="183" t="n">
         <f aca="false">Flujos!G6</f>
         <v>26963</v>
       </c>
-      <c r="H15" s="183" t="n">
+      <c r="H15" s="184" t="n">
         <f aca="false">+Utilidad!L66</f>
         <v>0</v>
       </c>
-      <c r="L15" s="177" t="n">
+      <c r="L15" s="178" t="n">
         <f aca="false">+Utilidad!K69</f>
         <v>0</v>
       </c>
-      <c r="N15" s="176" t="n">
+      <c r="N15" s="177" t="n">
         <f aca="false">+Utilidad!L72</f>
         <v>17270.7045</v>
       </c>
-      <c r="S15" s="172"/>
+      <c r="S15" s="173"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="171"/>
-      <c r="E16" s="184" t="n">
+      <c r="B16" s="172"/>
+      <c r="E16" s="185" t="n">
         <f aca="false">+C12-E10</f>
         <v>0</v>
       </c>
-      <c r="G16" s="185" t="n">
+      <c r="G16" s="186" t="n">
         <f aca="false">Flujos!H6</f>
         <v>0.1206</v>
       </c>
-      <c r="L16" s="178" t="n">
+      <c r="L16" s="179" t="n">
         <f aca="false">+Utilidad!L69</f>
         <v>0</v>
       </c>
       <c r="P16" s="126" t="s">
         <v>121</v>
       </c>
-      <c r="S16" s="172"/>
+      <c r="S16" s="173"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="171"/>
-      <c r="G17" s="186" t="n">
+      <c r="B17" s="172"/>
+      <c r="G17" s="187" t="n">
         <f aca="false">G15*G16</f>
         <v>3251.7378</v>
       </c>
-      <c r="P17" s="175" t="n">
+      <c r="P17" s="176" t="n">
         <f aca="false">Flujos!G70</f>
         <v>392</v>
       </c>
-      <c r="S17" s="172"/>
+      <c r="S17" s="173"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="171"/>
-      <c r="K18" s="173" t="n">
+      <c r="B18" s="172"/>
+      <c r="K18" s="174" t="n">
         <f aca="false">Flujos!C56</f>
         <v>41596</v>
       </c>
-      <c r="P18" s="177" t="n">
+      <c r="P18" s="178" t="n">
         <f aca="false">Flujos!H70</f>
         <v>0.5253</v>
       </c>
-      <c r="S18" s="172"/>
+      <c r="S18" s="173"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="171"/>
-      <c r="K19" s="174" t="n">
+      <c r="B19" s="172"/>
+      <c r="K19" s="175" t="n">
         <f aca="false">Flujos!D56</f>
         <v>0.4527</v>
       </c>
-      <c r="P19" s="178" t="n">
+      <c r="P19" s="179" t="n">
         <f aca="false">P17*P18</f>
         <v>205.9176</v>
       </c>
-      <c r="S19" s="172"/>
+      <c r="S19" s="173"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="171"/>
-      <c r="K20" s="176" t="n">
+      <c r="B20" s="172"/>
+      <c r="K20" s="177" t="n">
         <f aca="false">K18*K19</f>
         <v>18830.5092</v>
       </c>
-      <c r="L20" s="173" t="n">
+      <c r="L20" s="174" t="n">
         <f aca="false">+Utilidad!J76</f>
         <v>83697</v>
       </c>
-      <c r="N20" s="181" t="n">
+      <c r="N20" s="182" t="n">
         <f aca="false">+L14+N13+K18-M22-L20</f>
         <v>-1076</v>
       </c>
-      <c r="S20" s="172"/>
+      <c r="S20" s="173"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="171"/>
-      <c r="S21" s="172"/>
+      <c r="B21" s="172"/>
+      <c r="S21" s="173"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="171"/>
-      <c r="L22" s="174" t="n">
+      <c r="B22" s="172"/>
+      <c r="L22" s="175" t="n">
         <f aca="false">+Utilidad!K76</f>
         <v>0.43797188987</v>
       </c>
-      <c r="M22" s="173" t="n">
+      <c r="M22" s="174" t="n">
         <f aca="false">+Utilidad!J74</f>
         <v>0</v>
       </c>
-      <c r="O22" s="173" t="n">
+      <c r="O22" s="174" t="n">
         <f aca="false">+Utilidad!J73</f>
         <v>23460</v>
       </c>
-      <c r="S22" s="172"/>
+      <c r="S22" s="173"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="171"/>
-      <c r="L23" s="176" t="n">
+      <c r="B23" s="172"/>
+      <c r="L23" s="177" t="n">
         <f aca="false">+Utilidad!L76</f>
         <v>36656.9332664494</v>
       </c>
-      <c r="M23" s="174" t="n">
+      <c r="M23" s="175" t="n">
         <f aca="false">+Utilidad!K74</f>
         <v>0</v>
       </c>
-      <c r="O23" s="174" t="n">
+      <c r="O23" s="175" t="n">
         <f aca="false">+Utilidad!K73</f>
         <v>0.50587309641</v>
       </c>
-      <c r="S23" s="172"/>
+      <c r="S23" s="173"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="171"/>
-      <c r="M24" s="176" t="n">
+      <c r="B24" s="172"/>
+      <c r="M24" s="177" t="n">
         <f aca="false">+Utilidad!L74</f>
         <v>0</v>
       </c>
-      <c r="O24" s="176" t="n">
+      <c r="O24" s="177" t="n">
         <f aca="false">+Utilidad!L73</f>
         <v>11867.7828417786</v>
       </c>
@@ -20819,36 +20909,36 @@
         <f aca="false">+(O22+N13)/(L7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S24" s="172"/>
+      <c r="S24" s="173"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="171"/>
-      <c r="C25" s="187"/>
-      <c r="G25" s="173" t="n">
+      <c r="B25" s="172"/>
+      <c r="C25" s="188"/>
+      <c r="G25" s="174" t="n">
         <f aca="false">+Utilidad!J105</f>
         <v>0</v>
       </c>
-      <c r="S25" s="172"/>
+      <c r="S25" s="173"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="171"/>
-      <c r="C26" s="188" t="n">
+      <c r="B26" s="172"/>
+      <c r="C26" s="189" t="n">
         <f aca="false">+Utilidad!J103</f>
         <v>0</v>
       </c>
-      <c r="G26" s="174" t="n">
+      <c r="G26" s="175" t="n">
         <f aca="false">+Utilidad!K105</f>
         <v>0</v>
       </c>
-      <c r="S26" s="172"/>
+      <c r="S26" s="173"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="171"/>
-      <c r="C27" s="189" t="n">
+      <c r="B27" s="172"/>
+      <c r="C27" s="190" t="n">
         <f aca="false">+Utilidad!K103</f>
         <v>0</v>
       </c>
-      <c r="G27" s="176" t="n">
+      <c r="G27" s="177" t="n">
         <f aca="false">+Utilidad!L105</f>
         <v>0</v>
       </c>
@@ -20856,28 +20946,28 @@
         <f aca="false">+(K28)/(L20+M22+O22)</f>
         <v>0.628022434371996</v>
       </c>
-      <c r="S27" s="172"/>
+      <c r="S27" s="173"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="171"/>
-      <c r="C28" s="190" t="n">
+      <c r="B28" s="172"/>
+      <c r="C28" s="191" t="n">
         <f aca="false">+Utilidad!L103</f>
         <v>0</v>
       </c>
-      <c r="K28" s="182" t="n">
+      <c r="K28" s="183" t="n">
         <f aca="false">+Utilidad!J78</f>
         <v>67297</v>
       </c>
-      <c r="S28" s="172"/>
+      <c r="S28" s="173"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="171"/>
-      <c r="C29" s="187"/>
-      <c r="F29" s="191" t="n">
+      <c r="B29" s="172"/>
+      <c r="C29" s="188"/>
+      <c r="F29" s="192" t="n">
         <f aca="false">+C26-G25</f>
         <v>0</v>
       </c>
-      <c r="K29" s="185" t="n">
+      <c r="K29" s="186" t="n">
         <f aca="false">+Utilidad!K78</f>
         <v>0.665071</v>
       </c>
@@ -20885,1212 +20975,1212 @@
         <f aca="false">K28/(L20+M22+O22)</f>
         <v>0.628022434371996</v>
       </c>
-      <c r="O29" s="192" t="n">
+      <c r="O29" s="193" t="n">
         <f aca="false">O22+L20+M22</f>
         <v>107157</v>
       </c>
-      <c r="S29" s="172"/>
+      <c r="S29" s="173"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="171"/>
-      <c r="C30" s="187"/>
-      <c r="I30" s="182" t="n">
+      <c r="B30" s="172"/>
+      <c r="C30" s="188"/>
+      <c r="I30" s="183" t="n">
         <f aca="false">+Utilidad!J77</f>
         <v>39860</v>
       </c>
-      <c r="K30" s="186" t="n">
+      <c r="K30" s="187" t="n">
         <f aca="false">+Utilidad!L78</f>
         <v>44757.283087</v>
       </c>
-      <c r="O30" s="192" t="n">
+      <c r="O30" s="193" t="n">
         <f aca="false">O29-K28</f>
         <v>39860</v>
       </c>
-      <c r="S30" s="172"/>
+      <c r="S30" s="173"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="171"/>
-      <c r="C31" s="187"/>
-      <c r="I31" s="185" t="n">
+      <c r="B31" s="172"/>
+      <c r="C31" s="188"/>
+      <c r="I31" s="186" t="n">
         <f aca="false">+Utilidad!K77</f>
         <v>0.094516633742</v>
       </c>
-      <c r="S31" s="172"/>
+      <c r="S31" s="173"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="171"/>
-      <c r="C32" s="187"/>
-      <c r="I32" s="186" t="n">
+      <c r="B32" s="172"/>
+      <c r="C32" s="188"/>
+      <c r="I32" s="187" t="n">
         <f aca="false">I30*I31</f>
         <v>3767.43302095612</v>
       </c>
-      <c r="S32" s="172"/>
+      <c r="S32" s="173"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="171"/>
-      <c r="C33" s="187"/>
-      <c r="S33" s="172"/>
+      <c r="B33" s="172"/>
+      <c r="C33" s="188"/>
+      <c r="S33" s="173"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="171"/>
-      <c r="C34" s="187"/>
-      <c r="G34" s="173" t="n">
+      <c r="B34" s="172"/>
+      <c r="C34" s="188"/>
+      <c r="G34" s="174" t="n">
         <f aca="false">+Utilidad!J108</f>
         <v>0</v>
       </c>
-      <c r="L34" s="181"/>
-      <c r="S34" s="172"/>
+      <c r="L34" s="182"/>
+      <c r="S34" s="173"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="171"/>
-      <c r="C35" s="188" t="n">
+      <c r="B35" s="172"/>
+      <c r="C35" s="189" t="n">
         <f aca="false">+Utilidad!J106</f>
         <v>0</v>
       </c>
-      <c r="G35" s="174" t="n">
+      <c r="G35" s="175" t="n">
         <f aca="false">+Utilidad!K108</f>
         <v>0</v>
       </c>
-      <c r="M35" s="192"/>
-      <c r="N35" s="192"/>
-      <c r="S35" s="172"/>
+      <c r="M35" s="193"/>
+      <c r="N35" s="193"/>
+      <c r="S35" s="173"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="171"/>
-      <c r="C36" s="189" t="n">
+      <c r="B36" s="172"/>
+      <c r="C36" s="190" t="n">
         <f aca="false">+Utilidad!K106</f>
         <v>0</v>
       </c>
-      <c r="G36" s="176" t="n">
+      <c r="G36" s="177" t="n">
         <f aca="false">+Utilidad!L108</f>
         <v>0</v>
       </c>
-      <c r="S36" s="172"/>
+      <c r="S36" s="173"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="171"/>
-      <c r="C37" s="190" t="n">
+      <c r="B37" s="172"/>
+      <c r="C37" s="191" t="n">
         <f aca="false">+Utilidad!L106</f>
         <v>0</v>
       </c>
-      <c r="S37" s="172"/>
+      <c r="S37" s="173"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="171"/>
-      <c r="C38" s="187"/>
-      <c r="F38" s="191" t="n">
+      <c r="B38" s="172"/>
+      <c r="C38" s="188"/>
+      <c r="F38" s="192" t="n">
         <f aca="false">+C35-G34</f>
         <v>0</v>
       </c>
-      <c r="S38" s="172"/>
+      <c r="S38" s="173"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="171"/>
-      <c r="C39" s="187"/>
-      <c r="K39" s="193" t="n">
+      <c r="B39" s="172"/>
+      <c r="C39" s="188"/>
+      <c r="K39" s="194" t="n">
         <f aca="false">K28-(I53+L53)</f>
         <v>-5361</v>
       </c>
-      <c r="N39" s="192"/>
-      <c r="S39" s="172"/>
+      <c r="N39" s="193"/>
+      <c r="S39" s="173"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="171"/>
-      <c r="C40" s="187"/>
-      <c r="S40" s="172"/>
+      <c r="B40" s="172"/>
+      <c r="C40" s="188"/>
+      <c r="S40" s="173"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="171"/>
-      <c r="C41" s="187"/>
-      <c r="S41" s="172"/>
+      <c r="B41" s="172"/>
+      <c r="C41" s="188"/>
+      <c r="S41" s="173"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="171"/>
-      <c r="C42" s="187"/>
-      <c r="S42" s="172"/>
+      <c r="B42" s="172"/>
+      <c r="C42" s="188"/>
+      <c r="S42" s="173"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="171"/>
-      <c r="C43" s="187"/>
-      <c r="S43" s="172"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="188"/>
+      <c r="S43" s="173"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="171"/>
-      <c r="C44" s="188" t="n">
+      <c r="B44" s="172"/>
+      <c r="C44" s="189" t="n">
         <f aca="false">+Utilidad!J109</f>
         <v>0</v>
       </c>
-      <c r="G44" s="173" t="n">
+      <c r="G44" s="174" t="n">
         <f aca="false">+Utilidad!J111</f>
         <v>0</v>
       </c>
-      <c r="S44" s="172"/>
+      <c r="S44" s="173"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="171"/>
-      <c r="C45" s="189" t="n">
+      <c r="B45" s="172"/>
+      <c r="C45" s="190" t="n">
         <f aca="false">+Utilidad!K109</f>
         <v>0</v>
       </c>
-      <c r="G45" s="174" t="n">
+      <c r="G45" s="175" t="n">
         <f aca="false">+Utilidad!K111</f>
         <v>0</v>
       </c>
-      <c r="S45" s="172"/>
+      <c r="S45" s="173"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="171"/>
-      <c r="C46" s="190" t="n">
+      <c r="B46" s="172"/>
+      <c r="C46" s="191" t="n">
         <f aca="false">+Utilidad!L109</f>
         <v>0</v>
       </c>
-      <c r="G46" s="176" t="n">
+      <c r="G46" s="177" t="n">
         <f aca="false">+Utilidad!L111</f>
         <v>0</v>
       </c>
-      <c r="S46" s="172"/>
+      <c r="S46" s="173"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="171"/>
-      <c r="C47" s="187"/>
-      <c r="S47" s="172"/>
+      <c r="B47" s="172"/>
+      <c r="C47" s="188"/>
+      <c r="S47" s="173"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="171"/>
-      <c r="C48" s="187"/>
-      <c r="F48" s="191" t="n">
+      <c r="B48" s="172"/>
+      <c r="C48" s="188"/>
+      <c r="F48" s="192" t="n">
         <f aca="false">+C44-G44</f>
         <v>0</v>
       </c>
-      <c r="S48" s="172"/>
+      <c r="S48" s="173"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="171"/>
-      <c r="C49" s="187"/>
-      <c r="S49" s="172"/>
+      <c r="B49" s="172"/>
+      <c r="C49" s="188"/>
+      <c r="S49" s="173"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="171"/>
-      <c r="C50" s="187"/>
-      <c r="S50" s="172"/>
+      <c r="B50" s="172"/>
+      <c r="C50" s="188"/>
+      <c r="S50" s="173"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="171"/>
-      <c r="C51" s="187"/>
-      <c r="S51" s="172"/>
+      <c r="B51" s="172"/>
+      <c r="C51" s="188"/>
+      <c r="S51" s="173"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="171"/>
-      <c r="C52" s="187"/>
-      <c r="S52" s="172"/>
+      <c r="B52" s="172"/>
+      <c r="C52" s="188"/>
+      <c r="S52" s="173"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="171"/>
-      <c r="C53" s="187"/>
-      <c r="I53" s="179" t="n">
+      <c r="B53" s="172"/>
+      <c r="C53" s="188"/>
+      <c r="I53" s="180" t="n">
         <f aca="false">+Utilidad!J82</f>
         <v>1453</v>
       </c>
-      <c r="L53" s="179" t="n">
+      <c r="L53" s="180" t="n">
         <f aca="false">+Utilidad!J83</f>
         <v>71205</v>
       </c>
-      <c r="S53" s="172"/>
+      <c r="S53" s="173"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="171"/>
-      <c r="C54" s="188" t="n">
+      <c r="B54" s="172"/>
+      <c r="C54" s="189" t="n">
         <f aca="false">+Utilidad!J112</f>
         <v>0</v>
       </c>
-      <c r="I54" s="180" t="n">
+      <c r="I54" s="181" t="n">
         <f aca="false">+Utilidad!K82</f>
         <v>0.64646643925</v>
       </c>
-      <c r="L54" s="180" t="n">
+      <c r="L54" s="181" t="n">
         <f aca="false">+Utilidad!K83</f>
         <v>0.6636863737</v>
       </c>
-      <c r="S54" s="172"/>
+      <c r="S54" s="173"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="171"/>
-      <c r="C55" s="189" t="n">
+      <c r="B55" s="172"/>
+      <c r="C55" s="190" t="n">
         <f aca="false">+Utilidad!K112</f>
         <v>0</v>
       </c>
-      <c r="I55" s="183" t="n">
+      <c r="I55" s="184" t="n">
         <f aca="false">+Utilidad!L82</f>
         <v>939.31573623025</v>
       </c>
-      <c r="L55" s="183" t="n">
+      <c r="L55" s="184" t="n">
         <f aca="false">+Utilidad!L83</f>
         <v>47257.7882393085</v>
       </c>
-      <c r="S55" s="172"/>
+      <c r="S55" s="173"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="171"/>
-      <c r="C56" s="190" t="n">
+      <c r="B56" s="172"/>
+      <c r="C56" s="191" t="n">
         <f aca="false">+Utilidad!L112</f>
         <v>0</v>
       </c>
-      <c r="S56" s="172"/>
+      <c r="S56" s="173"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="171"/>
-      <c r="S57" s="172"/>
+      <c r="B57" s="172"/>
+      <c r="S57" s="173"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="171"/>
-      <c r="M58" s="175" t="n">
+      <c r="B58" s="172"/>
+      <c r="M58" s="176" t="n">
         <f aca="false">Flujos!G24</f>
         <v>1453</v>
       </c>
-      <c r="N58" s="194" t="n">
+      <c r="N58" s="195" t="n">
         <f aca="false">+M58/(L53+I53)</f>
         <v>0.0199977979025021</v>
       </c>
-      <c r="S58" s="172"/>
+      <c r="S58" s="173"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="171"/>
-      <c r="M59" s="177" t="n">
+      <c r="B59" s="172"/>
+      <c r="M59" s="178" t="n">
         <f aca="false">Flujos!H24</f>
         <v>0.64646643925</v>
       </c>
-      <c r="S59" s="172"/>
+      <c r="S59" s="173"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="171"/>
-      <c r="M60" s="178" t="n">
+      <c r="B60" s="172"/>
+      <c r="M60" s="179" t="n">
         <f aca="false">M59*M58</f>
         <v>939.31573623025</v>
       </c>
-      <c r="S60" s="172"/>
+      <c r="S60" s="173"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="171"/>
-      <c r="S61" s="172"/>
+      <c r="B61" s="172"/>
+      <c r="S61" s="173"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="171"/>
-      <c r="C62" s="173" t="n">
+      <c r="B62" s="172"/>
+      <c r="C62" s="174" t="n">
         <f aca="false">Flujos!C55</f>
         <v>41596</v>
       </c>
-      <c r="S62" s="172"/>
+      <c r="S62" s="173"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="171"/>
-      <c r="C63" s="174" t="n">
+      <c r="B63" s="172"/>
+      <c r="C63" s="175" t="n">
         <f aca="false">Flujos!D55</f>
         <v>0.4527</v>
       </c>
-      <c r="O63" s="179" t="n">
+      <c r="O63" s="180" t="n">
         <f aca="false">Flujos!G27</f>
         <v>4772</v>
       </c>
-      <c r="S63" s="172"/>
+      <c r="S63" s="173"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="171"/>
-      <c r="C64" s="176" t="n">
+      <c r="B64" s="172"/>
+      <c r="C64" s="177" t="n">
         <f aca="false">C63*C62</f>
         <v>18830.5092</v>
       </c>
-      <c r="O64" s="180" t="n">
+      <c r="O64" s="181" t="n">
         <f aca="false">Flujos!H27</f>
         <v>0.6482</v>
       </c>
-      <c r="S64" s="172"/>
+      <c r="S64" s="173"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="171"/>
-      <c r="F65" s="179" t="n">
+      <c r="B65" s="172"/>
+      <c r="F65" s="180" t="n">
         <f aca="false">I112</f>
         <v>0</v>
       </c>
       <c r="G65" s="126" t="s">
-        <v>153</v>
-      </c>
-      <c r="L65" s="175" t="n">
+        <v>157</v>
+      </c>
+      <c r="L65" s="176" t="n">
         <f aca="false">Flujos!G25</f>
         <v>71205</v>
       </c>
-      <c r="O65" s="183" t="n">
+      <c r="O65" s="184" t="n">
         <f aca="false">O63*O64</f>
         <v>3093.2104</v>
       </c>
-      <c r="S65" s="172"/>
+      <c r="S65" s="173"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="171"/>
-      <c r="F66" s="179" t="n">
+      <c r="B66" s="172"/>
+      <c r="F66" s="180" t="n">
         <f aca="false">I113</f>
         <v>2106</v>
       </c>
       <c r="G66" s="126" t="s">
-        <v>154</v>
-      </c>
-      <c r="L66" s="177" t="n">
+        <v>158</v>
+      </c>
+      <c r="L66" s="178" t="n">
         <f aca="false">Flujos!H25</f>
         <v>0.6636863737</v>
       </c>
-      <c r="S66" s="172"/>
+      <c r="S66" s="173"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="171"/>
-      <c r="F67" s="179" t="n">
+      <c r="B67" s="172"/>
+      <c r="F67" s="180" t="n">
         <f aca="false">I114</f>
         <v>0</v>
       </c>
       <c r="G67" s="126" t="s">
-        <v>155</v>
-      </c>
-      <c r="L67" s="178" t="n">
+        <v>159</v>
+      </c>
+      <c r="L67" s="179" t="n">
         <f aca="false">L66*L65</f>
         <v>47257.7882393085</v>
       </c>
-      <c r="N67" s="184" t="n">
+      <c r="N67" s="185" t="n">
         <f aca="false">Flujos!G26</f>
         <v>66433</v>
       </c>
-      <c r="O67" s="179" t="n">
+      <c r="O67" s="180" t="n">
         <f aca="false">Flujos!G28</f>
         <v>0</v>
       </c>
-      <c r="S67" s="172"/>
+      <c r="S67" s="173"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="171"/>
-      <c r="O68" s="180" t="n">
+      <c r="B68" s="172"/>
+      <c r="O68" s="181" t="n">
         <f aca="false">Flujos!H28</f>
         <v>0</v>
       </c>
-      <c r="S68" s="172"/>
+      <c r="S68" s="173"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="171"/>
-      <c r="O69" s="183" t="n">
+      <c r="B69" s="172"/>
+      <c r="O69" s="184" t="n">
         <f aca="false">O67*O68</f>
         <v>0</v>
       </c>
-      <c r="S69" s="172"/>
+      <c r="S69" s="173"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="171"/>
-      <c r="H70" s="179" t="n">
+      <c r="B70" s="172"/>
+      <c r="H70" s="180" t="n">
         <f aca="false">Flujos!G29</f>
         <v>0</v>
       </c>
-      <c r="K70" s="179" t="n">
+      <c r="K70" s="180" t="n">
         <f aca="false">Flujos!G22</f>
         <v>0</v>
       </c>
-      <c r="S70" s="172"/>
+      <c r="S70" s="173"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="171"/>
-      <c r="H71" s="180" t="n">
+      <c r="B71" s="172"/>
+      <c r="H71" s="181" t="n">
         <f aca="false">Flujos!H29</f>
         <v>0</v>
       </c>
-      <c r="K71" s="180" t="n">
+      <c r="K71" s="181" t="n">
         <f aca="false">Flujos!H22</f>
         <v>0</v>
       </c>
-      <c r="S71" s="172"/>
+      <c r="S71" s="173"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="171"/>
-      <c r="H72" s="183" t="n">
+      <c r="B72" s="172"/>
+      <c r="H72" s="184" t="n">
         <f aca="false">H70*H71</f>
         <v>0</v>
       </c>
-      <c r="K72" s="183" t="n">
+      <c r="K72" s="184" t="n">
         <f aca="false">K70*K71</f>
         <v>0</v>
       </c>
-      <c r="S72" s="172"/>
+      <c r="S72" s="173"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="171"/>
-      <c r="S73" s="172"/>
+      <c r="B73" s="172"/>
+      <c r="S73" s="173"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="171"/>
-      <c r="L74" s="179" t="n">
+      <c r="B74" s="172"/>
+      <c r="L74" s="180" t="n">
         <f aca="false">Flujos!G35</f>
         <v>0</v>
       </c>
-      <c r="O74" s="179" t="n">
+      <c r="O74" s="180" t="n">
         <f aca="false">Flujos!G33</f>
         <v>0</v>
       </c>
-      <c r="S74" s="172"/>
+      <c r="S74" s="173"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="171"/>
-      <c r="H75" s="179" t="n">
+      <c r="B75" s="172"/>
+      <c r="H75" s="180" t="n">
         <f aca="false">Flujos!G30</f>
         <v>0</v>
       </c>
-      <c r="J75" s="184" t="n">
+      <c r="J75" s="185" t="n">
         <f aca="false">Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="L75" s="180" t="n">
+      <c r="L75" s="181" t="n">
         <f aca="false">Flujos!H35</f>
         <v>0</v>
       </c>
-      <c r="N75" s="184" t="n">
+      <c r="N75" s="185" t="n">
         <f aca="false">Flujos!G34</f>
         <v>7132</v>
       </c>
-      <c r="O75" s="180" t="n">
+      <c r="O75" s="181" t="n">
         <f aca="false">Flujos!H33</f>
         <v>0</v>
       </c>
-      <c r="S75" s="172"/>
+      <c r="S75" s="173"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="171"/>
-      <c r="H76" s="180" t="n">
+      <c r="B76" s="172"/>
+      <c r="H76" s="181" t="n">
         <f aca="false">Flujos!H30</f>
         <v>0</v>
       </c>
-      <c r="L76" s="183" t="n">
+      <c r="L76" s="184" t="n">
         <f aca="false">L74*L75</f>
         <v>0</v>
       </c>
-      <c r="O76" s="183" t="n">
+      <c r="O76" s="184" t="n">
         <f aca="false">O74*O75</f>
         <v>0</v>
       </c>
-      <c r="S76" s="172"/>
+      <c r="S76" s="173"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="171"/>
-      <c r="H77" s="183" t="n">
+      <c r="B77" s="172"/>
+      <c r="H77" s="184" t="n">
         <f aca="false">H76*H75</f>
         <v>0</v>
       </c>
-      <c r="S77" s="172"/>
+      <c r="S77" s="173"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="171"/>
-      <c r="L78" s="179" t="n">
+      <c r="B78" s="172"/>
+      <c r="L78" s="180" t="n">
         <f aca="false">Flujos!G36</f>
         <v>0</v>
       </c>
-      <c r="S78" s="172"/>
+      <c r="S78" s="173"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="171"/>
-      <c r="L79" s="180" t="n">
+      <c r="B79" s="172"/>
+      <c r="L79" s="181" t="n">
         <f aca="false">Flujos!H36</f>
         <v>0</v>
       </c>
-      <c r="Q79" s="179" t="n">
+      <c r="Q79" s="180" t="n">
         <f aca="false">Flujos!G58</f>
         <v>0</v>
       </c>
-      <c r="S79" s="172"/>
+      <c r="S79" s="173"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="171"/>
-      <c r="L80" s="183" t="n">
+      <c r="B80" s="172"/>
+      <c r="L80" s="184" t="n">
         <f aca="false">L79*L78</f>
         <v>0</v>
       </c>
-      <c r="Q80" s="180" t="n">
+      <c r="Q80" s="181" t="n">
         <f aca="false">Flujos!H58</f>
         <v>0</v>
       </c>
-      <c r="S80" s="172"/>
+      <c r="S80" s="173"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="171"/>
-      <c r="Q81" s="183" t="n">
+      <c r="B81" s="172"/>
+      <c r="Q81" s="184" t="n">
         <f aca="false">Q79*Q80</f>
         <v>0</v>
       </c>
-      <c r="S81" s="172"/>
+      <c r="S81" s="173"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="171"/>
-      <c r="K82" s="179" t="n">
+      <c r="B82" s="172"/>
+      <c r="K82" s="180" t="n">
         <f aca="false">Flujos!G57</f>
         <v>5026</v>
       </c>
-      <c r="S82" s="172"/>
+      <c r="S82" s="173"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="171"/>
-      <c r="K83" s="180" t="n">
+      <c r="B83" s="172"/>
+      <c r="K83" s="181" t="n">
         <f aca="false">Flujos!H57</f>
         <v>0.6371</v>
       </c>
-      <c r="S83" s="172"/>
+      <c r="S83" s="173"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="171"/>
-      <c r="K84" s="183" t="n">
+      <c r="B84" s="172"/>
+      <c r="K84" s="184" t="n">
         <f aca="false">K82*K83</f>
         <v>3202.0646</v>
       </c>
-      <c r="O84" s="179" t="n">
+      <c r="O84" s="180" t="n">
         <f aca="false">Flujos!G40</f>
         <v>1632</v>
       </c>
-      <c r="S84" s="172"/>
+      <c r="S84" s="173"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="171"/>
-      <c r="H85" s="192" t="n">
+      <c r="B85" s="172"/>
+      <c r="H85" s="193" t="n">
         <f aca="false">5562+L74</f>
         <v>5562</v>
       </c>
-      <c r="O85" s="180" t="n">
+      <c r="O85" s="181" t="n">
         <f aca="false">Flujos!H40</f>
         <v>0.5831</v>
       </c>
-      <c r="S85" s="172"/>
+      <c r="S85" s="173"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="171"/>
-      <c r="K86" s="179" t="n">
+      <c r="B86" s="172"/>
+      <c r="K86" s="180" t="n">
         <f aca="false">+Utilidad!J98</f>
         <v>1632</v>
       </c>
-      <c r="O86" s="183" t="n">
+      <c r="O86" s="184" t="n">
         <f aca="false">O84*O85</f>
         <v>951.6192</v>
       </c>
-      <c r="S86" s="172"/>
+      <c r="S86" s="173"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="171"/>
-      <c r="K87" s="180" t="n">
+      <c r="B87" s="172"/>
+      <c r="K87" s="181" t="n">
         <f aca="false">+Utilidad!K98</f>
         <v>0.5831</v>
       </c>
       <c r="Q87" s="126" t="s">
-        <v>147</v>
-      </c>
-      <c r="S87" s="172"/>
+        <v>149</v>
+      </c>
+      <c r="S87" s="173"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="171"/>
-      <c r="K88" s="183" t="n">
+      <c r="B88" s="172"/>
+      <c r="K88" s="184" t="n">
         <f aca="false">+Utilidad!L98</f>
         <v>951.6192</v>
       </c>
-      <c r="N88" s="195" t="n">
+      <c r="N88" s="196" t="n">
         <f aca="false">+L90+K86-O84</f>
         <v>-1632</v>
       </c>
-      <c r="S88" s="172"/>
+      <c r="S88" s="173"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="171"/>
-      <c r="S89" s="172"/>
+      <c r="B89" s="172"/>
+      <c r="S89" s="173"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="171"/>
-      <c r="L90" s="179" t="n">
+      <c r="B90" s="172"/>
+      <c r="L90" s="180" t="n">
         <f aca="false">+Utilidad!J97</f>
         <v>-1632</v>
       </c>
       <c r="R90" s="126" t="s">
-        <v>148</v>
-      </c>
-      <c r="S90" s="172"/>
+        <v>150</v>
+      </c>
+      <c r="S90" s="173"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="171"/>
-      <c r="L91" s="180" t="n">
+      <c r="B91" s="172"/>
+      <c r="L91" s="181" t="n">
         <f aca="false">+Utilidad!K97</f>
         <v>0.5831</v>
       </c>
-      <c r="S91" s="172"/>
+      <c r="S91" s="173"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="171"/>
-      <c r="L92" s="183" t="n">
+      <c r="B92" s="172"/>
+      <c r="L92" s="184" t="n">
         <f aca="false">+Utilidad!L97</f>
         <v>-951.6192</v>
       </c>
-      <c r="S92" s="172"/>
+      <c r="S92" s="173"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="171"/>
+      <c r="B93" s="172"/>
       <c r="P93" s="126" t="s">
-        <v>149</v>
-      </c>
-      <c r="S93" s="172"/>
+        <v>151</v>
+      </c>
+      <c r="S93" s="173"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="196"/>
-      <c r="C94" s="197"/>
-      <c r="D94" s="197"/>
-      <c r="E94" s="197"/>
-      <c r="F94" s="197"/>
-      <c r="G94" s="197"/>
-      <c r="H94" s="197"/>
-      <c r="I94" s="197"/>
-      <c r="J94" s="197"/>
-      <c r="K94" s="197"/>
-      <c r="L94" s="197"/>
-      <c r="M94" s="197"/>
-      <c r="N94" s="197"/>
-      <c r="O94" s="197"/>
-      <c r="P94" s="198"/>
-      <c r="Q94" s="197"/>
-      <c r="R94" s="197"/>
-      <c r="S94" s="198"/>
+      <c r="B94" s="197"/>
+      <c r="C94" s="198"/>
+      <c r="D94" s="198"/>
+      <c r="E94" s="198"/>
+      <c r="F94" s="198"/>
+      <c r="G94" s="198"/>
+      <c r="H94" s="198"/>
+      <c r="I94" s="198"/>
+      <c r="J94" s="198"/>
+      <c r="K94" s="198"/>
+      <c r="L94" s="198"/>
+      <c r="M94" s="198"/>
+      <c r="N94" s="198"/>
+      <c r="O94" s="198"/>
+      <c r="P94" s="199"/>
+      <c r="Q94" s="198"/>
+      <c r="R94" s="198"/>
+      <c r="S94" s="199"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G95" s="199" t="s">
-        <v>156</v>
+      <c r="G95" s="200" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G96" s="200" t="s">
+      <c r="G96" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="H96" s="200"/>
-      <c r="I96" s="200"/>
-      <c r="J96" s="201" t="s">
-        <v>157</v>
-      </c>
-      <c r="K96" s="201"/>
-      <c r="L96" s="201"/>
-      <c r="M96" s="202" t="s">
+      <c r="H96" s="201"/>
+      <c r="I96" s="201"/>
+      <c r="J96" s="202" t="s">
+        <v>161</v>
+      </c>
+      <c r="K96" s="202"/>
+      <c r="L96" s="202"/>
+      <c r="M96" s="203" t="s">
         <v>47</v>
       </c>
-      <c r="N96" s="202"/>
-      <c r="O96" s="202"/>
-      <c r="P96" s="202"/>
+      <c r="N96" s="203"/>
+      <c r="O96" s="203"/>
+      <c r="P96" s="203"/>
     </row>
     <row r="97" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G97" s="203" t="s">
-        <v>158</v>
-      </c>
-      <c r="H97" s="203"/>
-      <c r="I97" s="204" t="n">
+      <c r="G97" s="204" t="s">
+        <v>162</v>
+      </c>
+      <c r="H97" s="204"/>
+      <c r="I97" s="205" t="n">
         <f aca="false">+E6</f>
         <v>122150</v>
       </c>
-      <c r="J97" s="205" t="s">
+      <c r="J97" s="206" t="s">
         <v>45</v>
       </c>
-      <c r="K97" s="205"/>
-      <c r="L97" s="206" t="n">
+      <c r="K97" s="206"/>
+      <c r="L97" s="207" t="n">
         <f aca="false">Flujos!G9</f>
         <v>0</v>
       </c>
-      <c r="M97" s="207" t="s">
-        <v>159</v>
-      </c>
-      <c r="N97" s="207"/>
-      <c r="O97" s="207"/>
-      <c r="P97" s="206" t="n">
+      <c r="M97" s="208" t="s">
+        <v>163</v>
+      </c>
+      <c r="N97" s="208"/>
+      <c r="O97" s="208"/>
+      <c r="P97" s="207" t="n">
         <f aca="false">+G15</f>
         <v>26963</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G98" s="203" t="s">
-        <v>160</v>
-      </c>
-      <c r="H98" s="203"/>
-      <c r="I98" s="204" t="n">
+      <c r="G98" s="204" t="s">
+        <v>164</v>
+      </c>
+      <c r="H98" s="204"/>
+      <c r="I98" s="205" t="n">
         <f aca="false">+C12</f>
         <v>0</v>
       </c>
-      <c r="J98" s="207" t="s">
+      <c r="J98" s="208" t="s">
         <v>46</v>
       </c>
-      <c r="K98" s="207"/>
-      <c r="L98" s="206" t="n">
+      <c r="K98" s="208"/>
+      <c r="L98" s="207" t="n">
         <f aca="false">Flujos!G17</f>
         <v>-243</v>
       </c>
-      <c r="M98" s="207" t="s">
-        <v>140</v>
-      </c>
-      <c r="N98" s="207"/>
-      <c r="O98" s="207"/>
-      <c r="P98" s="206" t="n">
+      <c r="M98" s="208" t="s">
+        <v>142</v>
+      </c>
+      <c r="N98" s="208"/>
+      <c r="O98" s="208"/>
+      <c r="P98" s="207" t="n">
         <f aca="false">+Q7</f>
         <v>21435.044983</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G99" s="203" t="s">
-        <v>161</v>
-      </c>
-      <c r="H99" s="203"/>
-      <c r="I99" s="204" t="n">
+      <c r="G99" s="204" t="s">
+        <v>165</v>
+      </c>
+      <c r="H99" s="204"/>
+      <c r="I99" s="205" t="n">
         <f aca="false">+H13</f>
         <v>0</v>
       </c>
-      <c r="J99" s="207" t="s">
-        <v>162</v>
-      </c>
-      <c r="K99" s="207"/>
-      <c r="L99" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="207" t="s">
+      <c r="J99" s="208" t="s">
+        <v>166</v>
+      </c>
+      <c r="K99" s="208"/>
+      <c r="L99" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="N99" s="207"/>
-      <c r="O99" s="207"/>
-      <c r="P99" s="206" t="n">
+      <c r="N99" s="208"/>
+      <c r="O99" s="208"/>
+      <c r="P99" s="207" t="n">
         <f aca="false">+Q11</f>
         <v>12796.955017</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G100" s="208" t="s">
-        <v>163</v>
-      </c>
-      <c r="H100" s="208"/>
-      <c r="I100" s="204" t="n">
+      <c r="G100" s="209" t="s">
+        <v>167</v>
+      </c>
+      <c r="H100" s="209"/>
+      <c r="I100" s="205" t="n">
         <f aca="false">+C26</f>
         <v>0</v>
       </c>
-      <c r="J100" s="207" t="s">
-        <v>164</v>
-      </c>
-      <c r="K100" s="207"/>
-      <c r="L100" s="206" t="n">
+      <c r="J100" s="208" t="s">
+        <v>168</v>
+      </c>
+      <c r="K100" s="208"/>
+      <c r="L100" s="207" t="n">
         <f aca="false">Flujos!G21</f>
         <v>-5362</v>
       </c>
-      <c r="M100" s="207" t="s">
-        <v>165</v>
-      </c>
-      <c r="N100" s="207"/>
-      <c r="O100" s="207"/>
-      <c r="P100" s="206" t="n">
+      <c r="M100" s="208" t="s">
+        <v>169</v>
+      </c>
+      <c r="N100" s="208"/>
+      <c r="O100" s="208"/>
+      <c r="P100" s="207" t="n">
         <f aca="false">+I30</f>
         <v>39860</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G101" s="208" t="s">
+      <c r="G101" s="209" t="s">
         <v>91</v>
       </c>
-      <c r="H101" s="208"/>
-      <c r="I101" s="204" t="n">
+      <c r="H101" s="209"/>
+      <c r="I101" s="205" t="n">
         <f aca="false">+C35</f>
         <v>0</v>
       </c>
-      <c r="J101" s="207" t="s">
-        <v>166</v>
-      </c>
-      <c r="K101" s="207"/>
-      <c r="L101" s="206" t="n">
+      <c r="J101" s="208" t="s">
+        <v>170</v>
+      </c>
+      <c r="K101" s="208"/>
+      <c r="L101" s="207" t="n">
         <f aca="false">Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="M101" s="207" t="s">
-        <v>167</v>
-      </c>
-      <c r="N101" s="207"/>
-      <c r="O101" s="207"/>
-      <c r="P101" s="206" t="n">
+      <c r="M101" s="208" t="s">
+        <v>171</v>
+      </c>
+      <c r="N101" s="208"/>
+      <c r="O101" s="208"/>
+      <c r="P101" s="207" t="n">
         <f aca="false">+M58</f>
         <v>1453</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G102" s="208" t="s">
+      <c r="G102" s="209" t="s">
         <v>94</v>
       </c>
-      <c r="H102" s="208"/>
-      <c r="I102" s="204" t="n">
+      <c r="H102" s="209"/>
+      <c r="I102" s="205" t="n">
         <f aca="false">+C44</f>
         <v>0</v>
       </c>
-      <c r="J102" s="207" t="s">
-        <v>168</v>
-      </c>
-      <c r="K102" s="207"/>
-      <c r="L102" s="206" t="n">
+      <c r="J102" s="208" t="s">
+        <v>172</v>
+      </c>
+      <c r="K102" s="208"/>
+      <c r="L102" s="207" t="n">
         <f aca="false">Flujos!G44</f>
         <v>0</v>
       </c>
-      <c r="M102" s="207" t="s">
+      <c r="M102" s="208" t="s">
         <v>111</v>
       </c>
-      <c r="N102" s="207"/>
-      <c r="O102" s="207"/>
-      <c r="P102" s="206" t="n">
+      <c r="N102" s="208"/>
+      <c r="O102" s="208"/>
+      <c r="P102" s="207" t="n">
         <f aca="false">+O63</f>
         <v>4772</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G103" s="208" t="s">
-        <v>169</v>
-      </c>
-      <c r="H103" s="208"/>
-      <c r="I103" s="204" t="n">
+      <c r="G103" s="209" t="s">
+        <v>173</v>
+      </c>
+      <c r="H103" s="209"/>
+      <c r="I103" s="205" t="n">
         <f aca="false">+C54</f>
         <v>0</v>
       </c>
-      <c r="J103" s="207" t="s">
-        <v>170</v>
-      </c>
-      <c r="K103" s="207"/>
-      <c r="L103" s="206" t="n">
+      <c r="J103" s="208" t="s">
+        <v>174</v>
+      </c>
+      <c r="K103" s="208"/>
+      <c r="L103" s="207" t="n">
         <f aca="false">Flujos!G47</f>
         <v>0</v>
       </c>
-      <c r="M103" s="207" t="s">
-        <v>171</v>
-      </c>
-      <c r="N103" s="207"/>
-      <c r="O103" s="207"/>
-      <c r="P103" s="206" t="n">
+      <c r="M103" s="208" t="s">
+        <v>175</v>
+      </c>
+      <c r="N103" s="208"/>
+      <c r="O103" s="208"/>
+      <c r="P103" s="207" t="n">
         <f aca="false">+O67</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G104" s="208" t="s">
-        <v>172</v>
-      </c>
-      <c r="H104" s="208"/>
-      <c r="I104" s="204" t="n">
+      <c r="G104" s="209" t="s">
+        <v>176</v>
+      </c>
+      <c r="H104" s="209"/>
+      <c r="I104" s="205" t="n">
         <f aca="false">+C62</f>
         <v>41596</v>
       </c>
-      <c r="J104" s="207" t="s">
-        <v>173</v>
-      </c>
-      <c r="K104" s="207"/>
-      <c r="L104" s="206" t="n">
+      <c r="J104" s="208" t="s">
+        <v>177</v>
+      </c>
+      <c r="K104" s="208"/>
+      <c r="L104" s="207" t="n">
         <f aca="false">Flujos!G50</f>
         <v>0</v>
       </c>
-      <c r="M104" s="207" t="s">
-        <v>174</v>
-      </c>
-      <c r="N104" s="207"/>
-      <c r="O104" s="207"/>
-      <c r="P104" s="206" t="n">
+      <c r="M104" s="208" t="s">
+        <v>178</v>
+      </c>
+      <c r="N104" s="208"/>
+      <c r="O104" s="208"/>
+      <c r="P104" s="207" t="n">
         <f aca="false">+O74</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G105" s="208" t="s">
-        <v>175</v>
-      </c>
-      <c r="H105" s="208"/>
-      <c r="I105" s="204" t="n">
+      <c r="G105" s="209" t="s">
+        <v>179</v>
+      </c>
+      <c r="H105" s="209"/>
+      <c r="I105" s="205" t="n">
         <f aca="false">+H70</f>
         <v>0</v>
       </c>
-      <c r="J105" s="207" t="s">
-        <v>176</v>
-      </c>
-      <c r="K105" s="207"/>
-      <c r="L105" s="206" t="n">
+      <c r="J105" s="208" t="s">
+        <v>180</v>
+      </c>
+      <c r="K105" s="208"/>
+      <c r="L105" s="207" t="n">
         <f aca="false">Flujos!G53</f>
         <v>0</v>
       </c>
-      <c r="M105" s="207" t="s">
+      <c r="M105" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="N105" s="207"/>
-      <c r="O105" s="207"/>
-      <c r="P105" s="206" t="n">
+      <c r="N105" s="208"/>
+      <c r="O105" s="208"/>
+      <c r="P105" s="207" t="n">
         <f aca="false">+O84</f>
         <v>1632</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G106" s="208" t="s">
-        <v>177</v>
-      </c>
-      <c r="H106" s="208"/>
-      <c r="I106" s="204" t="n">
+      <c r="G106" s="209" t="s">
+        <v>181</v>
+      </c>
+      <c r="H106" s="209"/>
+      <c r="I106" s="205" t="n">
         <f aca="false">+H75</f>
         <v>0</v>
       </c>
-      <c r="J106" s="207" t="s">
-        <v>178</v>
-      </c>
-      <c r="K106" s="207"/>
-      <c r="L106" s="206" t="n">
+      <c r="J106" s="208" t="s">
+        <v>182</v>
+      </c>
+      <c r="K106" s="208"/>
+      <c r="L106" s="207" t="n">
         <f aca="false">Flujos!G42</f>
         <v>0</v>
       </c>
-      <c r="M106" s="207" t="s">
-        <v>143</v>
-      </c>
-      <c r="N106" s="207"/>
-      <c r="O106" s="207"/>
-      <c r="P106" s="206" t="n">
+      <c r="M106" s="208" t="s">
+        <v>145</v>
+      </c>
+      <c r="N106" s="208"/>
+      <c r="O106" s="208"/>
+      <c r="P106" s="207" t="n">
         <f aca="false">Q79</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G107" s="209" t="s">
-        <v>179</v>
-      </c>
-      <c r="H107" s="210"/>
-      <c r="I107" s="204" t="n">
+      <c r="G107" s="210" t="s">
+        <v>183</v>
+      </c>
+      <c r="H107" s="211"/>
+      <c r="I107" s="205" t="n">
         <f aca="false">+L74</f>
         <v>0</v>
       </c>
-      <c r="J107" s="207" t="s">
-        <v>180</v>
-      </c>
-      <c r="K107" s="207"/>
-      <c r="L107" s="206" t="n">
+      <c r="J107" s="208" t="s">
+        <v>184</v>
+      </c>
+      <c r="K107" s="208"/>
+      <c r="L107" s="207" t="n">
         <f aca="false">Flujos!G26</f>
         <v>66433</v>
       </c>
-      <c r="M107" s="207" t="s">
-        <v>181</v>
-      </c>
-      <c r="N107" s="207"/>
-      <c r="O107" s="207"/>
-      <c r="P107" s="206"/>
+      <c r="M107" s="208" t="s">
+        <v>185</v>
+      </c>
+      <c r="N107" s="208"/>
+      <c r="O107" s="208"/>
+      <c r="P107" s="207"/>
     </row>
     <row r="108" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G108" s="209" t="s">
-        <v>182</v>
-      </c>
-      <c r="H108" s="210"/>
-      <c r="I108" s="204" t="n">
+      <c r="G108" s="210" t="s">
+        <v>186</v>
+      </c>
+      <c r="H108" s="211"/>
+      <c r="I108" s="205" t="n">
         <f aca="false">+L78</f>
         <v>0</v>
       </c>
-      <c r="J108" s="207" t="s">
-        <v>183</v>
-      </c>
-      <c r="K108" s="207"/>
-      <c r="L108" s="206" t="n">
+      <c r="J108" s="208" t="s">
+        <v>187</v>
+      </c>
+      <c r="K108" s="208"/>
+      <c r="L108" s="207" t="n">
         <f aca="false">Flujos!G34</f>
         <v>7132</v>
       </c>
-      <c r="M108" s="211"/>
-      <c r="N108" s="211"/>
-      <c r="O108" s="211"/>
-      <c r="P108" s="206"/>
+      <c r="M108" s="212"/>
+      <c r="N108" s="212"/>
+      <c r="O108" s="212"/>
+      <c r="P108" s="207"/>
     </row>
     <row r="109" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G109" s="209" t="s">
-        <v>184</v>
-      </c>
-      <c r="H109" s="210"/>
-      <c r="I109" s="204" t="n">
+      <c r="G109" s="210" t="s">
+        <v>188</v>
+      </c>
+      <c r="H109" s="211"/>
+      <c r="I109" s="205" t="n">
         <f aca="false">+K86</f>
         <v>1632</v>
       </c>
-      <c r="J109" s="207" t="s">
-        <v>185</v>
-      </c>
-      <c r="K109" s="207"/>
-      <c r="L109" s="206" t="n">
+      <c r="J109" s="208" t="s">
+        <v>189</v>
+      </c>
+      <c r="K109" s="208"/>
+      <c r="L109" s="207" t="n">
         <f aca="false">Flujos!G39</f>
         <v>-1632</v>
       </c>
-      <c r="M109" s="211"/>
-      <c r="N109" s="211"/>
-      <c r="O109" s="211"/>
-      <c r="P109" s="206"/>
+      <c r="M109" s="212"/>
+      <c r="N109" s="212"/>
+      <c r="O109" s="212"/>
+      <c r="P109" s="207"/>
     </row>
     <row r="110" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G110" s="208" t="s">
-        <v>186</v>
-      </c>
-      <c r="H110" s="208"/>
-      <c r="I110" s="204" t="n">
+      <c r="G110" s="209" t="s">
+        <v>190</v>
+      </c>
+      <c r="H110" s="209"/>
+      <c r="I110" s="205" t="n">
         <f aca="false">+L90</f>
         <v>-1632</v>
       </c>
-      <c r="J110" s="207" t="s">
-        <v>187</v>
-      </c>
-      <c r="K110" s="207"/>
-      <c r="L110" s="206" t="n">
+      <c r="J110" s="208" t="s">
+        <v>191</v>
+      </c>
+      <c r="K110" s="208"/>
+      <c r="L110" s="207" t="n">
         <f aca="false">Flujos!G69</f>
         <v>2055</v>
       </c>
-      <c r="M110" s="207"/>
-      <c r="N110" s="207"/>
-      <c r="O110" s="207"/>
-      <c r="P110" s="206"/>
+      <c r="M110" s="208"/>
+      <c r="N110" s="208"/>
+      <c r="O110" s="208"/>
+      <c r="P110" s="207"/>
     </row>
     <row r="111" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G111" s="208" t="s">
-        <v>188</v>
-      </c>
-      <c r="H111" s="208"/>
-      <c r="I111" s="204" t="n">
+      <c r="G111" s="209" t="s">
+        <v>192</v>
+      </c>
+      <c r="H111" s="209"/>
+      <c r="I111" s="205" t="n">
         <f aca="false">K82</f>
         <v>5026</v>
       </c>
-      <c r="J111" s="207"/>
-      <c r="K111" s="207"/>
-      <c r="L111" s="206"/>
-      <c r="M111" s="207"/>
-      <c r="N111" s="207"/>
-      <c r="O111" s="207"/>
-      <c r="P111" s="206"/>
+      <c r="J111" s="208"/>
+      <c r="K111" s="208"/>
+      <c r="L111" s="207"/>
+      <c r="M111" s="208"/>
+      <c r="N111" s="208"/>
+      <c r="O111" s="208"/>
+      <c r="P111" s="207"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G112" s="208" t="s">
-        <v>189</v>
-      </c>
-      <c r="H112" s="208" t="s">
-        <v>144</v>
-      </c>
-      <c r="I112" s="204" t="n">
+      <c r="G112" s="209" t="s">
+        <v>193</v>
+      </c>
+      <c r="H112" s="209" t="s">
+        <v>146</v>
+      </c>
+      <c r="I112" s="205" t="n">
         <f aca="false">Flujos!G59</f>
         <v>0</v>
       </c>
-      <c r="J112" s="207"/>
-      <c r="K112" s="207"/>
-      <c r="L112" s="206"/>
-      <c r="M112" s="207"/>
-      <c r="N112" s="207"/>
-      <c r="O112" s="207"/>
-      <c r="P112" s="206"/>
+      <c r="J112" s="208"/>
+      <c r="K112" s="208"/>
+      <c r="L112" s="207"/>
+      <c r="M112" s="208"/>
+      <c r="N112" s="208"/>
+      <c r="O112" s="208"/>
+      <c r="P112" s="207"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G113" s="208" t="s">
-        <v>190</v>
-      </c>
-      <c r="H113" s="208" t="s">
-        <v>145</v>
-      </c>
-      <c r="I113" s="204" t="n">
+      <c r="G113" s="209" t="s">
+        <v>194</v>
+      </c>
+      <c r="H113" s="209" t="s">
+        <v>147</v>
+      </c>
+      <c r="I113" s="205" t="n">
         <f aca="false">Flujos!G60</f>
         <v>2106</v>
       </c>
-      <c r="J113" s="207"/>
-      <c r="K113" s="207"/>
-      <c r="L113" s="206"/>
-      <c r="M113" s="207"/>
-      <c r="N113" s="207"/>
-      <c r="O113" s="207"/>
-      <c r="P113" s="206"/>
+      <c r="J113" s="208"/>
+      <c r="K113" s="208"/>
+      <c r="L113" s="207"/>
+      <c r="M113" s="208"/>
+      <c r="N113" s="208"/>
+      <c r="O113" s="208"/>
+      <c r="P113" s="207"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G114" s="208" t="s">
-        <v>191</v>
-      </c>
-      <c r="H114" s="208" t="s">
-        <v>146</v>
-      </c>
-      <c r="I114" s="204" t="n">
+      <c r="G114" s="209" t="s">
+        <v>195</v>
+      </c>
+      <c r="H114" s="209" t="s">
+        <v>148</v>
+      </c>
+      <c r="I114" s="205" t="n">
         <f aca="false">Flujos!G61</f>
         <v>0</v>
       </c>
-      <c r="J114" s="207"/>
-      <c r="K114" s="207"/>
-      <c r="L114" s="206"/>
-      <c r="M114" s="207"/>
-      <c r="N114" s="207"/>
-      <c r="O114" s="207"/>
-      <c r="P114" s="206"/>
+      <c r="J114" s="208"/>
+      <c r="K114" s="208"/>
+      <c r="L114" s="207"/>
+      <c r="M114" s="208"/>
+      <c r="N114" s="208"/>
+      <c r="O114" s="208"/>
+      <c r="P114" s="207"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G115" s="208" t="s">
-        <v>192</v>
-      </c>
-      <c r="H115" s="208"/>
-      <c r="I115" s="204" t="n">
+      <c r="G115" s="209" t="s">
+        <v>196</v>
+      </c>
+      <c r="H115" s="209"/>
+      <c r="I115" s="205" t="n">
         <f aca="false">Flujos!G62</f>
         <v>0</v>
       </c>
-      <c r="J115" s="207"/>
-      <c r="K115" s="207"/>
-      <c r="L115" s="206"/>
-      <c r="M115" s="207"/>
-      <c r="N115" s="207"/>
-      <c r="O115" s="207"/>
-      <c r="P115" s="206"/>
+      <c r="J115" s="208"/>
+      <c r="K115" s="208"/>
+      <c r="L115" s="207"/>
+      <c r="M115" s="208"/>
+      <c r="N115" s="208"/>
+      <c r="O115" s="208"/>
+      <c r="P115" s="207"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G116" s="208" t="s">
-        <v>193</v>
-      </c>
-      <c r="H116" s="208"/>
-      <c r="I116" s="204" t="n">
+      <c r="G116" s="209" t="s">
+        <v>197</v>
+      </c>
+      <c r="H116" s="209"/>
+      <c r="I116" s="205" t="n">
         <f aca="false">Flujos!G66</f>
         <v>0</v>
       </c>
-      <c r="J116" s="207"/>
-      <c r="K116" s="207"/>
-      <c r="L116" s="206"/>
-      <c r="M116" s="207"/>
-      <c r="N116" s="207"/>
-      <c r="O116" s="207"/>
-      <c r="P116" s="206"/>
+      <c r="J116" s="208"/>
+      <c r="K116" s="208"/>
+      <c r="L116" s="207"/>
+      <c r="M116" s="208"/>
+      <c r="N116" s="208"/>
+      <c r="O116" s="208"/>
+      <c r="P116" s="207"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G117" s="209" t="s">
-        <v>194</v>
-      </c>
-      <c r="H117" s="210"/>
-      <c r="I117" s="204" t="n">
+      <c r="G117" s="210" t="s">
+        <v>198</v>
+      </c>
+      <c r="H117" s="211"/>
+      <c r="I117" s="205" t="n">
         <f aca="false">Flujos!G67</f>
         <v>0</v>
       </c>
-      <c r="J117" s="212"/>
-      <c r="K117" s="212"/>
-      <c r="L117" s="206"/>
-      <c r="M117" s="207"/>
-      <c r="N117" s="207"/>
-      <c r="O117" s="207"/>
-      <c r="P117" s="206"/>
+      <c r="J117" s="213"/>
+      <c r="K117" s="213"/>
+      <c r="L117" s="207"/>
+      <c r="M117" s="208"/>
+      <c r="N117" s="208"/>
+      <c r="O117" s="208"/>
+      <c r="P117" s="207"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G118" s="209" t="s">
-        <v>195</v>
-      </c>
-      <c r="H118" s="210"/>
-      <c r="I118" s="204" t="n">
+      <c r="G118" s="210" t="s">
+        <v>199</v>
+      </c>
+      <c r="H118" s="211"/>
+      <c r="I118" s="205" t="n">
         <f aca="false">Flujos!G70</f>
         <v>392</v>
       </c>
-      <c r="J118" s="212"/>
-      <c r="K118" s="212"/>
-      <c r="L118" s="206"/>
-      <c r="M118" s="207"/>
-      <c r="N118" s="207"/>
-      <c r="O118" s="207"/>
-      <c r="P118" s="206"/>
+      <c r="J118" s="213"/>
+      <c r="K118" s="213"/>
+      <c r="L118" s="207"/>
+      <c r="M118" s="208"/>
+      <c r="N118" s="208"/>
+      <c r="O118" s="208"/>
+      <c r="P118" s="207"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G119" s="209" t="s">
-        <v>196</v>
-      </c>
-      <c r="H119" s="210"/>
-      <c r="I119" s="204" t="n">
+      <c r="G119" s="210" t="s">
+        <v>200</v>
+      </c>
+      <c r="H119" s="211"/>
+      <c r="I119" s="205" t="n">
         <f aca="false">Flujos!G72</f>
         <v>0</v>
       </c>
-      <c r="J119" s="207"/>
-      <c r="K119" s="207"/>
-      <c r="L119" s="206"/>
-      <c r="M119" s="207"/>
-      <c r="N119" s="207"/>
-      <c r="O119" s="207"/>
-      <c r="P119" s="206"/>
+      <c r="J119" s="208"/>
+      <c r="K119" s="208"/>
+      <c r="L119" s="207"/>
+      <c r="M119" s="208"/>
+      <c r="N119" s="208"/>
+      <c r="O119" s="208"/>
+      <c r="P119" s="207"/>
     </row>
     <row r="120" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G120" s="0"/>
@@ -22103,55 +22193,55 @@
       <c r="P120" s="0"/>
     </row>
     <row r="121" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G121" s="213" t="s">
-        <v>197</v>
-      </c>
-      <c r="H121" s="213"/>
-      <c r="I121" s="214" t="n">
+      <c r="G121" s="214" t="s">
+        <v>201</v>
+      </c>
+      <c r="H121" s="214"/>
+      <c r="I121" s="215" t="n">
         <f aca="false">+SUM(I97:I119)</f>
         <v>171270</v>
       </c>
-      <c r="J121" s="215" t="s">
-        <v>198</v>
-      </c>
-      <c r="K121" s="215"/>
-      <c r="L121" s="216" t="n">
+      <c r="J121" s="216" t="s">
+        <v>202</v>
+      </c>
+      <c r="K121" s="216"/>
+      <c r="L121" s="217" t="n">
         <f aca="false">+SUM(L97:L110)</f>
         <v>68383</v>
       </c>
-      <c r="M121" s="215" t="s">
-        <v>199</v>
-      </c>
-      <c r="N121" s="215"/>
-      <c r="O121" s="215"/>
-      <c r="P121" s="214" t="n">
+      <c r="M121" s="216" t="s">
+        <v>203</v>
+      </c>
+      <c r="N121" s="216"/>
+      <c r="O121" s="216"/>
+      <c r="P121" s="215" t="n">
         <f aca="false">+SUM(P97:P110)</f>
         <v>108912</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G122" s="217"/>
-      <c r="H122" s="217"/>
-      <c r="I122" s="217"/>
-      <c r="J122" s="217"/>
-      <c r="K122" s="217"/>
-      <c r="L122" s="217"/>
-      <c r="M122" s="217"/>
-      <c r="N122" s="217"/>
-      <c r="O122" s="217"/>
-      <c r="P122" s="217"/>
+      <c r="G122" s="218"/>
+      <c r="H122" s="218"/>
+      <c r="I122" s="218"/>
+      <c r="J122" s="218"/>
+      <c r="K122" s="218"/>
+      <c r="L122" s="218"/>
+      <c r="M122" s="218"/>
+      <c r="N122" s="218"/>
+      <c r="O122" s="218"/>
+      <c r="P122" s="218"/>
     </row>
     <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G123" s="217"/>
-      <c r="J123" s="217"/>
-      <c r="K123" s="217"/>
-      <c r="L123" s="218" t="s">
-        <v>200</v>
-      </c>
-      <c r="M123" s="219"/>
-      <c r="N123" s="220"/>
-      <c r="O123" s="219"/>
-      <c r="P123" s="221" t="n">
+      <c r="G123" s="218"/>
+      <c r="J123" s="218"/>
+      <c r="K123" s="218"/>
+      <c r="L123" s="219" t="s">
+        <v>204</v>
+      </c>
+      <c r="M123" s="220"/>
+      <c r="N123" s="221"/>
+      <c r="O123" s="220"/>
+      <c r="P123" s="222" t="n">
         <f aca="false">+I121-L121-P121</f>
         <v>-6025</v>
       </c>
@@ -22159,590 +22249,590 @@
     <row r="124" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="125" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="126" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G126" s="199" t="s">
-        <v>201</v>
+      <c r="G126" s="200" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G127" s="222" t="s">
+      <c r="G127" s="223" t="s">
         <v>10</v>
       </c>
-      <c r="H127" s="222"/>
-      <c r="I127" s="222"/>
-      <c r="J127" s="223" t="s">
-        <v>157</v>
-      </c>
-      <c r="K127" s="223"/>
-      <c r="L127" s="223"/>
-      <c r="M127" s="224" t="s">
+      <c r="H127" s="223"/>
+      <c r="I127" s="223"/>
+      <c r="J127" s="224" t="s">
+        <v>161</v>
+      </c>
+      <c r="K127" s="224"/>
+      <c r="L127" s="224"/>
+      <c r="M127" s="225" t="s">
         <v>47</v>
       </c>
-      <c r="N127" s="224"/>
-      <c r="O127" s="224"/>
-      <c r="P127" s="224"/>
+      <c r="N127" s="225"/>
+      <c r="O127" s="225"/>
+      <c r="P127" s="225"/>
     </row>
     <row r="128" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G128" s="203" t="s">
-        <v>158</v>
-      </c>
-      <c r="H128" s="203"/>
-      <c r="I128" s="204" t="n">
+      <c r="G128" s="204" t="s">
+        <v>162</v>
+      </c>
+      <c r="H128" s="204"/>
+      <c r="I128" s="205" t="n">
         <f aca="false">+E8</f>
         <v>36032.9704799715</v>
       </c>
-      <c r="J128" s="205" t="s">
+      <c r="J128" s="206" t="s">
         <v>45</v>
       </c>
-      <c r="K128" s="205"/>
-      <c r="L128" s="206" t="n">
+      <c r="K128" s="206"/>
+      <c r="L128" s="207" t="n">
         <f aca="false">Flujos!G9*Flujos!H9</f>
         <v>0</v>
       </c>
-      <c r="M128" s="207" t="s">
-        <v>159</v>
-      </c>
-      <c r="N128" s="207"/>
-      <c r="O128" s="207"/>
-      <c r="P128" s="206" t="n">
+      <c r="M128" s="208" t="s">
+        <v>163</v>
+      </c>
+      <c r="N128" s="208"/>
+      <c r="O128" s="208"/>
+      <c r="P128" s="207" t="n">
         <f aca="false">+G17</f>
         <v>3251.7378</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G129" s="225" t="s">
-        <v>160</v>
-      </c>
-      <c r="H129" s="226"/>
-      <c r="I129" s="204" t="n">
+      <c r="G129" s="226" t="s">
+        <v>164</v>
+      </c>
+      <c r="H129" s="227"/>
+      <c r="I129" s="205" t="n">
         <f aca="false">+C14</f>
         <v>0</v>
       </c>
-      <c r="J129" s="207" t="s">
+      <c r="J129" s="208" t="s">
         <v>46</v>
       </c>
-      <c r="K129" s="207"/>
-      <c r="L129" s="206" t="n">
+      <c r="K129" s="208"/>
+      <c r="L129" s="207" t="n">
         <f aca="false">Flujos!G17*Flujos!H17</f>
         <v>-107.69296620384</v>
       </c>
-      <c r="M129" s="207" t="s">
-        <v>140</v>
-      </c>
-      <c r="N129" s="207"/>
-      <c r="O129" s="207"/>
-      <c r="P129" s="206" t="n">
+      <c r="M129" s="208" t="s">
+        <v>142</v>
+      </c>
+      <c r="N129" s="208"/>
+      <c r="O129" s="208"/>
+      <c r="P129" s="207" t="n">
         <f aca="false">+Q9</f>
         <v>3424.17694844443</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G130" s="225" t="s">
-        <v>161</v>
-      </c>
-      <c r="H130" s="227"/>
-      <c r="I130" s="204" t="n">
+      <c r="G130" s="226" t="s">
+        <v>165</v>
+      </c>
+      <c r="H130" s="228"/>
+      <c r="I130" s="205" t="n">
         <f aca="false">+H15</f>
         <v>0</v>
       </c>
-      <c r="J130" s="207" t="s">
-        <v>162</v>
-      </c>
-      <c r="K130" s="207"/>
-      <c r="L130" s="206" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="207" t="s">
+      <c r="J130" s="208" t="s">
+        <v>166</v>
+      </c>
+      <c r="K130" s="208"/>
+      <c r="L130" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="208" t="s">
         <v>56</v>
       </c>
-      <c r="N130" s="207"/>
-      <c r="O130" s="207"/>
-      <c r="P130" s="206" t="n">
+      <c r="N130" s="208"/>
+      <c r="O130" s="208"/>
+      <c r="P130" s="207" t="n">
         <f aca="false">+Q13</f>
         <v>1061.53238891058</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G131" s="209" t="s">
-        <v>163</v>
-      </c>
-      <c r="H131" s="210"/>
-      <c r="I131" s="204" t="n">
+      <c r="G131" s="210" t="s">
+        <v>167</v>
+      </c>
+      <c r="H131" s="211"/>
+      <c r="I131" s="205" t="n">
         <f aca="false">+C28</f>
         <v>0</v>
       </c>
-      <c r="J131" s="207" t="s">
-        <v>164</v>
-      </c>
-      <c r="K131" s="207"/>
-      <c r="L131" s="206" t="n">
+      <c r="J131" s="208" t="s">
+        <v>168</v>
+      </c>
+      <c r="K131" s="208"/>
+      <c r="L131" s="207" t="n">
         <f aca="false">Flujos!G21*Flujos!H21</f>
         <v>-3439.82088845752</v>
       </c>
-      <c r="M131" s="207" t="s">
-        <v>165</v>
-      </c>
-      <c r="N131" s="207"/>
-      <c r="O131" s="207"/>
-      <c r="P131" s="206" t="n">
+      <c r="M131" s="208" t="s">
+        <v>169</v>
+      </c>
+      <c r="N131" s="208"/>
+      <c r="O131" s="208"/>
+      <c r="P131" s="207" t="n">
         <f aca="false">+I32</f>
         <v>3767.43302095612</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G132" s="209" t="s">
+      <c r="G132" s="210" t="s">
         <v>91</v>
       </c>
-      <c r="H132" s="210"/>
-      <c r="I132" s="204" t="n">
+      <c r="H132" s="211"/>
+      <c r="I132" s="205" t="n">
         <f aca="false">+C37</f>
         <v>0</v>
       </c>
-      <c r="J132" s="207" t="s">
-        <v>166</v>
-      </c>
-      <c r="K132" s="207"/>
-      <c r="L132" s="206" t="n">
+      <c r="J132" s="208" t="s">
+        <v>170</v>
+      </c>
+      <c r="K132" s="208"/>
+      <c r="L132" s="207" t="n">
         <f aca="false">Flujos!G31*Flujos!H31</f>
         <v>0</v>
       </c>
-      <c r="M132" s="207" t="s">
-        <v>167</v>
-      </c>
-      <c r="N132" s="207"/>
-      <c r="O132" s="207"/>
-      <c r="P132" s="206" t="n">
+      <c r="M132" s="208" t="s">
+        <v>171</v>
+      </c>
+      <c r="N132" s="208"/>
+      <c r="O132" s="208"/>
+      <c r="P132" s="207" t="n">
         <f aca="false">+M60</f>
         <v>939.31573623025</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G133" s="209" t="s">
+      <c r="G133" s="210" t="s">
         <v>94</v>
       </c>
-      <c r="H133" s="210"/>
-      <c r="I133" s="204" t="n">
+      <c r="H133" s="211"/>
+      <c r="I133" s="205" t="n">
         <f aca="false">+C46</f>
         <v>0</v>
       </c>
-      <c r="J133" s="207" t="s">
-        <v>168</v>
-      </c>
-      <c r="K133" s="207"/>
-      <c r="L133" s="206" t="n">
+      <c r="J133" s="208" t="s">
+        <v>172</v>
+      </c>
+      <c r="K133" s="208"/>
+      <c r="L133" s="207" t="n">
         <f aca="false">Flujos!G44*Flujos!H44</f>
         <v>0</v>
       </c>
-      <c r="M133" s="207" t="s">
+      <c r="M133" s="208" t="s">
         <v>111</v>
       </c>
-      <c r="N133" s="207"/>
-      <c r="O133" s="207"/>
-      <c r="P133" s="206" t="n">
+      <c r="N133" s="208"/>
+      <c r="O133" s="208"/>
+      <c r="P133" s="207" t="n">
         <f aca="false">+O65</f>
         <v>3093.2104</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G134" s="209" t="s">
-        <v>169</v>
-      </c>
-      <c r="H134" s="210"/>
-      <c r="I134" s="204" t="n">
+      <c r="G134" s="210" t="s">
+        <v>173</v>
+      </c>
+      <c r="H134" s="211"/>
+      <c r="I134" s="205" t="n">
         <f aca="false">+C56</f>
         <v>0</v>
       </c>
-      <c r="J134" s="207" t="s">
-        <v>170</v>
-      </c>
-      <c r="K134" s="207"/>
-      <c r="L134" s="206" t="n">
+      <c r="J134" s="208" t="s">
+        <v>174</v>
+      </c>
+      <c r="K134" s="208"/>
+      <c r="L134" s="207" t="n">
         <f aca="false">Flujos!G47*Flujos!H47</f>
         <v>0</v>
       </c>
-      <c r="M134" s="207" t="s">
-        <v>171</v>
-      </c>
-      <c r="N134" s="207"/>
-      <c r="O134" s="207"/>
-      <c r="P134" s="206" t="n">
+      <c r="M134" s="208" t="s">
+        <v>175</v>
+      </c>
+      <c r="N134" s="208"/>
+      <c r="O134" s="208"/>
+      <c r="P134" s="207" t="n">
         <f aca="false">+O69</f>
         <v>0</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G135" s="209" t="s">
-        <v>172</v>
-      </c>
-      <c r="H135" s="210"/>
-      <c r="I135" s="204" t="n">
+      <c r="G135" s="210" t="s">
+        <v>176</v>
+      </c>
+      <c r="H135" s="211"/>
+      <c r="I135" s="205" t="n">
         <f aca="false">C64</f>
         <v>18830.5092</v>
       </c>
-      <c r="J135" s="207" t="s">
-        <v>173</v>
-      </c>
-      <c r="K135" s="207"/>
-      <c r="L135" s="206" t="n">
+      <c r="J135" s="208" t="s">
+        <v>177</v>
+      </c>
+      <c r="K135" s="208"/>
+      <c r="L135" s="207" t="n">
         <f aca="false">Flujos!G50*Flujos!H50</f>
         <v>0</v>
       </c>
-      <c r="M135" s="207" t="s">
-        <v>174</v>
-      </c>
-      <c r="N135" s="207"/>
-      <c r="O135" s="207"/>
-      <c r="P135" s="206" t="n">
+      <c r="M135" s="208" t="s">
+        <v>178</v>
+      </c>
+      <c r="N135" s="208"/>
+      <c r="O135" s="208"/>
+      <c r="P135" s="207" t="n">
         <f aca="false">+O76</f>
         <v>0</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G136" s="209" t="s">
-        <v>175</v>
-      </c>
-      <c r="H136" s="210"/>
-      <c r="I136" s="204" t="n">
+      <c r="G136" s="210" t="s">
+        <v>179</v>
+      </c>
+      <c r="H136" s="211"/>
+      <c r="I136" s="205" t="n">
         <f aca="false">+H72</f>
         <v>0</v>
       </c>
-      <c r="J136" s="207" t="s">
-        <v>176</v>
-      </c>
-      <c r="K136" s="207"/>
-      <c r="L136" s="206" t="n">
+      <c r="J136" s="208" t="s">
+        <v>180</v>
+      </c>
+      <c r="K136" s="208"/>
+      <c r="L136" s="207" t="n">
         <f aca="false">Flujos!G53*Flujos!H53</f>
         <v>0</v>
       </c>
-      <c r="M136" s="207" t="s">
+      <c r="M136" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="N136" s="207"/>
-      <c r="O136" s="207"/>
-      <c r="P136" s="206" t="n">
+      <c r="N136" s="208"/>
+      <c r="O136" s="208"/>
+      <c r="P136" s="207" t="n">
         <f aca="false">+O86</f>
         <v>951.6192</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G137" s="209" t="s">
-        <v>177</v>
-      </c>
-      <c r="H137" s="210"/>
-      <c r="I137" s="204" t="n">
+      <c r="G137" s="210" t="s">
+        <v>181</v>
+      </c>
+      <c r="H137" s="211"/>
+      <c r="I137" s="205" t="n">
         <f aca="false">+H77</f>
         <v>0</v>
       </c>
-      <c r="J137" s="207" t="s">
-        <v>178</v>
-      </c>
-      <c r="K137" s="207"/>
-      <c r="L137" s="206" t="n">
+      <c r="J137" s="208" t="s">
+        <v>182</v>
+      </c>
+      <c r="K137" s="208"/>
+      <c r="L137" s="207" t="n">
         <f aca="false">Flujos!G42*Flujos!H42</f>
         <v>0</v>
       </c>
-      <c r="M137" s="207" t="s">
-        <v>143</v>
-      </c>
-      <c r="N137" s="207"/>
-      <c r="O137" s="207"/>
-      <c r="P137" s="206" t="n">
+      <c r="M137" s="208" t="s">
+        <v>145</v>
+      </c>
+      <c r="N137" s="208"/>
+      <c r="O137" s="208"/>
+      <c r="P137" s="207" t="n">
         <f aca="false">Q81</f>
         <v>0</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G138" s="209" t="s">
-        <v>179</v>
-      </c>
-      <c r="H138" s="210"/>
-      <c r="I138" s="204" t="n">
+      <c r="G138" s="210" t="s">
+        <v>183</v>
+      </c>
+      <c r="H138" s="211"/>
+      <c r="I138" s="205" t="n">
         <f aca="false">+L76</f>
         <v>0</v>
       </c>
-      <c r="J138" s="207" t="s">
-        <v>180</v>
-      </c>
-      <c r="K138" s="207"/>
-      <c r="L138" s="206" t="n">
+      <c r="J138" s="208" t="s">
+        <v>184</v>
+      </c>
+      <c r="K138" s="208"/>
+      <c r="L138" s="207" t="n">
         <f aca="false">Flujos!G26*Flujos!H26</f>
         <v>44164.5778393582</v>
       </c>
-      <c r="M138" s="207" t="s">
-        <v>181</v>
-      </c>
-      <c r="N138" s="207"/>
-      <c r="O138" s="207"/>
-      <c r="P138" s="206" t="n">
+      <c r="M138" s="208" t="s">
+        <v>185</v>
+      </c>
+      <c r="N138" s="208"/>
+      <c r="O138" s="208"/>
+      <c r="P138" s="207" t="n">
         <f aca="false">Flujos!G68*Flujos!H68</f>
         <v>0</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G139" s="209" t="s">
-        <v>182</v>
-      </c>
-      <c r="H139" s="210"/>
-      <c r="I139" s="204" t="n">
+      <c r="G139" s="210" t="s">
+        <v>186</v>
+      </c>
+      <c r="H139" s="211"/>
+      <c r="I139" s="205" t="n">
         <f aca="false">+L80</f>
         <v>0</v>
       </c>
-      <c r="J139" s="207" t="s">
-        <v>183</v>
-      </c>
-      <c r="K139" s="207"/>
-      <c r="L139" s="206" t="n">
+      <c r="J139" s="208" t="s">
+        <v>187</v>
+      </c>
+      <c r="K139" s="208"/>
+      <c r="L139" s="207" t="n">
         <f aca="false">Flujos!G34*Flujos!H34</f>
         <v>4533.2671999656</v>
       </c>
-      <c r="M139" s="211"/>
-      <c r="N139" s="211"/>
-      <c r="O139" s="211"/>
-      <c r="P139" s="206"/>
+      <c r="M139" s="212"/>
+      <c r="N139" s="212"/>
+      <c r="O139" s="212"/>
+      <c r="P139" s="207"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G140" s="209" t="s">
-        <v>184</v>
-      </c>
-      <c r="H140" s="210"/>
-      <c r="I140" s="204" t="n">
+      <c r="G140" s="210" t="s">
+        <v>188</v>
+      </c>
+      <c r="H140" s="211"/>
+      <c r="I140" s="205" t="n">
         <f aca="false">+K88</f>
         <v>951.6192</v>
       </c>
-      <c r="J140" s="207" t="s">
-        <v>185</v>
-      </c>
-      <c r="K140" s="207"/>
-      <c r="L140" s="206" t="n">
+      <c r="J140" s="208" t="s">
+        <v>189</v>
+      </c>
+      <c r="K140" s="208"/>
+      <c r="L140" s="207" t="n">
         <f aca="false">Flujos!G39*Flujos!H39</f>
         <v>-951.6192</v>
       </c>
-      <c r="M140" s="228"/>
-      <c r="N140" s="229"/>
-      <c r="O140" s="230"/>
-      <c r="P140" s="206"/>
+      <c r="M140" s="229"/>
+      <c r="N140" s="230"/>
+      <c r="O140" s="231"/>
+      <c r="P140" s="207"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G141" s="209" t="s">
-        <v>186</v>
-      </c>
-      <c r="H141" s="210"/>
-      <c r="I141" s="204" t="n">
+      <c r="G141" s="210" t="s">
+        <v>190</v>
+      </c>
+      <c r="H141" s="211"/>
+      <c r="I141" s="205" t="n">
         <f aca="false">+L92</f>
         <v>-951.6192</v>
       </c>
-      <c r="J141" s="207" t="s">
-        <v>187</v>
-      </c>
-      <c r="K141" s="207"/>
-      <c r="L141" s="206" t="n">
+      <c r="J141" s="208" t="s">
+        <v>191</v>
+      </c>
+      <c r="K141" s="208"/>
+      <c r="L141" s="207" t="n">
         <f aca="false">Flujos!G69*Flujos!H69</f>
         <v>1152.2385</v>
       </c>
-      <c r="M141" s="207"/>
-      <c r="N141" s="207"/>
-      <c r="O141" s="207"/>
-      <c r="P141" s="206"/>
+      <c r="M141" s="208"/>
+      <c r="N141" s="208"/>
+      <c r="O141" s="208"/>
+      <c r="P141" s="207"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G142" s="208" t="s">
-        <v>188</v>
-      </c>
-      <c r="H142" s="208"/>
-      <c r="I142" s="204" t="n">
+      <c r="G142" s="209" t="s">
+        <v>192</v>
+      </c>
+      <c r="H142" s="209"/>
+      <c r="I142" s="205" t="n">
         <f aca="false">K84</f>
         <v>3202.0646</v>
       </c>
-      <c r="M142" s="207"/>
-      <c r="N142" s="207"/>
-      <c r="O142" s="207"/>
-      <c r="P142" s="206"/>
+      <c r="M142" s="208"/>
+      <c r="N142" s="208"/>
+      <c r="O142" s="208"/>
+      <c r="P142" s="207"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G143" s="208" t="s">
-        <v>202</v>
-      </c>
-      <c r="H143" s="208"/>
-      <c r="I143" s="204" t="n">
+      <c r="G143" s="209" t="s">
+        <v>206</v>
+      </c>
+      <c r="H143" s="209"/>
+      <c r="I143" s="205" t="n">
         <f aca="false">Flujos!G59*Flujos!H59</f>
         <v>0</v>
       </c>
-      <c r="J143" s="207"/>
-      <c r="K143" s="207"/>
-      <c r="L143" s="206"/>
-      <c r="M143" s="231"/>
-      <c r="N143" s="231"/>
-      <c r="O143" s="231"/>
-      <c r="P143" s="206"/>
+      <c r="J143" s="208"/>
+      <c r="K143" s="208"/>
+      <c r="L143" s="207"/>
+      <c r="M143" s="232"/>
+      <c r="N143" s="232"/>
+      <c r="O143" s="232"/>
+      <c r="P143" s="207"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G144" s="208" t="s">
-        <v>203</v>
-      </c>
-      <c r="H144" s="208"/>
-      <c r="I144" s="204" t="n">
+      <c r="G144" s="209" t="s">
+        <v>207</v>
+      </c>
+      <c r="H144" s="209"/>
+      <c r="I144" s="205" t="n">
         <f aca="false">Flujos!G60*Flujos!H60</f>
         <v>1331.2026</v>
       </c>
-      <c r="J144" s="207"/>
-      <c r="K144" s="207"/>
-      <c r="L144" s="206"/>
-      <c r="M144" s="231"/>
-      <c r="N144" s="231"/>
-      <c r="O144" s="231"/>
-      <c r="P144" s="206"/>
+      <c r="J144" s="208"/>
+      <c r="K144" s="208"/>
+      <c r="L144" s="207"/>
+      <c r="M144" s="232"/>
+      <c r="N144" s="232"/>
+      <c r="O144" s="232"/>
+      <c r="P144" s="207"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G145" s="208" t="s">
-        <v>204</v>
-      </c>
-      <c r="H145" s="208"/>
-      <c r="I145" s="204" t="n">
+      <c r="G145" s="209" t="s">
+        <v>208</v>
+      </c>
+      <c r="H145" s="209"/>
+      <c r="I145" s="205" t="n">
         <f aca="false">Flujos!G61*Flujos!H61</f>
         <v>0</v>
       </c>
-      <c r="J145" s="207"/>
-      <c r="K145" s="207"/>
-      <c r="L145" s="206"/>
-      <c r="M145" s="231"/>
-      <c r="N145" s="231"/>
-      <c r="O145" s="231"/>
-      <c r="P145" s="206"/>
+      <c r="J145" s="208"/>
+      <c r="K145" s="208"/>
+      <c r="L145" s="207"/>
+      <c r="M145" s="232"/>
+      <c r="N145" s="232"/>
+      <c r="O145" s="232"/>
+      <c r="P145" s="207"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G146" s="208" t="s">
-        <v>192</v>
-      </c>
-      <c r="H146" s="208"/>
-      <c r="I146" s="204" t="n">
+      <c r="G146" s="209" t="s">
+        <v>196</v>
+      </c>
+      <c r="H146" s="209"/>
+      <c r="I146" s="205" t="n">
         <f aca="false">Flujos!G62*Flujos!H62</f>
         <v>0</v>
       </c>
-      <c r="J146" s="207"/>
-      <c r="K146" s="207"/>
-      <c r="L146" s="206"/>
-      <c r="M146" s="231"/>
-      <c r="N146" s="231"/>
-      <c r="O146" s="231"/>
-      <c r="P146" s="206"/>
+      <c r="J146" s="208"/>
+      <c r="K146" s="208"/>
+      <c r="L146" s="207"/>
+      <c r="M146" s="232"/>
+      <c r="N146" s="232"/>
+      <c r="O146" s="232"/>
+      <c r="P146" s="207"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G147" s="208" t="s">
-        <v>193</v>
-      </c>
-      <c r="H147" s="208"/>
-      <c r="I147" s="204" t="n">
+      <c r="G147" s="209" t="s">
+        <v>197</v>
+      </c>
+      <c r="H147" s="209"/>
+      <c r="I147" s="205" t="n">
         <f aca="false">Flujos!G66*Flujos!H66</f>
         <v>0</v>
       </c>
-      <c r="J147" s="207"/>
-      <c r="K147" s="207"/>
-      <c r="L147" s="206"/>
-      <c r="M147" s="207"/>
-      <c r="N147" s="207"/>
-      <c r="O147" s="207"/>
-      <c r="P147" s="206"/>
+      <c r="J147" s="208"/>
+      <c r="K147" s="208"/>
+      <c r="L147" s="207"/>
+      <c r="M147" s="208"/>
+      <c r="N147" s="208"/>
+      <c r="O147" s="208"/>
+      <c r="P147" s="207"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G148" s="209" t="s">
-        <v>194</v>
-      </c>
-      <c r="H148" s="210"/>
-      <c r="I148" s="204" t="n">
+      <c r="G148" s="210" t="s">
+        <v>198</v>
+      </c>
+      <c r="H148" s="211"/>
+      <c r="I148" s="205" t="n">
         <f aca="false">Flujos!G67*Flujos!H67</f>
         <v>0</v>
       </c>
-      <c r="J148" s="207"/>
-      <c r="K148" s="207"/>
-      <c r="L148" s="206"/>
-      <c r="M148" s="207"/>
-      <c r="N148" s="207"/>
-      <c r="O148" s="207"/>
-      <c r="P148" s="206"/>
+      <c r="J148" s="208"/>
+      <c r="K148" s="208"/>
+      <c r="L148" s="207"/>
+      <c r="M148" s="208"/>
+      <c r="N148" s="208"/>
+      <c r="O148" s="208"/>
+      <c r="P148" s="207"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G149" s="209" t="s">
-        <v>195</v>
-      </c>
-      <c r="H149" s="210"/>
-      <c r="I149" s="204" t="n">
+      <c r="G149" s="210" t="s">
+        <v>199</v>
+      </c>
+      <c r="H149" s="211"/>
+      <c r="I149" s="205" t="n">
         <f aca="false">Flujos!G70*Flujos!H70</f>
         <v>205.9176</v>
       </c>
-      <c r="J149" s="207"/>
-      <c r="K149" s="207"/>
-      <c r="L149" s="206"/>
-      <c r="M149" s="207"/>
-      <c r="N149" s="207"/>
-      <c r="O149" s="207"/>
-      <c r="P149" s="206"/>
+      <c r="J149" s="208"/>
+      <c r="K149" s="208"/>
+      <c r="L149" s="207"/>
+      <c r="M149" s="208"/>
+      <c r="N149" s="208"/>
+      <c r="O149" s="208"/>
+      <c r="P149" s="207"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G150" s="209" t="s">
-        <v>195</v>
-      </c>
-      <c r="H150" s="210"/>
-      <c r="I150" s="204" t="n">
+      <c r="G150" s="210" t="s">
+        <v>199</v>
+      </c>
+      <c r="H150" s="211"/>
+      <c r="I150" s="205" t="n">
         <f aca="false">Flujos!G72*Flujos!H72</f>
         <v>0</v>
       </c>
-      <c r="J150" s="207"/>
-      <c r="K150" s="207"/>
-      <c r="L150" s="206"/>
-      <c r="M150" s="207"/>
-      <c r="N150" s="207"/>
-      <c r="O150" s="207"/>
-      <c r="P150" s="206"/>
+      <c r="J150" s="208"/>
+      <c r="K150" s="208"/>
+      <c r="L150" s="207"/>
+      <c r="M150" s="208"/>
+      <c r="N150" s="208"/>
+      <c r="O150" s="208"/>
+      <c r="P150" s="207"/>
     </row>
     <row r="151" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G151" s="213" t="s">
-        <v>197</v>
-      </c>
-      <c r="H151" s="213"/>
-      <c r="I151" s="214" t="n">
+      <c r="G151" s="214" t="s">
+        <v>201</v>
+      </c>
+      <c r="H151" s="214"/>
+      <c r="I151" s="215" t="n">
         <f aca="false">+SUM(I128:I150)</f>
         <v>59602.6644799715</v>
       </c>
-      <c r="J151" s="215" t="s">
-        <v>198</v>
-      </c>
-      <c r="K151" s="215"/>
-      <c r="L151" s="216" t="n">
+      <c r="J151" s="216" t="s">
+        <v>202</v>
+      </c>
+      <c r="K151" s="216"/>
+      <c r="L151" s="217" t="n">
         <f aca="false">+SUM(L128:L141)</f>
         <v>45350.9504846625</v>
       </c>
-      <c r="M151" s="215" t="s">
-        <v>199</v>
-      </c>
-      <c r="N151" s="215"/>
-      <c r="O151" s="215"/>
-      <c r="P151" s="214" t="n">
+      <c r="M151" s="216" t="s">
+        <v>203</v>
+      </c>
+      <c r="N151" s="216"/>
+      <c r="O151" s="216"/>
+      <c r="P151" s="215" t="n">
         <f aca="false">+SUM(P128:P141)</f>
         <v>16489.0254945414</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G152" s="217"/>
-      <c r="H152" s="217"/>
-      <c r="I152" s="217"/>
-      <c r="J152" s="217"/>
-      <c r="K152" s="217"/>
-      <c r="L152" s="217"/>
-      <c r="M152" s="217"/>
-      <c r="N152" s="217"/>
-      <c r="O152" s="217"/>
-      <c r="P152" s="217"/>
+      <c r="G152" s="218"/>
+      <c r="H152" s="218"/>
+      <c r="I152" s="218"/>
+      <c r="J152" s="218"/>
+      <c r="K152" s="218"/>
+      <c r="L152" s="218"/>
+      <c r="M152" s="218"/>
+      <c r="N152" s="218"/>
+      <c r="O152" s="218"/>
+      <c r="P152" s="218"/>
     </row>
     <row r="153" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G153" s="217"/>
-      <c r="J153" s="217"/>
-      <c r="K153" s="217"/>
-      <c r="L153" s="218" t="s">
-        <v>200</v>
-      </c>
-      <c r="M153" s="219"/>
-      <c r="N153" s="220"/>
-      <c r="O153" s="219"/>
-      <c r="P153" s="221" t="n">
+      <c r="G153" s="218"/>
+      <c r="J153" s="218"/>
+      <c r="K153" s="218"/>
+      <c r="L153" s="219" t="s">
+        <v>204</v>
+      </c>
+      <c r="M153" s="220"/>
+      <c r="N153" s="221"/>
+      <c r="O153" s="220"/>
+      <c r="P153" s="222" t="n">
         <f aca="false">+I151-L151-P151</f>
         <v>-2237.3114992324</v>
       </c>
@@ -22848,7 +22938,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{1540C97C-D484-42F0-B390-541565331370}">
+          <x14:cfRule type="iconSet" priority="2" id="{9765DEB9-5318-4EF1-B17D-EE7126D4AC71}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22867,7 +22957,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{CD44E68F-D072-45FB-B7E2-10D781FE48E6}">
+          <x14:cfRule type="iconSet" priority="3" id="{78E998CA-943B-45EE-B7AA-3D15A8FFC3C0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22886,7 +22976,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{B2789339-9D20-4ED5-AD6A-134334DFC781}">
+          <x14:cfRule type="iconSet" priority="4" id="{E8E1A4B4-7448-4BF0-8DBC-711E99FF7125}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22905,7 +22995,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{21F0D6A6-107E-449F-912A-2BB7C59EC64A}">
+          <x14:cfRule type="iconSet" priority="5" id="{49EE5B24-A2A0-4ED3-98A9-EC65FD27EA68}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22924,7 +23014,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{63CDCCB5-AE7A-4F72-9A7E-3353F6D129DA}">
+          <x14:cfRule type="iconSet" priority="6" id="{CFFB3415-86D2-4D35-8649-B47FDFCB008A}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22943,7 +23033,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{DD8EFDBD-A890-4F93-A4C9-BB856DE2E1CA}">
+          <x14:cfRule type="iconSet" priority="7" id="{4DA4D58B-A498-4525-9DA9-40F277559C6E}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22962,7 +23052,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{C350D5EB-CE57-4FD8-B87E-5EDC6B185DD3}">
+          <x14:cfRule type="iconSet" priority="8" id="{35F667E1-1990-49CE-9934-25FB7CF739E7}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22981,7 +23071,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{2B17E6C8-5E20-4D50-AAA3-5AED1E776916}">
+          <x14:cfRule type="iconSet" priority="9" id="{50BE32B5-F4DF-4A2E-A63F-352194446570}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23000,7 +23090,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{3AF7197D-A68F-4649-A1BE-B6ABFD1D1FF4}">
+          <x14:cfRule type="iconSet" priority="10" id="{1AAD1CDD-D179-4DB1-AE93-601690BF9097}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23019,7 +23109,7 @@
           <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{8DBEA9BE-2C42-466C-8A69-318DDB564CC5}">
+          <x14:cfRule type="iconSet" priority="11" id="{A5D5857C-C587-42B7-827B-F1C2CFF5D4C8}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23038,7 +23128,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{71A2E8B4-1FDA-41DF-91C6-538FCB4E6F33}">
+          <x14:cfRule type="iconSet" priority="12" id="{9DDF5DF0-34D9-48F7-B0C1-21F8125D4DE0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23057,7 +23147,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{4095FB1C-C0AC-4BA0-A617-C8DF665354D7}">
+          <x14:cfRule type="iconSet" priority="13" id="{AB949B10-BD10-4D96-8159-894D76E04467}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23076,7 +23166,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{4C60B51A-D08C-446B-8760-46A568BFCF60}">
+          <x14:cfRule type="iconSet" priority="14" id="{9F1E5610-4D4E-425A-8C40-81A654393CD0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23095,7 +23185,7 @@
           <xm:sqref>N88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{6A727339-6FC8-4EFE-9E58-DE615E2034EC}">
+          <x14:cfRule type="iconSet" priority="15" id="{3B3162F3-F0B0-4C18-AF9E-471F5E2C7815}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" state="visible" r:id="rId3"/>
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="207">
   <si>
     <t xml:space="preserve">BALANCE METALÚRGICO - VALLE ELQUI</t>
   </si>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">Sinter SERCOOP (camiones)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sinter Santa Fe (camiones)</t>
+    <t xml:space="preserve">Sinter Tofo (camiones)</t>
   </si>
   <si>
     <t xml:space="preserve">Granzas Pleito</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">SF SERCOOP</t>
   </si>
   <si>
-    <t xml:space="preserve">SF Santa Fe</t>
+    <t xml:space="preserve">SF Tofo</t>
   </si>
   <si>
     <t xml:space="preserve">Resguardo</t>
@@ -785,53 +785,7 @@
     <t xml:space="preserve">GR PLEITO</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Embarque </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Preconcentrado Ventas</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Recepción Preconcentrado ventas</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Recepción</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Preconcentrado ventas</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Delta Preconcentrado Ventas</t>
@@ -963,7 +917,7 @@
     <t xml:space="preserve">Rec EL Dorado</t>
   </si>
   <si>
-    <t xml:space="preserve">Rec Santa Fe</t>
+    <t xml:space="preserve">Rec Tofo</t>
   </si>
   <si>
     <t xml:space="preserve">Rec Rsguardo</t>
@@ -1000,7 +954,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0\ %"/>
@@ -1015,7 +969,6 @@
     <numFmt numFmtId="175" formatCode="#,##0.000_ ;\-#,##0.000\ "/>
     <numFmt numFmtId="176" formatCode="#,##0.0000000_ ;\-#,##0.0000000\ "/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="178" formatCode="0.00\ %"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -1182,13 +1135,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1225,6 +1171,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1635,7 +1587,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="232">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2160,11 +2112,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2172,7 +2124,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2184,7 +2136,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2192,7 +2144,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2204,7 +2156,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2212,7 +2164,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="21" fillId="0" borderId="9" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="21" fillId="0" borderId="9" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2304,14 +2256,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2332,59 +2276,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2392,19 +2336,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="4" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2412,7 +2356,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2420,7 +2364,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2436,7 +2380,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2444,7 +2388,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="16" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="16" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2488,6 +2432,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2512,7 +2460,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2532,7 +2480,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="28" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2699,9 +2647,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>440280</xdr:colOff>
+      <xdr:colOff>439920</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>186840</xdr:rowOff>
+      <xdr:rowOff>186480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2715,7 +2663,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="716760" y="438480"/>
-          <a:ext cx="944640" cy="510480"/>
+          <a:ext cx="944280" cy="510120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2742,9 +2690,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>223200</xdr:colOff>
+      <xdr:colOff>222840</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>106200</xdr:rowOff>
+      <xdr:rowOff>105840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2754,7 +2702,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4093200" y="1426320"/>
-          <a:ext cx="1050480" cy="394560"/>
+          <a:ext cx="1050120" cy="394200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2821,9 +2769,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>647280</xdr:colOff>
+      <xdr:colOff>646920</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2833,7 +2781,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7032600" y="2008080"/>
-          <a:ext cx="499320" cy="377640"/>
+          <a:ext cx="498960" cy="377280"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -2874,9 +2822,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>378720</xdr:colOff>
+      <xdr:colOff>378360</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>68040</xdr:rowOff>
+      <xdr:rowOff>67680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2886,7 +2834,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6328800" y="1703520"/>
-          <a:ext cx="934560" cy="460080"/>
+          <a:ext cx="934200" cy="459720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2950,9 +2898,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>94680</xdr:colOff>
+      <xdr:colOff>94320</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>93600</xdr:rowOff>
+      <xdr:rowOff>93240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2962,7 +2910,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10133280" y="3195720"/>
-          <a:ext cx="1192680" cy="326880"/>
+          <a:ext cx="1192320" cy="326520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3026,9 +2974,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>408960</xdr:colOff>
+      <xdr:colOff>408600</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:rowOff>65880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3038,7 +2986,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7525440" y="6415920"/>
-          <a:ext cx="645120" cy="508320"/>
+          <a:ext cx="644760" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3079,9 +3027,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>75960</xdr:colOff>
+      <xdr:colOff>75600</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>23760</xdr:rowOff>
+      <xdr:rowOff>23400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3091,7 +3039,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6535800" y="8088840"/>
-          <a:ext cx="1301760" cy="507600"/>
+          <a:ext cx="1301400" cy="507240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3155,9 +3103,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>717480</xdr:colOff>
+      <xdr:colOff>717120</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>136080</xdr:rowOff>
+      <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3167,7 +3115,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7239960" y="10028520"/>
-          <a:ext cx="1239120" cy="394560"/>
+          <a:ext cx="1238760" cy="394200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3234,9 +3182,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>624960</xdr:colOff>
+      <xdr:colOff>624600</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>59400</xdr:rowOff>
+      <xdr:rowOff>59040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3246,7 +3194,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9572760" y="11553120"/>
-          <a:ext cx="576000" cy="507960"/>
+          <a:ext cx="575640" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3287,9 +3235,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>698400</xdr:colOff>
+      <xdr:colOff>698040</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>5760</xdr:rowOff>
+      <xdr:rowOff>5400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3299,7 +3247,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9934560" y="11643120"/>
-          <a:ext cx="1047600" cy="364320"/>
+          <a:ext cx="1047240" cy="363960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3363,9 +3311,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>654840</xdr:colOff>
+      <xdr:colOff>654480</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>68760</xdr:rowOff>
+      <xdr:rowOff>68400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3375,7 +3323,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9602640" y="12899160"/>
-          <a:ext cx="576000" cy="504720"/>
+          <a:ext cx="575640" cy="504360"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3416,9 +3364,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>461160</xdr:colOff>
+      <xdr:colOff>460800</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>93600</xdr:rowOff>
+      <xdr:rowOff>93240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3428,7 +3376,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9697320" y="12543120"/>
-          <a:ext cx="1047600" cy="504360"/>
+          <a:ext cx="1047240" cy="504000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3492,9 +3440,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>490680</xdr:colOff>
+      <xdr:colOff>490320</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>29520</xdr:rowOff>
+      <xdr:rowOff>29160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3504,7 +3452,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12092040" y="11523240"/>
-          <a:ext cx="2511000" cy="507960"/>
+          <a:ext cx="2510640" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3568,9 +3516,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>110520</xdr:colOff>
+      <xdr:colOff>110160</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>1080</xdr:rowOff>
+      <xdr:rowOff>720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3580,7 +3528,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12144240" y="12256920"/>
-          <a:ext cx="2893320" cy="507600"/>
+          <a:ext cx="2892960" cy="507240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3644,9 +3592,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>490680</xdr:colOff>
+      <xdr:colOff>490320</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>150840</xdr:rowOff>
+      <xdr:rowOff>150480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3656,7 +3604,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12092040" y="12977640"/>
-          <a:ext cx="2511000" cy="508320"/>
+          <a:ext cx="2510640" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3720,9 +3668,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>5760</xdr:colOff>
+      <xdr:colOff>5400</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>105480</xdr:rowOff>
+      <xdr:rowOff>105120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3732,7 +3680,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9715680" y="15218280"/>
-          <a:ext cx="573840" cy="508320"/>
+          <a:ext cx="573480" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -3773,9 +3721,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>729360</xdr:colOff>
+      <xdr:colOff>729000</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>163080</xdr:rowOff>
+      <xdr:rowOff>162720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3785,7 +3733,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10067400" y="15276240"/>
-          <a:ext cx="945720" cy="507960"/>
+          <a:ext cx="945360" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3849,9 +3797,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>603360</xdr:colOff>
+      <xdr:colOff>603000</xdr:colOff>
       <xdr:row>83</xdr:row>
-      <xdr:rowOff>12960</xdr:rowOff>
+      <xdr:rowOff>12600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3861,7 +3809,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12204720" y="15316560"/>
-          <a:ext cx="2511000" cy="507960"/>
+          <a:ext cx="2510640" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3925,9 +3873,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>577440</xdr:colOff>
+      <xdr:colOff>577080</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>118080</xdr:rowOff>
+      <xdr:rowOff>117720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3937,7 +3885,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5277960" y="4117680"/>
-          <a:ext cx="219960" cy="191520"/>
+          <a:ext cx="219600" cy="191160"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -4017,9 +3965,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>642960</xdr:colOff>
+      <xdr:colOff>642600</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>90720</xdr:rowOff>
+      <xdr:rowOff>90360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4029,7 +3977,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2747520" y="11114640"/>
-          <a:ext cx="1365840" cy="406080"/>
+          <a:ext cx="1365480" cy="405720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4093,9 +4041,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>12600</xdr:colOff>
+      <xdr:colOff>12240</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>142560</xdr:rowOff>
+      <xdr:rowOff>142200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4105,7 +4053,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2658960" y="666720"/>
-          <a:ext cx="1514160" cy="237960"/>
+          <a:ext cx="1513800" cy="237600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4208,9 +4156,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>682920</xdr:colOff>
+      <xdr:colOff>682560</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>99720</xdr:rowOff>
+      <xdr:rowOff>99360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4220,7 +4168,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2762640" y="2258640"/>
-          <a:ext cx="576000" cy="507960"/>
+          <a:ext cx="575640" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4261,9 +4209,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>162000</xdr:colOff>
+      <xdr:colOff>161640</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>77040</xdr:rowOff>
+      <xdr:rowOff>76680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4273,7 +4221,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2031480" y="2628360"/>
-          <a:ext cx="786240" cy="306360"/>
+          <a:ext cx="785880" cy="306000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4337,9 +4285,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>669600</xdr:colOff>
+      <xdr:colOff>669240</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>176400</xdr:rowOff>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4349,7 +4297,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="323280" y="2157120"/>
-          <a:ext cx="557640" cy="305280"/>
+          <a:ext cx="557280" cy="304920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4491,9 +4439,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>122040</xdr:colOff>
+      <xdr:colOff>121680</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>101880</xdr:rowOff>
+      <xdr:rowOff>101520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4503,7 +4451,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1205280" y="3620160"/>
-          <a:ext cx="1572480" cy="291600"/>
+          <a:ext cx="1572120" cy="291240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4682,9 +4630,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>712800</xdr:colOff>
+      <xdr:colOff>712440</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>111240</xdr:rowOff>
+      <xdr:rowOff>110880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4694,7 +4642,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4069080" y="2381040"/>
-          <a:ext cx="804240" cy="206640"/>
+          <a:ext cx="803880" cy="206280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4797,9 +4745,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>238680</xdr:colOff>
+      <xdr:colOff>238320</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>32040</xdr:rowOff>
+      <xdr:rowOff>31680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4809,7 +4757,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3080520" y="4476600"/>
-          <a:ext cx="628560" cy="508320"/>
+          <a:ext cx="628200" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -4850,9 +4798,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>714600</xdr:colOff>
+      <xdr:colOff>714240</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>37080</xdr:rowOff>
+      <xdr:rowOff>36720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4862,7 +4810,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2379960" y="4873680"/>
-          <a:ext cx="990360" cy="307080"/>
+          <a:ext cx="990000" cy="306720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4926,9 +4874,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>214560</xdr:colOff>
+      <xdr:colOff>214200</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>177840</xdr:rowOff>
+      <xdr:rowOff>177480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4938,7 +4886,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1979640" y="4444560"/>
-          <a:ext cx="890640" cy="305280"/>
+          <a:ext cx="890280" cy="304920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5080,9 +5028,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>142560</xdr:colOff>
+      <xdr:colOff>142200</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>128160</xdr:rowOff>
+      <xdr:rowOff>127800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5092,7 +5040,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3537000" y="4389480"/>
-          <a:ext cx="766080" cy="310680"/>
+          <a:ext cx="765720" cy="310320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5156,9 +5104,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>256320</xdr:colOff>
+      <xdr:colOff>255960</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>181800</xdr:rowOff>
+      <xdr:rowOff>181440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5168,7 +5116,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3098160" y="6150960"/>
-          <a:ext cx="628560" cy="507960"/>
+          <a:ext cx="628200" cy="507600"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5209,9 +5157,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>669600</xdr:colOff>
+      <xdr:colOff>669240</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:rowOff>16920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5221,7 +5169,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2337840" y="6646320"/>
-          <a:ext cx="987480" cy="419400"/>
+          <a:ext cx="987120" cy="419040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5363,9 +5311,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>363600</xdr:colOff>
+      <xdr:colOff>363240</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>47160</xdr:rowOff>
+      <xdr:rowOff>46800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5375,7 +5323,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3375000" y="5895000"/>
-          <a:ext cx="1149120" cy="438840"/>
+          <a:ext cx="1148760" cy="438480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5439,9 +5387,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>10080</xdr:colOff>
+      <xdr:colOff>9720</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>72720</xdr:rowOff>
+      <xdr:rowOff>72360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5451,7 +5399,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2113560" y="6151320"/>
-          <a:ext cx="552240" cy="208080"/>
+          <a:ext cx="551880" cy="207720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5554,9 +5502,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>264240</xdr:colOff>
+      <xdr:colOff>263880</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>23400</xdr:rowOff>
+      <xdr:rowOff>23040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5566,7 +5514,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3106080" y="7897680"/>
-          <a:ext cx="628560" cy="507600"/>
+          <a:ext cx="628200" cy="507240"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5607,9 +5555,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>744480</xdr:colOff>
+      <xdr:colOff>744120</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>145440</xdr:rowOff>
+      <xdr:rowOff>145080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5619,7 +5567,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2308680" y="8422560"/>
-          <a:ext cx="1091520" cy="295560"/>
+          <a:ext cx="1091160" cy="295200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5722,9 +5670,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>289080</xdr:colOff>
+      <xdr:colOff>288720</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>85320</xdr:rowOff>
+      <xdr:rowOff>84960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5734,7 +5682,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3390480" y="7627320"/>
-          <a:ext cx="1059120" cy="459000"/>
+          <a:ext cx="1058760" cy="458640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5798,9 +5746,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>18360</xdr:colOff>
+      <xdr:colOff>18000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>91080</xdr:rowOff>
+      <xdr:rowOff>90720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5810,7 +5758,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2121840" y="7761600"/>
-          <a:ext cx="552240" cy="330480"/>
+          <a:ext cx="551880" cy="330120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5913,9 +5861,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>213120</xdr:colOff>
+      <xdr:colOff>212760</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>43560</xdr:rowOff>
+      <xdr:rowOff>43200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5925,7 +5873,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3054960" y="9816480"/>
-          <a:ext cx="628560" cy="514080"/>
+          <a:ext cx="628200" cy="513720"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -5966,9 +5914,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>656280</xdr:colOff>
+      <xdr:colOff>655920</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>92880</xdr:rowOff>
+      <xdr:rowOff>92520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5978,7 +5926,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2683800" y="10378800"/>
-          <a:ext cx="1442880" cy="191520"/>
+          <a:ext cx="1442520" cy="191160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6081,9 +6029,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>415800</xdr:colOff>
+      <xdr:colOff>415440</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>166320</xdr:rowOff>
+      <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6093,7 +6041,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3511440" y="9511560"/>
-          <a:ext cx="1064880" cy="560880"/>
+          <a:ext cx="1064520" cy="560520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6157,9 +6105,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>118440</xdr:colOff>
+      <xdr:colOff>118080</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>96840</xdr:rowOff>
+      <xdr:rowOff>96480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6169,7 +6117,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1936080" y="9604080"/>
-          <a:ext cx="838080" cy="208440"/>
+          <a:ext cx="837720" cy="208080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6389,9 +6337,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>727200</xdr:colOff>
+      <xdr:colOff>726840</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6401,9 +6349,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="9675000" y="3014640"/>
-          <a:ext cx="576000" cy="508320"/>
+          <a:ext cx="575640" cy="507960"/>
           <a:chOff x="9675000" y="3014640"/>
-          <a:chExt cx="576000" cy="508320"/>
+          <a:chExt cx="575640" cy="507960"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6414,7 +6362,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9675000" y="3014640"/>
-            <a:ext cx="576000" cy="508320"/>
+            <a:ext cx="575640" cy="507960"/>
           </a:xfrm>
           <a:prstGeom prst="triangle">
             <a:avLst>
@@ -6452,7 +6400,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9892080" y="3105720"/>
-            <a:ext cx="142200" cy="117720"/>
+            <a:ext cx="141840" cy="117360"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6485,7 +6433,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="9964440" y="3247920"/>
-            <a:ext cx="142200" cy="117720"/>
+            <a:ext cx="141840" cy="117360"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6518,7 +6466,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10036440" y="3372840"/>
-            <a:ext cx="142200" cy="117720"/>
+            <a:ext cx="141840" cy="117360"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6555,9 +6503,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>534600</xdr:colOff>
+      <xdr:colOff>534240</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>15840</xdr:rowOff>
+      <xdr:rowOff>15480</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6567,9 +6515,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="10456200" y="1526400"/>
-          <a:ext cx="1309680" cy="394560"/>
+          <a:ext cx="1309320" cy="394200"/>
           <a:chOff x="10456200" y="1526400"/>
-          <a:chExt cx="1309680" cy="394560"/>
+          <a:chExt cx="1309320" cy="394200"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -6580,7 +6528,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="10456200" y="1526400"/>
-            <a:ext cx="1309680" cy="394560"/>
+            <a:ext cx="1309320" cy="394200"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6644,7 +6592,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="11439000" y="1801440"/>
-            <a:ext cx="165600" cy="117720"/>
+            <a:ext cx="165240" cy="117360"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -6757,9 +6705,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>932040</xdr:colOff>
+      <xdr:colOff>931680</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>65520</xdr:rowOff>
+      <xdr:rowOff>65160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6769,7 +6717,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11943720" y="1746720"/>
-          <a:ext cx="1034280" cy="414360"/>
+          <a:ext cx="1033920" cy="414000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6879,9 +6827,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>795960</xdr:colOff>
+      <xdr:colOff>795600</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>171000</xdr:rowOff>
+      <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6891,7 +6839,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="11890800" y="1023480"/>
-          <a:ext cx="951120" cy="480960"/>
+          <a:ext cx="950760" cy="480600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7001,9 +6949,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>682920</xdr:colOff>
+      <xdr:colOff>682560</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>164520</xdr:rowOff>
+      <xdr:rowOff>164160</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7013,9 +6961,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="7205400" y="4346280"/>
-          <a:ext cx="1239120" cy="390240"/>
+          <a:ext cx="1238760" cy="389880"/>
           <a:chOff x="7205400" y="4346280"/>
-          <a:chExt cx="1239120" cy="390240"/>
+          <a:chExt cx="1238760" cy="389880"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp>
@@ -7026,7 +6974,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="7205400" y="4347360"/>
-            <a:ext cx="1239120" cy="389160"/>
+            <a:ext cx="1238760" cy="388800"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7090,7 +7038,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="8280000" y="4346280"/>
-            <a:ext cx="156600" cy="116280"/>
+            <a:ext cx="156240" cy="115920"/>
           </a:xfrm>
           <a:prstGeom prst="ellipse">
             <a:avLst/>
@@ -7205,9 +7153,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>220320</xdr:colOff>
+      <xdr:colOff>219960</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>5760</xdr:rowOff>
+      <xdr:rowOff>5400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7217,7 +7165,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9765000" y="4384440"/>
-          <a:ext cx="739080" cy="193320"/>
+          <a:ext cx="738720" cy="192960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7281,9 +7229,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>149400</xdr:colOff>
+      <xdr:colOff>149040</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>132840</xdr:rowOff>
+      <xdr:rowOff>132480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7293,7 +7241,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10794240" y="4584960"/>
-          <a:ext cx="1401120" cy="310320"/>
+          <a:ext cx="1400760" cy="309960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7357,9 +7305,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>258840</xdr:colOff>
+      <xdr:colOff>258480</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>154440</xdr:rowOff>
+      <xdr:rowOff>154080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7369,7 +7317,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9444600" y="992520"/>
-          <a:ext cx="1098000" cy="304920"/>
+          <a:ext cx="1097640" cy="304560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7433,9 +7381,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>318240</xdr:colOff>
+      <xdr:colOff>317880</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>131040</xdr:rowOff>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7445,7 +7393,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5599800" y="4970160"/>
-          <a:ext cx="1603080" cy="304560"/>
+          <a:ext cx="1602720" cy="304200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7686,9 +7634,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>307440</xdr:colOff>
+      <xdr:colOff>307080</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>72360</xdr:rowOff>
+      <xdr:rowOff>72000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7698,7 +7646,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6005160" y="8893080"/>
-          <a:ext cx="1186920" cy="513720"/>
+          <a:ext cx="1186560" cy="513360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7808,9 +7756,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>507600</xdr:colOff>
+      <xdr:colOff>507240</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>90360</xdr:rowOff>
+      <xdr:rowOff>90000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7820,7 +7768,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8929080" y="8911080"/>
-          <a:ext cx="1102320" cy="513720"/>
+          <a:ext cx="1101960" cy="513360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7967,9 +7915,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>79920</xdr:colOff>
+      <xdr:colOff>79560</xdr:colOff>
       <xdr:row>56</xdr:row>
-      <xdr:rowOff>162000</xdr:rowOff>
+      <xdr:rowOff>161640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7979,7 +7927,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8493840" y="10322280"/>
-          <a:ext cx="1109880" cy="507600"/>
+          <a:ext cx="1109520" cy="507240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8121,9 +8069,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>645840</xdr:colOff>
+      <xdr:colOff>645480</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8133,7 +8081,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7144920" y="10947960"/>
-          <a:ext cx="1262520" cy="404280"/>
+          <a:ext cx="1262160" cy="403920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8266,9 +8214,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>596880</xdr:colOff>
+      <xdr:colOff>596520</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>74520</xdr:rowOff>
+      <xdr:rowOff>74160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8278,7 +8226,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6905520" y="12901320"/>
-          <a:ext cx="576000" cy="508320"/>
+          <a:ext cx="575640" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="triangle">
           <a:avLst>
@@ -8319,9 +8267,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>577440</xdr:colOff>
+      <xdr:colOff>577080</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>54720</xdr:rowOff>
+      <xdr:rowOff>54360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8331,7 +8279,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6275160" y="12501000"/>
-          <a:ext cx="1186920" cy="507600"/>
+          <a:ext cx="1186560" cy="507240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8551,9 +8499,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>752040</xdr:colOff>
+      <xdr:colOff>751680</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>145440</xdr:rowOff>
+      <xdr:rowOff>145080</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8563,7 +8511,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3934800" y="12781800"/>
-          <a:ext cx="977760" cy="508320"/>
+          <a:ext cx="977400" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8627,9 +8575,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>751680</xdr:colOff>
+      <xdr:colOff>751320</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>172080</xdr:rowOff>
+      <xdr:rowOff>171720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8639,7 +8587,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3934440" y="13570920"/>
-          <a:ext cx="977760" cy="507600"/>
+          <a:ext cx="977400" cy="507240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8742,9 +8690,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>30600</xdr:colOff>
+      <xdr:colOff>30240</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>183240</xdr:rowOff>
+      <xdr:rowOff>182880</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8754,7 +8702,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5558400" y="14147280"/>
-          <a:ext cx="1356840" cy="514080"/>
+          <a:ext cx="1356480" cy="513720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8857,9 +8805,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>714960</xdr:colOff>
+      <xdr:colOff>714600</xdr:colOff>
       <xdr:row>79</xdr:row>
-      <xdr:rowOff>172080</xdr:rowOff>
+      <xdr:rowOff>171720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8869,7 +8817,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6545520" y="14851440"/>
-          <a:ext cx="1054080" cy="370080"/>
+          <a:ext cx="1053720" cy="369720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8972,9 +8920,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>711720</xdr:colOff>
+      <xdr:colOff>711360</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>41040</xdr:rowOff>
+      <xdr:rowOff>40680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8984,7 +8932,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6343560" y="15667200"/>
-          <a:ext cx="1252800" cy="375840"/>
+          <a:ext cx="1252440" cy="375480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9087,9 +9035,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>16560</xdr:colOff>
+      <xdr:colOff>16200</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>169200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9099,7 +9047,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6410160" y="16366680"/>
-          <a:ext cx="1368000" cy="376560"/>
+          <a:ext cx="1367640" cy="376200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9241,9 +9189,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>32760</xdr:colOff>
+      <xdr:colOff>32400</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>64080</xdr:rowOff>
+      <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9253,7 +9201,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="12515040" y="14033880"/>
-          <a:ext cx="2444760" cy="508320"/>
+          <a:ext cx="2444400" cy="507960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9368,9 +9316,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>927720</xdr:colOff>
+      <xdr:colOff>927360</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>180360</xdr:rowOff>
+      <xdr:rowOff>180000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -9380,7 +9328,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7634880" y="14465160"/>
-          <a:ext cx="1054440" cy="383760"/>
+          <a:ext cx="1054080" cy="383400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20227,8 +20175,8 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="167" t="s">
-        <v>152</v>
+      <c r="B65" s="150" t="s">
+        <v>123</v>
       </c>
       <c r="C65" s="154" t="n">
         <f aca="false">Utilidad!A62</f>
@@ -20238,8 +20186,8 @@
         <f aca="false">IF(Utilidad!C62&gt;1,Utilidad!C62/100,Utilidad!C62)</f>
         <v>0.5607</v>
       </c>
-      <c r="F65" s="167" t="s">
-        <v>152</v>
+      <c r="F65" s="150" t="s">
+        <v>123</v>
       </c>
       <c r="G65" s="154" t="n">
         <f aca="false">Utilidad!B62</f>
@@ -20348,7 +20296,7 @@
     </row>
     <row r="68" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C68" s="154" t="n">
         <f aca="false">Utilidad!A65</f>
@@ -20358,8 +20306,8 @@
         <f aca="false">IF(Utilidad!C65&gt;1,Utilidad!C65/100,Utilidad!C65)</f>
         <v>0</v>
       </c>
-      <c r="F68" s="168" t="s">
-        <v>154</v>
+      <c r="F68" s="150" t="s">
+        <v>152</v>
       </c>
       <c r="G68" s="154" t="n">
         <f aca="false">Utilidad!B65</f>
@@ -20388,7 +20336,7 @@
     </row>
     <row r="69" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="150" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C69" s="154" t="n">
         <f aca="false">Utilidad!A66</f>
@@ -20399,7 +20347,7 @@
         <v>0.5607</v>
       </c>
       <c r="F69" s="150" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G69" s="154" t="n">
         <f aca="false">Utilidad!B66</f>
@@ -20508,7 +20456,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="150" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C72" s="154" t="n">
         <f aca="false">Utilidad!A69</f>
@@ -20519,7 +20467,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="150" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G72" s="154" t="n">
         <f aca="false">Utilidad!B69</f>
@@ -20552,14 +20500,9 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="J2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="L4:L5 J4:K70 J72:K72">
+  <conditionalFormatting sqref="L4:L5 J4:K70 J72:K72 J71:K72">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>ABS(J4)&gt;=10%</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J71:K72">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>ABS(J71)&gt;=10%</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -20593,315 +20536,315 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="169"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
-      <c r="G2" s="170"/>
-      <c r="H2" s="170"/>
-      <c r="I2" s="170"/>
-      <c r="J2" s="170"/>
-      <c r="K2" s="170"/>
-      <c r="L2" s="170"/>
-      <c r="M2" s="170"/>
-      <c r="N2" s="170"/>
-      <c r="O2" s="170"/>
-      <c r="P2" s="170"/>
-      <c r="Q2" s="170"/>
-      <c r="R2" s="170"/>
-      <c r="S2" s="171"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="168"/>
+      <c r="L2" s="168"/>
+      <c r="M2" s="168"/>
+      <c r="N2" s="168"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="168"/>
+      <c r="Q2" s="168"/>
+      <c r="R2" s="168"/>
+      <c r="S2" s="169"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="172"/>
-      <c r="S3" s="173"/>
+      <c r="B3" s="170"/>
+      <c r="S3" s="171"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="172"/>
-      <c r="S4" s="173"/>
+      <c r="B4" s="170"/>
+      <c r="S4" s="171"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="172"/>
-      <c r="S5" s="173"/>
+      <c r="B5" s="170"/>
+      <c r="S5" s="171"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="172"/>
-      <c r="E6" s="174" t="n">
+      <c r="B6" s="170"/>
+      <c r="E6" s="172" t="n">
         <f aca="false">Flujos!G4</f>
         <v>122150</v>
       </c>
-      <c r="S6" s="173"/>
+      <c r="S6" s="171"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="172"/>
-      <c r="E7" s="175" t="n">
+      <c r="B7" s="170"/>
+      <c r="E7" s="173" t="n">
         <f aca="false">Flujos!H4</f>
         <v>0.29498952501</v>
       </c>
-      <c r="I7" s="174" t="n">
+      <c r="I7" s="172" t="n">
         <f aca="false">+Utilidad!J65</f>
         <v>0</v>
       </c>
-      <c r="L7" s="176" t="n">
+      <c r="L7" s="174" t="n">
         <f aca="false">+Utilidad!J68</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="176" t="n">
+      <c r="Q7" s="174" t="n">
         <f aca="false">Flujos!G12</f>
         <v>21435.044983</v>
       </c>
-      <c r="S7" s="173"/>
+      <c r="S7" s="171"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="172"/>
-      <c r="E8" s="177" t="n">
+      <c r="B8" s="170"/>
+      <c r="E8" s="175" t="n">
         <f aca="false">E6*E7</f>
         <v>36032.9704799715</v>
       </c>
-      <c r="I8" s="175" t="n">
+      <c r="I8" s="173" t="n">
         <f aca="false">+Utilidad!K65</f>
         <v>0</v>
       </c>
-      <c r="L8" s="178" t="n">
+      <c r="L8" s="176" t="n">
         <f aca="false">+Utilidad!K68</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="178" t="n">
+      <c r="Q8" s="176" t="n">
         <f aca="false">Flujos!H12</f>
         <v>0.15974666492</v>
       </c>
-      <c r="S8" s="173"/>
+      <c r="S8" s="171"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="172"/>
-      <c r="I9" s="177" t="n">
+      <c r="B9" s="170"/>
+      <c r="I9" s="175" t="n">
         <f aca="false">+Utilidad!L65</f>
         <v>0</v>
       </c>
-      <c r="L9" s="179" t="n">
+      <c r="L9" s="177" t="n">
         <f aca="false">+Utilidad!L68</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="179" t="n">
+      <c r="Q9" s="177" t="n">
         <f aca="false">Q7*Q8</f>
         <v>3424.17694844443</v>
       </c>
-      <c r="S9" s="173"/>
+      <c r="S9" s="171"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="172"/>
-      <c r="E10" s="174" t="n">
+      <c r="B10" s="170"/>
+      <c r="E10" s="172" t="n">
         <f aca="false">+Utilidad!J63</f>
         <v>0</v>
       </c>
-      <c r="S10" s="173"/>
+      <c r="S10" s="171"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="172"/>
-      <c r="E11" s="175" t="n">
+      <c r="B11" s="170"/>
+      <c r="E11" s="173" t="n">
         <f aca="false">+Utilidad!K63</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="176" t="n">
+      <c r="Q11" s="174" t="n">
         <f aca="false">+Utilidad!J71</f>
         <v>12796.955017</v>
       </c>
-      <c r="S11" s="173"/>
+      <c r="S11" s="171"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="172"/>
-      <c r="C12" s="174" t="n">
+      <c r="B12" s="170"/>
+      <c r="C12" s="172" t="n">
         <f aca="false">+Utilidad!J101</f>
         <v>0</v>
       </c>
-      <c r="E12" s="177" t="n">
+      <c r="E12" s="175" t="n">
         <f aca="false">+Utilidad!L63</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="178" t="n">
+      <c r="Q12" s="176" t="n">
         <f aca="false">+Utilidad!K71</f>
         <v>0.082951951265</v>
       </c>
-      <c r="S12" s="173"/>
+      <c r="S12" s="171"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="172"/>
-      <c r="C13" s="175" t="n">
+      <c r="B13" s="170"/>
+      <c r="C13" s="173" t="n">
         <f aca="false">+Utilidad!K101</f>
         <v>0</v>
       </c>
-      <c r="H13" s="180" t="n">
+      <c r="H13" s="178" t="n">
         <f aca="false">+Utilidad!J66</f>
         <v>0</v>
       </c>
-      <c r="N13" s="174" t="n">
+      <c r="N13" s="172" t="n">
         <f aca="false">+Utilidad!J72</f>
         <v>41025</v>
       </c>
-      <c r="Q13" s="179" t="n">
+      <c r="Q13" s="177" t="n">
         <f aca="false">+Utilidad!L71</f>
         <v>1061.53238891058</v>
       </c>
-      <c r="S13" s="173"/>
+      <c r="S13" s="171"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="172"/>
-      <c r="C14" s="177" t="n">
+      <c r="B14" s="170"/>
+      <c r="C14" s="175" t="n">
         <f aca="false">+Utilidad!L101</f>
         <v>0</v>
       </c>
-      <c r="H14" s="181" t="n">
+      <c r="H14" s="179" t="n">
         <f aca="false">+Utilidad!K66</f>
         <v>0</v>
       </c>
-      <c r="J14" s="182" t="n">
+      <c r="J14" s="180" t="n">
         <f aca="false">+I7+H13-L14-L7</f>
         <v>0</v>
       </c>
-      <c r="L14" s="176" t="n">
+      <c r="L14" s="174" t="n">
         <f aca="false">+Utilidad!J69</f>
         <v>0</v>
       </c>
-      <c r="N14" s="175" t="n">
+      <c r="N14" s="173" t="n">
         <f aca="false">+Utilidad!K72</f>
         <v>0.42098</v>
       </c>
-      <c r="S14" s="173"/>
+      <c r="S14" s="171"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="172"/>
-      <c r="G15" s="183" t="n">
+      <c r="B15" s="170"/>
+      <c r="G15" s="181" t="n">
         <f aca="false">Flujos!G6</f>
         <v>26963</v>
       </c>
-      <c r="H15" s="184" t="n">
+      <c r="H15" s="182" t="n">
         <f aca="false">+Utilidad!L66</f>
         <v>0</v>
       </c>
-      <c r="L15" s="178" t="n">
+      <c r="L15" s="176" t="n">
         <f aca="false">+Utilidad!K69</f>
         <v>0</v>
       </c>
-      <c r="N15" s="177" t="n">
+      <c r="N15" s="175" t="n">
         <f aca="false">+Utilidad!L72</f>
         <v>17270.7045</v>
       </c>
-      <c r="S15" s="173"/>
+      <c r="S15" s="171"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="172"/>
-      <c r="E16" s="185" t="n">
+      <c r="B16" s="170"/>
+      <c r="E16" s="183" t="n">
         <f aca="false">+C12-E10</f>
         <v>0</v>
       </c>
-      <c r="G16" s="186" t="n">
+      <c r="G16" s="184" t="n">
         <f aca="false">Flujos!H6</f>
         <v>0.1206</v>
       </c>
-      <c r="L16" s="179" t="n">
+      <c r="L16" s="177" t="n">
         <f aca="false">+Utilidad!L69</f>
         <v>0</v>
       </c>
       <c r="P16" s="126" t="s">
         <v>121</v>
       </c>
-      <c r="S16" s="173"/>
+      <c r="S16" s="171"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="172"/>
-      <c r="G17" s="187" t="n">
+      <c r="B17" s="170"/>
+      <c r="G17" s="185" t="n">
         <f aca="false">G15*G16</f>
         <v>3251.7378</v>
       </c>
-      <c r="P17" s="176" t="n">
+      <c r="P17" s="174" t="n">
         <f aca="false">Flujos!G70</f>
         <v>392</v>
       </c>
-      <c r="S17" s="173"/>
+      <c r="S17" s="171"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="172"/>
-      <c r="K18" s="174" t="n">
+      <c r="B18" s="170"/>
+      <c r="K18" s="172" t="n">
         <f aca="false">Flujos!C56</f>
         <v>41596</v>
       </c>
-      <c r="P18" s="178" t="n">
+      <c r="P18" s="176" t="n">
         <f aca="false">Flujos!H70</f>
         <v>0.5253</v>
       </c>
-      <c r="S18" s="173"/>
+      <c r="S18" s="171"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="172"/>
-      <c r="K19" s="175" t="n">
+      <c r="B19" s="170"/>
+      <c r="K19" s="173" t="n">
         <f aca="false">Flujos!D56</f>
         <v>0.4527</v>
       </c>
-      <c r="P19" s="179" t="n">
+      <c r="P19" s="177" t="n">
         <f aca="false">P17*P18</f>
         <v>205.9176</v>
       </c>
-      <c r="S19" s="173"/>
+      <c r="S19" s="171"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="172"/>
-      <c r="K20" s="177" t="n">
+      <c r="B20" s="170"/>
+      <c r="K20" s="175" t="n">
         <f aca="false">K18*K19</f>
         <v>18830.5092</v>
       </c>
-      <c r="L20" s="174" t="n">
+      <c r="L20" s="172" t="n">
         <f aca="false">+Utilidad!J76</f>
         <v>83697</v>
       </c>
-      <c r="N20" s="182" t="n">
+      <c r="N20" s="180" t="n">
         <f aca="false">+L14+N13+K18-M22-L20</f>
         <v>-1076</v>
       </c>
-      <c r="S20" s="173"/>
+      <c r="S20" s="171"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="172"/>
-      <c r="S21" s="173"/>
+      <c r="B21" s="170"/>
+      <c r="S21" s="171"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="172"/>
-      <c r="L22" s="175" t="n">
+      <c r="B22" s="170"/>
+      <c r="L22" s="173" t="n">
         <f aca="false">+Utilidad!K76</f>
         <v>0.43797188987</v>
       </c>
-      <c r="M22" s="174" t="n">
+      <c r="M22" s="172" t="n">
         <f aca="false">+Utilidad!J74</f>
         <v>0</v>
       </c>
-      <c r="O22" s="174" t="n">
+      <c r="O22" s="172" t="n">
         <f aca="false">+Utilidad!J73</f>
         <v>23460</v>
       </c>
-      <c r="S22" s="173"/>
+      <c r="S22" s="171"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="172"/>
-      <c r="L23" s="177" t="n">
+      <c r="B23" s="170"/>
+      <c r="L23" s="175" t="n">
         <f aca="false">+Utilidad!L76</f>
         <v>36656.9332664494</v>
       </c>
-      <c r="M23" s="175" t="n">
+      <c r="M23" s="173" t="n">
         <f aca="false">+Utilidad!K74</f>
         <v>0</v>
       </c>
-      <c r="O23" s="175" t="n">
+      <c r="O23" s="173" t="n">
         <f aca="false">+Utilidad!K73</f>
         <v>0.50587309641</v>
       </c>
-      <c r="S23" s="173"/>
+      <c r="S23" s="171"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="172"/>
-      <c r="M24" s="177" t="n">
+      <c r="B24" s="170"/>
+      <c r="M24" s="175" t="n">
         <f aca="false">+Utilidad!L74</f>
         <v>0</v>
       </c>
-      <c r="O24" s="177" t="n">
+      <c r="O24" s="175" t="n">
         <f aca="false">+Utilidad!L73</f>
         <v>11867.7828417786</v>
       </c>
@@ -20909,36 +20852,36 @@
         <f aca="false">+(O22+N13)/(L7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S24" s="173"/>
+      <c r="S24" s="171"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="172"/>
-      <c r="C25" s="188"/>
-      <c r="G25" s="174" t="n">
+      <c r="B25" s="170"/>
+      <c r="C25" s="186"/>
+      <c r="G25" s="172" t="n">
         <f aca="false">+Utilidad!J105</f>
         <v>0</v>
       </c>
-      <c r="S25" s="173"/>
+      <c r="S25" s="171"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="172"/>
-      <c r="C26" s="189" t="n">
+      <c r="B26" s="170"/>
+      <c r="C26" s="187" t="n">
         <f aca="false">+Utilidad!J103</f>
         <v>0</v>
       </c>
-      <c r="G26" s="175" t="n">
+      <c r="G26" s="173" t="n">
         <f aca="false">+Utilidad!K105</f>
         <v>0</v>
       </c>
-      <c r="S26" s="173"/>
+      <c r="S26" s="171"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="172"/>
-      <c r="C27" s="190" t="n">
+      <c r="B27" s="170"/>
+      <c r="C27" s="188" t="n">
         <f aca="false">+Utilidad!K103</f>
         <v>0</v>
       </c>
-      <c r="G27" s="177" t="n">
+      <c r="G27" s="175" t="n">
         <f aca="false">+Utilidad!L105</f>
         <v>0</v>
       </c>
@@ -20946,28 +20889,28 @@
         <f aca="false">+(K28)/(L20+M22+O22)</f>
         <v>0.628022434371996</v>
       </c>
-      <c r="S27" s="173"/>
+      <c r="S27" s="171"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="172"/>
-      <c r="C28" s="191" t="n">
+      <c r="B28" s="170"/>
+      <c r="C28" s="189" t="n">
         <f aca="false">+Utilidad!L103</f>
         <v>0</v>
       </c>
-      <c r="K28" s="183" t="n">
+      <c r="K28" s="181" t="n">
         <f aca="false">+Utilidad!J78</f>
         <v>67297</v>
       </c>
-      <c r="S28" s="173"/>
+      <c r="S28" s="171"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="172"/>
-      <c r="C29" s="188"/>
-      <c r="F29" s="192" t="n">
+      <c r="B29" s="170"/>
+      <c r="C29" s="186"/>
+      <c r="F29" s="190" t="n">
         <f aca="false">+C26-G25</f>
         <v>0</v>
       </c>
-      <c r="K29" s="186" t="n">
+      <c r="K29" s="184" t="n">
         <f aca="false">+Utilidad!K78</f>
         <v>0.665071</v>
       </c>
@@ -20975,1273 +20918,1264 @@
         <f aca="false">K28/(L20+M22+O22)</f>
         <v>0.628022434371996</v>
       </c>
-      <c r="O29" s="193" t="n">
+      <c r="O29" s="191" t="n">
         <f aca="false">O22+L20+M22</f>
         <v>107157</v>
       </c>
-      <c r="S29" s="173"/>
+      <c r="S29" s="171"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="172"/>
-      <c r="C30" s="188"/>
-      <c r="I30" s="183" t="n">
+      <c r="B30" s="170"/>
+      <c r="C30" s="186"/>
+      <c r="I30" s="181" t="n">
         <f aca="false">+Utilidad!J77</f>
         <v>39860</v>
       </c>
-      <c r="K30" s="187" t="n">
+      <c r="K30" s="185" t="n">
         <f aca="false">+Utilidad!L78</f>
         <v>44757.283087</v>
       </c>
-      <c r="O30" s="193" t="n">
+      <c r="O30" s="191" t="n">
         <f aca="false">O29-K28</f>
         <v>39860</v>
       </c>
-      <c r="S30" s="173"/>
+      <c r="S30" s="171"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="172"/>
-      <c r="C31" s="188"/>
-      <c r="I31" s="186" t="n">
+      <c r="B31" s="170"/>
+      <c r="C31" s="186"/>
+      <c r="I31" s="184" t="n">
         <f aca="false">+Utilidad!K77</f>
         <v>0.094516633742</v>
       </c>
-      <c r="S31" s="173"/>
+      <c r="S31" s="171"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="172"/>
-      <c r="C32" s="188"/>
-      <c r="I32" s="187" t="n">
+      <c r="B32" s="170"/>
+      <c r="C32" s="186"/>
+      <c r="I32" s="185" t="n">
         <f aca="false">I30*I31</f>
         <v>3767.43302095612</v>
       </c>
-      <c r="S32" s="173"/>
+      <c r="S32" s="171"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="172"/>
-      <c r="C33" s="188"/>
-      <c r="S33" s="173"/>
+      <c r="B33" s="170"/>
+      <c r="C33" s="186"/>
+      <c r="S33" s="171"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="172"/>
-      <c r="C34" s="188"/>
-      <c r="G34" s="174" t="n">
+      <c r="B34" s="170"/>
+      <c r="C34" s="186"/>
+      <c r="G34" s="172" t="n">
         <f aca="false">+Utilidad!J108</f>
         <v>0</v>
       </c>
-      <c r="L34" s="182"/>
-      <c r="S34" s="173"/>
+      <c r="L34" s="180"/>
+      <c r="S34" s="171"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="172"/>
-      <c r="C35" s="189" t="n">
+      <c r="B35" s="170"/>
+      <c r="C35" s="187" t="n">
         <f aca="false">+Utilidad!J106</f>
         <v>0</v>
       </c>
-      <c r="G35" s="175" t="n">
+      <c r="G35" s="173" t="n">
         <f aca="false">+Utilidad!K108</f>
         <v>0</v>
       </c>
-      <c r="M35" s="193"/>
-      <c r="N35" s="193"/>
-      <c r="S35" s="173"/>
+      <c r="M35" s="191"/>
+      <c r="N35" s="191"/>
+      <c r="S35" s="171"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="172"/>
-      <c r="C36" s="190" t="n">
+      <c r="B36" s="170"/>
+      <c r="C36" s="188" t="n">
         <f aca="false">+Utilidad!K106</f>
         <v>0</v>
       </c>
-      <c r="G36" s="177" t="n">
+      <c r="G36" s="175" t="n">
         <f aca="false">+Utilidad!L108</f>
         <v>0</v>
       </c>
-      <c r="S36" s="173"/>
+      <c r="S36" s="171"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="172"/>
-      <c r="C37" s="191" t="n">
+      <c r="B37" s="170"/>
+      <c r="C37" s="189" t="n">
         <f aca="false">+Utilidad!L106</f>
         <v>0</v>
       </c>
-      <c r="S37" s="173"/>
+      <c r="S37" s="171"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="172"/>
-      <c r="C38" s="188"/>
-      <c r="F38" s="192" t="n">
+      <c r="B38" s="170"/>
+      <c r="C38" s="186"/>
+      <c r="F38" s="190" t="n">
         <f aca="false">+C35-G34</f>
         <v>0</v>
       </c>
-      <c r="S38" s="173"/>
+      <c r="S38" s="171"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="172"/>
-      <c r="C39" s="188"/>
-      <c r="K39" s="194" t="n">
+      <c r="B39" s="170"/>
+      <c r="C39" s="186"/>
+      <c r="K39" s="192" t="n">
         <f aca="false">K28-(I53+L53)</f>
         <v>-5361</v>
       </c>
-      <c r="N39" s="193"/>
-      <c r="S39" s="173"/>
+      <c r="N39" s="191"/>
+      <c r="S39" s="171"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="172"/>
-      <c r="C40" s="188"/>
-      <c r="S40" s="173"/>
+      <c r="B40" s="170"/>
+      <c r="C40" s="186"/>
+      <c r="S40" s="171"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="172"/>
-      <c r="C41" s="188"/>
-      <c r="S41" s="173"/>
+      <c r="B41" s="170"/>
+      <c r="C41" s="186"/>
+      <c r="S41" s="171"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="172"/>
-      <c r="C42" s="188"/>
-      <c r="S42" s="173"/>
+      <c r="B42" s="170"/>
+      <c r="C42" s="186"/>
+      <c r="S42" s="171"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="172"/>
-      <c r="C43" s="188"/>
-      <c r="S43" s="173"/>
+      <c r="B43" s="170"/>
+      <c r="C43" s="186"/>
+      <c r="S43" s="171"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="172"/>
-      <c r="C44" s="189" t="n">
+      <c r="B44" s="170"/>
+      <c r="C44" s="187" t="n">
         <f aca="false">+Utilidad!J109</f>
         <v>0</v>
       </c>
-      <c r="G44" s="174" t="n">
+      <c r="G44" s="172" t="n">
         <f aca="false">+Utilidad!J111</f>
         <v>0</v>
       </c>
-      <c r="S44" s="173"/>
+      <c r="S44" s="171"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="172"/>
-      <c r="C45" s="190" t="n">
+      <c r="B45" s="170"/>
+      <c r="C45" s="188" t="n">
         <f aca="false">+Utilidad!K109</f>
         <v>0</v>
       </c>
-      <c r="G45" s="175" t="n">
+      <c r="G45" s="173" t="n">
         <f aca="false">+Utilidad!K111</f>
         <v>0</v>
       </c>
-      <c r="S45" s="173"/>
+      <c r="S45" s="171"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="172"/>
-      <c r="C46" s="191" t="n">
+      <c r="B46" s="170"/>
+      <c r="C46" s="189" t="n">
         <f aca="false">+Utilidad!L109</f>
         <v>0</v>
       </c>
-      <c r="G46" s="177" t="n">
+      <c r="G46" s="175" t="n">
         <f aca="false">+Utilidad!L111</f>
         <v>0</v>
       </c>
-      <c r="S46" s="173"/>
+      <c r="S46" s="171"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="172"/>
-      <c r="C47" s="188"/>
-      <c r="S47" s="173"/>
+      <c r="B47" s="170"/>
+      <c r="C47" s="186"/>
+      <c r="S47" s="171"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="172"/>
-      <c r="C48" s="188"/>
-      <c r="F48" s="192" t="n">
+      <c r="B48" s="170"/>
+      <c r="C48" s="186"/>
+      <c r="F48" s="190" t="n">
         <f aca="false">+C44-G44</f>
         <v>0</v>
       </c>
-      <c r="S48" s="173"/>
+      <c r="S48" s="171"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="172"/>
-      <c r="C49" s="188"/>
-      <c r="S49" s="173"/>
+      <c r="B49" s="170"/>
+      <c r="C49" s="186"/>
+      <c r="S49" s="171"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="172"/>
-      <c r="C50" s="188"/>
-      <c r="S50" s="173"/>
+      <c r="B50" s="170"/>
+      <c r="C50" s="186"/>
+      <c r="S50" s="171"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="172"/>
-      <c r="C51" s="188"/>
-      <c r="S51" s="173"/>
+      <c r="B51" s="170"/>
+      <c r="C51" s="186"/>
+      <c r="S51" s="171"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="172"/>
-      <c r="C52" s="188"/>
-      <c r="S52" s="173"/>
+      <c r="B52" s="170"/>
+      <c r="C52" s="186"/>
+      <c r="S52" s="171"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="172"/>
-      <c r="C53" s="188"/>
-      <c r="I53" s="180" t="n">
+      <c r="B53" s="170"/>
+      <c r="C53" s="186"/>
+      <c r="I53" s="178" t="n">
         <f aca="false">+Utilidad!J82</f>
         <v>1453</v>
       </c>
-      <c r="L53" s="180" t="n">
+      <c r="L53" s="178" t="n">
         <f aca="false">+Utilidad!J83</f>
         <v>71205</v>
       </c>
-      <c r="S53" s="173"/>
+      <c r="S53" s="171"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="172"/>
-      <c r="C54" s="189" t="n">
+      <c r="B54" s="170"/>
+      <c r="C54" s="187" t="n">
         <f aca="false">+Utilidad!J112</f>
         <v>0</v>
       </c>
-      <c r="I54" s="181" t="n">
+      <c r="I54" s="179" t="n">
         <f aca="false">+Utilidad!K82</f>
         <v>0.64646643925</v>
       </c>
-      <c r="L54" s="181" t="n">
+      <c r="L54" s="179" t="n">
         <f aca="false">+Utilidad!K83</f>
         <v>0.6636863737</v>
       </c>
-      <c r="S54" s="173"/>
+      <c r="S54" s="171"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="172"/>
-      <c r="C55" s="190" t="n">
+      <c r="B55" s="170"/>
+      <c r="C55" s="188" t="n">
         <f aca="false">+Utilidad!K112</f>
         <v>0</v>
       </c>
-      <c r="I55" s="184" t="n">
+      <c r="I55" s="182" t="n">
         <f aca="false">+Utilidad!L82</f>
         <v>939.31573623025</v>
       </c>
-      <c r="L55" s="184" t="n">
+      <c r="L55" s="182" t="n">
         <f aca="false">+Utilidad!L83</f>
         <v>47257.7882393085</v>
       </c>
-      <c r="S55" s="173"/>
+      <c r="S55" s="171"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="172"/>
-      <c r="C56" s="191" t="n">
+      <c r="B56" s="170"/>
+      <c r="C56" s="189" t="n">
         <f aca="false">+Utilidad!L112</f>
         <v>0</v>
       </c>
-      <c r="S56" s="173"/>
+      <c r="S56" s="171"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="172"/>
-      <c r="S57" s="173"/>
+      <c r="B57" s="170"/>
+      <c r="S57" s="171"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="172"/>
-      <c r="M58" s="176" t="n">
+      <c r="B58" s="170"/>
+      <c r="M58" s="174" t="n">
         <f aca="false">Flujos!G24</f>
         <v>1453</v>
       </c>
-      <c r="N58" s="195" t="n">
+      <c r="N58" s="193" t="n">
         <f aca="false">+M58/(L53+I53)</f>
         <v>0.0199977979025021</v>
       </c>
-      <c r="S58" s="173"/>
+      <c r="S58" s="171"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="172"/>
-      <c r="M59" s="178" t="n">
+      <c r="B59" s="170"/>
+      <c r="M59" s="176" t="n">
         <f aca="false">Flujos!H24</f>
         <v>0.64646643925</v>
       </c>
-      <c r="S59" s="173"/>
+      <c r="S59" s="171"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="172"/>
-      <c r="M60" s="179" t="n">
+      <c r="B60" s="170"/>
+      <c r="M60" s="177" t="n">
         <f aca="false">M59*M58</f>
         <v>939.31573623025</v>
       </c>
-      <c r="S60" s="173"/>
+      <c r="S60" s="171"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="172"/>
-      <c r="S61" s="173"/>
+      <c r="B61" s="170"/>
+      <c r="S61" s="171"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="172"/>
-      <c r="C62" s="174" t="n">
+      <c r="B62" s="170"/>
+      <c r="C62" s="172" t="n">
         <f aca="false">Flujos!C55</f>
         <v>41596</v>
       </c>
-      <c r="S62" s="173"/>
+      <c r="S62" s="171"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="172"/>
-      <c r="C63" s="175" t="n">
+      <c r="B63" s="170"/>
+      <c r="C63" s="173" t="n">
         <f aca="false">Flujos!D55</f>
         <v>0.4527</v>
       </c>
-      <c r="O63" s="180" t="n">
+      <c r="O63" s="178" t="n">
         <f aca="false">Flujos!G27</f>
         <v>4772</v>
       </c>
-      <c r="S63" s="173"/>
+      <c r="S63" s="171"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="172"/>
-      <c r="C64" s="177" t="n">
+      <c r="B64" s="170"/>
+      <c r="C64" s="175" t="n">
         <f aca="false">C63*C62</f>
         <v>18830.5092</v>
       </c>
-      <c r="O64" s="181" t="n">
+      <c r="O64" s="179" t="n">
         <f aca="false">Flujos!H27</f>
         <v>0.6482</v>
       </c>
-      <c r="S64" s="173"/>
+      <c r="S64" s="171"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="172"/>
-      <c r="F65" s="180" t="n">
+      <c r="B65" s="170"/>
+      <c r="F65" s="178" t="n">
         <f aca="false">I112</f>
         <v>0</v>
       </c>
       <c r="G65" s="126" t="s">
-        <v>157</v>
-      </c>
-      <c r="L65" s="176" t="n">
+        <v>155</v>
+      </c>
+      <c r="L65" s="174" t="n">
         <f aca="false">Flujos!G25</f>
         <v>71205</v>
       </c>
-      <c r="O65" s="184" t="n">
+      <c r="O65" s="182" t="n">
         <f aca="false">O63*O64</f>
         <v>3093.2104</v>
       </c>
-      <c r="S65" s="173"/>
+      <c r="S65" s="171"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="172"/>
-      <c r="F66" s="180" t="n">
+      <c r="B66" s="170"/>
+      <c r="F66" s="178" t="n">
         <f aca="false">I113</f>
         <v>2106</v>
       </c>
       <c r="G66" s="126" t="s">
-        <v>158</v>
-      </c>
-      <c r="L66" s="178" t="n">
+        <v>156</v>
+      </c>
+      <c r="L66" s="176" t="n">
         <f aca="false">Flujos!H25</f>
         <v>0.6636863737</v>
       </c>
-      <c r="S66" s="173"/>
+      <c r="S66" s="171"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="172"/>
-      <c r="F67" s="180" t="n">
+      <c r="B67" s="170"/>
+      <c r="F67" s="178" t="n">
         <f aca="false">I114</f>
         <v>0</v>
       </c>
       <c r="G67" s="126" t="s">
-        <v>159</v>
-      </c>
-      <c r="L67" s="179" t="n">
+        <v>157</v>
+      </c>
+      <c r="L67" s="177" t="n">
         <f aca="false">L66*L65</f>
         <v>47257.7882393085</v>
       </c>
-      <c r="N67" s="185" t="n">
+      <c r="N67" s="183" t="n">
         <f aca="false">Flujos!G26</f>
         <v>66433</v>
       </c>
-      <c r="O67" s="180" t="n">
+      <c r="O67" s="178" t="n">
         <f aca="false">Flujos!G28</f>
         <v>0</v>
       </c>
-      <c r="S67" s="173"/>
+      <c r="S67" s="171"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="172"/>
-      <c r="O68" s="181" t="n">
+      <c r="B68" s="170"/>
+      <c r="O68" s="179" t="n">
         <f aca="false">Flujos!H28</f>
         <v>0</v>
       </c>
-      <c r="S68" s="173"/>
+      <c r="S68" s="171"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="172"/>
-      <c r="O69" s="184" t="n">
+      <c r="B69" s="170"/>
+      <c r="O69" s="182" t="n">
         <f aca="false">O67*O68</f>
         <v>0</v>
       </c>
-      <c r="S69" s="173"/>
+      <c r="S69" s="171"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="172"/>
-      <c r="H70" s="180" t="n">
+      <c r="B70" s="170"/>
+      <c r="H70" s="178" t="n">
         <f aca="false">Flujos!G29</f>
         <v>0</v>
       </c>
-      <c r="K70" s="180" t="n">
+      <c r="K70" s="178" t="n">
         <f aca="false">Flujos!G22</f>
         <v>0</v>
       </c>
-      <c r="S70" s="173"/>
+      <c r="S70" s="171"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="172"/>
-      <c r="H71" s="181" t="n">
+      <c r="B71" s="170"/>
+      <c r="H71" s="179" t="n">
         <f aca="false">Flujos!H29</f>
         <v>0</v>
       </c>
-      <c r="K71" s="181" t="n">
+      <c r="K71" s="179" t="n">
         <f aca="false">Flujos!H22</f>
         <v>0</v>
       </c>
-      <c r="S71" s="173"/>
+      <c r="S71" s="171"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="172"/>
-      <c r="H72" s="184" t="n">
+      <c r="B72" s="170"/>
+      <c r="H72" s="182" t="n">
         <f aca="false">H70*H71</f>
         <v>0</v>
       </c>
-      <c r="K72" s="184" t="n">
+      <c r="K72" s="182" t="n">
         <f aca="false">K70*K71</f>
         <v>0</v>
       </c>
-      <c r="S72" s="173"/>
+      <c r="S72" s="171"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="172"/>
-      <c r="S73" s="173"/>
+      <c r="B73" s="170"/>
+      <c r="S73" s="171"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="172"/>
-      <c r="L74" s="180" t="n">
+      <c r="B74" s="170"/>
+      <c r="L74" s="178" t="n">
         <f aca="false">Flujos!G35</f>
         <v>0</v>
       </c>
-      <c r="O74" s="180" t="n">
+      <c r="O74" s="178" t="n">
         <f aca="false">Flujos!G33</f>
         <v>0</v>
       </c>
-      <c r="S74" s="173"/>
+      <c r="S74" s="171"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="172"/>
-      <c r="H75" s="180" t="n">
+      <c r="B75" s="170"/>
+      <c r="H75" s="178" t="n">
         <f aca="false">Flujos!G30</f>
         <v>0</v>
       </c>
-      <c r="J75" s="185" t="n">
+      <c r="J75" s="183" t="n">
         <f aca="false">Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="L75" s="181" t="n">
+      <c r="L75" s="179" t="n">
         <f aca="false">Flujos!H35</f>
         <v>0</v>
       </c>
-      <c r="N75" s="185" t="n">
+      <c r="N75" s="183" t="n">
         <f aca="false">Flujos!G34</f>
         <v>7132</v>
       </c>
-      <c r="O75" s="181" t="n">
+      <c r="O75" s="179" t="n">
         <f aca="false">Flujos!H33</f>
         <v>0</v>
       </c>
-      <c r="S75" s="173"/>
+      <c r="S75" s="171"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="172"/>
-      <c r="H76" s="181" t="n">
+      <c r="B76" s="170"/>
+      <c r="H76" s="179" t="n">
         <f aca="false">Flujos!H30</f>
         <v>0</v>
       </c>
-      <c r="L76" s="184" t="n">
+      <c r="L76" s="182" t="n">
         <f aca="false">L74*L75</f>
         <v>0</v>
       </c>
-      <c r="O76" s="184" t="n">
+      <c r="O76" s="182" t="n">
         <f aca="false">O74*O75</f>
         <v>0</v>
       </c>
-      <c r="S76" s="173"/>
+      <c r="S76" s="171"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="172"/>
-      <c r="H77" s="184" t="n">
+      <c r="B77" s="170"/>
+      <c r="H77" s="182" t="n">
         <f aca="false">H76*H75</f>
         <v>0</v>
       </c>
-      <c r="S77" s="173"/>
+      <c r="S77" s="171"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="172"/>
-      <c r="L78" s="180" t="n">
+      <c r="B78" s="170"/>
+      <c r="L78" s="178" t="n">
         <f aca="false">Flujos!G36</f>
         <v>0</v>
       </c>
-      <c r="S78" s="173"/>
+      <c r="S78" s="171"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="172"/>
-      <c r="L79" s="181" t="n">
+      <c r="B79" s="170"/>
+      <c r="L79" s="179" t="n">
         <f aca="false">Flujos!H36</f>
         <v>0</v>
       </c>
-      <c r="Q79" s="180" t="n">
+      <c r="Q79" s="178" t="n">
         <f aca="false">Flujos!G58</f>
         <v>0</v>
       </c>
-      <c r="S79" s="173"/>
+      <c r="S79" s="171"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="172"/>
-      <c r="L80" s="184" t="n">
+      <c r="B80" s="170"/>
+      <c r="L80" s="182" t="n">
         <f aca="false">L79*L78</f>
         <v>0</v>
       </c>
-      <c r="Q80" s="181" t="n">
+      <c r="Q80" s="179" t="n">
         <f aca="false">Flujos!H58</f>
         <v>0</v>
       </c>
-      <c r="S80" s="173"/>
+      <c r="S80" s="171"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="172"/>
-      <c r="Q81" s="184" t="n">
+      <c r="B81" s="170"/>
+      <c r="Q81" s="182" t="n">
         <f aca="false">Q79*Q80</f>
         <v>0</v>
       </c>
-      <c r="S81" s="173"/>
+      <c r="S81" s="171"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="172"/>
-      <c r="K82" s="180" t="n">
+      <c r="B82" s="170"/>
+      <c r="K82" s="178" t="n">
         <f aca="false">Flujos!G57</f>
         <v>5026</v>
       </c>
-      <c r="S82" s="173"/>
+      <c r="S82" s="171"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="172"/>
-      <c r="K83" s="181" t="n">
+      <c r="B83" s="170"/>
+      <c r="K83" s="179" t="n">
         <f aca="false">Flujos!H57</f>
         <v>0.6371</v>
       </c>
-      <c r="S83" s="173"/>
+      <c r="S83" s="171"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="172"/>
-      <c r="K84" s="184" t="n">
+      <c r="B84" s="170"/>
+      <c r="K84" s="182" t="n">
         <f aca="false">K82*K83</f>
         <v>3202.0646</v>
       </c>
-      <c r="O84" s="180" t="n">
+      <c r="O84" s="178" t="n">
         <f aca="false">Flujos!G40</f>
         <v>1632</v>
       </c>
-      <c r="S84" s="173"/>
+      <c r="S84" s="171"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="172"/>
-      <c r="H85" s="193" t="n">
+      <c r="B85" s="170"/>
+      <c r="H85" s="191" t="n">
         <f aca="false">5562+L74</f>
         <v>5562</v>
       </c>
-      <c r="O85" s="181" t="n">
+      <c r="O85" s="179" t="n">
         <f aca="false">Flujos!H40</f>
         <v>0.5831</v>
       </c>
-      <c r="S85" s="173"/>
+      <c r="S85" s="171"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="172"/>
-      <c r="K86" s="180" t="n">
+      <c r="B86" s="170"/>
+      <c r="K86" s="178" t="n">
         <f aca="false">+Utilidad!J98</f>
         <v>1632</v>
       </c>
-      <c r="O86" s="184" t="n">
+      <c r="O86" s="182" t="n">
         <f aca="false">O84*O85</f>
         <v>951.6192</v>
       </c>
-      <c r="S86" s="173"/>
+      <c r="S86" s="171"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="172"/>
-      <c r="K87" s="181" t="n">
+      <c r="B87" s="170"/>
+      <c r="K87" s="179" t="n">
         <f aca="false">+Utilidad!K98</f>
         <v>0.5831</v>
       </c>
       <c r="Q87" s="126" t="s">
         <v>149</v>
       </c>
-      <c r="S87" s="173"/>
+      <c r="S87" s="171"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="172"/>
-      <c r="K88" s="184" t="n">
+      <c r="B88" s="170"/>
+      <c r="K88" s="182" t="n">
         <f aca="false">+Utilidad!L98</f>
         <v>951.6192</v>
       </c>
-      <c r="N88" s="196" t="n">
+      <c r="N88" s="194" t="n">
         <f aca="false">+L90+K86-O84</f>
         <v>-1632</v>
       </c>
-      <c r="S88" s="173"/>
+      <c r="S88" s="171"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="172"/>
-      <c r="S89" s="173"/>
+      <c r="B89" s="170"/>
+      <c r="S89" s="171"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="172"/>
-      <c r="L90" s="180" t="n">
+      <c r="B90" s="170"/>
+      <c r="L90" s="178" t="n">
         <f aca="false">+Utilidad!J97</f>
         <v>-1632</v>
       </c>
       <c r="R90" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="S90" s="173"/>
+      <c r="S90" s="171"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="172"/>
-      <c r="L91" s="181" t="n">
+      <c r="B91" s="170"/>
+      <c r="L91" s="179" t="n">
         <f aca="false">+Utilidad!K97</f>
         <v>0.5831</v>
       </c>
-      <c r="S91" s="173"/>
+      <c r="S91" s="171"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="172"/>
-      <c r="L92" s="184" t="n">
+      <c r="B92" s="170"/>
+      <c r="L92" s="182" t="n">
         <f aca="false">+Utilidad!L97</f>
         <v>-951.6192</v>
       </c>
-      <c r="S92" s="173"/>
+      <c r="S92" s="171"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="172"/>
+      <c r="B93" s="170"/>
       <c r="P93" s="126" t="s">
         <v>151</v>
       </c>
-      <c r="S93" s="173"/>
+      <c r="S93" s="171"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="197"/>
-      <c r="C94" s="198"/>
-      <c r="D94" s="198"/>
-      <c r="E94" s="198"/>
-      <c r="F94" s="198"/>
-      <c r="G94" s="198"/>
-      <c r="H94" s="198"/>
-      <c r="I94" s="198"/>
-      <c r="J94" s="198"/>
-      <c r="K94" s="198"/>
-      <c r="L94" s="198"/>
-      <c r="M94" s="198"/>
-      <c r="N94" s="198"/>
-      <c r="O94" s="198"/>
-      <c r="P94" s="199"/>
-      <c r="Q94" s="198"/>
-      <c r="R94" s="198"/>
-      <c r="S94" s="199"/>
+      <c r="B94" s="195"/>
+      <c r="C94" s="196"/>
+      <c r="D94" s="196"/>
+      <c r="E94" s="196"/>
+      <c r="F94" s="196"/>
+      <c r="G94" s="196"/>
+      <c r="H94" s="196"/>
+      <c r="I94" s="196"/>
+      <c r="J94" s="196"/>
+      <c r="K94" s="196"/>
+      <c r="L94" s="196"/>
+      <c r="M94" s="196"/>
+      <c r="N94" s="196"/>
+      <c r="O94" s="196"/>
+      <c r="P94" s="197"/>
+      <c r="Q94" s="196"/>
+      <c r="R94" s="196"/>
+      <c r="S94" s="197"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G95" s="200" t="s">
+      <c r="G95" s="198" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G96" s="199" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="199"/>
+      <c r="I96" s="199"/>
+      <c r="J96" s="200" t="s">
+        <v>159</v>
+      </c>
+      <c r="K96" s="200"/>
+      <c r="L96" s="200"/>
+      <c r="M96" s="201" t="s">
+        <v>47</v>
+      </c>
+      <c r="N96" s="201"/>
+      <c r="O96" s="201"/>
+      <c r="P96" s="201"/>
+    </row>
+    <row r="97" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G97" s="202" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G96" s="201" t="s">
-        <v>10</v>
-      </c>
-      <c r="H96" s="201"/>
-      <c r="I96" s="201"/>
-      <c r="J96" s="202" t="s">
-        <v>161</v>
-      </c>
-      <c r="K96" s="202"/>
-      <c r="L96" s="202"/>
-      <c r="M96" s="203" t="s">
-        <v>47</v>
-      </c>
-      <c r="N96" s="203"/>
-      <c r="O96" s="203"/>
-      <c r="P96" s="203"/>
-    </row>
-    <row r="97" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G97" s="204" t="s">
-        <v>162</v>
-      </c>
-      <c r="H97" s="204"/>
-      <c r="I97" s="205" t="n">
+      <c r="H97" s="202"/>
+      <c r="I97" s="203" t="n">
         <f aca="false">+E6</f>
         <v>122150</v>
       </c>
-      <c r="J97" s="206" t="s">
+      <c r="J97" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="K97" s="206"/>
-      <c r="L97" s="207" t="n">
+      <c r="K97" s="204"/>
+      <c r="L97" s="205" t="n">
         <f aca="false">Flujos!G9</f>
         <v>0</v>
       </c>
-      <c r="M97" s="208" t="s">
-        <v>163</v>
-      </c>
-      <c r="N97" s="208"/>
-      <c r="O97" s="208"/>
-      <c r="P97" s="207" t="n">
+      <c r="M97" s="206" t="s">
+        <v>161</v>
+      </c>
+      <c r="N97" s="206"/>
+      <c r="O97" s="206"/>
+      <c r="P97" s="205" t="n">
         <f aca="false">+G15</f>
         <v>26963</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G98" s="204" t="s">
-        <v>164</v>
-      </c>
-      <c r="H98" s="204"/>
-      <c r="I98" s="205" t="n">
+      <c r="G98" s="202" t="s">
+        <v>162</v>
+      </c>
+      <c r="H98" s="202"/>
+      <c r="I98" s="203" t="n">
         <f aca="false">+C12</f>
         <v>0</v>
       </c>
-      <c r="J98" s="208" t="s">
+      <c r="J98" s="206" t="s">
         <v>46</v>
       </c>
-      <c r="K98" s="208"/>
-      <c r="L98" s="207" t="n">
+      <c r="K98" s="206"/>
+      <c r="L98" s="205" t="n">
         <f aca="false">Flujos!G17</f>
         <v>-243</v>
       </c>
-      <c r="M98" s="208" t="s">
+      <c r="M98" s="206" t="s">
         <v>142</v>
       </c>
-      <c r="N98" s="208"/>
-      <c r="O98" s="208"/>
-      <c r="P98" s="207" t="n">
+      <c r="N98" s="206"/>
+      <c r="O98" s="206"/>
+      <c r="P98" s="205" t="n">
         <f aca="false">+Q7</f>
         <v>21435.044983</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G99" s="204" t="s">
-        <v>165</v>
-      </c>
-      <c r="H99" s="204"/>
-      <c r="I99" s="205" t="n">
+      <c r="G99" s="202" t="s">
+        <v>163</v>
+      </c>
+      <c r="H99" s="202"/>
+      <c r="I99" s="203" t="n">
         <f aca="false">+H13</f>
         <v>0</v>
       </c>
-      <c r="J99" s="208" t="s">
-        <v>166</v>
-      </c>
-      <c r="K99" s="208"/>
-      <c r="L99" s="207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="208" t="s">
+      <c r="J99" s="206" t="s">
+        <v>164</v>
+      </c>
+      <c r="K99" s="206"/>
+      <c r="L99" s="205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="206" t="s">
         <v>56</v>
       </c>
-      <c r="N99" s="208"/>
-      <c r="O99" s="208"/>
-      <c r="P99" s="207" t="n">
+      <c r="N99" s="206"/>
+      <c r="O99" s="206"/>
+      <c r="P99" s="205" t="n">
         <f aca="false">+Q11</f>
         <v>12796.955017</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G100" s="209" t="s">
-        <v>167</v>
-      </c>
-      <c r="H100" s="209"/>
-      <c r="I100" s="205" t="n">
+      <c r="G100" s="207" t="s">
+        <v>165</v>
+      </c>
+      <c r="H100" s="207"/>
+      <c r="I100" s="203" t="n">
         <f aca="false">+C26</f>
         <v>0</v>
       </c>
-      <c r="J100" s="208" t="s">
-        <v>168</v>
-      </c>
-      <c r="K100" s="208"/>
-      <c r="L100" s="207" t="n">
+      <c r="J100" s="206" t="s">
+        <v>166</v>
+      </c>
+      <c r="K100" s="206"/>
+      <c r="L100" s="205" t="n">
         <f aca="false">Flujos!G21</f>
         <v>-5362</v>
       </c>
-      <c r="M100" s="208" t="s">
-        <v>169</v>
-      </c>
-      <c r="N100" s="208"/>
-      <c r="O100" s="208"/>
-      <c r="P100" s="207" t="n">
+      <c r="M100" s="206" t="s">
+        <v>167</v>
+      </c>
+      <c r="N100" s="206"/>
+      <c r="O100" s="206"/>
+      <c r="P100" s="205" t="n">
         <f aca="false">+I30</f>
         <v>39860</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G101" s="209" t="s">
+      <c r="G101" s="207" t="s">
         <v>91</v>
       </c>
-      <c r="H101" s="209"/>
-      <c r="I101" s="205" t="n">
+      <c r="H101" s="207"/>
+      <c r="I101" s="203" t="n">
         <f aca="false">+C35</f>
         <v>0</v>
       </c>
-      <c r="J101" s="208" t="s">
-        <v>170</v>
-      </c>
-      <c r="K101" s="208"/>
-      <c r="L101" s="207" t="n">
+      <c r="J101" s="206" t="s">
+        <v>168</v>
+      </c>
+      <c r="K101" s="206"/>
+      <c r="L101" s="205" t="n">
         <f aca="false">Flujos!G31</f>
         <v>0</v>
       </c>
-      <c r="M101" s="208" t="s">
-        <v>171</v>
-      </c>
-      <c r="N101" s="208"/>
-      <c r="O101" s="208"/>
-      <c r="P101" s="207" t="n">
+      <c r="M101" s="206" t="s">
+        <v>169</v>
+      </c>
+      <c r="N101" s="206"/>
+      <c r="O101" s="206"/>
+      <c r="P101" s="205" t="n">
         <f aca="false">+M58</f>
         <v>1453</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G102" s="209" t="s">
+      <c r="G102" s="207" t="s">
         <v>94</v>
       </c>
-      <c r="H102" s="209"/>
-      <c r="I102" s="205" t="n">
+      <c r="H102" s="207"/>
+      <c r="I102" s="203" t="n">
         <f aca="false">+C44</f>
         <v>0</v>
       </c>
-      <c r="J102" s="208" t="s">
-        <v>172</v>
-      </c>
-      <c r="K102" s="208"/>
-      <c r="L102" s="207" t="n">
+      <c r="J102" s="206" t="s">
+        <v>170</v>
+      </c>
+      <c r="K102" s="206"/>
+      <c r="L102" s="205" t="n">
         <f aca="false">Flujos!G44</f>
         <v>0</v>
       </c>
-      <c r="M102" s="208" t="s">
+      <c r="M102" s="206" t="s">
         <v>111</v>
       </c>
-      <c r="N102" s="208"/>
-      <c r="O102" s="208"/>
-      <c r="P102" s="207" t="n">
+      <c r="N102" s="206"/>
+      <c r="O102" s="206"/>
+      <c r="P102" s="205" t="n">
         <f aca="false">+O63</f>
         <v>4772</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G103" s="209" t="s">
+      <c r="G103" s="207" t="s">
+        <v>171</v>
+      </c>
+      <c r="H103" s="207"/>
+      <c r="I103" s="203" t="n">
+        <f aca="false">+C54</f>
+        <v>0</v>
+      </c>
+      <c r="J103" s="206" t="s">
+        <v>172</v>
+      </c>
+      <c r="K103" s="206"/>
+      <c r="L103" s="205" t="n">
+        <f aca="false">Flujos!G47</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="206" t="s">
         <v>173</v>
       </c>
-      <c r="H103" s="209"/>
-      <c r="I103" s="205" t="n">
-        <f aca="false">+C54</f>
-        <v>0</v>
-      </c>
-      <c r="J103" s="208" t="s">
+      <c r="N103" s="206"/>
+      <c r="O103" s="206"/>
+      <c r="P103" s="205" t="n">
+        <f aca="false">+O67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G104" s="207" t="s">
         <v>174</v>
       </c>
-      <c r="K103" s="208"/>
-      <c r="L103" s="207" t="n">
-        <f aca="false">Flujos!G47</f>
-        <v>0</v>
-      </c>
-      <c r="M103" s="208" t="s">
-        <v>175</v>
-      </c>
-      <c r="N103" s="208"/>
-      <c r="O103" s="208"/>
-      <c r="P103" s="207" t="n">
-        <f aca="false">+O67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G104" s="209" t="s">
-        <v>176</v>
-      </c>
-      <c r="H104" s="209"/>
-      <c r="I104" s="205" t="n">
+      <c r="H104" s="207"/>
+      <c r="I104" s="203" t="n">
         <f aca="false">+C62</f>
         <v>41596</v>
       </c>
-      <c r="J104" s="208" t="s">
+      <c r="J104" s="206" t="s">
+        <v>175</v>
+      </c>
+      <c r="K104" s="206"/>
+      <c r="L104" s="205" t="n">
+        <f aca="false">Flujos!G50</f>
+        <v>0</v>
+      </c>
+      <c r="M104" s="206" t="s">
+        <v>176</v>
+      </c>
+      <c r="N104" s="206"/>
+      <c r="O104" s="206"/>
+      <c r="P104" s="205" t="n">
+        <f aca="false">+O74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G105" s="207" t="s">
         <v>177</v>
       </c>
-      <c r="K104" s="208"/>
-      <c r="L104" s="207" t="n">
-        <f aca="false">Flujos!G50</f>
-        <v>0</v>
-      </c>
-      <c r="M104" s="208" t="s">
+      <c r="H105" s="207"/>
+      <c r="I105" s="203" t="n">
+        <f aca="false">+H70</f>
+        <v>0</v>
+      </c>
+      <c r="J105" s="206" t="s">
         <v>178</v>
       </c>
-      <c r="N104" s="208"/>
-      <c r="O104" s="208"/>
-      <c r="P104" s="207" t="n">
-        <f aca="false">+O74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G105" s="209" t="s">
-        <v>179</v>
-      </c>
-      <c r="H105" s="209"/>
-      <c r="I105" s="205" t="n">
-        <f aca="false">+H70</f>
-        <v>0</v>
-      </c>
-      <c r="J105" s="208" t="s">
-        <v>180</v>
-      </c>
-      <c r="K105" s="208"/>
-      <c r="L105" s="207" t="n">
+      <c r="K105" s="206"/>
+      <c r="L105" s="205" t="n">
         <f aca="false">Flujos!G53</f>
         <v>0</v>
       </c>
-      <c r="M105" s="208" t="s">
+      <c r="M105" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="N105" s="208"/>
-      <c r="O105" s="208"/>
-      <c r="P105" s="207" t="n">
+      <c r="N105" s="206"/>
+      <c r="O105" s="206"/>
+      <c r="P105" s="205" t="n">
         <f aca="false">+O84</f>
         <v>1632</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G106" s="209" t="s">
+      <c r="G106" s="207" t="s">
+        <v>179</v>
+      </c>
+      <c r="H106" s="207"/>
+      <c r="I106" s="203" t="n">
+        <f aca="false">+H75</f>
+        <v>0</v>
+      </c>
+      <c r="J106" s="206" t="s">
+        <v>180</v>
+      </c>
+      <c r="K106" s="206"/>
+      <c r="L106" s="205" t="n">
+        <f aca="false">Flujos!G42</f>
+        <v>0</v>
+      </c>
+      <c r="M106" s="206" t="s">
+        <v>145</v>
+      </c>
+      <c r="N106" s="206"/>
+      <c r="O106" s="206"/>
+      <c r="P106" s="205" t="n">
+        <f aca="false">Q79</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G107" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="H106" s="209"/>
-      <c r="I106" s="205" t="n">
-        <f aca="false">+H75</f>
-        <v>0</v>
-      </c>
-      <c r="J106" s="208" t="s">
+      <c r="H107" s="209"/>
+      <c r="I107" s="203" t="n">
+        <f aca="false">+L74</f>
+        <v>0</v>
+      </c>
+      <c r="J107" s="206" t="s">
         <v>182</v>
       </c>
-      <c r="K106" s="208"/>
-      <c r="L106" s="207" t="n">
-        <f aca="false">Flujos!G42</f>
-        <v>0</v>
-      </c>
-      <c r="M106" s="208" t="s">
-        <v>145</v>
-      </c>
-      <c r="N106" s="208"/>
-      <c r="O106" s="208"/>
-      <c r="P106" s="207" t="n">
-        <f aca="false">Q79</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G107" s="210" t="s">
-        <v>183</v>
-      </c>
-      <c r="H107" s="211"/>
-      <c r="I107" s="205" t="n">
-        <f aca="false">+L74</f>
-        <v>0</v>
-      </c>
-      <c r="J107" s="208" t="s">
-        <v>184</v>
-      </c>
-      <c r="K107" s="208"/>
-      <c r="L107" s="207" t="n">
+      <c r="K107" s="206"/>
+      <c r="L107" s="205" t="n">
         <f aca="false">Flujos!G26</f>
         <v>66433</v>
       </c>
-      <c r="M107" s="208" t="s">
+      <c r="M107" s="206" t="s">
+        <v>183</v>
+      </c>
+      <c r="N107" s="206"/>
+      <c r="O107" s="206"/>
+      <c r="P107" s="205"/>
+    </row>
+    <row r="108" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G108" s="208" t="s">
+        <v>184</v>
+      </c>
+      <c r="H108" s="209"/>
+      <c r="I108" s="203" t="n">
+        <f aca="false">+L78</f>
+        <v>0</v>
+      </c>
+      <c r="J108" s="206" t="s">
         <v>185</v>
       </c>
-      <c r="N107" s="208"/>
-      <c r="O107" s="208"/>
-      <c r="P107" s="207"/>
-    </row>
-    <row r="108" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G108" s="210" t="s">
-        <v>186</v>
-      </c>
-      <c r="H108" s="211"/>
-      <c r="I108" s="205" t="n">
-        <f aca="false">+L78</f>
-        <v>0</v>
-      </c>
-      <c r="J108" s="208" t="s">
-        <v>187</v>
-      </c>
-      <c r="K108" s="208"/>
-      <c r="L108" s="207" t="n">
+      <c r="K108" s="206"/>
+      <c r="L108" s="205" t="n">
         <f aca="false">Flujos!G34</f>
         <v>7132</v>
       </c>
-      <c r="M108" s="212"/>
-      <c r="N108" s="212"/>
-      <c r="O108" s="212"/>
-      <c r="P108" s="207"/>
+      <c r="M108" s="210"/>
+      <c r="N108" s="210"/>
+      <c r="O108" s="210"/>
+      <c r="P108" s="205"/>
     </row>
     <row r="109" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G109" s="210" t="s">
-        <v>188</v>
-      </c>
-      <c r="H109" s="211"/>
-      <c r="I109" s="205" t="n">
+      <c r="G109" s="208" t="s">
+        <v>186</v>
+      </c>
+      <c r="H109" s="209"/>
+      <c r="I109" s="203" t="n">
         <f aca="false">+K86</f>
         <v>1632</v>
       </c>
-      <c r="J109" s="208" t="s">
-        <v>189</v>
-      </c>
-      <c r="K109" s="208"/>
-      <c r="L109" s="207" t="n">
+      <c r="J109" s="206" t="s">
+        <v>187</v>
+      </c>
+      <c r="K109" s="206"/>
+      <c r="L109" s="205" t="n">
         <f aca="false">Flujos!G39</f>
         <v>-1632</v>
       </c>
-      <c r="M109" s="212"/>
-      <c r="N109" s="212"/>
-      <c r="O109" s="212"/>
-      <c r="P109" s="207"/>
+      <c r="M109" s="210"/>
+      <c r="N109" s="210"/>
+      <c r="O109" s="210"/>
+      <c r="P109" s="205"/>
     </row>
     <row r="110" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G110" s="209" t="s">
-        <v>190</v>
-      </c>
-      <c r="H110" s="209"/>
-      <c r="I110" s="205" t="n">
+      <c r="G110" s="207" t="s">
+        <v>188</v>
+      </c>
+      <c r="H110" s="207"/>
+      <c r="I110" s="203" t="n">
         <f aca="false">+L90</f>
         <v>-1632</v>
       </c>
-      <c r="J110" s="208" t="s">
-        <v>191</v>
-      </c>
-      <c r="K110" s="208"/>
-      <c r="L110" s="207" t="n">
+      <c r="J110" s="206" t="s">
+        <v>189</v>
+      </c>
+      <c r="K110" s="206"/>
+      <c r="L110" s="205" t="n">
         <f aca="false">Flujos!G69</f>
         <v>2055</v>
       </c>
-      <c r="M110" s="208"/>
-      <c r="N110" s="208"/>
-      <c r="O110" s="208"/>
-      <c r="P110" s="207"/>
+      <c r="M110" s="206"/>
+      <c r="N110" s="206"/>
+      <c r="O110" s="206"/>
+      <c r="P110" s="205"/>
     </row>
     <row r="111" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G111" s="209" t="s">
-        <v>192</v>
-      </c>
-      <c r="H111" s="209"/>
-      <c r="I111" s="205" t="n">
+      <c r="G111" s="207" t="s">
+        <v>190</v>
+      </c>
+      <c r="H111" s="207"/>
+      <c r="I111" s="203" t="n">
         <f aca="false">K82</f>
         <v>5026</v>
       </c>
-      <c r="J111" s="208"/>
-      <c r="K111" s="208"/>
-      <c r="L111" s="207"/>
-      <c r="M111" s="208"/>
-      <c r="N111" s="208"/>
-      <c r="O111" s="208"/>
-      <c r="P111" s="207"/>
+      <c r="J111" s="206"/>
+      <c r="K111" s="206"/>
+      <c r="L111" s="205"/>
+      <c r="M111" s="206"/>
+      <c r="N111" s="206"/>
+      <c r="O111" s="206"/>
+      <c r="P111" s="205"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G112" s="209" t="s">
-        <v>193</v>
-      </c>
-      <c r="H112" s="209" t="s">
+      <c r="G112" s="207" t="s">
+        <v>191</v>
+      </c>
+      <c r="H112" s="207" t="s">
         <v>146</v>
       </c>
-      <c r="I112" s="205" t="n">
+      <c r="I112" s="203" t="n">
         <f aca="false">Flujos!G59</f>
         <v>0</v>
       </c>
-      <c r="J112" s="208"/>
-      <c r="K112" s="208"/>
-      <c r="L112" s="207"/>
-      <c r="M112" s="208"/>
-      <c r="N112" s="208"/>
-      <c r="O112" s="208"/>
-      <c r="P112" s="207"/>
+      <c r="J112" s="206"/>
+      <c r="K112" s="206"/>
+      <c r="L112" s="205"/>
+      <c r="M112" s="206"/>
+      <c r="N112" s="206"/>
+      <c r="O112" s="206"/>
+      <c r="P112" s="205"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G113" s="209" t="s">
-        <v>194</v>
-      </c>
-      <c r="H113" s="209" t="s">
+      <c r="G113" s="207" t="s">
+        <v>192</v>
+      </c>
+      <c r="H113" s="207" t="s">
         <v>147</v>
       </c>
-      <c r="I113" s="205" t="n">
+      <c r="I113" s="203" t="n">
         <f aca="false">Flujos!G60</f>
         <v>2106</v>
       </c>
-      <c r="J113" s="208"/>
-      <c r="K113" s="208"/>
-      <c r="L113" s="207"/>
-      <c r="M113" s="208"/>
-      <c r="N113" s="208"/>
-      <c r="O113" s="208"/>
-      <c r="P113" s="207"/>
+      <c r="J113" s="206"/>
+      <c r="K113" s="206"/>
+      <c r="L113" s="205"/>
+      <c r="M113" s="206"/>
+      <c r="N113" s="206"/>
+      <c r="O113" s="206"/>
+      <c r="P113" s="205"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G114" s="209" t="s">
+      <c r="G114" s="207" t="s">
+        <v>193</v>
+      </c>
+      <c r="H114" s="207" t="s">
+        <v>148</v>
+      </c>
+      <c r="I114" s="203" t="n">
+        <f aca="false">Flujos!G61</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="206"/>
+      <c r="K114" s="206"/>
+      <c r="L114" s="205"/>
+      <c r="M114" s="206"/>
+      <c r="N114" s="206"/>
+      <c r="O114" s="206"/>
+      <c r="P114" s="205"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G115" s="207" t="s">
+        <v>194</v>
+      </c>
+      <c r="H115" s="207"/>
+      <c r="I115" s="203" t="n">
+        <f aca="false">Flujos!G62</f>
+        <v>0</v>
+      </c>
+      <c r="J115" s="206"/>
+      <c r="K115" s="206"/>
+      <c r="L115" s="205"/>
+      <c r="M115" s="206"/>
+      <c r="N115" s="206"/>
+      <c r="O115" s="206"/>
+      <c r="P115" s="205"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G116" s="207" t="s">
         <v>195</v>
       </c>
-      <c r="H114" s="209" t="s">
-        <v>148</v>
-      </c>
-      <c r="I114" s="205" t="n">
-        <f aca="false">Flujos!G61</f>
-        <v>0</v>
-      </c>
-      <c r="J114" s="208"/>
-      <c r="K114" s="208"/>
-      <c r="L114" s="207"/>
-      <c r="M114" s="208"/>
-      <c r="N114" s="208"/>
-      <c r="O114" s="208"/>
-      <c r="P114" s="207"/>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G115" s="209" t="s">
+      <c r="H116" s="207"/>
+      <c r="I116" s="203" t="n">
+        <f aca="false">Flujos!G66</f>
+        <v>0</v>
+      </c>
+      <c r="J116" s="206"/>
+      <c r="K116" s="206"/>
+      <c r="L116" s="205"/>
+      <c r="M116" s="206"/>
+      <c r="N116" s="206"/>
+      <c r="O116" s="206"/>
+      <c r="P116" s="205"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G117" s="211" t="s">
         <v>196</v>
       </c>
-      <c r="H115" s="209"/>
-      <c r="I115" s="205" t="n">
-        <f aca="false">Flujos!G62</f>
-        <v>0</v>
-      </c>
-      <c r="J115" s="208"/>
-      <c r="K115" s="208"/>
-      <c r="L115" s="207"/>
-      <c r="M115" s="208"/>
-      <c r="N115" s="208"/>
-      <c r="O115" s="208"/>
-      <c r="P115" s="207"/>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G116" s="209" t="s">
+      <c r="H117" s="209"/>
+      <c r="I117" s="203" t="n">
+        <f aca="false">Flujos!G67</f>
+        <v>0</v>
+      </c>
+      <c r="J117" s="212"/>
+      <c r="K117" s="212"/>
+      <c r="L117" s="205"/>
+      <c r="M117" s="206"/>
+      <c r="N117" s="206"/>
+      <c r="O117" s="206"/>
+      <c r="P117" s="205"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G118" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="H116" s="209"/>
-      <c r="I116" s="205" t="n">
-        <f aca="false">Flujos!G66</f>
-        <v>0</v>
-      </c>
-      <c r="J116" s="208"/>
-      <c r="K116" s="208"/>
-      <c r="L116" s="207"/>
-      <c r="M116" s="208"/>
-      <c r="N116" s="208"/>
-      <c r="O116" s="208"/>
-      <c r="P116" s="207"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G117" s="210" t="s">
-        <v>198</v>
-      </c>
-      <c r="H117" s="211"/>
-      <c r="I117" s="205" t="n">
-        <f aca="false">Flujos!G67</f>
-        <v>0</v>
-      </c>
-      <c r="J117" s="213"/>
-      <c r="K117" s="213"/>
-      <c r="L117" s="207"/>
-      <c r="M117" s="208"/>
-      <c r="N117" s="208"/>
-      <c r="O117" s="208"/>
-      <c r="P117" s="207"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G118" s="210" t="s">
-        <v>199</v>
-      </c>
-      <c r="H118" s="211"/>
-      <c r="I118" s="205" t="n">
+      <c r="H118" s="209"/>
+      <c r="I118" s="203" t="n">
         <f aca="false">Flujos!G70</f>
         <v>392</v>
       </c>
-      <c r="J118" s="213"/>
-      <c r="K118" s="213"/>
-      <c r="L118" s="207"/>
-      <c r="M118" s="208"/>
-      <c r="N118" s="208"/>
-      <c r="O118" s="208"/>
-      <c r="P118" s="207"/>
+      <c r="J118" s="212"/>
+      <c r="K118" s="212"/>
+      <c r="L118" s="205"/>
+      <c r="M118" s="206"/>
+      <c r="N118" s="206"/>
+      <c r="O118" s="206"/>
+      <c r="P118" s="205"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G119" s="210" t="s">
-        <v>200</v>
-      </c>
-      <c r="H119" s="211"/>
-      <c r="I119" s="205" t="n">
+      <c r="G119" s="208" t="s">
+        <v>198</v>
+      </c>
+      <c r="H119" s="209"/>
+      <c r="I119" s="203" t="n">
         <f aca="false">Flujos!G72</f>
         <v>0</v>
       </c>
-      <c r="J119" s="208"/>
-      <c r="K119" s="208"/>
-      <c r="L119" s="207"/>
-      <c r="M119" s="208"/>
-      <c r="N119" s="208"/>
-      <c r="O119" s="208"/>
-      <c r="P119" s="207"/>
-    </row>
-    <row r="120" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G120" s="0"/>
-      <c r="H120" s="0"/>
-      <c r="I120" s="0"/>
-      <c r="J120" s="0"/>
-      <c r="K120" s="0"/>
-      <c r="M120" s="0"/>
-      <c r="N120" s="0"/>
-      <c r="P120" s="0"/>
-    </row>
+      <c r="J119" s="206"/>
+      <c r="K119" s="206"/>
+      <c r="L119" s="205"/>
+      <c r="M119" s="206"/>
+      <c r="N119" s="206"/>
+      <c r="O119" s="206"/>
+      <c r="P119" s="205"/>
+    </row>
+    <row r="120" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="121" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G121" s="214" t="s">
-        <v>201</v>
-      </c>
-      <c r="H121" s="214"/>
-      <c r="I121" s="215" t="n">
+      <c r="G121" s="213" t="s">
+        <v>199</v>
+      </c>
+      <c r="H121" s="213"/>
+      <c r="I121" s="214" t="n">
         <f aca="false">+SUM(I97:I119)</f>
         <v>171270</v>
       </c>
-      <c r="J121" s="216" t="s">
-        <v>202</v>
-      </c>
-      <c r="K121" s="216"/>
-      <c r="L121" s="217" t="n">
+      <c r="J121" s="215" t="s">
+        <v>200</v>
+      </c>
+      <c r="K121" s="215"/>
+      <c r="L121" s="216" t="n">
         <f aca="false">+SUM(L97:L110)</f>
         <v>68383</v>
       </c>
-      <c r="M121" s="216" t="s">
-        <v>203</v>
-      </c>
-      <c r="N121" s="216"/>
-      <c r="O121" s="216"/>
-      <c r="P121" s="215" t="n">
+      <c r="M121" s="215" t="s">
+        <v>201</v>
+      </c>
+      <c r="N121" s="215"/>
+      <c r="O121" s="215"/>
+      <c r="P121" s="214" t="n">
         <f aca="false">+SUM(P97:P110)</f>
         <v>108912</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G122" s="218"/>
-      <c r="H122" s="218"/>
-      <c r="I122" s="218"/>
-      <c r="J122" s="218"/>
-      <c r="K122" s="218"/>
-      <c r="L122" s="218"/>
-      <c r="M122" s="218"/>
-      <c r="N122" s="218"/>
-      <c r="O122" s="218"/>
-      <c r="P122" s="218"/>
+      <c r="G122" s="217"/>
+      <c r="H122" s="217"/>
+      <c r="I122" s="217"/>
+      <c r="J122" s="217"/>
+      <c r="K122" s="217"/>
+      <c r="L122" s="217"/>
+      <c r="M122" s="217"/>
+      <c r="N122" s="217"/>
+      <c r="O122" s="217"/>
+      <c r="P122" s="217"/>
     </row>
     <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G123" s="218"/>
-      <c r="J123" s="218"/>
-      <c r="K123" s="218"/>
-      <c r="L123" s="219" t="s">
-        <v>204</v>
-      </c>
-      <c r="M123" s="220"/>
-      <c r="N123" s="221"/>
-      <c r="O123" s="220"/>
-      <c r="P123" s="222" t="n">
+      <c r="G123" s="217"/>
+      <c r="J123" s="217"/>
+      <c r="K123" s="217"/>
+      <c r="L123" s="218" t="s">
+        <v>202</v>
+      </c>
+      <c r="M123" s="219"/>
+      <c r="N123" s="220"/>
+      <c r="O123" s="219"/>
+      <c r="P123" s="221" t="n">
         <f aca="false">+I121-L121-P121</f>
         <v>-6025</v>
       </c>
@@ -22249,590 +22183,590 @@
     <row r="124" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="125" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="126" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G126" s="200" t="s">
-        <v>205</v>
+      <c r="G126" s="198" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G127" s="223" t="s">
+      <c r="G127" s="222" t="s">
         <v>10</v>
       </c>
-      <c r="H127" s="223"/>
-      <c r="I127" s="223"/>
-      <c r="J127" s="224" t="s">
-        <v>161</v>
-      </c>
-      <c r="K127" s="224"/>
-      <c r="L127" s="224"/>
-      <c r="M127" s="225" t="s">
+      <c r="H127" s="222"/>
+      <c r="I127" s="222"/>
+      <c r="J127" s="223" t="s">
+        <v>159</v>
+      </c>
+      <c r="K127" s="223"/>
+      <c r="L127" s="223"/>
+      <c r="M127" s="224" t="s">
         <v>47</v>
       </c>
-      <c r="N127" s="225"/>
-      <c r="O127" s="225"/>
-      <c r="P127" s="225"/>
+      <c r="N127" s="224"/>
+      <c r="O127" s="224"/>
+      <c r="P127" s="224"/>
     </row>
     <row r="128" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G128" s="204" t="s">
-        <v>162</v>
-      </c>
-      <c r="H128" s="204"/>
-      <c r="I128" s="205" t="n">
+      <c r="G128" s="202" t="s">
+        <v>160</v>
+      </c>
+      <c r="H128" s="202"/>
+      <c r="I128" s="203" t="n">
         <f aca="false">+E8</f>
         <v>36032.9704799715</v>
       </c>
-      <c r="J128" s="206" t="s">
+      <c r="J128" s="204" t="s">
         <v>45</v>
       </c>
-      <c r="K128" s="206"/>
-      <c r="L128" s="207" t="n">
+      <c r="K128" s="204"/>
+      <c r="L128" s="205" t="n">
         <f aca="false">Flujos!G9*Flujos!H9</f>
         <v>0</v>
       </c>
-      <c r="M128" s="208" t="s">
-        <v>163</v>
-      </c>
-      <c r="N128" s="208"/>
-      <c r="O128" s="208"/>
-      <c r="P128" s="207" t="n">
+      <c r="M128" s="206" t="s">
+        <v>161</v>
+      </c>
+      <c r="N128" s="206"/>
+      <c r="O128" s="206"/>
+      <c r="P128" s="205" t="n">
         <f aca="false">+G17</f>
         <v>3251.7378</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G129" s="226" t="s">
-        <v>164</v>
-      </c>
-      <c r="H129" s="227"/>
-      <c r="I129" s="205" t="n">
+      <c r="G129" s="225" t="s">
+        <v>162</v>
+      </c>
+      <c r="H129" s="226"/>
+      <c r="I129" s="203" t="n">
         <f aca="false">+C14</f>
         <v>0</v>
       </c>
-      <c r="J129" s="208" t="s">
+      <c r="J129" s="206" t="s">
         <v>46</v>
       </c>
-      <c r="K129" s="208"/>
-      <c r="L129" s="207" t="n">
+      <c r="K129" s="206"/>
+      <c r="L129" s="205" t="n">
         <f aca="false">Flujos!G17*Flujos!H17</f>
         <v>-107.69296620384</v>
       </c>
-      <c r="M129" s="208" t="s">
+      <c r="M129" s="206" t="s">
         <v>142</v>
       </c>
-      <c r="N129" s="208"/>
-      <c r="O129" s="208"/>
-      <c r="P129" s="207" t="n">
+      <c r="N129" s="206"/>
+      <c r="O129" s="206"/>
+      <c r="P129" s="205" t="n">
         <f aca="false">+Q9</f>
         <v>3424.17694844443</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G130" s="226" t="s">
-        <v>165</v>
-      </c>
-      <c r="H130" s="228"/>
-      <c r="I130" s="205" t="n">
+      <c r="G130" s="225" t="s">
+        <v>163</v>
+      </c>
+      <c r="H130" s="227"/>
+      <c r="I130" s="203" t="n">
         <f aca="false">+H15</f>
         <v>0</v>
       </c>
-      <c r="J130" s="208" t="s">
-        <v>166</v>
-      </c>
-      <c r="K130" s="208"/>
-      <c r="L130" s="207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="208" t="s">
+      <c r="J130" s="206" t="s">
+        <v>164</v>
+      </c>
+      <c r="K130" s="206"/>
+      <c r="L130" s="205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="206" t="s">
         <v>56</v>
       </c>
-      <c r="N130" s="208"/>
-      <c r="O130" s="208"/>
-      <c r="P130" s="207" t="n">
+      <c r="N130" s="206"/>
+      <c r="O130" s="206"/>
+      <c r="P130" s="205" t="n">
         <f aca="false">+Q13</f>
         <v>1061.53238891058</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G131" s="210" t="s">
-        <v>167</v>
-      </c>
-      <c r="H131" s="211"/>
-      <c r="I131" s="205" t="n">
+      <c r="G131" s="208" t="s">
+        <v>165</v>
+      </c>
+      <c r="H131" s="209"/>
+      <c r="I131" s="203" t="n">
         <f aca="false">+C28</f>
         <v>0</v>
       </c>
-      <c r="J131" s="208" t="s">
-        <v>168</v>
-      </c>
-      <c r="K131" s="208"/>
-      <c r="L131" s="207" t="n">
+      <c r="J131" s="206" t="s">
+        <v>166</v>
+      </c>
+      <c r="K131" s="206"/>
+      <c r="L131" s="205" t="n">
         <f aca="false">Flujos!G21*Flujos!H21</f>
         <v>-3439.82088845752</v>
       </c>
-      <c r="M131" s="208" t="s">
-        <v>169</v>
-      </c>
-      <c r="N131" s="208"/>
-      <c r="O131" s="208"/>
-      <c r="P131" s="207" t="n">
+      <c r="M131" s="206" t="s">
+        <v>167</v>
+      </c>
+      <c r="N131" s="206"/>
+      <c r="O131" s="206"/>
+      <c r="P131" s="205" t="n">
         <f aca="false">+I32</f>
         <v>3767.43302095612</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G132" s="210" t="s">
+      <c r="G132" s="208" t="s">
         <v>91</v>
       </c>
-      <c r="H132" s="211"/>
-      <c r="I132" s="205" t="n">
+      <c r="H132" s="209"/>
+      <c r="I132" s="203" t="n">
         <f aca="false">+C37</f>
         <v>0</v>
       </c>
-      <c r="J132" s="208" t="s">
-        <v>170</v>
-      </c>
-      <c r="K132" s="208"/>
-      <c r="L132" s="207" t="n">
+      <c r="J132" s="206" t="s">
+        <v>168</v>
+      </c>
+      <c r="K132" s="206"/>
+      <c r="L132" s="205" t="n">
         <f aca="false">Flujos!G31*Flujos!H31</f>
         <v>0</v>
       </c>
-      <c r="M132" s="208" t="s">
-        <v>171</v>
-      </c>
-      <c r="N132" s="208"/>
-      <c r="O132" s="208"/>
-      <c r="P132" s="207" t="n">
+      <c r="M132" s="206" t="s">
+        <v>169</v>
+      </c>
+      <c r="N132" s="206"/>
+      <c r="O132" s="206"/>
+      <c r="P132" s="205" t="n">
         <f aca="false">+M60</f>
         <v>939.31573623025</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G133" s="210" t="s">
+      <c r="G133" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="H133" s="211"/>
-      <c r="I133" s="205" t="n">
+      <c r="H133" s="209"/>
+      <c r="I133" s="203" t="n">
         <f aca="false">+C46</f>
         <v>0</v>
       </c>
-      <c r="J133" s="208" t="s">
-        <v>172</v>
-      </c>
-      <c r="K133" s="208"/>
-      <c r="L133" s="207" t="n">
+      <c r="J133" s="206" t="s">
+        <v>170</v>
+      </c>
+      <c r="K133" s="206"/>
+      <c r="L133" s="205" t="n">
         <f aca="false">Flujos!G44*Flujos!H44</f>
         <v>0</v>
       </c>
-      <c r="M133" s="208" t="s">
+      <c r="M133" s="206" t="s">
         <v>111</v>
       </c>
-      <c r="N133" s="208"/>
-      <c r="O133" s="208"/>
-      <c r="P133" s="207" t="n">
+      <c r="N133" s="206"/>
+      <c r="O133" s="206"/>
+      <c r="P133" s="205" t="n">
         <f aca="false">+O65</f>
         <v>3093.2104</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G134" s="210" t="s">
+      <c r="G134" s="208" t="s">
+        <v>171</v>
+      </c>
+      <c r="H134" s="209"/>
+      <c r="I134" s="203" t="n">
+        <f aca="false">+C56</f>
+        <v>0</v>
+      </c>
+      <c r="J134" s="206" t="s">
+        <v>172</v>
+      </c>
+      <c r="K134" s="206"/>
+      <c r="L134" s="205" t="n">
+        <f aca="false">Flujos!G47*Flujos!H47</f>
+        <v>0</v>
+      </c>
+      <c r="M134" s="206" t="s">
         <v>173</v>
       </c>
-      <c r="H134" s="211"/>
-      <c r="I134" s="205" t="n">
-        <f aca="false">+C56</f>
-        <v>0</v>
-      </c>
-      <c r="J134" s="208" t="s">
+      <c r="N134" s="206"/>
+      <c r="O134" s="206"/>
+      <c r="P134" s="205" t="n">
+        <f aca="false">+O69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G135" s="208" t="s">
         <v>174</v>
       </c>
-      <c r="K134" s="208"/>
-      <c r="L134" s="207" t="n">
-        <f aca="false">Flujos!G47*Flujos!H47</f>
-        <v>0</v>
-      </c>
-      <c r="M134" s="208" t="s">
-        <v>175</v>
-      </c>
-      <c r="N134" s="208"/>
-      <c r="O134" s="208"/>
-      <c r="P134" s="207" t="n">
-        <f aca="false">+O69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G135" s="210" t="s">
-        <v>176</v>
-      </c>
-      <c r="H135" s="211"/>
-      <c r="I135" s="205" t="n">
+      <c r="H135" s="209"/>
+      <c r="I135" s="203" t="n">
         <f aca="false">C64</f>
         <v>18830.5092</v>
       </c>
-      <c r="J135" s="208" t="s">
+      <c r="J135" s="206" t="s">
+        <v>175</v>
+      </c>
+      <c r="K135" s="206"/>
+      <c r="L135" s="205" t="n">
+        <f aca="false">Flujos!G50*Flujos!H50</f>
+        <v>0</v>
+      </c>
+      <c r="M135" s="206" t="s">
+        <v>176</v>
+      </c>
+      <c r="N135" s="206"/>
+      <c r="O135" s="206"/>
+      <c r="P135" s="205" t="n">
+        <f aca="false">+O76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G136" s="208" t="s">
         <v>177</v>
       </c>
-      <c r="K135" s="208"/>
-      <c r="L135" s="207" t="n">
-        <f aca="false">Flujos!G50*Flujos!H50</f>
-        <v>0</v>
-      </c>
-      <c r="M135" s="208" t="s">
+      <c r="H136" s="209"/>
+      <c r="I136" s="203" t="n">
+        <f aca="false">+H72</f>
+        <v>0</v>
+      </c>
+      <c r="J136" s="206" t="s">
         <v>178</v>
       </c>
-      <c r="N135" s="208"/>
-      <c r="O135" s="208"/>
-      <c r="P135" s="207" t="n">
-        <f aca="false">+O76</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G136" s="210" t="s">
-        <v>179</v>
-      </c>
-      <c r="H136" s="211"/>
-      <c r="I136" s="205" t="n">
-        <f aca="false">+H72</f>
-        <v>0</v>
-      </c>
-      <c r="J136" s="208" t="s">
-        <v>180</v>
-      </c>
-      <c r="K136" s="208"/>
-      <c r="L136" s="207" t="n">
+      <c r="K136" s="206"/>
+      <c r="L136" s="205" t="n">
         <f aca="false">Flujos!G53*Flujos!H53</f>
         <v>0</v>
       </c>
-      <c r="M136" s="208" t="s">
+      <c r="M136" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="N136" s="208"/>
-      <c r="O136" s="208"/>
-      <c r="P136" s="207" t="n">
+      <c r="N136" s="206"/>
+      <c r="O136" s="206"/>
+      <c r="P136" s="205" t="n">
         <f aca="false">+O86</f>
         <v>951.6192</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G137" s="210" t="s">
+      <c r="G137" s="208" t="s">
+        <v>179</v>
+      </c>
+      <c r="H137" s="209"/>
+      <c r="I137" s="203" t="n">
+        <f aca="false">+H77</f>
+        <v>0</v>
+      </c>
+      <c r="J137" s="206" t="s">
+        <v>180</v>
+      </c>
+      <c r="K137" s="206"/>
+      <c r="L137" s="205" t="n">
+        <f aca="false">Flujos!G42*Flujos!H42</f>
+        <v>0</v>
+      </c>
+      <c r="M137" s="206" t="s">
+        <v>145</v>
+      </c>
+      <c r="N137" s="206"/>
+      <c r="O137" s="206"/>
+      <c r="P137" s="205" t="n">
+        <f aca="false">Q81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G138" s="208" t="s">
         <v>181</v>
       </c>
-      <c r="H137" s="211"/>
-      <c r="I137" s="205" t="n">
-        <f aca="false">+H77</f>
-        <v>0</v>
-      </c>
-      <c r="J137" s="208" t="s">
+      <c r="H138" s="209"/>
+      <c r="I138" s="203" t="n">
+        <f aca="false">+L76</f>
+        <v>0</v>
+      </c>
+      <c r="J138" s="206" t="s">
         <v>182</v>
       </c>
-      <c r="K137" s="208"/>
-      <c r="L137" s="207" t="n">
-        <f aca="false">Flujos!G42*Flujos!H42</f>
-        <v>0</v>
-      </c>
-      <c r="M137" s="208" t="s">
-        <v>145</v>
-      </c>
-      <c r="N137" s="208"/>
-      <c r="O137" s="208"/>
-      <c r="P137" s="207" t="n">
-        <f aca="false">Q81</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G138" s="210" t="s">
-        <v>183</v>
-      </c>
-      <c r="H138" s="211"/>
-      <c r="I138" s="205" t="n">
-        <f aca="false">+L76</f>
-        <v>0</v>
-      </c>
-      <c r="J138" s="208" t="s">
-        <v>184</v>
-      </c>
-      <c r="K138" s="208"/>
-      <c r="L138" s="207" t="n">
+      <c r="K138" s="206"/>
+      <c r="L138" s="205" t="n">
         <f aca="false">Flujos!G26*Flujos!H26</f>
         <v>44164.5778393582</v>
       </c>
-      <c r="M138" s="208" t="s">
+      <c r="M138" s="206" t="s">
+        <v>183</v>
+      </c>
+      <c r="N138" s="206"/>
+      <c r="O138" s="206"/>
+      <c r="P138" s="205" t="n">
+        <f aca="false">Flujos!G68*Flujos!H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G139" s="208" t="s">
+        <v>184</v>
+      </c>
+      <c r="H139" s="209"/>
+      <c r="I139" s="203" t="n">
+        <f aca="false">+L80</f>
+        <v>0</v>
+      </c>
+      <c r="J139" s="206" t="s">
         <v>185</v>
       </c>
-      <c r="N138" s="208"/>
-      <c r="O138" s="208"/>
-      <c r="P138" s="207" t="n">
-        <f aca="false">Flujos!G68*Flujos!H68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G139" s="210" t="s">
-        <v>186</v>
-      </c>
-      <c r="H139" s="211"/>
-      <c r="I139" s="205" t="n">
-        <f aca="false">+L80</f>
-        <v>0</v>
-      </c>
-      <c r="J139" s="208" t="s">
-        <v>187</v>
-      </c>
-      <c r="K139" s="208"/>
-      <c r="L139" s="207" t="n">
+      <c r="K139" s="206"/>
+      <c r="L139" s="205" t="n">
         <f aca="false">Flujos!G34*Flujos!H34</f>
         <v>4533.2671999656</v>
       </c>
-      <c r="M139" s="212"/>
-      <c r="N139" s="212"/>
-      <c r="O139" s="212"/>
-      <c r="P139" s="207"/>
+      <c r="M139" s="210"/>
+      <c r="N139" s="210"/>
+      <c r="O139" s="210"/>
+      <c r="P139" s="205"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G140" s="210" t="s">
-        <v>188</v>
-      </c>
-      <c r="H140" s="211"/>
-      <c r="I140" s="205" t="n">
+      <c r="G140" s="208" t="s">
+        <v>186</v>
+      </c>
+      <c r="H140" s="209"/>
+      <c r="I140" s="203" t="n">
         <f aca="false">+K88</f>
         <v>951.6192</v>
       </c>
-      <c r="J140" s="208" t="s">
-        <v>189</v>
-      </c>
-      <c r="K140" s="208"/>
-      <c r="L140" s="207" t="n">
+      <c r="J140" s="206" t="s">
+        <v>187</v>
+      </c>
+      <c r="K140" s="206"/>
+      <c r="L140" s="205" t="n">
         <f aca="false">Flujos!G39*Flujos!H39</f>
         <v>-951.6192</v>
       </c>
-      <c r="M140" s="229"/>
-      <c r="N140" s="230"/>
-      <c r="O140" s="231"/>
-      <c r="P140" s="207"/>
+      <c r="M140" s="228"/>
+      <c r="N140" s="229"/>
+      <c r="O140" s="230"/>
+      <c r="P140" s="205"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G141" s="210" t="s">
-        <v>190</v>
-      </c>
-      <c r="H141" s="211"/>
-      <c r="I141" s="205" t="n">
+      <c r="G141" s="208" t="s">
+        <v>188</v>
+      </c>
+      <c r="H141" s="209"/>
+      <c r="I141" s="203" t="n">
         <f aca="false">+L92</f>
         <v>-951.6192</v>
       </c>
-      <c r="J141" s="208" t="s">
-        <v>191</v>
-      </c>
-      <c r="K141" s="208"/>
-      <c r="L141" s="207" t="n">
+      <c r="J141" s="206" t="s">
+        <v>189</v>
+      </c>
+      <c r="K141" s="206"/>
+      <c r="L141" s="205" t="n">
         <f aca="false">Flujos!G69*Flujos!H69</f>
         <v>1152.2385</v>
       </c>
-      <c r="M141" s="208"/>
-      <c r="N141" s="208"/>
-      <c r="O141" s="208"/>
-      <c r="P141" s="207"/>
+      <c r="M141" s="206"/>
+      <c r="N141" s="206"/>
+      <c r="O141" s="206"/>
+      <c r="P141" s="205"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G142" s="209" t="s">
-        <v>192</v>
-      </c>
-      <c r="H142" s="209"/>
-      <c r="I142" s="205" t="n">
+      <c r="G142" s="207" t="s">
+        <v>190</v>
+      </c>
+      <c r="H142" s="207"/>
+      <c r="I142" s="203" t="n">
         <f aca="false">K84</f>
         <v>3202.0646</v>
       </c>
-      <c r="M142" s="208"/>
-      <c r="N142" s="208"/>
-      <c r="O142" s="208"/>
-      <c r="P142" s="207"/>
+      <c r="M142" s="206"/>
+      <c r="N142" s="206"/>
+      <c r="O142" s="206"/>
+      <c r="P142" s="205"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G143" s="209" t="s">
-        <v>206</v>
-      </c>
-      <c r="H143" s="209"/>
-      <c r="I143" s="205" t="n">
+      <c r="G143" s="207" t="s">
+        <v>204</v>
+      </c>
+      <c r="H143" s="207"/>
+      <c r="I143" s="203" t="n">
         <f aca="false">Flujos!G59*Flujos!H59</f>
         <v>0</v>
       </c>
-      <c r="J143" s="208"/>
-      <c r="K143" s="208"/>
-      <c r="L143" s="207"/>
-      <c r="M143" s="232"/>
-      <c r="N143" s="232"/>
-      <c r="O143" s="232"/>
-      <c r="P143" s="207"/>
+      <c r="J143" s="206"/>
+      <c r="K143" s="206"/>
+      <c r="L143" s="205"/>
+      <c r="M143" s="231"/>
+      <c r="N143" s="231"/>
+      <c r="O143" s="231"/>
+      <c r="P143" s="205"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G144" s="209" t="s">
-        <v>207</v>
-      </c>
-      <c r="H144" s="209"/>
-      <c r="I144" s="205" t="n">
+      <c r="G144" s="207" t="s">
+        <v>205</v>
+      </c>
+      <c r="H144" s="207"/>
+      <c r="I144" s="203" t="n">
         <f aca="false">Flujos!G60*Flujos!H60</f>
         <v>1331.2026</v>
       </c>
-      <c r="J144" s="208"/>
-      <c r="K144" s="208"/>
-      <c r="L144" s="207"/>
-      <c r="M144" s="232"/>
-      <c r="N144" s="232"/>
-      <c r="O144" s="232"/>
-      <c r="P144" s="207"/>
+      <c r="J144" s="206"/>
+      <c r="K144" s="206"/>
+      <c r="L144" s="205"/>
+      <c r="M144" s="231"/>
+      <c r="N144" s="231"/>
+      <c r="O144" s="231"/>
+      <c r="P144" s="205"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G145" s="209" t="s">
-        <v>208</v>
-      </c>
-      <c r="H145" s="209"/>
-      <c r="I145" s="205" t="n">
+      <c r="G145" s="207" t="s">
+        <v>206</v>
+      </c>
+      <c r="H145" s="207"/>
+      <c r="I145" s="203" t="n">
         <f aca="false">Flujos!G61*Flujos!H61</f>
         <v>0</v>
       </c>
-      <c r="J145" s="208"/>
-      <c r="K145" s="208"/>
-      <c r="L145" s="207"/>
-      <c r="M145" s="232"/>
-      <c r="N145" s="232"/>
-      <c r="O145" s="232"/>
-      <c r="P145" s="207"/>
+      <c r="J145" s="206"/>
+      <c r="K145" s="206"/>
+      <c r="L145" s="205"/>
+      <c r="M145" s="231"/>
+      <c r="N145" s="231"/>
+      <c r="O145" s="231"/>
+      <c r="P145" s="205"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G146" s="209" t="s">
+      <c r="G146" s="207" t="s">
+        <v>194</v>
+      </c>
+      <c r="H146" s="207"/>
+      <c r="I146" s="203" t="n">
+        <f aca="false">Flujos!G62*Flujos!H62</f>
+        <v>0</v>
+      </c>
+      <c r="J146" s="206"/>
+      <c r="K146" s="206"/>
+      <c r="L146" s="205"/>
+      <c r="M146" s="231"/>
+      <c r="N146" s="231"/>
+      <c r="O146" s="231"/>
+      <c r="P146" s="205"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G147" s="207" t="s">
+        <v>195</v>
+      </c>
+      <c r="H147" s="207"/>
+      <c r="I147" s="203" t="n">
+        <f aca="false">Flujos!G66*Flujos!H66</f>
+        <v>0</v>
+      </c>
+      <c r="J147" s="206"/>
+      <c r="K147" s="206"/>
+      <c r="L147" s="205"/>
+      <c r="M147" s="206"/>
+      <c r="N147" s="206"/>
+      <c r="O147" s="206"/>
+      <c r="P147" s="205"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G148" s="208" t="s">
         <v>196</v>
       </c>
-      <c r="H146" s="209"/>
-      <c r="I146" s="205" t="n">
-        <f aca="false">Flujos!G62*Flujos!H62</f>
-        <v>0</v>
-      </c>
-      <c r="J146" s="208"/>
-      <c r="K146" s="208"/>
-      <c r="L146" s="207"/>
-      <c r="M146" s="232"/>
-      <c r="N146" s="232"/>
-      <c r="O146" s="232"/>
-      <c r="P146" s="207"/>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G147" s="209" t="s">
+      <c r="H148" s="209"/>
+      <c r="I148" s="203" t="n">
+        <f aca="false">Flujos!G67*Flujos!H67</f>
+        <v>0</v>
+      </c>
+      <c r="J148" s="206"/>
+      <c r="K148" s="206"/>
+      <c r="L148" s="205"/>
+      <c r="M148" s="206"/>
+      <c r="N148" s="206"/>
+      <c r="O148" s="206"/>
+      <c r="P148" s="205"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G149" s="208" t="s">
         <v>197</v>
       </c>
-      <c r="H147" s="209"/>
-      <c r="I147" s="205" t="n">
-        <f aca="false">Flujos!G66*Flujos!H66</f>
-        <v>0</v>
-      </c>
-      <c r="J147" s="208"/>
-      <c r="K147" s="208"/>
-      <c r="L147" s="207"/>
-      <c r="M147" s="208"/>
-      <c r="N147" s="208"/>
-      <c r="O147" s="208"/>
-      <c r="P147" s="207"/>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G148" s="210" t="s">
-        <v>198</v>
-      </c>
-      <c r="H148" s="211"/>
-      <c r="I148" s="205" t="n">
-        <f aca="false">Flujos!G67*Flujos!H67</f>
-        <v>0</v>
-      </c>
-      <c r="J148" s="208"/>
-      <c r="K148" s="208"/>
-      <c r="L148" s="207"/>
-      <c r="M148" s="208"/>
-      <c r="N148" s="208"/>
-      <c r="O148" s="208"/>
-      <c r="P148" s="207"/>
-    </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G149" s="210" t="s">
-        <v>199</v>
-      </c>
-      <c r="H149" s="211"/>
-      <c r="I149" s="205" t="n">
+      <c r="H149" s="209"/>
+      <c r="I149" s="203" t="n">
         <f aca="false">Flujos!G70*Flujos!H70</f>
         <v>205.9176</v>
       </c>
-      <c r="J149" s="208"/>
-      <c r="K149" s="208"/>
-      <c r="L149" s="207"/>
-      <c r="M149" s="208"/>
-      <c r="N149" s="208"/>
-      <c r="O149" s="208"/>
-      <c r="P149" s="207"/>
+      <c r="J149" s="206"/>
+      <c r="K149" s="206"/>
+      <c r="L149" s="205"/>
+      <c r="M149" s="206"/>
+      <c r="N149" s="206"/>
+      <c r="O149" s="206"/>
+      <c r="P149" s="205"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G150" s="210" t="s">
+      <c r="G150" s="208" t="s">
+        <v>197</v>
+      </c>
+      <c r="H150" s="209"/>
+      <c r="I150" s="203" t="n">
+        <f aca="false">Flujos!G72*Flujos!H72</f>
+        <v>0</v>
+      </c>
+      <c r="J150" s="206"/>
+      <c r="K150" s="206"/>
+      <c r="L150" s="205"/>
+      <c r="M150" s="206"/>
+      <c r="N150" s="206"/>
+      <c r="O150" s="206"/>
+      <c r="P150" s="205"/>
+    </row>
+    <row r="151" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G151" s="213" t="s">
         <v>199</v>
       </c>
-      <c r="H150" s="211"/>
-      <c r="I150" s="205" t="n">
-        <f aca="false">Flujos!G72*Flujos!H72</f>
-        <v>0</v>
-      </c>
-      <c r="J150" s="208"/>
-      <c r="K150" s="208"/>
-      <c r="L150" s="207"/>
-      <c r="M150" s="208"/>
-      <c r="N150" s="208"/>
-      <c r="O150" s="208"/>
-      <c r="P150" s="207"/>
-    </row>
-    <row r="151" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G151" s="214" t="s">
-        <v>201</v>
-      </c>
-      <c r="H151" s="214"/>
-      <c r="I151" s="215" t="n">
+      <c r="H151" s="213"/>
+      <c r="I151" s="214" t="n">
         <f aca="false">+SUM(I128:I150)</f>
         <v>59602.6644799715</v>
       </c>
-      <c r="J151" s="216" t="s">
-        <v>202</v>
-      </c>
-      <c r="K151" s="216"/>
-      <c r="L151" s="217" t="n">
+      <c r="J151" s="215" t="s">
+        <v>200</v>
+      </c>
+      <c r="K151" s="215"/>
+      <c r="L151" s="216" t="n">
         <f aca="false">+SUM(L128:L141)</f>
         <v>45350.9504846625</v>
       </c>
-      <c r="M151" s="216" t="s">
-        <v>203</v>
-      </c>
-      <c r="N151" s="216"/>
-      <c r="O151" s="216"/>
-      <c r="P151" s="215" t="n">
+      <c r="M151" s="215" t="s">
+        <v>201</v>
+      </c>
+      <c r="N151" s="215"/>
+      <c r="O151" s="215"/>
+      <c r="P151" s="214" t="n">
         <f aca="false">+SUM(P128:P141)</f>
         <v>16489.0254945414</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G152" s="218"/>
-      <c r="H152" s="218"/>
-      <c r="I152" s="218"/>
-      <c r="J152" s="218"/>
-      <c r="K152" s="218"/>
-      <c r="L152" s="218"/>
-      <c r="M152" s="218"/>
-      <c r="N152" s="218"/>
-      <c r="O152" s="218"/>
-      <c r="P152" s="218"/>
+      <c r="G152" s="217"/>
+      <c r="H152" s="217"/>
+      <c r="I152" s="217"/>
+      <c r="J152" s="217"/>
+      <c r="K152" s="217"/>
+      <c r="L152" s="217"/>
+      <c r="M152" s="217"/>
+      <c r="N152" s="217"/>
+      <c r="O152" s="217"/>
+      <c r="P152" s="217"/>
     </row>
     <row r="153" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G153" s="218"/>
-      <c r="J153" s="218"/>
-      <c r="K153" s="218"/>
-      <c r="L153" s="219" t="s">
-        <v>204</v>
-      </c>
-      <c r="M153" s="220"/>
-      <c r="N153" s="221"/>
-      <c r="O153" s="220"/>
-      <c r="P153" s="222" t="n">
+      <c r="G153" s="217"/>
+      <c r="J153" s="217"/>
+      <c r="K153" s="217"/>
+      <c r="L153" s="218" t="s">
+        <v>202</v>
+      </c>
+      <c r="M153" s="219"/>
+      <c r="N153" s="220"/>
+      <c r="O153" s="219"/>
+      <c r="P153" s="221" t="n">
         <f aca="false">+I151-L151-P151</f>
         <v>-2237.3114992324</v>
       </c>
@@ -22938,7 +22872,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{9765DEB9-5318-4EF1-B17D-EE7126D4AC71}">
+          <x14:cfRule type="iconSet" priority="2" id="{DEA06030-94A0-4362-A615-3D33BDF55EC9}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22957,7 +22891,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{78E998CA-943B-45EE-B7AA-3D15A8FFC3C0}">
+          <x14:cfRule type="iconSet" priority="3" id="{E0901022-D3A0-4D1B-8E27-1BC67781AE27}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22976,7 +22910,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{E8E1A4B4-7448-4BF0-8DBC-711E99FF7125}">
+          <x14:cfRule type="iconSet" priority="4" id="{60331839-B5AB-4820-B07C-9D576845B9E4}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22995,7 +22929,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{49EE5B24-A2A0-4ED3-98A9-EC65FD27EA68}">
+          <x14:cfRule type="iconSet" priority="5" id="{9884F2BC-B0A2-40F1-8254-48932FE33EAB}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23014,7 +22948,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{CFFB3415-86D2-4D35-8649-B47FDFCB008A}">
+          <x14:cfRule type="iconSet" priority="6" id="{D6C2A2F2-486A-47E1-8A51-53754034B057}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23033,7 +22967,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{4DA4D58B-A498-4525-9DA9-40F277559C6E}">
+          <x14:cfRule type="iconSet" priority="7" id="{A145CCF1-58F5-40F1-875C-77E43793A148}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23052,7 +22986,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{35F667E1-1990-49CE-9934-25FB7CF739E7}">
+          <x14:cfRule type="iconSet" priority="8" id="{B360733D-53C4-4F3B-85FF-30EE36ABDD4D}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23071,7 +23005,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{50BE32B5-F4DF-4A2E-A63F-352194446570}">
+          <x14:cfRule type="iconSet" priority="9" id="{AC5635D1-8A1E-4C54-91D1-9457BA824275}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23090,7 +23024,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{1AAD1CDD-D179-4DB1-AE93-601690BF9097}">
+          <x14:cfRule type="iconSet" priority="10" id="{71A4E9A8-ACED-4FA1-955A-AABBF712D958}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23109,7 +23043,7 @@
           <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{A5D5857C-C587-42B7-827B-F1C2CFF5D4C8}">
+          <x14:cfRule type="iconSet" priority="11" id="{8BE96B6C-318E-47D2-8876-C82A506763E5}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23128,7 +23062,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{9DDF5DF0-34D9-48F7-B0C1-21F8125D4DE0}">
+          <x14:cfRule type="iconSet" priority="12" id="{B935D76A-4E19-412A-97A0-CACF74174BCD}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23147,7 +23081,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{AB949B10-BD10-4D96-8159-894D76E04467}">
+          <x14:cfRule type="iconSet" priority="13" id="{3FCC9033-AB28-41AF-80E0-BCD7F7DBB16D}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23166,7 +23100,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{9F1E5610-4D4E-425A-8C40-81A654393CD0}">
+          <x14:cfRule type="iconSet" priority="14" id="{7B23F824-6F4C-40B8-91EE-89212C83B0C8}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23185,7 +23119,7 @@
           <xm:sqref>N88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{3B3162F3-F0B0-4C18-AF9E-471F5E2C7815}">
+          <x14:cfRule type="iconSet" priority="15" id="{29BAE4A0-C24A-4899-B21F-CC8678E8A12D}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -13186,7 +13186,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="27" t="n">
-        <f aca="false">N27/(1-'Datos Extra'!D42)</f>
+        <f aca="false">N27/(1-'Datos Extra'!D43)</f>
         <v>0</v>
       </c>
       <c r="P27" s="28" t="n">
@@ -22872,7 +22872,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{DEA06030-94A0-4362-A615-3D33BDF55EC9}">
+          <x14:cfRule type="iconSet" priority="2" id="{75A4E7E5-BC19-41DA-A396-689DDE9238EC}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22891,7 +22891,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{E0901022-D3A0-4D1B-8E27-1BC67781AE27}">
+          <x14:cfRule type="iconSet" priority="3" id="{69753F9F-6342-4624-A7A3-4E1418386971}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22910,7 +22910,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{60331839-B5AB-4820-B07C-9D576845B9E4}">
+          <x14:cfRule type="iconSet" priority="4" id="{654158B0-25B3-4252-9E3A-994D4DE6A2A7}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22929,7 +22929,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{9884F2BC-B0A2-40F1-8254-48932FE33EAB}">
+          <x14:cfRule type="iconSet" priority="5" id="{C1DFF443-6D64-4B98-AB9A-20138EF24EE1}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22948,7 +22948,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{D6C2A2F2-486A-47E1-8A51-53754034B057}">
+          <x14:cfRule type="iconSet" priority="6" id="{5A3D484B-691E-47A0-8AEF-2775D5BA3BB8}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22967,7 +22967,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{A145CCF1-58F5-40F1-875C-77E43793A148}">
+          <x14:cfRule type="iconSet" priority="7" id="{F1D97B25-6583-4FD0-871B-5B95DD86BBE4}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22986,7 +22986,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{B360733D-53C4-4F3B-85FF-30EE36ABDD4D}">
+          <x14:cfRule type="iconSet" priority="8" id="{C7B16B25-825F-40B6-9741-99A13B11C7D4}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23005,7 +23005,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{AC5635D1-8A1E-4C54-91D1-9457BA824275}">
+          <x14:cfRule type="iconSet" priority="9" id="{3E852FC3-3526-49CF-B0D2-5061AEB8AA27}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23024,7 +23024,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{71A4E9A8-ACED-4FA1-955A-AABBF712D958}">
+          <x14:cfRule type="iconSet" priority="10" id="{FF97E457-CC2E-4056-951D-3F677C8BD189}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23043,7 +23043,7 @@
           <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{8BE96B6C-318E-47D2-8876-C82A506763E5}">
+          <x14:cfRule type="iconSet" priority="11" id="{A1D945F8-5C2B-4E17-9D27-B056466C80A1}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23062,7 +23062,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{B935D76A-4E19-412A-97A0-CACF74174BCD}">
+          <x14:cfRule type="iconSet" priority="12" id="{7826A72F-347C-493A-A9CC-EA9E11D1ADC7}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23081,7 +23081,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{3FCC9033-AB28-41AF-80E0-BCD7F7DBB16D}">
+          <x14:cfRule type="iconSet" priority="13" id="{51AF9F57-2A61-4DCC-8030-3743C1535D29}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23100,7 +23100,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{7B23F824-6F4C-40B8-91EE-89212C83B0C8}">
+          <x14:cfRule type="iconSet" priority="14" id="{6A6487E6-CF35-4400-9EA7-B4D13FACC05B}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23119,7 +23119,7 @@
           <xm:sqref>N88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{29BAE4A0-C24A-4899-B21F-CC8678E8A12D}">
+          <x14:cfRule type="iconSet" priority="15" id="{DB484598-2BB9-4A20-808D-E543F4D8D55D}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>

--- a/public/Export/Exportar_Elqui_Elqui.xlsx
+++ b/public/Export/Exportar_Elqui_Elqui.xlsx
@@ -13152,7 +13152,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="31" t="n">
-        <f aca="false">N26/(1-'Datos Extra'!D41)</f>
+        <f aca="false">N26/(1-'Datos Extra'!D42)</f>
         <v>0</v>
       </c>
       <c r="P26" s="63" t="n">
@@ -22872,7 +22872,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{75A4E7E5-BC19-41DA-A396-689DDE9238EC}">
+          <x14:cfRule type="iconSet" priority="2" id="{C02FC114-F022-4FD3-B8C0-69F351E21551}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22891,7 +22891,7 @@
           <xm:sqref>E16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{69753F9F-6342-4624-A7A3-4E1418386971}">
+          <x14:cfRule type="iconSet" priority="3" id="{37A06045-6E8D-4EC0-8878-56AAE1F0F384}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22910,7 +22910,7 @@
           <xm:sqref>F29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{654158B0-25B3-4252-9E3A-994D4DE6A2A7}">
+          <x14:cfRule type="iconSet" priority="4" id="{F180EBA9-95BA-4E43-9E1D-D02AC870ACC0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22929,7 +22929,7 @@
           <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{C1DFF443-6D64-4B98-AB9A-20138EF24EE1}">
+          <x14:cfRule type="iconSet" priority="5" id="{22EA62E8-AAD7-4018-AD34-2E6A924A3D1A}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22948,7 +22948,7 @@
           <xm:sqref>F48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{5A3D484B-691E-47A0-8AEF-2775D5BA3BB8}">
+          <x14:cfRule type="iconSet" priority="6" id="{3E62663E-CACC-4791-85D0-8A4D2C53BC90}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22967,7 +22967,7 @@
           <xm:sqref>J14</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="7" id="{F1D97B25-6583-4FD0-871B-5B95DD86BBE4}">
+          <x14:cfRule type="iconSet" priority="7" id="{62307F58-80E6-43F1-9B4F-AF6C8D7AA4B5}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -22986,7 +22986,7 @@
           <xm:sqref>J75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="8" id="{C7B16B25-825F-40B6-9741-99A13B11C7D4}">
+          <x14:cfRule type="iconSet" priority="8" id="{CF3525BE-4666-4B6D-A717-6A3C9131FBAC}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23005,7 +23005,7 @@
           <xm:sqref>K39</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="9" id="{3E852FC3-3526-49CF-B0D2-5061AEB8AA27}">
+          <x14:cfRule type="iconSet" priority="9" id="{28B4F43E-B4F0-40AB-A0A3-94339D6042BF}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23024,7 +23024,7 @@
           <xm:sqref>L34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="10" id="{FF97E457-CC2E-4056-951D-3F677C8BD189}">
+          <x14:cfRule type="iconSet" priority="10" id="{33957A3A-9066-4163-B7F7-D4A088E0751B}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23043,7 +23043,7 @@
           <xm:sqref>L151</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{A1D945F8-5C2B-4E17-9D27-B056466C80A1}">
+          <x14:cfRule type="iconSet" priority="11" id="{ADC577FB-2848-4C76-BB68-2459DA6B67B0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23062,7 +23062,7 @@
           <xm:sqref>N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{7826A72F-347C-493A-A9CC-EA9E11D1ADC7}">
+          <x14:cfRule type="iconSet" priority="12" id="{A4FFDFC9-5071-411D-B89A-59EF8A6729F9}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23081,7 +23081,7 @@
           <xm:sqref>N67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="13" id="{51AF9F57-2A61-4DCC-8030-3743C1535D29}">
+          <x14:cfRule type="iconSet" priority="13" id="{E22657CC-B1AC-4D59-ACAE-D894433CCCFA}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23100,7 +23100,7 @@
           <xm:sqref>N75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="14" id="{6A6487E6-CF35-4400-9EA7-B4D13FACC05B}">
+          <x14:cfRule type="iconSet" priority="14" id="{AFA673DD-A1B8-4DAA-9ECE-DD9B50723FF0}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -23119,7 +23119,7 @@
           <xm:sqref>N88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="15" id="{DB484598-2BB9-4A20-808D-E543F4D8D55D}">
+          <x14:cfRule type="iconSet" priority="15" id="{46CA96DE-619C-4A20-A194-9387106C5223}">
             <x14:iconSet iconSet="3Arrows" custom="1" reverse="0" showValue="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
